--- a/资源录入表新.xlsx
+++ b/资源录入表新.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="206">
   <si>
     <t>剧名</t>
   </si>
@@ -74,7 +74,7 @@
     <t>1080P</t>
   </si>
   <si>
-    <t>更19集</t>
+    <t>更21集</t>
   </si>
   <si>
     <t>更新中</t>
@@ -606,6 +606,450 @@
   </si>
   <si>
     <t xml:space="preserve">链接: https://pan.baidu.com/s/1dpGGDyDQ1rMhPp7LVjQNwg 提取码: a372 </t>
+  </si>
+  <si>
+    <t>悬案</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>剧情</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>悬疑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>犯罪</t>
+    </r>
+  </si>
+  <si>
+    <t>17集全</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>王传君</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>江奇霖</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>杨烁</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>郎月婷</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>岳云鹏</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1mjCjUmDR_M1wq9SR51hvMQ 提取码: seqj </t>
+  </si>
+  <si>
+    <t>宿敌恋人</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>剧情</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>爱情</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>同性</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>普洛伊湘普</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>素帕莎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>芭莉雅皮</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>余</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/17IfE4v3SrPF6Y18CdlHkaA 提取码: kxjd </t>
+  </si>
+  <si>
+    <t>爱情没有神话</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>剧情</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>爱情</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>唐嫣</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>赵又廷</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>杨采钰</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>冯绍峰</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> /</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/11-pn6zJgsVQp3MufmiSEnA 提取码: y9i6 </t>
   </si>
 </sst>
 </file>
@@ -618,13 +1062,30 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9.75"/>
+      <color rgb="FF111111"/>
+      <name val="Helvetica"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -770,13 +1231,34 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Helvetica"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Helvetica"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -965,7 +1447,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -1009,6 +1491,19 @@
       <top style="thin">
         <color auto="1"/>
       </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -1132,137 +1627,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1278,6 +1773,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1285,6 +1783,24 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1820,12 +2336,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O49"/>
+  <dimension ref="A1:O65"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="31.125" style="2" customWidth="1"/>
-    <col min="2" max="7" width="9" style="1"/>
-    <col min="8" max="8" width="20.5" style="1" customWidth="1"/>
+    <col min="1" max="1" width="17.625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="9" style="1"/>
+    <col min="3" max="3" width="18.625" style="1" customWidth="1"/>
+    <col min="4" max="7" width="9" style="1"/>
+    <col min="8" max="8" width="31.375" style="1" customWidth="1"/>
     <col min="9" max="9" width="74.25" style="1" customWidth="1"/>
     <col min="10" max="15" width="9" style="1"/>
   </cols>
@@ -1882,7 +2400,7 @@
       <c r="D2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F2" s="4" t="s">
@@ -2548,8 +3066,8 @@
       <c r="D20" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E20" s="4">
-        <v>5</v>
+      <c r="E20" s="5">
+        <v>6</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>16</v>
@@ -2641,38 +3159,38 @@
       <c r="O22" s="4"/>
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:15">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="D23" s="6" t="s">
+      <c r="D23" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E23" s="6">
+      <c r="E23" s="7">
         <v>4</v>
       </c>
-      <c r="F23" s="6" t="s">
+      <c r="F23" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="G23" s="6">
+      <c r="G23" s="7">
         <v>2025</v>
       </c>
-      <c r="H23" s="6"/>
+      <c r="H23" s="7"/>
       <c r="I23" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="J23" s="6"/>
-      <c r="K23" s="6"/>
-      <c r="L23" s="6" t="s">
+      <c r="J23" s="7"/>
+      <c r="K23" s="7"/>
+      <c r="L23" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="M23" s="6"/>
-      <c r="N23" s="6"/>
+      <c r="M23" s="7"/>
+      <c r="N23" s="7"/>
       <c r="O23" s="4"/>
     </row>
     <row r="24" ht="25" customHeight="1" spans="1:15">
@@ -2688,8 +3206,8 @@
       <c r="D24" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E24" s="4">
-        <v>11</v>
+      <c r="E24" s="5">
+        <v>12</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>16</v>
@@ -2710,7 +3228,7 @@
       </c>
       <c r="M24" s="4"/>
       <c r="N24" s="4"/>
-      <c r="O24" s="7"/>
+      <c r="O24" s="8"/>
     </row>
     <row r="25" ht="25" customHeight="1" spans="1:15">
       <c r="A25" s="3" t="s">
@@ -2745,7 +3263,7 @@
       </c>
       <c r="M25" s="4"/>
       <c r="N25" s="4"/>
-      <c r="O25" s="7"/>
+      <c r="O25" s="8"/>
     </row>
     <row r="26" ht="25" customHeight="1" spans="1:15">
       <c r="A26" s="3" t="s">
@@ -2780,7 +3298,7 @@
       </c>
       <c r="M26" s="4"/>
       <c r="N26" s="4"/>
-      <c r="O26" s="7"/>
+      <c r="O26" s="8"/>
     </row>
     <row r="27" ht="25" customHeight="1" spans="1:15">
       <c r="A27" s="3" t="s">
@@ -2815,7 +3333,7 @@
       </c>
       <c r="M27" s="4"/>
       <c r="N27" s="4"/>
-      <c r="O27" s="7"/>
+      <c r="O27" s="8"/>
     </row>
     <row r="28" ht="25" customHeight="1" spans="1:15">
       <c r="A28" s="3" t="s">
@@ -2850,7 +3368,7 @@
       </c>
       <c r="M28" s="4"/>
       <c r="N28" s="4"/>
-      <c r="O28" s="7"/>
+      <c r="O28" s="8"/>
     </row>
     <row r="29" ht="25" customHeight="1" spans="1:15">
       <c r="A29" s="3" t="s">
@@ -2885,7 +3403,7 @@
       </c>
       <c r="M29" s="4"/>
       <c r="N29" s="4"/>
-      <c r="O29" s="7"/>
+      <c r="O29" s="8"/>
     </row>
     <row r="30" ht="25" customHeight="1" spans="1:15">
       <c r="A30" s="3" t="s">
@@ -2922,7 +3440,7 @@
       </c>
       <c r="M30" s="4"/>
       <c r="N30" s="4"/>
-      <c r="O30" s="7"/>
+      <c r="O30" s="8"/>
     </row>
     <row r="31" ht="25" customHeight="1" spans="1:15">
       <c r="A31" s="3" t="s">
@@ -2945,7 +3463,7 @@
       <c r="L31" s="4"/>
       <c r="M31" s="4"/>
       <c r="N31" s="4"/>
-      <c r="O31" s="7"/>
+      <c r="O31" s="8"/>
     </row>
     <row r="32" ht="25" customHeight="1" spans="1:15">
       <c r="A32" s="3" t="s">
@@ -2954,8 +3472,8 @@
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
       <c r="D32" s="4"/>
-      <c r="E32" s="4">
-        <v>20</v>
+      <c r="E32" s="5">
+        <v>14</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>16</v>
@@ -2970,7 +3488,7 @@
       <c r="L32" s="4"/>
       <c r="M32" s="4"/>
       <c r="N32" s="4"/>
-      <c r="O32" s="7"/>
+      <c r="O32" s="8"/>
     </row>
     <row r="33" ht="25" customHeight="1" spans="1:15">
       <c r="A33" s="3" t="s">
@@ -2993,7 +3511,7 @@
       <c r="L33" s="4"/>
       <c r="M33" s="4"/>
       <c r="N33" s="4"/>
-      <c r="O33" s="7"/>
+      <c r="O33" s="8"/>
     </row>
     <row r="34" ht="25" customHeight="1" spans="1:15">
       <c r="A34" s="3" t="s">
@@ -3016,7 +3534,7 @@
       <c r="L34" s="4"/>
       <c r="M34" s="4"/>
       <c r="N34" s="4"/>
-      <c r="O34" s="7"/>
+      <c r="O34" s="8"/>
     </row>
     <row r="35" ht="25" customHeight="1" spans="1:15">
       <c r="A35" s="3" t="s">
@@ -3039,7 +3557,7 @@
       <c r="L35" s="4"/>
       <c r="M35" s="4"/>
       <c r="N35" s="4"/>
-      <c r="O35" s="7"/>
+      <c r="O35" s="8"/>
     </row>
     <row r="36" ht="25" customHeight="1" spans="1:15">
       <c r="A36" s="3" t="s">
@@ -3062,7 +3580,7 @@
       <c r="L36" s="4"/>
       <c r="M36" s="4"/>
       <c r="N36" s="4"/>
-      <c r="O36" s="7"/>
+      <c r="O36" s="8"/>
     </row>
     <row r="37" ht="25" customHeight="1" spans="1:15">
       <c r="A37" s="3" t="s">
@@ -3085,7 +3603,7 @@
       <c r="L37" s="4"/>
       <c r="M37" s="4"/>
       <c r="N37" s="4"/>
-      <c r="O37" s="7"/>
+      <c r="O37" s="8"/>
     </row>
     <row r="38" ht="25" customHeight="1" spans="1:15">
       <c r="A38" s="3" t="s">
@@ -3108,7 +3626,7 @@
       <c r="L38" s="4"/>
       <c r="M38" s="4"/>
       <c r="N38" s="4"/>
-      <c r="O38" s="7"/>
+      <c r="O38" s="8"/>
     </row>
     <row r="39" ht="25" customHeight="1" spans="1:15">
       <c r="A39" s="3" t="s">
@@ -3131,7 +3649,7 @@
       <c r="L39" s="4"/>
       <c r="M39" s="4"/>
       <c r="N39" s="4"/>
-      <c r="O39" s="7"/>
+      <c r="O39" s="8"/>
     </row>
     <row r="40" ht="25" customHeight="1" spans="1:15">
       <c r="A40" s="3" t="s">
@@ -3154,7 +3672,7 @@
       <c r="L40" s="4"/>
       <c r="M40" s="4"/>
       <c r="N40" s="4"/>
-      <c r="O40" s="7"/>
+      <c r="O40" s="8"/>
     </row>
     <row r="41" ht="25" customHeight="1" spans="1:15">
       <c r="A41" s="3" t="s">
@@ -3177,7 +3695,7 @@
       <c r="L41" s="4"/>
       <c r="M41" s="4"/>
       <c r="N41" s="4"/>
-      <c r="O41" s="7"/>
+      <c r="O41" s="8"/>
     </row>
     <row r="42" ht="25" customHeight="1" spans="1:15">
       <c r="A42" s="3" t="s">
@@ -3200,28 +3718,28 @@
       <c r="L42" s="4"/>
       <c r="M42" s="4"/>
       <c r="N42" s="4"/>
-      <c r="O42" s="7"/>
+      <c r="O42" s="8"/>
     </row>
     <row r="43" ht="25" customHeight="1" spans="1:15">
-      <c r="A43" s="3" t="s">
+      <c r="A43" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="B43" s="4"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="4"/>
-      <c r="E43" s="4"/>
-      <c r="F43" s="4"/>
-      <c r="G43" s="4"/>
-      <c r="H43" s="4"/>
+      <c r="B43" s="7"/>
+      <c r="C43" s="7"/>
+      <c r="D43" s="7"/>
+      <c r="E43" s="7"/>
+      <c r="F43" s="7"/>
+      <c r="G43" s="7"/>
+      <c r="H43" s="7"/>
       <c r="I43" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="J43" s="4"/>
+      <c r="J43" s="7"/>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
       <c r="M43" s="4"/>
       <c r="N43" s="4"/>
-      <c r="O43" s="7"/>
+      <c r="O43" s="8"/>
     </row>
     <row r="44" ht="25" customHeight="1" spans="1:15">
       <c r="A44" s="3" t="s">
@@ -3234,7 +3752,7 @@
       <c r="F44" s="4"/>
       <c r="G44" s="4"/>
       <c r="H44" s="4"/>
-      <c r="I44" s="1" t="s">
+      <c r="I44" s="9" t="s">
         <v>182</v>
       </c>
       <c r="J44" s="4"/>
@@ -3242,7 +3760,7 @@
       <c r="L44" s="4"/>
       <c r="M44" s="4"/>
       <c r="N44" s="4"/>
-      <c r="O44" s="7"/>
+      <c r="O44" s="8"/>
     </row>
     <row r="45" ht="25" customHeight="1" spans="1:15">
       <c r="A45" s="3" t="s">
@@ -3255,7 +3773,7 @@
       <c r="F45" s="4"/>
       <c r="G45" s="4"/>
       <c r="H45" s="4"/>
-      <c r="I45" s="1" t="s">
+      <c r="I45" s="9" t="s">
         <v>184</v>
       </c>
       <c r="J45" s="4"/>
@@ -3263,7 +3781,7 @@
       <c r="L45" s="4"/>
       <c r="M45" s="4"/>
       <c r="N45" s="4"/>
-      <c r="O45" s="7"/>
+      <c r="O45" s="8"/>
     </row>
     <row r="46" ht="25" customHeight="1" spans="1:15">
       <c r="A46" s="3" t="s">
@@ -3276,7 +3794,7 @@
       <c r="F46" s="4"/>
       <c r="G46" s="4"/>
       <c r="H46" s="4"/>
-      <c r="I46" s="1" t="s">
+      <c r="I46" s="9" t="s">
         <v>186</v>
       </c>
       <c r="J46" s="4"/>
@@ -3284,7 +3802,7 @@
       <c r="L46" s="4"/>
       <c r="M46" s="4"/>
       <c r="N46" s="4"/>
-      <c r="O46" s="7"/>
+      <c r="O46" s="8"/>
     </row>
     <row r="47" ht="25" customHeight="1" spans="1:15">
       <c r="A47" s="3" t="s">
@@ -3297,7 +3815,7 @@
       <c r="F47" s="4"/>
       <c r="G47" s="4"/>
       <c r="H47" s="4"/>
-      <c r="I47" s="1" t="s">
+      <c r="I47" s="9" t="s">
         <v>188</v>
       </c>
       <c r="J47" s="4"/>
@@ -3305,7 +3823,7 @@
       <c r="L47" s="4"/>
       <c r="M47" s="4"/>
       <c r="N47" s="4"/>
-      <c r="O47" s="7"/>
+      <c r="O47" s="8"/>
     </row>
     <row r="48" ht="25" customHeight="1" spans="1:15">
       <c r="A48" s="3" t="s">
@@ -3326,7 +3844,7 @@
       <c r="L48" s="4"/>
       <c r="M48" s="4"/>
       <c r="N48" s="4"/>
-      <c r="O48" s="7"/>
+      <c r="O48" s="8"/>
     </row>
     <row r="49" ht="25" customHeight="1" spans="1:15">
       <c r="A49" s="3" t="s">
@@ -3339,7 +3857,7 @@
       <c r="F49" s="4"/>
       <c r="G49" s="4"/>
       <c r="H49" s="4"/>
-      <c r="I49" s="1" t="s">
+      <c r="I49" s="9" t="s">
         <v>192</v>
       </c>
       <c r="J49" s="4"/>
@@ -3347,9 +3865,317 @@
       <c r="L49" s="4"/>
       <c r="M49" s="4"/>
       <c r="N49" s="4"/>
-      <c r="O49" s="7"/>
+      <c r="O49" s="8"/>
+    </row>
+    <row r="50" ht="25" customHeight="1" spans="1:15">
+      <c r="A50" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="D50" s="4"/>
+      <c r="E50" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G50" s="4"/>
+      <c r="H50" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="I50" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="J50" s="4"/>
+      <c r="K50" s="4"/>
+      <c r="L50" s="4"/>
+      <c r="M50" s="4"/>
+      <c r="N50" s="4"/>
+      <c r="O50" s="8"/>
+    </row>
+    <row r="51" ht="25" customHeight="1" spans="1:15">
+      <c r="A51" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="D51" s="4"/>
+      <c r="E51" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G51" s="4"/>
+      <c r="H51" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="I51" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="J51" s="4"/>
+      <c r="K51" s="4"/>
+      <c r="L51" s="4"/>
+      <c r="M51" s="4"/>
+      <c r="N51" s="4"/>
+      <c r="O51" s="8"/>
+    </row>
+    <row r="52" ht="25" customHeight="1" spans="1:15">
+      <c r="A52" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C52" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="D52" s="4"/>
+      <c r="E52" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G52" s="4"/>
+      <c r="H52" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="I52" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="J52" s="4"/>
+      <c r="K52" s="4"/>
+      <c r="L52" s="4"/>
+      <c r="M52" s="4"/>
+      <c r="N52" s="4"/>
+      <c r="O52" s="8"/>
+    </row>
+    <row r="53" ht="25" customHeight="1" spans="1:15">
+      <c r="A53" s="3"/>
+      <c r="B53" s="4"/>
+      <c r="C53" s="4"/>
+      <c r="D53" s="4"/>
+      <c r="E53" s="4"/>
+      <c r="F53" s="4"/>
+      <c r="G53" s="4"/>
+      <c r="H53" s="4"/>
+      <c r="I53" s="9"/>
+      <c r="J53" s="4"/>
+      <c r="K53" s="4"/>
+      <c r="L53" s="4"/>
+      <c r="M53" s="4"/>
+      <c r="N53" s="4"/>
+      <c r="O53" s="8"/>
+    </row>
+    <row r="54" ht="25" customHeight="1" spans="1:15">
+      <c r="A54" s="3"/>
+      <c r="B54" s="4"/>
+      <c r="C54" s="4"/>
+      <c r="D54" s="4"/>
+      <c r="E54" s="4"/>
+      <c r="F54" s="4"/>
+      <c r="G54" s="4"/>
+      <c r="H54" s="4"/>
+      <c r="I54" s="9"/>
+      <c r="J54" s="4"/>
+      <c r="K54" s="4"/>
+      <c r="L54" s="4"/>
+      <c r="M54" s="4"/>
+      <c r="N54" s="4"/>
+      <c r="O54" s="8"/>
+    </row>
+    <row r="55" ht="25" customHeight="1" spans="1:15">
+      <c r="A55" s="3"/>
+      <c r="B55" s="4"/>
+      <c r="C55" s="4"/>
+      <c r="D55" s="4"/>
+      <c r="E55" s="4"/>
+      <c r="F55" s="4"/>
+      <c r="G55" s="4"/>
+      <c r="H55" s="4"/>
+      <c r="I55" s="9"/>
+      <c r="J55" s="4"/>
+      <c r="K55" s="4"/>
+      <c r="L55" s="4"/>
+      <c r="M55" s="4"/>
+      <c r="N55" s="4"/>
+      <c r="O55" s="8"/>
+    </row>
+    <row r="56" ht="25" customHeight="1" spans="1:15">
+      <c r="A56" s="3"/>
+      <c r="B56" s="4"/>
+      <c r="C56" s="4"/>
+      <c r="D56" s="4"/>
+      <c r="E56" s="4"/>
+      <c r="F56" s="4"/>
+      <c r="G56" s="4"/>
+      <c r="H56" s="4"/>
+      <c r="I56" s="9"/>
+      <c r="J56" s="4"/>
+      <c r="K56" s="4"/>
+      <c r="L56" s="4"/>
+      <c r="M56" s="4"/>
+      <c r="N56" s="4"/>
+      <c r="O56" s="8"/>
+    </row>
+    <row r="57" ht="25" customHeight="1" spans="1:15">
+      <c r="A57" s="13"/>
+      <c r="B57" s="14"/>
+      <c r="C57" s="14"/>
+      <c r="D57" s="14"/>
+      <c r="E57" s="14"/>
+      <c r="F57" s="14"/>
+      <c r="G57" s="14"/>
+      <c r="H57" s="14"/>
+      <c r="J57" s="14"/>
+      <c r="K57" s="4"/>
+      <c r="L57" s="4"/>
+      <c r="M57" s="4"/>
+      <c r="N57" s="4"/>
+      <c r="O57" s="8"/>
+    </row>
+    <row r="58" ht="25" customHeight="1" spans="1:15">
+      <c r="A58" s="3"/>
+      <c r="B58" s="4"/>
+      <c r="C58" s="4"/>
+      <c r="D58" s="4"/>
+      <c r="E58" s="4"/>
+      <c r="F58" s="4"/>
+      <c r="G58" s="4"/>
+      <c r="H58" s="4"/>
+      <c r="J58" s="4"/>
+      <c r="K58" s="4"/>
+      <c r="L58" s="4"/>
+      <c r="M58" s="4"/>
+      <c r="N58" s="4"/>
+      <c r="O58" s="8"/>
+    </row>
+    <row r="59" ht="25" customHeight="1" spans="1:15">
+      <c r="A59" s="3"/>
+      <c r="B59" s="4"/>
+      <c r="C59" s="4"/>
+      <c r="D59" s="4"/>
+      <c r="E59" s="4"/>
+      <c r="F59" s="4"/>
+      <c r="G59" s="4"/>
+      <c r="H59" s="4"/>
+      <c r="J59" s="4"/>
+      <c r="K59" s="4"/>
+      <c r="L59" s="4"/>
+      <c r="M59" s="4"/>
+      <c r="N59" s="4"/>
+      <c r="O59" s="8"/>
+    </row>
+    <row r="60" ht="25" customHeight="1" spans="1:15">
+      <c r="A60" s="3"/>
+      <c r="B60" s="4"/>
+      <c r="C60" s="4"/>
+      <c r="D60" s="4"/>
+      <c r="E60" s="4"/>
+      <c r="F60" s="4"/>
+      <c r="G60" s="4"/>
+      <c r="H60" s="4"/>
+      <c r="J60" s="4"/>
+      <c r="K60" s="4"/>
+      <c r="L60" s="4"/>
+      <c r="M60" s="4"/>
+      <c r="N60" s="4"/>
+      <c r="O60" s="8"/>
+    </row>
+    <row r="61" ht="25" customHeight="1" spans="1:15">
+      <c r="A61" s="3"/>
+      <c r="B61" s="4"/>
+      <c r="C61" s="4"/>
+      <c r="D61" s="4"/>
+      <c r="E61" s="4"/>
+      <c r="F61" s="4"/>
+      <c r="G61" s="4"/>
+      <c r="H61" s="4"/>
+      <c r="J61" s="4"/>
+      <c r="K61" s="4"/>
+      <c r="L61" s="4"/>
+      <c r="M61" s="4"/>
+      <c r="N61" s="4"/>
+      <c r="O61" s="8"/>
+    </row>
+    <row r="62" ht="25" customHeight="1" spans="1:15">
+      <c r="A62" s="3"/>
+      <c r="B62" s="4"/>
+      <c r="C62" s="4"/>
+      <c r="D62" s="4"/>
+      <c r="E62" s="4"/>
+      <c r="F62" s="4"/>
+      <c r="G62" s="4"/>
+      <c r="H62" s="4"/>
+      <c r="J62" s="4"/>
+      <c r="K62" s="4"/>
+      <c r="L62" s="4"/>
+      <c r="M62" s="4"/>
+      <c r="N62" s="4"/>
+      <c r="O62" s="8"/>
+    </row>
+    <row r="63" ht="25" customHeight="1" spans="1:15">
+      <c r="A63" s="3"/>
+      <c r="B63" s="4"/>
+      <c r="C63" s="4"/>
+      <c r="D63" s="4"/>
+      <c r="E63" s="4"/>
+      <c r="F63" s="4"/>
+      <c r="G63" s="4"/>
+      <c r="H63" s="4"/>
+      <c r="J63" s="4"/>
+      <c r="K63" s="4"/>
+      <c r="L63" s="4"/>
+      <c r="M63" s="4"/>
+      <c r="N63" s="4"/>
+      <c r="O63" s="8"/>
+    </row>
+    <row r="64" ht="25" customHeight="1" spans="1:15">
+      <c r="A64" s="3"/>
+      <c r="B64" s="4"/>
+      <c r="C64" s="4"/>
+      <c r="D64" s="4"/>
+      <c r="E64" s="4"/>
+      <c r="F64" s="4"/>
+      <c r="G64" s="4"/>
+      <c r="H64" s="4"/>
+      <c r="J64" s="4"/>
+      <c r="K64" s="4"/>
+      <c r="L64" s="4"/>
+      <c r="M64" s="4"/>
+      <c r="N64" s="4"/>
+      <c r="O64" s="8"/>
+    </row>
+    <row r="65" ht="25" customHeight="1" spans="1:15">
+      <c r="A65" s="3"/>
+      <c r="B65" s="4"/>
+      <c r="C65" s="4"/>
+      <c r="D65" s="4"/>
+      <c r="E65" s="4"/>
+      <c r="F65" s="4"/>
+      <c r="G65" s="4"/>
+      <c r="H65" s="4"/>
+      <c r="J65" s="4"/>
+      <c r="K65" s="4"/>
+      <c r="L65" s="4"/>
+      <c r="M65" s="4"/>
+      <c r="N65" s="4"/>
+      <c r="O65" s="8"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H51" r:id="rId1" display="普洛伊湘普·素帕莎 / 芭莉雅皮·余 " tooltip="https://www.douban.com/personage/30264980/"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>

--- a/资源录入表新.xlsx
+++ b/资源录入表新.xlsx
@@ -26,8 +26,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="231">
   <si>
     <t>剧名</t>
   </si>
@@ -1050,6 +1072,576 @@
   </si>
   <si>
     <t xml:space="preserve">链接: https://pan.baidu.com/s/11-pn6zJgsVQp3MufmiSEnA 提取码: y9i6 </t>
+  </si>
+  <si>
+    <t>李熊猫</t>
+  </si>
+  <si>
+    <t>动漫</t>
+  </si>
+  <si>
+    <t>喜剧 / 动作 / 动画 / 奇幻</t>
+  </si>
+  <si>
+    <t>齐璇 / 小连杀 / 魏一凡 / 朱祎</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1paCsTOrm0Myk2sgF96UkcA 提取码: zb9w </t>
+  </si>
+  <si>
+    <t>春日之地</t>
+  </si>
+  <si>
+    <r>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>悬疑</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF3377AA"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>赵仁杰</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF3377AA"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>袁姗姗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF3377AA"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>漆昱辰</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF3377AA"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>丁嘉毅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/16GRCZK3niBDnbG3ND6mVtw 提取码: xjma </t>
+  </si>
+  <si>
+    <t>折金枝</t>
+  </si>
+  <si>
+    <r>
+      <t>古装</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111111"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>权谋</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>张赫</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF3377AA"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>徐轸轸</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1C11-1DhDULL7qOeytJ9LTw 提取码: fp76 </t>
+  </si>
+  <si>
+    <t>逆爱成河</t>
+  </si>
+  <si>
+    <r>
+      <t>剧情</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>爱情</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>泽</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF3377AA"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>韩乐瑶</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF3377AA"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>王灿亓</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF3377AA"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>王予</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1q_97xAgzeg63fujXsQoHNQ 提取码: rj5c </t>
+  </si>
+  <si>
+    <t>夺命许愿</t>
+  </si>
+  <si>
+    <r>
+      <t>剧情</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>恐怖</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>昭映</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF3377AA"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>姜美娜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF3377AA"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>白善浩</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF3377AA"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>玄宇锡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1wvdr54elVEWkt-5xM-qUKQ 提取码: udkd </t>
+  </si>
+  <si>
+    <t>御廷谣</t>
+  </si>
+  <si>
+    <r>
+      <t>爱情</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>古装</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">吴谨言 / 陈哲远 / 梁永棋 / 赵昭仪 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1o9b-WmhM1MJozXH7W07kdA 提取码: 2dh5 </t>
   </si>
 </sst>
 </file>
@@ -1062,7 +1654,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1232,6 +1824,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9.75"/>
+      <color rgb="FF3377AA"/>
+      <name val="Helvetica"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="10"/>
       <name val="Helvetica"/>
       <charset val="134"/>
@@ -1244,6 +1842,18 @@
     <font>
       <sz val="11"/>
       <name val="Helvetica"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF111111"/>
+      <name val="Helvetica"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF111111"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1757,7 +2367,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1785,17 +2395,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2336,7 +2949,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O65"/>
+  <dimension ref="A1:O66"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="17.625" style="2" customWidth="1"/>
@@ -3752,7 +4365,7 @@
       <c r="F44" s="4"/>
       <c r="G44" s="4"/>
       <c r="H44" s="4"/>
-      <c r="I44" s="9" t="s">
+      <c r="I44" s="4" t="s">
         <v>182</v>
       </c>
       <c r="J44" s="4"/>
@@ -3773,7 +4386,7 @@
       <c r="F45" s="4"/>
       <c r="G45" s="4"/>
       <c r="H45" s="4"/>
-      <c r="I45" s="9" t="s">
+      <c r="I45" s="4" t="s">
         <v>184</v>
       </c>
       <c r="J45" s="4"/>
@@ -3794,7 +4407,7 @@
       <c r="F46" s="4"/>
       <c r="G46" s="4"/>
       <c r="H46" s="4"/>
-      <c r="I46" s="9" t="s">
+      <c r="I46" s="4" t="s">
         <v>186</v>
       </c>
       <c r="J46" s="4"/>
@@ -3815,7 +4428,7 @@
       <c r="F47" s="4"/>
       <c r="G47" s="4"/>
       <c r="H47" s="4"/>
-      <c r="I47" s="9" t="s">
+      <c r="I47" s="4" t="s">
         <v>188</v>
       </c>
       <c r="J47" s="4"/>
@@ -3857,7 +4470,7 @@
       <c r="F49" s="4"/>
       <c r="G49" s="4"/>
       <c r="H49" s="4"/>
-      <c r="I49" s="9" t="s">
+      <c r="I49" s="4" t="s">
         <v>192</v>
       </c>
       <c r="J49" s="4"/>
@@ -3885,10 +4498,10 @@
         <v>23</v>
       </c>
       <c r="G50" s="4"/>
-      <c r="H50" s="10" t="s">
+      <c r="H50" s="9" t="s">
         <v>196</v>
       </c>
-      <c r="I50" s="9" t="s">
+      <c r="I50" s="4" t="s">
         <v>197</v>
       </c>
       <c r="J50" s="4"/>
@@ -3916,10 +4529,10 @@
         <v>23</v>
       </c>
       <c r="G51" s="4"/>
-      <c r="H51" s="10" t="s">
+      <c r="H51" s="9" t="s">
         <v>200</v>
       </c>
-      <c r="I51" s="9" t="s">
+      <c r="I51" s="4" t="s">
         <v>201</v>
       </c>
       <c r="J51" s="4"/>
@@ -3936,7 +4549,7 @@
       <c r="B52" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C52" s="11" t="s">
+      <c r="C52" s="10" t="s">
         <v>203</v>
       </c>
       <c r="D52" s="4"/>
@@ -3947,10 +4560,10 @@
         <v>23</v>
       </c>
       <c r="G52" s="4"/>
-      <c r="H52" s="12" t="s">
+      <c r="H52" s="11" t="s">
         <v>204</v>
       </c>
-      <c r="I52" s="9" t="s">
+      <c r="I52" s="4" t="s">
         <v>205</v>
       </c>
       <c r="J52" s="4"/>
@@ -3961,15 +4574,29 @@
       <c r="O52" s="8"/>
     </row>
     <row r="53" ht="25" customHeight="1" spans="1:15">
-      <c r="A53" s="3"/>
-      <c r="B53" s="4"/>
-      <c r="C53" s="4"/>
-      <c r="D53" s="4"/>
-      <c r="E53" s="4"/>
-      <c r="F53" s="4"/>
-      <c r="G53" s="4"/>
-      <c r="H53" s="4"/>
-      <c r="I53" s="9"/>
+      <c r="A53" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="D53" s="5"/>
+      <c r="E53" s="5">
+        <v>3</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G53" s="5"/>
+      <c r="H53" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="I53" s="13" t="s">
+        <v>210</v>
+      </c>
       <c r="J53" s="4"/>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -3978,15 +4605,29 @@
       <c r="O53" s="8"/>
     </row>
     <row r="54" ht="25" customHeight="1" spans="1:15">
-      <c r="A54" s="3"/>
-      <c r="B54" s="4"/>
-      <c r="C54" s="4"/>
-      <c r="D54" s="4"/>
-      <c r="E54" s="4"/>
-      <c r="F54" s="4"/>
-      <c r="G54" s="4"/>
-      <c r="H54" s="4"/>
-      <c r="I54" s="9"/>
+      <c r="A54" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="D54" s="5"/>
+      <c r="E54" s="5">
+        <v>24</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G54" s="5"/>
+      <c r="H54" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="I54" s="13" t="s">
+        <v>214</v>
+      </c>
       <c r="J54" s="4"/>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>
@@ -3995,15 +4636,29 @@
       <c r="O54" s="8"/>
     </row>
     <row r="55" ht="25" customHeight="1" spans="1:15">
-      <c r="A55" s="3"/>
-      <c r="B55" s="4"/>
-      <c r="C55" s="4"/>
-      <c r="D55" s="4"/>
-      <c r="E55" s="4"/>
-      <c r="F55" s="4"/>
-      <c r="G55" s="4"/>
-      <c r="H55" s="4"/>
-      <c r="I55" s="9"/>
+      <c r="A55" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="D55" s="5"/>
+      <c r="E55" s="5">
+        <v>18</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G55" s="5"/>
+      <c r="H55" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="I55" s="13" t="s">
+        <v>218</v>
+      </c>
       <c r="J55" s="4"/>
       <c r="K55" s="4"/>
       <c r="L55" s="4"/>
@@ -4012,15 +4667,29 @@
       <c r="O55" s="8"/>
     </row>
     <row r="56" ht="25" customHeight="1" spans="1:15">
-      <c r="A56" s="3"/>
-      <c r="B56" s="4"/>
-      <c r="C56" s="4"/>
-      <c r="D56" s="4"/>
-      <c r="E56" s="4"/>
-      <c r="F56" s="4"/>
-      <c r="G56" s="4"/>
-      <c r="H56" s="4"/>
-      <c r="I56" s="9"/>
+      <c r="A56" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="D56" s="5"/>
+      <c r="E56" s="5">
+        <v>24</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G56" s="5"/>
+      <c r="H56" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="I56" s="13" t="s">
+        <v>222</v>
+      </c>
       <c r="J56" s="4"/>
       <c r="K56" s="4"/>
       <c r="L56" s="4"/>
@@ -4029,15 +4698,30 @@
       <c r="O56" s="8"/>
     </row>
     <row r="57" ht="25" customHeight="1" spans="1:15">
-      <c r="A57" s="13"/>
-      <c r="B57" s="14"/>
-      <c r="C57" s="14"/>
-      <c r="D57" s="14"/>
-      <c r="E57" s="14"/>
-      <c r="F57" s="14"/>
-      <c r="G57" s="14"/>
-      <c r="H57" s="14"/>
-      <c r="J57" s="14"/>
+      <c r="A57" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="D57" s="5"/>
+      <c r="E57" s="5">
+        <v>8</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G57" s="5"/>
+      <c r="H57" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="I57" s="13" t="s">
+        <v>226</v>
+      </c>
+      <c r="J57" s="4"/>
       <c r="K57" s="4"/>
       <c r="L57" s="4"/>
       <c r="M57" s="4"/>
@@ -4045,14 +4729,29 @@
       <c r="O57" s="8"/>
     </row>
     <row r="58" ht="25" customHeight="1" spans="1:15">
-      <c r="A58" s="3"/>
-      <c r="B58" s="4"/>
-      <c r="C58" s="4"/>
-      <c r="D58" s="4"/>
-      <c r="E58" s="4"/>
-      <c r="F58" s="4"/>
-      <c r="G58" s="4"/>
-      <c r="H58" s="4"/>
+      <c r="A58" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="D58" s="5"/>
+      <c r="E58" s="5">
+        <v>6</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G58" s="5"/>
+      <c r="H58" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="I58" s="13" t="s">
+        <v>230</v>
+      </c>
       <c r="J58" s="4"/>
       <c r="K58" s="4"/>
       <c r="L58" s="4"/>
@@ -4061,15 +4760,15 @@
       <c r="O58" s="8"/>
     </row>
     <row r="59" ht="25" customHeight="1" spans="1:15">
-      <c r="A59" s="3"/>
-      <c r="B59" s="4"/>
-      <c r="C59" s="4"/>
-      <c r="D59" s="4"/>
-      <c r="E59" s="4"/>
-      <c r="F59" s="4"/>
-      <c r="G59" s="4"/>
-      <c r="H59" s="4"/>
-      <c r="J59" s="4"/>
+      <c r="A59" s="14"/>
+      <c r="B59" s="15"/>
+      <c r="C59" s="15"/>
+      <c r="D59" s="15"/>
+      <c r="E59" s="15"/>
+      <c r="F59" s="15"/>
+      <c r="G59" s="15"/>
+      <c r="H59" s="15"/>
+      <c r="J59" s="15"/>
       <c r="K59" s="4"/>
       <c r="L59" s="4"/>
       <c r="M59" s="4"/>
@@ -4085,6 +4784,7 @@
       <c r="F60" s="4"/>
       <c r="G60" s="4"/>
       <c r="H60" s="4"/>
+      <c r="I60" s="1"/>
       <c r="J60" s="4"/>
       <c r="K60" s="4"/>
       <c r="L60" s="4"/>
@@ -4117,6 +4817,7 @@
       <c r="F62" s="4"/>
       <c r="G62" s="4"/>
       <c r="H62" s="4"/>
+      <c r="I62" s="1"/>
       <c r="J62" s="4"/>
       <c r="K62" s="4"/>
       <c r="L62" s="4"/>
@@ -4149,6 +4850,7 @@
       <c r="F64" s="4"/>
       <c r="G64" s="4"/>
       <c r="H64" s="4"/>
+      <c r="I64" s="1"/>
       <c r="J64" s="4"/>
       <c r="K64" s="4"/>
       <c r="L64" s="4"/>
@@ -4172,6 +4874,12 @@
       <c r="N65" s="4"/>
       <c r="O65" s="8"/>
     </row>
+    <row r="66" spans="1:15">
+      <c r="I66" s="1" t="e" cm="1">
+        <f t="array" ref="I66">--来自百度网盘超级会员v1的分享</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="H51" r:id="rId1" display="普洛伊湘普·素帕莎 / 芭莉雅皮·余 " tooltip="https://www.douban.com/personage/30264980/"/>

--- a/资源录入表新.xlsx
+++ b/资源录入表新.xlsx
@@ -1093,6 +1093,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t> </t>
     </r>
     <r>
@@ -1107,6 +1114,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>:</t>
     </r>
     <r>
@@ -1199,6 +1213,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>古装</t>
     </r>
     <r>
@@ -1222,6 +1243,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>张赫</t>
     </r>
     <r>
@@ -1269,6 +1297,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>剧情</t>
     </r>
     <r>
@@ -1310,6 +1345,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>泽</t>
     </r>
     <r>
@@ -1429,6 +1471,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>剧情</t>
     </r>
     <r>
@@ -1470,6 +1519,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>昭映</t>
     </r>
     <r>
@@ -1598,6 +1654,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>爱情</t>
     </r>
     <r>
@@ -1824,12 +1887,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9.75"/>
-      <color rgb="FF3377AA"/>
-      <name val="Helvetica"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="10"/>
       <name val="Helvetica"/>
       <charset val="134"/>
@@ -1837,11 +1894,6 @@
     <font>
       <sz val="10"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Helvetica"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1854,6 +1906,17 @@
       <sz val="10"/>
       <color rgb="FF111111"/>
       <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Helvetica"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9.75"/>
+      <color rgb="FF3377AA"/>
+      <name val="Helvetica"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -2367,7 +2430,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2406,9 +2469,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -4594,7 +4654,7 @@
       <c r="H53" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="I53" s="13" t="s">
+      <c r="I53" s="4" t="s">
         <v>210</v>
       </c>
       <c r="J53" s="4"/>
@@ -4625,7 +4685,7 @@
       <c r="H54" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="I54" s="13" t="s">
+      <c r="I54" s="4" t="s">
         <v>214</v>
       </c>
       <c r="J54" s="4"/>
@@ -4656,7 +4716,7 @@
       <c r="H55" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="I55" s="13" t="s">
+      <c r="I55" s="4" t="s">
         <v>218</v>
       </c>
       <c r="J55" s="4"/>
@@ -4687,7 +4747,7 @@
       <c r="H56" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="I56" s="13" t="s">
+      <c r="I56" s="4" t="s">
         <v>222</v>
       </c>
       <c r="J56" s="4"/>
@@ -4718,7 +4778,7 @@
       <c r="H57" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="I57" s="13" t="s">
+      <c r="I57" s="4" t="s">
         <v>226</v>
       </c>
       <c r="J57" s="4"/>
@@ -4749,7 +4809,7 @@
       <c r="H58" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="I58" s="13" t="s">
+      <c r="I58" s="4" t="s">
         <v>230</v>
       </c>
       <c r="J58" s="4"/>
@@ -4760,15 +4820,15 @@
       <c r="O58" s="8"/>
     </row>
     <row r="59" ht="25" customHeight="1" spans="1:15">
-      <c r="A59" s="14"/>
-      <c r="B59" s="15"/>
-      <c r="C59" s="15"/>
-      <c r="D59" s="15"/>
-      <c r="E59" s="15"/>
-      <c r="F59" s="15"/>
-      <c r="G59" s="15"/>
-      <c r="H59" s="15"/>
-      <c r="J59" s="15"/>
+      <c r="A59" s="13"/>
+      <c r="B59" s="14"/>
+      <c r="C59" s="14"/>
+      <c r="D59" s="14"/>
+      <c r="E59" s="14"/>
+      <c r="F59" s="14"/>
+      <c r="G59" s="14"/>
+      <c r="H59" s="14"/>
+      <c r="J59" s="14"/>
       <c r="K59" s="4"/>
       <c r="L59" s="4"/>
       <c r="M59" s="4"/>
@@ -4784,7 +4844,6 @@
       <c r="F60" s="4"/>
       <c r="G60" s="4"/>
       <c r="H60" s="4"/>
-      <c r="I60" s="1"/>
       <c r="J60" s="4"/>
       <c r="K60" s="4"/>
       <c r="L60" s="4"/>
@@ -4817,7 +4876,6 @@
       <c r="F62" s="4"/>
       <c r="G62" s="4"/>
       <c r="H62" s="4"/>
-      <c r="I62" s="1"/>
       <c r="J62" s="4"/>
       <c r="K62" s="4"/>
       <c r="L62" s="4"/>
@@ -4850,7 +4908,6 @@
       <c r="F64" s="4"/>
       <c r="G64" s="4"/>
       <c r="H64" s="4"/>
-      <c r="I64" s="1"/>
       <c r="J64" s="4"/>
       <c r="K64" s="4"/>
       <c r="L64" s="4"/>

--- a/资源录入表新.xlsx
+++ b/资源录入表新.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="253">
   <si>
     <t>剧名</t>
   </si>
@@ -948,6 +948,207 @@
   <si>
     <t xml:space="preserve">链接: https://pan.baidu.com/s/1o9b-WmhM1MJozXH7W07kdA 提取码: 2dh5 </t>
   </si>
+  <si>
+    <t>九门2</t>
+  </si>
+  <si>
+    <t>剧情 / 奇幻 / 冒险</t>
+  </si>
+  <si>
+    <t>陈伟霆 / 陈瑶 / 曾舜晞 / 王茂蕾 / 王奕婷 / 李乃文 / 释小龙 / 应灏铭 / 季肖冰 / 胡耘豪 / 徐正溪 / 章涛 / 王祖一</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1V8VWsfDlUm1NhfIO2dMB0Q 提取码: a5m2 </t>
+  </si>
+  <si>
+    <t>东大高武学院</t>
+  </si>
+  <si>
+    <r>
+      <t>动作</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>动画</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>奇幻</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>云惟一</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>万舒心</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>刘琮</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>张惠霖</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>李铮</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1xgB5NP2JFKwnC0tnE_vV-Q 提取码: grug </t>
+  </si>
+  <si>
+    <t>楚人美游记</t>
+  </si>
+  <si>
+    <r>
+      <t>志怪</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> #</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>法术</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1hQKA0Oc-JJIQ4XxdY13YmQ 提取码: j1h2 </t>
+  </si>
+  <si>
+    <t>神的游戏</t>
+  </si>
+  <si>
+    <t>AI真人格斗番</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1IpJblba6yx_ULc6AQ9FKzQ 提取码: 7zcj </t>
+  </si>
+  <si>
+    <t>天庭三大反骨仔系列</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1xQB5aGDByNbjg5T13pwr7w 提取码: eui7 </t>
+  </si>
+  <si>
+    <t>枭</t>
+  </si>
+  <si>
+    <r>
+      <t>真人AI/志怪</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> #</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>法术</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1Ll1Z9gnTo6af9Z7H3zOLBw 提取码: vrby </t>
+  </si>
 </sst>
 </file>
 
@@ -959,7 +1160,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1131,6 +1332,26 @@
     <font>
       <sz val="11"/>
       <name val="Helvetica"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9.75"/>
+      <name val="Helvetica"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9.75"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1334,7 +1555,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -1378,19 +1599,6 @@
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -1520,7 +1728,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1532,34 +1740,34 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1644,16 +1852,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1663,40 +1868,52 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2231,11 +2448,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:O65"/>
+  <sheetPr/>
+  <dimension ref="A1:O81"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="17.625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="17.625" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="1"/>
     <col min="3" max="3" width="18.625" style="1" customWidth="1"/>
     <col min="4" max="7" width="9" style="1"/>
@@ -2245,1943 +2462,2282 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
-      <c r="O1" s="5"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:15">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="5">
         <v>22</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="5">
+      <c r="G2" s="4">
         <v>2026</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5" t="s">
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-    </row>
-    <row r="3" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A3" s="4" t="s">
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+    </row>
+    <row r="3" ht="25" customHeight="1" spans="1:15">
+      <c r="A3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="5">
+      <c r="G3" s="4">
         <v>2026</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="4" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5" t="s">
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
-    </row>
-    <row r="4" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A4" s="4" t="s">
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
+    </row>
+    <row r="4" ht="25" customHeight="1" spans="1:15">
+      <c r="A4" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="4">
         <v>2025</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="4" t="s">
         <v>29</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5" t="s">
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-    </row>
-    <row r="5" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A5" s="4" t="s">
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
+      <c r="O4" s="4"/>
+    </row>
+    <row r="5" ht="25" customHeight="1" spans="1:15">
+      <c r="A5" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5" s="4">
         <v>2026</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="4" t="s">
         <v>35</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5" t="s">
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
-    </row>
-    <row r="6" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A6" s="4" t="s">
+      <c r="M5" s="4"/>
+      <c r="N5" s="4"/>
+      <c r="O5" s="4"/>
+    </row>
+    <row r="6" ht="25" customHeight="1" spans="1:15">
+      <c r="A6" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G6" s="4">
         <v>2026</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="H6" s="4" t="s">
         <v>41</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5" t="s">
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="M6" s="5"/>
-      <c r="N6" s="5"/>
-      <c r="O6" s="5"/>
-    </row>
-    <row r="7" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A7" s="4" t="s">
+      <c r="M6" s="4"/>
+      <c r="N6" s="4"/>
+      <c r="O6" s="4"/>
+    </row>
+    <row r="7" ht="25" customHeight="1" spans="1:15">
+      <c r="A7" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G7" s="4">
         <v>2025</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="H7" s="4" t="s">
         <v>47</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5" t="s">
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="M7" s="5"/>
-      <c r="N7" s="5"/>
-      <c r="O7" s="5"/>
-    </row>
-    <row r="8" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A8" s="4" t="s">
+      <c r="M7" s="4"/>
+      <c r="N7" s="4"/>
+      <c r="O7" s="4"/>
+    </row>
+    <row r="8" ht="25" customHeight="1" spans="1:15">
+      <c r="A8" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="5">
+      <c r="G8" s="4">
         <v>2026</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="H8" s="4" t="s">
         <v>53</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5" t="s">
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="M8" s="5"/>
-      <c r="N8" s="5"/>
-      <c r="O8" s="5"/>
-    </row>
-    <row r="9" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A9" s="4" t="s">
+      <c r="M8" s="4"/>
+      <c r="N8" s="4"/>
+      <c r="O8" s="4"/>
+    </row>
+    <row r="9" ht="25" customHeight="1" spans="1:15">
+      <c r="A9" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G9" s="5">
+      <c r="G9" s="4">
         <v>2026</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="H9" s="4" t="s">
         <v>59</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5" t="s">
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="M9" s="5"/>
-      <c r="N9" s="5"/>
-      <c r="O9" s="5"/>
-    </row>
-    <row r="10" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A10" s="4" t="s">
+      <c r="M9" s="4"/>
+      <c r="N9" s="4"/>
+      <c r="O9" s="4"/>
+    </row>
+    <row r="10" ht="25" customHeight="1" spans="1:15">
+      <c r="A10" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G10" s="5">
+      <c r="G10" s="4">
         <v>2024</v>
       </c>
-      <c r="H10" s="5" t="s">
+      <c r="H10" s="4" t="s">
         <v>65</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
-      <c r="L10" s="5" t="s">
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="M10" s="5"/>
-      <c r="N10" s="5"/>
-      <c r="O10" s="5"/>
-    </row>
-    <row r="11" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A11" s="4" t="s">
+      <c r="M10" s="4"/>
+      <c r="N10" s="4"/>
+      <c r="O10" s="4"/>
+    </row>
+    <row r="11" ht="25" customHeight="1" spans="1:15">
+      <c r="A11" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G11" s="5">
+      <c r="G11" s="4">
         <v>2024</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="H11" s="4" t="s">
         <v>71</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5"/>
-      <c r="L11" s="5" t="s">
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="M11" s="5"/>
-      <c r="N11" s="5"/>
-      <c r="O11" s="5"/>
-    </row>
-    <row r="12" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A12" s="4" t="s">
+      <c r="M11" s="4"/>
+      <c r="N11" s="4"/>
+      <c r="O11" s="4"/>
+    </row>
+    <row r="12" ht="25" customHeight="1" spans="1:15">
+      <c r="A12" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="F12" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G12" s="5">
+      <c r="G12" s="4">
         <v>2026</v>
       </c>
-      <c r="H12" s="5" t="s">
+      <c r="H12" s="4" t="s">
         <v>75</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5"/>
-      <c r="L12" s="5" t="s">
+      <c r="J12" s="4"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="M12" s="5"/>
-      <c r="N12" s="5"/>
-      <c r="O12" s="5"/>
-    </row>
-    <row r="13" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A13" s="4" t="s">
+      <c r="M12" s="4"/>
+      <c r="N12" s="4"/>
+      <c r="O12" s="4"/>
+    </row>
+    <row r="13" ht="25" customHeight="1" spans="1:15">
+      <c r="A13" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="F13" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G13" s="5">
+      <c r="G13" s="4">
         <v>2025</v>
       </c>
-      <c r="H13" s="5" t="s">
+      <c r="H13" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="I13" s="5" t="s">
+      <c r="I13" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
-      <c r="L13" s="5" t="s">
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="M13" s="5"/>
-      <c r="N13" s="5"/>
-      <c r="O13" s="5"/>
-    </row>
-    <row r="14" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A14" s="4" t="s">
+      <c r="M13" s="4"/>
+      <c r="N13" s="4"/>
+      <c r="O13" s="4"/>
+    </row>
+    <row r="14" ht="25" customHeight="1" spans="1:15">
+      <c r="A14" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="F14" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G14" s="5">
+      <c r="G14" s="4">
         <v>2026</v>
       </c>
-      <c r="H14" s="5" t="s">
+      <c r="H14" s="4" t="s">
         <v>86</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
-      <c r="L14" s="5" t="s">
+      <c r="J14" s="4"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="M14" s="5"/>
-      <c r="N14" s="5"/>
-      <c r="O14" s="5"/>
-    </row>
-    <row r="15" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A15" s="4" t="s">
+      <c r="M14" s="4"/>
+      <c r="N14" s="4"/>
+      <c r="O14" s="4"/>
+    </row>
+    <row r="15" ht="25" customHeight="1" spans="1:15">
+      <c r="A15" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="F15" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G15" s="5">
+      <c r="G15" s="4">
         <v>2026</v>
       </c>
-      <c r="H15" s="5" t="s">
+      <c r="H15" s="4" t="s">
         <v>91</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5"/>
-      <c r="L15" s="5" t="s">
+      <c r="J15" s="4"/>
+      <c r="K15" s="4"/>
+      <c r="L15" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="M15" s="5"/>
-      <c r="N15" s="5"/>
-      <c r="O15" s="5"/>
-    </row>
-    <row r="16" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A16" s="4" t="s">
+      <c r="M15" s="4"/>
+      <c r="N15" s="4"/>
+      <c r="O15" s="4"/>
+    </row>
+    <row r="16" ht="25" customHeight="1" spans="1:15">
+      <c r="A16" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="F16" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G16" s="5">
+      <c r="G16" s="4">
         <v>2026</v>
       </c>
-      <c r="H16" s="5" t="s">
+      <c r="H16" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="I16" s="5" t="s">
+      <c r="I16" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="J16" s="5"/>
-      <c r="K16" s="5"/>
-      <c r="L16" s="5" t="s">
+      <c r="J16" s="4"/>
+      <c r="K16" s="4"/>
+      <c r="L16" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="M16" s="5"/>
-      <c r="N16" s="5"/>
-      <c r="O16" s="5"/>
-    </row>
-    <row r="17" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A17" s="4" t="s">
+      <c r="M16" s="4"/>
+      <c r="N16" s="4"/>
+      <c r="O16" s="4"/>
+    </row>
+    <row r="17" ht="25" customHeight="1" spans="1:15">
+      <c r="A17" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="F17" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G17" s="5">
+      <c r="G17" s="4">
         <v>2025</v>
       </c>
-      <c r="H17" s="5" t="s">
+      <c r="H17" s="4" t="s">
         <v>101</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="J17" s="5"/>
-      <c r="K17" s="5"/>
-      <c r="L17" s="5" t="s">
+      <c r="J17" s="4"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="M17" s="5"/>
-      <c r="N17" s="5"/>
-      <c r="O17" s="5"/>
-    </row>
-    <row r="18" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A18" s="4" t="s">
+      <c r="M17" s="4"/>
+      <c r="N17" s="4"/>
+      <c r="O17" s="4"/>
+    </row>
+    <row r="18" ht="25" customHeight="1" spans="1:15">
+      <c r="A18" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="F18" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G18" s="5">
+      <c r="G18" s="4">
         <v>2026</v>
       </c>
-      <c r="H18" s="5" t="s">
+      <c r="H18" s="4" t="s">
         <v>107</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="J18" s="5"/>
-      <c r="K18" s="5"/>
-      <c r="L18" s="5" t="s">
+      <c r="J18" s="4"/>
+      <c r="K18" s="4"/>
+      <c r="L18" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="M18" s="5"/>
-      <c r="N18" s="5"/>
-      <c r="O18" s="5"/>
-    </row>
-    <row r="19" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A19" s="4" t="s">
+      <c r="M18" s="4"/>
+      <c r="N18" s="4"/>
+      <c r="O18" s="4"/>
+    </row>
+    <row r="19" ht="25" customHeight="1" spans="1:15">
+      <c r="A19" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D19" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="E19" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="F19" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G19" s="5">
+      <c r="G19" s="4">
         <v>2026</v>
       </c>
-      <c r="H19" s="5" t="s">
+      <c r="H19" s="4" t="s">
         <v>112</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="J19" s="5"/>
-      <c r="K19" s="5"/>
-      <c r="L19" s="5" t="s">
+      <c r="J19" s="4"/>
+      <c r="K19" s="4"/>
+      <c r="L19" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="M19" s="5"/>
-      <c r="N19" s="5"/>
-      <c r="O19" s="5"/>
+      <c r="M19" s="4"/>
+      <c r="N19" s="4"/>
+      <c r="O19" s="4"/>
     </row>
     <row r="20" ht="25" customHeight="1" spans="1:15">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D20" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E20" s="7">
+      <c r="E20" s="6">
         <v>6</v>
       </c>
-      <c r="F20" s="5" t="s">
+      <c r="F20" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G20" s="5">
+      <c r="G20" s="4">
         <v>2025</v>
       </c>
-      <c r="H20" s="5"/>
+      <c r="H20" s="4"/>
       <c r="I20" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="J20" s="5"/>
-      <c r="K20" s="5"/>
-      <c r="L20" s="5" t="s">
+      <c r="J20" s="4"/>
+      <c r="K20" s="4"/>
+      <c r="L20" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="M20" s="5"/>
-      <c r="N20" s="5"/>
-      <c r="O20" s="5"/>
+      <c r="M20" s="4"/>
+      <c r="N20" s="4"/>
+      <c r="O20" s="4"/>
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:15">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D21" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E21" s="7">
+      <c r="E21" s="6">
         <v>6</v>
       </c>
-      <c r="F21" s="5" t="s">
+      <c r="F21" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G21" s="5">
+      <c r="G21" s="4">
         <v>2025</v>
       </c>
-      <c r="H21" s="5"/>
+      <c r="H21" s="4"/>
       <c r="I21" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J21" s="5"/>
-      <c r="K21" s="5"/>
-      <c r="L21" s="5" t="s">
+      <c r="J21" s="4"/>
+      <c r="K21" s="4"/>
+      <c r="L21" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="M21" s="5"/>
-      <c r="N21" s="5"/>
-      <c r="O21" s="5"/>
+      <c r="M21" s="4"/>
+      <c r="N21" s="4"/>
+      <c r="O21" s="4"/>
     </row>
     <row r="22" ht="25" customHeight="1" spans="1:15">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D22" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E22" s="6" t="s">
+      <c r="E22" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="F22" s="5" t="s">
+      <c r="F22" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G22" s="5">
+      <c r="G22" s="4">
         <v>2025</v>
       </c>
-      <c r="H22" s="5"/>
+      <c r="H22" s="4"/>
       <c r="I22" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="J22" s="5"/>
-      <c r="K22" s="5"/>
-      <c r="L22" s="5" t="s">
+      <c r="J22" s="4"/>
+      <c r="K22" s="4"/>
+      <c r="L22" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="M22" s="5"/>
-      <c r="N22" s="5"/>
-      <c r="O22" s="5"/>
+      <c r="M22" s="4"/>
+      <c r="N22" s="4"/>
+      <c r="O22" s="4"/>
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:15">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B23" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="D23" s="9" t="s">
+      <c r="D23" s="8" t="s">
         <v>14</v>
       </c>
       <c r="E23" s="9">
         <v>4</v>
       </c>
-      <c r="F23" s="9" t="s">
+      <c r="F23" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G23" s="9">
+      <c r="G23" s="8">
         <v>2025</v>
       </c>
-      <c r="H23" s="9"/>
+      <c r="H23" s="8"/>
       <c r="I23" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="J23" s="9"/>
-      <c r="K23" s="9"/>
-      <c r="L23" s="9" t="s">
+      <c r="J23" s="8"/>
+      <c r="K23" s="8"/>
+      <c r="L23" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="M23" s="9"/>
-      <c r="N23" s="9"/>
-      <c r="O23" s="5"/>
+      <c r="M23" s="8"/>
+      <c r="N23" s="8"/>
+      <c r="O23" s="4"/>
     </row>
     <row r="24" ht="25" customHeight="1" spans="1:15">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="D24" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E24" s="6" t="s">
+      <c r="E24" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="F24" s="5" t="s">
+      <c r="F24" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G24" s="5">
+      <c r="G24" s="4">
         <v>2025</v>
       </c>
-      <c r="H24" s="5" t="s">
+      <c r="H24" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="I24" s="5" t="s">
+      <c r="I24" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="J24" s="5"/>
-      <c r="K24" s="5"/>
-      <c r="L24" s="5" t="s">
+      <c r="J24" s="4"/>
+      <c r="K24" s="4"/>
+      <c r="L24" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="M24" s="5"/>
-      <c r="N24" s="5"/>
+      <c r="M24" s="4"/>
+      <c r="N24" s="4"/>
       <c r="O24" s="10"/>
     </row>
     <row r="25" ht="25" customHeight="1" spans="1:15">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="D25" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E25" s="5">
+      <c r="E25" s="4">
         <v>6</v>
       </c>
-      <c r="F25" s="5" t="s">
+      <c r="F25" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G25" s="5">
+      <c r="G25" s="4">
         <v>2025</v>
       </c>
-      <c r="H25" s="5"/>
-      <c r="I25" s="5" t="s">
+      <c r="H25" s="4"/>
+      <c r="I25" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="J25" s="5"/>
-      <c r="K25" s="5"/>
-      <c r="L25" s="5" t="s">
+      <c r="J25" s="4"/>
+      <c r="K25" s="4"/>
+      <c r="L25" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="M25" s="5"/>
-      <c r="N25" s="5"/>
+      <c r="M25" s="4"/>
+      <c r="N25" s="4"/>
       <c r="O25" s="10"/>
     </row>
     <row r="26" ht="25" customHeight="1" spans="1:15">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="D26" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E26" s="5">
+      <c r="E26" s="4">
         <v>8</v>
       </c>
-      <c r="F26" s="5" t="s">
+      <c r="F26" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G26" s="5">
+      <c r="G26" s="4">
         <v>2025</v>
       </c>
-      <c r="H26" s="5"/>
-      <c r="I26" s="5" t="s">
+      <c r="H26" s="4"/>
+      <c r="I26" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="J26" s="5"/>
-      <c r="K26" s="5"/>
-      <c r="L26" s="5" t="s">
+      <c r="J26" s="4"/>
+      <c r="K26" s="4"/>
+      <c r="L26" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="M26" s="5"/>
-      <c r="N26" s="5"/>
+      <c r="M26" s="4"/>
+      <c r="N26" s="4"/>
       <c r="O26" s="10"/>
     </row>
     <row r="27" ht="25" customHeight="1" spans="1:15">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="D27" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E27" s="5">
+      <c r="E27" s="4">
         <v>10</v>
       </c>
-      <c r="F27" s="5" t="s">
+      <c r="F27" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G27" s="5">
+      <c r="G27" s="4">
         <v>2025</v>
       </c>
-      <c r="H27" s="5"/>
-      <c r="I27" s="5" t="s">
+      <c r="H27" s="4"/>
+      <c r="I27" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="J27" s="5"/>
-      <c r="K27" s="5"/>
-      <c r="L27" s="5" t="s">
+      <c r="J27" s="4"/>
+      <c r="K27" s="4"/>
+      <c r="L27" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="M27" s="5"/>
-      <c r="N27" s="5"/>
+      <c r="M27" s="4"/>
+      <c r="N27" s="4"/>
       <c r="O27" s="10"/>
     </row>
     <row r="28" ht="25" customHeight="1" spans="1:15">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C28" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="D28" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E28" s="5">
+      <c r="E28" s="4">
         <v>2</v>
       </c>
-      <c r="F28" s="5" t="s">
+      <c r="F28" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G28" s="5">
+      <c r="G28" s="4">
         <v>2025</v>
       </c>
-      <c r="H28" s="5"/>
-      <c r="I28" s="5" t="s">
+      <c r="H28" s="4"/>
+      <c r="I28" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="J28" s="5"/>
-      <c r="K28" s="5"/>
-      <c r="L28" s="5" t="s">
+      <c r="J28" s="4"/>
+      <c r="K28" s="4"/>
+      <c r="L28" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="M28" s="5"/>
-      <c r="N28" s="5"/>
+      <c r="M28" s="4"/>
+      <c r="N28" s="4"/>
       <c r="O28" s="10"/>
     </row>
     <row r="29" ht="25" customHeight="1" spans="1:15">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="D29" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E29" s="6">
+      <c r="E29" s="5">
         <v>7</v>
       </c>
-      <c r="F29" s="5" t="s">
+      <c r="F29" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G29" s="5">
+      <c r="G29" s="4">
         <v>2025</v>
       </c>
-      <c r="H29" s="5"/>
-      <c r="I29" s="5" t="s">
+      <c r="H29" s="4"/>
+      <c r="I29" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="J29" s="5"/>
-      <c r="K29" s="5"/>
-      <c r="L29" s="5" t="s">
+      <c r="J29" s="4"/>
+      <c r="K29" s="4"/>
+      <c r="L29" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="M29" s="5"/>
-      <c r="N29" s="5"/>
+      <c r="M29" s="4"/>
+      <c r="N29" s="4"/>
       <c r="O29" s="10"/>
     </row>
-    <row r="30" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A30" s="4" t="s">
+    <row r="30" ht="25" customHeight="1" spans="1:15">
+      <c r="A30" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C30" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="D30" s="5" t="s">
+      <c r="D30" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E30" s="5" t="s">
+      <c r="E30" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F30" s="5" t="s">
+      <c r="F30" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G30" s="5">
+      <c r="G30" s="4">
         <v>2026</v>
       </c>
-      <c r="H30" s="5" t="s">
+      <c r="H30" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="I30" s="5" t="s">
+      <c r="I30" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="J30" s="5"/>
-      <c r="K30" s="5"/>
-      <c r="L30" s="5" t="s">
+      <c r="J30" s="4"/>
+      <c r="K30" s="4"/>
+      <c r="L30" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="M30" s="5"/>
-      <c r="N30" s="5"/>
+      <c r="M30" s="4"/>
+      <c r="N30" s="4"/>
       <c r="O30" s="10"/>
     </row>
-    <row r="31" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A31" s="4" t="s">
+    <row r="31" ht="25" customHeight="1" spans="1:15">
+      <c r="A31" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="B31" s="5"/>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5" t="s">
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G31" s="5"/>
-      <c r="H31" s="5"/>
-      <c r="I31" s="5" t="s">
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="J31" s="5"/>
-      <c r="K31" s="5"/>
-      <c r="L31" s="5"/>
-      <c r="M31" s="5"/>
-      <c r="N31" s="5"/>
+      <c r="J31" s="4"/>
+      <c r="K31" s="4"/>
+      <c r="L31" s="4"/>
+      <c r="M31" s="4"/>
+      <c r="N31" s="4"/>
       <c r="O31" s="10"/>
     </row>
     <row r="32" ht="25" customHeight="1" spans="1:15">
-      <c r="A32" s="4" t="s">
+      <c r="A32" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="B32" s="5"/>
-      <c r="C32" s="5"/>
-      <c r="D32" s="5"/>
-      <c r="E32" s="6">
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="5">
         <v>16</v>
       </c>
-      <c r="F32" s="5" t="s">
+      <c r="F32" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G32" s="5"/>
-      <c r="H32" s="5"/>
-      <c r="I32" s="5" t="s">
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="J32" s="5"/>
-      <c r="K32" s="5"/>
-      <c r="L32" s="5"/>
-      <c r="M32" s="5"/>
-      <c r="N32" s="5"/>
+      <c r="J32" s="4"/>
+      <c r="K32" s="4"/>
+      <c r="L32" s="4"/>
+      <c r="M32" s="4"/>
+      <c r="N32" s="4"/>
       <c r="O32" s="10"/>
     </row>
-    <row r="33" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A33" s="4" t="s">
+    <row r="33" ht="25" customHeight="1" spans="1:15">
+      <c r="A33" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="B33" s="5"/>
-      <c r="C33" s="5"/>
-      <c r="D33" s="5"/>
-      <c r="E33" s="5"/>
-      <c r="F33" s="5" t="s">
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G33" s="5"/>
-      <c r="H33" s="5"/>
-      <c r="I33" s="5" t="s">
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="J33" s="5"/>
-      <c r="K33" s="5"/>
-      <c r="L33" s="5"/>
-      <c r="M33" s="5"/>
-      <c r="N33" s="5"/>
+      <c r="J33" s="4"/>
+      <c r="K33" s="4"/>
+      <c r="L33" s="4"/>
+      <c r="M33" s="4"/>
+      <c r="N33" s="4"/>
       <c r="O33" s="10"/>
     </row>
-    <row r="34" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A34" s="4" t="s">
+    <row r="34" ht="25" customHeight="1" spans="1:15">
+      <c r="A34" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="B34" s="5"/>
-      <c r="C34" s="5"/>
-      <c r="D34" s="5"/>
-      <c r="E34" s="5"/>
-      <c r="F34" s="5" t="s">
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G34" s="5"/>
-      <c r="H34" s="5"/>
-      <c r="I34" s="5" t="s">
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="J34" s="5"/>
-      <c r="K34" s="5"/>
-      <c r="L34" s="5"/>
-      <c r="M34" s="5"/>
-      <c r="N34" s="5"/>
+      <c r="J34" s="4"/>
+      <c r="K34" s="4"/>
+      <c r="L34" s="4"/>
+      <c r="M34" s="4"/>
+      <c r="N34" s="4"/>
       <c r="O34" s="10"/>
     </row>
-    <row r="35" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A35" s="4" t="s">
+    <row r="35" ht="25" customHeight="1" spans="1:15">
+      <c r="A35" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="B35" s="5"/>
-      <c r="C35" s="5"/>
-      <c r="D35" s="5"/>
-      <c r="E35" s="5"/>
-      <c r="F35" s="5" t="s">
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G35" s="5"/>
-      <c r="H35" s="5"/>
-      <c r="I35" s="5" t="s">
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="J35" s="5"/>
-      <c r="K35" s="5"/>
-      <c r="L35" s="5"/>
-      <c r="M35" s="5"/>
-      <c r="N35" s="5"/>
+      <c r="J35" s="4"/>
+      <c r="K35" s="4"/>
+      <c r="L35" s="4"/>
+      <c r="M35" s="4"/>
+      <c r="N35" s="4"/>
       <c r="O35" s="10"/>
     </row>
-    <row r="36" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A36" s="4" t="s">
+    <row r="36" ht="25" customHeight="1" spans="1:15">
+      <c r="A36" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="B36" s="5"/>
-      <c r="C36" s="5"/>
-      <c r="D36" s="5"/>
-      <c r="E36" s="5"/>
-      <c r="F36" s="5" t="s">
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G36" s="5"/>
-      <c r="H36" s="5"/>
-      <c r="I36" s="5" t="s">
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
+      <c r="I36" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="J36" s="5"/>
-      <c r="K36" s="5"/>
-      <c r="L36" s="5"/>
-      <c r="M36" s="5"/>
-      <c r="N36" s="5"/>
+      <c r="J36" s="4"/>
+      <c r="K36" s="4"/>
+      <c r="L36" s="4"/>
+      <c r="M36" s="4"/>
+      <c r="N36" s="4"/>
       <c r="O36" s="10"/>
     </row>
-    <row r="37" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A37" s="4" t="s">
+    <row r="37" ht="25" customHeight="1" spans="1:15">
+      <c r="A37" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="B37" s="5"/>
-      <c r="C37" s="5"/>
-      <c r="D37" s="5"/>
-      <c r="E37" s="5"/>
-      <c r="F37" s="5" t="s">
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G37" s="5"/>
-      <c r="H37" s="5"/>
-      <c r="I37" s="5" t="s">
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="J37" s="5"/>
-      <c r="K37" s="5"/>
-      <c r="L37" s="5"/>
-      <c r="M37" s="5"/>
-      <c r="N37" s="5"/>
+      <c r="J37" s="4"/>
+      <c r="K37" s="4"/>
+      <c r="L37" s="4"/>
+      <c r="M37" s="4"/>
+      <c r="N37" s="4"/>
       <c r="O37" s="10"/>
     </row>
-    <row r="38" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A38" s="4" t="s">
+    <row r="38" ht="25" customHeight="1" spans="1:15">
+      <c r="A38" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="B38" s="5"/>
-      <c r="C38" s="5"/>
-      <c r="D38" s="5"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="5" t="s">
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G38" s="5"/>
-      <c r="H38" s="5"/>
-      <c r="I38" s="5" t="s">
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="J38" s="5"/>
-      <c r="K38" s="5"/>
-      <c r="L38" s="5"/>
-      <c r="M38" s="5"/>
-      <c r="N38" s="5"/>
+      <c r="J38" s="4"/>
+      <c r="K38" s="4"/>
+      <c r="L38" s="4"/>
+      <c r="M38" s="4"/>
+      <c r="N38" s="4"/>
       <c r="O38" s="10"/>
     </row>
-    <row r="39" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A39" s="4" t="s">
+    <row r="39" ht="25" customHeight="1" spans="1:15">
+      <c r="A39" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="B39" s="5"/>
-      <c r="C39" s="5"/>
-      <c r="D39" s="5"/>
-      <c r="E39" s="5"/>
-      <c r="F39" s="5" t="s">
+      <c r="B39" s="4"/>
+      <c r="C39" s="4"/>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G39" s="5"/>
-      <c r="H39" s="5"/>
-      <c r="I39" s="5" t="s">
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="J39" s="5"/>
-      <c r="K39" s="5"/>
-      <c r="L39" s="5"/>
-      <c r="M39" s="5"/>
-      <c r="N39" s="5"/>
+      <c r="J39" s="4"/>
+      <c r="K39" s="4"/>
+      <c r="L39" s="4"/>
+      <c r="M39" s="4"/>
+      <c r="N39" s="4"/>
       <c r="O39" s="10"/>
     </row>
-    <row r="40" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A40" s="4" t="s">
+    <row r="40" ht="25" customHeight="1" spans="1:15">
+      <c r="A40" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="B40" s="5"/>
-      <c r="C40" s="5"/>
-      <c r="D40" s="5"/>
-      <c r="E40" s="5"/>
-      <c r="F40" s="5" t="s">
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G40" s="5"/>
-      <c r="H40" s="5"/>
-      <c r="I40" s="5" t="s">
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="J40" s="5"/>
-      <c r="K40" s="5"/>
-      <c r="L40" s="5"/>
-      <c r="M40" s="5"/>
-      <c r="N40" s="5"/>
+      <c r="J40" s="4"/>
+      <c r="K40" s="4"/>
+      <c r="L40" s="4"/>
+      <c r="M40" s="4"/>
+      <c r="N40" s="4"/>
       <c r="O40" s="10"/>
     </row>
-    <row r="41" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A41" s="4" t="s">
+    <row r="41" ht="25" customHeight="1" spans="1:15">
+      <c r="A41" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="B41" s="5"/>
-      <c r="C41" s="5"/>
-      <c r="D41" s="5"/>
-      <c r="E41" s="5"/>
-      <c r="F41" s="5" t="s">
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G41" s="5"/>
-      <c r="H41" s="5"/>
-      <c r="I41" s="5" t="s">
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="J41" s="5"/>
-      <c r="K41" s="5"/>
-      <c r="L41" s="5"/>
-      <c r="M41" s="5"/>
-      <c r="N41" s="5"/>
+      <c r="J41" s="4"/>
+      <c r="K41" s="4"/>
+      <c r="L41" s="4"/>
+      <c r="M41" s="4"/>
+      <c r="N41" s="4"/>
       <c r="O41" s="10"/>
     </row>
-    <row r="42" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A42" s="4" t="s">
+    <row r="42" ht="25" customHeight="1" spans="1:15">
+      <c r="A42" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="B42" s="5"/>
-      <c r="C42" s="5"/>
-      <c r="D42" s="5"/>
-      <c r="E42" s="5"/>
-      <c r="F42" s="5" t="s">
+      <c r="B42" s="4"/>
+      <c r="C42" s="4"/>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G42" s="5"/>
-      <c r="H42" s="5"/>
-      <c r="I42" s="5" t="s">
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="J42" s="5"/>
-      <c r="K42" s="5"/>
-      <c r="L42" s="5"/>
-      <c r="M42" s="5"/>
-      <c r="N42" s="5"/>
+      <c r="J42" s="4"/>
+      <c r="K42" s="4"/>
+      <c r="L42" s="4"/>
+      <c r="M42" s="4"/>
+      <c r="N42" s="4"/>
       <c r="O42" s="10"/>
     </row>
-    <row r="43" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A43" s="8" t="s">
+    <row r="43" ht="25" customHeight="1" spans="1:15">
+      <c r="A43" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="B43" s="9"/>
-      <c r="C43" s="9"/>
-      <c r="D43" s="9"/>
-      <c r="E43" s="9"/>
-      <c r="F43" s="5" t="s">
+      <c r="B43" s="8"/>
+      <c r="C43" s="8"/>
+      <c r="D43" s="8"/>
+      <c r="E43" s="8"/>
+      <c r="F43" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G43" s="9"/>
-      <c r="H43" s="9"/>
+      <c r="G43" s="8"/>
+      <c r="H43" s="8"/>
       <c r="I43" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="J43" s="9"/>
-      <c r="K43" s="5"/>
-      <c r="L43" s="5"/>
-      <c r="M43" s="5"/>
-      <c r="N43" s="5"/>
+      <c r="J43" s="8"/>
+      <c r="K43" s="4"/>
+      <c r="L43" s="4"/>
+      <c r="M43" s="4"/>
+      <c r="N43" s="4"/>
       <c r="O43" s="10"/>
     </row>
-    <row r="44" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A44" s="4" t="s">
+    <row r="44" ht="25" customHeight="1" spans="1:15">
+      <c r="A44" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="B44" s="5"/>
-      <c r="C44" s="5"/>
-      <c r="D44" s="5"/>
-      <c r="E44" s="5"/>
-      <c r="F44" s="5" t="s">
+      <c r="B44" s="4"/>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G44" s="5"/>
-      <c r="H44" s="5"/>
-      <c r="I44" s="5" t="s">
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="J44" s="5"/>
-      <c r="K44" s="5"/>
-      <c r="L44" s="5"/>
-      <c r="M44" s="5"/>
-      <c r="N44" s="5"/>
+      <c r="J44" s="4"/>
+      <c r="K44" s="4"/>
+      <c r="L44" s="4"/>
+      <c r="M44" s="4"/>
+      <c r="N44" s="4"/>
       <c r="O44" s="10"/>
     </row>
-    <row r="45" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A45" s="4" t="s">
+    <row r="45" ht="25" customHeight="1" spans="1:15">
+      <c r="A45" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="B45" s="5"/>
-      <c r="C45" s="5"/>
-      <c r="D45" s="5"/>
-      <c r="E45" s="5"/>
-      <c r="F45" s="5" t="s">
+      <c r="B45" s="4"/>
+      <c r="C45" s="4"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G45" s="5"/>
-      <c r="H45" s="5"/>
-      <c r="I45" s="5" t="s">
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="J45" s="5"/>
-      <c r="K45" s="5"/>
-      <c r="L45" s="5"/>
-      <c r="M45" s="5"/>
-      <c r="N45" s="5"/>
+      <c r="J45" s="4"/>
+      <c r="K45" s="4"/>
+      <c r="L45" s="4"/>
+      <c r="M45" s="4"/>
+      <c r="N45" s="4"/>
       <c r="O45" s="10"/>
     </row>
-    <row r="46" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A46" s="4" t="s">
+    <row r="46" ht="25" customHeight="1" spans="1:15">
+      <c r="A46" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="B46" s="5"/>
-      <c r="C46" s="5"/>
-      <c r="D46" s="5"/>
-      <c r="E46" s="5"/>
-      <c r="F46" s="5" t="s">
+      <c r="B46" s="4"/>
+      <c r="C46" s="4"/>
+      <c r="D46" s="4"/>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G46" s="5"/>
-      <c r="H46" s="5"/>
-      <c r="I46" s="5" t="s">
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="J46" s="5"/>
-      <c r="K46" s="5"/>
-      <c r="L46" s="5"/>
-      <c r="M46" s="5"/>
-      <c r="N46" s="5"/>
+      <c r="J46" s="4"/>
+      <c r="K46" s="4"/>
+      <c r="L46" s="4"/>
+      <c r="M46" s="4"/>
+      <c r="N46" s="4"/>
       <c r="O46" s="10"/>
     </row>
-    <row r="47" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A47" s="4" t="s">
+    <row r="47" ht="25" customHeight="1" spans="1:15">
+      <c r="A47" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="B47" s="5"/>
-      <c r="C47" s="5"/>
-      <c r="D47" s="5"/>
-      <c r="E47" s="5"/>
-      <c r="F47" s="5" t="s">
+      <c r="B47" s="4"/>
+      <c r="C47" s="4"/>
+      <c r="D47" s="4"/>
+      <c r="E47" s="4"/>
+      <c r="F47" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G47" s="5"/>
-      <c r="H47" s="5"/>
-      <c r="I47" s="5" t="s">
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="J47" s="5"/>
-      <c r="K47" s="5"/>
-      <c r="L47" s="5"/>
-      <c r="M47" s="5"/>
-      <c r="N47" s="5"/>
+      <c r="J47" s="4"/>
+      <c r="K47" s="4"/>
+      <c r="L47" s="4"/>
+      <c r="M47" s="4"/>
+      <c r="N47" s="4"/>
       <c r="O47" s="10"/>
     </row>
-    <row r="48" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A48" s="4" t="s">
+    <row r="48" ht="25" customHeight="1" spans="1:15">
+      <c r="A48" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="B48" s="5"/>
-      <c r="C48" s="5"/>
-      <c r="D48" s="5"/>
-      <c r="E48" s="5"/>
-      <c r="F48" s="5" t="s">
+      <c r="B48" s="4"/>
+      <c r="C48" s="4"/>
+      <c r="D48" s="4"/>
+      <c r="E48" s="4"/>
+      <c r="F48" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G48" s="5"/>
-      <c r="H48" s="5"/>
-      <c r="I48" s="5" t="s">
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="J48" s="5"/>
-      <c r="K48" s="5"/>
-      <c r="L48" s="5"/>
-      <c r="M48" s="5"/>
-      <c r="N48" s="5"/>
+      <c r="J48" s="4"/>
+      <c r="K48" s="4"/>
+      <c r="L48" s="4"/>
+      <c r="M48" s="4"/>
+      <c r="N48" s="4"/>
       <c r="O48" s="10"/>
     </row>
-    <row r="49" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A49" s="4" t="s">
+    <row r="49" ht="25" customHeight="1" spans="1:15">
+      <c r="A49" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="B49" s="5"/>
-      <c r="C49" s="5"/>
-      <c r="D49" s="5"/>
-      <c r="E49" s="5"/>
-      <c r="F49" s="5" t="s">
+      <c r="B49" s="4"/>
+      <c r="C49" s="4"/>
+      <c r="D49" s="4"/>
+      <c r="E49" s="4"/>
+      <c r="F49" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G49" s="5"/>
-      <c r="H49" s="5"/>
-      <c r="I49" s="5" t="s">
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="J49" s="5"/>
-      <c r="K49" s="5"/>
-      <c r="L49" s="5"/>
-      <c r="M49" s="5"/>
-      <c r="N49" s="5"/>
+      <c r="J49" s="4"/>
+      <c r="K49" s="4"/>
+      <c r="L49" s="4"/>
+      <c r="M49" s="4"/>
+      <c r="N49" s="4"/>
       <c r="O49" s="10"/>
     </row>
-    <row r="50" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A50" s="4" t="s">
+    <row r="50" ht="25" customHeight="1" spans="1:15">
+      <c r="A50" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="B50" s="5" t="s">
+      <c r="B50" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C50" s="11" t="s">
         <v>195</v>
       </c>
-      <c r="D50" s="5"/>
-      <c r="E50" s="5" t="s">
+      <c r="D50" s="4"/>
+      <c r="E50" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="F50" s="5" t="s">
+      <c r="F50" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G50" s="5"/>
+      <c r="G50" s="4"/>
       <c r="H50" s="12" t="s">
         <v>197</v>
       </c>
-      <c r="I50" s="5" t="s">
+      <c r="I50" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="J50" s="5"/>
-      <c r="K50" s="5"/>
-      <c r="L50" s="5"/>
-      <c r="M50" s="5"/>
-      <c r="N50" s="5"/>
+      <c r="J50" s="4"/>
+      <c r="K50" s="4"/>
+      <c r="L50" s="4"/>
+      <c r="M50" s="4"/>
+      <c r="N50" s="4"/>
       <c r="O50" s="10"/>
     </row>
-    <row r="51" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A51" s="4" t="s">
+    <row r="51" ht="25" customHeight="1" spans="1:15">
+      <c r="A51" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="B51" s="5" t="s">
+      <c r="B51" s="4" t="s">
         <v>116</v>
       </c>
       <c r="C51" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="D51" s="5"/>
-      <c r="E51" s="5" t="s">
+      <c r="D51" s="4"/>
+      <c r="E51" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F51" s="5" t="s">
+      <c r="F51" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G51" s="5"/>
+      <c r="G51" s="4"/>
       <c r="H51" s="12" t="s">
         <v>201</v>
       </c>
-      <c r="I51" s="5" t="s">
+      <c r="I51" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="J51" s="5"/>
-      <c r="K51" s="5"/>
-      <c r="L51" s="5"/>
-      <c r="M51" s="5"/>
-      <c r="N51" s="5"/>
+      <c r="J51" s="4"/>
+      <c r="K51" s="4"/>
+      <c r="L51" s="4"/>
+      <c r="M51" s="4"/>
+      <c r="N51" s="4"/>
       <c r="O51" s="10"/>
     </row>
-    <row r="52" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A52" s="4" t="s">
+    <row r="52" ht="25" customHeight="1" spans="1:15">
+      <c r="A52" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="B52" s="5" t="s">
+      <c r="B52" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C52" s="13" t="s">
         <v>204</v>
       </c>
-      <c r="D52" s="5"/>
-      <c r="E52" s="5" t="s">
+      <c r="D52" s="4"/>
+      <c r="E52" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="F52" s="5" t="s">
+      <c r="F52" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G52" s="5"/>
+      <c r="G52" s="4"/>
       <c r="H52" s="12" t="s">
         <v>205</v>
       </c>
-      <c r="I52" s="5" t="s">
+      <c r="I52" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="J52" s="5"/>
-      <c r="K52" s="5"/>
-      <c r="L52" s="5"/>
-      <c r="M52" s="5"/>
-      <c r="N52" s="5"/>
+      <c r="J52" s="4"/>
+      <c r="K52" s="4"/>
+      <c r="L52" s="4"/>
+      <c r="M52" s="4"/>
+      <c r="N52" s="4"/>
       <c r="O52" s="10"/>
     </row>
     <row r="53" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A53" s="4" t="s">
+      <c r="A53" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="B53" s="5" t="s">
+      <c r="B53" s="4" t="s">
         <v>208</v>
       </c>
       <c r="C53" s="11" t="s">
         <v>209</v>
       </c>
-      <c r="D53" s="5"/>
-      <c r="E53" s="5">
+      <c r="D53" s="4"/>
+      <c r="E53" s="4">
         <v>3</v>
       </c>
-      <c r="F53" s="5" t="s">
+      <c r="F53" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G53" s="5"/>
+      <c r="G53" s="4"/>
       <c r="H53" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="I53" s="5" t="s">
+      <c r="I53" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="J53" s="5"/>
-      <c r="K53" s="5"/>
-      <c r="L53" s="5"/>
-      <c r="M53" s="5"/>
-      <c r="N53" s="5"/>
+      <c r="J53" s="4"/>
+      <c r="K53" s="4"/>
+      <c r="L53" s="4"/>
+      <c r="M53" s="4"/>
+      <c r="N53" s="4"/>
       <c r="O53" s="10"/>
     </row>
-    <row r="54" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A54" s="4" t="s">
+    <row r="54" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A54" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="B54" s="5" t="s">
+      <c r="B54" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C54" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="D54" s="5"/>
-      <c r="E54" s="5" t="s">
+      <c r="D54" s="4"/>
+      <c r="E54" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="F54" s="5" t="s">
+      <c r="F54" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G54" s="5"/>
+      <c r="G54" s="4"/>
       <c r="H54" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="I54" s="5" t="s">
+      <c r="I54" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="J54" s="5"/>
-      <c r="K54" s="5"/>
-      <c r="L54" s="5"/>
-      <c r="M54" s="5"/>
-      <c r="N54" s="5"/>
+      <c r="J54" s="4"/>
+      <c r="K54" s="4"/>
+      <c r="L54" s="4"/>
+      <c r="M54" s="4"/>
+      <c r="N54" s="4"/>
       <c r="O54" s="10"/>
     </row>
     <row r="55" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A55" s="4" t="s">
+      <c r="A55" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="B55" s="5" t="s">
+      <c r="B55" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C55" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="D55" s="5"/>
-      <c r="E55" s="5">
+      <c r="D55" s="4"/>
+      <c r="E55" s="4">
         <v>18</v>
       </c>
-      <c r="F55" s="5" t="s">
+      <c r="F55" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G55" s="5"/>
+      <c r="G55" s="4"/>
       <c r="H55" s="12" t="s">
         <v>219</v>
       </c>
-      <c r="I55" s="5" t="s">
+      <c r="I55" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="J55" s="5"/>
-      <c r="K55" s="5"/>
-      <c r="L55" s="5"/>
-      <c r="M55" s="5"/>
-      <c r="N55" s="5"/>
+      <c r="J55" s="4"/>
+      <c r="K55" s="4"/>
+      <c r="L55" s="4"/>
+      <c r="M55" s="4"/>
+      <c r="N55" s="4"/>
       <c r="O55" s="10"/>
     </row>
-    <row r="56" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A56" s="4" t="s">
+    <row r="56" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A56" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="B56" s="5" t="s">
+      <c r="B56" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C56" s="11" t="s">
         <v>222</v>
       </c>
-      <c r="D56" s="5"/>
-      <c r="E56" s="5" t="s">
+      <c r="D56" s="4"/>
+      <c r="E56" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="F56" s="5" t="s">
+      <c r="F56" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G56" s="5"/>
+      <c r="G56" s="4"/>
       <c r="H56" s="12" t="s">
         <v>223</v>
       </c>
-      <c r="I56" s="5" t="s">
+      <c r="I56" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="J56" s="5"/>
-      <c r="K56" s="5"/>
-      <c r="L56" s="5"/>
-      <c r="M56" s="5"/>
-      <c r="N56" s="5"/>
+      <c r="J56" s="4"/>
+      <c r="K56" s="4"/>
+      <c r="L56" s="4"/>
+      <c r="M56" s="4"/>
+      <c r="N56" s="4"/>
       <c r="O56" s="10"/>
     </row>
-    <row r="57" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A57" s="4" t="s">
+    <row r="57" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A57" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="B57" s="5" t="s">
+      <c r="B57" s="4" t="s">
         <v>119</v>
       </c>
       <c r="C57" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="D57" s="5"/>
-      <c r="E57" s="5" t="s">
+      <c r="D57" s="4"/>
+      <c r="E57" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="F57" s="5" t="s">
+      <c r="F57" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G57" s="5"/>
+      <c r="G57" s="4"/>
       <c r="H57" s="12" t="s">
         <v>228</v>
       </c>
-      <c r="I57" s="5" t="s">
+      <c r="I57" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="J57" s="5"/>
-      <c r="K57" s="5"/>
-      <c r="L57" s="5"/>
-      <c r="M57" s="5"/>
-      <c r="N57" s="5"/>
+      <c r="J57" s="4"/>
+      <c r="K57" s="4"/>
+      <c r="L57" s="4"/>
+      <c r="M57" s="4"/>
+      <c r="N57" s="4"/>
       <c r="O57" s="10"/>
     </row>
     <row r="58" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A58" s="4" t="s">
+      <c r="A58" s="14" t="s">
         <v>230</v>
       </c>
-      <c r="B58" s="5" t="s">
+      <c r="B58" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C58" s="11" t="s">
+      <c r="C58" s="16" t="s">
         <v>231</v>
       </c>
-      <c r="D58" s="5"/>
-      <c r="E58" s="6">
+      <c r="D58" s="15"/>
+      <c r="E58" s="15">
         <v>6</v>
       </c>
-      <c r="F58" s="5" t="s">
+      <c r="F58" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="G58" s="5"/>
-      <c r="H58" s="12" t="s">
+      <c r="G58" s="15"/>
+      <c r="H58" s="17" t="s">
         <v>232</v>
       </c>
-      <c r="I58" s="5" t="s">
+      <c r="I58" s="15" t="s">
         <v>233</v>
       </c>
-      <c r="J58" s="5"/>
-      <c r="K58" s="5"/>
-      <c r="L58" s="5"/>
-      <c r="M58" s="5"/>
-      <c r="N58" s="5"/>
-      <c r="O58" s="10"/>
-    </row>
-    <row r="59" s="2" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A59" s="14"/>
-      <c r="B59" s="15"/>
-      <c r="C59" s="15"/>
-      <c r="D59" s="15"/>
-      <c r="E59" s="15"/>
-      <c r="F59" s="15"/>
-      <c r="G59" s="15"/>
-      <c r="H59" s="15"/>
-      <c r="I59" s="16"/>
-      <c r="J59" s="15"/>
-      <c r="K59" s="16"/>
-      <c r="L59" s="16"/>
-      <c r="M59" s="16"/>
-      <c r="N59" s="16"/>
-      <c r="O59" s="17"/>
+      <c r="J58" s="4"/>
+      <c r="K58" s="4"/>
+      <c r="L58" s="4"/>
+      <c r="M58" s="4"/>
+      <c r="N58" s="4"/>
+      <c r="O58" s="4"/>
+    </row>
+    <row r="59" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A59" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C59" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="D59" s="18"/>
+      <c r="E59" s="18">
+        <v>4</v>
+      </c>
+      <c r="F59" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G59" s="18"/>
+      <c r="H59" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="I59" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="J59" s="4"/>
+      <c r="K59" s="4"/>
+      <c r="L59" s="4"/>
+      <c r="M59" s="4"/>
+      <c r="N59" s="4"/>
+      <c r="O59" s="10"/>
     </row>
     <row r="60" ht="25" customHeight="1" spans="1:15">
-      <c r="A60" s="4"/>
-      <c r="B60" s="5"/>
-      <c r="C60" s="5"/>
-      <c r="D60" s="5"/>
-      <c r="E60" s="5"/>
-      <c r="F60" s="5"/>
-      <c r="G60" s="5"/>
-      <c r="H60" s="5"/>
-      <c r="I60" s="5"/>
-      <c r="J60" s="5"/>
-      <c r="K60" s="5"/>
-      <c r="L60" s="5"/>
-      <c r="M60" s="5"/>
-      <c r="N60" s="5"/>
+      <c r="A60" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="C60" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="D60" s="18"/>
+      <c r="E60" s="18">
+        <v>4</v>
+      </c>
+      <c r="F60" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G60" s="18"/>
+      <c r="H60" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="I60" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="J60" s="4"/>
+      <c r="K60" s="4"/>
+      <c r="L60" s="4"/>
+      <c r="M60" s="4"/>
+      <c r="N60" s="4"/>
       <c r="O60" s="10"/>
     </row>
     <row r="61" ht="25" customHeight="1" spans="1:15">
-      <c r="A61" s="4"/>
-      <c r="B61" s="5"/>
-      <c r="C61" s="5"/>
-      <c r="D61" s="5"/>
-      <c r="E61" s="5"/>
-      <c r="F61" s="5"/>
-      <c r="G61" s="5"/>
-      <c r="H61" s="5"/>
-      <c r="I61" s="5"/>
-      <c r="J61" s="5"/>
-      <c r="K61" s="5"/>
-      <c r="L61" s="5"/>
-      <c r="M61" s="5"/>
-      <c r="N61" s="5"/>
+      <c r="A61" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="C61" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="D61" s="18"/>
+      <c r="E61" s="18"/>
+      <c r="F61" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G61" s="18"/>
+      <c r="H61" s="12"/>
+      <c r="I61" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="J61" s="4"/>
+      <c r="K61" s="4"/>
+      <c r="L61" s="4"/>
+      <c r="M61" s="4"/>
+      <c r="N61" s="4"/>
       <c r="O61" s="10"/>
     </row>
     <row r="62" ht="25" customHeight="1" spans="1:15">
-      <c r="A62" s="4"/>
-      <c r="B62" s="5"/>
-      <c r="C62" s="5"/>
-      <c r="D62" s="5"/>
-      <c r="E62" s="5"/>
-      <c r="F62" s="5"/>
-      <c r="G62" s="5"/>
-      <c r="H62" s="5"/>
-      <c r="I62" s="5"/>
-      <c r="J62" s="5"/>
-      <c r="K62" s="5"/>
-      <c r="L62" s="5"/>
-      <c r="M62" s="5"/>
-      <c r="N62" s="5"/>
+      <c r="A62" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="C62" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="D62" s="18"/>
+      <c r="E62" s="18">
+        <v>7</v>
+      </c>
+      <c r="F62" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G62" s="18"/>
+      <c r="H62" s="12"/>
+      <c r="I62" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="J62" s="4"/>
+      <c r="K62" s="4"/>
+      <c r="L62" s="4"/>
+      <c r="M62" s="4"/>
+      <c r="N62" s="4"/>
       <c r="O62" s="10"/>
     </row>
     <row r="63" ht="25" customHeight="1" spans="1:15">
-      <c r="A63" s="4"/>
-      <c r="B63" s="5"/>
-      <c r="C63" s="5"/>
-      <c r="D63" s="5"/>
-      <c r="E63" s="5"/>
-      <c r="F63" s="5"/>
-      <c r="G63" s="5"/>
-      <c r="H63" s="5"/>
-      <c r="I63" s="5"/>
-      <c r="J63" s="5"/>
-      <c r="K63" s="5"/>
-      <c r="L63" s="5"/>
-      <c r="M63" s="5"/>
-      <c r="N63" s="5"/>
+      <c r="A63" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="C63" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="D63" s="18"/>
+      <c r="E63" s="18"/>
+      <c r="F63" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G63" s="18"/>
+      <c r="H63" s="12"/>
+      <c r="I63" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="J63" s="4"/>
+      <c r="K63" s="4"/>
+      <c r="L63" s="4"/>
+      <c r="M63" s="4"/>
+      <c r="N63" s="4"/>
       <c r="O63" s="10"/>
     </row>
     <row r="64" ht="25" customHeight="1" spans="1:15">
-      <c r="A64" s="4"/>
-      <c r="B64" s="5"/>
-      <c r="C64" s="5"/>
-      <c r="D64" s="5"/>
-      <c r="E64" s="5"/>
-      <c r="F64" s="5"/>
-      <c r="G64" s="5"/>
-      <c r="H64" s="5"/>
-      <c r="I64" s="5"/>
-      <c r="J64" s="5"/>
-      <c r="K64" s="5"/>
-      <c r="L64" s="5"/>
-      <c r="M64" s="5"/>
-      <c r="N64" s="5"/>
+      <c r="A64" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="C64" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="D64" s="18"/>
+      <c r="E64" s="18">
+        <v>4</v>
+      </c>
+      <c r="F64" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G64" s="18"/>
+      <c r="H64" s="12"/>
+      <c r="I64" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="J64" s="4"/>
+      <c r="K64" s="4"/>
+      <c r="L64" s="4"/>
+      <c r="M64" s="4"/>
+      <c r="N64" s="4"/>
       <c r="O64" s="10"/>
     </row>
     <row r="65" ht="25" customHeight="1" spans="1:15">
-      <c r="A65" s="4"/>
-      <c r="B65" s="5"/>
-      <c r="C65" s="5"/>
-      <c r="D65" s="5"/>
-      <c r="E65" s="5"/>
-      <c r="F65" s="5"/>
-      <c r="G65" s="5"/>
-      <c r="H65" s="5"/>
-      <c r="I65" s="5"/>
-      <c r="J65" s="5"/>
-      <c r="K65" s="5"/>
-      <c r="L65" s="5"/>
-      <c r="M65" s="5"/>
-      <c r="N65" s="5"/>
-      <c r="O65" s="10"/>
+      <c r="A65" s="3"/>
+      <c r="B65" s="4"/>
+      <c r="C65" s="4"/>
+      <c r="D65" s="4"/>
+      <c r="E65" s="4"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="4"/>
+      <c r="H65" s="4"/>
+      <c r="I65" s="20"/>
+      <c r="J65" s="4"/>
+      <c r="K65" s="4"/>
+      <c r="L65" s="4"/>
+      <c r="M65" s="4"/>
+      <c r="N65" s="4"/>
+      <c r="O65" s="4"/>
+    </row>
+    <row r="66" ht="25" customHeight="1" spans="1:15">
+      <c r="A66" s="3"/>
+      <c r="B66" s="4"/>
+      <c r="C66" s="4"/>
+      <c r="D66" s="4"/>
+      <c r="E66" s="4"/>
+      <c r="F66" s="19"/>
+      <c r="G66" s="4"/>
+      <c r="H66" s="4"/>
+      <c r="I66" s="20"/>
+      <c r="J66" s="4"/>
+      <c r="K66" s="4"/>
+      <c r="L66" s="4"/>
+      <c r="M66" s="4"/>
+      <c r="N66" s="4"/>
+      <c r="O66" s="4"/>
+    </row>
+    <row r="67" ht="25" customHeight="1" spans="1:15">
+      <c r="A67" s="3"/>
+      <c r="B67" s="4"/>
+      <c r="C67" s="4"/>
+      <c r="D67" s="4"/>
+      <c r="E67" s="4"/>
+      <c r="F67" s="19"/>
+      <c r="G67" s="4"/>
+      <c r="H67" s="4"/>
+      <c r="I67" s="20"/>
+      <c r="J67" s="4"/>
+      <c r="K67" s="4"/>
+      <c r="L67" s="4"/>
+      <c r="M67" s="4"/>
+      <c r="N67" s="4"/>
+      <c r="O67" s="4"/>
+    </row>
+    <row r="68" ht="25" customHeight="1" spans="1:15">
+      <c r="A68" s="3"/>
+      <c r="B68" s="4"/>
+      <c r="C68" s="4"/>
+      <c r="D68" s="4"/>
+      <c r="E68" s="4"/>
+      <c r="F68" s="19"/>
+      <c r="G68" s="4"/>
+      <c r="H68" s="4"/>
+      <c r="I68" s="20"/>
+      <c r="J68" s="4"/>
+      <c r="K68" s="4"/>
+      <c r="L68" s="4"/>
+      <c r="M68" s="4"/>
+      <c r="N68" s="4"/>
+      <c r="O68" s="4"/>
+    </row>
+    <row r="69" ht="25" customHeight="1" spans="1:15">
+      <c r="A69" s="3"/>
+      <c r="B69" s="4"/>
+      <c r="C69" s="4"/>
+      <c r="D69" s="4"/>
+      <c r="E69" s="4"/>
+      <c r="F69" s="19"/>
+      <c r="G69" s="4"/>
+      <c r="H69" s="4"/>
+      <c r="I69" s="20"/>
+      <c r="J69" s="4"/>
+      <c r="K69" s="4"/>
+      <c r="L69" s="4"/>
+      <c r="M69" s="4"/>
+      <c r="N69" s="4"/>
+      <c r="O69" s="4"/>
+    </row>
+    <row r="70" ht="25" customHeight="1" spans="1:15">
+      <c r="A70" s="3"/>
+      <c r="B70" s="4"/>
+      <c r="C70" s="4"/>
+      <c r="D70" s="4"/>
+      <c r="E70" s="4"/>
+      <c r="F70" s="19"/>
+      <c r="G70" s="4"/>
+      <c r="H70" s="4"/>
+      <c r="I70" s="20"/>
+      <c r="J70" s="4"/>
+      <c r="K70" s="4"/>
+      <c r="L70" s="4"/>
+      <c r="M70" s="4"/>
+      <c r="N70" s="4"/>
+      <c r="O70" s="4"/>
+    </row>
+    <row r="71" ht="25" customHeight="1" spans="1:15">
+      <c r="A71" s="3"/>
+      <c r="B71" s="4"/>
+      <c r="C71" s="4"/>
+      <c r="D71" s="4"/>
+      <c r="E71" s="4"/>
+      <c r="F71" s="19"/>
+      <c r="G71" s="4"/>
+      <c r="H71" s="4"/>
+      <c r="I71" s="20"/>
+      <c r="J71" s="4"/>
+      <c r="K71" s="4"/>
+      <c r="L71" s="4"/>
+      <c r="M71" s="4"/>
+      <c r="N71" s="4"/>
+      <c r="O71" s="4"/>
+    </row>
+    <row r="72" ht="25" customHeight="1" spans="1:15">
+      <c r="A72" s="3"/>
+      <c r="B72" s="4"/>
+      <c r="C72" s="4"/>
+      <c r="D72" s="4"/>
+      <c r="E72" s="4"/>
+      <c r="F72" s="19"/>
+      <c r="G72" s="4"/>
+      <c r="H72" s="4"/>
+      <c r="I72" s="20"/>
+      <c r="J72" s="4"/>
+      <c r="K72" s="4"/>
+      <c r="L72" s="4"/>
+      <c r="M72" s="4"/>
+      <c r="N72" s="4"/>
+      <c r="O72" s="4"/>
+    </row>
+    <row r="73" ht="25" customHeight="1" spans="1:15">
+      <c r="A73" s="3"/>
+      <c r="B73" s="4"/>
+      <c r="C73" s="4"/>
+      <c r="D73" s="4"/>
+      <c r="E73" s="4"/>
+      <c r="F73" s="19"/>
+      <c r="G73" s="4"/>
+      <c r="H73" s="4"/>
+      <c r="I73" s="20"/>
+      <c r="J73" s="4"/>
+      <c r="K73" s="4"/>
+      <c r="L73" s="4"/>
+      <c r="M73" s="4"/>
+      <c r="N73" s="4"/>
+      <c r="O73" s="4"/>
+    </row>
+    <row r="74" ht="25" customHeight="1" spans="1:15">
+      <c r="A74" s="3"/>
+      <c r="B74" s="4"/>
+      <c r="C74" s="4"/>
+      <c r="D74" s="4"/>
+      <c r="E74" s="4"/>
+      <c r="F74" s="19"/>
+      <c r="G74" s="4"/>
+      <c r="H74" s="4"/>
+      <c r="I74" s="20"/>
+      <c r="J74" s="4"/>
+      <c r="K74" s="4"/>
+      <c r="L74" s="4"/>
+      <c r="M74" s="4"/>
+      <c r="N74" s="4"/>
+      <c r="O74" s="4"/>
+    </row>
+    <row r="75" ht="25" customHeight="1" spans="1:15">
+      <c r="A75" s="3"/>
+      <c r="B75" s="4"/>
+      <c r="C75" s="4"/>
+      <c r="D75" s="4"/>
+      <c r="E75" s="4"/>
+      <c r="F75" s="19"/>
+      <c r="G75" s="4"/>
+      <c r="H75" s="4"/>
+      <c r="I75" s="20"/>
+      <c r="J75" s="4"/>
+      <c r="K75" s="4"/>
+      <c r="L75" s="4"/>
+      <c r="M75" s="4"/>
+      <c r="N75" s="4"/>
+      <c r="O75" s="4"/>
+    </row>
+    <row r="76" ht="25" customHeight="1" spans="1:15">
+      <c r="A76" s="3"/>
+      <c r="B76" s="4"/>
+      <c r="C76" s="4"/>
+      <c r="D76" s="4"/>
+      <c r="E76" s="4"/>
+      <c r="F76" s="19"/>
+      <c r="G76" s="4"/>
+      <c r="H76" s="4"/>
+      <c r="I76" s="20"/>
+      <c r="J76" s="4"/>
+      <c r="K76" s="4"/>
+      <c r="L76" s="4"/>
+      <c r="M76" s="4"/>
+      <c r="N76" s="4"/>
+      <c r="O76" s="4"/>
+    </row>
+    <row r="77" ht="25" customHeight="1" spans="1:15">
+      <c r="A77" s="3"/>
+      <c r="B77" s="4"/>
+      <c r="C77" s="4"/>
+      <c r="D77" s="4"/>
+      <c r="E77" s="4"/>
+      <c r="F77" s="19"/>
+      <c r="G77" s="4"/>
+      <c r="H77" s="4"/>
+      <c r="I77" s="20"/>
+      <c r="J77" s="4"/>
+      <c r="K77" s="4"/>
+      <c r="L77" s="4"/>
+      <c r="M77" s="4"/>
+      <c r="N77" s="4"/>
+      <c r="O77" s="4"/>
+    </row>
+    <row r="78" ht="25" customHeight="1" spans="1:15">
+      <c r="A78" s="3"/>
+      <c r="B78" s="4"/>
+      <c r="C78" s="4"/>
+      <c r="D78" s="4"/>
+      <c r="E78" s="4"/>
+      <c r="F78" s="19"/>
+      <c r="G78" s="4"/>
+      <c r="H78" s="4"/>
+      <c r="I78" s="20"/>
+      <c r="J78" s="4"/>
+      <c r="K78" s="4"/>
+      <c r="L78" s="4"/>
+      <c r="M78" s="4"/>
+      <c r="N78" s="4"/>
+      <c r="O78" s="4"/>
+    </row>
+    <row r="79" ht="25" customHeight="1" spans="1:15">
+      <c r="A79" s="3"/>
+      <c r="B79" s="4"/>
+      <c r="C79" s="4"/>
+      <c r="D79" s="4"/>
+      <c r="E79" s="4"/>
+      <c r="F79" s="19"/>
+      <c r="G79" s="4"/>
+      <c r="H79" s="4"/>
+      <c r="I79" s="20"/>
+      <c r="J79" s="4"/>
+      <c r="K79" s="4"/>
+      <c r="L79" s="4"/>
+      <c r="M79" s="4"/>
+      <c r="N79" s="4"/>
+      <c r="O79" s="4"/>
+    </row>
+    <row r="80" ht="25" customHeight="1" spans="1:15">
+      <c r="A80" s="3"/>
+      <c r="B80" s="4"/>
+      <c r="C80" s="4"/>
+      <c r="D80" s="4"/>
+      <c r="E80" s="4"/>
+      <c r="F80" s="19"/>
+      <c r="G80" s="4"/>
+      <c r="H80" s="4"/>
+      <c r="I80" s="20"/>
+      <c r="J80" s="4"/>
+      <c r="K80" s="4"/>
+      <c r="L80" s="4"/>
+      <c r="M80" s="4"/>
+      <c r="N80" s="4"/>
+      <c r="O80" s="4"/>
+    </row>
+    <row r="81" ht="25" customHeight="1" spans="1:15">
+      <c r="A81" s="3"/>
+      <c r="B81" s="4"/>
+      <c r="C81" s="4"/>
+      <c r="D81" s="4"/>
+      <c r="E81" s="4"/>
+      <c r="F81" s="19"/>
+      <c r="G81" s="4"/>
+      <c r="H81" s="4"/>
+      <c r="I81" s="20"/>
+      <c r="J81" s="4"/>
+      <c r="K81" s="4"/>
+      <c r="L81" s="4"/>
+      <c r="M81" s="4"/>
+      <c r="N81" s="4"/>
+      <c r="O81" s="4"/>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:O58" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="5">
-      <filters>
-        <filter val="更新中"/>
-      </filters>
-    </filterColumn>
     <extLst/>
   </autoFilter>
   <hyperlinks>

--- a/资源录入表新.xlsx
+++ b/资源录入表新.xlsx
@@ -10,7 +10,7 @@
     <sheet name="资源录入表" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">资源录入表!$A$1:$O$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">资源录入表!$A$1:$O$64</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="253">
   <si>
     <t>剧名</t>
   </si>
@@ -965,6 +965,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>动作</t>
     </r>
     <r>
@@ -1002,6 +1008,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="major"/>
+      </rPr>
       <t> </t>
     </r>
     <r>
@@ -1085,6 +1097,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>志怪</t>
     </r>
     <r>
@@ -1127,6 +1145,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>真人AI/志怪</t>
     </r>
     <r>
@@ -1330,6 +1354,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9.75"/>
+      <name val="Helvetica"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9.75"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="11"/>
       <name val="Helvetica"/>
       <charset val="134"/>
@@ -1341,16 +1375,6 @@
     </font>
     <font>
       <sz val="10.5"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9.75"/>
-      <name val="Helvetica"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9.75"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1852,7 +1876,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1868,12 +1892,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1898,22 +1922,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1968,7 +1980,15 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="18">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2162,25 +2182,25 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="6"/>
+      <tableStyleElement type="totalRow" dxfId="5"/>
+      <tableStyleElement type="firstColumn" dxfId="4"/>
+      <tableStyleElement type="lastColumn" dxfId="3"/>
+      <tableStyleElement type="firstRowStripe" dxfId="2"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="1"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="17"/>
+      <tableStyleElement type="totalRow" dxfId="16"/>
+      <tableStyleElement type="firstRowStripe" dxfId="15"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="14"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="13"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="11"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="10"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="9"/>
+      <tableStyleElement type="pageFieldValues" dxfId="8"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -2448,7 +2468,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:O81"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
@@ -2514,7 +2534,7 @@
         <v>14</v>
       </c>
       <c r="E2" s="5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>15</v>
@@ -2537,7 +2557,7 @@
       <c r="N2" s="4"/>
       <c r="O2" s="4"/>
     </row>
-    <row r="3" ht="25" customHeight="1" spans="1:15">
+    <row r="3" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A3" s="3" t="s">
         <v>19</v>
       </c>
@@ -2574,7 +2594,7 @@
       <c r="N3" s="4"/>
       <c r="O3" s="4"/>
     </row>
-    <row r="4" ht="25" customHeight="1" spans="1:15">
+    <row r="4" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A4" s="3" t="s">
         <v>26</v>
       </c>
@@ -2611,7 +2631,7 @@
       <c r="N4" s="4"/>
       <c r="O4" s="4"/>
     </row>
-    <row r="5" ht="25" customHeight="1" spans="1:15">
+    <row r="5" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A5" s="3" t="s">
         <v>32</v>
       </c>
@@ -2648,7 +2668,7 @@
       <c r="N5" s="4"/>
       <c r="O5" s="4"/>
     </row>
-    <row r="6" ht="25" customHeight="1" spans="1:15">
+    <row r="6" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A6" s="3" t="s">
         <v>38</v>
       </c>
@@ -2685,7 +2705,7 @@
       <c r="N6" s="4"/>
       <c r="O6" s="4"/>
     </row>
-    <row r="7" ht="25" customHeight="1" spans="1:15">
+    <row r="7" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A7" s="3" t="s">
         <v>44</v>
       </c>
@@ -2722,7 +2742,7 @@
       <c r="N7" s="4"/>
       <c r="O7" s="4"/>
     </row>
-    <row r="8" ht="25" customHeight="1" spans="1:15">
+    <row r="8" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A8" s="3" t="s">
         <v>50</v>
       </c>
@@ -2759,7 +2779,7 @@
       <c r="N8" s="4"/>
       <c r="O8" s="4"/>
     </row>
-    <row r="9" ht="25" customHeight="1" spans="1:15">
+    <row r="9" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A9" s="3" t="s">
         <v>56</v>
       </c>
@@ -2796,7 +2816,7 @@
       <c r="N9" s="4"/>
       <c r="O9" s="4"/>
     </row>
-    <row r="10" ht="25" customHeight="1" spans="1:15">
+    <row r="10" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A10" s="3" t="s">
         <v>62</v>
       </c>
@@ -2833,7 +2853,7 @@
       <c r="N10" s="4"/>
       <c r="O10" s="4"/>
     </row>
-    <row r="11" ht="25" customHeight="1" spans="1:15">
+    <row r="11" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A11" s="3" t="s">
         <v>68</v>
       </c>
@@ -2870,7 +2890,7 @@
       <c r="N11" s="4"/>
       <c r="O11" s="4"/>
     </row>
-    <row r="12" ht="25" customHeight="1" spans="1:15">
+    <row r="12" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A12" s="3" t="s">
         <v>74</v>
       </c>
@@ -2907,7 +2927,7 @@
       <c r="N12" s="4"/>
       <c r="O12" s="4"/>
     </row>
-    <row r="13" ht="25" customHeight="1" spans="1:15">
+    <row r="13" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A13" s="3" t="s">
         <v>78</v>
       </c>
@@ -2944,7 +2964,7 @@
       <c r="N13" s="4"/>
       <c r="O13" s="4"/>
     </row>
-    <row r="14" ht="25" customHeight="1" spans="1:15">
+    <row r="14" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A14" s="3" t="s">
         <v>84</v>
       </c>
@@ -2981,7 +3001,7 @@
       <c r="N14" s="4"/>
       <c r="O14" s="4"/>
     </row>
-    <row r="15" ht="25" customHeight="1" spans="1:15">
+    <row r="15" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A15" s="3" t="s">
         <v>89</v>
       </c>
@@ -3018,7 +3038,7 @@
       <c r="N15" s="4"/>
       <c r="O15" s="4"/>
     </row>
-    <row r="16" ht="25" customHeight="1" spans="1:15">
+    <row r="16" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A16" s="3" t="s">
         <v>94</v>
       </c>
@@ -3055,7 +3075,7 @@
       <c r="N16" s="4"/>
       <c r="O16" s="4"/>
     </row>
-    <row r="17" ht="25" customHeight="1" spans="1:15">
+    <row r="17" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A17" s="3" t="s">
         <v>99</v>
       </c>
@@ -3092,7 +3112,7 @@
       <c r="N17" s="4"/>
       <c r="O17" s="4"/>
     </row>
-    <row r="18" ht="25" customHeight="1" spans="1:15">
+    <row r="18" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A18" s="3" t="s">
         <v>104</v>
       </c>
@@ -3129,7 +3149,7 @@
       <c r="N18" s="4"/>
       <c r="O18" s="4"/>
     </row>
-    <row r="19" ht="25" customHeight="1" spans="1:15">
+    <row r="19" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A19" s="3" t="s">
         <v>110</v>
       </c>
@@ -3166,7 +3186,7 @@
       <c r="N19" s="4"/>
       <c r="O19" s="4"/>
     </row>
-    <row r="20" ht="25" customHeight="1" spans="1:15">
+    <row r="20" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A20" s="3" t="s">
         <v>115</v>
       </c>
@@ -3201,7 +3221,7 @@
       <c r="N20" s="4"/>
       <c r="O20" s="4"/>
     </row>
-    <row r="21" ht="25" customHeight="1" spans="1:15">
+    <row r="21" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A21" s="3" t="s">
         <v>120</v>
       </c>
@@ -3236,7 +3256,7 @@
       <c r="N21" s="4"/>
       <c r="O21" s="4"/>
     </row>
-    <row r="22" ht="25" customHeight="1" spans="1:15">
+    <row r="22" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A22" s="3" t="s">
         <v>123</v>
       </c>
@@ -3249,7 +3269,7 @@
       <c r="D22" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="E22" s="6" t="s">
         <v>125</v>
       </c>
       <c r="F22" s="4" t="s">
@@ -3271,7 +3291,7 @@
       <c r="N22" s="4"/>
       <c r="O22" s="4"/>
     </row>
-    <row r="23" ht="25" customHeight="1" spans="1:15">
+    <row r="23" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A23" s="7" t="s">
         <v>127</v>
       </c>
@@ -3306,7 +3326,7 @@
       <c r="N23" s="8"/>
       <c r="O23" s="4"/>
     </row>
-    <row r="24" ht="25" customHeight="1" spans="1:15">
+    <row r="24" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A24" s="3" t="s">
         <v>130</v>
       </c>
@@ -3319,7 +3339,7 @@
       <c r="D24" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="E24" s="6" t="s">
         <v>132</v>
       </c>
       <c r="F24" s="4" t="s">
@@ -3343,7 +3363,7 @@
       <c r="N24" s="4"/>
       <c r="O24" s="10"/>
     </row>
-    <row r="25" ht="25" customHeight="1" spans="1:15">
+    <row r="25" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A25" s="3" t="s">
         <v>136</v>
       </c>
@@ -3378,7 +3398,7 @@
       <c r="N25" s="4"/>
       <c r="O25" s="10"/>
     </row>
-    <row r="26" ht="25" customHeight="1" spans="1:15">
+    <row r="26" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A26" s="3" t="s">
         <v>139</v>
       </c>
@@ -3426,11 +3446,11 @@
       <c r="D27" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E27" s="4">
-        <v>10</v>
+      <c r="E27" s="5" t="s">
+        <v>125</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G27" s="4">
         <v>2025</v>
@@ -3461,8 +3481,8 @@
       <c r="D28" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E28" s="4">
-        <v>2</v>
+      <c r="E28" s="5">
+        <v>4</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>15</v>
@@ -3497,7 +3517,7 @@
         <v>14</v>
       </c>
       <c r="E29" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>15</v>
@@ -3518,7 +3538,7 @@
       <c r="N29" s="4"/>
       <c r="O29" s="10"/>
     </row>
-    <row r="30" ht="25" customHeight="1" spans="1:15">
+    <row r="30" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A30" s="3" t="s">
         <v>151</v>
       </c>
@@ -3555,7 +3575,7 @@
       <c r="N30" s="4"/>
       <c r="O30" s="10"/>
     </row>
-    <row r="31" ht="25" customHeight="1" spans="1:15">
+    <row r="31" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A31" s="3" t="s">
         <v>156</v>
       </c>
@@ -3586,7 +3606,7 @@
       <c r="C32" s="4"/>
       <c r="D32" s="4"/>
       <c r="E32" s="5">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>15</v>
@@ -3603,7 +3623,7 @@
       <c r="N32" s="4"/>
       <c r="O32" s="10"/>
     </row>
-    <row r="33" ht="25" customHeight="1" spans="1:15">
+    <row r="33" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A33" s="3" t="s">
         <v>160</v>
       </c>
@@ -3626,7 +3646,7 @@
       <c r="N33" s="4"/>
       <c r="O33" s="10"/>
     </row>
-    <row r="34" ht="25" customHeight="1" spans="1:15">
+    <row r="34" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A34" s="3" t="s">
         <v>162</v>
       </c>
@@ -3649,7 +3669,7 @@
       <c r="N34" s="4"/>
       <c r="O34" s="10"/>
     </row>
-    <row r="35" ht="25" customHeight="1" spans="1:15">
+    <row r="35" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A35" s="3" t="s">
         <v>164</v>
       </c>
@@ -3672,7 +3692,7 @@
       <c r="N35" s="4"/>
       <c r="O35" s="10"/>
     </row>
-    <row r="36" ht="25" customHeight="1" spans="1:15">
+    <row r="36" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A36" s="3" t="s">
         <v>166</v>
       </c>
@@ -3695,7 +3715,7 @@
       <c r="N36" s="4"/>
       <c r="O36" s="10"/>
     </row>
-    <row r="37" ht="25" customHeight="1" spans="1:15">
+    <row r="37" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A37" s="3" t="s">
         <v>168</v>
       </c>
@@ -3718,7 +3738,7 @@
       <c r="N37" s="4"/>
       <c r="O37" s="10"/>
     </row>
-    <row r="38" ht="25" customHeight="1" spans="1:15">
+    <row r="38" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A38" s="3" t="s">
         <v>170</v>
       </c>
@@ -3741,7 +3761,7 @@
       <c r="N38" s="4"/>
       <c r="O38" s="10"/>
     </row>
-    <row r="39" ht="25" customHeight="1" spans="1:15">
+    <row r="39" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A39" s="3" t="s">
         <v>172</v>
       </c>
@@ -3764,7 +3784,7 @@
       <c r="N39" s="4"/>
       <c r="O39" s="10"/>
     </row>
-    <row r="40" ht="25" customHeight="1" spans="1:15">
+    <row r="40" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A40" s="3" t="s">
         <v>174</v>
       </c>
@@ -3787,7 +3807,7 @@
       <c r="N40" s="4"/>
       <c r="O40" s="10"/>
     </row>
-    <row r="41" ht="25" customHeight="1" spans="1:15">
+    <row r="41" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A41" s="3" t="s">
         <v>176</v>
       </c>
@@ -3810,7 +3830,7 @@
       <c r="N41" s="4"/>
       <c r="O41" s="10"/>
     </row>
-    <row r="42" ht="25" customHeight="1" spans="1:15">
+    <row r="42" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A42" s="3" t="s">
         <v>178</v>
       </c>
@@ -3833,7 +3853,7 @@
       <c r="N42" s="4"/>
       <c r="O42" s="10"/>
     </row>
-    <row r="43" ht="25" customHeight="1" spans="1:15">
+    <row r="43" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A43" s="7" t="s">
         <v>180</v>
       </c>
@@ -3856,7 +3876,7 @@
       <c r="N43" s="4"/>
       <c r="O43" s="10"/>
     </row>
-    <row r="44" ht="25" customHeight="1" spans="1:15">
+    <row r="44" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A44" s="3" t="s">
         <v>182</v>
       </c>
@@ -3879,7 +3899,7 @@
       <c r="N44" s="4"/>
       <c r="O44" s="10"/>
     </row>
-    <row r="45" ht="25" customHeight="1" spans="1:15">
+    <row r="45" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A45" s="3" t="s">
         <v>184</v>
       </c>
@@ -3902,7 +3922,7 @@
       <c r="N45" s="4"/>
       <c r="O45" s="10"/>
     </row>
-    <row r="46" ht="25" customHeight="1" spans="1:15">
+    <row r="46" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A46" s="3" t="s">
         <v>186</v>
       </c>
@@ -3925,7 +3945,7 @@
       <c r="N46" s="4"/>
       <c r="O46" s="10"/>
     </row>
-    <row r="47" ht="25" customHeight="1" spans="1:15">
+    <row r="47" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A47" s="3" t="s">
         <v>188</v>
       </c>
@@ -3948,7 +3968,7 @@
       <c r="N47" s="4"/>
       <c r="O47" s="10"/>
     </row>
-    <row r="48" ht="25" customHeight="1" spans="1:15">
+    <row r="48" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A48" s="3" t="s">
         <v>190</v>
       </c>
@@ -3971,7 +3991,7 @@
       <c r="N48" s="4"/>
       <c r="O48" s="10"/>
     </row>
-    <row r="49" ht="25" customHeight="1" spans="1:15">
+    <row r="49" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A49" s="3" t="s">
         <v>192</v>
       </c>
@@ -3994,7 +4014,7 @@
       <c r="N49" s="4"/>
       <c r="O49" s="10"/>
     </row>
-    <row r="50" ht="25" customHeight="1" spans="1:15">
+    <row r="50" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A50" s="3" t="s">
         <v>194</v>
       </c>
@@ -4025,7 +4045,7 @@
       <c r="N50" s="4"/>
       <c r="O50" s="10"/>
     </row>
-    <row r="51" ht="25" customHeight="1" spans="1:15">
+    <row r="51" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A51" s="3" t="s">
         <v>199</v>
       </c>
@@ -4056,7 +4076,7 @@
       <c r="N51" s="4"/>
       <c r="O51" s="10"/>
     </row>
-    <row r="52" ht="25" customHeight="1" spans="1:15">
+    <row r="52" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A52" s="3" t="s">
         <v>203</v>
       </c>
@@ -4087,7 +4107,7 @@
       <c r="N52" s="4"/>
       <c r="O52" s="10"/>
     </row>
-    <row r="53" customFormat="1" ht="25" customHeight="1" spans="1:15">
+    <row r="53" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A53" s="3" t="s">
         <v>207</v>
       </c>
@@ -4118,7 +4138,7 @@
       <c r="N53" s="4"/>
       <c r="O53" s="10"/>
     </row>
-    <row r="54" customFormat="1" ht="25" customHeight="1" spans="1:15">
+    <row r="54" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A54" s="3" t="s">
         <v>212</v>
       </c>
@@ -4160,8 +4180,8 @@
         <v>218</v>
       </c>
       <c r="D55" s="4"/>
-      <c r="E55" s="4">
-        <v>18</v>
+      <c r="E55" s="5">
+        <v>20</v>
       </c>
       <c r="F55" s="4" t="s">
         <v>15</v>
@@ -4180,7 +4200,7 @@
       <c r="N55" s="4"/>
       <c r="O55" s="10"/>
     </row>
-    <row r="56" customFormat="1" ht="25" customHeight="1" spans="1:15">
+    <row r="56" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A56" s="3" t="s">
         <v>221</v>
       </c>
@@ -4211,7 +4231,7 @@
       <c r="N56" s="4"/>
       <c r="O56" s="10"/>
     </row>
-    <row r="57" customFormat="1" ht="25" customHeight="1" spans="1:15">
+    <row r="57" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A57" s="3" t="s">
         <v>225</v>
       </c>
@@ -4246,24 +4266,24 @@
       <c r="A58" s="14" t="s">
         <v>230</v>
       </c>
-      <c r="B58" s="15" t="s">
+      <c r="B58" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C58" s="16" t="s">
+      <c r="C58" s="15" t="s">
         <v>231</v>
       </c>
-      <c r="D58" s="15"/>
-      <c r="E58" s="15">
-        <v>6</v>
-      </c>
-      <c r="F58" s="15" t="s">
+      <c r="D58" s="5"/>
+      <c r="E58" s="5">
+        <v>8</v>
+      </c>
+      <c r="F58" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G58" s="15"/>
-      <c r="H58" s="17" t="s">
+      <c r="G58" s="5"/>
+      <c r="H58" s="16" t="s">
         <v>232</v>
       </c>
-      <c r="I58" s="15" t="s">
+      <c r="I58" s="5" t="s">
         <v>233</v>
       </c>
       <c r="J58" s="4"/>
@@ -4273,7 +4293,7 @@
       <c r="N58" s="4"/>
       <c r="O58" s="4"/>
     </row>
-    <row r="59" customFormat="1" ht="25" customHeight="1" spans="1:15">
+    <row r="59" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A59" s="3" t="s">
         <v>234</v>
       </c>
@@ -4283,14 +4303,14 @@
       <c r="C59" s="11" t="s">
         <v>235</v>
       </c>
-      <c r="D59" s="18"/>
-      <c r="E59" s="18">
+      <c r="D59" s="11"/>
+      <c r="E59" s="11">
         <v>4</v>
       </c>
       <c r="F59" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="G59" s="18"/>
+      <c r="G59" s="11"/>
       <c r="H59" s="12" t="s">
         <v>236</v>
       </c>
@@ -4304,7 +4324,7 @@
       <c r="N59" s="4"/>
       <c r="O59" s="10"/>
     </row>
-    <row r="60" ht="25" customHeight="1" spans="1:15">
+    <row r="60" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A60" s="3" t="s">
         <v>238</v>
       </c>
@@ -4314,14 +4334,14 @@
       <c r="C60" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="D60" s="18"/>
-      <c r="E60" s="18">
+      <c r="D60" s="11"/>
+      <c r="E60" s="11">
         <v>4</v>
       </c>
       <c r="F60" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="G60" s="18"/>
+      <c r="G60" s="11"/>
       <c r="H60" s="12" t="s">
         <v>240</v>
       </c>
@@ -4335,7 +4355,7 @@
       <c r="N60" s="4"/>
       <c r="O60" s="10"/>
     </row>
-    <row r="61" ht="25" customHeight="1" spans="1:15">
+    <row r="61" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A61" s="3" t="s">
         <v>242</v>
       </c>
@@ -4345,12 +4365,12 @@
       <c r="C61" s="11" t="s">
         <v>243</v>
       </c>
-      <c r="D61" s="18"/>
-      <c r="E61" s="18"/>
+      <c r="D61" s="11"/>
+      <c r="E61" s="11"/>
       <c r="F61" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G61" s="18"/>
+      <c r="G61" s="11"/>
       <c r="H61" s="12"/>
       <c r="I61" s="4" t="s">
         <v>244</v>
@@ -4362,7 +4382,7 @@
       <c r="N61" s="4"/>
       <c r="O61" s="10"/>
     </row>
-    <row r="62" ht="25" customHeight="1" spans="1:15">
+    <row r="62" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A62" s="3" t="s">
         <v>245</v>
       </c>
@@ -4372,14 +4392,14 @@
       <c r="C62" s="11" t="s">
         <v>246</v>
       </c>
-      <c r="D62" s="18"/>
-      <c r="E62" s="18">
+      <c r="D62" s="11"/>
+      <c r="E62" s="11">
         <v>7</v>
       </c>
       <c r="F62" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="G62" s="18"/>
+      <c r="G62" s="11"/>
       <c r="H62" s="12"/>
       <c r="I62" s="4" t="s">
         <v>247</v>
@@ -4391,7 +4411,7 @@
       <c r="N62" s="4"/>
       <c r="O62" s="10"/>
     </row>
-    <row r="63" ht="25" customHeight="1" spans="1:15">
+    <row r="63" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A63" s="3" t="s">
         <v>248</v>
       </c>
@@ -4401,12 +4421,12 @@
       <c r="C63" s="11" t="s">
         <v>243</v>
       </c>
-      <c r="D63" s="18"/>
-      <c r="E63" s="18"/>
+      <c r="D63" s="11"/>
+      <c r="E63" s="11"/>
       <c r="F63" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G63" s="18"/>
+      <c r="G63" s="11"/>
       <c r="H63" s="12"/>
       <c r="I63" s="4" t="s">
         <v>249</v>
@@ -4418,7 +4438,7 @@
       <c r="N63" s="4"/>
       <c r="O63" s="10"/>
     </row>
-    <row r="64" ht="25" customHeight="1" spans="1:15">
+    <row r="64" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A64" s="3" t="s">
         <v>250</v>
       </c>
@@ -4428,14 +4448,14 @@
       <c r="C64" s="11" t="s">
         <v>251</v>
       </c>
-      <c r="D64" s="18"/>
-      <c r="E64" s="18">
+      <c r="D64" s="11"/>
+      <c r="E64" s="11">
         <v>4</v>
       </c>
       <c r="F64" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="G64" s="18"/>
+      <c r="G64" s="11"/>
       <c r="H64" s="12"/>
       <c r="I64" s="4" t="s">
         <v>252</v>
@@ -4453,10 +4473,10 @@
       <c r="C65" s="4"/>
       <c r="D65" s="4"/>
       <c r="E65" s="4"/>
-      <c r="F65" s="19"/>
+      <c r="F65" s="6"/>
       <c r="G65" s="4"/>
       <c r="H65" s="4"/>
-      <c r="I65" s="20"/>
+      <c r="I65" s="4"/>
       <c r="J65" s="4"/>
       <c r="K65" s="4"/>
       <c r="L65" s="4"/>
@@ -4470,10 +4490,10 @@
       <c r="C66" s="4"/>
       <c r="D66" s="4"/>
       <c r="E66" s="4"/>
-      <c r="F66" s="19"/>
+      <c r="F66" s="6"/>
       <c r="G66" s="4"/>
       <c r="H66" s="4"/>
-      <c r="I66" s="20"/>
+      <c r="I66" s="4"/>
       <c r="J66" s="4"/>
       <c r="K66" s="4"/>
       <c r="L66" s="4"/>
@@ -4487,10 +4507,10 @@
       <c r="C67" s="4"/>
       <c r="D67" s="4"/>
       <c r="E67" s="4"/>
-      <c r="F67" s="19"/>
+      <c r="F67" s="6"/>
       <c r="G67" s="4"/>
       <c r="H67" s="4"/>
-      <c r="I67" s="20"/>
+      <c r="I67" s="4"/>
       <c r="J67" s="4"/>
       <c r="K67" s="4"/>
       <c r="L67" s="4"/>
@@ -4504,10 +4524,10 @@
       <c r="C68" s="4"/>
       <c r="D68" s="4"/>
       <c r="E68" s="4"/>
-      <c r="F68" s="19"/>
+      <c r="F68" s="6"/>
       <c r="G68" s="4"/>
       <c r="H68" s="4"/>
-      <c r="I68" s="20"/>
+      <c r="I68" s="4"/>
       <c r="J68" s="4"/>
       <c r="K68" s="4"/>
       <c r="L68" s="4"/>
@@ -4521,10 +4541,10 @@
       <c r="C69" s="4"/>
       <c r="D69" s="4"/>
       <c r="E69" s="4"/>
-      <c r="F69" s="19"/>
+      <c r="F69" s="6"/>
       <c r="G69" s="4"/>
       <c r="H69" s="4"/>
-      <c r="I69" s="20"/>
+      <c r="I69" s="4"/>
       <c r="J69" s="4"/>
       <c r="K69" s="4"/>
       <c r="L69" s="4"/>
@@ -4538,10 +4558,10 @@
       <c r="C70" s="4"/>
       <c r="D70" s="4"/>
       <c r="E70" s="4"/>
-      <c r="F70" s="19"/>
+      <c r="F70" s="6"/>
       <c r="G70" s="4"/>
       <c r="H70" s="4"/>
-      <c r="I70" s="20"/>
+      <c r="I70" s="4"/>
       <c r="J70" s="4"/>
       <c r="K70" s="4"/>
       <c r="L70" s="4"/>
@@ -4555,10 +4575,10 @@
       <c r="C71" s="4"/>
       <c r="D71" s="4"/>
       <c r="E71" s="4"/>
-      <c r="F71" s="19"/>
+      <c r="F71" s="6"/>
       <c r="G71" s="4"/>
       <c r="H71" s="4"/>
-      <c r="I71" s="20"/>
+      <c r="I71" s="4"/>
       <c r="J71" s="4"/>
       <c r="K71" s="4"/>
       <c r="L71" s="4"/>
@@ -4572,10 +4592,10 @@
       <c r="C72" s="4"/>
       <c r="D72" s="4"/>
       <c r="E72" s="4"/>
-      <c r="F72" s="19"/>
+      <c r="F72" s="6"/>
       <c r="G72" s="4"/>
       <c r="H72" s="4"/>
-      <c r="I72" s="20"/>
+      <c r="I72" s="4"/>
       <c r="J72" s="4"/>
       <c r="K72" s="4"/>
       <c r="L72" s="4"/>
@@ -4589,10 +4609,10 @@
       <c r="C73" s="4"/>
       <c r="D73" s="4"/>
       <c r="E73" s="4"/>
-      <c r="F73" s="19"/>
+      <c r="F73" s="6"/>
       <c r="G73" s="4"/>
       <c r="H73" s="4"/>
-      <c r="I73" s="20"/>
+      <c r="I73" s="4"/>
       <c r="J73" s="4"/>
       <c r="K73" s="4"/>
       <c r="L73" s="4"/>
@@ -4606,10 +4626,10 @@
       <c r="C74" s="4"/>
       <c r="D74" s="4"/>
       <c r="E74" s="4"/>
-      <c r="F74" s="19"/>
+      <c r="F74" s="6"/>
       <c r="G74" s="4"/>
       <c r="H74" s="4"/>
-      <c r="I74" s="20"/>
+      <c r="I74" s="4"/>
       <c r="J74" s="4"/>
       <c r="K74" s="4"/>
       <c r="L74" s="4"/>
@@ -4623,10 +4643,10 @@
       <c r="C75" s="4"/>
       <c r="D75" s="4"/>
       <c r="E75" s="4"/>
-      <c r="F75" s="19"/>
+      <c r="F75" s="6"/>
       <c r="G75" s="4"/>
       <c r="H75" s="4"/>
-      <c r="I75" s="20"/>
+      <c r="I75" s="4"/>
       <c r="J75" s="4"/>
       <c r="K75" s="4"/>
       <c r="L75" s="4"/>
@@ -4640,10 +4660,10 @@
       <c r="C76" s="4"/>
       <c r="D76" s="4"/>
       <c r="E76" s="4"/>
-      <c r="F76" s="19"/>
+      <c r="F76" s="6"/>
       <c r="G76" s="4"/>
       <c r="H76" s="4"/>
-      <c r="I76" s="20"/>
+      <c r="I76" s="4"/>
       <c r="J76" s="4"/>
       <c r="K76" s="4"/>
       <c r="L76" s="4"/>
@@ -4657,10 +4677,10 @@
       <c r="C77" s="4"/>
       <c r="D77" s="4"/>
       <c r="E77" s="4"/>
-      <c r="F77" s="19"/>
+      <c r="F77" s="6"/>
       <c r="G77" s="4"/>
       <c r="H77" s="4"/>
-      <c r="I77" s="20"/>
+      <c r="I77" s="4"/>
       <c r="J77" s="4"/>
       <c r="K77" s="4"/>
       <c r="L77" s="4"/>
@@ -4674,10 +4694,10 @@
       <c r="C78" s="4"/>
       <c r="D78" s="4"/>
       <c r="E78" s="4"/>
-      <c r="F78" s="19"/>
+      <c r="F78" s="6"/>
       <c r="G78" s="4"/>
       <c r="H78" s="4"/>
-      <c r="I78" s="20"/>
+      <c r="I78" s="4"/>
       <c r="J78" s="4"/>
       <c r="K78" s="4"/>
       <c r="L78" s="4"/>
@@ -4691,10 +4711,10 @@
       <c r="C79" s="4"/>
       <c r="D79" s="4"/>
       <c r="E79" s="4"/>
-      <c r="F79" s="19"/>
+      <c r="F79" s="6"/>
       <c r="G79" s="4"/>
       <c r="H79" s="4"/>
-      <c r="I79" s="20"/>
+      <c r="I79" s="4"/>
       <c r="J79" s="4"/>
       <c r="K79" s="4"/>
       <c r="L79" s="4"/>
@@ -4708,10 +4728,10 @@
       <c r="C80" s="4"/>
       <c r="D80" s="4"/>
       <c r="E80" s="4"/>
-      <c r="F80" s="19"/>
+      <c r="F80" s="6"/>
       <c r="G80" s="4"/>
       <c r="H80" s="4"/>
-      <c r="I80" s="20"/>
+      <c r="I80" s="4"/>
       <c r="J80" s="4"/>
       <c r="K80" s="4"/>
       <c r="L80" s="4"/>
@@ -4725,10 +4745,10 @@
       <c r="C81" s="4"/>
       <c r="D81" s="4"/>
       <c r="E81" s="4"/>
-      <c r="F81" s="19"/>
+      <c r="F81" s="6"/>
       <c r="G81" s="4"/>
       <c r="H81" s="4"/>
-      <c r="I81" s="20"/>
+      <c r="I81" s="4"/>
       <c r="J81" s="4"/>
       <c r="K81" s="4"/>
       <c r="L81" s="4"/>
@@ -4737,7 +4757,10 @@
       <c r="O81" s="4"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:O58" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:O64" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="4">
+      <colorFilter dxfId="0"/>
+    </filterColumn>
     <extLst/>
   </autoFilter>
   <hyperlinks>

--- a/资源录入表新.xlsx
+++ b/资源录入表新.xlsx
@@ -1,16 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\RedFox平台热点分析\狄仁杰系列电影\yingshi-site\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12255" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="资源录入表" sheetId="1" r:id="rId1"/>
+    <sheet name="资源录入表 (2)" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">资源录入表!$A$1:$O$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'资源录入表 (2)'!$A$1:$I$19</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="265">
   <si>
     <t>剧名</t>
   </si>
@@ -65,19 +72,43 @@
     <t>简介</t>
   </si>
   <si>
+    <t>九门2</t>
+  </si>
+  <si>
+    <t>热播剧</t>
+  </si>
+  <si>
+    <t>剧情 / 奇幻 / 冒险</t>
+  </si>
+  <si>
+    <t>1080P</t>
+  </si>
+  <si>
+    <t>更新中</t>
+  </si>
+  <si>
+    <t xml:space="preserve">陈伟霆/陈瑶/曾舜晞/王茂蕾/王奕婷/李乃文/释小龙/应灏铭/季肖冰/胡耘豪/徐正溪 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1V8VWsfDlUm1NhfIO2dMB0Q 提取码: a5m2 </t>
+  </si>
+  <si>
+    <t>御廷谣</t>
+  </si>
+  <si>
+    <t>爱情/古装</t>
+  </si>
+  <si>
+    <t xml:space="preserve">吴谨言 / 陈哲远 / 梁永棋 / 赵昭仪 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1o9b-WmhM1MJozXH7W07kdA 提取码: 2dh5 </t>
+  </si>
+  <si>
     <t>这一秒过火</t>
   </si>
   <si>
-    <t>热播剧</t>
-  </si>
-  <si>
-    <t>民国/虐恋/2026</t>
-  </si>
-  <si>
-    <t>1080P</t>
-  </si>
-  <si>
-    <t>更新中</t>
+    <t>民国/虐恋</t>
   </si>
   <si>
     <t>张凌赫/王楚然/付辛博</t>
@@ -89,6 +120,207 @@
     <t>改编自匪我思存小说，民国虐恋剧</t>
   </si>
   <si>
+    <t>兵自风中来</t>
+  </si>
+  <si>
+    <t>剧情/动作</t>
+  </si>
+  <si>
+    <t> 欧豪/蓝盈莹/丁勇岱/史兰芽/刘奕君 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1sg514-ZHQvotLItTuc9AXA 提取码: e4nt </t>
+  </si>
+  <si>
+    <t>折金枝</t>
+  </si>
+  <si>
+    <t>古装/权谋</t>
+  </si>
+  <si>
+    <t>张赫/徐轸轸</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1C11-1DhDULL7qOeytJ9LTw 提取码: fp76 </t>
+  </si>
+  <si>
+    <t>李熊猫</t>
+  </si>
+  <si>
+    <t>动漫</t>
+  </si>
+  <si>
+    <t>喜剧/动作/动画/奇幻</t>
+  </si>
+  <si>
+    <t>齐璇/小连杀/ 魏一凡/ 朱祎</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1paCsTOrm0Myk2sgF96UkcA 提取码: zb9w </t>
+  </si>
+  <si>
+    <t>东大高武学院</t>
+  </si>
+  <si>
+    <t>动作/动画/奇幻</t>
+  </si>
+  <si>
+    <t> 云惟一/万舒心/刘琮/张惠霖/李铮</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1xgB5NP2JFKwnC0tnE_vV-Q 提取码: grug </t>
+  </si>
+  <si>
+    <t>给你梦想</t>
+  </si>
+  <si>
+    <t>韩剧</t>
+  </si>
+  <si>
+    <t>喜剧/爱情</t>
+  </si>
+  <si>
+    <t>黄寅烨/李惠利</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1hu1DbgYjceKybWF8nd2MtA 提取码: sw7v </t>
+  </si>
+  <si>
+    <t>绘梦婚礼</t>
+  </si>
+  <si>
+    <t>泰剧</t>
+  </si>
+  <si>
+    <t>韩剧/爱情</t>
+  </si>
+  <si>
+    <t>邝玲玲/珙恩娜帕·瑟塔拉塔那彭</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1x2-yT0DcRgCtCvnYSO-KIg 提取码: ggm6 </t>
+  </si>
+  <si>
+    <t>毛骨悚然的恋爱</t>
+  </si>
+  <si>
+    <t>朴恩斌/梁世宗/邕圣祐</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1C_0yn98Bq6a52Wt_XaMEgw 提取码: 7363 </t>
+  </si>
+  <si>
+    <t>公寓黑风暴</t>
+  </si>
+  <si>
+    <t>剧情/喜剧</t>
+  </si>
+  <si>
+    <t> 池晟/河允庆/朴炳垠/文素利/郑顺元</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1uERe5JKbQkRo4R8FOLCyoQ 提取码: bt69 </t>
+  </si>
+  <si>
+    <t>婚姻之后</t>
+  </si>
+  <si>
+    <t> 剧情/爱情/惊悚</t>
+  </si>
+  <si>
+    <t xml:space="preserve">南宫珉/李雪 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/14X6ahDyNcojmd6yDB2sTPg 提取码: nw74 </t>
+  </si>
+  <si>
+    <t>杀人者的购物中心2</t>
+  </si>
+  <si>
+    <t> 剧情/动作/悬疑/惊悚</t>
+  </si>
+  <si>
+    <t>李栋旭/金慧埈/赵汉善/玄理</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1Q-cu6oXhrCF8LB-uKvPEzw 提取码: sb2x </t>
+  </si>
+  <si>
+    <t>韩剧 杀人者的购物中心第二季</t>
+  </si>
+  <si>
+    <t>罪与爱</t>
+  </si>
+  <si>
+    <t>短片/同性</t>
+  </si>
+  <si>
+    <t>金贤叙/郑明哲</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1jcYGkulnR65vgKIM9W8d_w 提取码: gwxm </t>
+  </si>
+  <si>
+    <t>神的游戏</t>
+  </si>
+  <si>
+    <t>AI真人格斗番</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1IpJblba6yx_ULc6AQ9FKzQ 提取码: 7zcj </t>
+  </si>
+  <si>
+    <t>枭</t>
+  </si>
+  <si>
+    <t>真人AI/志怪 #法术</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1Ll1Z9gnTo6af9Z7H3zOLBw 提取码: vrby </t>
+  </si>
+  <si>
+    <t>楚人美游记</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>志怪</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> #</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>法术</t>
+    </r>
+  </si>
+  <si>
+    <t>已完结</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1hQKA0Oc-JJIQ4XxdY13YmQ 提取码: j1h2 </t>
+  </si>
+  <si>
+    <t>天庭三大反骨仔系列</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1xQB5aGDByNbjg5T13pwr7w 提取码: eui7 </t>
+  </si>
+  <si>
     <t>百花杀</t>
   </si>
   <si>
@@ -98,9 +330,6 @@
     <t>36集全</t>
   </si>
   <si>
-    <t>已完结</t>
-  </si>
-  <si>
     <t>孟子义/何与</t>
   </si>
   <si>
@@ -377,33 +606,12 @@
     <t>又名莫道桑榆晚 芒果TV</t>
   </si>
   <si>
-    <t>给你梦想</t>
+    <t>检察官室的提案</t>
   </si>
   <si>
     <t>外剧</t>
   </si>
   <si>
-    <t>韩剧/励志</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1hu1DbgYjceKybWF8nd2MtA 提取码: sw7v </t>
-  </si>
-  <si>
-    <t>韩剧</t>
-  </si>
-  <si>
-    <t>绘梦婚礼</t>
-  </si>
-  <si>
-    <t>韩剧/爱情</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1x2-yT0DcRgCtCvnYSO-KIg 提取码: ggm6 </t>
-  </si>
-  <si>
-    <t>检察官室的提案</t>
-  </si>
-  <si>
     <t>韩剧/律政</t>
   </si>
   <si>
@@ -413,15 +621,6 @@
     <t xml:space="preserve">链接: https://pan.baidu.com/s/1jvr5zI23AKq4GmnhIAUcQA 提取码: tb3q </t>
   </si>
   <si>
-    <t>毛骨悚然的恋爱</t>
-  </si>
-  <si>
-    <t>韩剧/悬疑/爱情</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1C_0yn98Bq6a52Wt_XaMEgw 提取码: 7363 </t>
-  </si>
-  <si>
     <t>明天也要上班</t>
   </si>
   <si>
@@ -440,24 +639,6 @@
     <t>韩剧 姜美娜主演</t>
   </si>
   <si>
-    <t>公寓黑风暴</t>
-  </si>
-  <si>
-    <t>韩剧/悬疑/犯罪</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1uERe5JKbQkRo4R8FOLCyoQ 提取码: bt69 </t>
-  </si>
-  <si>
-    <t>婚姻之后</t>
-  </si>
-  <si>
-    <t>韩剧/爱情/婚姻</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/14X6ahDyNcojmd6yDB2sTPg 提取码: nw74 </t>
-  </si>
-  <si>
     <t>金特务·本色回归</t>
   </si>
   <si>
@@ -467,24 +648,6 @@
     <t xml:space="preserve">链接: https://pan.baidu.com/s/1Fb4YyOJqWJU5Bnrjpp5Hhg 提取码: e65c </t>
   </si>
   <si>
-    <t>杀人者的购物中心2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1Q-cu6oXhrCF8LB-uKvPEzw 提取码: sb2x </t>
-  </si>
-  <si>
-    <t>韩剧 杀人者的购物中心第二季</t>
-  </si>
-  <si>
-    <t>罪与爱</t>
-  </si>
-  <si>
-    <t>韩剧/犯罪/爱情</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1jcYGkulnR65vgKIM9W8d_w 提取码: gwxm </t>
-  </si>
-  <si>
     <t>聪明镇</t>
   </si>
   <si>
@@ -504,12 +667,6 @@
   </si>
   <si>
     <t xml:space="preserve">链接: https://pan.baidu.com/s/1zpmelbjW0vTTsJXTpweg8w 提取码: 5brf </t>
-  </si>
-  <si>
-    <t>兵自风中来</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1sg514-ZHQvotLItTuc9AXA 提取码: e4nt </t>
   </si>
   <si>
     <t>克制升温</t>
@@ -756,21 +913,6 @@
     <t xml:space="preserve">链接: https://pan.baidu.com/s/11-pn6zJgsVQp3MufmiSEnA 提取码: y9i6 </t>
   </si>
   <si>
-    <t>李熊猫</t>
-  </si>
-  <si>
-    <t>动漫</t>
-  </si>
-  <si>
-    <t>喜剧/动作/动画/奇幻</t>
-  </si>
-  <si>
-    <t>齐璇 / 小连杀 / 魏一凡 / 朱祎</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1paCsTOrm0Myk2sgF96UkcA 提取码: zb9w </t>
-  </si>
-  <si>
     <t>春日之地</t>
   </si>
   <si>
@@ -800,42 +942,6 @@
   </si>
   <si>
     <t xml:space="preserve">链接: https://pan.baidu.com/s/16GRCZK3niBDnbG3ND6mVtw 提取码: xjma </t>
-  </si>
-  <si>
-    <t>折金枝</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>古装</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Helvetica"/>
-        <charset val="134"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>权谋</t>
-    </r>
-  </si>
-  <si>
-    <t>张赫 / 徐轸轸</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1C11-1DhDULL7qOeytJ9LTw 提取码: fp76 </t>
   </si>
   <si>
     <t>逆爱成河</t>
@@ -913,201 +1019,15 @@
     <t xml:space="preserve">链接: https://pan.baidu.com/s/1wvdr54elVEWkt-5xM-qUKQ 提取码: udkd </t>
   </si>
   <si>
-    <t>御廷谣</t>
+    <t>剧情/奇幻/冒险</t>
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>爱情</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Helvetica"/>
-        <charset val="134"/>
-      </rPr>
-      <t> / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>古装</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">吴谨言 / 陈哲远 / 梁永棋 / 赵昭仪 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1o9b-WmhM1MJozXH7W07kdA 提取码: 2dh5 </t>
-  </si>
-  <si>
-    <t>九门2</t>
-  </si>
-  <si>
-    <t>剧情 / 奇幻 / 冒险</t>
-  </si>
-  <si>
-    <t>陈伟霆 / 陈瑶 / 曾舜晞 / 王茂蕾 / 王奕婷 / 李乃文 / 释小龙 / 应灏铭 / 季肖冰 / 胡耘豪 / 徐正溪 / 章涛 / 王祖一</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1V8VWsfDlUm1NhfIO2dMB0Q 提取码: a5m2 </t>
-  </si>
-  <si>
-    <t>东大高武学院</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>动作</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.75"/>
-        <rFont val="Helvetica"/>
-        <charset val="134"/>
-      </rPr>
-      <t> / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.75"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>动画</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.75"/>
-        <rFont val="Helvetica"/>
-        <charset val="134"/>
-      </rPr>
-      <t> / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.75"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>奇幻</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="major"/>
-      </rPr>
-      <t> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.75"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>云惟一</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.75"/>
-        <rFont val="Helvetica"/>
-        <charset val="134"/>
-      </rPr>
-      <t> / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.75"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>万舒心</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.75"/>
-        <rFont val="Helvetica"/>
-        <charset val="134"/>
-      </rPr>
-      <t> / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.75"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>刘琮</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.75"/>
-        <rFont val="Helvetica"/>
-        <charset val="134"/>
-      </rPr>
-      <t> / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.75"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>张惠霖</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.75"/>
-        <rFont val="Helvetica"/>
-        <charset val="134"/>
-      </rPr>
-      <t> / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.75"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>李铮</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1xgB5NP2JFKwnC0tnE_vV-Q 提取码: grug </t>
-  </si>
-  <si>
-    <t>楚人美游记</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>志怪</t>
     </r>
     <r>
       <rPr>
-        <sz val="10.5"/>
+        <sz val="12"/>
         <rFont val="Arial"/>
         <charset val="134"/>
       </rPr>
@@ -1115,63 +1035,12 @@
     </r>
     <r>
       <rPr>
-        <sz val="10.5"/>
+        <sz val="12"/>
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
       <t>法术</t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1hQKA0Oc-JJIQ4XxdY13YmQ 提取码: j1h2 </t>
-  </si>
-  <si>
-    <t>神的游戏</t>
-  </si>
-  <si>
-    <t>AI真人格斗番</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1IpJblba6yx_ULc6AQ9FKzQ 提取码: 7zcj </t>
-  </si>
-  <si>
-    <t>天庭三大反骨仔系列</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1xQB5aGDByNbjg5T13pwr7w 提取码: eui7 </t>
-  </si>
-  <si>
-    <t>枭</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>真人AI/志怪</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> #</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>法术</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1Ll1Z9gnTo6af9Z7H3zOLBw 提取码: vrby </t>
   </si>
 </sst>
 </file>
@@ -1184,10 +1053,35 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1197,12 +1091,6 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="major"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1354,16 +1242,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9.75"/>
-      <name val="Helvetica"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9.75"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="11"/>
       <name val="Helvetica"/>
       <charset val="134"/>
@@ -1375,6 +1253,16 @@
     </font>
     <font>
       <sz val="10.5"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1746,137 +1634,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1886,15 +1774,45 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1904,28 +1822,34 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1980,15 +1904,7 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="18">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2182,25 +2098,25 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="7"/>
-      <tableStyleElement type="headerRow" dxfId="6"/>
-      <tableStyleElement type="totalRow" dxfId="5"/>
-      <tableStyleElement type="firstColumn" dxfId="4"/>
-      <tableStyleElement type="lastColumn" dxfId="3"/>
-      <tableStyleElement type="firstRowStripe" dxfId="2"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="1"/>
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="17"/>
-      <tableStyleElement type="totalRow" dxfId="16"/>
-      <tableStyleElement type="firstRowStripe" dxfId="15"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="14"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="13"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="11"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="10"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="9"/>
-      <tableStyleElement type="pageFieldValues" dxfId="8"/>
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -2468,21 +2384,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr filterMode="1"/>
+  <sheetPr/>
   <dimension ref="A1:O81"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="17.625" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="1"/>
-    <col min="3" max="3" width="18.625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="30.5833333333333" style="1" customWidth="1"/>
     <col min="4" max="7" width="9" style="1"/>
-    <col min="8" max="8" width="31.375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="80.2916666666667" style="1" customWidth="1"/>
     <col min="9" max="9" width="74.25" style="1" customWidth="1"/>
-    <col min="10" max="15" width="9" style="1"/>
+    <col min="10" max="10" width="9" style="1"/>
+    <col min="11" max="11" width="9.99166666666667" style="1" customWidth="1"/>
+    <col min="12" max="12" width="44.85" style="1" customWidth="1"/>
+    <col min="13" max="15" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
@@ -2521,1959 +2440,2019 @@
       <c r="O1" s="4"/>
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:15">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="5">
-        <v>23</v>
-      </c>
-      <c r="F2" s="4" t="s">
+      <c r="D2" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="8">
+        <v>4</v>
+      </c>
+      <c r="F2" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="4">
+      <c r="G2" s="24">
         <v>2026</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="8" t="s">
         <v>17</v>
       </c>
       <c r="J2" s="4"/>
       <c r="K2" s="4"/>
-      <c r="L2" s="4" t="s">
-        <v>18</v>
-      </c>
+      <c r="L2" s="4"/>
       <c r="M2" s="4"/>
       <c r="N2" s="4"/>
       <c r="O2" s="4"/>
     </row>
-    <row r="3" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A3" s="3" t="s">
+    <row r="3" ht="25" customHeight="1" spans="1:15">
+      <c r="A3" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="24">
+        <v>8</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="24">
+        <v>2026</v>
+      </c>
+      <c r="H3" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="4" t="s">
+      <c r="I3" s="8" t="s">
         <v>21</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" s="4">
-        <v>2026</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>24</v>
       </c>
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
-      <c r="L3" s="4" t="s">
-        <v>25</v>
-      </c>
+      <c r="L3" s="4"/>
       <c r="M3" s="4"/>
       <c r="N3" s="4"/>
       <c r="O3" s="4"/>
     </row>
-    <row r="4" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A4" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B4" s="4" t="s">
+    <row r="4" ht="25" customHeight="1" spans="1:15">
+      <c r="A4" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4" s="4">
-        <v>2025</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>30</v>
+      <c r="C4" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="24">
+        <v>23</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="24">
+        <v>2026</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>25</v>
       </c>
       <c r="J4" s="4"/>
       <c r="K4" s="4"/>
       <c r="L4" s="4" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="M4" s="4"/>
       <c r="N4" s="4"/>
       <c r="O4" s="4"/>
     </row>
-    <row r="5" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A5" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B5" s="4" t="s">
+    <row r="5" ht="25" customHeight="1" spans="1:15">
+      <c r="A5" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G5" s="4">
+      <c r="C5" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="24">
+        <v>18</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="24">
         <v>2026</v>
       </c>
-      <c r="H5" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>36</v>
+      <c r="H5" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>30</v>
       </c>
       <c r="J5" s="4"/>
       <c r="K5" s="4"/>
-      <c r="L5" s="4" t="s">
-        <v>37</v>
-      </c>
+      <c r="L5" s="4"/>
       <c r="M5" s="4"/>
       <c r="N5" s="4"/>
       <c r="O5" s="4"/>
     </row>
-    <row r="6" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A6" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B6" s="4" t="s">
+    <row r="6" ht="25" customHeight="1" spans="1:15">
+      <c r="A6" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" s="4">
+      <c r="C6" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="24">
+        <v>20</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="24">
         <v>2026</v>
       </c>
-      <c r="H6" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>42</v>
+      <c r="H6" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="J6" s="4"/>
       <c r="K6" s="4"/>
-      <c r="L6" s="4" t="s">
-        <v>43</v>
-      </c>
+      <c r="L6" s="4"/>
       <c r="M6" s="4"/>
       <c r="N6" s="4"/>
       <c r="O6" s="4"/>
     </row>
-    <row r="7" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A7" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G7" s="4">
-        <v>2025</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>48</v>
+    <row r="7" ht="25" customHeight="1" spans="1:15">
+      <c r="A7" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="24">
+        <v>3</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="24">
+        <v>2026</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>39</v>
       </c>
       <c r="J7" s="4"/>
       <c r="K7" s="4"/>
-      <c r="L7" s="4" t="s">
-        <v>49</v>
-      </c>
+      <c r="L7" s="4"/>
       <c r="M7" s="4"/>
       <c r="N7" s="4"/>
       <c r="O7" s="4"/>
     </row>
-    <row r="8" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A8" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8" s="4">
+    <row r="8" ht="25" customHeight="1" spans="1:15">
+      <c r="A8" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="8">
+        <v>4</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" s="24">
         <v>2026</v>
       </c>
-      <c r="H8" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>54</v>
+      <c r="H8" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>43</v>
       </c>
       <c r="J8" s="4"/>
       <c r="K8" s="4"/>
-      <c r="L8" s="4" t="s">
-        <v>55</v>
-      </c>
+      <c r="L8" s="4"/>
       <c r="M8" s="4"/>
       <c r="N8" s="4"/>
       <c r="O8" s="4"/>
     </row>
-    <row r="9" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A9" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G9" s="4">
+    <row r="9" ht="25" customHeight="1" spans="1:15">
+      <c r="A9" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="24">
+        <v>6</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" s="24">
         <v>2026</v>
       </c>
-      <c r="H9" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>60</v>
+      <c r="H9" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>48</v>
       </c>
       <c r="J9" s="4"/>
       <c r="K9" s="4"/>
       <c r="L9" s="4" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="M9" s="4"/>
       <c r="N9" s="4"/>
       <c r="O9" s="4"/>
     </row>
-    <row r="10" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A10" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G10" s="4">
-        <v>2024</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>66</v>
+    <row r="10" ht="25" customHeight="1" spans="1:15">
+      <c r="A10" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="24">
+        <v>6</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" s="24">
+        <v>2026</v>
+      </c>
+      <c r="H10" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="I10" s="10" t="s">
+        <v>53</v>
       </c>
       <c r="J10" s="4"/>
       <c r="K10" s="4"/>
       <c r="L10" s="4" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="M10" s="4"/>
       <c r="N10" s="4"/>
       <c r="O10" s="4"/>
     </row>
-    <row r="11" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A11" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G11" s="4">
-        <v>2024</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>72</v>
+    <row r="11" ht="25" customHeight="1" spans="1:15">
+      <c r="A11" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="24">
+        <v>4</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" s="24">
+        <v>2026</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="I11" s="10" t="s">
+        <v>56</v>
       </c>
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>
       <c r="L11" s="4" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="M11" s="4"/>
       <c r="N11" s="4"/>
       <c r="O11" s="4"/>
     </row>
-    <row r="12" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A12" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G12" s="4">
+    <row r="12" ht="25" customHeight="1" spans="1:15">
+      <c r="A12" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="24">
+        <v>6</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="24">
         <v>2026</v>
       </c>
-      <c r="H12" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>76</v>
+      <c r="H12" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>60</v>
       </c>
       <c r="J12" s="4"/>
       <c r="K12" s="4"/>
       <c r="L12" s="4" t="s">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="M12" s="4"/>
       <c r="N12" s="4"/>
       <c r="O12" s="4"/>
     </row>
-    <row r="13" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A13" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G13" s="4">
-        <v>2025</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>82</v>
+    <row r="13" ht="25" customHeight="1" spans="1:15">
+      <c r="A13" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="24">
+        <v>8</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" s="24">
+        <v>2026</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>64</v>
       </c>
       <c r="J13" s="4"/>
       <c r="K13" s="4"/>
       <c r="L13" s="4" t="s">
-        <v>83</v>
+        <v>45</v>
       </c>
       <c r="M13" s="4"/>
       <c r="N13" s="4"/>
       <c r="O13" s="4"/>
     </row>
-    <row r="14" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A14" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G14" s="4">
+    <row r="14" ht="25" customHeight="1" spans="1:15">
+      <c r="A14" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" s="24">
+        <v>4</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14" s="24">
         <v>2026</v>
       </c>
-      <c r="H14" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>87</v>
+      <c r="H14" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>68</v>
       </c>
       <c r="J14" s="4"/>
       <c r="K14" s="4"/>
       <c r="L14" s="4" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="M14" s="4"/>
       <c r="N14" s="4"/>
       <c r="O14" s="4"/>
     </row>
-    <row r="15" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A15" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G15" s="4">
+    <row r="15" ht="25" customHeight="1" spans="1:15">
+      <c r="A15" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C15" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" s="24">
+        <v>8</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" s="24">
         <v>2026</v>
       </c>
-      <c r="H15" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>92</v>
+      <c r="H15" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>73</v>
       </c>
       <c r="J15" s="4"/>
       <c r="K15" s="4"/>
       <c r="L15" s="4" t="s">
-        <v>93</v>
+        <v>45</v>
       </c>
       <c r="M15" s="4"/>
       <c r="N15" s="4"/>
       <c r="O15" s="4"/>
     </row>
-    <row r="16" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A16" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G16" s="4">
+    <row r="16" ht="25" customHeight="1" spans="1:15">
+      <c r="A16" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" s="8">
+        <v>7</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16" s="24">
         <v>2026</v>
       </c>
-      <c r="H16" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="I16" s="4" t="s">
-        <v>97</v>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8" t="s">
+        <v>76</v>
       </c>
       <c r="J16" s="4"/>
       <c r="K16" s="4"/>
-      <c r="L16" s="4" t="s">
-        <v>98</v>
-      </c>
+      <c r="L16" s="4"/>
       <c r="M16" s="4"/>
       <c r="N16" s="4"/>
       <c r="O16" s="4"/>
     </row>
-    <row r="17" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A17" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G17" s="4">
-        <v>2025</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>102</v>
+    <row r="17" ht="25" customHeight="1" spans="1:15">
+      <c r="A17" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E17" s="8">
+        <v>4</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G17" s="24">
+        <v>2026</v>
+      </c>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8" t="s">
+        <v>79</v>
       </c>
       <c r="J17" s="4"/>
       <c r="K17" s="4"/>
-      <c r="L17" s="4" t="s">
-        <v>103</v>
-      </c>
+      <c r="L17" s="4"/>
       <c r="M17" s="4"/>
       <c r="N17" s="4"/>
       <c r="O17" s="4"/>
     </row>
-    <row r="18" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A18" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G18" s="4">
+    <row r="18" ht="25" customHeight="1" spans="1:15">
+      <c r="A18" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="27"/>
+      <c r="F18" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="G18" s="24">
         <v>2026</v>
       </c>
-      <c r="H18" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>108</v>
+      <c r="H18" s="8"/>
+      <c r="I18" s="14" t="s">
+        <v>83</v>
       </c>
       <c r="J18" s="4"/>
       <c r="K18" s="4"/>
-      <c r="L18" s="4" t="s">
-        <v>109</v>
-      </c>
+      <c r="L18" s="4"/>
       <c r="M18" s="4"/>
       <c r="N18" s="4"/>
-      <c r="O18" s="4"/>
-    </row>
-    <row r="19" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A19" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G19" s="4">
+      <c r="O18" s="28"/>
+    </row>
+    <row r="19" ht="25" customHeight="1" spans="1:15">
+      <c r="A19" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19" s="27"/>
+      <c r="F19" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="G19" s="24">
         <v>2026</v>
       </c>
-      <c r="H19" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>113</v>
+      <c r="H19" s="8"/>
+      <c r="I19" s="14" t="s">
+        <v>85</v>
       </c>
       <c r="J19" s="4"/>
       <c r="K19" s="4"/>
-      <c r="L19" s="4" t="s">
-        <v>114</v>
-      </c>
+      <c r="L19" s="4"/>
       <c r="M19" s="4"/>
       <c r="N19" s="4"/>
-      <c r="O19" s="4"/>
-    </row>
-    <row r="20" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A20" s="3" t="s">
-        <v>115</v>
+      <c r="O19" s="28"/>
+    </row>
+    <row r="20" ht="25" customHeight="1" spans="1:15">
+      <c r="A20" s="15" t="s">
+        <v>86</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>116</v>
+        <v>12</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>117</v>
+        <v>87</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E20" s="6">
-        <v>6</v>
+      <c r="E20" s="4" t="s">
+        <v>88</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>15</v>
+        <v>82</v>
       </c>
       <c r="G20" s="4">
-        <v>2025</v>
-      </c>
-      <c r="H20" s="4"/>
+        <v>2026</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>89</v>
+      </c>
       <c r="I20" s="1" t="s">
-        <v>118</v>
+        <v>90</v>
       </c>
       <c r="J20" s="4"/>
       <c r="K20" s="4"/>
       <c r="L20" s="4" t="s">
-        <v>119</v>
+        <v>91</v>
       </c>
       <c r="M20" s="4"/>
       <c r="N20" s="4"/>
       <c r="O20" s="4"/>
     </row>
-    <row r="21" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A21" s="3" t="s">
-        <v>120</v>
+    <row r="21" ht="25" customHeight="1" spans="1:15">
+      <c r="A21" s="15" t="s">
+        <v>92</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>116</v>
+        <v>12</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>121</v>
+        <v>93</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E21" s="6">
-        <v>6</v>
+      <c r="E21" s="4" t="s">
+        <v>94</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>15</v>
+        <v>82</v>
       </c>
       <c r="G21" s="4">
         <v>2025</v>
       </c>
-      <c r="H21" s="4"/>
+      <c r="H21" s="4" t="s">
+        <v>95</v>
+      </c>
       <c r="I21" s="1" t="s">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="J21" s="4"/>
       <c r="K21" s="4"/>
       <c r="L21" s="4" t="s">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="M21" s="4"/>
       <c r="N21" s="4"/>
       <c r="O21" s="4"/>
     </row>
-    <row r="22" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A22" s="3" t="s">
-        <v>123</v>
+    <row r="22" ht="25" customHeight="1" spans="1:15">
+      <c r="A22" s="15" t="s">
+        <v>98</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>116</v>
+        <v>12</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E22" s="6" t="s">
-        <v>125</v>
+      <c r="E22" s="4" t="s">
+        <v>100</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="G22" s="4">
-        <v>2025</v>
-      </c>
-      <c r="H22" s="4"/>
+        <v>2026</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>101</v>
+      </c>
       <c r="I22" s="1" t="s">
-        <v>126</v>
+        <v>102</v>
       </c>
       <c r="J22" s="4"/>
       <c r="K22" s="4"/>
       <c r="L22" s="4" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="M22" s="4"/>
       <c r="N22" s="4"/>
       <c r="O22" s="4"/>
     </row>
-    <row r="23" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A23" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E23" s="9">
-        <v>4</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G23" s="8">
-        <v>2025</v>
-      </c>
-      <c r="H23" s="8"/>
+    <row r="23" ht="25" customHeight="1" spans="1:15">
+      <c r="A23" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G23" s="4">
+        <v>2026</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>107</v>
+      </c>
       <c r="I23" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="J23" s="8"/>
-      <c r="K23" s="8"/>
-      <c r="L23" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="M23" s="8"/>
-      <c r="N23" s="8"/>
+        <v>108</v>
+      </c>
+      <c r="J23" s="4"/>
+      <c r="K23" s="4"/>
+      <c r="L23" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="M23" s="4"/>
+      <c r="N23" s="4"/>
       <c r="O23" s="4"/>
     </row>
-    <row r="24" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A24" s="3" t="s">
-        <v>130</v>
+    <row r="24" ht="25" customHeight="1" spans="1:15">
+      <c r="A24" s="15" t="s">
+        <v>110</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>116</v>
+        <v>12</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E24" s="6" t="s">
-        <v>132</v>
+      <c r="E24" s="4" t="s">
+        <v>112</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="G24" s="4">
         <v>2025</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="I24" s="4" t="s">
-        <v>134</v>
+        <v>113</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>114</v>
       </c>
       <c r="J24" s="4"/>
       <c r="K24" s="4"/>
       <c r="L24" s="4" t="s">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="M24" s="4"/>
       <c r="N24" s="4"/>
-      <c r="O24" s="10"/>
-    </row>
-    <row r="25" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A25" s="3" t="s">
-        <v>136</v>
+      <c r="O24" s="4"/>
+    </row>
+    <row r="25" ht="25" customHeight="1" spans="1:15">
+      <c r="A25" s="15" t="s">
+        <v>116</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>116</v>
+        <v>12</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>137</v>
+        <v>117</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E25" s="4">
-        <v>6</v>
+      <c r="E25" s="4" t="s">
+        <v>118</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>15</v>
+        <v>82</v>
       </c>
       <c r="G25" s="4">
-        <v>2025</v>
-      </c>
-      <c r="H25" s="4"/>
-      <c r="I25" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="J25" s="4"/>
-      <c r="K25" s="4"/>
-      <c r="L25" s="4" t="s">
+        <v>2026</v>
+      </c>
+      <c r="H25" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="M25" s="4"/>
-      <c r="N25" s="4"/>
-      <c r="O25" s="10"/>
-    </row>
-    <row r="26" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A26" s="3" t="s">
-        <v>139</v>
+      <c r="I25" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="J25" s="18"/>
+      <c r="K25" s="18"/>
+      <c r="L25" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="M25" s="18"/>
+      <c r="N25" s="18"/>
+      <c r="O25" s="4"/>
+    </row>
+    <row r="26" ht="25" customHeight="1" spans="1:15">
+      <c r="A26" s="15" t="s">
+        <v>122</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>116</v>
+        <v>12</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E26" s="4">
-        <v>8</v>
+      <c r="E26" s="4" t="s">
+        <v>124</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>15</v>
+        <v>82</v>
       </c>
       <c r="G26" s="4">
-        <v>2025</v>
-      </c>
-      <c r="H26" s="4"/>
+        <v>2026</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>125</v>
+      </c>
       <c r="I26" s="4" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="J26" s="4"/>
       <c r="K26" s="4"/>
       <c r="L26" s="4" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="M26" s="4"/>
       <c r="N26" s="4"/>
-      <c r="O26" s="10"/>
+      <c r="O26" s="28"/>
     </row>
     <row r="27" ht="25" customHeight="1" spans="1:15">
-      <c r="A27" s="3" t="s">
-        <v>142</v>
+      <c r="A27" s="15" t="s">
+        <v>128</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>116</v>
+        <v>12</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E27" s="5" t="s">
-        <v>125</v>
+      <c r="E27" s="4" t="s">
+        <v>130</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="G27" s="4">
-        <v>2025</v>
-      </c>
-      <c r="H27" s="4"/>
+        <v>2024</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>131</v>
+      </c>
       <c r="I27" s="4" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="J27" s="4"/>
       <c r="K27" s="4"/>
       <c r="L27" s="4" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="M27" s="4"/>
       <c r="N27" s="4"/>
-      <c r="O27" s="10"/>
+      <c r="O27" s="28"/>
     </row>
     <row r="28" ht="25" customHeight="1" spans="1:15">
-      <c r="A28" s="3" t="s">
-        <v>145</v>
+      <c r="A28" s="15" t="s">
+        <v>134</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>116</v>
+        <v>12</v>
       </c>
       <c r="C28" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G28" s="4">
+        <v>2024</v>
+      </c>
+      <c r="H28" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="D28" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E28" s="5">
-        <v>4</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G28" s="4">
-        <v>2025</v>
-      </c>
-      <c r="H28" s="4"/>
       <c r="I28" s="4" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="J28" s="4"/>
       <c r="K28" s="4"/>
       <c r="L28" s="4" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="M28" s="4"/>
       <c r="N28" s="4"/>
-      <c r="O28" s="10"/>
+      <c r="O28" s="28"/>
     </row>
     <row r="29" ht="25" customHeight="1" spans="1:15">
-      <c r="A29" s="3" t="s">
-        <v>148</v>
+      <c r="A29" s="15" t="s">
+        <v>140</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>116</v>
+        <v>12</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>149</v>
+        <v>105</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E29" s="5">
-        <v>8</v>
+      <c r="E29" s="4" t="s">
+        <v>106</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>15</v>
+        <v>82</v>
       </c>
       <c r="G29" s="4">
-        <v>2025</v>
-      </c>
-      <c r="H29" s="4"/>
+        <v>2026</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>141</v>
+      </c>
       <c r="I29" s="4" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="J29" s="4"/>
       <c r="K29" s="4"/>
       <c r="L29" s="4" t="s">
-        <v>119</v>
+        <v>143</v>
       </c>
       <c r="M29" s="4"/>
       <c r="N29" s="4"/>
-      <c r="O29" s="10"/>
-    </row>
-    <row r="30" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A30" s="3" t="s">
-        <v>151</v>
+      <c r="O29" s="28"/>
+    </row>
+    <row r="30" ht="25" customHeight="1" spans="1:15">
+      <c r="A30" s="15" t="s">
+        <v>144</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>116</v>
+        <v>12</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>14</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>34</v>
+        <v>146</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="G30" s="4">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="J30" s="4"/>
       <c r="K30" s="4"/>
       <c r="L30" s="4" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="M30" s="4"/>
       <c r="N30" s="4"/>
-      <c r="O30" s="10"/>
-    </row>
-    <row r="31" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A31" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
+      <c r="O30" s="28"/>
+    </row>
+    <row r="31" ht="25" customHeight="1" spans="1:15">
+      <c r="A31" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>124</v>
+      </c>
       <c r="F31" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G31" s="4"/>
-      <c r="H31" s="4"/>
+        <v>82</v>
+      </c>
+      <c r="G31" s="4">
+        <v>2026</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>152</v>
+      </c>
       <c r="I31" s="4" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="J31" s="4"/>
       <c r="K31" s="4"/>
-      <c r="L31" s="4"/>
+      <c r="L31" s="4" t="s">
+        <v>154</v>
+      </c>
       <c r="M31" s="4"/>
       <c r="N31" s="4"/>
-      <c r="O31" s="10"/>
+      <c r="O31" s="28"/>
     </row>
     <row r="32" ht="25" customHeight="1" spans="1:15">
-      <c r="A32" s="3" t="s">
+      <c r="A32" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G32" s="4">
+        <v>2026</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="I32" s="4" t="s">
         <v>158</v>
-      </c>
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="5">
-        <v>18</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G32" s="4"/>
-      <c r="H32" s="4"/>
-      <c r="I32" s="4" t="s">
-        <v>159</v>
       </c>
       <c r="J32" s="4"/>
       <c r="K32" s="4"/>
-      <c r="L32" s="4"/>
+      <c r="L32" s="4" t="s">
+        <v>159</v>
+      </c>
       <c r="M32" s="4"/>
       <c r="N32" s="4"/>
-      <c r="O32" s="10"/>
-    </row>
-    <row r="33" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A33" s="3" t="s">
+      <c r="O32" s="28"/>
+    </row>
+    <row r="33" ht="25" customHeight="1" spans="1:15">
+      <c r="A33" s="15" t="s">
         <v>160</v>
       </c>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
+      <c r="B33" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>88</v>
+      </c>
       <c r="F33" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G33" s="4"/>
-      <c r="H33" s="4"/>
+        <v>82</v>
+      </c>
+      <c r="G33" s="4">
+        <v>2026</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>162</v>
+      </c>
       <c r="I33" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="J33" s="4"/>
       <c r="K33" s="4"/>
-      <c r="L33" s="4"/>
+      <c r="L33" s="4" t="s">
+        <v>164</v>
+      </c>
       <c r="M33" s="4"/>
       <c r="N33" s="4"/>
-      <c r="O33" s="10"/>
-    </row>
-    <row r="34" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A34" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
+      <c r="O33" s="28"/>
+    </row>
+    <row r="34" ht="25" customHeight="1" spans="1:15">
+      <c r="A34" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>166</v>
+      </c>
       <c r="F34" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
+        <v>82</v>
+      </c>
+      <c r="G34" s="4">
+        <v>2025</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>167</v>
+      </c>
       <c r="I34" s="4" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="J34" s="4"/>
       <c r="K34" s="4"/>
-      <c r="L34" s="4"/>
+      <c r="L34" s="4" t="s">
+        <v>169</v>
+      </c>
       <c r="M34" s="4"/>
       <c r="N34" s="4"/>
-      <c r="O34" s="10"/>
-    </row>
-    <row r="35" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A35" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
+      <c r="O34" s="28"/>
+    </row>
+    <row r="35" ht="25" customHeight="1" spans="1:15">
+      <c r="A35" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>172</v>
+      </c>
       <c r="F35" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
+        <v>82</v>
+      </c>
+      <c r="G35" s="4">
+        <v>2026</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>173</v>
+      </c>
       <c r="I35" s="4" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="J35" s="4"/>
       <c r="K35" s="4"/>
-      <c r="L35" s="4"/>
+      <c r="L35" s="4" t="s">
+        <v>175</v>
+      </c>
       <c r="M35" s="4"/>
       <c r="N35" s="4"/>
-      <c r="O35" s="10"/>
-    </row>
-    <row r="36" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A36" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
+      <c r="O35" s="28"/>
+    </row>
+    <row r="36" ht="25" customHeight="1" spans="1:15">
+      <c r="A36" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>94</v>
+      </c>
       <c r="F36" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
+        <v>82</v>
+      </c>
+      <c r="G36" s="4">
+        <v>2026</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>178</v>
+      </c>
       <c r="I36" s="4" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="J36" s="4"/>
       <c r="K36" s="4"/>
-      <c r="L36" s="4"/>
+      <c r="L36" s="4" t="s">
+        <v>180</v>
+      </c>
       <c r="M36" s="4"/>
       <c r="N36" s="4"/>
-      <c r="O36" s="10"/>
-    </row>
-    <row r="37" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A37" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
+      <c r="O36" s="28"/>
+    </row>
+    <row r="37" ht="25" customHeight="1" spans="1:15">
+      <c r="A37" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E37" s="16" t="s">
+        <v>184</v>
+      </c>
       <c r="F37" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G37" s="4"/>
+        <v>82</v>
+      </c>
+      <c r="G37" s="4">
+        <v>2025</v>
+      </c>
       <c r="H37" s="4"/>
       <c r="I37" s="4" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="J37" s="4"/>
       <c r="K37" s="4"/>
-      <c r="L37" s="4"/>
+      <c r="L37" s="4" t="s">
+        <v>45</v>
+      </c>
       <c r="M37" s="4"/>
       <c r="N37" s="4"/>
-      <c r="O37" s="10"/>
-    </row>
-    <row r="38" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A38" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
+      <c r="O37" s="28"/>
+    </row>
+    <row r="38" ht="25" customHeight="1" spans="1:15">
+      <c r="A38" s="15" t="s">
+        <v>186</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E38" s="16" t="s">
+        <v>188</v>
+      </c>
       <c r="F38" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
+        <v>82</v>
+      </c>
+      <c r="G38" s="4">
+        <v>2025</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>189</v>
+      </c>
       <c r="I38" s="4" t="s">
-        <v>171</v>
+        <v>190</v>
       </c>
       <c r="J38" s="4"/>
       <c r="K38" s="4"/>
-      <c r="L38" s="4"/>
+      <c r="L38" s="4" t="s">
+        <v>191</v>
+      </c>
       <c r="M38" s="4"/>
       <c r="N38" s="4"/>
-      <c r="O38" s="10"/>
-    </row>
-    <row r="39" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A39" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="4"/>
-      <c r="E39" s="4"/>
+      <c r="O38" s="28"/>
+    </row>
+    <row r="39" ht="25" customHeight="1" spans="1:15">
+      <c r="A39" s="15" t="s">
+        <v>192</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E39" s="14" t="s">
+        <v>184</v>
+      </c>
       <c r="F39" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G39" s="4"/>
+        <v>82</v>
+      </c>
+      <c r="G39" s="4">
+        <v>2025</v>
+      </c>
       <c r="H39" s="4"/>
       <c r="I39" s="4" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="J39" s="4"/>
       <c r="K39" s="4"/>
-      <c r="L39" s="4"/>
+      <c r="L39" s="4" t="s">
+        <v>45</v>
+      </c>
       <c r="M39" s="4"/>
       <c r="N39" s="4"/>
-      <c r="O39" s="10"/>
-    </row>
-    <row r="40" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A40" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="B40" s="4"/>
-      <c r="C40" s="4"/>
-      <c r="D40" s="4"/>
-      <c r="E40" s="4"/>
+      <c r="O39" s="28"/>
+    </row>
+    <row r="40" ht="25" customHeight="1" spans="1:15">
+      <c r="A40" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>100</v>
+      </c>
       <c r="F40" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G40" s="4"/>
-      <c r="H40" s="4"/>
+        <v>82</v>
+      </c>
+      <c r="G40" s="4">
+        <v>2026</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>197</v>
+      </c>
       <c r="I40" s="4" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="J40" s="4"/>
       <c r="K40" s="4"/>
-      <c r="L40" s="4"/>
+      <c r="L40" s="4" t="s">
+        <v>199</v>
+      </c>
       <c r="M40" s="4"/>
       <c r="N40" s="4"/>
-      <c r="O40" s="10"/>
-    </row>
-    <row r="41" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A41" s="3" t="s">
-        <v>176</v>
+      <c r="O40" s="28"/>
+    </row>
+    <row r="41" ht="25" customHeight="1" spans="1:15">
+      <c r="A41" s="15" t="s">
+        <v>200</v>
       </c>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
       <c r="F41" s="4" t="s">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="G41" s="4"/>
       <c r="H41" s="4"/>
       <c r="I41" s="4" t="s">
-        <v>177</v>
+        <v>201</v>
       </c>
       <c r="J41" s="4"/>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
       <c r="M41" s="4"/>
       <c r="N41" s="4"/>
-      <c r="O41" s="10"/>
-    </row>
-    <row r="42" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A42" s="3" t="s">
-        <v>178</v>
+      <c r="O41" s="28"/>
+    </row>
+    <row r="42" ht="25" customHeight="1" spans="1:15">
+      <c r="A42" s="15" t="s">
+        <v>202</v>
       </c>
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
       <c r="F42" s="4" t="s">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
       <c r="I42" s="4" t="s">
-        <v>179</v>
+        <v>203</v>
       </c>
       <c r="J42" s="4"/>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
       <c r="M42" s="4"/>
       <c r="N42" s="4"/>
-      <c r="O42" s="10"/>
-    </row>
-    <row r="43" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A43" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="B43" s="8"/>
-      <c r="C43" s="8"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
+      <c r="O42" s="28"/>
+    </row>
+    <row r="43" ht="25" customHeight="1" spans="1:15">
+      <c r="A43" s="15" t="s">
+        <v>204</v>
+      </c>
+      <c r="B43" s="4"/>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
       <c r="F43" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G43" s="8"/>
-      <c r="H43" s="8"/>
-      <c r="I43" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="J43" s="8"/>
+        <v>82</v>
+      </c>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="J43" s="4"/>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
       <c r="M43" s="4"/>
       <c r="N43" s="4"/>
-      <c r="O43" s="10"/>
-    </row>
-    <row r="44" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A44" s="3" t="s">
-        <v>182</v>
+      <c r="O43" s="28"/>
+    </row>
+    <row r="44" ht="25" customHeight="1" spans="1:15">
+      <c r="A44" s="15" t="s">
+        <v>206</v>
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
       <c r="F44" s="4" t="s">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="G44" s="4"/>
       <c r="H44" s="4"/>
       <c r="I44" s="4" t="s">
-        <v>183</v>
+        <v>207</v>
       </c>
       <c r="J44" s="4"/>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
       <c r="M44" s="4"/>
       <c r="N44" s="4"/>
-      <c r="O44" s="10"/>
-    </row>
-    <row r="45" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A45" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="B45" s="4"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="4"/>
-      <c r="E45" s="4"/>
+      <c r="O44" s="28"/>
+    </row>
+    <row r="45" ht="25" customHeight="1" spans="1:15">
+      <c r="A45" s="17" t="s">
+        <v>208</v>
+      </c>
+      <c r="B45" s="18"/>
+      <c r="C45" s="18"/>
+      <c r="D45" s="18"/>
+      <c r="E45" s="18"/>
       <c r="F45" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G45" s="4"/>
-      <c r="H45" s="4"/>
-      <c r="I45" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="J45" s="4"/>
+        <v>82</v>
+      </c>
+      <c r="G45" s="18"/>
+      <c r="H45" s="18"/>
+      <c r="I45" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="J45" s="18"/>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
       <c r="M45" s="4"/>
       <c r="N45" s="4"/>
-      <c r="O45" s="10"/>
-    </row>
-    <row r="46" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A46" s="3" t="s">
-        <v>186</v>
+      <c r="O45" s="28"/>
+    </row>
+    <row r="46" ht="25" customHeight="1" spans="1:15">
+      <c r="A46" s="15" t="s">
+        <v>210</v>
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
       <c r="F46" s="4" t="s">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="G46" s="4"/>
       <c r="H46" s="4"/>
       <c r="I46" s="4" t="s">
-        <v>187</v>
+        <v>211</v>
       </c>
       <c r="J46" s="4"/>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
       <c r="M46" s="4"/>
       <c r="N46" s="4"/>
-      <c r="O46" s="10"/>
-    </row>
-    <row r="47" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A47" s="3" t="s">
-        <v>188</v>
+      <c r="O46" s="28"/>
+    </row>
+    <row r="47" ht="25" customHeight="1" spans="1:15">
+      <c r="A47" s="15" t="s">
+        <v>212</v>
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
       <c r="F47" s="4" t="s">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="G47" s="4"/>
       <c r="H47" s="4"/>
       <c r="I47" s="4" t="s">
-        <v>189</v>
+        <v>213</v>
       </c>
       <c r="J47" s="4"/>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
       <c r="M47" s="4"/>
       <c r="N47" s="4"/>
-      <c r="O47" s="10"/>
-    </row>
-    <row r="48" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A48" s="3" t="s">
-        <v>190</v>
+      <c r="O47" s="28"/>
+    </row>
+    <row r="48" ht="25" customHeight="1" spans="1:15">
+      <c r="A48" s="15" t="s">
+        <v>214</v>
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
       <c r="F48" s="4" t="s">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="G48" s="4"/>
       <c r="H48" s="4"/>
       <c r="I48" s="4" t="s">
-        <v>191</v>
+        <v>215</v>
       </c>
       <c r="J48" s="4"/>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
       <c r="M48" s="4"/>
       <c r="N48" s="4"/>
-      <c r="O48" s="10"/>
-    </row>
-    <row r="49" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A49" s="3" t="s">
-        <v>192</v>
+      <c r="O48" s="28"/>
+    </row>
+    <row r="49" ht="25" customHeight="1" spans="1:15">
+      <c r="A49" s="15" t="s">
+        <v>216</v>
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
       <c r="F49" s="4" t="s">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="G49" s="4"/>
       <c r="H49" s="4"/>
       <c r="I49" s="4" t="s">
-        <v>193</v>
+        <v>217</v>
       </c>
       <c r="J49" s="4"/>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
       <c r="M49" s="4"/>
       <c r="N49" s="4"/>
-      <c r="O49" s="10"/>
-    </row>
-    <row r="50" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A50" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C50" s="11" t="s">
-        <v>195</v>
-      </c>
+      <c r="O49" s="28"/>
+    </row>
+    <row r="50" ht="25" customHeight="1" spans="1:15">
+      <c r="A50" s="15" t="s">
+        <v>218</v>
+      </c>
+      <c r="B50" s="4"/>
+      <c r="C50" s="4"/>
       <c r="D50" s="4"/>
-      <c r="E50" s="4" t="s">
-        <v>196</v>
-      </c>
+      <c r="E50" s="4"/>
       <c r="F50" s="4" t="s">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="G50" s="4"/>
-      <c r="H50" s="12" t="s">
-        <v>197</v>
-      </c>
+      <c r="H50" s="4"/>
       <c r="I50" s="4" t="s">
-        <v>198</v>
+        <v>219</v>
       </c>
       <c r="J50" s="4"/>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
       <c r="M50" s="4"/>
       <c r="N50" s="4"/>
-      <c r="O50" s="10"/>
-    </row>
-    <row r="51" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A51" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="C51" s="11" t="s">
-        <v>200</v>
-      </c>
+      <c r="O50" s="28"/>
+    </row>
+    <row r="51" ht="25" customHeight="1" spans="1:15">
+      <c r="A51" s="15" t="s">
+        <v>220</v>
+      </c>
+      <c r="B51" s="4"/>
+      <c r="C51" s="4"/>
       <c r="D51" s="4"/>
-      <c r="E51" s="4" t="s">
-        <v>34</v>
-      </c>
+      <c r="E51" s="4"/>
       <c r="F51" s="4" t="s">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="G51" s="4"/>
-      <c r="H51" s="12" t="s">
-        <v>201</v>
-      </c>
+      <c r="H51" s="4"/>
       <c r="I51" s="4" t="s">
-        <v>202</v>
+        <v>221</v>
       </c>
       <c r="J51" s="4"/>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
       <c r="M51" s="4"/>
       <c r="N51" s="4"/>
-      <c r="O51" s="10"/>
-    </row>
-    <row r="52" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A52" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C52" s="13" t="s">
-        <v>204</v>
-      </c>
+      <c r="O51" s="28"/>
+    </row>
+    <row r="52" ht="25" customHeight="1" spans="1:15">
+      <c r="A52" s="15" t="s">
+        <v>222</v>
+      </c>
+      <c r="B52" s="4"/>
+      <c r="C52" s="4"/>
       <c r="D52" s="4"/>
-      <c r="E52" s="4" t="s">
-        <v>40</v>
-      </c>
+      <c r="E52" s="4"/>
       <c r="F52" s="4" t="s">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="G52" s="4"/>
-      <c r="H52" s="12" t="s">
-        <v>205</v>
-      </c>
+      <c r="H52" s="4"/>
       <c r="I52" s="4" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="J52" s="4"/>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
       <c r="M52" s="4"/>
       <c r="N52" s="4"/>
-      <c r="O52" s="10"/>
-    </row>
-    <row r="53" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A53" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="C53" s="11" t="s">
-        <v>209</v>
-      </c>
+      <c r="O52" s="28"/>
+    </row>
+    <row r="53" ht="25" customHeight="1" spans="1:15">
+      <c r="A53" s="15" t="s">
+        <v>224</v>
+      </c>
+      <c r="B53" s="4"/>
+      <c r="C53" s="4"/>
       <c r="D53" s="4"/>
-      <c r="E53" s="4">
-        <v>3</v>
-      </c>
+      <c r="E53" s="4"/>
       <c r="F53" s="4" t="s">
-        <v>15</v>
+        <v>82</v>
       </c>
       <c r="G53" s="4"/>
-      <c r="H53" s="12" t="s">
-        <v>210</v>
-      </c>
+      <c r="H53" s="4"/>
       <c r="I53" s="4" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="J53" s="4"/>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
       <c r="M53" s="4"/>
       <c r="N53" s="4"/>
-      <c r="O53" s="10"/>
-    </row>
-    <row r="54" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A54" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C54" s="11" t="s">
-        <v>213</v>
-      </c>
+      <c r="O53" s="28"/>
+    </row>
+    <row r="54" ht="25" customHeight="1" spans="1:15">
+      <c r="A54" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="B54" s="4"/>
+      <c r="C54" s="4"/>
       <c r="D54" s="4"/>
-      <c r="E54" s="4" t="s">
-        <v>214</v>
-      </c>
+      <c r="E54" s="4"/>
       <c r="F54" s="4" t="s">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="G54" s="4"/>
-      <c r="H54" s="12" t="s">
-        <v>215</v>
-      </c>
+      <c r="H54" s="4"/>
       <c r="I54" s="4" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="J54" s="4"/>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>
       <c r="M54" s="4"/>
       <c r="N54" s="4"/>
-      <c r="O54" s="10"/>
+      <c r="O54" s="28"/>
     </row>
     <row r="55" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A55" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C55" s="11" t="s">
-        <v>218</v>
-      </c>
+      <c r="A55" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="B55" s="4"/>
+      <c r="C55" s="4"/>
       <c r="D55" s="4"/>
-      <c r="E55" s="5">
-        <v>20</v>
-      </c>
+      <c r="E55" s="4"/>
       <c r="F55" s="4" t="s">
-        <v>15</v>
+        <v>82</v>
       </c>
       <c r="G55" s="4"/>
-      <c r="H55" s="12" t="s">
-        <v>219</v>
-      </c>
+      <c r="H55" s="4"/>
       <c r="I55" s="4" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="J55" s="4"/>
       <c r="K55" s="4"/>
       <c r="L55" s="4"/>
       <c r="M55" s="4"/>
       <c r="N55" s="4"/>
-      <c r="O55" s="10"/>
-    </row>
-    <row r="56" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A56" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="B56" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C56" s="11" t="s">
-        <v>222</v>
-      </c>
+      <c r="O55" s="28"/>
+    </row>
+    <row r="56" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A56" s="15" t="s">
+        <v>230</v>
+      </c>
+      <c r="B56" s="4"/>
+      <c r="C56" s="4"/>
       <c r="D56" s="4"/>
-      <c r="E56" s="4" t="s">
-        <v>214</v>
-      </c>
+      <c r="E56" s="4"/>
       <c r="F56" s="4" t="s">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="G56" s="4"/>
-      <c r="H56" s="12" t="s">
-        <v>223</v>
-      </c>
+      <c r="H56" s="4"/>
       <c r="I56" s="4" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="J56" s="4"/>
       <c r="K56" s="4"/>
       <c r="L56" s="4"/>
       <c r="M56" s="4"/>
       <c r="N56" s="4"/>
-      <c r="O56" s="10"/>
-    </row>
-    <row r="57" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A57" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="B57" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="C57" s="11" t="s">
-        <v>226</v>
-      </c>
+      <c r="O56" s="28"/>
+    </row>
+    <row r="57" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A57" s="15" t="s">
+        <v>232</v>
+      </c>
+      <c r="B57" s="4"/>
+      <c r="C57" s="4"/>
       <c r="D57" s="4"/>
-      <c r="E57" s="4" t="s">
-        <v>227</v>
-      </c>
+      <c r="E57" s="4"/>
       <c r="F57" s="4" t="s">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="G57" s="4"/>
-      <c r="H57" s="12" t="s">
-        <v>228</v>
-      </c>
+      <c r="H57" s="4"/>
       <c r="I57" s="4" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="J57" s="4"/>
       <c r="K57" s="4"/>
       <c r="L57" s="4"/>
       <c r="M57" s="4"/>
       <c r="N57" s="4"/>
-      <c r="O57" s="10"/>
+      <c r="O57" s="28"/>
     </row>
     <row r="58" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A58" s="14" t="s">
-        <v>230</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C58" s="15" t="s">
-        <v>231</v>
-      </c>
-      <c r="D58" s="5"/>
-      <c r="E58" s="5">
-        <v>8</v>
-      </c>
-      <c r="F58" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G58" s="5"/>
-      <c r="H58" s="16" t="s">
-        <v>232</v>
-      </c>
-      <c r="I58" s="5" t="s">
-        <v>233</v>
+      <c r="A58" s="15" t="s">
+        <v>234</v>
+      </c>
+      <c r="B58" s="4"/>
+      <c r="C58" s="4"/>
+      <c r="D58" s="4"/>
+      <c r="E58" s="4"/>
+      <c r="F58" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G58" s="4"/>
+      <c r="H58" s="4"/>
+      <c r="I58" s="4" t="s">
+        <v>235</v>
       </c>
       <c r="J58" s="4"/>
       <c r="K58" s="4"/>
       <c r="L58" s="4"/>
       <c r="M58" s="4"/>
       <c r="N58" s="4"/>
-      <c r="O58" s="4"/>
-    </row>
-    <row r="59" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A59" s="3" t="s">
-        <v>234</v>
+      <c r="O58" s="28"/>
+    </row>
+    <row r="59" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A59" s="15" t="s">
+        <v>236</v>
       </c>
       <c r="B59" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C59" s="11" t="s">
-        <v>235</v>
-      </c>
-      <c r="D59" s="11"/>
-      <c r="E59" s="11">
-        <v>4</v>
-      </c>
-      <c r="F59" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G59" s="11"/>
-      <c r="H59" s="12" t="s">
-        <v>236</v>
+      <c r="C59" s="20" t="s">
+        <v>237</v>
+      </c>
+      <c r="D59" s="4"/>
+      <c r="E59" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G59" s="4"/>
+      <c r="H59" s="21" t="s">
+        <v>239</v>
       </c>
       <c r="I59" s="4" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="J59" s="4"/>
       <c r="K59" s="4"/>
       <c r="L59" s="4"/>
       <c r="M59" s="4"/>
       <c r="N59" s="4"/>
-      <c r="O59" s="10"/>
-    </row>
-    <row r="60" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A60" s="3" t="s">
-        <v>238</v>
+      <c r="O59" s="28"/>
+    </row>
+    <row r="60" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A60" s="15" t="s">
+        <v>241</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="C60" s="11" t="s">
-        <v>239</v>
-      </c>
-      <c r="D60" s="11"/>
-      <c r="E60" s="11">
-        <v>4</v>
-      </c>
-      <c r="F60" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G60" s="11"/>
-      <c r="H60" s="12" t="s">
-        <v>240</v>
+        <v>182</v>
+      </c>
+      <c r="C60" s="20" t="s">
+        <v>242</v>
+      </c>
+      <c r="D60" s="4"/>
+      <c r="E60" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G60" s="4"/>
+      <c r="H60" s="21" t="s">
+        <v>243</v>
       </c>
       <c r="I60" s="4" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="J60" s="4"/>
       <c r="K60" s="4"/>
       <c r="L60" s="4"/>
       <c r="M60" s="4"/>
       <c r="N60" s="4"/>
-      <c r="O60" s="10"/>
-    </row>
-    <row r="61" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A61" s="3" t="s">
-        <v>242</v>
+      <c r="O60" s="4"/>
+    </row>
+    <row r="61" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A61" s="15" t="s">
+        <v>245</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="C61" s="11" t="s">
-        <v>243</v>
-      </c>
-      <c r="D61" s="11"/>
-      <c r="E61" s="11"/>
-      <c r="F61" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G61" s="11"/>
-      <c r="H61" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="C61" s="22" t="s">
+        <v>246</v>
+      </c>
+      <c r="D61" s="4"/>
+      <c r="E61" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G61" s="4"/>
+      <c r="H61" s="21" t="s">
+        <v>247</v>
+      </c>
       <c r="I61" s="4" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="J61" s="4"/>
       <c r="K61" s="4"/>
       <c r="L61" s="4"/>
       <c r="M61" s="4"/>
       <c r="N61" s="4"/>
-      <c r="O61" s="10"/>
-    </row>
-    <row r="62" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A62" s="3" t="s">
-        <v>245</v>
+      <c r="O61" s="28"/>
+    </row>
+    <row r="62" ht="25" customHeight="1" spans="1:15">
+      <c r="A62" s="15" t="s">
+        <v>249</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="C62" s="11" t="s">
-        <v>246</v>
-      </c>
-      <c r="D62" s="11"/>
-      <c r="E62" s="11">
-        <v>7</v>
-      </c>
-      <c r="F62" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G62" s="11"/>
-      <c r="H62" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="C62" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="D62" s="4"/>
+      <c r="E62" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G62" s="4"/>
+      <c r="H62" s="21" t="s">
+        <v>252</v>
+      </c>
       <c r="I62" s="4" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="J62" s="4"/>
       <c r="K62" s="4"/>
       <c r="L62" s="4"/>
       <c r="M62" s="4"/>
       <c r="N62" s="4"/>
-      <c r="O62" s="10"/>
-    </row>
-    <row r="63" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A63" s="3" t="s">
-        <v>248</v>
+      <c r="O62" s="28"/>
+    </row>
+    <row r="63" ht="25" customHeight="1" spans="1:15">
+      <c r="A63" s="15" t="s">
+        <v>254</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="C63" s="11" t="s">
-        <v>243</v>
-      </c>
-      <c r="D63" s="11"/>
-      <c r="E63" s="11"/>
-      <c r="F63" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G63" s="11"/>
-      <c r="H63" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="C63" s="20" t="s">
+        <v>255</v>
+      </c>
+      <c r="D63" s="4"/>
+      <c r="E63" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G63" s="4"/>
+      <c r="H63" s="21" t="s">
+        <v>256</v>
+      </c>
       <c r="I63" s="4" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="J63" s="4"/>
       <c r="K63" s="4"/>
       <c r="L63" s="4"/>
       <c r="M63" s="4"/>
       <c r="N63" s="4"/>
-      <c r="O63" s="10"/>
-    </row>
-    <row r="64" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A64" s="3" t="s">
-        <v>250</v>
+      <c r="O63" s="28"/>
+    </row>
+    <row r="64" ht="25" customHeight="1" spans="1:15">
+      <c r="A64" s="15" t="s">
+        <v>258</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="C64" s="11" t="s">
-        <v>251</v>
-      </c>
-      <c r="D64" s="11"/>
-      <c r="E64" s="11">
-        <v>4</v>
-      </c>
-      <c r="F64" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G64" s="11"/>
-      <c r="H64" s="12"/>
+        <v>45</v>
+      </c>
+      <c r="C64" s="20" t="s">
+        <v>259</v>
+      </c>
+      <c r="D64" s="4"/>
+      <c r="E64" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G64" s="4"/>
+      <c r="H64" s="21" t="s">
+        <v>261</v>
+      </c>
       <c r="I64" s="4" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="J64" s="4"/>
       <c r="K64" s="4"/>
       <c r="L64" s="4"/>
       <c r="M64" s="4"/>
       <c r="N64" s="4"/>
-      <c r="O64" s="10"/>
+      <c r="O64" s="28"/>
     </row>
     <row r="65" ht="25" customHeight="1" spans="1:15">
-      <c r="A65" s="3"/>
+      <c r="A65" s="15"/>
       <c r="B65" s="4"/>
       <c r="C65" s="4"/>
       <c r="D65" s="4"/>
       <c r="E65" s="4"/>
-      <c r="F65" s="6"/>
+      <c r="F65" s="16"/>
       <c r="G65" s="4"/>
       <c r="H65" s="4"/>
       <c r="I65" s="4"/>
@@ -4485,12 +4464,12 @@
       <c r="O65" s="4"/>
     </row>
     <row r="66" ht="25" customHeight="1" spans="1:15">
-      <c r="A66" s="3"/>
+      <c r="A66" s="15"/>
       <c r="B66" s="4"/>
       <c r="C66" s="4"/>
       <c r="D66" s="4"/>
       <c r="E66" s="4"/>
-      <c r="F66" s="6"/>
+      <c r="F66" s="16"/>
       <c r="G66" s="4"/>
       <c r="H66" s="4"/>
       <c r="I66" s="4"/>
@@ -4502,12 +4481,12 @@
       <c r="O66" s="4"/>
     </row>
     <row r="67" ht="25" customHeight="1" spans="1:15">
-      <c r="A67" s="3"/>
+      <c r="A67" s="15"/>
       <c r="B67" s="4"/>
       <c r="C67" s="4"/>
       <c r="D67" s="4"/>
       <c r="E67" s="4"/>
-      <c r="F67" s="6"/>
+      <c r="F67" s="16"/>
       <c r="G67" s="4"/>
       <c r="H67" s="4"/>
       <c r="I67" s="4"/>
@@ -4519,12 +4498,12 @@
       <c r="O67" s="4"/>
     </row>
     <row r="68" ht="25" customHeight="1" spans="1:15">
-      <c r="A68" s="3"/>
+      <c r="A68" s="15"/>
       <c r="B68" s="4"/>
       <c r="C68" s="4"/>
       <c r="D68" s="4"/>
       <c r="E68" s="4"/>
-      <c r="F68" s="6"/>
+      <c r="F68" s="16"/>
       <c r="G68" s="4"/>
       <c r="H68" s="4"/>
       <c r="I68" s="4"/>
@@ -4536,12 +4515,12 @@
       <c r="O68" s="4"/>
     </row>
     <row r="69" ht="25" customHeight="1" spans="1:15">
-      <c r="A69" s="3"/>
+      <c r="A69" s="15"/>
       <c r="B69" s="4"/>
       <c r="C69" s="4"/>
       <c r="D69" s="4"/>
       <c r="E69" s="4"/>
-      <c r="F69" s="6"/>
+      <c r="F69" s="16"/>
       <c r="G69" s="4"/>
       <c r="H69" s="4"/>
       <c r="I69" s="4"/>
@@ -4553,12 +4532,12 @@
       <c r="O69" s="4"/>
     </row>
     <row r="70" ht="25" customHeight="1" spans="1:15">
-      <c r="A70" s="3"/>
+      <c r="A70" s="15"/>
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
       <c r="D70" s="4"/>
       <c r="E70" s="4"/>
-      <c r="F70" s="6"/>
+      <c r="F70" s="16"/>
       <c r="G70" s="4"/>
       <c r="H70" s="4"/>
       <c r="I70" s="4"/>
@@ -4570,12 +4549,12 @@
       <c r="O70" s="4"/>
     </row>
     <row r="71" ht="25" customHeight="1" spans="1:15">
-      <c r="A71" s="3"/>
+      <c r="A71" s="15"/>
       <c r="B71" s="4"/>
       <c r="C71" s="4"/>
       <c r="D71" s="4"/>
       <c r="E71" s="4"/>
-      <c r="F71" s="6"/>
+      <c r="F71" s="16"/>
       <c r="G71" s="4"/>
       <c r="H71" s="4"/>
       <c r="I71" s="4"/>
@@ -4587,12 +4566,12 @@
       <c r="O71" s="4"/>
     </row>
     <row r="72" ht="25" customHeight="1" spans="1:15">
-      <c r="A72" s="3"/>
+      <c r="A72" s="15"/>
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
       <c r="D72" s="4"/>
       <c r="E72" s="4"/>
-      <c r="F72" s="6"/>
+      <c r="F72" s="16"/>
       <c r="G72" s="4"/>
       <c r="H72" s="4"/>
       <c r="I72" s="4"/>
@@ -4604,12 +4583,12 @@
       <c r="O72" s="4"/>
     </row>
     <row r="73" ht="25" customHeight="1" spans="1:15">
-      <c r="A73" s="3"/>
+      <c r="A73" s="15"/>
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
       <c r="D73" s="4"/>
       <c r="E73" s="4"/>
-      <c r="F73" s="6"/>
+      <c r="F73" s="16"/>
       <c r="G73" s="4"/>
       <c r="H73" s="4"/>
       <c r="I73" s="4"/>
@@ -4621,12 +4600,12 @@
       <c r="O73" s="4"/>
     </row>
     <row r="74" ht="25" customHeight="1" spans="1:15">
-      <c r="A74" s="3"/>
+      <c r="A74" s="15"/>
       <c r="B74" s="4"/>
       <c r="C74" s="4"/>
       <c r="D74" s="4"/>
       <c r="E74" s="4"/>
-      <c r="F74" s="6"/>
+      <c r="F74" s="16"/>
       <c r="G74" s="4"/>
       <c r="H74" s="4"/>
       <c r="I74" s="4"/>
@@ -4638,12 +4617,12 @@
       <c r="O74" s="4"/>
     </row>
     <row r="75" ht="25" customHeight="1" spans="1:15">
-      <c r="A75" s="3"/>
+      <c r="A75" s="15"/>
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
       <c r="D75" s="4"/>
       <c r="E75" s="4"/>
-      <c r="F75" s="6"/>
+      <c r="F75" s="16"/>
       <c r="G75" s="4"/>
       <c r="H75" s="4"/>
       <c r="I75" s="4"/>
@@ -4655,12 +4634,12 @@
       <c r="O75" s="4"/>
     </row>
     <row r="76" ht="25" customHeight="1" spans="1:15">
-      <c r="A76" s="3"/>
+      <c r="A76" s="15"/>
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
       <c r="D76" s="4"/>
       <c r="E76" s="4"/>
-      <c r="F76" s="6"/>
+      <c r="F76" s="16"/>
       <c r="G76" s="4"/>
       <c r="H76" s="4"/>
       <c r="I76" s="4"/>
@@ -4672,12 +4651,12 @@
       <c r="O76" s="4"/>
     </row>
     <row r="77" ht="25" customHeight="1" spans="1:15">
-      <c r="A77" s="3"/>
+      <c r="A77" s="15"/>
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
       <c r="D77" s="4"/>
       <c r="E77" s="4"/>
-      <c r="F77" s="6"/>
+      <c r="F77" s="16"/>
       <c r="G77" s="4"/>
       <c r="H77" s="4"/>
       <c r="I77" s="4"/>
@@ -4689,12 +4668,12 @@
       <c r="O77" s="4"/>
     </row>
     <row r="78" ht="25" customHeight="1" spans="1:15">
-      <c r="A78" s="3"/>
+      <c r="A78" s="15"/>
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
       <c r="D78" s="4"/>
       <c r="E78" s="4"/>
-      <c r="F78" s="6"/>
+      <c r="F78" s="16"/>
       <c r="G78" s="4"/>
       <c r="H78" s="4"/>
       <c r="I78" s="4"/>
@@ -4706,12 +4685,12 @@
       <c r="O78" s="4"/>
     </row>
     <row r="79" ht="25" customHeight="1" spans="1:15">
-      <c r="A79" s="3"/>
+      <c r="A79" s="15"/>
       <c r="B79" s="4"/>
       <c r="C79" s="4"/>
       <c r="D79" s="4"/>
       <c r="E79" s="4"/>
-      <c r="F79" s="6"/>
+      <c r="F79" s="16"/>
       <c r="G79" s="4"/>
       <c r="H79" s="4"/>
       <c r="I79" s="4"/>
@@ -4723,12 +4702,12 @@
       <c r="O79" s="4"/>
     </row>
     <row r="80" ht="25" customHeight="1" spans="1:15">
-      <c r="A80" s="3"/>
+      <c r="A80" s="15"/>
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
       <c r="D80" s="4"/>
       <c r="E80" s="4"/>
-      <c r="F80" s="6"/>
+      <c r="F80" s="16"/>
       <c r="G80" s="4"/>
       <c r="H80" s="4"/>
       <c r="I80" s="4"/>
@@ -4740,12 +4719,12 @@
       <c r="O80" s="4"/>
     </row>
     <row r="81" ht="25" customHeight="1" spans="1:15">
-      <c r="A81" s="3"/>
+      <c r="A81" s="15"/>
       <c r="B81" s="4"/>
       <c r="C81" s="4"/>
       <c r="D81" s="4"/>
       <c r="E81" s="4"/>
-      <c r="F81" s="6"/>
+      <c r="F81" s="16"/>
       <c r="G81" s="4"/>
       <c r="H81" s="4"/>
       <c r="I81" s="4"/>
@@ -4758,13 +4737,1826 @@
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:O64" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="4">
-      <colorFilter dxfId="0"/>
-    </filterColumn>
+    <sortState ref="A2:O64">
+      <sortCondition ref="F1"/>
+    </sortState>
     <extLst/>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="H51" r:id="rId1" display="普洛伊湘普·素帕莎 / 芭莉雅皮·余 " tooltip="https://www.douban.com/personage/30264980/"/>
+    <hyperlink ref="H60" r:id="rId1" display="普洛伊湘普·素帕莎 / 芭莉雅皮·余 " tooltip="https://www.douban.com/personage/30264980/"/>
+    <hyperlink ref="H15" r:id="rId2" display="金贤叙/郑明哲" tooltip="https://www.douban.com/personage/37338980/"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:I81"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="24.2666666666667" style="2" customWidth="1"/>
+    <col min="2" max="2" width="9" style="1"/>
+    <col min="3" max="3" width="30.5833333333333" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9" style="1" hidden="1" customWidth="1"/>
+    <col min="5" max="7" width="9" style="1"/>
+    <col min="8" max="8" width="80.2916666666667" style="1" customWidth="1"/>
+    <col min="9" max="9" width="74.25" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="32" customHeight="1" spans="1:9">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1" spans="1:9">
+      <c r="A2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="6">
+        <v>4</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="7">
+        <v>2026</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1" spans="1:9">
+      <c r="A3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="7">
+        <v>8</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="7">
+        <v>2026</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="1:9">
+      <c r="A4" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="7">
+        <v>23</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="7">
+        <v>2026</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1" spans="1:9">
+      <c r="A5" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="7">
+        <v>18</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="7">
+        <v>2026</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1" spans="1:9">
+      <c r="A6" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="7">
+        <v>20</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="7">
+        <v>2026</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1" spans="1:9">
+      <c r="A7" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="7">
+        <v>3</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="7">
+        <v>2026</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1" spans="1:9">
+      <c r="A8" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="6">
+        <v>4</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" s="7">
+        <v>2026</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1" spans="1:9">
+      <c r="A9" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="7">
+        <v>6</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" s="7">
+        <v>2026</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1" spans="1:9">
+      <c r="A10" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="7">
+        <v>6</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" s="7">
+        <v>2026</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="I10" s="10" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1" spans="1:9">
+      <c r="A11" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="7">
+        <v>4</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" s="7">
+        <v>2026</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="I11" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1" spans="1:9">
+      <c r="A12" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="7">
+        <v>6</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="7">
+        <v>2026</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1" spans="1:9">
+      <c r="A13" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="7">
+        <v>8</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" s="7">
+        <v>2026</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1" spans="1:9">
+      <c r="A14" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" s="7">
+        <v>4</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14" s="7">
+        <v>2026</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1" spans="1:9">
+      <c r="A15" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" s="7">
+        <v>8</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" s="7">
+        <v>2026</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1" spans="1:9">
+      <c r="A16" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" s="6">
+        <v>7</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16" s="7">
+        <v>2026</v>
+      </c>
+      <c r="H16" s="6"/>
+      <c r="I16" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1" spans="1:9">
+      <c r="A17" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E17" s="6">
+        <v>4</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G17" s="7">
+        <v>2026</v>
+      </c>
+      <c r="H17" s="6"/>
+      <c r="I17" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1" spans="1:9">
+      <c r="A18" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>264</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="G18" s="7">
+        <v>2026</v>
+      </c>
+      <c r="H18" s="6"/>
+      <c r="I18" s="14" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1" spans="1:9">
+      <c r="A19" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>264</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="G19" s="7">
+        <v>2026</v>
+      </c>
+      <c r="H19" s="6"/>
+      <c r="I19" s="14" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1" spans="1:9">
+      <c r="A20" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G20" s="4">
+        <v>2026</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1" spans="1:9">
+      <c r="A21" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G21" s="4">
+        <v>2025</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1" spans="1:9">
+      <c r="A22" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G22" s="4">
+        <v>2026</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1" spans="1:9">
+      <c r="A23" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G23" s="4">
+        <v>2026</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1" spans="1:9">
+      <c r="A24" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G24" s="4">
+        <v>2025</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1" spans="1:9">
+      <c r="A25" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G25" s="4">
+        <v>2026</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1" spans="1:9">
+      <c r="A26" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G26" s="4">
+        <v>2026</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1" spans="1:9">
+      <c r="A27" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G27" s="4">
+        <v>2024</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="28" ht="25" customHeight="1" spans="1:9">
+      <c r="A28" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G28" s="4">
+        <v>2024</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="29" ht="25" customHeight="1" spans="1:9">
+      <c r="A29" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G29" s="4">
+        <v>2026</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="30" ht="25" customHeight="1" spans="1:9">
+      <c r="A30" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G30" s="4">
+        <v>2025</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="31" ht="25" customHeight="1" spans="1:9">
+      <c r="A31" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G31" s="4">
+        <v>2026</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="I31" s="4" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="32" ht="25" customHeight="1" spans="1:9">
+      <c r="A32" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G32" s="4">
+        <v>2026</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="33" ht="25" customHeight="1" spans="1:9">
+      <c r="A33" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G33" s="4">
+        <v>2026</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="34" ht="25" customHeight="1" spans="1:9">
+      <c r="A34" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G34" s="4">
+        <v>2025</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="35" ht="25" customHeight="1" spans="1:9">
+      <c r="A35" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G35" s="4">
+        <v>2026</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="36" ht="25" customHeight="1" spans="1:9">
+      <c r="A36" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G36" s="4">
+        <v>2026</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="37" ht="25" customHeight="1" spans="1:9">
+      <c r="A37" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E37" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G37" s="4">
+        <v>2025</v>
+      </c>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="38" ht="25" customHeight="1" spans="1:9">
+      <c r="A38" s="15" t="s">
+        <v>186</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E38" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G38" s="4">
+        <v>2025</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="I38" s="4" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="39" ht="25" customHeight="1" spans="1:9">
+      <c r="A39" s="15" t="s">
+        <v>192</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E39" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G39" s="4">
+        <v>2025</v>
+      </c>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="40" ht="25" customHeight="1" spans="1:9">
+      <c r="A40" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G40" s="4">
+        <v>2026</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="I40" s="4" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="41" ht="25" customHeight="1" spans="1:9">
+      <c r="A41" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="42" ht="25" customHeight="1" spans="1:9">
+      <c r="A42" s="15" t="s">
+        <v>202</v>
+      </c>
+      <c r="B42" s="4"/>
+      <c r="C42" s="4"/>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="43" ht="25" customHeight="1" spans="1:9">
+      <c r="A43" s="15" t="s">
+        <v>204</v>
+      </c>
+      <c r="B43" s="4"/>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="44" ht="25" customHeight="1" spans="1:9">
+      <c r="A44" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="B44" s="4"/>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="45" ht="25" customHeight="1" spans="1:9">
+      <c r="A45" s="17" t="s">
+        <v>208</v>
+      </c>
+      <c r="B45" s="18"/>
+      <c r="C45" s="18"/>
+      <c r="D45" s="18"/>
+      <c r="E45" s="18"/>
+      <c r="F45" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G45" s="18"/>
+      <c r="H45" s="18"/>
+      <c r="I45" s="19" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="46" ht="25" customHeight="1" spans="1:9">
+      <c r="A46" s="15" t="s">
+        <v>210</v>
+      </c>
+      <c r="B46" s="4"/>
+      <c r="C46" s="4"/>
+      <c r="D46" s="4"/>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="47" ht="25" customHeight="1" spans="1:9">
+      <c r="A47" s="15" t="s">
+        <v>212</v>
+      </c>
+      <c r="B47" s="4"/>
+      <c r="C47" s="4"/>
+      <c r="D47" s="4"/>
+      <c r="E47" s="4"/>
+      <c r="F47" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="48" ht="25" customHeight="1" spans="1:9">
+      <c r="A48" s="15" t="s">
+        <v>214</v>
+      </c>
+      <c r="B48" s="4"/>
+      <c r="C48" s="4"/>
+      <c r="D48" s="4"/>
+      <c r="E48" s="4"/>
+      <c r="F48" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="49" ht="25" customHeight="1" spans="1:9">
+      <c r="A49" s="15" t="s">
+        <v>216</v>
+      </c>
+      <c r="B49" s="4"/>
+      <c r="C49" s="4"/>
+      <c r="D49" s="4"/>
+      <c r="E49" s="4"/>
+      <c r="F49" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="50" ht="25" customHeight="1" spans="1:9">
+      <c r="A50" s="15" t="s">
+        <v>218</v>
+      </c>
+      <c r="B50" s="4"/>
+      <c r="C50" s="4"/>
+      <c r="D50" s="4"/>
+      <c r="E50" s="4"/>
+      <c r="F50" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="51" ht="25" customHeight="1" spans="1:9">
+      <c r="A51" s="15" t="s">
+        <v>220</v>
+      </c>
+      <c r="B51" s="4"/>
+      <c r="C51" s="4"/>
+      <c r="D51" s="4"/>
+      <c r="E51" s="4"/>
+      <c r="F51" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G51" s="4"/>
+      <c r="H51" s="4"/>
+      <c r="I51" s="4" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="52" ht="25" customHeight="1" spans="1:9">
+      <c r="A52" s="15" t="s">
+        <v>222</v>
+      </c>
+      <c r="B52" s="4"/>
+      <c r="C52" s="4"/>
+      <c r="D52" s="4"/>
+      <c r="E52" s="4"/>
+      <c r="F52" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G52" s="4"/>
+      <c r="H52" s="4"/>
+      <c r="I52" s="4" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="53" ht="25" customHeight="1" spans="1:9">
+      <c r="A53" s="15" t="s">
+        <v>224</v>
+      </c>
+      <c r="B53" s="4"/>
+      <c r="C53" s="4"/>
+      <c r="D53" s="4"/>
+      <c r="E53" s="4"/>
+      <c r="F53" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G53" s="4"/>
+      <c r="H53" s="4"/>
+      <c r="I53" s="4" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="54" ht="25" customHeight="1" spans="1:9">
+      <c r="A54" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="B54" s="4"/>
+      <c r="C54" s="4"/>
+      <c r="D54" s="4"/>
+      <c r="E54" s="4"/>
+      <c r="F54" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G54" s="4"/>
+      <c r="H54" s="4"/>
+      <c r="I54" s="4" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="55" customFormat="1" ht="25" customHeight="1" spans="1:9">
+      <c r="A55" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="B55" s="4"/>
+      <c r="C55" s="4"/>
+      <c r="D55" s="4"/>
+      <c r="E55" s="4"/>
+      <c r="F55" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G55" s="4"/>
+      <c r="H55" s="4"/>
+      <c r="I55" s="4" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="56" customFormat="1" ht="25" customHeight="1" spans="1:9">
+      <c r="A56" s="15" t="s">
+        <v>230</v>
+      </c>
+      <c r="B56" s="4"/>
+      <c r="C56" s="4"/>
+      <c r="D56" s="4"/>
+      <c r="E56" s="4"/>
+      <c r="F56" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G56" s="4"/>
+      <c r="H56" s="4"/>
+      <c r="I56" s="4" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="57" customFormat="1" ht="25" customHeight="1" spans="1:9">
+      <c r="A57" s="15" t="s">
+        <v>232</v>
+      </c>
+      <c r="B57" s="4"/>
+      <c r="C57" s="4"/>
+      <c r="D57" s="4"/>
+      <c r="E57" s="4"/>
+      <c r="F57" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G57" s="4"/>
+      <c r="H57" s="4"/>
+      <c r="I57" s="4" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="58" customFormat="1" ht="25" customHeight="1" spans="1:9">
+      <c r="A58" s="15" t="s">
+        <v>234</v>
+      </c>
+      <c r="B58" s="4"/>
+      <c r="C58" s="4"/>
+      <c r="D58" s="4"/>
+      <c r="E58" s="4"/>
+      <c r="F58" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G58" s="4"/>
+      <c r="H58" s="4"/>
+      <c r="I58" s="4" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="59" customFormat="1" ht="25" customHeight="1" spans="1:9">
+      <c r="A59" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C59" s="20" t="s">
+        <v>237</v>
+      </c>
+      <c r="D59" s="4"/>
+      <c r="E59" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G59" s="4"/>
+      <c r="H59" s="21" t="s">
+        <v>239</v>
+      </c>
+      <c r="I59" s="4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="60" customFormat="1" ht="25" customHeight="1" spans="1:9">
+      <c r="A60" s="15" t="s">
+        <v>241</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="C60" s="20" t="s">
+        <v>242</v>
+      </c>
+      <c r="D60" s="4"/>
+      <c r="E60" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G60" s="4"/>
+      <c r="H60" s="21" t="s">
+        <v>243</v>
+      </c>
+      <c r="I60" s="4" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="61" customFormat="1" ht="25" customHeight="1" spans="1:9">
+      <c r="A61" s="15" t="s">
+        <v>245</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C61" s="22" t="s">
+        <v>246</v>
+      </c>
+      <c r="D61" s="4"/>
+      <c r="E61" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G61" s="4"/>
+      <c r="H61" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="I61" s="4" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="62" ht="25" customHeight="1" spans="1:9">
+      <c r="A62" s="15" t="s">
+        <v>249</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C62" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="D62" s="4"/>
+      <c r="E62" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G62" s="4"/>
+      <c r="H62" s="21" t="s">
+        <v>252</v>
+      </c>
+      <c r="I62" s="4" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="63" ht="25" customHeight="1" spans="1:9">
+      <c r="A63" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C63" s="20" t="s">
+        <v>255</v>
+      </c>
+      <c r="D63" s="4"/>
+      <c r="E63" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G63" s="4"/>
+      <c r="H63" s="21" t="s">
+        <v>256</v>
+      </c>
+      <c r="I63" s="4" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="64" ht="25" customHeight="1" spans="1:9">
+      <c r="A64" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C64" s="20" t="s">
+        <v>259</v>
+      </c>
+      <c r="D64" s="4"/>
+      <c r="E64" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G64" s="4"/>
+      <c r="H64" s="21" t="s">
+        <v>261</v>
+      </c>
+      <c r="I64" s="4" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="65" ht="25" customHeight="1" spans="1:9">
+      <c r="A65" s="15"/>
+      <c r="B65" s="4"/>
+      <c r="C65" s="4"/>
+      <c r="D65" s="4"/>
+      <c r="E65" s="4"/>
+      <c r="F65" s="16"/>
+      <c r="G65" s="4"/>
+      <c r="H65" s="4"/>
+      <c r="I65" s="4"/>
+    </row>
+    <row r="66" ht="25" customHeight="1" spans="1:9">
+      <c r="A66" s="15"/>
+      <c r="B66" s="4"/>
+      <c r="C66" s="4"/>
+      <c r="D66" s="4"/>
+      <c r="E66" s="4"/>
+      <c r="F66" s="16"/>
+      <c r="G66" s="4"/>
+      <c r="H66" s="4"/>
+      <c r="I66" s="4"/>
+    </row>
+    <row r="67" ht="25" customHeight="1" spans="1:9">
+      <c r="A67" s="15"/>
+      <c r="B67" s="4"/>
+      <c r="C67" s="4"/>
+      <c r="D67" s="4"/>
+      <c r="E67" s="4"/>
+      <c r="F67" s="16"/>
+      <c r="G67" s="4"/>
+      <c r="H67" s="4"/>
+      <c r="I67" s="4"/>
+    </row>
+    <row r="68" ht="25" customHeight="1" spans="1:9">
+      <c r="A68" s="15"/>
+      <c r="B68" s="4"/>
+      <c r="C68" s="4"/>
+      <c r="D68" s="4"/>
+      <c r="E68" s="4"/>
+      <c r="F68" s="16"/>
+      <c r="G68" s="4"/>
+      <c r="H68" s="4"/>
+      <c r="I68" s="4"/>
+    </row>
+    <row r="69" ht="25" customHeight="1" spans="1:9">
+      <c r="A69" s="15"/>
+      <c r="B69" s="4"/>
+      <c r="C69" s="4"/>
+      <c r="D69" s="4"/>
+      <c r="E69" s="4"/>
+      <c r="F69" s="16"/>
+      <c r="G69" s="4"/>
+      <c r="H69" s="4"/>
+      <c r="I69" s="4"/>
+    </row>
+    <row r="70" ht="25" customHeight="1" spans="1:9">
+      <c r="A70" s="15"/>
+      <c r="B70" s="4"/>
+      <c r="C70" s="4"/>
+      <c r="D70" s="4"/>
+      <c r="E70" s="4"/>
+      <c r="F70" s="16"/>
+      <c r="G70" s="4"/>
+      <c r="H70" s="4"/>
+      <c r="I70" s="4"/>
+    </row>
+    <row r="71" ht="25" customHeight="1" spans="1:9">
+      <c r="A71" s="15"/>
+      <c r="B71" s="4"/>
+      <c r="C71" s="4"/>
+      <c r="D71" s="4"/>
+      <c r="E71" s="4"/>
+      <c r="F71" s="16"/>
+      <c r="G71" s="4"/>
+      <c r="H71" s="4"/>
+      <c r="I71" s="4"/>
+    </row>
+    <row r="72" ht="25" customHeight="1" spans="1:9">
+      <c r="A72" s="15"/>
+      <c r="B72" s="4"/>
+      <c r="C72" s="4"/>
+      <c r="D72" s="4"/>
+      <c r="E72" s="4"/>
+      <c r="F72" s="16"/>
+      <c r="G72" s="4"/>
+      <c r="H72" s="4"/>
+      <c r="I72" s="4"/>
+    </row>
+    <row r="73" ht="25" customHeight="1" spans="1:9">
+      <c r="A73" s="15"/>
+      <c r="B73" s="4"/>
+      <c r="C73" s="4"/>
+      <c r="D73" s="4"/>
+      <c r="E73" s="4"/>
+      <c r="F73" s="16"/>
+      <c r="G73" s="4"/>
+      <c r="H73" s="4"/>
+      <c r="I73" s="4"/>
+    </row>
+    <row r="74" ht="25" customHeight="1" spans="1:9">
+      <c r="A74" s="15"/>
+      <c r="B74" s="4"/>
+      <c r="C74" s="4"/>
+      <c r="D74" s="4"/>
+      <c r="E74" s="4"/>
+      <c r="F74" s="16"/>
+      <c r="G74" s="4"/>
+      <c r="H74" s="4"/>
+      <c r="I74" s="4"/>
+    </row>
+    <row r="75" ht="25" customHeight="1" spans="1:9">
+      <c r="A75" s="15"/>
+      <c r="B75" s="4"/>
+      <c r="C75" s="4"/>
+      <c r="D75" s="4"/>
+      <c r="E75" s="4"/>
+      <c r="F75" s="16"/>
+      <c r="G75" s="4"/>
+      <c r="H75" s="4"/>
+      <c r="I75" s="4"/>
+    </row>
+    <row r="76" ht="25" customHeight="1" spans="1:9">
+      <c r="A76" s="15"/>
+      <c r="B76" s="4"/>
+      <c r="C76" s="4"/>
+      <c r="D76" s="4"/>
+      <c r="E76" s="4"/>
+      <c r="F76" s="16"/>
+      <c r="G76" s="4"/>
+      <c r="H76" s="4"/>
+      <c r="I76" s="4"/>
+    </row>
+    <row r="77" ht="25" customHeight="1" spans="1:9">
+      <c r="A77" s="15"/>
+      <c r="B77" s="4"/>
+      <c r="C77" s="4"/>
+      <c r="D77" s="4"/>
+      <c r="E77" s="4"/>
+      <c r="F77" s="16"/>
+      <c r="G77" s="4"/>
+      <c r="H77" s="4"/>
+      <c r="I77" s="4"/>
+    </row>
+    <row r="78" ht="25" customHeight="1" spans="1:9">
+      <c r="A78" s="15"/>
+      <c r="B78" s="4"/>
+      <c r="C78" s="4"/>
+      <c r="D78" s="4"/>
+      <c r="E78" s="4"/>
+      <c r="F78" s="16"/>
+      <c r="G78" s="4"/>
+      <c r="H78" s="4"/>
+      <c r="I78" s="4"/>
+    </row>
+    <row r="79" ht="25" customHeight="1" spans="1:9">
+      <c r="A79" s="15"/>
+      <c r="B79" s="4"/>
+      <c r="C79" s="4"/>
+      <c r="D79" s="4"/>
+      <c r="E79" s="4"/>
+      <c r="F79" s="16"/>
+      <c r="G79" s="4"/>
+      <c r="H79" s="4"/>
+      <c r="I79" s="4"/>
+    </row>
+    <row r="80" ht="25" customHeight="1" spans="1:9">
+      <c r="A80" s="15"/>
+      <c r="B80" s="4"/>
+      <c r="C80" s="4"/>
+      <c r="D80" s="4"/>
+      <c r="E80" s="4"/>
+      <c r="F80" s="16"/>
+      <c r="G80" s="4"/>
+      <c r="H80" s="4"/>
+      <c r="I80" s="4"/>
+    </row>
+    <row r="81" ht="25" customHeight="1" spans="1:9">
+      <c r="A81" s="15"/>
+      <c r="B81" s="4"/>
+      <c r="C81" s="4"/>
+      <c r="D81" s="4"/>
+      <c r="E81" s="4"/>
+      <c r="F81" s="16"/>
+      <c r="G81" s="4"/>
+      <c r="H81" s="4"/>
+      <c r="I81" s="4"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H60" r:id="rId1" display="普洛伊湘普·素帕莎 / 芭莉雅皮·余 " tooltip="https://www.douban.com/personage/30264980/"/>
+    <hyperlink ref="H15" r:id="rId2" display="金贤叙/郑明哲" tooltip="https://www.douban.com/personage/37338980/"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/资源录入表新.xlsx
+++ b/资源录入表新.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">资源录入表!$A$1:$O$64</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'资源录入表 (2)'!$A$1:$I$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'资源录入表 (2)'!$A$2:$I$20</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="270">
   <si>
     <t>剧名</t>
   </si>
@@ -1019,6 +1019,9 @@
     <t xml:space="preserve">链接: https://pan.baidu.com/s/1wvdr54elVEWkt-5xM-qUKQ 提取码: udkd </t>
   </si>
   <si>
+    <t>网站观影指南</t>
+  </si>
+  <si>
     <t>剧情/奇幻/冒险</t>
   </si>
   <si>
@@ -1042,6 +1045,18 @@
       <t>法术</t>
     </r>
   </si>
+  <si>
+    <t>唐嫣/赵又廷/杨采钰/冯绍峰</t>
+  </si>
+  <si>
+    <t>: 赵仁杰/袁姗姗/漆昱辰/丁嘉毅 </t>
+  </si>
+  <si>
+    <t>金泽/韩乐瑶/王灿亓/王予</t>
+  </si>
+  <si>
+    <t>昭映/姜美娜/白善浩/玄宇锡 </t>
+  </si>
 </sst>
 </file>
 
@@ -1053,8 +1068,16 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="32">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -1634,137 +1657,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1774,37 +1797,43 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1816,6 +1845,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1825,28 +1857,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2401,2339 +2433,2339 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:15">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="8">
+      <c r="D2" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="10">
         <v>4</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="24">
+      <c r="G2" s="27">
         <v>2026</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
     </row>
     <row r="3" ht="25" customHeight="1" spans="1:15">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="24">
+      <c r="D3" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="27">
         <v>8</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="24">
+      <c r="G3" s="27">
         <v>2026</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
-      <c r="N3" s="4"/>
-      <c r="O3" s="4"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
     </row>
     <row r="4" ht="25" customHeight="1" spans="1:15">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="24">
+      <c r="D4" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="27">
         <v>23</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="24">
+      <c r="G4" s="27">
         <v>2026</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="I4" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4" t="s">
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="M4" s="4"/>
-      <c r="N4" s="4"/>
-      <c r="O4" s="4"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
     </row>
     <row r="5" ht="25" customHeight="1" spans="1:15">
-      <c r="A5" s="23" t="s">
+      <c r="A5" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="25" t="s">
+      <c r="C5" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="24">
+      <c r="D5" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="27">
         <v>18</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="24">
+      <c r="G5" s="27">
         <v>2026</v>
       </c>
-      <c r="H5" s="25" t="s">
+      <c r="H5" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="I5" s="8" t="s">
+      <c r="I5" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
-      <c r="N5" s="4"/>
-      <c r="O5" s="4"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="6"/>
     </row>
     <row r="6" ht="25" customHeight="1" spans="1:15">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="24">
+      <c r="D6" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="27">
         <v>20</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G6" s="24">
+      <c r="G6" s="27">
         <v>2026</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="H6" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="I6" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4"/>
-      <c r="M6" s="4"/>
-      <c r="N6" s="4"/>
-      <c r="O6" s="4"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="6"/>
     </row>
     <row r="7" ht="25" customHeight="1" spans="1:15">
-      <c r="A7" s="23" t="s">
+      <c r="A7" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="24">
+      <c r="D7" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="27">
         <v>3</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G7" s="24">
+      <c r="G7" s="27">
         <v>2026</v>
       </c>
-      <c r="H7" s="8" t="s">
+      <c r="H7" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="I7" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="J7" s="4"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="4"/>
-      <c r="M7" s="4"/>
-      <c r="N7" s="4"/>
-      <c r="O7" s="4"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="6"/>
     </row>
     <row r="8" ht="25" customHeight="1" spans="1:15">
-      <c r="A8" s="23" t="s">
+      <c r="A8" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="D8" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="8">
+      <c r="D8" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="10">
         <v>4</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F8" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G8" s="24">
+      <c r="G8" s="27">
         <v>2026</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="H8" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="I8" s="8" t="s">
+      <c r="I8" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="J8" s="4"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4"/>
-      <c r="M8" s="4"/>
-      <c r="N8" s="4"/>
-      <c r="O8" s="4"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="6"/>
+      <c r="O8" s="6"/>
     </row>
     <row r="9" ht="25" customHeight="1" spans="1:15">
-      <c r="A9" s="23" t="s">
+      <c r="A9" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="C9" s="25" t="s">
+      <c r="C9" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="D9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" s="24">
+      <c r="D9" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="27">
         <v>6</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G9" s="24">
+      <c r="G9" s="27">
         <v>2026</v>
       </c>
-      <c r="H9" s="25" t="s">
+      <c r="H9" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="I9" s="10" t="s">
+      <c r="I9" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="J9" s="4"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="4" t="s">
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="M9" s="4"/>
-      <c r="N9" s="4"/>
-      <c r="O9" s="4"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="6"/>
+      <c r="O9" s="6"/>
     </row>
     <row r="10" ht="25" customHeight="1" spans="1:15">
-      <c r="A10" s="23" t="s">
+      <c r="A10" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="D10" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="24">
+      <c r="D10" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="27">
         <v>6</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="F10" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G10" s="24">
+      <c r="G10" s="27">
         <v>2026</v>
       </c>
-      <c r="H10" s="25" t="s">
+      <c r="H10" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="I10" s="10" t="s">
+      <c r="I10" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="J10" s="4"/>
-      <c r="K10" s="4"/>
-      <c r="L10" s="4" t="s">
+      <c r="J10" s="6"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="M10" s="4"/>
-      <c r="N10" s="4"/>
-      <c r="O10" s="4"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="6"/>
+      <c r="O10" s="6"/>
     </row>
     <row r="11" ht="25" customHeight="1" spans="1:15">
-      <c r="A11" s="23" t="s">
+      <c r="A11" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="25" t="s">
+      <c r="C11" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="D11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="24">
+      <c r="D11" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="27">
         <v>4</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="F11" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G11" s="24">
+      <c r="G11" s="27">
         <v>2026</v>
       </c>
-      <c r="H11" s="8" t="s">
+      <c r="H11" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="I11" s="10" t="s">
+      <c r="I11" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="J11" s="4"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="4" t="s">
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="M11" s="4"/>
-      <c r="N11" s="4"/>
-      <c r="O11" s="4"/>
+      <c r="M11" s="6"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="6"/>
     </row>
     <row r="12" ht="25" customHeight="1" spans="1:15">
-      <c r="A12" s="23" t="s">
+      <c r="A12" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="C12" s="25" t="s">
+      <c r="C12" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="D12" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E12" s="24">
+      <c r="D12" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="27">
         <v>6</v>
       </c>
-      <c r="F12" s="8" t="s">
+      <c r="F12" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G12" s="24">
+      <c r="G12" s="27">
         <v>2026</v>
       </c>
-      <c r="H12" s="25" t="s">
+      <c r="H12" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="I12" s="8" t="s">
+      <c r="I12" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="J12" s="4"/>
-      <c r="K12" s="4"/>
-      <c r="L12" s="4" t="s">
+      <c r="J12" s="6"/>
+      <c r="K12" s="6"/>
+      <c r="L12" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="M12" s="4"/>
-      <c r="N12" s="4"/>
-      <c r="O12" s="4"/>
+      <c r="M12" s="6"/>
+      <c r="N12" s="6"/>
+      <c r="O12" s="6"/>
     </row>
     <row r="13" ht="25" customHeight="1" spans="1:15">
-      <c r="A13" s="23" t="s">
+      <c r="A13" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="25" t="s">
+      <c r="C13" s="28" t="s">
         <v>62</v>
       </c>
-      <c r="D13" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E13" s="24">
+      <c r="D13" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="27">
         <v>8</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="F13" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G13" s="24">
+      <c r="G13" s="27">
         <v>2026</v>
       </c>
-      <c r="H13" s="8" t="s">
+      <c r="H13" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="I13" s="8" t="s">
+      <c r="I13" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="J13" s="4"/>
-      <c r="K13" s="4"/>
-      <c r="L13" s="4" t="s">
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="M13" s="4"/>
-      <c r="N13" s="4"/>
-      <c r="O13" s="4"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="6"/>
     </row>
     <row r="14" ht="25" customHeight="1" spans="1:15">
-      <c r="A14" s="23" t="s">
+      <c r="A14" s="26" t="s">
         <v>65</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="C14" s="25" t="s">
+      <c r="C14" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="D14" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" s="24">
+      <c r="D14" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" s="27">
         <v>4</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="F14" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G14" s="24">
+      <c r="G14" s="27">
         <v>2026</v>
       </c>
-      <c r="H14" s="25" t="s">
+      <c r="H14" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="I14" s="8" t="s">
+      <c r="I14" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="J14" s="4"/>
-      <c r="K14" s="4"/>
-      <c r="L14" s="4" t="s">
+      <c r="J14" s="6"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="M14" s="4"/>
-      <c r="N14" s="4"/>
-      <c r="O14" s="4"/>
+      <c r="M14" s="6"/>
+      <c r="N14" s="6"/>
+      <c r="O14" s="6"/>
     </row>
     <row r="15" ht="25" customHeight="1" spans="1:15">
-      <c r="A15" s="23" t="s">
+      <c r="A15" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="C15" s="25" t="s">
+      <c r="C15" s="28" t="s">
         <v>71</v>
       </c>
-      <c r="D15" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E15" s="24">
+      <c r="D15" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" s="27">
         <v>8</v>
       </c>
-      <c r="F15" s="8" t="s">
+      <c r="F15" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G15" s="24">
+      <c r="G15" s="27">
         <v>2026</v>
       </c>
-      <c r="H15" s="25" t="s">
+      <c r="H15" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="I15" s="8" t="s">
+      <c r="I15" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="J15" s="4"/>
-      <c r="K15" s="4"/>
-      <c r="L15" s="4" t="s">
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="M15" s="4"/>
-      <c r="N15" s="4"/>
-      <c r="O15" s="4"/>
+      <c r="M15" s="6"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="6"/>
     </row>
     <row r="16" ht="25" customHeight="1" spans="1:15">
-      <c r="A16" s="23" t="s">
+      <c r="A16" s="26" t="s">
         <v>74</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="D16" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E16" s="8">
+      <c r="D16" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" s="10">
         <v>7</v>
       </c>
-      <c r="F16" s="8" t="s">
+      <c r="F16" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G16" s="24">
+      <c r="G16" s="27">
         <v>2026</v>
       </c>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8" t="s">
+      <c r="H16" s="10"/>
+      <c r="I16" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="J16" s="4"/>
-      <c r="K16" s="4"/>
-      <c r="L16" s="4"/>
-      <c r="M16" s="4"/>
-      <c r="N16" s="4"/>
-      <c r="O16" s="4"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="6"/>
+      <c r="M16" s="6"/>
+      <c r="N16" s="6"/>
+      <c r="O16" s="6"/>
     </row>
     <row r="17" ht="25" customHeight="1" spans="1:15">
-      <c r="A17" s="23" t="s">
+      <c r="A17" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="D17" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E17" s="8">
+      <c r="D17" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E17" s="10">
         <v>4</v>
       </c>
-      <c r="F17" s="8" t="s">
+      <c r="F17" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G17" s="24">
+      <c r="G17" s="27">
         <v>2026</v>
       </c>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8" t="s">
+      <c r="H17" s="10"/>
+      <c r="I17" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="J17" s="4"/>
-      <c r="K17" s="4"/>
-      <c r="L17" s="4"/>
-      <c r="M17" s="4"/>
-      <c r="N17" s="4"/>
-      <c r="O17" s="4"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="6"/>
+      <c r="O17" s="6"/>
     </row>
     <row r="18" ht="25" customHeight="1" spans="1:15">
-      <c r="A18" s="26" t="s">
+      <c r="A18" s="29" t="s">
         <v>80</v>
       </c>
-      <c r="B18" s="14" t="s">
+      <c r="B18" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C18" s="27" t="s">
+      <c r="C18" s="30" t="s">
         <v>81</v>
       </c>
-      <c r="D18" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E18" s="27"/>
-      <c r="F18" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="G18" s="24">
+      <c r="D18" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="30"/>
+      <c r="F18" s="30" t="s">
+        <v>82</v>
+      </c>
+      <c r="G18" s="27">
         <v>2026</v>
       </c>
-      <c r="H18" s="8"/>
-      <c r="I18" s="14" t="s">
+      <c r="H18" s="10"/>
+      <c r="I18" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="J18" s="4"/>
-      <c r="K18" s="4"/>
-      <c r="L18" s="4"/>
-      <c r="M18" s="4"/>
-      <c r="N18" s="4"/>
-      <c r="O18" s="28"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="6"/>
+      <c r="L18" s="6"/>
+      <c r="M18" s="6"/>
+      <c r="N18" s="6"/>
+      <c r="O18" s="31"/>
     </row>
     <row r="19" ht="25" customHeight="1" spans="1:15">
-      <c r="A19" s="26" t="s">
+      <c r="A19" s="29" t="s">
         <v>84</v>
       </c>
-      <c r="B19" s="14" t="s">
+      <c r="B19" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C19" s="27" t="s">
+      <c r="C19" s="30" t="s">
         <v>81</v>
       </c>
-      <c r="D19" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E19" s="27"/>
-      <c r="F19" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="G19" s="24">
+      <c r="D19" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19" s="30"/>
+      <c r="F19" s="30" t="s">
+        <v>82</v>
+      </c>
+      <c r="G19" s="27">
         <v>2026</v>
       </c>
-      <c r="H19" s="8"/>
-      <c r="I19" s="14" t="s">
+      <c r="H19" s="10"/>
+      <c r="I19" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="J19" s="4"/>
-      <c r="K19" s="4"/>
-      <c r="L19" s="4"/>
-      <c r="M19" s="4"/>
-      <c r="N19" s="4"/>
-      <c r="O19" s="28"/>
+      <c r="J19" s="6"/>
+      <c r="K19" s="6"/>
+      <c r="L19" s="6"/>
+      <c r="M19" s="6"/>
+      <c r="N19" s="6"/>
+      <c r="O19" s="31"/>
     </row>
     <row r="20" ht="25" customHeight="1" spans="1:15">
-      <c r="A20" s="15" t="s">
+      <c r="A20" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="D20" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E20" s="4" t="s">
+      <c r="D20" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E20" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="F20" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G20" s="4">
+      <c r="F20" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G20" s="6">
         <v>2026</v>
       </c>
-      <c r="H20" s="4" t="s">
+      <c r="H20" s="6" t="s">
         <v>89</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="J20" s="4"/>
-      <c r="K20" s="4"/>
-      <c r="L20" s="4" t="s">
+      <c r="J20" s="6"/>
+      <c r="K20" s="6"/>
+      <c r="L20" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="M20" s="4"/>
-      <c r="N20" s="4"/>
-      <c r="O20" s="4"/>
+      <c r="M20" s="6"/>
+      <c r="N20" s="6"/>
+      <c r="O20" s="6"/>
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:15">
-      <c r="A21" s="15" t="s">
+      <c r="A21" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D21" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E21" s="4" t="s">
+      <c r="D21" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E21" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="F21" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G21" s="4">
+      <c r="F21" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G21" s="6">
         <v>2025</v>
       </c>
-      <c r="H21" s="4" t="s">
+      <c r="H21" s="6" t="s">
         <v>95</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="J21" s="4"/>
-      <c r="K21" s="4"/>
-      <c r="L21" s="4" t="s">
+      <c r="J21" s="6"/>
+      <c r="K21" s="6"/>
+      <c r="L21" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="M21" s="4"/>
-      <c r="N21" s="4"/>
-      <c r="O21" s="4"/>
+      <c r="M21" s="6"/>
+      <c r="N21" s="6"/>
+      <c r="O21" s="6"/>
     </row>
     <row r="22" ht="25" customHeight="1" spans="1:15">
-      <c r="A22" s="15" t="s">
+      <c r="A22" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="D22" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E22" s="4" t="s">
+      <c r="D22" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E22" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="F22" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G22" s="4">
+      <c r="F22" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G22" s="6">
         <v>2026</v>
       </c>
-      <c r="H22" s="4" t="s">
+      <c r="H22" s="6" t="s">
         <v>101</v>
       </c>
       <c r="I22" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="J22" s="4"/>
-      <c r="K22" s="4"/>
-      <c r="L22" s="4" t="s">
+      <c r="J22" s="6"/>
+      <c r="K22" s="6"/>
+      <c r="L22" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="M22" s="4"/>
-      <c r="N22" s="4"/>
-      <c r="O22" s="4"/>
+      <c r="M22" s="6"/>
+      <c r="N22" s="6"/>
+      <c r="O22" s="6"/>
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:15">
-      <c r="A23" s="15" t="s">
+      <c r="A23" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="D23" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E23" s="4" t="s">
+      <c r="D23" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E23" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="F23" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G23" s="4">
+      <c r="F23" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G23" s="6">
         <v>2026</v>
       </c>
-      <c r="H23" s="4" t="s">
+      <c r="H23" s="6" t="s">
         <v>107</v>
       </c>
       <c r="I23" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="J23" s="4"/>
-      <c r="K23" s="4"/>
-      <c r="L23" s="4" t="s">
+      <c r="J23" s="6"/>
+      <c r="K23" s="6"/>
+      <c r="L23" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="M23" s="4"/>
-      <c r="N23" s="4"/>
-      <c r="O23" s="4"/>
+      <c r="M23" s="6"/>
+      <c r="N23" s="6"/>
+      <c r="O23" s="6"/>
     </row>
     <row r="24" ht="25" customHeight="1" spans="1:15">
-      <c r="A24" s="15" t="s">
+      <c r="A24" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="D24" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E24" s="4" t="s">
+      <c r="D24" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E24" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="F24" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G24" s="4">
+      <c r="F24" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G24" s="6">
         <v>2025</v>
       </c>
-      <c r="H24" s="4" t="s">
+      <c r="H24" s="6" t="s">
         <v>113</v>
       </c>
       <c r="I24" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="J24" s="4"/>
-      <c r="K24" s="4"/>
-      <c r="L24" s="4" t="s">
+      <c r="J24" s="6"/>
+      <c r="K24" s="6"/>
+      <c r="L24" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="M24" s="4"/>
-      <c r="N24" s="4"/>
-      <c r="O24" s="4"/>
+      <c r="M24" s="6"/>
+      <c r="N24" s="6"/>
+      <c r="O24" s="6"/>
     </row>
     <row r="25" ht="25" customHeight="1" spans="1:15">
-      <c r="A25" s="15" t="s">
+      <c r="A25" s="17" t="s">
         <v>116</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="D25" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E25" s="4" t="s">
+      <c r="D25" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E25" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="F25" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G25" s="4">
+      <c r="F25" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G25" s="6">
         <v>2026</v>
       </c>
-      <c r="H25" s="4" t="s">
+      <c r="H25" s="6" t="s">
         <v>119</v>
       </c>
       <c r="I25" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="J25" s="18"/>
-      <c r="K25" s="18"/>
-      <c r="L25" s="18" t="s">
+      <c r="J25" s="21"/>
+      <c r="K25" s="21"/>
+      <c r="L25" s="21" t="s">
         <v>121</v>
       </c>
-      <c r="M25" s="18"/>
-      <c r="N25" s="18"/>
-      <c r="O25" s="4"/>
+      <c r="M25" s="21"/>
+      <c r="N25" s="21"/>
+      <c r="O25" s="6"/>
     </row>
     <row r="26" ht="25" customHeight="1" spans="1:15">
-      <c r="A26" s="15" t="s">
+      <c r="A26" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="D26" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E26" s="4" t="s">
+      <c r="D26" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E26" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="F26" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G26" s="4">
+      <c r="F26" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G26" s="6">
         <v>2026</v>
       </c>
-      <c r="H26" s="4" t="s">
+      <c r="H26" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="I26" s="4" t="s">
+      <c r="I26" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="J26" s="4"/>
-      <c r="K26" s="4"/>
-      <c r="L26" s="4" t="s">
+      <c r="J26" s="6"/>
+      <c r="K26" s="6"/>
+      <c r="L26" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="M26" s="4"/>
-      <c r="N26" s="4"/>
-      <c r="O26" s="28"/>
+      <c r="M26" s="6"/>
+      <c r="N26" s="6"/>
+      <c r="O26" s="31"/>
     </row>
     <row r="27" ht="25" customHeight="1" spans="1:15">
-      <c r="A27" s="15" t="s">
+      <c r="A27" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C27" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="D27" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E27" s="4" t="s">
+      <c r="D27" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E27" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="F27" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G27" s="4">
+      <c r="F27" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G27" s="6">
         <v>2024</v>
       </c>
-      <c r="H27" s="4" t="s">
+      <c r="H27" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="I27" s="4" t="s">
+      <c r="I27" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="J27" s="4"/>
-      <c r="K27" s="4"/>
-      <c r="L27" s="4" t="s">
+      <c r="J27" s="6"/>
+      <c r="K27" s="6"/>
+      <c r="L27" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="M27" s="4"/>
-      <c r="N27" s="4"/>
-      <c r="O27" s="28"/>
+      <c r="M27" s="6"/>
+      <c r="N27" s="6"/>
+      <c r="O27" s="31"/>
     </row>
     <row r="28" ht="25" customHeight="1" spans="1:15">
-      <c r="A28" s="15" t="s">
+      <c r="A28" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="D28" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E28" s="4" t="s">
+      <c r="D28" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E28" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="F28" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G28" s="4">
+      <c r="F28" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G28" s="6">
         <v>2024</v>
       </c>
-      <c r="H28" s="4" t="s">
+      <c r="H28" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="I28" s="4" t="s">
+      <c r="I28" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="J28" s="4"/>
-      <c r="K28" s="4"/>
-      <c r="L28" s="4" t="s">
+      <c r="J28" s="6"/>
+      <c r="K28" s="6"/>
+      <c r="L28" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="M28" s="4"/>
-      <c r="N28" s="4"/>
-      <c r="O28" s="28"/>
+      <c r="M28" s="6"/>
+      <c r="N28" s="6"/>
+      <c r="O28" s="31"/>
     </row>
     <row r="29" ht="25" customHeight="1" spans="1:15">
-      <c r="A29" s="15" t="s">
+      <c r="A29" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C29" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="D29" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E29" s="4" t="s">
+      <c r="D29" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E29" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="F29" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G29" s="4">
+      <c r="F29" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G29" s="6">
         <v>2026</v>
       </c>
-      <c r="H29" s="4" t="s">
+      <c r="H29" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="I29" s="4" t="s">
+      <c r="I29" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="J29" s="4"/>
-      <c r="K29" s="4"/>
-      <c r="L29" s="4" t="s">
+      <c r="J29" s="6"/>
+      <c r="K29" s="6"/>
+      <c r="L29" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="M29" s="4"/>
-      <c r="N29" s="4"/>
-      <c r="O29" s="28"/>
+      <c r="M29" s="6"/>
+      <c r="N29" s="6"/>
+      <c r="O29" s="31"/>
     </row>
     <row r="30" ht="25" customHeight="1" spans="1:15">
-      <c r="A30" s="15" t="s">
+      <c r="A30" s="17" t="s">
         <v>144</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C30" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="D30" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E30" s="4" t="s">
+      <c r="D30" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E30" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="F30" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G30" s="4">
+      <c r="F30" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G30" s="6">
         <v>2025</v>
       </c>
-      <c r="H30" s="4" t="s">
+      <c r="H30" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="I30" s="4" t="s">
+      <c r="I30" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="J30" s="4"/>
-      <c r="K30" s="4"/>
-      <c r="L30" s="4" t="s">
+      <c r="J30" s="6"/>
+      <c r="K30" s="6"/>
+      <c r="L30" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="M30" s="4"/>
-      <c r="N30" s="4"/>
-      <c r="O30" s="28"/>
+      <c r="M30" s="6"/>
+      <c r="N30" s="6"/>
+      <c r="O30" s="31"/>
     </row>
     <row r="31" ht="25" customHeight="1" spans="1:15">
-      <c r="A31" s="15" t="s">
+      <c r="A31" s="17" t="s">
         <v>150</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C31" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="D31" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E31" s="4" t="s">
+      <c r="D31" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E31" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="F31" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G31" s="4">
+      <c r="F31" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G31" s="6">
         <v>2026</v>
       </c>
-      <c r="H31" s="4" t="s">
+      <c r="H31" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="I31" s="4" t="s">
+      <c r="I31" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="J31" s="4"/>
-      <c r="K31" s="4"/>
-      <c r="L31" s="4" t="s">
+      <c r="J31" s="6"/>
+      <c r="K31" s="6"/>
+      <c r="L31" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="M31" s="4"/>
-      <c r="N31" s="4"/>
-      <c r="O31" s="28"/>
+      <c r="M31" s="6"/>
+      <c r="N31" s="6"/>
+      <c r="O31" s="31"/>
     </row>
     <row r="32" ht="25" customHeight="1" spans="1:15">
-      <c r="A32" s="15" t="s">
+      <c r="A32" s="17" t="s">
         <v>155</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="C32" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="D32" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E32" s="4" t="s">
+      <c r="D32" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E32" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="F32" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G32" s="4">
+      <c r="F32" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G32" s="6">
         <v>2026</v>
       </c>
-      <c r="H32" s="4" t="s">
+      <c r="H32" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="I32" s="4" t="s">
+      <c r="I32" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="J32" s="4"/>
-      <c r="K32" s="4"/>
-      <c r="L32" s="4" t="s">
+      <c r="J32" s="6"/>
+      <c r="K32" s="6"/>
+      <c r="L32" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="M32" s="4"/>
-      <c r="N32" s="4"/>
-      <c r="O32" s="28"/>
+      <c r="M32" s="6"/>
+      <c r="N32" s="6"/>
+      <c r="O32" s="31"/>
     </row>
     <row r="33" ht="25" customHeight="1" spans="1:15">
-      <c r="A33" s="15" t="s">
+      <c r="A33" s="17" t="s">
         <v>160</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B33" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="C33" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="D33" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E33" s="4" t="s">
+      <c r="D33" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E33" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="F33" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G33" s="4">
+      <c r="F33" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G33" s="6">
         <v>2026</v>
       </c>
-      <c r="H33" s="4" t="s">
+      <c r="H33" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="I33" s="4" t="s">
+      <c r="I33" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="J33" s="4"/>
-      <c r="K33" s="4"/>
-      <c r="L33" s="4" t="s">
+      <c r="J33" s="6"/>
+      <c r="K33" s="6"/>
+      <c r="L33" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="M33" s="4"/>
-      <c r="N33" s="4"/>
-      <c r="O33" s="28"/>
+      <c r="M33" s="6"/>
+      <c r="N33" s="6"/>
+      <c r="O33" s="31"/>
     </row>
     <row r="34" ht="25" customHeight="1" spans="1:15">
-      <c r="A34" s="15" t="s">
+      <c r="A34" s="17" t="s">
         <v>165</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="C34" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="D34" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E34" s="4" t="s">
+      <c r="D34" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E34" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="F34" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G34" s="4">
+      <c r="F34" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G34" s="6">
         <v>2025</v>
       </c>
-      <c r="H34" s="4" t="s">
+      <c r="H34" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="I34" s="4" t="s">
+      <c r="I34" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="J34" s="4"/>
-      <c r="K34" s="4"/>
-      <c r="L34" s="4" t="s">
+      <c r="J34" s="6"/>
+      <c r="K34" s="6"/>
+      <c r="L34" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="M34" s="4"/>
-      <c r="N34" s="4"/>
-      <c r="O34" s="28"/>
+      <c r="M34" s="6"/>
+      <c r="N34" s="6"/>
+      <c r="O34" s="31"/>
     </row>
     <row r="35" ht="25" customHeight="1" spans="1:15">
-      <c r="A35" s="15" t="s">
+      <c r="A35" s="17" t="s">
         <v>170</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C35" s="4" t="s">
+      <c r="C35" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="D35" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E35" s="4" t="s">
+      <c r="D35" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E35" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="F35" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G35" s="4">
+      <c r="F35" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G35" s="6">
         <v>2026</v>
       </c>
-      <c r="H35" s="4" t="s">
+      <c r="H35" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="I35" s="4" t="s">
+      <c r="I35" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="J35" s="4"/>
-      <c r="K35" s="4"/>
-      <c r="L35" s="4" t="s">
+      <c r="J35" s="6"/>
+      <c r="K35" s="6"/>
+      <c r="L35" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="M35" s="4"/>
-      <c r="N35" s="4"/>
-      <c r="O35" s="28"/>
+      <c r="M35" s="6"/>
+      <c r="N35" s="6"/>
+      <c r="O35" s="31"/>
     </row>
     <row r="36" ht="25" customHeight="1" spans="1:15">
-      <c r="A36" s="15" t="s">
+      <c r="A36" s="17" t="s">
         <v>176</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="C36" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="D36" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E36" s="4" t="s">
+      <c r="D36" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E36" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="F36" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G36" s="4">
+      <c r="F36" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G36" s="6">
         <v>2026</v>
       </c>
-      <c r="H36" s="4" t="s">
+      <c r="H36" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="I36" s="4" t="s">
+      <c r="I36" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="J36" s="4"/>
-      <c r="K36" s="4"/>
-      <c r="L36" s="4" t="s">
+      <c r="J36" s="6"/>
+      <c r="K36" s="6"/>
+      <c r="L36" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="M36" s="4"/>
-      <c r="N36" s="4"/>
-      <c r="O36" s="28"/>
+      <c r="M36" s="6"/>
+      <c r="N36" s="6"/>
+      <c r="O36" s="31"/>
     </row>
     <row r="37" ht="25" customHeight="1" spans="1:15">
-      <c r="A37" s="15" t="s">
+      <c r="A37" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="C37" s="4" t="s">
+      <c r="C37" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="D37" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E37" s="16" t="s">
+      <c r="D37" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E37" s="18" t="s">
         <v>184</v>
       </c>
-      <c r="F37" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G37" s="4">
+      <c r="F37" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G37" s="6">
         <v>2025</v>
       </c>
-      <c r="H37" s="4"/>
-      <c r="I37" s="4" t="s">
+      <c r="H37" s="6"/>
+      <c r="I37" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="J37" s="4"/>
-      <c r="K37" s="4"/>
-      <c r="L37" s="4" t="s">
+      <c r="J37" s="6"/>
+      <c r="K37" s="6"/>
+      <c r="L37" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="M37" s="4"/>
-      <c r="N37" s="4"/>
-      <c r="O37" s="28"/>
+      <c r="M37" s="6"/>
+      <c r="N37" s="6"/>
+      <c r="O37" s="31"/>
     </row>
     <row r="38" ht="25" customHeight="1" spans="1:15">
-      <c r="A38" s="15" t="s">
+      <c r="A38" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="C38" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="D38" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E38" s="16" t="s">
+      <c r="D38" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E38" s="18" t="s">
         <v>188</v>
       </c>
-      <c r="F38" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G38" s="4">
+      <c r="F38" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G38" s="6">
         <v>2025</v>
       </c>
-      <c r="H38" s="4" t="s">
+      <c r="H38" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="I38" s="4" t="s">
+      <c r="I38" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="J38" s="4"/>
-      <c r="K38" s="4"/>
-      <c r="L38" s="4" t="s">
+      <c r="J38" s="6"/>
+      <c r="K38" s="6"/>
+      <c r="L38" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="M38" s="4"/>
-      <c r="N38" s="4"/>
-      <c r="O38" s="28"/>
+      <c r="M38" s="6"/>
+      <c r="N38" s="6"/>
+      <c r="O38" s="31"/>
     </row>
     <row r="39" ht="25" customHeight="1" spans="1:15">
-      <c r="A39" s="15" t="s">
+      <c r="A39" s="17" t="s">
         <v>192</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="C39" s="4" t="s">
+      <c r="C39" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="D39" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E39" s="14" t="s">
+      <c r="D39" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E39" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="F39" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G39" s="4">
+      <c r="F39" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G39" s="6">
         <v>2025</v>
       </c>
-      <c r="H39" s="4"/>
-      <c r="I39" s="4" t="s">
+      <c r="H39" s="6"/>
+      <c r="I39" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="J39" s="4"/>
-      <c r="K39" s="4"/>
-      <c r="L39" s="4" t="s">
+      <c r="J39" s="6"/>
+      <c r="K39" s="6"/>
+      <c r="L39" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="M39" s="4"/>
-      <c r="N39" s="4"/>
-      <c r="O39" s="28"/>
+      <c r="M39" s="6"/>
+      <c r="N39" s="6"/>
+      <c r="O39" s="31"/>
     </row>
     <row r="40" ht="25" customHeight="1" spans="1:15">
-      <c r="A40" s="15" t="s">
+      <c r="A40" s="17" t="s">
         <v>195</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="C40" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="D40" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E40" s="4" t="s">
+      <c r="D40" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E40" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="F40" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G40" s="4">
+      <c r="F40" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G40" s="6">
         <v>2026</v>
       </c>
-      <c r="H40" s="4" t="s">
+      <c r="H40" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="I40" s="4" t="s">
+      <c r="I40" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="J40" s="4"/>
-      <c r="K40" s="4"/>
-      <c r="L40" s="4" t="s">
+      <c r="J40" s="6"/>
+      <c r="K40" s="6"/>
+      <c r="L40" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="M40" s="4"/>
-      <c r="N40" s="4"/>
-      <c r="O40" s="28"/>
+      <c r="M40" s="6"/>
+      <c r="N40" s="6"/>
+      <c r="O40" s="31"/>
     </row>
     <row r="41" ht="25" customHeight="1" spans="1:15">
-      <c r="A41" s="15" t="s">
+      <c r="A41" s="17" t="s">
         <v>200</v>
       </c>
-      <c r="B41" s="4"/>
-      <c r="C41" s="4"/>
-      <c r="D41" s="4"/>
-      <c r="E41" s="4"/>
-      <c r="F41" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G41" s="4"/>
-      <c r="H41" s="4"/>
-      <c r="I41" s="4" t="s">
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G41" s="6"/>
+      <c r="H41" s="6"/>
+      <c r="I41" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="J41" s="4"/>
-      <c r="K41" s="4"/>
-      <c r="L41" s="4"/>
-      <c r="M41" s="4"/>
-      <c r="N41" s="4"/>
-      <c r="O41" s="28"/>
+      <c r="J41" s="6"/>
+      <c r="K41" s="6"/>
+      <c r="L41" s="6"/>
+      <c r="M41" s="6"/>
+      <c r="N41" s="6"/>
+      <c r="O41" s="31"/>
     </row>
     <row r="42" ht="25" customHeight="1" spans="1:15">
-      <c r="A42" s="15" t="s">
+      <c r="A42" s="17" t="s">
         <v>202</v>
       </c>
-      <c r="B42" s="4"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="4"/>
-      <c r="E42" s="4"/>
-      <c r="F42" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G42" s="4"/>
-      <c r="H42" s="4"/>
-      <c r="I42" s="4" t="s">
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G42" s="6"/>
+      <c r="H42" s="6"/>
+      <c r="I42" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="J42" s="4"/>
-      <c r="K42" s="4"/>
-      <c r="L42" s="4"/>
-      <c r="M42" s="4"/>
-      <c r="N42" s="4"/>
-      <c r="O42" s="28"/>
+      <c r="J42" s="6"/>
+      <c r="K42" s="6"/>
+      <c r="L42" s="6"/>
+      <c r="M42" s="6"/>
+      <c r="N42" s="6"/>
+      <c r="O42" s="31"/>
     </row>
     <row r="43" ht="25" customHeight="1" spans="1:15">
-      <c r="A43" s="15" t="s">
+      <c r="A43" s="17" t="s">
         <v>204</v>
       </c>
-      <c r="B43" s="4"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="4"/>
-      <c r="E43" s="4"/>
-      <c r="F43" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G43" s="4"/>
-      <c r="H43" s="4"/>
-      <c r="I43" s="4" t="s">
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G43" s="6"/>
+      <c r="H43" s="6"/>
+      <c r="I43" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="J43" s="4"/>
-      <c r="K43" s="4"/>
-      <c r="L43" s="4"/>
-      <c r="M43" s="4"/>
-      <c r="N43" s="4"/>
-      <c r="O43" s="28"/>
+      <c r="J43" s="6"/>
+      <c r="K43" s="6"/>
+      <c r="L43" s="6"/>
+      <c r="M43" s="6"/>
+      <c r="N43" s="6"/>
+      <c r="O43" s="31"/>
     </row>
     <row r="44" ht="25" customHeight="1" spans="1:15">
-      <c r="A44" s="15" t="s">
+      <c r="A44" s="17" t="s">
         <v>206</v>
       </c>
-      <c r="B44" s="4"/>
-      <c r="C44" s="4"/>
-      <c r="D44" s="4"/>
-      <c r="E44" s="4"/>
-      <c r="F44" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G44" s="4"/>
-      <c r="H44" s="4"/>
-      <c r="I44" s="4" t="s">
+      <c r="B44" s="6"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="6"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G44" s="6"/>
+      <c r="H44" s="6"/>
+      <c r="I44" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="J44" s="4"/>
-      <c r="K44" s="4"/>
-      <c r="L44" s="4"/>
-      <c r="M44" s="4"/>
-      <c r="N44" s="4"/>
-      <c r="O44" s="28"/>
+      <c r="J44" s="6"/>
+      <c r="K44" s="6"/>
+      <c r="L44" s="6"/>
+      <c r="M44" s="6"/>
+      <c r="N44" s="6"/>
+      <c r="O44" s="31"/>
     </row>
     <row r="45" ht="25" customHeight="1" spans="1:15">
-      <c r="A45" s="17" t="s">
+      <c r="A45" s="20" t="s">
         <v>208</v>
       </c>
-      <c r="B45" s="18"/>
-      <c r="C45" s="18"/>
-      <c r="D45" s="18"/>
-      <c r="E45" s="18"/>
-      <c r="F45" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G45" s="18"/>
-      <c r="H45" s="18"/>
-      <c r="I45" s="19" t="s">
+      <c r="B45" s="21"/>
+      <c r="C45" s="21"/>
+      <c r="D45" s="21"/>
+      <c r="E45" s="21"/>
+      <c r="F45" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G45" s="21"/>
+      <c r="H45" s="21"/>
+      <c r="I45" s="22" t="s">
         <v>209</v>
       </c>
-      <c r="J45" s="18"/>
-      <c r="K45" s="4"/>
-      <c r="L45" s="4"/>
-      <c r="M45" s="4"/>
-      <c r="N45" s="4"/>
-      <c r="O45" s="28"/>
+      <c r="J45" s="21"/>
+      <c r="K45" s="6"/>
+      <c r="L45" s="6"/>
+      <c r="M45" s="6"/>
+      <c r="N45" s="6"/>
+      <c r="O45" s="31"/>
     </row>
     <row r="46" ht="25" customHeight="1" spans="1:15">
-      <c r="A46" s="15" t="s">
+      <c r="A46" s="17" t="s">
         <v>210</v>
       </c>
-      <c r="B46" s="4"/>
-      <c r="C46" s="4"/>
-      <c r="D46" s="4"/>
-      <c r="E46" s="4"/>
-      <c r="F46" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G46" s="4"/>
-      <c r="H46" s="4"/>
-      <c r="I46" s="4" t="s">
+      <c r="B46" s="6"/>
+      <c r="C46" s="6"/>
+      <c r="D46" s="6"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G46" s="6"/>
+      <c r="H46" s="6"/>
+      <c r="I46" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="J46" s="4"/>
-      <c r="K46" s="4"/>
-      <c r="L46" s="4"/>
-      <c r="M46" s="4"/>
-      <c r="N46" s="4"/>
-      <c r="O46" s="28"/>
+      <c r="J46" s="6"/>
+      <c r="K46" s="6"/>
+      <c r="L46" s="6"/>
+      <c r="M46" s="6"/>
+      <c r="N46" s="6"/>
+      <c r="O46" s="31"/>
     </row>
     <row r="47" ht="25" customHeight="1" spans="1:15">
-      <c r="A47" s="15" t="s">
+      <c r="A47" s="17" t="s">
         <v>212</v>
       </c>
-      <c r="B47" s="4"/>
-      <c r="C47" s="4"/>
-      <c r="D47" s="4"/>
-      <c r="E47" s="4"/>
-      <c r="F47" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G47" s="4"/>
-      <c r="H47" s="4"/>
-      <c r="I47" s="4" t="s">
+      <c r="B47" s="6"/>
+      <c r="C47" s="6"/>
+      <c r="D47" s="6"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G47" s="6"/>
+      <c r="H47" s="6"/>
+      <c r="I47" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="J47" s="4"/>
-      <c r="K47" s="4"/>
-      <c r="L47" s="4"/>
-      <c r="M47" s="4"/>
-      <c r="N47" s="4"/>
-      <c r="O47" s="28"/>
+      <c r="J47" s="6"/>
+      <c r="K47" s="6"/>
+      <c r="L47" s="6"/>
+      <c r="M47" s="6"/>
+      <c r="N47" s="6"/>
+      <c r="O47" s="31"/>
     </row>
     <row r="48" ht="25" customHeight="1" spans="1:15">
-      <c r="A48" s="15" t="s">
+      <c r="A48" s="17" t="s">
         <v>214</v>
       </c>
-      <c r="B48" s="4"/>
-      <c r="C48" s="4"/>
-      <c r="D48" s="4"/>
-      <c r="E48" s="4"/>
-      <c r="F48" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G48" s="4"/>
-      <c r="H48" s="4"/>
-      <c r="I48" s="4" t="s">
+      <c r="B48" s="6"/>
+      <c r="C48" s="6"/>
+      <c r="D48" s="6"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G48" s="6"/>
+      <c r="H48" s="6"/>
+      <c r="I48" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="J48" s="4"/>
-      <c r="K48" s="4"/>
-      <c r="L48" s="4"/>
-      <c r="M48" s="4"/>
-      <c r="N48" s="4"/>
-      <c r="O48" s="28"/>
+      <c r="J48" s="6"/>
+      <c r="K48" s="6"/>
+      <c r="L48" s="6"/>
+      <c r="M48" s="6"/>
+      <c r="N48" s="6"/>
+      <c r="O48" s="31"/>
     </row>
     <row r="49" ht="25" customHeight="1" spans="1:15">
-      <c r="A49" s="15" t="s">
+      <c r="A49" s="17" t="s">
         <v>216</v>
       </c>
-      <c r="B49" s="4"/>
-      <c r="C49" s="4"/>
-      <c r="D49" s="4"/>
-      <c r="E49" s="4"/>
-      <c r="F49" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G49" s="4"/>
-      <c r="H49" s="4"/>
-      <c r="I49" s="4" t="s">
+      <c r="B49" s="6"/>
+      <c r="C49" s="6"/>
+      <c r="D49" s="6"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G49" s="6"/>
+      <c r="H49" s="6"/>
+      <c r="I49" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="J49" s="4"/>
-      <c r="K49" s="4"/>
-      <c r="L49" s="4"/>
-      <c r="M49" s="4"/>
-      <c r="N49" s="4"/>
-      <c r="O49" s="28"/>
+      <c r="J49" s="6"/>
+      <c r="K49" s="6"/>
+      <c r="L49" s="6"/>
+      <c r="M49" s="6"/>
+      <c r="N49" s="6"/>
+      <c r="O49" s="31"/>
     </row>
     <row r="50" ht="25" customHeight="1" spans="1:15">
-      <c r="A50" s="15" t="s">
+      <c r="A50" s="17" t="s">
         <v>218</v>
       </c>
-      <c r="B50" s="4"/>
-      <c r="C50" s="4"/>
-      <c r="D50" s="4"/>
-      <c r="E50" s="4"/>
-      <c r="F50" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G50" s="4"/>
-      <c r="H50" s="4"/>
-      <c r="I50" s="4" t="s">
+      <c r="B50" s="6"/>
+      <c r="C50" s="6"/>
+      <c r="D50" s="6"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G50" s="6"/>
+      <c r="H50" s="6"/>
+      <c r="I50" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="J50" s="4"/>
-      <c r="K50" s="4"/>
-      <c r="L50" s="4"/>
-      <c r="M50" s="4"/>
-      <c r="N50" s="4"/>
-      <c r="O50" s="28"/>
+      <c r="J50" s="6"/>
+      <c r="K50" s="6"/>
+      <c r="L50" s="6"/>
+      <c r="M50" s="6"/>
+      <c r="N50" s="6"/>
+      <c r="O50" s="31"/>
     </row>
     <row r="51" ht="25" customHeight="1" spans="1:15">
-      <c r="A51" s="15" t="s">
+      <c r="A51" s="17" t="s">
         <v>220</v>
       </c>
-      <c r="B51" s="4"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="4"/>
-      <c r="E51" s="4"/>
-      <c r="F51" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G51" s="4"/>
-      <c r="H51" s="4"/>
-      <c r="I51" s="4" t="s">
+      <c r="B51" s="6"/>
+      <c r="C51" s="6"/>
+      <c r="D51" s="6"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G51" s="6"/>
+      <c r="H51" s="6"/>
+      <c r="I51" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="J51" s="4"/>
-      <c r="K51" s="4"/>
-      <c r="L51" s="4"/>
-      <c r="M51" s="4"/>
-      <c r="N51" s="4"/>
-      <c r="O51" s="28"/>
+      <c r="J51" s="6"/>
+      <c r="K51" s="6"/>
+      <c r="L51" s="6"/>
+      <c r="M51" s="6"/>
+      <c r="N51" s="6"/>
+      <c r="O51" s="31"/>
     </row>
     <row r="52" ht="25" customHeight="1" spans="1:15">
-      <c r="A52" s="15" t="s">
+      <c r="A52" s="17" t="s">
         <v>222</v>
       </c>
-      <c r="B52" s="4"/>
-      <c r="C52" s="4"/>
-      <c r="D52" s="4"/>
-      <c r="E52" s="4"/>
-      <c r="F52" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G52" s="4"/>
-      <c r="H52" s="4"/>
-      <c r="I52" s="4" t="s">
+      <c r="B52" s="6"/>
+      <c r="C52" s="6"/>
+      <c r="D52" s="6"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G52" s="6"/>
+      <c r="H52" s="6"/>
+      <c r="I52" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="J52" s="4"/>
-      <c r="K52" s="4"/>
-      <c r="L52" s="4"/>
-      <c r="M52" s="4"/>
-      <c r="N52" s="4"/>
-      <c r="O52" s="28"/>
+      <c r="J52" s="6"/>
+      <c r="K52" s="6"/>
+      <c r="L52" s="6"/>
+      <c r="M52" s="6"/>
+      <c r="N52" s="6"/>
+      <c r="O52" s="31"/>
     </row>
     <row r="53" ht="25" customHeight="1" spans="1:15">
-      <c r="A53" s="15" t="s">
+      <c r="A53" s="17" t="s">
         <v>224</v>
       </c>
-      <c r="B53" s="4"/>
-      <c r="C53" s="4"/>
-      <c r="D53" s="4"/>
-      <c r="E53" s="4"/>
-      <c r="F53" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G53" s="4"/>
-      <c r="H53" s="4"/>
-      <c r="I53" s="4" t="s">
+      <c r="B53" s="6"/>
+      <c r="C53" s="6"/>
+      <c r="D53" s="6"/>
+      <c r="E53" s="6"/>
+      <c r="F53" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G53" s="6"/>
+      <c r="H53" s="6"/>
+      <c r="I53" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="J53" s="4"/>
-      <c r="K53" s="4"/>
-      <c r="L53" s="4"/>
-      <c r="M53" s="4"/>
-      <c r="N53" s="4"/>
-      <c r="O53" s="28"/>
+      <c r="J53" s="6"/>
+      <c r="K53" s="6"/>
+      <c r="L53" s="6"/>
+      <c r="M53" s="6"/>
+      <c r="N53" s="6"/>
+      <c r="O53" s="31"/>
     </row>
     <row r="54" ht="25" customHeight="1" spans="1:15">
-      <c r="A54" s="15" t="s">
+      <c r="A54" s="17" t="s">
         <v>226</v>
       </c>
-      <c r="B54" s="4"/>
-      <c r="C54" s="4"/>
-      <c r="D54" s="4"/>
-      <c r="E54" s="4"/>
-      <c r="F54" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G54" s="4"/>
-      <c r="H54" s="4"/>
-      <c r="I54" s="4" t="s">
+      <c r="B54" s="6"/>
+      <c r="C54" s="6"/>
+      <c r="D54" s="6"/>
+      <c r="E54" s="6"/>
+      <c r="F54" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G54" s="6"/>
+      <c r="H54" s="6"/>
+      <c r="I54" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="J54" s="4"/>
-      <c r="K54" s="4"/>
-      <c r="L54" s="4"/>
-      <c r="M54" s="4"/>
-      <c r="N54" s="4"/>
-      <c r="O54" s="28"/>
+      <c r="J54" s="6"/>
+      <c r="K54" s="6"/>
+      <c r="L54" s="6"/>
+      <c r="M54" s="6"/>
+      <c r="N54" s="6"/>
+      <c r="O54" s="31"/>
     </row>
     <row r="55" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A55" s="15" t="s">
+      <c r="A55" s="17" t="s">
         <v>228</v>
       </c>
-      <c r="B55" s="4"/>
-      <c r="C55" s="4"/>
-      <c r="D55" s="4"/>
-      <c r="E55" s="4"/>
-      <c r="F55" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G55" s="4"/>
-      <c r="H55" s="4"/>
-      <c r="I55" s="4" t="s">
+      <c r="B55" s="6"/>
+      <c r="C55" s="6"/>
+      <c r="D55" s="6"/>
+      <c r="E55" s="6"/>
+      <c r="F55" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G55" s="6"/>
+      <c r="H55" s="6"/>
+      <c r="I55" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="J55" s="4"/>
-      <c r="K55" s="4"/>
-      <c r="L55" s="4"/>
-      <c r="M55" s="4"/>
-      <c r="N55" s="4"/>
-      <c r="O55" s="28"/>
+      <c r="J55" s="6"/>
+      <c r="K55" s="6"/>
+      <c r="L55" s="6"/>
+      <c r="M55" s="6"/>
+      <c r="N55" s="6"/>
+      <c r="O55" s="31"/>
     </row>
     <row r="56" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A56" s="15" t="s">
+      <c r="A56" s="17" t="s">
         <v>230</v>
       </c>
-      <c r="B56" s="4"/>
-      <c r="C56" s="4"/>
-      <c r="D56" s="4"/>
-      <c r="E56" s="4"/>
-      <c r="F56" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G56" s="4"/>
-      <c r="H56" s="4"/>
-      <c r="I56" s="4" t="s">
+      <c r="B56" s="6"/>
+      <c r="C56" s="6"/>
+      <c r="D56" s="6"/>
+      <c r="E56" s="6"/>
+      <c r="F56" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G56" s="6"/>
+      <c r="H56" s="6"/>
+      <c r="I56" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="J56" s="4"/>
-      <c r="K56" s="4"/>
-      <c r="L56" s="4"/>
-      <c r="M56" s="4"/>
-      <c r="N56" s="4"/>
-      <c r="O56" s="28"/>
+      <c r="J56" s="6"/>
+      <c r="K56" s="6"/>
+      <c r="L56" s="6"/>
+      <c r="M56" s="6"/>
+      <c r="N56" s="6"/>
+      <c r="O56" s="31"/>
     </row>
     <row r="57" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A57" s="15" t="s">
+      <c r="A57" s="17" t="s">
         <v>232</v>
       </c>
-      <c r="B57" s="4"/>
-      <c r="C57" s="4"/>
-      <c r="D57" s="4"/>
-      <c r="E57" s="4"/>
-      <c r="F57" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G57" s="4"/>
-      <c r="H57" s="4"/>
-      <c r="I57" s="4" t="s">
+      <c r="B57" s="6"/>
+      <c r="C57" s="6"/>
+      <c r="D57" s="6"/>
+      <c r="E57" s="6"/>
+      <c r="F57" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G57" s="6"/>
+      <c r="H57" s="6"/>
+      <c r="I57" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="J57" s="4"/>
-      <c r="K57" s="4"/>
-      <c r="L57" s="4"/>
-      <c r="M57" s="4"/>
-      <c r="N57" s="4"/>
-      <c r="O57" s="28"/>
+      <c r="J57" s="6"/>
+      <c r="K57" s="6"/>
+      <c r="L57" s="6"/>
+      <c r="M57" s="6"/>
+      <c r="N57" s="6"/>
+      <c r="O57" s="31"/>
     </row>
     <row r="58" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A58" s="15" t="s">
+      <c r="A58" s="17" t="s">
         <v>234</v>
       </c>
-      <c r="B58" s="4"/>
-      <c r="C58" s="4"/>
-      <c r="D58" s="4"/>
-      <c r="E58" s="4"/>
-      <c r="F58" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G58" s="4"/>
-      <c r="H58" s="4"/>
-      <c r="I58" s="4" t="s">
+      <c r="B58" s="6"/>
+      <c r="C58" s="6"/>
+      <c r="D58" s="6"/>
+      <c r="E58" s="6"/>
+      <c r="F58" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G58" s="6"/>
+      <c r="H58" s="6"/>
+      <c r="I58" s="6" t="s">
         <v>235</v>
       </c>
-      <c r="J58" s="4"/>
-      <c r="K58" s="4"/>
-      <c r="L58" s="4"/>
-      <c r="M58" s="4"/>
-      <c r="N58" s="4"/>
-      <c r="O58" s="28"/>
+      <c r="J58" s="6"/>
+      <c r="K58" s="6"/>
+      <c r="L58" s="6"/>
+      <c r="M58" s="6"/>
+      <c r="N58" s="6"/>
+      <c r="O58" s="31"/>
     </row>
     <row r="59" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A59" s="15" t="s">
+      <c r="A59" s="17" t="s">
         <v>236</v>
       </c>
-      <c r="B59" s="4" t="s">
+      <c r="B59" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C59" s="20" t="s">
+      <c r="C59" s="23" t="s">
         <v>237</v>
       </c>
-      <c r="D59" s="4"/>
-      <c r="E59" s="4" t="s">
+      <c r="D59" s="6"/>
+      <c r="E59" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="F59" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G59" s="4"/>
-      <c r="H59" s="21" t="s">
+      <c r="F59" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G59" s="6"/>
+      <c r="H59" s="24" t="s">
         <v>239</v>
       </c>
-      <c r="I59" s="4" t="s">
+      <c r="I59" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="J59" s="4"/>
-      <c r="K59" s="4"/>
-      <c r="L59" s="4"/>
-      <c r="M59" s="4"/>
-      <c r="N59" s="4"/>
-      <c r="O59" s="28"/>
+      <c r="J59" s="6"/>
+      <c r="K59" s="6"/>
+      <c r="L59" s="6"/>
+      <c r="M59" s="6"/>
+      <c r="N59" s="6"/>
+      <c r="O59" s="31"/>
     </row>
     <row r="60" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A60" s="15" t="s">
+      <c r="A60" s="17" t="s">
         <v>241</v>
       </c>
-      <c r="B60" s="4" t="s">
+      <c r="B60" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="C60" s="20" t="s">
+      <c r="C60" s="23" t="s">
         <v>242</v>
       </c>
-      <c r="D60" s="4"/>
-      <c r="E60" s="4" t="s">
+      <c r="D60" s="6"/>
+      <c r="E60" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="F60" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G60" s="4"/>
-      <c r="H60" s="21" t="s">
+      <c r="F60" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G60" s="6"/>
+      <c r="H60" s="24" t="s">
         <v>243</v>
       </c>
-      <c r="I60" s="4" t="s">
+      <c r="I60" s="6" t="s">
         <v>244</v>
       </c>
-      <c r="J60" s="4"/>
-      <c r="K60" s="4"/>
-      <c r="L60" s="4"/>
-      <c r="M60" s="4"/>
-      <c r="N60" s="4"/>
-      <c r="O60" s="4"/>
+      <c r="J60" s="6"/>
+      <c r="K60" s="6"/>
+      <c r="L60" s="6"/>
+      <c r="M60" s="6"/>
+      <c r="N60" s="6"/>
+      <c r="O60" s="6"/>
     </row>
     <row r="61" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A61" s="15" t="s">
+      <c r="A61" s="17" t="s">
         <v>245</v>
       </c>
-      <c r="B61" s="4" t="s">
+      <c r="B61" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C61" s="22" t="s">
+      <c r="C61" s="25" t="s">
         <v>246</v>
       </c>
-      <c r="D61" s="4"/>
-      <c r="E61" s="4" t="s">
+      <c r="D61" s="6"/>
+      <c r="E61" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="F61" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G61" s="4"/>
-      <c r="H61" s="21" t="s">
+      <c r="F61" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G61" s="6"/>
+      <c r="H61" s="24" t="s">
         <v>247</v>
       </c>
-      <c r="I61" s="4" t="s">
+      <c r="I61" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="J61" s="4"/>
-      <c r="K61" s="4"/>
-      <c r="L61" s="4"/>
-      <c r="M61" s="4"/>
-      <c r="N61" s="4"/>
-      <c r="O61" s="28"/>
+      <c r="J61" s="6"/>
+      <c r="K61" s="6"/>
+      <c r="L61" s="6"/>
+      <c r="M61" s="6"/>
+      <c r="N61" s="6"/>
+      <c r="O61" s="31"/>
     </row>
     <row r="62" ht="25" customHeight="1" spans="1:15">
-      <c r="A62" s="15" t="s">
+      <c r="A62" s="17" t="s">
         <v>249</v>
       </c>
-      <c r="B62" s="4" t="s">
+      <c r="B62" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C62" s="20" t="s">
+      <c r="C62" s="23" t="s">
         <v>250</v>
       </c>
-      <c r="D62" s="4"/>
-      <c r="E62" s="4" t="s">
+      <c r="D62" s="6"/>
+      <c r="E62" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="F62" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G62" s="4"/>
-      <c r="H62" s="21" t="s">
+      <c r="F62" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G62" s="6"/>
+      <c r="H62" s="24" t="s">
         <v>252</v>
       </c>
-      <c r="I62" s="4" t="s">
+      <c r="I62" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="J62" s="4"/>
-      <c r="K62" s="4"/>
-      <c r="L62" s="4"/>
-      <c r="M62" s="4"/>
-      <c r="N62" s="4"/>
-      <c r="O62" s="28"/>
+      <c r="J62" s="6"/>
+      <c r="K62" s="6"/>
+      <c r="L62" s="6"/>
+      <c r="M62" s="6"/>
+      <c r="N62" s="6"/>
+      <c r="O62" s="31"/>
     </row>
     <row r="63" ht="25" customHeight="1" spans="1:15">
-      <c r="A63" s="15" t="s">
+      <c r="A63" s="17" t="s">
         <v>254</v>
       </c>
-      <c r="B63" s="4" t="s">
+      <c r="B63" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C63" s="20" t="s">
+      <c r="C63" s="23" t="s">
         <v>255</v>
       </c>
-      <c r="D63" s="4"/>
-      <c r="E63" s="4" t="s">
+      <c r="D63" s="6"/>
+      <c r="E63" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="F63" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G63" s="4"/>
-      <c r="H63" s="21" t="s">
+      <c r="F63" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G63" s="6"/>
+      <c r="H63" s="24" t="s">
         <v>256</v>
       </c>
-      <c r="I63" s="4" t="s">
+      <c r="I63" s="6" t="s">
         <v>257</v>
       </c>
-      <c r="J63" s="4"/>
-      <c r="K63" s="4"/>
-      <c r="L63" s="4"/>
-      <c r="M63" s="4"/>
-      <c r="N63" s="4"/>
-      <c r="O63" s="28"/>
+      <c r="J63" s="6"/>
+      <c r="K63" s="6"/>
+      <c r="L63" s="6"/>
+      <c r="M63" s="6"/>
+      <c r="N63" s="6"/>
+      <c r="O63" s="31"/>
     </row>
     <row r="64" ht="25" customHeight="1" spans="1:15">
-      <c r="A64" s="15" t="s">
+      <c r="A64" s="17" t="s">
         <v>258</v>
       </c>
-      <c r="B64" s="4" t="s">
+      <c r="B64" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="C64" s="20" t="s">
+      <c r="C64" s="23" t="s">
         <v>259</v>
       </c>
-      <c r="D64" s="4"/>
-      <c r="E64" s="4" t="s">
+      <c r="D64" s="6"/>
+      <c r="E64" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="F64" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G64" s="4"/>
-      <c r="H64" s="21" t="s">
+      <c r="F64" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G64" s="6"/>
+      <c r="H64" s="24" t="s">
         <v>261</v>
       </c>
-      <c r="I64" s="4" t="s">
+      <c r="I64" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="J64" s="4"/>
-      <c r="K64" s="4"/>
-      <c r="L64" s="4"/>
-      <c r="M64" s="4"/>
-      <c r="N64" s="4"/>
-      <c r="O64" s="28"/>
+      <c r="J64" s="6"/>
+      <c r="K64" s="6"/>
+      <c r="L64" s="6"/>
+      <c r="M64" s="6"/>
+      <c r="N64" s="6"/>
+      <c r="O64" s="31"/>
     </row>
     <row r="65" ht="25" customHeight="1" spans="1:15">
-      <c r="A65" s="15"/>
-      <c r="B65" s="4"/>
-      <c r="C65" s="4"/>
-      <c r="D65" s="4"/>
-      <c r="E65" s="4"/>
-      <c r="F65" s="16"/>
-      <c r="G65" s="4"/>
-      <c r="H65" s="4"/>
-      <c r="I65" s="4"/>
-      <c r="J65" s="4"/>
-      <c r="K65" s="4"/>
-      <c r="L65" s="4"/>
-      <c r="M65" s="4"/>
-      <c r="N65" s="4"/>
-      <c r="O65" s="4"/>
+      <c r="A65" s="17"/>
+      <c r="B65" s="6"/>
+      <c r="C65" s="6"/>
+      <c r="D65" s="6"/>
+      <c r="E65" s="6"/>
+      <c r="F65" s="18"/>
+      <c r="G65" s="6"/>
+      <c r="H65" s="6"/>
+      <c r="I65" s="6"/>
+      <c r="J65" s="6"/>
+      <c r="K65" s="6"/>
+      <c r="L65" s="6"/>
+      <c r="M65" s="6"/>
+      <c r="N65" s="6"/>
+      <c r="O65" s="6"/>
     </row>
     <row r="66" ht="25" customHeight="1" spans="1:15">
-      <c r="A66" s="15"/>
-      <c r="B66" s="4"/>
-      <c r="C66" s="4"/>
-      <c r="D66" s="4"/>
-      <c r="E66" s="4"/>
-      <c r="F66" s="16"/>
-      <c r="G66" s="4"/>
-      <c r="H66" s="4"/>
-      <c r="I66" s="4"/>
-      <c r="J66" s="4"/>
-      <c r="K66" s="4"/>
-      <c r="L66" s="4"/>
-      <c r="M66" s="4"/>
-      <c r="N66" s="4"/>
-      <c r="O66" s="4"/>
+      <c r="A66" s="17"/>
+      <c r="B66" s="6"/>
+      <c r="C66" s="6"/>
+      <c r="D66" s="6"/>
+      <c r="E66" s="6"/>
+      <c r="F66" s="18"/>
+      <c r="G66" s="6"/>
+      <c r="H66" s="6"/>
+      <c r="I66" s="6"/>
+      <c r="J66" s="6"/>
+      <c r="K66" s="6"/>
+      <c r="L66" s="6"/>
+      <c r="M66" s="6"/>
+      <c r="N66" s="6"/>
+      <c r="O66" s="6"/>
     </row>
     <row r="67" ht="25" customHeight="1" spans="1:15">
-      <c r="A67" s="15"/>
-      <c r="B67" s="4"/>
-      <c r="C67" s="4"/>
-      <c r="D67" s="4"/>
-      <c r="E67" s="4"/>
-      <c r="F67" s="16"/>
-      <c r="G67" s="4"/>
-      <c r="H67" s="4"/>
-      <c r="I67" s="4"/>
-      <c r="J67" s="4"/>
-      <c r="K67" s="4"/>
-      <c r="L67" s="4"/>
-      <c r="M67" s="4"/>
-      <c r="N67" s="4"/>
-      <c r="O67" s="4"/>
+      <c r="A67" s="17"/>
+      <c r="B67" s="6"/>
+      <c r="C67" s="6"/>
+      <c r="D67" s="6"/>
+      <c r="E67" s="6"/>
+      <c r="F67" s="18"/>
+      <c r="G67" s="6"/>
+      <c r="H67" s="6"/>
+      <c r="I67" s="6"/>
+      <c r="J67" s="6"/>
+      <c r="K67" s="6"/>
+      <c r="L67" s="6"/>
+      <c r="M67" s="6"/>
+      <c r="N67" s="6"/>
+      <c r="O67" s="6"/>
     </row>
     <row r="68" ht="25" customHeight="1" spans="1:15">
-      <c r="A68" s="15"/>
-      <c r="B68" s="4"/>
-      <c r="C68" s="4"/>
-      <c r="D68" s="4"/>
-      <c r="E68" s="4"/>
-      <c r="F68" s="16"/>
-      <c r="G68" s="4"/>
-      <c r="H68" s="4"/>
-      <c r="I68" s="4"/>
-      <c r="J68" s="4"/>
-      <c r="K68" s="4"/>
-      <c r="L68" s="4"/>
-      <c r="M68" s="4"/>
-      <c r="N68" s="4"/>
-      <c r="O68" s="4"/>
+      <c r="A68" s="17"/>
+      <c r="B68" s="6"/>
+      <c r="C68" s="6"/>
+      <c r="D68" s="6"/>
+      <c r="E68" s="6"/>
+      <c r="F68" s="18"/>
+      <c r="G68" s="6"/>
+      <c r="H68" s="6"/>
+      <c r="I68" s="6"/>
+      <c r="J68" s="6"/>
+      <c r="K68" s="6"/>
+      <c r="L68" s="6"/>
+      <c r="M68" s="6"/>
+      <c r="N68" s="6"/>
+      <c r="O68" s="6"/>
     </row>
     <row r="69" ht="25" customHeight="1" spans="1:15">
-      <c r="A69" s="15"/>
-      <c r="B69" s="4"/>
-      <c r="C69" s="4"/>
-      <c r="D69" s="4"/>
-      <c r="E69" s="4"/>
-      <c r="F69" s="16"/>
-      <c r="G69" s="4"/>
-      <c r="H69" s="4"/>
-      <c r="I69" s="4"/>
-      <c r="J69" s="4"/>
-      <c r="K69" s="4"/>
-      <c r="L69" s="4"/>
-      <c r="M69" s="4"/>
-      <c r="N69" s="4"/>
-      <c r="O69" s="4"/>
+      <c r="A69" s="17"/>
+      <c r="B69" s="6"/>
+      <c r="C69" s="6"/>
+      <c r="D69" s="6"/>
+      <c r="E69" s="6"/>
+      <c r="F69" s="18"/>
+      <c r="G69" s="6"/>
+      <c r="H69" s="6"/>
+      <c r="I69" s="6"/>
+      <c r="J69" s="6"/>
+      <c r="K69" s="6"/>
+      <c r="L69" s="6"/>
+      <c r="M69" s="6"/>
+      <c r="N69" s="6"/>
+      <c r="O69" s="6"/>
     </row>
     <row r="70" ht="25" customHeight="1" spans="1:15">
-      <c r="A70" s="15"/>
-      <c r="B70" s="4"/>
-      <c r="C70" s="4"/>
-      <c r="D70" s="4"/>
-      <c r="E70" s="4"/>
-      <c r="F70" s="16"/>
-      <c r="G70" s="4"/>
-      <c r="H70" s="4"/>
-      <c r="I70" s="4"/>
-      <c r="J70" s="4"/>
-      <c r="K70" s="4"/>
-      <c r="L70" s="4"/>
-      <c r="M70" s="4"/>
-      <c r="N70" s="4"/>
-      <c r="O70" s="4"/>
+      <c r="A70" s="17"/>
+      <c r="B70" s="6"/>
+      <c r="C70" s="6"/>
+      <c r="D70" s="6"/>
+      <c r="E70" s="6"/>
+      <c r="F70" s="18"/>
+      <c r="G70" s="6"/>
+      <c r="H70" s="6"/>
+      <c r="I70" s="6"/>
+      <c r="J70" s="6"/>
+      <c r="K70" s="6"/>
+      <c r="L70" s="6"/>
+      <c r="M70" s="6"/>
+      <c r="N70" s="6"/>
+      <c r="O70" s="6"/>
     </row>
     <row r="71" ht="25" customHeight="1" spans="1:15">
-      <c r="A71" s="15"/>
-      <c r="B71" s="4"/>
-      <c r="C71" s="4"/>
-      <c r="D71" s="4"/>
-      <c r="E71" s="4"/>
-      <c r="F71" s="16"/>
-      <c r="G71" s="4"/>
-      <c r="H71" s="4"/>
-      <c r="I71" s="4"/>
-      <c r="J71" s="4"/>
-      <c r="K71" s="4"/>
-      <c r="L71" s="4"/>
-      <c r="M71" s="4"/>
-      <c r="N71" s="4"/>
-      <c r="O71" s="4"/>
+      <c r="A71" s="17"/>
+      <c r="B71" s="6"/>
+      <c r="C71" s="6"/>
+      <c r="D71" s="6"/>
+      <c r="E71" s="6"/>
+      <c r="F71" s="18"/>
+      <c r="G71" s="6"/>
+      <c r="H71" s="6"/>
+      <c r="I71" s="6"/>
+      <c r="J71" s="6"/>
+      <c r="K71" s="6"/>
+      <c r="L71" s="6"/>
+      <c r="M71" s="6"/>
+      <c r="N71" s="6"/>
+      <c r="O71" s="6"/>
     </row>
     <row r="72" ht="25" customHeight="1" spans="1:15">
-      <c r="A72" s="15"/>
-      <c r="B72" s="4"/>
-      <c r="C72" s="4"/>
-      <c r="D72" s="4"/>
-      <c r="E72" s="4"/>
-      <c r="F72" s="16"/>
-      <c r="G72" s="4"/>
-      <c r="H72" s="4"/>
-      <c r="I72" s="4"/>
-      <c r="J72" s="4"/>
-      <c r="K72" s="4"/>
-      <c r="L72" s="4"/>
-      <c r="M72" s="4"/>
-      <c r="N72" s="4"/>
-      <c r="O72" s="4"/>
+      <c r="A72" s="17"/>
+      <c r="B72" s="6"/>
+      <c r="C72" s="6"/>
+      <c r="D72" s="6"/>
+      <c r="E72" s="6"/>
+      <c r="F72" s="18"/>
+      <c r="G72" s="6"/>
+      <c r="H72" s="6"/>
+      <c r="I72" s="6"/>
+      <c r="J72" s="6"/>
+      <c r="K72" s="6"/>
+      <c r="L72" s="6"/>
+      <c r="M72" s="6"/>
+      <c r="N72" s="6"/>
+      <c r="O72" s="6"/>
     </row>
     <row r="73" ht="25" customHeight="1" spans="1:15">
-      <c r="A73" s="15"/>
-      <c r="B73" s="4"/>
-      <c r="C73" s="4"/>
-      <c r="D73" s="4"/>
-      <c r="E73" s="4"/>
-      <c r="F73" s="16"/>
-      <c r="G73" s="4"/>
-      <c r="H73" s="4"/>
-      <c r="I73" s="4"/>
-      <c r="J73" s="4"/>
-      <c r="K73" s="4"/>
-      <c r="L73" s="4"/>
-      <c r="M73" s="4"/>
-      <c r="N73" s="4"/>
-      <c r="O73" s="4"/>
+      <c r="A73" s="17"/>
+      <c r="B73" s="6"/>
+      <c r="C73" s="6"/>
+      <c r="D73" s="6"/>
+      <c r="E73" s="6"/>
+      <c r="F73" s="18"/>
+      <c r="G73" s="6"/>
+      <c r="H73" s="6"/>
+      <c r="I73" s="6"/>
+      <c r="J73" s="6"/>
+      <c r="K73" s="6"/>
+      <c r="L73" s="6"/>
+      <c r="M73" s="6"/>
+      <c r="N73" s="6"/>
+      <c r="O73" s="6"/>
     </row>
     <row r="74" ht="25" customHeight="1" spans="1:15">
-      <c r="A74" s="15"/>
-      <c r="B74" s="4"/>
-      <c r="C74" s="4"/>
-      <c r="D74" s="4"/>
-      <c r="E74" s="4"/>
-      <c r="F74" s="16"/>
-      <c r="G74" s="4"/>
-      <c r="H74" s="4"/>
-      <c r="I74" s="4"/>
-      <c r="J74" s="4"/>
-      <c r="K74" s="4"/>
-      <c r="L74" s="4"/>
-      <c r="M74" s="4"/>
-      <c r="N74" s="4"/>
-      <c r="O74" s="4"/>
+      <c r="A74" s="17"/>
+      <c r="B74" s="6"/>
+      <c r="C74" s="6"/>
+      <c r="D74" s="6"/>
+      <c r="E74" s="6"/>
+      <c r="F74" s="18"/>
+      <c r="G74" s="6"/>
+      <c r="H74" s="6"/>
+      <c r="I74" s="6"/>
+      <c r="J74" s="6"/>
+      <c r="K74" s="6"/>
+      <c r="L74" s="6"/>
+      <c r="M74" s="6"/>
+      <c r="N74" s="6"/>
+      <c r="O74" s="6"/>
     </row>
     <row r="75" ht="25" customHeight="1" spans="1:15">
-      <c r="A75" s="15"/>
-      <c r="B75" s="4"/>
-      <c r="C75" s="4"/>
-      <c r="D75" s="4"/>
-      <c r="E75" s="4"/>
-      <c r="F75" s="16"/>
-      <c r="G75" s="4"/>
-      <c r="H75" s="4"/>
-      <c r="I75" s="4"/>
-      <c r="J75" s="4"/>
-      <c r="K75" s="4"/>
-      <c r="L75" s="4"/>
-      <c r="M75" s="4"/>
-      <c r="N75" s="4"/>
-      <c r="O75" s="4"/>
+      <c r="A75" s="17"/>
+      <c r="B75" s="6"/>
+      <c r="C75" s="6"/>
+      <c r="D75" s="6"/>
+      <c r="E75" s="6"/>
+      <c r="F75" s="18"/>
+      <c r="G75" s="6"/>
+      <c r="H75" s="6"/>
+      <c r="I75" s="6"/>
+      <c r="J75" s="6"/>
+      <c r="K75" s="6"/>
+      <c r="L75" s="6"/>
+      <c r="M75" s="6"/>
+      <c r="N75" s="6"/>
+      <c r="O75" s="6"/>
     </row>
     <row r="76" ht="25" customHeight="1" spans="1:15">
-      <c r="A76" s="15"/>
-      <c r="B76" s="4"/>
-      <c r="C76" s="4"/>
-      <c r="D76" s="4"/>
-      <c r="E76" s="4"/>
-      <c r="F76" s="16"/>
-      <c r="G76" s="4"/>
-      <c r="H76" s="4"/>
-      <c r="I76" s="4"/>
-      <c r="J76" s="4"/>
-      <c r="K76" s="4"/>
-      <c r="L76" s="4"/>
-      <c r="M76" s="4"/>
-      <c r="N76" s="4"/>
-      <c r="O76" s="4"/>
+      <c r="A76" s="17"/>
+      <c r="B76" s="6"/>
+      <c r="C76" s="6"/>
+      <c r="D76" s="6"/>
+      <c r="E76" s="6"/>
+      <c r="F76" s="18"/>
+      <c r="G76" s="6"/>
+      <c r="H76" s="6"/>
+      <c r="I76" s="6"/>
+      <c r="J76" s="6"/>
+      <c r="K76" s="6"/>
+      <c r="L76" s="6"/>
+      <c r="M76" s="6"/>
+      <c r="N76" s="6"/>
+      <c r="O76" s="6"/>
     </row>
     <row r="77" ht="25" customHeight="1" spans="1:15">
-      <c r="A77" s="15"/>
-      <c r="B77" s="4"/>
-      <c r="C77" s="4"/>
-      <c r="D77" s="4"/>
-      <c r="E77" s="4"/>
-      <c r="F77" s="16"/>
-      <c r="G77" s="4"/>
-      <c r="H77" s="4"/>
-      <c r="I77" s="4"/>
-      <c r="J77" s="4"/>
-      <c r="K77" s="4"/>
-      <c r="L77" s="4"/>
-      <c r="M77" s="4"/>
-      <c r="N77" s="4"/>
-      <c r="O77" s="4"/>
+      <c r="A77" s="17"/>
+      <c r="B77" s="6"/>
+      <c r="C77" s="6"/>
+      <c r="D77" s="6"/>
+      <c r="E77" s="6"/>
+      <c r="F77" s="18"/>
+      <c r="G77" s="6"/>
+      <c r="H77" s="6"/>
+      <c r="I77" s="6"/>
+      <c r="J77" s="6"/>
+      <c r="K77" s="6"/>
+      <c r="L77" s="6"/>
+      <c r="M77" s="6"/>
+      <c r="N77" s="6"/>
+      <c r="O77" s="6"/>
     </row>
     <row r="78" ht="25" customHeight="1" spans="1:15">
-      <c r="A78" s="15"/>
-      <c r="B78" s="4"/>
-      <c r="C78" s="4"/>
-      <c r="D78" s="4"/>
-      <c r="E78" s="4"/>
-      <c r="F78" s="16"/>
-      <c r="G78" s="4"/>
-      <c r="H78" s="4"/>
-      <c r="I78" s="4"/>
-      <c r="J78" s="4"/>
-      <c r="K78" s="4"/>
-      <c r="L78" s="4"/>
-      <c r="M78" s="4"/>
-      <c r="N78" s="4"/>
-      <c r="O78" s="4"/>
+      <c r="A78" s="17"/>
+      <c r="B78" s="6"/>
+      <c r="C78" s="6"/>
+      <c r="D78" s="6"/>
+      <c r="E78" s="6"/>
+      <c r="F78" s="18"/>
+      <c r="G78" s="6"/>
+      <c r="H78" s="6"/>
+      <c r="I78" s="6"/>
+      <c r="J78" s="6"/>
+      <c r="K78" s="6"/>
+      <c r="L78" s="6"/>
+      <c r="M78" s="6"/>
+      <c r="N78" s="6"/>
+      <c r="O78" s="6"/>
     </row>
     <row r="79" ht="25" customHeight="1" spans="1:15">
-      <c r="A79" s="15"/>
-      <c r="B79" s="4"/>
-      <c r="C79" s="4"/>
-      <c r="D79" s="4"/>
-      <c r="E79" s="4"/>
-      <c r="F79" s="16"/>
-      <c r="G79" s="4"/>
-      <c r="H79" s="4"/>
-      <c r="I79" s="4"/>
-      <c r="J79" s="4"/>
-      <c r="K79" s="4"/>
-      <c r="L79" s="4"/>
-      <c r="M79" s="4"/>
-      <c r="N79" s="4"/>
-      <c r="O79" s="4"/>
+      <c r="A79" s="17"/>
+      <c r="B79" s="6"/>
+      <c r="C79" s="6"/>
+      <c r="D79" s="6"/>
+      <c r="E79" s="6"/>
+      <c r="F79" s="18"/>
+      <c r="G79" s="6"/>
+      <c r="H79" s="6"/>
+      <c r="I79" s="6"/>
+      <c r="J79" s="6"/>
+      <c r="K79" s="6"/>
+      <c r="L79" s="6"/>
+      <c r="M79" s="6"/>
+      <c r="N79" s="6"/>
+      <c r="O79" s="6"/>
     </row>
     <row r="80" ht="25" customHeight="1" spans="1:15">
-      <c r="A80" s="15"/>
-      <c r="B80" s="4"/>
-      <c r="C80" s="4"/>
-      <c r="D80" s="4"/>
-      <c r="E80" s="4"/>
-      <c r="F80" s="16"/>
-      <c r="G80" s="4"/>
-      <c r="H80" s="4"/>
-      <c r="I80" s="4"/>
-      <c r="J80" s="4"/>
-      <c r="K80" s="4"/>
-      <c r="L80" s="4"/>
-      <c r="M80" s="4"/>
-      <c r="N80" s="4"/>
-      <c r="O80" s="4"/>
+      <c r="A80" s="17"/>
+      <c r="B80" s="6"/>
+      <c r="C80" s="6"/>
+      <c r="D80" s="6"/>
+      <c r="E80" s="6"/>
+      <c r="F80" s="18"/>
+      <c r="G80" s="6"/>
+      <c r="H80" s="6"/>
+      <c r="I80" s="6"/>
+      <c r="J80" s="6"/>
+      <c r="K80" s="6"/>
+      <c r="L80" s="6"/>
+      <c r="M80" s="6"/>
+      <c r="N80" s="6"/>
+      <c r="O80" s="6"/>
     </row>
     <row r="81" ht="25" customHeight="1" spans="1:15">
-      <c r="A81" s="15"/>
-      <c r="B81" s="4"/>
-      <c r="C81" s="4"/>
-      <c r="D81" s="4"/>
-      <c r="E81" s="4"/>
-      <c r="F81" s="16"/>
-      <c r="G81" s="4"/>
-      <c r="H81" s="4"/>
-      <c r="I81" s="4"/>
-      <c r="J81" s="4"/>
-      <c r="K81" s="4"/>
-      <c r="L81" s="4"/>
-      <c r="M81" s="4"/>
-      <c r="N81" s="4"/>
-      <c r="O81" s="4"/>
+      <c r="A81" s="17"/>
+      <c r="B81" s="6"/>
+      <c r="C81" s="6"/>
+      <c r="D81" s="6"/>
+      <c r="E81" s="6"/>
+      <c r="F81" s="18"/>
+      <c r="G81" s="6"/>
+      <c r="H81" s="6"/>
+      <c r="I81" s="6"/>
+      <c r="J81" s="6"/>
+      <c r="K81" s="6"/>
+      <c r="L81" s="6"/>
+      <c r="M81" s="6"/>
+      <c r="N81" s="6"/>
+      <c r="O81" s="6"/>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:O64" etc:filterBottomFollowUsedRange="0">
@@ -4754,1809 +4786,1824 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I81"/>
+  <dimension ref="A1:I82"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="24.2666666666667" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="1"/>
     <col min="3" max="3" width="30.5833333333333" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9" style="1" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="13.375" style="1" customWidth="1"/>
     <col min="5" max="7" width="9" style="1"/>
-    <col min="8" max="8" width="80.2916666666667" style="1" customWidth="1"/>
+    <col min="8" max="8" width="79.1166666666667" style="1" customWidth="1"/>
     <col min="9" max="9" width="74.25" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="32" customHeight="1" spans="1:9">
+    <row r="1" ht="33" customHeight="1" spans="1:9">
       <c r="A1" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="32" customHeight="1" spans="1:9">
+      <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I2" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1" spans="1:9">
-      <c r="A2" s="5" t="s">
+    <row r="3" ht="30" customHeight="1" spans="1:9">
+      <c r="A3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="6" t="s">
-        <v>263</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="6">
+      <c r="C3" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="8">
         <v>4</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F3" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="7">
+      <c r="G3" s="9">
         <v>2026</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H3" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I3" s="10" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1" spans="1:9">
-      <c r="A3" s="5" t="s">
+    <row r="4" ht="30" customHeight="1" spans="1:9">
+      <c r="A4" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C4" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="7">
+      <c r="D4" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="9">
         <v>8</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F4" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="7">
+      <c r="G4" s="9">
         <v>2026</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H4" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I4" s="10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1" spans="1:9">
-      <c r="A4" s="5" t="s">
+    <row r="5" ht="30" customHeight="1" spans="1:9">
+      <c r="A5" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B5" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C5" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="7">
+      <c r="D5" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="9">
         <v>23</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F5" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G5" s="9">
         <v>2026</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H5" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="I5" s="10" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1" spans="1:9">
-      <c r="A5" s="5" t="s">
+    <row r="6" ht="30" customHeight="1" spans="1:9">
+      <c r="A6" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B6" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C6" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="7">
+      <c r="D6" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="9">
         <v>18</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F6" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G6" s="9">
         <v>2026</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="H6" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="I5" s="8" t="s">
+      <c r="I6" s="10" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1" spans="1:9">
-      <c r="A6" s="5" t="s">
+    <row r="7" ht="30" customHeight="1" spans="1:9">
+      <c r="A7" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B7" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C7" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="7">
+      <c r="D7" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="9">
         <v>20</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F7" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G7" s="9">
         <v>2026</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="H7" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="I7" s="10" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1" spans="1:9">
-      <c r="A7" s="5" t="s">
+    <row r="8" ht="30" customHeight="1" spans="1:9">
+      <c r="A8" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B8" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C8" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="7">
+      <c r="D8" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="9">
         <v>3</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F8" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G8" s="9">
         <v>2026</v>
       </c>
-      <c r="H7" s="6" t="s">
+      <c r="H8" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="I8" s="10" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1" spans="1:9">
-      <c r="A8" s="5" t="s">
+    <row r="9" ht="30" customHeight="1" spans="1:9">
+      <c r="A9" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B9" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C9" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="6">
+      <c r="D9" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="8">
         <v>4</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F9" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G9" s="9">
         <v>2026</v>
       </c>
-      <c r="H8" s="6" t="s">
+      <c r="H9" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="I8" s="8" t="s">
+      <c r="I9" s="10" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1" spans="1:9">
-      <c r="A9" s="5" t="s">
+    <row r="10" ht="30" customHeight="1" spans="1:9">
+      <c r="A10" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B10" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C10" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" s="7">
+      <c r="D10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="9">
         <v>6</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F10" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G9" s="7">
+      <c r="G10" s="9">
         <v>2026</v>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="H10" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="I9" s="10" t="s">
+      <c r="I10" s="12" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1" spans="1:9">
-      <c r="A10" s="5" t="s">
+    <row r="11" ht="30" customHeight="1" spans="1:9">
+      <c r="A11" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B11" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C11" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="D10" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="7">
+      <c r="D11" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="9">
         <v>6</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F11" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G10" s="7">
+      <c r="G11" s="9">
         <v>2026</v>
       </c>
-      <c r="H10" s="9" t="s">
+      <c r="H11" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="I10" s="10" t="s">
+      <c r="I11" s="12" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1" spans="1:9">
-      <c r="A11" s="5" t="s">
+    <row r="12" ht="30" customHeight="1" spans="1:9">
+      <c r="A12" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B12" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C12" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="D11" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="7">
+      <c r="D12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="9">
         <v>4</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="F12" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G11" s="7">
+      <c r="G12" s="9">
         <v>2026</v>
       </c>
-      <c r="H11" s="6" t="s">
+      <c r="H12" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="I11" s="10" t="s">
+      <c r="I12" s="12" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1" spans="1:9">
-      <c r="A12" s="5" t="s">
+    <row r="13" ht="30" customHeight="1" spans="1:9">
+      <c r="A13" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B13" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C13" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="D12" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E12" s="7">
+      <c r="D13" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="9">
         <v>6</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="F13" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G12" s="7">
+      <c r="G13" s="9">
         <v>2026</v>
       </c>
-      <c r="H12" s="9" t="s">
+      <c r="H13" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="I12" s="8" t="s">
+      <c r="I13" s="10" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1" spans="1:9">
-      <c r="A13" s="5" t="s">
+    <row r="14" ht="30" customHeight="1" spans="1:9">
+      <c r="A14" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B14" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C14" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="D13" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E13" s="7">
+      <c r="D14" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" s="9">
         <v>8</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="F14" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G13" s="7">
+      <c r="G14" s="9">
         <v>2026</v>
       </c>
-      <c r="H13" s="6" t="s">
+      <c r="H14" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="I13" s="8" t="s">
+      <c r="I14" s="10" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1" spans="1:9">
-      <c r="A14" s="5" t="s">
+    <row r="15" ht="30" customHeight="1" spans="1:9">
+      <c r="A15" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B15" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C15" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="D14" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" s="7">
+      <c r="D15" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" s="9">
         <v>4</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="F15" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G14" s="7">
+      <c r="G15" s="9">
         <v>2026</v>
       </c>
-      <c r="H14" s="9" t="s">
+      <c r="H15" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="I14" s="8" t="s">
+      <c r="I15" s="10" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1" spans="1:9">
-      <c r="A15" s="5" t="s">
+    <row r="16" ht="30" customHeight="1" spans="1:9">
+      <c r="A16" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B16" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C16" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="D15" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E15" s="7">
+      <c r="D16" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" s="9">
         <v>8</v>
       </c>
-      <c r="F15" s="6" t="s">
+      <c r="F16" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G15" s="7">
+      <c r="G16" s="9">
         <v>2026</v>
       </c>
-      <c r="H15" s="9" t="s">
+      <c r="H16" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="I15" s="8" t="s">
+      <c r="I16" s="10" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1" spans="1:9">
-      <c r="A16" s="5" t="s">
+    <row r="17" ht="30" customHeight="1" spans="1:9">
+      <c r="A17" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B17" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C17" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="D16" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E16" s="6">
+      <c r="D17" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E17" s="8">
         <v>7</v>
       </c>
-      <c r="F16" s="6" t="s">
+      <c r="F17" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G16" s="7">
+      <c r="G17" s="9">
         <v>2026</v>
       </c>
-      <c r="H16" s="6"/>
-      <c r="I16" s="8" t="s">
+      <c r="H17" s="8"/>
+      <c r="I17" s="10" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1" spans="1:9">
-      <c r="A17" s="5" t="s">
+    <row r="18" ht="30" customHeight="1" spans="1:9">
+      <c r="A18" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B18" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C18" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="D17" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E17" s="6">
+      <c r="D18" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="8">
         <v>4</v>
       </c>
-      <c r="F17" s="6" t="s">
+      <c r="F18" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G17" s="7">
+      <c r="G18" s="9">
         <v>2026</v>
       </c>
-      <c r="H17" s="6"/>
-      <c r="I17" s="8" t="s">
+      <c r="H18" s="8"/>
+      <c r="I18" s="10" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="18" ht="30" customHeight="1" spans="1:9">
-      <c r="A18" s="11" t="s">
+    <row r="19" ht="30" customHeight="1" spans="1:9">
+      <c r="A19" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="B18" s="12" t="s">
+      <c r="B19" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>264</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="G18" s="7">
+      <c r="C19" s="15" t="s">
+        <v>265</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="G19" s="9">
         <v>2026</v>
       </c>
-      <c r="H18" s="6"/>
-      <c r="I18" s="14" t="s">
+      <c r="H19" s="8"/>
+      <c r="I19" s="16" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1" spans="1:9">
-      <c r="A19" s="11" t="s">
+    <row r="20" ht="30" customHeight="1" spans="1:9">
+      <c r="A20" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="B19" s="12" t="s">
+      <c r="B20" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="C19" s="13" t="s">
-        <v>264</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="G19" s="7">
+      <c r="C20" s="15" t="s">
+        <v>265</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="G20" s="9">
         <v>2026</v>
       </c>
-      <c r="H19" s="6"/>
-      <c r="I19" s="14" t="s">
+      <c r="H20" s="8"/>
+      <c r="I20" s="16" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="20" ht="30" customHeight="1" spans="1:9">
-      <c r="A20" s="15" t="s">
+    <row r="21" ht="30" customHeight="1" spans="1:9">
+      <c r="A21" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B21" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C21" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="D20" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E20" s="4" t="s">
+      <c r="D21" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E21" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="F20" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G20" s="4">
+      <c r="F21" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G21" s="6">
         <v>2026</v>
       </c>
-      <c r="H20" s="4" t="s">
+      <c r="H21" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="I20" s="1" t="s">
+      <c r="I21" s="1" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="21" ht="30" customHeight="1" spans="1:9">
-      <c r="A21" s="15" t="s">
+    <row r="22" ht="30" customHeight="1" spans="1:9">
+      <c r="A22" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B22" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C22" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D21" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E21" s="4" t="s">
+      <c r="D22" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E22" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="F21" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G21" s="4">
+      <c r="F22" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G22" s="6">
         <v>2025</v>
       </c>
-      <c r="H21" s="4" t="s">
+      <c r="H22" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="I21" s="1" t="s">
+      <c r="I22" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="22" ht="30" customHeight="1" spans="1:9">
-      <c r="A22" s="15" t="s">
+    <row r="23" ht="30" customHeight="1" spans="1:9">
+      <c r="A23" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B23" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C23" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="D22" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E22" s="4" t="s">
+      <c r="D23" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E23" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="F22" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G22" s="4">
+      <c r="F23" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G23" s="6">
         <v>2026</v>
       </c>
-      <c r="H22" s="4" t="s">
+      <c r="H23" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="I22" s="1" t="s">
+      <c r="I23" s="1" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="23" ht="30" customHeight="1" spans="1:9">
-      <c r="A23" s="15" t="s">
+    <row r="24" ht="30" customHeight="1" spans="1:9">
+      <c r="A24" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B24" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C24" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="D23" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E23" s="4" t="s">
+      <c r="D24" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E24" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="F23" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G23" s="4">
+      <c r="F24" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G24" s="6">
         <v>2026</v>
       </c>
-      <c r="H23" s="4" t="s">
+      <c r="H24" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="I23" s="1" t="s">
+      <c r="I24" s="1" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="24" ht="30" customHeight="1" spans="1:9">
-      <c r="A24" s="15" t="s">
+    <row r="25" ht="30" customHeight="1" spans="1:9">
+      <c r="A25" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B25" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C25" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="D24" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E24" s="4" t="s">
+      <c r="D25" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E25" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="F24" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G24" s="4">
+      <c r="F25" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G25" s="6">
         <v>2025</v>
       </c>
-      <c r="H24" s="4" t="s">
+      <c r="H25" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="I24" s="1" t="s">
+      <c r="I25" s="1" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="25" ht="30" customHeight="1" spans="1:9">
-      <c r="A25" s="15" t="s">
+    <row r="26" ht="30" customHeight="1" spans="1:9">
+      <c r="A26" s="17" t="s">
         <v>116</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B26" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C26" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="D25" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E25" s="4" t="s">
+      <c r="D26" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E26" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="F25" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G25" s="4">
+      <c r="F26" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G26" s="6">
         <v>2026</v>
       </c>
-      <c r="H25" s="4" t="s">
+      <c r="H26" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="I25" s="1" t="s">
+      <c r="I26" s="1" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="26" ht="30" customHeight="1" spans="1:9">
-      <c r="A26" s="15" t="s">
+    <row r="27" ht="30" customHeight="1" spans="1:9">
+      <c r="A27" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B27" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C27" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="D26" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E26" s="4" t="s">
+      <c r="D27" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E27" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="F26" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G26" s="4">
+      <c r="F27" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G27" s="6">
         <v>2026</v>
       </c>
-      <c r="H26" s="4" t="s">
+      <c r="H27" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="I26" s="4" t="s">
+      <c r="I27" s="6" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="27" ht="30" customHeight="1" spans="1:9">
-      <c r="A27" s="15" t="s">
+    <row r="28" ht="30" customHeight="1" spans="1:9">
+      <c r="A28" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B28" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C28" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="D27" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E27" s="4" t="s">
+      <c r="D28" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E28" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="F27" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G27" s="4">
+      <c r="F28" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G28" s="6">
         <v>2024</v>
       </c>
-      <c r="H27" s="4" t="s">
+      <c r="H28" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="I27" s="4" t="s">
+      <c r="I28" s="6" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="28" ht="25" customHeight="1" spans="1:9">
-      <c r="A28" s="15" t="s">
+    <row r="29" ht="25" customHeight="1" spans="1:9">
+      <c r="A29" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B29" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C29" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="D28" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E28" s="4" t="s">
+      <c r="D29" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E29" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="F28" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G28" s="4">
+      <c r="F29" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G29" s="6">
         <v>2024</v>
       </c>
-      <c r="H28" s="4" t="s">
+      <c r="H29" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="I28" s="4" t="s">
+      <c r="I29" s="6" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="29" ht="25" customHeight="1" spans="1:9">
-      <c r="A29" s="15" t="s">
+    <row r="30" ht="25" customHeight="1" spans="1:9">
+      <c r="A30" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B30" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C30" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="D29" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E29" s="4" t="s">
+      <c r="D30" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E30" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="F29" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G29" s="4">
+      <c r="F30" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G30" s="6">
         <v>2026</v>
       </c>
-      <c r="H29" s="4" t="s">
+      <c r="H30" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="I29" s="4" t="s">
+      <c r="I30" s="6" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="30" ht="25" customHeight="1" spans="1:9">
-      <c r="A30" s="15" t="s">
+    <row r="31" ht="25" customHeight="1" spans="1:9">
+      <c r="A31" s="17" t="s">
         <v>144</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B31" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C31" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="D30" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E30" s="4" t="s">
+      <c r="D31" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E31" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="F30" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G30" s="4">
+      <c r="F31" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G31" s="6">
         <v>2025</v>
       </c>
-      <c r="H30" s="4" t="s">
+      <c r="H31" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="I30" s="4" t="s">
+      <c r="I31" s="6" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="31" ht="25" customHeight="1" spans="1:9">
-      <c r="A31" s="15" t="s">
+    <row r="32" ht="25" customHeight="1" spans="1:9">
+      <c r="A32" s="17" t="s">
         <v>150</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B32" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C32" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="D31" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E31" s="4" t="s">
+      <c r="D32" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E32" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="F31" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G31" s="4">
+      <c r="F32" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G32" s="6">
         <v>2026</v>
       </c>
-      <c r="H31" s="4" t="s">
+      <c r="H32" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="I31" s="4" t="s">
+      <c r="I32" s="6" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="32" ht="25" customHeight="1" spans="1:9">
-      <c r="A32" s="15" t="s">
+    <row r="33" ht="25" customHeight="1" spans="1:9">
+      <c r="A33" s="17" t="s">
         <v>155</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B33" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="C33" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="D32" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E32" s="4" t="s">
+      <c r="D33" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E33" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="F32" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G32" s="4">
+      <c r="F33" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G33" s="6">
         <v>2026</v>
       </c>
-      <c r="H32" s="4" t="s">
+      <c r="H33" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="I32" s="4" t="s">
+      <c r="I33" s="6" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="33" ht="25" customHeight="1" spans="1:9">
-      <c r="A33" s="15" t="s">
+    <row r="34" ht="25" customHeight="1" spans="1:9">
+      <c r="A34" s="17" t="s">
         <v>160</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B34" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="C34" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="D33" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E33" s="4" t="s">
+      <c r="D34" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E34" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="F33" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G33" s="4">
+      <c r="F34" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G34" s="6">
         <v>2026</v>
       </c>
-      <c r="H33" s="4" t="s">
+      <c r="H34" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="I33" s="4" t="s">
+      <c r="I34" s="6" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="34" ht="25" customHeight="1" spans="1:9">
-      <c r="A34" s="15" t="s">
+    <row r="35" ht="25" customHeight="1" spans="1:9">
+      <c r="A35" s="17" t="s">
         <v>165</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B35" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="C35" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="D34" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E34" s="4" t="s">
+      <c r="D35" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E35" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="F34" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G34" s="4">
+      <c r="F35" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G35" s="6">
         <v>2025</v>
       </c>
-      <c r="H34" s="4" t="s">
+      <c r="H35" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="I34" s="4" t="s">
+      <c r="I35" s="6" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="35" ht="25" customHeight="1" spans="1:9">
-      <c r="A35" s="15" t="s">
+    <row r="36" ht="25" customHeight="1" spans="1:9">
+      <c r="A36" s="17" t="s">
         <v>170</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B36" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C35" s="4" t="s">
+      <c r="C36" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="D35" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E35" s="4" t="s">
+      <c r="D36" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E36" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="F35" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G35" s="4">
+      <c r="F36" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G36" s="6">
         <v>2026</v>
       </c>
-      <c r="H35" s="4" t="s">
+      <c r="H36" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="I35" s="4" t="s">
+      <c r="I36" s="6" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="36" ht="25" customHeight="1" spans="1:9">
-      <c r="A36" s="15" t="s">
+    <row r="37" ht="25" customHeight="1" spans="1:9">
+      <c r="A37" s="17" t="s">
         <v>176</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B37" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="C37" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="D36" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E36" s="4" t="s">
+      <c r="D37" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E37" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="F36" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G36" s="4">
+      <c r="F37" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G37" s="6">
         <v>2026</v>
       </c>
-      <c r="H36" s="4" t="s">
+      <c r="H37" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="I36" s="4" t="s">
+      <c r="I37" s="6" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="37" ht="25" customHeight="1" spans="1:9">
-      <c r="A37" s="15" t="s">
+    <row r="38" ht="25" customHeight="1" spans="1:9">
+      <c r="A38" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B38" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="C37" s="4" t="s">
+      <c r="C38" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="D37" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E37" s="16" t="s">
+      <c r="D38" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E38" s="18" t="s">
         <v>184</v>
       </c>
-      <c r="F37" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G37" s="4">
+      <c r="F38" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G38" s="6">
         <v>2025</v>
       </c>
-      <c r="H37" s="4"/>
-      <c r="I37" s="4" t="s">
+      <c r="H38" s="6"/>
+      <c r="I38" s="6" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="38" ht="25" customHeight="1" spans="1:9">
-      <c r="A38" s="15" t="s">
+    <row r="39" ht="25" customHeight="1" spans="1:9">
+      <c r="A39" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B39" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="C39" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="D38" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E38" s="16" t="s">
+      <c r="D39" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E39" s="18" t="s">
         <v>188</v>
       </c>
-      <c r="F38" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G38" s="4">
+      <c r="F39" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G39" s="6">
         <v>2025</v>
       </c>
-      <c r="H38" s="4" t="s">
+      <c r="H39" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="I38" s="4" t="s">
+      <c r="I39" s="6" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="39" ht="25" customHeight="1" spans="1:9">
-      <c r="A39" s="15" t="s">
+    <row r="40" ht="25" customHeight="1" spans="1:9">
+      <c r="A40" s="17" t="s">
         <v>192</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B40" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="C39" s="4" t="s">
+      <c r="C40" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="D39" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E39" s="14" t="s">
+      <c r="D40" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E40" s="19" t="s">
         <v>184</v>
       </c>
-      <c r="F39" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G39" s="4">
+      <c r="F40" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G40" s="6">
         <v>2025</v>
       </c>
-      <c r="H39" s="4"/>
-      <c r="I39" s="4" t="s">
+      <c r="H40" s="6"/>
+      <c r="I40" s="6" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="40" ht="25" customHeight="1" spans="1:9">
-      <c r="A40" s="15" t="s">
+    <row r="41" ht="25" customHeight="1" spans="1:9">
+      <c r="A41" s="17" t="s">
         <v>195</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B41" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="C41" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="D40" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E40" s="4" t="s">
+      <c r="D41" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E41" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="F40" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G40" s="4">
+      <c r="F41" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G41" s="6">
         <v>2026</v>
       </c>
-      <c r="H40" s="4" t="s">
+      <c r="H41" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="I40" s="4" t="s">
+      <c r="I41" s="6" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="41" ht="25" customHeight="1" spans="1:9">
-      <c r="A41" s="15" t="s">
+    <row r="42" ht="25" customHeight="1" spans="1:9">
+      <c r="A42" s="17" t="s">
         <v>200</v>
       </c>
-      <c r="B41" s="4"/>
-      <c r="C41" s="4"/>
-      <c r="D41" s="4"/>
-      <c r="E41" s="4"/>
-      <c r="F41" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G41" s="4"/>
-      <c r="H41" s="4"/>
-      <c r="I41" s="4" t="s">
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G42" s="6"/>
+      <c r="H42" s="6"/>
+      <c r="I42" s="6" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="42" ht="25" customHeight="1" spans="1:9">
-      <c r="A42" s="15" t="s">
+    <row r="43" ht="25" customHeight="1" spans="1:9">
+      <c r="A43" s="17" t="s">
         <v>202</v>
       </c>
-      <c r="B42" s="4"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="4"/>
-      <c r="E42" s="4"/>
-      <c r="F42" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G42" s="4"/>
-      <c r="H42" s="4"/>
-      <c r="I42" s="4" t="s">
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G43" s="6"/>
+      <c r="H43" s="6"/>
+      <c r="I43" s="6" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="43" ht="25" customHeight="1" spans="1:9">
-      <c r="A43" s="15" t="s">
+    <row r="44" ht="25" customHeight="1" spans="1:9">
+      <c r="A44" s="17" t="s">
         <v>204</v>
       </c>
-      <c r="B43" s="4"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="4"/>
-      <c r="E43" s="4"/>
-      <c r="F43" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G43" s="4"/>
-      <c r="H43" s="4"/>
-      <c r="I43" s="4" t="s">
+      <c r="B44" s="6"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="6"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G44" s="6"/>
+      <c r="H44" s="6"/>
+      <c r="I44" s="6" t="s">
         <v>205</v>
-      </c>
-    </row>
-    <row r="44" ht="25" customHeight="1" spans="1:9">
-      <c r="A44" s="15" t="s">
-        <v>206</v>
-      </c>
-      <c r="B44" s="4"/>
-      <c r="C44" s="4"/>
-      <c r="D44" s="4"/>
-      <c r="E44" s="4"/>
-      <c r="F44" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G44" s="4"/>
-      <c r="H44" s="4"/>
-      <c r="I44" s="4" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="45" ht="25" customHeight="1" spans="1:9">
       <c r="A45" s="17" t="s">
+        <v>206</v>
+      </c>
+      <c r="B45" s="6"/>
+      <c r="C45" s="6"/>
+      <c r="D45" s="6"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G45" s="6"/>
+      <c r="H45" s="6"/>
+      <c r="I45" s="6" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="46" ht="25" customHeight="1" spans="1:9">
+      <c r="A46" s="20" t="s">
         <v>208</v>
       </c>
-      <c r="B45" s="18"/>
-      <c r="C45" s="18"/>
-      <c r="D45" s="18"/>
-      <c r="E45" s="18"/>
-      <c r="F45" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G45" s="18"/>
-      <c r="H45" s="18"/>
-      <c r="I45" s="19" t="s">
+      <c r="B46" s="21"/>
+      <c r="C46" s="21"/>
+      <c r="D46" s="21"/>
+      <c r="E46" s="21"/>
+      <c r="F46" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G46" s="21"/>
+      <c r="H46" s="21"/>
+      <c r="I46" s="22" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="46" ht="25" customHeight="1" spans="1:9">
-      <c r="A46" s="15" t="s">
+    <row r="47" ht="25" customHeight="1" spans="1:9">
+      <c r="A47" s="17" t="s">
         <v>210</v>
       </c>
-      <c r="B46" s="4"/>
-      <c r="C46" s="4"/>
-      <c r="D46" s="4"/>
-      <c r="E46" s="4"/>
-      <c r="F46" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G46" s="4"/>
-      <c r="H46" s="4"/>
-      <c r="I46" s="4" t="s">
+      <c r="B47" s="6"/>
+      <c r="C47" s="6"/>
+      <c r="D47" s="6"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G47" s="6"/>
+      <c r="H47" s="6"/>
+      <c r="I47" s="6" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="47" ht="25" customHeight="1" spans="1:9">
-      <c r="A47" s="15" t="s">
+    <row r="48" ht="25" customHeight="1" spans="1:9">
+      <c r="A48" s="17" t="s">
         <v>212</v>
       </c>
-      <c r="B47" s="4"/>
-      <c r="C47" s="4"/>
-      <c r="D47" s="4"/>
-      <c r="E47" s="4"/>
-      <c r="F47" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G47" s="4"/>
-      <c r="H47" s="4"/>
-      <c r="I47" s="4" t="s">
+      <c r="B48" s="6"/>
+      <c r="C48" s="6"/>
+      <c r="D48" s="6"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G48" s="6"/>
+      <c r="H48" s="6"/>
+      <c r="I48" s="6" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="48" ht="25" customHeight="1" spans="1:9">
-      <c r="A48" s="15" t="s">
+    <row r="49" ht="25" customHeight="1" spans="1:9">
+      <c r="A49" s="17" t="s">
         <v>214</v>
       </c>
-      <c r="B48" s="4"/>
-      <c r="C48" s="4"/>
-      <c r="D48" s="4"/>
-      <c r="E48" s="4"/>
-      <c r="F48" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G48" s="4"/>
-      <c r="H48" s="4"/>
-      <c r="I48" s="4" t="s">
+      <c r="B49" s="6"/>
+      <c r="C49" s="6"/>
+      <c r="D49" s="6"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G49" s="6"/>
+      <c r="H49" s="6"/>
+      <c r="I49" s="6" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="49" ht="25" customHeight="1" spans="1:9">
-      <c r="A49" s="15" t="s">
+    <row r="50" ht="25" customHeight="1" spans="1:9">
+      <c r="A50" s="17" t="s">
         <v>216</v>
       </c>
-      <c r="B49" s="4"/>
-      <c r="C49" s="4"/>
-      <c r="D49" s="4"/>
-      <c r="E49" s="4"/>
-      <c r="F49" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G49" s="4"/>
-      <c r="H49" s="4"/>
-      <c r="I49" s="4" t="s">
+      <c r="B50" s="6"/>
+      <c r="C50" s="6"/>
+      <c r="D50" s="6"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G50" s="6"/>
+      <c r="H50" s="6"/>
+      <c r="I50" s="6" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="50" ht="25" customHeight="1" spans="1:9">
-      <c r="A50" s="15" t="s">
+    <row r="51" ht="25" customHeight="1" spans="1:9">
+      <c r="A51" s="17" t="s">
         <v>218</v>
       </c>
-      <c r="B50" s="4"/>
-      <c r="C50" s="4"/>
-      <c r="D50" s="4"/>
-      <c r="E50" s="4"/>
-      <c r="F50" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G50" s="4"/>
-      <c r="H50" s="4"/>
-      <c r="I50" s="4" t="s">
+      <c r="B51" s="6"/>
+      <c r="C51" s="6"/>
+      <c r="D51" s="6"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G51" s="6"/>
+      <c r="H51" s="6"/>
+      <c r="I51" s="6" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="51" ht="25" customHeight="1" spans="1:9">
-      <c r="A51" s="15" t="s">
+    <row r="52" ht="25" customHeight="1" spans="1:9">
+      <c r="A52" s="17" t="s">
         <v>220</v>
       </c>
-      <c r="B51" s="4"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="4"/>
-      <c r="E51" s="4"/>
-      <c r="F51" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G51" s="4"/>
-      <c r="H51" s="4"/>
-      <c r="I51" s="4" t="s">
+      <c r="B52" s="6"/>
+      <c r="C52" s="6"/>
+      <c r="D52" s="6"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G52" s="6"/>
+      <c r="H52" s="6"/>
+      <c r="I52" s="6" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="52" ht="25" customHeight="1" spans="1:9">
-      <c r="A52" s="15" t="s">
+    <row r="53" customFormat="1" ht="25" customHeight="1" spans="1:9">
+      <c r="A53" s="17" t="s">
+        <v>236</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C53" s="23" t="s">
+        <v>237</v>
+      </c>
+      <c r="D53" s="6"/>
+      <c r="E53" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="F53" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G53" s="6"/>
+      <c r="H53" s="24" t="s">
+        <v>239</v>
+      </c>
+      <c r="I53" s="6" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="54" customFormat="1" ht="25" customHeight="1" spans="1:9">
+      <c r="A54" s="17" t="s">
+        <v>241</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="C54" s="23" t="s">
+        <v>242</v>
+      </c>
+      <c r="D54" s="6"/>
+      <c r="E54" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G54" s="6"/>
+      <c r="H54" s="24" t="s">
+        <v>243</v>
+      </c>
+      <c r="I54" s="6" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="55" customFormat="1" ht="25" customHeight="1" spans="1:9">
+      <c r="A55" s="17" t="s">
+        <v>245</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C55" s="25" t="s">
+        <v>246</v>
+      </c>
+      <c r="D55" s="6"/>
+      <c r="E55" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="F55" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G55" s="6"/>
+      <c r="H55" s="24" t="s">
+        <v>266</v>
+      </c>
+      <c r="I55" s="6" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="56" ht="25" customHeight="1" spans="1:9">
+      <c r="A56" s="17" t="s">
+        <v>249</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C56" s="23" t="s">
+        <v>250</v>
+      </c>
+      <c r="D56" s="6"/>
+      <c r="E56" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="F56" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G56" s="6"/>
+      <c r="H56" s="24" t="s">
+        <v>267</v>
+      </c>
+      <c r="I56" s="6" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="57" ht="25" customHeight="1" spans="1:9">
+      <c r="A57" s="17" t="s">
+        <v>254</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C57" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="D57" s="6"/>
+      <c r="E57" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="F57" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G57" s="6"/>
+      <c r="H57" s="24" t="s">
+        <v>268</v>
+      </c>
+      <c r="I57" s="6" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="58" ht="25" customHeight="1" spans="1:9">
+      <c r="A58" s="17" t="s">
+        <v>258</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C58" s="23" t="s">
+        <v>259</v>
+      </c>
+      <c r="D58" s="6"/>
+      <c r="E58" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="F58" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G58" s="6"/>
+      <c r="H58" s="24" t="s">
+        <v>269</v>
+      </c>
+      <c r="I58" s="6" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="59" ht="25" customHeight="1" spans="1:9">
+      <c r="A59" s="17" t="s">
         <v>222</v>
       </c>
-      <c r="B52" s="4"/>
-      <c r="C52" s="4"/>
-      <c r="D52" s="4"/>
-      <c r="E52" s="4"/>
-      <c r="F52" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G52" s="4"/>
-      <c r="H52" s="4"/>
-      <c r="I52" s="4" t="s">
+      <c r="B59" s="6"/>
+      <c r="C59" s="6"/>
+      <c r="D59" s="6"/>
+      <c r="E59" s="6"/>
+      <c r="F59" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G59" s="6"/>
+      <c r="H59" s="6"/>
+      <c r="I59" s="6" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="53" ht="25" customHeight="1" spans="1:9">
-      <c r="A53" s="15" t="s">
+    <row r="60" ht="25" customHeight="1" spans="1:9">
+      <c r="A60" s="17" t="s">
         <v>224</v>
       </c>
-      <c r="B53" s="4"/>
-      <c r="C53" s="4"/>
-      <c r="D53" s="4"/>
-      <c r="E53" s="4"/>
-      <c r="F53" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G53" s="4"/>
-      <c r="H53" s="4"/>
-      <c r="I53" s="4" t="s">
+      <c r="B60" s="6"/>
+      <c r="C60" s="6"/>
+      <c r="D60" s="6"/>
+      <c r="E60" s="6"/>
+      <c r="F60" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G60" s="6"/>
+      <c r="H60" s="6"/>
+      <c r="I60" s="6" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="54" ht="25" customHeight="1" spans="1:9">
-      <c r="A54" s="15" t="s">
+    <row r="61" ht="25" customHeight="1" spans="1:9">
+      <c r="A61" s="17" t="s">
         <v>226</v>
       </c>
-      <c r="B54" s="4"/>
-      <c r="C54" s="4"/>
-      <c r="D54" s="4"/>
-      <c r="E54" s="4"/>
-      <c r="F54" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G54" s="4"/>
-      <c r="H54" s="4"/>
-      <c r="I54" s="4" t="s">
+      <c r="B61" s="6"/>
+      <c r="C61" s="6"/>
+      <c r="D61" s="6"/>
+      <c r="E61" s="6"/>
+      <c r="F61" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G61" s="6"/>
+      <c r="H61" s="6"/>
+      <c r="I61" s="6" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="55" customFormat="1" ht="25" customHeight="1" spans="1:9">
-      <c r="A55" s="15" t="s">
+    <row r="62" customFormat="1" ht="25" customHeight="1" spans="1:9">
+      <c r="A62" s="17" t="s">
         <v>228</v>
       </c>
-      <c r="B55" s="4"/>
-      <c r="C55" s="4"/>
-      <c r="D55" s="4"/>
-      <c r="E55" s="4"/>
-      <c r="F55" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G55" s="4"/>
-      <c r="H55" s="4"/>
-      <c r="I55" s="4" t="s">
+      <c r="B62" s="6"/>
+      <c r="C62" s="6"/>
+      <c r="D62" s="6"/>
+      <c r="E62" s="6"/>
+      <c r="F62" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G62" s="6"/>
+      <c r="H62" s="6"/>
+      <c r="I62" s="6" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="56" customFormat="1" ht="25" customHeight="1" spans="1:9">
-      <c r="A56" s="15" t="s">
+    <row r="63" customFormat="1" ht="25" customHeight="1" spans="1:9">
+      <c r="A63" s="17" t="s">
         <v>230</v>
       </c>
-      <c r="B56" s="4"/>
-      <c r="C56" s="4"/>
-      <c r="D56" s="4"/>
-      <c r="E56" s="4"/>
-      <c r="F56" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G56" s="4"/>
-      <c r="H56" s="4"/>
-      <c r="I56" s="4" t="s">
+      <c r="B63" s="6"/>
+      <c r="C63" s="6"/>
+      <c r="D63" s="6"/>
+      <c r="E63" s="6"/>
+      <c r="F63" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G63" s="6"/>
+      <c r="H63" s="6"/>
+      <c r="I63" s="6" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="57" customFormat="1" ht="25" customHeight="1" spans="1:9">
-      <c r="A57" s="15" t="s">
+    <row r="64" customFormat="1" ht="25" customHeight="1" spans="1:9">
+      <c r="A64" s="17" t="s">
         <v>232</v>
       </c>
-      <c r="B57" s="4"/>
-      <c r="C57" s="4"/>
-      <c r="D57" s="4"/>
-      <c r="E57" s="4"/>
-      <c r="F57" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G57" s="4"/>
-      <c r="H57" s="4"/>
-      <c r="I57" s="4" t="s">
+      <c r="B64" s="6"/>
+      <c r="C64" s="6"/>
+      <c r="D64" s="6"/>
+      <c r="E64" s="6"/>
+      <c r="F64" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G64" s="6"/>
+      <c r="H64" s="6"/>
+      <c r="I64" s="6" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="58" customFormat="1" ht="25" customHeight="1" spans="1:9">
-      <c r="A58" s="15" t="s">
+    <row r="65" customFormat="1" ht="25" customHeight="1" spans="1:9">
+      <c r="A65" s="17" t="s">
         <v>234</v>
       </c>
-      <c r="B58" s="4"/>
-      <c r="C58" s="4"/>
-      <c r="D58" s="4"/>
-      <c r="E58" s="4"/>
-      <c r="F58" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G58" s="4"/>
-      <c r="H58" s="4"/>
-      <c r="I58" s="4" t="s">
+      <c r="B65" s="6"/>
+      <c r="C65" s="6"/>
+      <c r="D65" s="6"/>
+      <c r="E65" s="6"/>
+      <c r="F65" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G65" s="6"/>
+      <c r="H65" s="6"/>
+      <c r="I65" s="6" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="59" customFormat="1" ht="25" customHeight="1" spans="1:9">
-      <c r="A59" s="15" t="s">
-        <v>236</v>
-      </c>
-      <c r="B59" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C59" s="20" t="s">
-        <v>237</v>
-      </c>
-      <c r="D59" s="4"/>
-      <c r="E59" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="F59" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G59" s="4"/>
-      <c r="H59" s="21" t="s">
-        <v>239</v>
-      </c>
-      <c r="I59" s="4" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="60" customFormat="1" ht="25" customHeight="1" spans="1:9">
-      <c r="A60" s="15" t="s">
-        <v>241</v>
-      </c>
-      <c r="B60" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="C60" s="20" t="s">
-        <v>242</v>
-      </c>
-      <c r="D60" s="4"/>
-      <c r="E60" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="F60" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G60" s="4"/>
-      <c r="H60" s="21" t="s">
-        <v>243</v>
-      </c>
-      <c r="I60" s="4" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="61" customFormat="1" ht="25" customHeight="1" spans="1:9">
-      <c r="A61" s="15" t="s">
-        <v>245</v>
-      </c>
-      <c r="B61" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C61" s="22" t="s">
-        <v>246</v>
-      </c>
-      <c r="D61" s="4"/>
-      <c r="E61" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="F61" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G61" s="4"/>
-      <c r="H61" s="21" t="s">
-        <v>247</v>
-      </c>
-      <c r="I61" s="4" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="62" ht="25" customHeight="1" spans="1:9">
-      <c r="A62" s="15" t="s">
-        <v>249</v>
-      </c>
-      <c r="B62" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C62" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="D62" s="4"/>
-      <c r="E62" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="F62" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G62" s="4"/>
-      <c r="H62" s="21" t="s">
-        <v>252</v>
-      </c>
-      <c r="I62" s="4" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="63" ht="25" customHeight="1" spans="1:9">
-      <c r="A63" s="15" t="s">
-        <v>254</v>
-      </c>
-      <c r="B63" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C63" s="20" t="s">
-        <v>255</v>
-      </c>
-      <c r="D63" s="4"/>
-      <c r="E63" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="F63" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G63" s="4"/>
-      <c r="H63" s="21" t="s">
-        <v>256</v>
-      </c>
-      <c r="I63" s="4" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="64" ht="25" customHeight="1" spans="1:9">
-      <c r="A64" s="15" t="s">
-        <v>258</v>
-      </c>
-      <c r="B64" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C64" s="20" t="s">
-        <v>259</v>
-      </c>
-      <c r="D64" s="4"/>
-      <c r="E64" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="F64" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G64" s="4"/>
-      <c r="H64" s="21" t="s">
-        <v>261</v>
-      </c>
-      <c r="I64" s="4" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="65" ht="25" customHeight="1" spans="1:9">
-      <c r="A65" s="15"/>
-      <c r="B65" s="4"/>
-      <c r="C65" s="4"/>
-      <c r="D65" s="4"/>
-      <c r="E65" s="4"/>
-      <c r="F65" s="16"/>
-      <c r="G65" s="4"/>
-      <c r="H65" s="4"/>
-      <c r="I65" s="4"/>
-    </row>
     <row r="66" ht="25" customHeight="1" spans="1:9">
-      <c r="A66" s="15"/>
-      <c r="B66" s="4"/>
-      <c r="C66" s="4"/>
-      <c r="D66" s="4"/>
-      <c r="E66" s="4"/>
-      <c r="F66" s="16"/>
-      <c r="G66" s="4"/>
-      <c r="H66" s="4"/>
-      <c r="I66" s="4"/>
+      <c r="A66" s="17"/>
+      <c r="B66" s="6"/>
+      <c r="C66" s="6"/>
+      <c r="D66" s="6"/>
+      <c r="E66" s="6"/>
+      <c r="F66" s="18"/>
+      <c r="G66" s="6"/>
+      <c r="H66" s="6"/>
+      <c r="I66" s="6"/>
     </row>
     <row r="67" ht="25" customHeight="1" spans="1:9">
-      <c r="A67" s="15"/>
-      <c r="B67" s="4"/>
-      <c r="C67" s="4"/>
-      <c r="D67" s="4"/>
-      <c r="E67" s="4"/>
-      <c r="F67" s="16"/>
-      <c r="G67" s="4"/>
-      <c r="H67" s="4"/>
-      <c r="I67" s="4"/>
+      <c r="A67" s="17"/>
+      <c r="B67" s="6"/>
+      <c r="C67" s="6"/>
+      <c r="D67" s="6"/>
+      <c r="E67" s="6"/>
+      <c r="F67" s="18"/>
+      <c r="G67" s="6"/>
+      <c r="H67" s="6"/>
+      <c r="I67" s="6"/>
     </row>
     <row r="68" ht="25" customHeight="1" spans="1:9">
-      <c r="A68" s="15"/>
-      <c r="B68" s="4"/>
-      <c r="C68" s="4"/>
-      <c r="D68" s="4"/>
-      <c r="E68" s="4"/>
-      <c r="F68" s="16"/>
-      <c r="G68" s="4"/>
-      <c r="H68" s="4"/>
-      <c r="I68" s="4"/>
+      <c r="A68" s="17"/>
+      <c r="B68" s="6"/>
+      <c r="C68" s="6"/>
+      <c r="D68" s="6"/>
+      <c r="E68" s="6"/>
+      <c r="F68" s="18"/>
+      <c r="G68" s="6"/>
+      <c r="H68" s="6"/>
+      <c r="I68" s="6"/>
     </row>
     <row r="69" ht="25" customHeight="1" spans="1:9">
-      <c r="A69" s="15"/>
-      <c r="B69" s="4"/>
-      <c r="C69" s="4"/>
-      <c r="D69" s="4"/>
-      <c r="E69" s="4"/>
-      <c r="F69" s="16"/>
-      <c r="G69" s="4"/>
-      <c r="H69" s="4"/>
-      <c r="I69" s="4"/>
+      <c r="A69" s="17"/>
+      <c r="B69" s="6"/>
+      <c r="C69" s="6"/>
+      <c r="D69" s="6"/>
+      <c r="E69" s="6"/>
+      <c r="F69" s="18"/>
+      <c r="G69" s="6"/>
+      <c r="H69" s="6"/>
+      <c r="I69" s="6"/>
     </row>
     <row r="70" ht="25" customHeight="1" spans="1:9">
-      <c r="A70" s="15"/>
-      <c r="B70" s="4"/>
-      <c r="C70" s="4"/>
-      <c r="D70" s="4"/>
-      <c r="E70" s="4"/>
-      <c r="F70" s="16"/>
-      <c r="G70" s="4"/>
-      <c r="H70" s="4"/>
-      <c r="I70" s="4"/>
+      <c r="A70" s="17"/>
+      <c r="B70" s="6"/>
+      <c r="C70" s="6"/>
+      <c r="D70" s="6"/>
+      <c r="E70" s="6"/>
+      <c r="F70" s="18"/>
+      <c r="G70" s="6"/>
+      <c r="H70" s="6"/>
+      <c r="I70" s="6"/>
     </row>
     <row r="71" ht="25" customHeight="1" spans="1:9">
-      <c r="A71" s="15"/>
-      <c r="B71" s="4"/>
-      <c r="C71" s="4"/>
-      <c r="D71" s="4"/>
-      <c r="E71" s="4"/>
-      <c r="F71" s="16"/>
-      <c r="G71" s="4"/>
-      <c r="H71" s="4"/>
-      <c r="I71" s="4"/>
+      <c r="A71" s="17"/>
+      <c r="B71" s="6"/>
+      <c r="C71" s="6"/>
+      <c r="D71" s="6"/>
+      <c r="E71" s="6"/>
+      <c r="F71" s="18"/>
+      <c r="G71" s="6"/>
+      <c r="H71" s="6"/>
+      <c r="I71" s="6"/>
     </row>
     <row r="72" ht="25" customHeight="1" spans="1:9">
-      <c r="A72" s="15"/>
-      <c r="B72" s="4"/>
-      <c r="C72" s="4"/>
-      <c r="D72" s="4"/>
-      <c r="E72" s="4"/>
-      <c r="F72" s="16"/>
-      <c r="G72" s="4"/>
-      <c r="H72" s="4"/>
-      <c r="I72" s="4"/>
+      <c r="A72" s="17"/>
+      <c r="B72" s="6"/>
+      <c r="C72" s="6"/>
+      <c r="D72" s="6"/>
+      <c r="E72" s="6"/>
+      <c r="F72" s="18"/>
+      <c r="G72" s="6"/>
+      <c r="H72" s="6"/>
+      <c r="I72" s="6"/>
     </row>
     <row r="73" ht="25" customHeight="1" spans="1:9">
-      <c r="A73" s="15"/>
-      <c r="B73" s="4"/>
-      <c r="C73" s="4"/>
-      <c r="D73" s="4"/>
-      <c r="E73" s="4"/>
-      <c r="F73" s="16"/>
-      <c r="G73" s="4"/>
-      <c r="H73" s="4"/>
-      <c r="I73" s="4"/>
+      <c r="A73" s="17"/>
+      <c r="B73" s="6"/>
+      <c r="C73" s="6"/>
+      <c r="D73" s="6"/>
+      <c r="E73" s="6"/>
+      <c r="F73" s="18"/>
+      <c r="G73" s="6"/>
+      <c r="H73" s="6"/>
+      <c r="I73" s="6"/>
     </row>
     <row r="74" ht="25" customHeight="1" spans="1:9">
-      <c r="A74" s="15"/>
-      <c r="B74" s="4"/>
-      <c r="C74" s="4"/>
-      <c r="D74" s="4"/>
-      <c r="E74" s="4"/>
-      <c r="F74" s="16"/>
-      <c r="G74" s="4"/>
-      <c r="H74" s="4"/>
-      <c r="I74" s="4"/>
+      <c r="A74" s="17"/>
+      <c r="B74" s="6"/>
+      <c r="C74" s="6"/>
+      <c r="D74" s="6"/>
+      <c r="E74" s="6"/>
+      <c r="F74" s="18"/>
+      <c r="G74" s="6"/>
+      <c r="H74" s="6"/>
+      <c r="I74" s="6"/>
     </row>
     <row r="75" ht="25" customHeight="1" spans="1:9">
-      <c r="A75" s="15"/>
-      <c r="B75" s="4"/>
-      <c r="C75" s="4"/>
-      <c r="D75" s="4"/>
-      <c r="E75" s="4"/>
-      <c r="F75" s="16"/>
-      <c r="G75" s="4"/>
-      <c r="H75" s="4"/>
-      <c r="I75" s="4"/>
+      <c r="A75" s="17"/>
+      <c r="B75" s="6"/>
+      <c r="C75" s="6"/>
+      <c r="D75" s="6"/>
+      <c r="E75" s="6"/>
+      <c r="F75" s="18"/>
+      <c r="G75" s="6"/>
+      <c r="H75" s="6"/>
+      <c r="I75" s="6"/>
     </row>
     <row r="76" ht="25" customHeight="1" spans="1:9">
-      <c r="A76" s="15"/>
-      <c r="B76" s="4"/>
-      <c r="C76" s="4"/>
-      <c r="D76" s="4"/>
-      <c r="E76" s="4"/>
-      <c r="F76" s="16"/>
-      <c r="G76" s="4"/>
-      <c r="H76" s="4"/>
-      <c r="I76" s="4"/>
+      <c r="A76" s="17"/>
+      <c r="B76" s="6"/>
+      <c r="C76" s="6"/>
+      <c r="D76" s="6"/>
+      <c r="E76" s="6"/>
+      <c r="F76" s="18"/>
+      <c r="G76" s="6"/>
+      <c r="H76" s="6"/>
+      <c r="I76" s="6"/>
     </row>
     <row r="77" ht="25" customHeight="1" spans="1:9">
-      <c r="A77" s="15"/>
-      <c r="B77" s="4"/>
-      <c r="C77" s="4"/>
-      <c r="D77" s="4"/>
-      <c r="E77" s="4"/>
-      <c r="F77" s="16"/>
-      <c r="G77" s="4"/>
-      <c r="H77" s="4"/>
-      <c r="I77" s="4"/>
+      <c r="A77" s="17"/>
+      <c r="B77" s="6"/>
+      <c r="C77" s="6"/>
+      <c r="D77" s="6"/>
+      <c r="E77" s="6"/>
+      <c r="F77" s="18"/>
+      <c r="G77" s="6"/>
+      <c r="H77" s="6"/>
+      <c r="I77" s="6"/>
     </row>
     <row r="78" ht="25" customHeight="1" spans="1:9">
-      <c r="A78" s="15"/>
-      <c r="B78" s="4"/>
-      <c r="C78" s="4"/>
-      <c r="D78" s="4"/>
-      <c r="E78" s="4"/>
-      <c r="F78" s="16"/>
-      <c r="G78" s="4"/>
-      <c r="H78" s="4"/>
-      <c r="I78" s="4"/>
+      <c r="A78" s="17"/>
+      <c r="B78" s="6"/>
+      <c r="C78" s="6"/>
+      <c r="D78" s="6"/>
+      <c r="E78" s="6"/>
+      <c r="F78" s="18"/>
+      <c r="G78" s="6"/>
+      <c r="H78" s="6"/>
+      <c r="I78" s="6"/>
     </row>
     <row r="79" ht="25" customHeight="1" spans="1:9">
-      <c r="A79" s="15"/>
-      <c r="B79" s="4"/>
-      <c r="C79" s="4"/>
-      <c r="D79" s="4"/>
-      <c r="E79" s="4"/>
-      <c r="F79" s="16"/>
-      <c r="G79" s="4"/>
-      <c r="H79" s="4"/>
-      <c r="I79" s="4"/>
+      <c r="A79" s="17"/>
+      <c r="B79" s="6"/>
+      <c r="C79" s="6"/>
+      <c r="D79" s="6"/>
+      <c r="E79" s="6"/>
+      <c r="F79" s="18"/>
+      <c r="G79" s="6"/>
+      <c r="H79" s="6"/>
+      <c r="I79" s="6"/>
     </row>
     <row r="80" ht="25" customHeight="1" spans="1:9">
-      <c r="A80" s="15"/>
-      <c r="B80" s="4"/>
-      <c r="C80" s="4"/>
-      <c r="D80" s="4"/>
-      <c r="E80" s="4"/>
-      <c r="F80" s="16"/>
-      <c r="G80" s="4"/>
-      <c r="H80" s="4"/>
-      <c r="I80" s="4"/>
+      <c r="A80" s="17"/>
+      <c r="B80" s="6"/>
+      <c r="C80" s="6"/>
+      <c r="D80" s="6"/>
+      <c r="E80" s="6"/>
+      <c r="F80" s="18"/>
+      <c r="G80" s="6"/>
+      <c r="H80" s="6"/>
+      <c r="I80" s="6"/>
     </row>
     <row r="81" ht="25" customHeight="1" spans="1:9">
-      <c r="A81" s="15"/>
-      <c r="B81" s="4"/>
-      <c r="C81" s="4"/>
-      <c r="D81" s="4"/>
-      <c r="E81" s="4"/>
-      <c r="F81" s="16"/>
-      <c r="G81" s="4"/>
-      <c r="H81" s="4"/>
-      <c r="I81" s="4"/>
+      <c r="A81" s="17"/>
+      <c r="B81" s="6"/>
+      <c r="C81" s="6"/>
+      <c r="D81" s="6"/>
+      <c r="E81" s="6"/>
+      <c r="F81" s="18"/>
+      <c r="G81" s="6"/>
+      <c r="H81" s="6"/>
+      <c r="I81" s="6"/>
+    </row>
+    <row r="82" ht="25" customHeight="1" spans="1:9">
+      <c r="A82" s="17"/>
+      <c r="B82" s="6"/>
+      <c r="C82" s="6"/>
+      <c r="D82" s="6"/>
+      <c r="E82" s="6"/>
+      <c r="F82" s="18"/>
+      <c r="G82" s="6"/>
+      <c r="H82" s="6"/>
+      <c r="I82" s="6"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
   <hyperlinks>
-    <hyperlink ref="H60" r:id="rId1" display="普洛伊湘普·素帕莎 / 芭莉雅皮·余 " tooltip="https://www.douban.com/personage/30264980/"/>
-    <hyperlink ref="H15" r:id="rId2" display="金贤叙/郑明哲" tooltip="https://www.douban.com/personage/37338980/"/>
+    <hyperlink ref="H54" r:id="rId1" display="普洛伊湘普·素帕莎 / 芭莉雅皮·余 " tooltip="https://www.douban.com/personage/30264980/"/>
+    <hyperlink ref="H16" r:id="rId2" display="金贤叙/郑明哲" tooltip="https://www.douban.com/personage/37338980/"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/资源录入表新.xlsx
+++ b/资源录入表新.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="资源录入表" sheetId="1" r:id="rId1"/>
@@ -1026,6 +1026,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>志怪</t>
     </r>
     <r>
@@ -1787,7 +1793,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1800,9 +1806,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1815,24 +1818,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1845,9 +1836,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1868,12 +1856,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2433,2343 +2415,2343 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="K1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:15">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="8">
         <v>4</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="27">
+      <c r="G2" s="8">
         <v>2026</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="H2" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="I2" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
     </row>
     <row r="3" ht="25" customHeight="1" spans="1:15">
-      <c r="A3" s="26" t="s">
+      <c r="A3" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="27">
+      <c r="D3" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="8">
         <v>8</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="27">
+      <c r="G3" s="8">
         <v>2026</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H3" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="10" t="s">
+      <c r="I3" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
     </row>
     <row r="4" ht="25" customHeight="1" spans="1:15">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="27">
+      <c r="D4" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="8">
         <v>23</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="27">
+      <c r="G4" s="8">
         <v>2026</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H4" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="I4" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6" t="s">
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6"/>
-      <c r="O4" s="6"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
     </row>
     <row r="5" ht="25" customHeight="1" spans="1:15">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="28" t="s">
+      <c r="C5" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="27">
+      <c r="D5" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="8">
         <v>18</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="27">
+      <c r="G5" s="8">
         <v>2026</v>
       </c>
-      <c r="H5" s="28" t="s">
+      <c r="H5" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="I5" s="10" t="s">
+      <c r="I5" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6"/>
-      <c r="O5" s="6"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
     </row>
     <row r="6" ht="25" customHeight="1" spans="1:15">
-      <c r="A6" s="26" t="s">
+      <c r="A6" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="27">
+      <c r="D6" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="8">
         <v>20</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="F6" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G6" s="27">
+      <c r="G6" s="8">
         <v>2026</v>
       </c>
-      <c r="H6" s="10" t="s">
+      <c r="H6" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="I6" s="10" t="s">
+      <c r="I6" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
     </row>
     <row r="7" ht="25" customHeight="1" spans="1:15">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="27">
+      <c r="D7" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="8">
         <v>3</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="F7" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G7" s="27">
+      <c r="G7" s="8">
         <v>2026</v>
       </c>
-      <c r="H7" s="10" t="s">
+      <c r="H7" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="I7" s="10" t="s">
+      <c r="I7" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="6"/>
-      <c r="O7" s="6"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
+      <c r="L7" s="5"/>
+      <c r="M7" s="5"/>
+      <c r="N7" s="5"/>
+      <c r="O7" s="5"/>
     </row>
     <row r="8" ht="25" customHeight="1" spans="1:15">
-      <c r="A8" s="26" t="s">
+      <c r="A8" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="D8" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="10">
+      <c r="D8" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="8">
         <v>4</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F8" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G8" s="27">
+      <c r="G8" s="8">
         <v>2026</v>
       </c>
-      <c r="H8" s="10" t="s">
+      <c r="H8" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="I8" s="10" t="s">
+      <c r="I8" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="6"/>
-      <c r="O8" s="6"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
     </row>
     <row r="9" ht="25" customHeight="1" spans="1:15">
-      <c r="A9" s="26" t="s">
+      <c r="A9" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C9" s="28" t="s">
+      <c r="C9" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="D9" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" s="27">
+      <c r="D9" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="8">
         <v>6</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="F9" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G9" s="27">
+      <c r="G9" s="8">
         <v>2026</v>
       </c>
-      <c r="H9" s="28" t="s">
+      <c r="H9" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="I9" s="12" t="s">
+      <c r="I9" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="6" t="s">
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="M9" s="6"/>
-      <c r="N9" s="6"/>
-      <c r="O9" s="6"/>
+      <c r="M9" s="5"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
     </row>
     <row r="10" ht="25" customHeight="1" spans="1:15">
-      <c r="A10" s="26" t="s">
+      <c r="A10" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="D10" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="27">
+      <c r="D10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="8">
         <v>6</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="F10" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G10" s="27">
+      <c r="G10" s="8">
         <v>2026</v>
       </c>
-      <c r="H10" s="28" t="s">
+      <c r="H10" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="I10" s="12" t="s">
+      <c r="I10" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="J10" s="6"/>
-      <c r="K10" s="6"/>
-      <c r="L10" s="6" t="s">
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="M10" s="6"/>
-      <c r="N10" s="6"/>
-      <c r="O10" s="6"/>
+      <c r="M10" s="5"/>
+      <c r="N10" s="5"/>
+      <c r="O10" s="5"/>
     </row>
     <row r="11" ht="25" customHeight="1" spans="1:15">
-      <c r="A11" s="26" t="s">
+      <c r="A11" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="28" t="s">
+      <c r="C11" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="D11" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="27">
+      <c r="D11" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="8">
         <v>4</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="F11" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G11" s="27">
+      <c r="G11" s="8">
         <v>2026</v>
       </c>
-      <c r="H11" s="10" t="s">
+      <c r="H11" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="I11" s="12" t="s">
+      <c r="I11" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
-      <c r="L11" s="6" t="s">
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="M11" s="6"/>
-      <c r="N11" s="6"/>
-      <c r="O11" s="6"/>
+      <c r="M11" s="5"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="5"/>
     </row>
     <row r="12" ht="25" customHeight="1" spans="1:15">
-      <c r="A12" s="26" t="s">
+      <c r="A12" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C12" s="28" t="s">
+      <c r="C12" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="D12" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="E12" s="27">
+      <c r="D12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="8">
         <v>6</v>
       </c>
-      <c r="F12" s="10" t="s">
+      <c r="F12" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G12" s="27">
+      <c r="G12" s="8">
         <v>2026</v>
       </c>
-      <c r="H12" s="28" t="s">
+      <c r="H12" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="I12" s="10" t="s">
+      <c r="I12" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6" t="s">
+      <c r="J12" s="5"/>
+      <c r="K12" s="5"/>
+      <c r="L12" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="M12" s="6"/>
-      <c r="N12" s="6"/>
-      <c r="O12" s="6"/>
+      <c r="M12" s="5"/>
+      <c r="N12" s="5"/>
+      <c r="O12" s="5"/>
     </row>
     <row r="13" ht="25" customHeight="1" spans="1:15">
-      <c r="A13" s="26" t="s">
+      <c r="A13" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="28" t="s">
+      <c r="C13" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="D13" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="E13" s="27">
+      <c r="D13" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="8">
         <v>8</v>
       </c>
-      <c r="F13" s="10" t="s">
+      <c r="F13" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G13" s="27">
+      <c r="G13" s="8">
         <v>2026</v>
       </c>
-      <c r="H13" s="10" t="s">
+      <c r="H13" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="I13" s="10" t="s">
+      <c r="I13" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="J13" s="6"/>
-      <c r="K13" s="6"/>
-      <c r="L13" s="6" t="s">
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="M13" s="6"/>
-      <c r="N13" s="6"/>
-      <c r="O13" s="6"/>
+      <c r="M13" s="5"/>
+      <c r="N13" s="5"/>
+      <c r="O13" s="5"/>
     </row>
     <row r="14" ht="25" customHeight="1" spans="1:15">
-      <c r="A14" s="26" t="s">
+      <c r="A14" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C14" s="28" t="s">
+      <c r="C14" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="D14" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" s="27">
+      <c r="D14" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" s="8">
         <v>4</v>
       </c>
-      <c r="F14" s="10" t="s">
+      <c r="F14" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G14" s="27">
+      <c r="G14" s="8">
         <v>2026</v>
       </c>
-      <c r="H14" s="28" t="s">
+      <c r="H14" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="I14" s="10" t="s">
+      <c r="I14" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
-      <c r="L14" s="6" t="s">
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="M14" s="6"/>
-      <c r="N14" s="6"/>
-      <c r="O14" s="6"/>
+      <c r="M14" s="5"/>
+      <c r="N14" s="5"/>
+      <c r="O14" s="5"/>
     </row>
     <row r="15" ht="25" customHeight="1" spans="1:15">
-      <c r="A15" s="26" t="s">
+      <c r="A15" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B15" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C15" s="28" t="s">
+      <c r="C15" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="D15" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="E15" s="27">
+      <c r="D15" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" s="8">
         <v>8</v>
       </c>
-      <c r="F15" s="10" t="s">
+      <c r="F15" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G15" s="27">
+      <c r="G15" s="8">
         <v>2026</v>
       </c>
-      <c r="H15" s="28" t="s">
+      <c r="H15" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="I15" s="10" t="s">
+      <c r="I15" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="J15" s="6"/>
-      <c r="K15" s="6"/>
-      <c r="L15" s="6" t="s">
+      <c r="J15" s="5"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="M15" s="6"/>
-      <c r="N15" s="6"/>
-      <c r="O15" s="6"/>
+      <c r="M15" s="5"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="5"/>
     </row>
     <row r="16" ht="25" customHeight="1" spans="1:15">
-      <c r="A16" s="26" t="s">
+      <c r="A16" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="B16" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="D16" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="E16" s="10">
+      <c r="D16" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" s="8">
         <v>7</v>
       </c>
-      <c r="F16" s="10" t="s">
+      <c r="F16" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G16" s="27">
+      <c r="G16" s="8">
         <v>2026</v>
       </c>
-      <c r="H16" s="10"/>
-      <c r="I16" s="10" t="s">
+      <c r="H16" s="8"/>
+      <c r="I16" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="J16" s="6"/>
-      <c r="K16" s="6"/>
-      <c r="L16" s="6"/>
-      <c r="M16" s="6"/>
-      <c r="N16" s="6"/>
-      <c r="O16" s="6"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="5"/>
+      <c r="N16" s="5"/>
+      <c r="O16" s="5"/>
     </row>
     <row r="17" ht="25" customHeight="1" spans="1:15">
-      <c r="A17" s="26" t="s">
+      <c r="A17" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="B17" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="D17" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="E17" s="10">
+      <c r="D17" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E17" s="8">
         <v>4</v>
       </c>
-      <c r="F17" s="10" t="s">
+      <c r="F17" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G17" s="27">
+      <c r="G17" s="8">
         <v>2026</v>
       </c>
-      <c r="H17" s="10"/>
-      <c r="I17" s="10" t="s">
+      <c r="H17" s="8"/>
+      <c r="I17" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="J17" s="6"/>
-      <c r="K17" s="6"/>
-      <c r="L17" s="6"/>
-      <c r="M17" s="6"/>
-      <c r="N17" s="6"/>
-      <c r="O17" s="6"/>
+      <c r="J17" s="5"/>
+      <c r="K17" s="5"/>
+      <c r="L17" s="5"/>
+      <c r="M17" s="5"/>
+      <c r="N17" s="5"/>
+      <c r="O17" s="5"/>
     </row>
     <row r="18" ht="25" customHeight="1" spans="1:15">
-      <c r="A18" s="29" t="s">
+      <c r="A18" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="B18" s="16" t="s">
+      <c r="B18" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="C18" s="30" t="s">
+      <c r="C18" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="D18" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="E18" s="30"/>
-      <c r="F18" s="30" t="s">
-        <v>82</v>
-      </c>
-      <c r="G18" s="27">
+      <c r="D18" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="22"/>
+      <c r="F18" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="G18" s="8">
         <v>2026</v>
       </c>
-      <c r="H18" s="10"/>
-      <c r="I18" s="16" t="s">
+      <c r="H18" s="8"/>
+      <c r="I18" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="J18" s="6"/>
-      <c r="K18" s="6"/>
-      <c r="L18" s="6"/>
-      <c r="M18" s="6"/>
-      <c r="N18" s="6"/>
-      <c r="O18" s="31"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="5"/>
+      <c r="L18" s="5"/>
+      <c r="M18" s="5"/>
+      <c r="N18" s="5"/>
+      <c r="O18" s="23"/>
     </row>
     <row r="19" ht="25" customHeight="1" spans="1:15">
-      <c r="A19" s="29" t="s">
+      <c r="A19" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="B19" s="16" t="s">
+      <c r="B19" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="C19" s="30" t="s">
+      <c r="C19" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="D19" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="E19" s="30"/>
-      <c r="F19" s="30" t="s">
-        <v>82</v>
-      </c>
-      <c r="G19" s="27">
+      <c r="D19" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19" s="22"/>
+      <c r="F19" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="G19" s="8">
         <v>2026</v>
       </c>
-      <c r="H19" s="10"/>
-      <c r="I19" s="16" t="s">
+      <c r="H19" s="8"/>
+      <c r="I19" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="J19" s="6"/>
-      <c r="K19" s="6"/>
-      <c r="L19" s="6"/>
-      <c r="M19" s="6"/>
-      <c r="N19" s="6"/>
-      <c r="O19" s="31"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="5"/>
+      <c r="L19" s="5"/>
+      <c r="M19" s="5"/>
+      <c r="N19" s="5"/>
+      <c r="O19" s="23"/>
     </row>
     <row r="20" ht="25" customHeight="1" spans="1:15">
-      <c r="A20" s="17" t="s">
+      <c r="A20" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="D20" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E20" s="6" t="s">
+      <c r="D20" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E20" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="F20" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G20" s="6">
+      <c r="F20" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G20" s="5">
         <v>2026</v>
       </c>
-      <c r="H20" s="6" t="s">
+      <c r="H20" s="5" t="s">
         <v>89</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="J20" s="6"/>
-      <c r="K20" s="6"/>
-      <c r="L20" s="6" t="s">
+      <c r="J20" s="5"/>
+      <c r="K20" s="5"/>
+      <c r="L20" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="M20" s="6"/>
-      <c r="N20" s="6"/>
-      <c r="O20" s="6"/>
+      <c r="M20" s="5"/>
+      <c r="N20" s="5"/>
+      <c r="O20" s="5"/>
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:15">
-      <c r="A21" s="17" t="s">
+      <c r="A21" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="D21" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E21" s="6" t="s">
+      <c r="D21" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E21" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="F21" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G21" s="6">
+      <c r="F21" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G21" s="5">
         <v>2025</v>
       </c>
-      <c r="H21" s="6" t="s">
+      <c r="H21" s="5" t="s">
         <v>95</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="J21" s="6"/>
-      <c r="K21" s="6"/>
-      <c r="L21" s="6" t="s">
+      <c r="J21" s="5"/>
+      <c r="K21" s="5"/>
+      <c r="L21" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="M21" s="6"/>
-      <c r="N21" s="6"/>
-      <c r="O21" s="6"/>
+      <c r="M21" s="5"/>
+      <c r="N21" s="5"/>
+      <c r="O21" s="5"/>
     </row>
     <row r="22" ht="25" customHeight="1" spans="1:15">
-      <c r="A22" s="17" t="s">
+      <c r="A22" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="D22" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E22" s="6" t="s">
+      <c r="D22" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E22" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="F22" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G22" s="6">
+      <c r="F22" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G22" s="5">
         <v>2026</v>
       </c>
-      <c r="H22" s="6" t="s">
+      <c r="H22" s="5" t="s">
         <v>101</v>
       </c>
       <c r="I22" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="J22" s="6"/>
-      <c r="K22" s="6"/>
-      <c r="L22" s="6" t="s">
+      <c r="J22" s="5"/>
+      <c r="K22" s="5"/>
+      <c r="L22" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="M22" s="6"/>
-      <c r="N22" s="6"/>
-      <c r="O22" s="6"/>
+      <c r="M22" s="5"/>
+      <c r="N22" s="5"/>
+      <c r="O22" s="5"/>
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:15">
-      <c r="A23" s="17" t="s">
+      <c r="A23" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="D23" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E23" s="6" t="s">
+      <c r="D23" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E23" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="F23" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G23" s="6">
+      <c r="F23" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G23" s="5">
         <v>2026</v>
       </c>
-      <c r="H23" s="6" t="s">
+      <c r="H23" s="5" t="s">
         <v>107</v>
       </c>
       <c r="I23" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="J23" s="6"/>
-      <c r="K23" s="6"/>
-      <c r="L23" s="6" t="s">
+      <c r="J23" s="5"/>
+      <c r="K23" s="5"/>
+      <c r="L23" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="M23" s="6"/>
-      <c r="N23" s="6"/>
-      <c r="O23" s="6"/>
+      <c r="M23" s="5"/>
+      <c r="N23" s="5"/>
+      <c r="O23" s="5"/>
     </row>
     <row r="24" ht="25" customHeight="1" spans="1:15">
-      <c r="A24" s="17" t="s">
+      <c r="A24" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="D24" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E24" s="6" t="s">
+      <c r="D24" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E24" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="F24" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G24" s="6">
+      <c r="F24" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G24" s="5">
         <v>2025</v>
       </c>
-      <c r="H24" s="6" t="s">
+      <c r="H24" s="5" t="s">
         <v>113</v>
       </c>
       <c r="I24" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="J24" s="6"/>
-      <c r="K24" s="6"/>
-      <c r="L24" s="6" t="s">
+      <c r="J24" s="5"/>
+      <c r="K24" s="5"/>
+      <c r="L24" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="M24" s="6"/>
-      <c r="N24" s="6"/>
-      <c r="O24" s="6"/>
+      <c r="M24" s="5"/>
+      <c r="N24" s="5"/>
+      <c r="O24" s="5"/>
     </row>
     <row r="25" ht="25" customHeight="1" spans="1:15">
-      <c r="A25" s="17" t="s">
+      <c r="A25" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="D25" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E25" s="6" t="s">
+      <c r="D25" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E25" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="F25" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G25" s="6">
+      <c r="F25" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G25" s="5">
         <v>2026</v>
       </c>
-      <c r="H25" s="6" t="s">
+      <c r="H25" s="5" t="s">
         <v>119</v>
       </c>
       <c r="I25" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="J25" s="21"/>
-      <c r="K25" s="21"/>
-      <c r="L25" s="21" t="s">
+      <c r="J25" s="15"/>
+      <c r="K25" s="15"/>
+      <c r="L25" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="M25" s="21"/>
-      <c r="N25" s="21"/>
-      <c r="O25" s="6"/>
+      <c r="M25" s="15"/>
+      <c r="N25" s="15"/>
+      <c r="O25" s="5"/>
     </row>
     <row r="26" ht="25" customHeight="1" spans="1:15">
-      <c r="A26" s="17" t="s">
+      <c r="A26" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="C26" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="D26" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E26" s="6" t="s">
+      <c r="D26" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E26" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="F26" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G26" s="6">
+      <c r="F26" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G26" s="5">
         <v>2026</v>
       </c>
-      <c r="H26" s="6" t="s">
+      <c r="H26" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="I26" s="6" t="s">
+      <c r="I26" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="J26" s="6"/>
-      <c r="K26" s="6"/>
-      <c r="L26" s="6" t="s">
+      <c r="J26" s="5"/>
+      <c r="K26" s="5"/>
+      <c r="L26" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="M26" s="6"/>
-      <c r="N26" s="6"/>
-      <c r="O26" s="31"/>
+      <c r="M26" s="5"/>
+      <c r="N26" s="5"/>
+      <c r="O26" s="23"/>
     </row>
     <row r="27" ht="25" customHeight="1" spans="1:15">
-      <c r="A27" s="17" t="s">
+      <c r="A27" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C27" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="D27" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E27" s="6" t="s">
+      <c r="D27" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E27" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="F27" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G27" s="6">
+      <c r="F27" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G27" s="5">
         <v>2024</v>
       </c>
-      <c r="H27" s="6" t="s">
+      <c r="H27" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="I27" s="6" t="s">
+      <c r="I27" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="J27" s="6"/>
-      <c r="K27" s="6"/>
-      <c r="L27" s="6" t="s">
+      <c r="J27" s="5"/>
+      <c r="K27" s="5"/>
+      <c r="L27" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="M27" s="6"/>
-      <c r="N27" s="6"/>
-      <c r="O27" s="31"/>
+      <c r="M27" s="5"/>
+      <c r="N27" s="5"/>
+      <c r="O27" s="23"/>
     </row>
     <row r="28" ht="25" customHeight="1" spans="1:15">
-      <c r="A28" s="17" t="s">
+      <c r="A28" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C28" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="D28" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E28" s="6" t="s">
+      <c r="D28" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E28" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="F28" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G28" s="6">
+      <c r="F28" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G28" s="5">
         <v>2024</v>
       </c>
-      <c r="H28" s="6" t="s">
+      <c r="H28" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="I28" s="6" t="s">
+      <c r="I28" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="J28" s="6"/>
-      <c r="K28" s="6"/>
-      <c r="L28" s="6" t="s">
+      <c r="J28" s="5"/>
+      <c r="K28" s="5"/>
+      <c r="L28" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="M28" s="6"/>
-      <c r="N28" s="6"/>
-      <c r="O28" s="31"/>
+      <c r="M28" s="5"/>
+      <c r="N28" s="5"/>
+      <c r="O28" s="23"/>
     </row>
     <row r="29" ht="25" customHeight="1" spans="1:15">
-      <c r="A29" s="17" t="s">
+      <c r="A29" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C29" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="D29" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E29" s="6" t="s">
+      <c r="D29" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E29" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="F29" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G29" s="6">
+      <c r="F29" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G29" s="5">
         <v>2026</v>
       </c>
-      <c r="H29" s="6" t="s">
+      <c r="H29" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="I29" s="6" t="s">
+      <c r="I29" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="J29" s="6"/>
-      <c r="K29" s="6"/>
-      <c r="L29" s="6" t="s">
+      <c r="J29" s="5"/>
+      <c r="K29" s="5"/>
+      <c r="L29" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="M29" s="6"/>
-      <c r="N29" s="6"/>
-      <c r="O29" s="31"/>
+      <c r="M29" s="5"/>
+      <c r="N29" s="5"/>
+      <c r="O29" s="23"/>
     </row>
     <row r="30" ht="25" customHeight="1" spans="1:15">
-      <c r="A30" s="17" t="s">
+      <c r="A30" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C30" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="D30" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E30" s="6" t="s">
+      <c r="D30" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E30" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="F30" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G30" s="6">
+      <c r="F30" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G30" s="5">
         <v>2025</v>
       </c>
-      <c r="H30" s="6" t="s">
+      <c r="H30" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="I30" s="6" t="s">
+      <c r="I30" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="J30" s="6"/>
-      <c r="K30" s="6"/>
-      <c r="L30" s="6" t="s">
+      <c r="J30" s="5"/>
+      <c r="K30" s="5"/>
+      <c r="L30" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="M30" s="6"/>
-      <c r="N30" s="6"/>
-      <c r="O30" s="31"/>
+      <c r="M30" s="5"/>
+      <c r="N30" s="5"/>
+      <c r="O30" s="23"/>
     </row>
     <row r="31" ht="25" customHeight="1" spans="1:15">
-      <c r="A31" s="17" t="s">
+      <c r="A31" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="C31" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="D31" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E31" s="6" t="s">
+      <c r="D31" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E31" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="F31" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G31" s="6">
+      <c r="F31" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G31" s="5">
         <v>2026</v>
       </c>
-      <c r="H31" s="6" t="s">
+      <c r="H31" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="I31" s="6" t="s">
+      <c r="I31" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="J31" s="6"/>
-      <c r="K31" s="6"/>
-      <c r="L31" s="6" t="s">
+      <c r="J31" s="5"/>
+      <c r="K31" s="5"/>
+      <c r="L31" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="M31" s="6"/>
-      <c r="N31" s="6"/>
-      <c r="O31" s="31"/>
+      <c r="M31" s="5"/>
+      <c r="N31" s="5"/>
+      <c r="O31" s="23"/>
     </row>
     <row r="32" ht="25" customHeight="1" spans="1:15">
-      <c r="A32" s="17" t="s">
+      <c r="A32" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="B32" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C32" s="6" t="s">
+      <c r="C32" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="D32" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E32" s="6" t="s">
+      <c r="D32" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E32" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="F32" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G32" s="6">
+      <c r="F32" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G32" s="5">
         <v>2026</v>
       </c>
-      <c r="H32" s="6" t="s">
+      <c r="H32" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="I32" s="6" t="s">
+      <c r="I32" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="J32" s="6"/>
-      <c r="K32" s="6"/>
-      <c r="L32" s="6" t="s">
+      <c r="J32" s="5"/>
+      <c r="K32" s="5"/>
+      <c r="L32" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="M32" s="6"/>
-      <c r="N32" s="6"/>
-      <c r="O32" s="31"/>
+      <c r="M32" s="5"/>
+      <c r="N32" s="5"/>
+      <c r="O32" s="23"/>
     </row>
     <row r="33" ht="25" customHeight="1" spans="1:15">
-      <c r="A33" s="17" t="s">
+      <c r="A33" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="C33" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="D33" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E33" s="6" t="s">
+      <c r="D33" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E33" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="F33" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G33" s="6">
+      <c r="F33" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G33" s="5">
         <v>2026</v>
       </c>
-      <c r="H33" s="6" t="s">
+      <c r="H33" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="I33" s="6" t="s">
+      <c r="I33" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="J33" s="6"/>
-      <c r="K33" s="6"/>
-      <c r="L33" s="6" t="s">
+      <c r="J33" s="5"/>
+      <c r="K33" s="5"/>
+      <c r="L33" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="M33" s="6"/>
-      <c r="N33" s="6"/>
-      <c r="O33" s="31"/>
+      <c r="M33" s="5"/>
+      <c r="N33" s="5"/>
+      <c r="O33" s="23"/>
     </row>
     <row r="34" ht="25" customHeight="1" spans="1:15">
-      <c r="A34" s="17" t="s">
+      <c r="A34" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C34" s="6" t="s">
+      <c r="C34" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="D34" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E34" s="6" t="s">
+      <c r="D34" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E34" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="F34" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G34" s="6">
+      <c r="F34" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G34" s="5">
         <v>2025</v>
       </c>
-      <c r="H34" s="6" t="s">
+      <c r="H34" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="I34" s="6" t="s">
+      <c r="I34" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="J34" s="6"/>
-      <c r="K34" s="6"/>
-      <c r="L34" s="6" t="s">
+      <c r="J34" s="5"/>
+      <c r="K34" s="5"/>
+      <c r="L34" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="M34" s="6"/>
-      <c r="N34" s="6"/>
-      <c r="O34" s="31"/>
+      <c r="M34" s="5"/>
+      <c r="N34" s="5"/>
+      <c r="O34" s="23"/>
     </row>
     <row r="35" ht="25" customHeight="1" spans="1:15">
-      <c r="A35" s="17" t="s">
+      <c r="A35" s="12" t="s">
         <v>170</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="B35" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C35" s="6" t="s">
+      <c r="C35" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="D35" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E35" s="6" t="s">
+      <c r="D35" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E35" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="F35" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G35" s="6">
+      <c r="F35" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G35" s="5">
         <v>2026</v>
       </c>
-      <c r="H35" s="6" t="s">
+      <c r="H35" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="I35" s="6" t="s">
+      <c r="I35" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="J35" s="6"/>
-      <c r="K35" s="6"/>
-      <c r="L35" s="6" t="s">
+      <c r="J35" s="5"/>
+      <c r="K35" s="5"/>
+      <c r="L35" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="M35" s="6"/>
-      <c r="N35" s="6"/>
-      <c r="O35" s="31"/>
+      <c r="M35" s="5"/>
+      <c r="N35" s="5"/>
+      <c r="O35" s="23"/>
     </row>
     <row r="36" ht="25" customHeight="1" spans="1:15">
-      <c r="A36" s="17" t="s">
+      <c r="A36" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="B36" s="6" t="s">
+      <c r="B36" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C36" s="6" t="s">
+      <c r="C36" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="D36" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E36" s="6" t="s">
+      <c r="D36" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E36" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="F36" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G36" s="6">
+      <c r="F36" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G36" s="5">
         <v>2026</v>
       </c>
-      <c r="H36" s="6" t="s">
+      <c r="H36" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="I36" s="6" t="s">
+      <c r="I36" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="J36" s="6"/>
-      <c r="K36" s="6"/>
-      <c r="L36" s="6" t="s">
+      <c r="J36" s="5"/>
+      <c r="K36" s="5"/>
+      <c r="L36" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="M36" s="6"/>
-      <c r="N36" s="6"/>
-      <c r="O36" s="31"/>
+      <c r="M36" s="5"/>
+      <c r="N36" s="5"/>
+      <c r="O36" s="23"/>
     </row>
     <row r="37" ht="25" customHeight="1" spans="1:15">
-      <c r="A37" s="17" t="s">
+      <c r="A37" s="12" t="s">
         <v>181</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="B37" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="C37" s="6" t="s">
+      <c r="C37" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="D37" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E37" s="18" t="s">
+      <c r="D37" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E37" s="13" t="s">
         <v>184</v>
       </c>
-      <c r="F37" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G37" s="6">
+      <c r="F37" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G37" s="5">
         <v>2025</v>
       </c>
-      <c r="H37" s="6"/>
-      <c r="I37" s="6" t="s">
+      <c r="H37" s="5"/>
+      <c r="I37" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="J37" s="6"/>
-      <c r="K37" s="6"/>
-      <c r="L37" s="6" t="s">
+      <c r="J37" s="5"/>
+      <c r="K37" s="5"/>
+      <c r="L37" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="M37" s="6"/>
-      <c r="N37" s="6"/>
-      <c r="O37" s="31"/>
+      <c r="M37" s="5"/>
+      <c r="N37" s="5"/>
+      <c r="O37" s="23"/>
     </row>
     <row r="38" ht="25" customHeight="1" spans="1:15">
-      <c r="A38" s="17" t="s">
+      <c r="A38" s="12" t="s">
         <v>186</v>
       </c>
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="C38" s="6" t="s">
+      <c r="C38" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="D38" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E38" s="18" t="s">
+      <c r="D38" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E38" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="F38" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G38" s="6">
+      <c r="F38" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G38" s="5">
         <v>2025</v>
       </c>
-      <c r="H38" s="6" t="s">
+      <c r="H38" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="I38" s="6" t="s">
+      <c r="I38" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="J38" s="6"/>
-      <c r="K38" s="6"/>
-      <c r="L38" s="6" t="s">
+      <c r="J38" s="5"/>
+      <c r="K38" s="5"/>
+      <c r="L38" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="M38" s="6"/>
-      <c r="N38" s="6"/>
-      <c r="O38" s="31"/>
+      <c r="M38" s="5"/>
+      <c r="N38" s="5"/>
+      <c r="O38" s="23"/>
     </row>
     <row r="39" ht="25" customHeight="1" spans="1:15">
-      <c r="A39" s="17" t="s">
+      <c r="A39" s="12" t="s">
         <v>192</v>
       </c>
-      <c r="B39" s="6" t="s">
+      <c r="B39" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="C39" s="6" t="s">
+      <c r="C39" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="D39" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E39" s="16" t="s">
+      <c r="D39" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E39" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="F39" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G39" s="6">
+      <c r="F39" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G39" s="5">
         <v>2025</v>
       </c>
-      <c r="H39" s="6"/>
-      <c r="I39" s="6" t="s">
+      <c r="H39" s="5"/>
+      <c r="I39" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="J39" s="6"/>
-      <c r="K39" s="6"/>
-      <c r="L39" s="6" t="s">
+      <c r="J39" s="5"/>
+      <c r="K39" s="5"/>
+      <c r="L39" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="M39" s="6"/>
-      <c r="N39" s="6"/>
-      <c r="O39" s="31"/>
+      <c r="M39" s="5"/>
+      <c r="N39" s="5"/>
+      <c r="O39" s="23"/>
     </row>
     <row r="40" ht="25" customHeight="1" spans="1:15">
-      <c r="A40" s="17" t="s">
+      <c r="A40" s="12" t="s">
         <v>195</v>
       </c>
-      <c r="B40" s="6" t="s">
+      <c r="B40" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="C40" s="6" t="s">
+      <c r="C40" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="D40" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E40" s="6" t="s">
+      <c r="D40" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E40" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="F40" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G40" s="6">
+      <c r="F40" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G40" s="5">
         <v>2026</v>
       </c>
-      <c r="H40" s="6" t="s">
+      <c r="H40" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="I40" s="6" t="s">
+      <c r="I40" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="J40" s="6"/>
-      <c r="K40" s="6"/>
-      <c r="L40" s="6" t="s">
+      <c r="J40" s="5"/>
+      <c r="K40" s="5"/>
+      <c r="L40" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="M40" s="6"/>
-      <c r="N40" s="6"/>
-      <c r="O40" s="31"/>
+      <c r="M40" s="5"/>
+      <c r="N40" s="5"/>
+      <c r="O40" s="23"/>
     </row>
     <row r="41" ht="25" customHeight="1" spans="1:15">
-      <c r="A41" s="17" t="s">
+      <c r="A41" s="12" t="s">
         <v>200</v>
       </c>
-      <c r="B41" s="6"/>
-      <c r="C41" s="6"/>
-      <c r="D41" s="6"/>
-      <c r="E41" s="6"/>
-      <c r="F41" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G41" s="6"/>
-      <c r="H41" s="6"/>
-      <c r="I41" s="6" t="s">
+      <c r="B41" s="5"/>
+      <c r="C41" s="5"/>
+      <c r="D41" s="5"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G41" s="5"/>
+      <c r="H41" s="5"/>
+      <c r="I41" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="J41" s="6"/>
-      <c r="K41" s="6"/>
-      <c r="L41" s="6"/>
-      <c r="M41" s="6"/>
-      <c r="N41" s="6"/>
-      <c r="O41" s="31"/>
+      <c r="J41" s="5"/>
+      <c r="K41" s="5"/>
+      <c r="L41" s="5"/>
+      <c r="M41" s="5"/>
+      <c r="N41" s="5"/>
+      <c r="O41" s="23"/>
     </row>
     <row r="42" ht="25" customHeight="1" spans="1:15">
-      <c r="A42" s="17" t="s">
+      <c r="A42" s="12" t="s">
         <v>202</v>
       </c>
-      <c r="B42" s="6"/>
-      <c r="C42" s="6"/>
-      <c r="D42" s="6"/>
-      <c r="E42" s="6"/>
-      <c r="F42" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G42" s="6"/>
-      <c r="H42" s="6"/>
-      <c r="I42" s="6" t="s">
+      <c r="B42" s="5"/>
+      <c r="C42" s="5"/>
+      <c r="D42" s="5"/>
+      <c r="E42" s="5"/>
+      <c r="F42" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G42" s="5"/>
+      <c r="H42" s="5"/>
+      <c r="I42" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="J42" s="6"/>
-      <c r="K42" s="6"/>
-      <c r="L42" s="6"/>
-      <c r="M42" s="6"/>
-      <c r="N42" s="6"/>
-      <c r="O42" s="31"/>
+      <c r="J42" s="5"/>
+      <c r="K42" s="5"/>
+      <c r="L42" s="5"/>
+      <c r="M42" s="5"/>
+      <c r="N42" s="5"/>
+      <c r="O42" s="23"/>
     </row>
     <row r="43" ht="25" customHeight="1" spans="1:15">
-      <c r="A43" s="17" t="s">
+      <c r="A43" s="12" t="s">
         <v>204</v>
       </c>
-      <c r="B43" s="6"/>
-      <c r="C43" s="6"/>
-      <c r="D43" s="6"/>
-      <c r="E43" s="6"/>
-      <c r="F43" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G43" s="6"/>
-      <c r="H43" s="6"/>
-      <c r="I43" s="6" t="s">
+      <c r="B43" s="5"/>
+      <c r="C43" s="5"/>
+      <c r="D43" s="5"/>
+      <c r="E43" s="5"/>
+      <c r="F43" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G43" s="5"/>
+      <c r="H43" s="5"/>
+      <c r="I43" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="J43" s="6"/>
-      <c r="K43" s="6"/>
-      <c r="L43" s="6"/>
-      <c r="M43" s="6"/>
-      <c r="N43" s="6"/>
-      <c r="O43" s="31"/>
+      <c r="J43" s="5"/>
+      <c r="K43" s="5"/>
+      <c r="L43" s="5"/>
+      <c r="M43" s="5"/>
+      <c r="N43" s="5"/>
+      <c r="O43" s="23"/>
     </row>
     <row r="44" ht="25" customHeight="1" spans="1:15">
-      <c r="A44" s="17" t="s">
+      <c r="A44" s="12" t="s">
         <v>206</v>
       </c>
-      <c r="B44" s="6"/>
-      <c r="C44" s="6"/>
-      <c r="D44" s="6"/>
-      <c r="E44" s="6"/>
-      <c r="F44" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G44" s="6"/>
-      <c r="H44" s="6"/>
-      <c r="I44" s="6" t="s">
+      <c r="B44" s="5"/>
+      <c r="C44" s="5"/>
+      <c r="D44" s="5"/>
+      <c r="E44" s="5"/>
+      <c r="F44" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G44" s="5"/>
+      <c r="H44" s="5"/>
+      <c r="I44" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="J44" s="6"/>
-      <c r="K44" s="6"/>
-      <c r="L44" s="6"/>
-      <c r="M44" s="6"/>
-      <c r="N44" s="6"/>
-      <c r="O44" s="31"/>
+      <c r="J44" s="5"/>
+      <c r="K44" s="5"/>
+      <c r="L44" s="5"/>
+      <c r="M44" s="5"/>
+      <c r="N44" s="5"/>
+      <c r="O44" s="23"/>
     </row>
     <row r="45" ht="25" customHeight="1" spans="1:15">
-      <c r="A45" s="20" t="s">
+      <c r="A45" s="14" t="s">
         <v>208</v>
       </c>
-      <c r="B45" s="21"/>
-      <c r="C45" s="21"/>
-      <c r="D45" s="21"/>
-      <c r="E45" s="21"/>
-      <c r="F45" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G45" s="21"/>
-      <c r="H45" s="21"/>
-      <c r="I45" s="22" t="s">
+      <c r="B45" s="15"/>
+      <c r="C45" s="15"/>
+      <c r="D45" s="15"/>
+      <c r="E45" s="15"/>
+      <c r="F45" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G45" s="15"/>
+      <c r="H45" s="15"/>
+      <c r="I45" s="16" t="s">
         <v>209</v>
       </c>
-      <c r="J45" s="21"/>
-      <c r="K45" s="6"/>
-      <c r="L45" s="6"/>
-      <c r="M45" s="6"/>
-      <c r="N45" s="6"/>
-      <c r="O45" s="31"/>
+      <c r="J45" s="15"/>
+      <c r="K45" s="5"/>
+      <c r="L45" s="5"/>
+      <c r="M45" s="5"/>
+      <c r="N45" s="5"/>
+      <c r="O45" s="23"/>
     </row>
     <row r="46" ht="25" customHeight="1" spans="1:15">
-      <c r="A46" s="17" t="s">
+      <c r="A46" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="B46" s="6"/>
-      <c r="C46" s="6"/>
-      <c r="D46" s="6"/>
-      <c r="E46" s="6"/>
-      <c r="F46" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G46" s="6"/>
-      <c r="H46" s="6"/>
-      <c r="I46" s="6" t="s">
+      <c r="B46" s="5"/>
+      <c r="C46" s="5"/>
+      <c r="D46" s="5"/>
+      <c r="E46" s="5"/>
+      <c r="F46" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G46" s="5"/>
+      <c r="H46" s="5"/>
+      <c r="I46" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="J46" s="6"/>
-      <c r="K46" s="6"/>
-      <c r="L46" s="6"/>
-      <c r="M46" s="6"/>
-      <c r="N46" s="6"/>
-      <c r="O46" s="31"/>
+      <c r="J46" s="5"/>
+      <c r="K46" s="5"/>
+      <c r="L46" s="5"/>
+      <c r="M46" s="5"/>
+      <c r="N46" s="5"/>
+      <c r="O46" s="23"/>
     </row>
     <row r="47" ht="25" customHeight="1" spans="1:15">
-      <c r="A47" s="17" t="s">
+      <c r="A47" s="12" t="s">
         <v>212</v>
       </c>
-      <c r="B47" s="6"/>
-      <c r="C47" s="6"/>
-      <c r="D47" s="6"/>
-      <c r="E47" s="6"/>
-      <c r="F47" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G47" s="6"/>
-      <c r="H47" s="6"/>
-      <c r="I47" s="6" t="s">
+      <c r="B47" s="5"/>
+      <c r="C47" s="5"/>
+      <c r="D47" s="5"/>
+      <c r="E47" s="5"/>
+      <c r="F47" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G47" s="5"/>
+      <c r="H47" s="5"/>
+      <c r="I47" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="J47" s="6"/>
-      <c r="K47" s="6"/>
-      <c r="L47" s="6"/>
-      <c r="M47" s="6"/>
-      <c r="N47" s="6"/>
-      <c r="O47" s="31"/>
+      <c r="J47" s="5"/>
+      <c r="K47" s="5"/>
+      <c r="L47" s="5"/>
+      <c r="M47" s="5"/>
+      <c r="N47" s="5"/>
+      <c r="O47" s="23"/>
     </row>
     <row r="48" ht="25" customHeight="1" spans="1:15">
-      <c r="A48" s="17" t="s">
+      <c r="A48" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="B48" s="6"/>
-      <c r="C48" s="6"/>
-      <c r="D48" s="6"/>
-      <c r="E48" s="6"/>
-      <c r="F48" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G48" s="6"/>
-      <c r="H48" s="6"/>
-      <c r="I48" s="6" t="s">
+      <c r="B48" s="5"/>
+      <c r="C48" s="5"/>
+      <c r="D48" s="5"/>
+      <c r="E48" s="5"/>
+      <c r="F48" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G48" s="5"/>
+      <c r="H48" s="5"/>
+      <c r="I48" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="J48" s="6"/>
-      <c r="K48" s="6"/>
-      <c r="L48" s="6"/>
-      <c r="M48" s="6"/>
-      <c r="N48" s="6"/>
-      <c r="O48" s="31"/>
+      <c r="J48" s="5"/>
+      <c r="K48" s="5"/>
+      <c r="L48" s="5"/>
+      <c r="M48" s="5"/>
+      <c r="N48" s="5"/>
+      <c r="O48" s="23"/>
     </row>
     <row r="49" ht="25" customHeight="1" spans="1:15">
-      <c r="A49" s="17" t="s">
+      <c r="A49" s="12" t="s">
         <v>216</v>
       </c>
-      <c r="B49" s="6"/>
-      <c r="C49" s="6"/>
-      <c r="D49" s="6"/>
-      <c r="E49" s="6"/>
-      <c r="F49" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G49" s="6"/>
-      <c r="H49" s="6"/>
-      <c r="I49" s="6" t="s">
+      <c r="B49" s="5"/>
+      <c r="C49" s="5"/>
+      <c r="D49" s="5"/>
+      <c r="E49" s="5"/>
+      <c r="F49" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G49" s="5"/>
+      <c r="H49" s="5"/>
+      <c r="I49" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="J49" s="6"/>
-      <c r="K49" s="6"/>
-      <c r="L49" s="6"/>
-      <c r="M49" s="6"/>
-      <c r="N49" s="6"/>
-      <c r="O49" s="31"/>
+      <c r="J49" s="5"/>
+      <c r="K49" s="5"/>
+      <c r="L49" s="5"/>
+      <c r="M49" s="5"/>
+      <c r="N49" s="5"/>
+      <c r="O49" s="23"/>
     </row>
     <row r="50" ht="25" customHeight="1" spans="1:15">
-      <c r="A50" s="17" t="s">
+      <c r="A50" s="12" t="s">
         <v>218</v>
       </c>
-      <c r="B50" s="6"/>
-      <c r="C50" s="6"/>
-      <c r="D50" s="6"/>
-      <c r="E50" s="6"/>
-      <c r="F50" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G50" s="6"/>
-      <c r="H50" s="6"/>
-      <c r="I50" s="6" t="s">
+      <c r="B50" s="5"/>
+      <c r="C50" s="5"/>
+      <c r="D50" s="5"/>
+      <c r="E50" s="5"/>
+      <c r="F50" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G50" s="5"/>
+      <c r="H50" s="5"/>
+      <c r="I50" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="J50" s="6"/>
-      <c r="K50" s="6"/>
-      <c r="L50" s="6"/>
-      <c r="M50" s="6"/>
-      <c r="N50" s="6"/>
-      <c r="O50" s="31"/>
+      <c r="J50" s="5"/>
+      <c r="K50" s="5"/>
+      <c r="L50" s="5"/>
+      <c r="M50" s="5"/>
+      <c r="N50" s="5"/>
+      <c r="O50" s="23"/>
     </row>
     <row r="51" ht="25" customHeight="1" spans="1:15">
-      <c r="A51" s="17" t="s">
+      <c r="A51" s="12" t="s">
         <v>220</v>
       </c>
-      <c r="B51" s="6"/>
-      <c r="C51" s="6"/>
-      <c r="D51" s="6"/>
-      <c r="E51" s="6"/>
-      <c r="F51" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G51" s="6"/>
-      <c r="H51" s="6"/>
-      <c r="I51" s="6" t="s">
+      <c r="B51" s="5"/>
+      <c r="C51" s="5"/>
+      <c r="D51" s="5"/>
+      <c r="E51" s="5"/>
+      <c r="F51" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G51" s="5"/>
+      <c r="H51" s="5"/>
+      <c r="I51" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="J51" s="6"/>
-      <c r="K51" s="6"/>
-      <c r="L51" s="6"/>
-      <c r="M51" s="6"/>
-      <c r="N51" s="6"/>
-      <c r="O51" s="31"/>
+      <c r="J51" s="5"/>
+      <c r="K51" s="5"/>
+      <c r="L51" s="5"/>
+      <c r="M51" s="5"/>
+      <c r="N51" s="5"/>
+      <c r="O51" s="23"/>
     </row>
     <row r="52" ht="25" customHeight="1" spans="1:15">
-      <c r="A52" s="17" t="s">
+      <c r="A52" s="12" t="s">
         <v>222</v>
       </c>
-      <c r="B52" s="6"/>
-      <c r="C52" s="6"/>
-      <c r="D52" s="6"/>
-      <c r="E52" s="6"/>
-      <c r="F52" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G52" s="6"/>
-      <c r="H52" s="6"/>
-      <c r="I52" s="6" t="s">
+      <c r="B52" s="5"/>
+      <c r="C52" s="5"/>
+      <c r="D52" s="5"/>
+      <c r="E52" s="5"/>
+      <c r="F52" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G52" s="5"/>
+      <c r="H52" s="5"/>
+      <c r="I52" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="J52" s="6"/>
-      <c r="K52" s="6"/>
-      <c r="L52" s="6"/>
-      <c r="M52" s="6"/>
-      <c r="N52" s="6"/>
-      <c r="O52" s="31"/>
+      <c r="J52" s="5"/>
+      <c r="K52" s="5"/>
+      <c r="L52" s="5"/>
+      <c r="M52" s="5"/>
+      <c r="N52" s="5"/>
+      <c r="O52" s="23"/>
     </row>
     <row r="53" ht="25" customHeight="1" spans="1:15">
-      <c r="A53" s="17" t="s">
+      <c r="A53" s="12" t="s">
         <v>224</v>
       </c>
-      <c r="B53" s="6"/>
-      <c r="C53" s="6"/>
-      <c r="D53" s="6"/>
-      <c r="E53" s="6"/>
-      <c r="F53" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G53" s="6"/>
-      <c r="H53" s="6"/>
-      <c r="I53" s="6" t="s">
+      <c r="B53" s="5"/>
+      <c r="C53" s="5"/>
+      <c r="D53" s="5"/>
+      <c r="E53" s="5"/>
+      <c r="F53" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G53" s="5"/>
+      <c r="H53" s="5"/>
+      <c r="I53" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="J53" s="6"/>
-      <c r="K53" s="6"/>
-      <c r="L53" s="6"/>
-      <c r="M53" s="6"/>
-      <c r="N53" s="6"/>
-      <c r="O53" s="31"/>
+      <c r="J53" s="5"/>
+      <c r="K53" s="5"/>
+      <c r="L53" s="5"/>
+      <c r="M53" s="5"/>
+      <c r="N53" s="5"/>
+      <c r="O53" s="23"/>
     </row>
     <row r="54" ht="25" customHeight="1" spans="1:15">
-      <c r="A54" s="17" t="s">
+      <c r="A54" s="12" t="s">
         <v>226</v>
       </c>
-      <c r="B54" s="6"/>
-      <c r="C54" s="6"/>
-      <c r="D54" s="6"/>
-      <c r="E54" s="6"/>
-      <c r="F54" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G54" s="6"/>
-      <c r="H54" s="6"/>
-      <c r="I54" s="6" t="s">
+      <c r="B54" s="5"/>
+      <c r="C54" s="5"/>
+      <c r="D54" s="5"/>
+      <c r="E54" s="5"/>
+      <c r="F54" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G54" s="5"/>
+      <c r="H54" s="5"/>
+      <c r="I54" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="J54" s="6"/>
-      <c r="K54" s="6"/>
-      <c r="L54" s="6"/>
-      <c r="M54" s="6"/>
-      <c r="N54" s="6"/>
-      <c r="O54" s="31"/>
+      <c r="J54" s="5"/>
+      <c r="K54" s="5"/>
+      <c r="L54" s="5"/>
+      <c r="M54" s="5"/>
+      <c r="N54" s="5"/>
+      <c r="O54" s="23"/>
     </row>
     <row r="55" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A55" s="17" t="s">
+      <c r="A55" s="12" t="s">
         <v>228</v>
       </c>
-      <c r="B55" s="6"/>
-      <c r="C55" s="6"/>
-      <c r="D55" s="6"/>
-      <c r="E55" s="6"/>
-      <c r="F55" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G55" s="6"/>
-      <c r="H55" s="6"/>
-      <c r="I55" s="6" t="s">
+      <c r="B55" s="5"/>
+      <c r="C55" s="5"/>
+      <c r="D55" s="5"/>
+      <c r="E55" s="5"/>
+      <c r="F55" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G55" s="5"/>
+      <c r="H55" s="5"/>
+      <c r="I55" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="J55" s="6"/>
-      <c r="K55" s="6"/>
-      <c r="L55" s="6"/>
-      <c r="M55" s="6"/>
-      <c r="N55" s="6"/>
-      <c r="O55" s="31"/>
+      <c r="J55" s="5"/>
+      <c r="K55" s="5"/>
+      <c r="L55" s="5"/>
+      <c r="M55" s="5"/>
+      <c r="N55" s="5"/>
+      <c r="O55" s="23"/>
     </row>
     <row r="56" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A56" s="17" t="s">
+      <c r="A56" s="12" t="s">
         <v>230</v>
       </c>
-      <c r="B56" s="6"/>
-      <c r="C56" s="6"/>
-      <c r="D56" s="6"/>
-      <c r="E56" s="6"/>
-      <c r="F56" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G56" s="6"/>
-      <c r="H56" s="6"/>
-      <c r="I56" s="6" t="s">
+      <c r="B56" s="5"/>
+      <c r="C56" s="5"/>
+      <c r="D56" s="5"/>
+      <c r="E56" s="5"/>
+      <c r="F56" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G56" s="5"/>
+      <c r="H56" s="5"/>
+      <c r="I56" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="J56" s="6"/>
-      <c r="K56" s="6"/>
-      <c r="L56" s="6"/>
-      <c r="M56" s="6"/>
-      <c r="N56" s="6"/>
-      <c r="O56" s="31"/>
+      <c r="J56" s="5"/>
+      <c r="K56" s="5"/>
+      <c r="L56" s="5"/>
+      <c r="M56" s="5"/>
+      <c r="N56" s="5"/>
+      <c r="O56" s="23"/>
     </row>
     <row r="57" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A57" s="17" t="s">
+      <c r="A57" s="12" t="s">
         <v>232</v>
       </c>
-      <c r="B57" s="6"/>
-      <c r="C57" s="6"/>
-      <c r="D57" s="6"/>
-      <c r="E57" s="6"/>
-      <c r="F57" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G57" s="6"/>
-      <c r="H57" s="6"/>
-      <c r="I57" s="6" t="s">
+      <c r="B57" s="5"/>
+      <c r="C57" s="5"/>
+      <c r="D57" s="5"/>
+      <c r="E57" s="5"/>
+      <c r="F57" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G57" s="5"/>
+      <c r="H57" s="5"/>
+      <c r="I57" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="J57" s="6"/>
-      <c r="K57" s="6"/>
-      <c r="L57" s="6"/>
-      <c r="M57" s="6"/>
-      <c r="N57" s="6"/>
-      <c r="O57" s="31"/>
+      <c r="J57" s="5"/>
+      <c r="K57" s="5"/>
+      <c r="L57" s="5"/>
+      <c r="M57" s="5"/>
+      <c r="N57" s="5"/>
+      <c r="O57" s="23"/>
     </row>
     <row r="58" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A58" s="17" t="s">
+      <c r="A58" s="12" t="s">
         <v>234</v>
       </c>
-      <c r="B58" s="6"/>
-      <c r="C58" s="6"/>
-      <c r="D58" s="6"/>
-      <c r="E58" s="6"/>
-      <c r="F58" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G58" s="6"/>
-      <c r="H58" s="6"/>
-      <c r="I58" s="6" t="s">
+      <c r="B58" s="5"/>
+      <c r="C58" s="5"/>
+      <c r="D58" s="5"/>
+      <c r="E58" s="5"/>
+      <c r="F58" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G58" s="5"/>
+      <c r="H58" s="5"/>
+      <c r="I58" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="J58" s="6"/>
-      <c r="K58" s="6"/>
-      <c r="L58" s="6"/>
-      <c r="M58" s="6"/>
-      <c r="N58" s="6"/>
-      <c r="O58" s="31"/>
+      <c r="J58" s="5"/>
+      <c r="K58" s="5"/>
+      <c r="L58" s="5"/>
+      <c r="M58" s="5"/>
+      <c r="N58" s="5"/>
+      <c r="O58" s="23"/>
     </row>
     <row r="59" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A59" s="17" t="s">
+      <c r="A59" s="12" t="s">
         <v>236</v>
       </c>
-      <c r="B59" s="6" t="s">
+      <c r="B59" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C59" s="23" t="s">
+      <c r="C59" s="17" t="s">
         <v>237</v>
       </c>
-      <c r="D59" s="6"/>
-      <c r="E59" s="6" t="s">
+      <c r="D59" s="5"/>
+      <c r="E59" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="F59" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G59" s="6"/>
-      <c r="H59" s="24" t="s">
+      <c r="F59" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G59" s="5"/>
+      <c r="H59" s="18" t="s">
         <v>239</v>
       </c>
-      <c r="I59" s="6" t="s">
+      <c r="I59" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="J59" s="6"/>
-      <c r="K59" s="6"/>
-      <c r="L59" s="6"/>
-      <c r="M59" s="6"/>
-      <c r="N59" s="6"/>
-      <c r="O59" s="31"/>
+      <c r="J59" s="5"/>
+      <c r="K59" s="5"/>
+      <c r="L59" s="5"/>
+      <c r="M59" s="5"/>
+      <c r="N59" s="5"/>
+      <c r="O59" s="23"/>
     </row>
     <row r="60" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A60" s="17" t="s">
+      <c r="A60" s="12" t="s">
         <v>241</v>
       </c>
-      <c r="B60" s="6" t="s">
+      <c r="B60" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="C60" s="23" t="s">
+      <c r="C60" s="17" t="s">
         <v>242</v>
       </c>
-      <c r="D60" s="6"/>
-      <c r="E60" s="6" t="s">
+      <c r="D60" s="5"/>
+      <c r="E60" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="F60" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G60" s="6"/>
-      <c r="H60" s="24" t="s">
+      <c r="F60" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G60" s="5"/>
+      <c r="H60" s="18" t="s">
         <v>243</v>
       </c>
-      <c r="I60" s="6" t="s">
+      <c r="I60" s="5" t="s">
         <v>244</v>
       </c>
-      <c r="J60" s="6"/>
-      <c r="K60" s="6"/>
-      <c r="L60" s="6"/>
-      <c r="M60" s="6"/>
-      <c r="N60" s="6"/>
-      <c r="O60" s="6"/>
+      <c r="J60" s="5"/>
+      <c r="K60" s="5"/>
+      <c r="L60" s="5"/>
+      <c r="M60" s="5"/>
+      <c r="N60" s="5"/>
+      <c r="O60" s="5"/>
     </row>
     <row r="61" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A61" s="17" t="s">
+      <c r="A61" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="B61" s="6" t="s">
+      <c r="B61" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C61" s="25" t="s">
+      <c r="C61" s="19" t="s">
         <v>246</v>
       </c>
-      <c r="D61" s="6"/>
-      <c r="E61" s="6" t="s">
+      <c r="D61" s="5"/>
+      <c r="E61" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="F61" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G61" s="6"/>
-      <c r="H61" s="24" t="s">
+      <c r="F61" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G61" s="5"/>
+      <c r="H61" s="18" t="s">
         <v>247</v>
       </c>
-      <c r="I61" s="6" t="s">
+      <c r="I61" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="J61" s="6"/>
-      <c r="K61" s="6"/>
-      <c r="L61" s="6"/>
-      <c r="M61" s="6"/>
-      <c r="N61" s="6"/>
-      <c r="O61" s="31"/>
+      <c r="J61" s="5"/>
+      <c r="K61" s="5"/>
+      <c r="L61" s="5"/>
+      <c r="M61" s="5"/>
+      <c r="N61" s="5"/>
+      <c r="O61" s="23"/>
     </row>
     <row r="62" ht="25" customHeight="1" spans="1:15">
-      <c r="A62" s="17" t="s">
+      <c r="A62" s="12" t="s">
         <v>249</v>
       </c>
-      <c r="B62" s="6" t="s">
+      <c r="B62" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C62" s="23" t="s">
+      <c r="C62" s="17" t="s">
         <v>250</v>
       </c>
-      <c r="D62" s="6"/>
-      <c r="E62" s="6" t="s">
+      <c r="D62" s="5"/>
+      <c r="E62" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="F62" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G62" s="6"/>
-      <c r="H62" s="24" t="s">
+      <c r="F62" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G62" s="5"/>
+      <c r="H62" s="18" t="s">
         <v>252</v>
       </c>
-      <c r="I62" s="6" t="s">
+      <c r="I62" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="J62" s="6"/>
-      <c r="K62" s="6"/>
-      <c r="L62" s="6"/>
-      <c r="M62" s="6"/>
-      <c r="N62" s="6"/>
-      <c r="O62" s="31"/>
+      <c r="J62" s="5"/>
+      <c r="K62" s="5"/>
+      <c r="L62" s="5"/>
+      <c r="M62" s="5"/>
+      <c r="N62" s="5"/>
+      <c r="O62" s="23"/>
     </row>
     <row r="63" ht="25" customHeight="1" spans="1:15">
-      <c r="A63" s="17" t="s">
+      <c r="A63" s="12" t="s">
         <v>254</v>
       </c>
-      <c r="B63" s="6" t="s">
+      <c r="B63" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C63" s="23" t="s">
+      <c r="C63" s="17" t="s">
         <v>255</v>
       </c>
-      <c r="D63" s="6"/>
-      <c r="E63" s="6" t="s">
+      <c r="D63" s="5"/>
+      <c r="E63" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="F63" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G63" s="6"/>
-      <c r="H63" s="24" t="s">
+      <c r="F63" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G63" s="5"/>
+      <c r="H63" s="18" t="s">
         <v>256</v>
       </c>
-      <c r="I63" s="6" t="s">
+      <c r="I63" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="J63" s="6"/>
-      <c r="K63" s="6"/>
-      <c r="L63" s="6"/>
-      <c r="M63" s="6"/>
-      <c r="N63" s="6"/>
-      <c r="O63" s="31"/>
+      <c r="J63" s="5"/>
+      <c r="K63" s="5"/>
+      <c r="L63" s="5"/>
+      <c r="M63" s="5"/>
+      <c r="N63" s="5"/>
+      <c r="O63" s="23"/>
     </row>
     <row r="64" ht="25" customHeight="1" spans="1:15">
-      <c r="A64" s="17" t="s">
+      <c r="A64" s="12" t="s">
         <v>258</v>
       </c>
-      <c r="B64" s="6" t="s">
+      <c r="B64" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C64" s="23" t="s">
+      <c r="C64" s="17" t="s">
         <v>259</v>
       </c>
-      <c r="D64" s="6"/>
-      <c r="E64" s="6" t="s">
+      <c r="D64" s="5"/>
+      <c r="E64" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="F64" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G64" s="6"/>
-      <c r="H64" s="24" t="s">
+      <c r="F64" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G64" s="5"/>
+      <c r="H64" s="18" t="s">
         <v>261</v>
       </c>
-      <c r="I64" s="6" t="s">
+      <c r="I64" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="J64" s="6"/>
-      <c r="K64" s="6"/>
-      <c r="L64" s="6"/>
-      <c r="M64" s="6"/>
-      <c r="N64" s="6"/>
-      <c r="O64" s="31"/>
+      <c r="J64" s="5"/>
+      <c r="K64" s="5"/>
+      <c r="L64" s="5"/>
+      <c r="M64" s="5"/>
+      <c r="N64" s="5"/>
+      <c r="O64" s="23"/>
     </row>
     <row r="65" ht="25" customHeight="1" spans="1:15">
-      <c r="A65" s="17"/>
-      <c r="B65" s="6"/>
-      <c r="C65" s="6"/>
-      <c r="D65" s="6"/>
-      <c r="E65" s="6"/>
-      <c r="F65" s="18"/>
-      <c r="G65" s="6"/>
-      <c r="H65" s="6"/>
-      <c r="I65" s="6"/>
-      <c r="J65" s="6"/>
-      <c r="K65" s="6"/>
-      <c r="L65" s="6"/>
-      <c r="M65" s="6"/>
-      <c r="N65" s="6"/>
-      <c r="O65" s="6"/>
+      <c r="A65" s="12"/>
+      <c r="B65" s="5"/>
+      <c r="C65" s="5"/>
+      <c r="D65" s="5"/>
+      <c r="E65" s="5"/>
+      <c r="F65" s="13"/>
+      <c r="G65" s="5"/>
+      <c r="H65" s="5"/>
+      <c r="I65" s="5"/>
+      <c r="J65" s="5"/>
+      <c r="K65" s="5"/>
+      <c r="L65" s="5"/>
+      <c r="M65" s="5"/>
+      <c r="N65" s="5"/>
+      <c r="O65" s="5"/>
     </row>
     <row r="66" ht="25" customHeight="1" spans="1:15">
-      <c r="A66" s="17"/>
-      <c r="B66" s="6"/>
-      <c r="C66" s="6"/>
-      <c r="D66" s="6"/>
-      <c r="E66" s="6"/>
-      <c r="F66" s="18"/>
-      <c r="G66" s="6"/>
-      <c r="H66" s="6"/>
-      <c r="I66" s="6"/>
-      <c r="J66" s="6"/>
-      <c r="K66" s="6"/>
-      <c r="L66" s="6"/>
-      <c r="M66" s="6"/>
-      <c r="N66" s="6"/>
-      <c r="O66" s="6"/>
+      <c r="A66" s="12"/>
+      <c r="B66" s="5"/>
+      <c r="C66" s="5"/>
+      <c r="D66" s="5"/>
+      <c r="E66" s="5"/>
+      <c r="F66" s="13"/>
+      <c r="G66" s="5"/>
+      <c r="H66" s="5"/>
+      <c r="I66" s="5"/>
+      <c r="J66" s="5"/>
+      <c r="K66" s="5"/>
+      <c r="L66" s="5"/>
+      <c r="M66" s="5"/>
+      <c r="N66" s="5"/>
+      <c r="O66" s="5"/>
     </row>
     <row r="67" ht="25" customHeight="1" spans="1:15">
-      <c r="A67" s="17"/>
-      <c r="B67" s="6"/>
-      <c r="C67" s="6"/>
-      <c r="D67" s="6"/>
-      <c r="E67" s="6"/>
-      <c r="F67" s="18"/>
-      <c r="G67" s="6"/>
-      <c r="H67" s="6"/>
-      <c r="I67" s="6"/>
-      <c r="J67" s="6"/>
-      <c r="K67" s="6"/>
-      <c r="L67" s="6"/>
-      <c r="M67" s="6"/>
-      <c r="N67" s="6"/>
-      <c r="O67" s="6"/>
+      <c r="A67" s="12"/>
+      <c r="B67" s="5"/>
+      <c r="C67" s="5"/>
+      <c r="D67" s="5"/>
+      <c r="E67" s="5"/>
+      <c r="F67" s="13"/>
+      <c r="G67" s="5"/>
+      <c r="H67" s="5"/>
+      <c r="I67" s="5"/>
+      <c r="J67" s="5"/>
+      <c r="K67" s="5"/>
+      <c r="L67" s="5"/>
+      <c r="M67" s="5"/>
+      <c r="N67" s="5"/>
+      <c r="O67" s="5"/>
     </row>
     <row r="68" ht="25" customHeight="1" spans="1:15">
-      <c r="A68" s="17"/>
-      <c r="B68" s="6"/>
-      <c r="C68" s="6"/>
-      <c r="D68" s="6"/>
-      <c r="E68" s="6"/>
-      <c r="F68" s="18"/>
-      <c r="G68" s="6"/>
-      <c r="H68" s="6"/>
-      <c r="I68" s="6"/>
-      <c r="J68" s="6"/>
-      <c r="K68" s="6"/>
-      <c r="L68" s="6"/>
-      <c r="M68" s="6"/>
-      <c r="N68" s="6"/>
-      <c r="O68" s="6"/>
+      <c r="A68" s="12"/>
+      <c r="B68" s="5"/>
+      <c r="C68" s="5"/>
+      <c r="D68" s="5"/>
+      <c r="E68" s="5"/>
+      <c r="F68" s="13"/>
+      <c r="G68" s="5"/>
+      <c r="H68" s="5"/>
+      <c r="I68" s="5"/>
+      <c r="J68" s="5"/>
+      <c r="K68" s="5"/>
+      <c r="L68" s="5"/>
+      <c r="M68" s="5"/>
+      <c r="N68" s="5"/>
+      <c r="O68" s="5"/>
     </row>
     <row r="69" ht="25" customHeight="1" spans="1:15">
-      <c r="A69" s="17"/>
-      <c r="B69" s="6"/>
-      <c r="C69" s="6"/>
-      <c r="D69" s="6"/>
-      <c r="E69" s="6"/>
-      <c r="F69" s="18"/>
-      <c r="G69" s="6"/>
-      <c r="H69" s="6"/>
-      <c r="I69" s="6"/>
-      <c r="J69" s="6"/>
-      <c r="K69" s="6"/>
-      <c r="L69" s="6"/>
-      <c r="M69" s="6"/>
-      <c r="N69" s="6"/>
-      <c r="O69" s="6"/>
+      <c r="A69" s="12"/>
+      <c r="B69" s="5"/>
+      <c r="C69" s="5"/>
+      <c r="D69" s="5"/>
+      <c r="E69" s="5"/>
+      <c r="F69" s="13"/>
+      <c r="G69" s="5"/>
+      <c r="H69" s="5"/>
+      <c r="I69" s="5"/>
+      <c r="J69" s="5"/>
+      <c r="K69" s="5"/>
+      <c r="L69" s="5"/>
+      <c r="M69" s="5"/>
+      <c r="N69" s="5"/>
+      <c r="O69" s="5"/>
     </row>
     <row r="70" ht="25" customHeight="1" spans="1:15">
-      <c r="A70" s="17"/>
-      <c r="B70" s="6"/>
-      <c r="C70" s="6"/>
-      <c r="D70" s="6"/>
-      <c r="E70" s="6"/>
-      <c r="F70" s="18"/>
-      <c r="G70" s="6"/>
-      <c r="H70" s="6"/>
-      <c r="I70" s="6"/>
-      <c r="J70" s="6"/>
-      <c r="K70" s="6"/>
-      <c r="L70" s="6"/>
-      <c r="M70" s="6"/>
-      <c r="N70" s="6"/>
-      <c r="O70" s="6"/>
+      <c r="A70" s="12"/>
+      <c r="B70" s="5"/>
+      <c r="C70" s="5"/>
+      <c r="D70" s="5"/>
+      <c r="E70" s="5"/>
+      <c r="F70" s="13"/>
+      <c r="G70" s="5"/>
+      <c r="H70" s="5"/>
+      <c r="I70" s="5"/>
+      <c r="J70" s="5"/>
+      <c r="K70" s="5"/>
+      <c r="L70" s="5"/>
+      <c r="M70" s="5"/>
+      <c r="N70" s="5"/>
+      <c r="O70" s="5"/>
     </row>
     <row r="71" ht="25" customHeight="1" spans="1:15">
-      <c r="A71" s="17"/>
-      <c r="B71" s="6"/>
-      <c r="C71" s="6"/>
-      <c r="D71" s="6"/>
-      <c r="E71" s="6"/>
-      <c r="F71" s="18"/>
-      <c r="G71" s="6"/>
-      <c r="H71" s="6"/>
-      <c r="I71" s="6"/>
-      <c r="J71" s="6"/>
-      <c r="K71" s="6"/>
-      <c r="L71" s="6"/>
-      <c r="M71" s="6"/>
-      <c r="N71" s="6"/>
-      <c r="O71" s="6"/>
+      <c r="A71" s="12"/>
+      <c r="B71" s="5"/>
+      <c r="C71" s="5"/>
+      <c r="D71" s="5"/>
+      <c r="E71" s="5"/>
+      <c r="F71" s="13"/>
+      <c r="G71" s="5"/>
+      <c r="H71" s="5"/>
+      <c r="I71" s="5"/>
+      <c r="J71" s="5"/>
+      <c r="K71" s="5"/>
+      <c r="L71" s="5"/>
+      <c r="M71" s="5"/>
+      <c r="N71" s="5"/>
+      <c r="O71" s="5"/>
     </row>
     <row r="72" ht="25" customHeight="1" spans="1:15">
-      <c r="A72" s="17"/>
-      <c r="B72" s="6"/>
-      <c r="C72" s="6"/>
-      <c r="D72" s="6"/>
-      <c r="E72" s="6"/>
-      <c r="F72" s="18"/>
-      <c r="G72" s="6"/>
-      <c r="H72" s="6"/>
-      <c r="I72" s="6"/>
-      <c r="J72" s="6"/>
-      <c r="K72" s="6"/>
-      <c r="L72" s="6"/>
-      <c r="M72" s="6"/>
-      <c r="N72" s="6"/>
-      <c r="O72" s="6"/>
+      <c r="A72" s="12"/>
+      <c r="B72" s="5"/>
+      <c r="C72" s="5"/>
+      <c r="D72" s="5"/>
+      <c r="E72" s="5"/>
+      <c r="F72" s="13"/>
+      <c r="G72" s="5"/>
+      <c r="H72" s="5"/>
+      <c r="I72" s="5"/>
+      <c r="J72" s="5"/>
+      <c r="K72" s="5"/>
+      <c r="L72" s="5"/>
+      <c r="M72" s="5"/>
+      <c r="N72" s="5"/>
+      <c r="O72" s="5"/>
     </row>
     <row r="73" ht="25" customHeight="1" spans="1:15">
-      <c r="A73" s="17"/>
-      <c r="B73" s="6"/>
-      <c r="C73" s="6"/>
-      <c r="D73" s="6"/>
-      <c r="E73" s="6"/>
-      <c r="F73" s="18"/>
-      <c r="G73" s="6"/>
-      <c r="H73" s="6"/>
-      <c r="I73" s="6"/>
-      <c r="J73" s="6"/>
-      <c r="K73" s="6"/>
-      <c r="L73" s="6"/>
-      <c r="M73" s="6"/>
-      <c r="N73" s="6"/>
-      <c r="O73" s="6"/>
+      <c r="A73" s="12"/>
+      <c r="B73" s="5"/>
+      <c r="C73" s="5"/>
+      <c r="D73" s="5"/>
+      <c r="E73" s="5"/>
+      <c r="F73" s="13"/>
+      <c r="G73" s="5"/>
+      <c r="H73" s="5"/>
+      <c r="I73" s="5"/>
+      <c r="J73" s="5"/>
+      <c r="K73" s="5"/>
+      <c r="L73" s="5"/>
+      <c r="M73" s="5"/>
+      <c r="N73" s="5"/>
+      <c r="O73" s="5"/>
     </row>
     <row r="74" ht="25" customHeight="1" spans="1:15">
-      <c r="A74" s="17"/>
-      <c r="B74" s="6"/>
-      <c r="C74" s="6"/>
-      <c r="D74" s="6"/>
-      <c r="E74" s="6"/>
-      <c r="F74" s="18"/>
-      <c r="G74" s="6"/>
-      <c r="H74" s="6"/>
-      <c r="I74" s="6"/>
-      <c r="J74" s="6"/>
-      <c r="K74" s="6"/>
-      <c r="L74" s="6"/>
-      <c r="M74" s="6"/>
-      <c r="N74" s="6"/>
-      <c r="O74" s="6"/>
+      <c r="A74" s="12"/>
+      <c r="B74" s="5"/>
+      <c r="C74" s="5"/>
+      <c r="D74" s="5"/>
+      <c r="E74" s="5"/>
+      <c r="F74" s="13"/>
+      <c r="G74" s="5"/>
+      <c r="H74" s="5"/>
+      <c r="I74" s="5"/>
+      <c r="J74" s="5"/>
+      <c r="K74" s="5"/>
+      <c r="L74" s="5"/>
+      <c r="M74" s="5"/>
+      <c r="N74" s="5"/>
+      <c r="O74" s="5"/>
     </row>
     <row r="75" ht="25" customHeight="1" spans="1:15">
-      <c r="A75" s="17"/>
-      <c r="B75" s="6"/>
-      <c r="C75" s="6"/>
-      <c r="D75" s="6"/>
-      <c r="E75" s="6"/>
-      <c r="F75" s="18"/>
-      <c r="G75" s="6"/>
-      <c r="H75" s="6"/>
-      <c r="I75" s="6"/>
-      <c r="J75" s="6"/>
-      <c r="K75" s="6"/>
-      <c r="L75" s="6"/>
-      <c r="M75" s="6"/>
-      <c r="N75" s="6"/>
-      <c r="O75" s="6"/>
+      <c r="A75" s="12"/>
+      <c r="B75" s="5"/>
+      <c r="C75" s="5"/>
+      <c r="D75" s="5"/>
+      <c r="E75" s="5"/>
+      <c r="F75" s="13"/>
+      <c r="G75" s="5"/>
+      <c r="H75" s="5"/>
+      <c r="I75" s="5"/>
+      <c r="J75" s="5"/>
+      <c r="K75" s="5"/>
+      <c r="L75" s="5"/>
+      <c r="M75" s="5"/>
+      <c r="N75" s="5"/>
+      <c r="O75" s="5"/>
     </row>
     <row r="76" ht="25" customHeight="1" spans="1:15">
-      <c r="A76" s="17"/>
-      <c r="B76" s="6"/>
-      <c r="C76" s="6"/>
-      <c r="D76" s="6"/>
-      <c r="E76" s="6"/>
-      <c r="F76" s="18"/>
-      <c r="G76" s="6"/>
-      <c r="H76" s="6"/>
-      <c r="I76" s="6"/>
-      <c r="J76" s="6"/>
-      <c r="K76" s="6"/>
-      <c r="L76" s="6"/>
-      <c r="M76" s="6"/>
-      <c r="N76" s="6"/>
-      <c r="O76" s="6"/>
+      <c r="A76" s="12"/>
+      <c r="B76" s="5"/>
+      <c r="C76" s="5"/>
+      <c r="D76" s="5"/>
+      <c r="E76" s="5"/>
+      <c r="F76" s="13"/>
+      <c r="G76" s="5"/>
+      <c r="H76" s="5"/>
+      <c r="I76" s="5"/>
+      <c r="J76" s="5"/>
+      <c r="K76" s="5"/>
+      <c r="L76" s="5"/>
+      <c r="M76" s="5"/>
+      <c r="N76" s="5"/>
+      <c r="O76" s="5"/>
     </row>
     <row r="77" ht="25" customHeight="1" spans="1:15">
-      <c r="A77" s="17"/>
-      <c r="B77" s="6"/>
-      <c r="C77" s="6"/>
-      <c r="D77" s="6"/>
-      <c r="E77" s="6"/>
-      <c r="F77" s="18"/>
-      <c r="G77" s="6"/>
-      <c r="H77" s="6"/>
-      <c r="I77" s="6"/>
-      <c r="J77" s="6"/>
-      <c r="K77" s="6"/>
-      <c r="L77" s="6"/>
-      <c r="M77" s="6"/>
-      <c r="N77" s="6"/>
-      <c r="O77" s="6"/>
+      <c r="A77" s="12"/>
+      <c r="B77" s="5"/>
+      <c r="C77" s="5"/>
+      <c r="D77" s="5"/>
+      <c r="E77" s="5"/>
+      <c r="F77" s="13"/>
+      <c r="G77" s="5"/>
+      <c r="H77" s="5"/>
+      <c r="I77" s="5"/>
+      <c r="J77" s="5"/>
+      <c r="K77" s="5"/>
+      <c r="L77" s="5"/>
+      <c r="M77" s="5"/>
+      <c r="N77" s="5"/>
+      <c r="O77" s="5"/>
     </row>
     <row r="78" ht="25" customHeight="1" spans="1:15">
-      <c r="A78" s="17"/>
-      <c r="B78" s="6"/>
-      <c r="C78" s="6"/>
-      <c r="D78" s="6"/>
-      <c r="E78" s="6"/>
-      <c r="F78" s="18"/>
-      <c r="G78" s="6"/>
-      <c r="H78" s="6"/>
-      <c r="I78" s="6"/>
-      <c r="J78" s="6"/>
-      <c r="K78" s="6"/>
-      <c r="L78" s="6"/>
-      <c r="M78" s="6"/>
-      <c r="N78" s="6"/>
-      <c r="O78" s="6"/>
+      <c r="A78" s="12"/>
+      <c r="B78" s="5"/>
+      <c r="C78" s="5"/>
+      <c r="D78" s="5"/>
+      <c r="E78" s="5"/>
+      <c r="F78" s="13"/>
+      <c r="G78" s="5"/>
+      <c r="H78" s="5"/>
+      <c r="I78" s="5"/>
+      <c r="J78" s="5"/>
+      <c r="K78" s="5"/>
+      <c r="L78" s="5"/>
+      <c r="M78" s="5"/>
+      <c r="N78" s="5"/>
+      <c r="O78" s="5"/>
     </row>
     <row r="79" ht="25" customHeight="1" spans="1:15">
-      <c r="A79" s="17"/>
-      <c r="B79" s="6"/>
-      <c r="C79" s="6"/>
-      <c r="D79" s="6"/>
-      <c r="E79" s="6"/>
-      <c r="F79" s="18"/>
-      <c r="G79" s="6"/>
-      <c r="H79" s="6"/>
-      <c r="I79" s="6"/>
-      <c r="J79" s="6"/>
-      <c r="K79" s="6"/>
-      <c r="L79" s="6"/>
-      <c r="M79" s="6"/>
-      <c r="N79" s="6"/>
-      <c r="O79" s="6"/>
+      <c r="A79" s="12"/>
+      <c r="B79" s="5"/>
+      <c r="C79" s="5"/>
+      <c r="D79" s="5"/>
+      <c r="E79" s="5"/>
+      <c r="F79" s="13"/>
+      <c r="G79" s="5"/>
+      <c r="H79" s="5"/>
+      <c r="I79" s="5"/>
+      <c r="J79" s="5"/>
+      <c r="K79" s="5"/>
+      <c r="L79" s="5"/>
+      <c r="M79" s="5"/>
+      <c r="N79" s="5"/>
+      <c r="O79" s="5"/>
     </row>
     <row r="80" ht="25" customHeight="1" spans="1:15">
-      <c r="A80" s="17"/>
-      <c r="B80" s="6"/>
-      <c r="C80" s="6"/>
-      <c r="D80" s="6"/>
-      <c r="E80" s="6"/>
-      <c r="F80" s="18"/>
-      <c r="G80" s="6"/>
-      <c r="H80" s="6"/>
-      <c r="I80" s="6"/>
-      <c r="J80" s="6"/>
-      <c r="K80" s="6"/>
-      <c r="L80" s="6"/>
-      <c r="M80" s="6"/>
-      <c r="N80" s="6"/>
-      <c r="O80" s="6"/>
+      <c r="A80" s="12"/>
+      <c r="B80" s="5"/>
+      <c r="C80" s="5"/>
+      <c r="D80" s="5"/>
+      <c r="E80" s="5"/>
+      <c r="F80" s="13"/>
+      <c r="G80" s="5"/>
+      <c r="H80" s="5"/>
+      <c r="I80" s="5"/>
+      <c r="J80" s="5"/>
+      <c r="K80" s="5"/>
+      <c r="L80" s="5"/>
+      <c r="M80" s="5"/>
+      <c r="N80" s="5"/>
+      <c r="O80" s="5"/>
     </row>
     <row r="81" ht="25" customHeight="1" spans="1:15">
-      <c r="A81" s="17"/>
-      <c r="B81" s="6"/>
-      <c r="C81" s="6"/>
-      <c r="D81" s="6"/>
-      <c r="E81" s="6"/>
-      <c r="F81" s="18"/>
-      <c r="G81" s="6"/>
-      <c r="H81" s="6"/>
-      <c r="I81" s="6"/>
-      <c r="J81" s="6"/>
-      <c r="K81" s="6"/>
-      <c r="L81" s="6"/>
-      <c r="M81" s="6"/>
-      <c r="N81" s="6"/>
-      <c r="O81" s="6"/>
+      <c r="A81" s="12"/>
+      <c r="B81" s="5"/>
+      <c r="C81" s="5"/>
+      <c r="D81" s="5"/>
+      <c r="E81" s="5"/>
+      <c r="F81" s="13"/>
+      <c r="G81" s="5"/>
+      <c r="H81" s="5"/>
+      <c r="I81" s="5"/>
+      <c r="J81" s="5"/>
+      <c r="K81" s="5"/>
+      <c r="L81" s="5"/>
+      <c r="M81" s="5"/>
+      <c r="N81" s="5"/>
+      <c r="O81" s="5"/>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:O64" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A2:O64">
+    <sortState ref="A1:O64">
       <sortCondition ref="F1"/>
     </sortState>
     <extLst/>
@@ -4802,576 +4784,576 @@
       <c r="A1" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
     </row>
     <row r="2" s="1" customFormat="1" ht="32" customHeight="1" spans="1:9">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="5" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:9">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="7" t="s">
         <v>264</v>
       </c>
-      <c r="D3" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="8">
+      <c r="D3" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="7">
         <v>4</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="9">
+      <c r="G3" s="7">
         <v>2026</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="10" t="s">
+      <c r="I3" s="8" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:9">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="9">
+      <c r="D4" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="7">
         <v>8</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="9">
+      <c r="G4" s="7">
         <v>2026</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="I4" s="8" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:9">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="9">
+      <c r="D5" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="7">
         <v>23</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="9">
+      <c r="G5" s="7">
         <v>2026</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="H5" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="I5" s="10" t="s">
+      <c r="I5" s="8" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:9">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="9">
+      <c r="D6" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="7">
         <v>18</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G6" s="7">
         <v>2026</v>
       </c>
-      <c r="H6" s="11" t="s">
+      <c r="H6" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="I6" s="10" t="s">
+      <c r="I6" s="8" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:9">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="9">
+      <c r="D7" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="7">
         <v>20</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G7" s="7">
         <v>2026</v>
       </c>
-      <c r="H7" s="8" t="s">
+      <c r="H7" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="I7" s="10" t="s">
+      <c r="I7" s="8" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:9">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D8" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="9">
+      <c r="D8" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="7">
         <v>3</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F8" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="G8" s="9">
+      <c r="G8" s="7">
         <v>2026</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="H8" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="I8" s="10" t="s">
+      <c r="I8" s="8" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:9">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" s="8">
+      <c r="D9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="7">
         <v>4</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="G9" s="9">
+      <c r="G9" s="7">
         <v>2026</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="I9" s="10" t="s">
+      <c r="I9" s="8" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:9">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="D10" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="9">
+      <c r="D10" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="7">
         <v>6</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="F10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="G10" s="9">
+      <c r="G10" s="7">
         <v>2026</v>
       </c>
-      <c r="H10" s="11" t="s">
+      <c r="H10" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="I10" s="12" t="s">
+      <c r="I10" s="8" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:9">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="9">
+      <c r="D11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="7">
         <v>6</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="F11" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="G11" s="9">
+      <c r="G11" s="7">
         <v>2026</v>
       </c>
-      <c r="H11" s="11" t="s">
+      <c r="H11" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="I11" s="12" t="s">
+      <c r="I11" s="8" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:9">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E12" s="9">
+      <c r="D12" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="7">
         <v>4</v>
       </c>
-      <c r="F12" s="8" t="s">
+      <c r="F12" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="G12" s="9">
+      <c r="G12" s="7">
         <v>2026</v>
       </c>
-      <c r="H12" s="8" t="s">
+      <c r="H12" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="I12" s="12" t="s">
+      <c r="I12" s="8" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:9">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="D13" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E13" s="9">
+      <c r="D13" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="7">
         <v>6</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="F13" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="G13" s="9">
+      <c r="G13" s="7">
         <v>2026</v>
       </c>
-      <c r="H13" s="11" t="s">
+      <c r="H13" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="I13" s="10" t="s">
+      <c r="I13" s="8" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:9">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="D14" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" s="9">
+      <c r="D14" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" s="7">
         <v>8</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="F14" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="G14" s="9">
+      <c r="G14" s="7">
         <v>2026</v>
       </c>
-      <c r="H14" s="8" t="s">
+      <c r="H14" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="I14" s="10" t="s">
+      <c r="I14" s="8" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:9">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="D15" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E15" s="9">
+      <c r="D15" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" s="7">
         <v>4</v>
       </c>
-      <c r="F15" s="8" t="s">
+      <c r="F15" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="G15" s="9">
+      <c r="G15" s="7">
         <v>2026</v>
       </c>
-      <c r="H15" s="11" t="s">
+      <c r="H15" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="I15" s="10" t="s">
+      <c r="I15" s="8" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:9">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="D16" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E16" s="9">
+      <c r="D16" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" s="7">
         <v>8</v>
       </c>
-      <c r="F16" s="8" t="s">
+      <c r="F16" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="G16" s="9">
+      <c r="G16" s="7">
         <v>2026</v>
       </c>
-      <c r="H16" s="11" t="s">
+      <c r="H16" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="I16" s="10" t="s">
+      <c r="I16" s="8" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:9">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="D17" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E17" s="8">
+      <c r="D17" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E17" s="7">
         <v>7</v>
       </c>
-      <c r="F17" s="8" t="s">
+      <c r="F17" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="G17" s="9">
+      <c r="G17" s="7">
         <v>2026</v>
       </c>
-      <c r="H17" s="8"/>
-      <c r="I17" s="10" t="s">
+      <c r="H17" s="7"/>
+      <c r="I17" s="8" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:9">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="D18" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E18" s="8">
+      <c r="D18" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="7">
         <v>4</v>
       </c>
-      <c r="F18" s="8" t="s">
+      <c r="F18" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="G18" s="9">
+      <c r="G18" s="7">
         <v>2026</v>
       </c>
-      <c r="H18" s="8"/>
-      <c r="I18" s="10" t="s">
+      <c r="H18" s="7"/>
+      <c r="I18" s="8" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" spans="1:9">
-      <c r="A19" s="13" t="s">
+      <c r="A19" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="B19" s="14" t="s">
+      <c r="B19" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="C19" s="10" t="s">
         <v>265</v>
       </c>
-      <c r="D19" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="G19" s="9">
+      <c r="D19" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19" s="10"/>
+      <c r="F19" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="G19" s="7">
         <v>2026</v>
       </c>
-      <c r="H19" s="8"/>
-      <c r="I19" s="16" t="s">
+      <c r="H19" s="7"/>
+      <c r="I19" s="11" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" spans="1:9">
-      <c r="A20" s="13" t="s">
+      <c r="A20" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="B20" s="14" t="s">
+      <c r="B20" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="C20" s="10" t="s">
         <v>265</v>
       </c>
-      <c r="D20" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="G20" s="9">
+      <c r="D20" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E20" s="10"/>
+      <c r="F20" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="G20" s="7">
         <v>2026</v>
       </c>
-      <c r="H20" s="8"/>
-      <c r="I20" s="16" t="s">
+      <c r="H20" s="7"/>
+      <c r="I20" s="11" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1" spans="1:9">
-      <c r="A21" s="17" t="s">
+      <c r="A21" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="D21" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E21" s="6" t="s">
+      <c r="D21" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E21" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="F21" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G21" s="6">
+      <c r="F21" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G21" s="5">
         <v>2026</v>
       </c>
-      <c r="H21" s="6" t="s">
+      <c r="H21" s="5" t="s">
         <v>89</v>
       </c>
       <c r="I21" s="1" t="s">
@@ -5379,28 +5361,28 @@
       </c>
     </row>
     <row r="22" ht="30" customHeight="1" spans="1:9">
-      <c r="A22" s="17" t="s">
+      <c r="A22" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="D22" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E22" s="6" t="s">
+      <c r="D22" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E22" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="F22" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G22" s="6">
+      <c r="F22" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G22" s="5">
         <v>2025</v>
       </c>
-      <c r="H22" s="6" t="s">
+      <c r="H22" s="5" t="s">
         <v>95</v>
       </c>
       <c r="I22" s="1" t="s">
@@ -5408,28 +5390,28 @@
       </c>
     </row>
     <row r="23" ht="30" customHeight="1" spans="1:9">
-      <c r="A23" s="17" t="s">
+      <c r="A23" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="D23" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E23" s="6" t="s">
+      <c r="D23" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E23" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="F23" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G23" s="6">
+      <c r="F23" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G23" s="5">
         <v>2026</v>
       </c>
-      <c r="H23" s="6" t="s">
+      <c r="H23" s="5" t="s">
         <v>101</v>
       </c>
       <c r="I23" s="1" t="s">
@@ -5437,28 +5419,28 @@
       </c>
     </row>
     <row r="24" ht="30" customHeight="1" spans="1:9">
-      <c r="A24" s="17" t="s">
+      <c r="A24" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="D24" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E24" s="6" t="s">
+      <c r="D24" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E24" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="F24" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G24" s="6">
+      <c r="F24" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G24" s="5">
         <v>2026</v>
       </c>
-      <c r="H24" s="6" t="s">
+      <c r="H24" s="5" t="s">
         <v>107</v>
       </c>
       <c r="I24" s="1" t="s">
@@ -5466,28 +5448,28 @@
       </c>
     </row>
     <row r="25" ht="30" customHeight="1" spans="1:9">
-      <c r="A25" s="17" t="s">
+      <c r="A25" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="D25" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E25" s="6" t="s">
+      <c r="D25" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E25" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="F25" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G25" s="6">
+      <c r="F25" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G25" s="5">
         <v>2025</v>
       </c>
-      <c r="H25" s="6" t="s">
+      <c r="H25" s="5" t="s">
         <v>113</v>
       </c>
       <c r="I25" s="1" t="s">
@@ -5495,28 +5477,28 @@
       </c>
     </row>
     <row r="26" ht="30" customHeight="1" spans="1:9">
-      <c r="A26" s="17" t="s">
+      <c r="A26" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="C26" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="D26" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E26" s="6" t="s">
+      <c r="D26" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E26" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="F26" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G26" s="6">
+      <c r="F26" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G26" s="5">
         <v>2026</v>
       </c>
-      <c r="H26" s="6" t="s">
+      <c r="H26" s="5" t="s">
         <v>119</v>
       </c>
       <c r="I26" s="1" t="s">
@@ -5524,1078 +5506,1078 @@
       </c>
     </row>
     <row r="27" ht="30" customHeight="1" spans="1:9">
-      <c r="A27" s="17" t="s">
+      <c r="A27" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C27" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="D27" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E27" s="6" t="s">
+      <c r="D27" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E27" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="F27" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G27" s="6">
+      <c r="F27" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G27" s="5">
         <v>2026</v>
       </c>
-      <c r="H27" s="6" t="s">
+      <c r="H27" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="I27" s="6" t="s">
+      <c r="I27" s="5" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1" spans="1:9">
-      <c r="A28" s="17" t="s">
+      <c r="A28" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C28" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="D28" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E28" s="6" t="s">
+      <c r="D28" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E28" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="F28" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G28" s="6">
+      <c r="F28" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G28" s="5">
         <v>2024</v>
       </c>
-      <c r="H28" s="6" t="s">
+      <c r="H28" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="I28" s="6" t="s">
+      <c r="I28" s="5" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="29" ht="25" customHeight="1" spans="1:9">
-      <c r="A29" s="17" t="s">
+      <c r="A29" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C29" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="D29" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E29" s="6" t="s">
+      <c r="D29" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E29" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="F29" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G29" s="6">
+      <c r="F29" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G29" s="5">
         <v>2024</v>
       </c>
-      <c r="H29" s="6" t="s">
+      <c r="H29" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="I29" s="6" t="s">
+      <c r="I29" s="5" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="30" ht="25" customHeight="1" spans="1:9">
-      <c r="A30" s="17" t="s">
+      <c r="A30" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C30" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="D30" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E30" s="6" t="s">
+      <c r="D30" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E30" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="F30" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G30" s="6">
+      <c r="F30" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G30" s="5">
         <v>2026</v>
       </c>
-      <c r="H30" s="6" t="s">
+      <c r="H30" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="I30" s="6" t="s">
+      <c r="I30" s="5" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="31" ht="25" customHeight="1" spans="1:9">
-      <c r="A31" s="17" t="s">
+      <c r="A31" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="C31" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="D31" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E31" s="6" t="s">
+      <c r="D31" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E31" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="F31" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G31" s="6">
+      <c r="F31" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G31" s="5">
         <v>2025</v>
       </c>
-      <c r="H31" s="6" t="s">
+      <c r="H31" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="I31" s="6" t="s">
+      <c r="I31" s="5" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="32" ht="25" customHeight="1" spans="1:9">
-      <c r="A32" s="17" t="s">
+      <c r="A32" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="B32" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C32" s="6" t="s">
+      <c r="C32" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="D32" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E32" s="6" t="s">
+      <c r="D32" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E32" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="F32" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G32" s="6">
+      <c r="F32" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G32" s="5">
         <v>2026</v>
       </c>
-      <c r="H32" s="6" t="s">
+      <c r="H32" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="I32" s="6" t="s">
+      <c r="I32" s="5" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="33" ht="25" customHeight="1" spans="1:9">
-      <c r="A33" s="17" t="s">
+      <c r="A33" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="C33" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="D33" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E33" s="6" t="s">
+      <c r="D33" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E33" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="F33" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G33" s="6">
+      <c r="F33" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G33" s="5">
         <v>2026</v>
       </c>
-      <c r="H33" s="6" t="s">
+      <c r="H33" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="I33" s="6" t="s">
+      <c r="I33" s="5" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="34" ht="25" customHeight="1" spans="1:9">
-      <c r="A34" s="17" t="s">
+      <c r="A34" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C34" s="6" t="s">
+      <c r="C34" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="D34" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E34" s="6" t="s">
+      <c r="D34" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E34" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="F34" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G34" s="6">
+      <c r="F34" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G34" s="5">
         <v>2026</v>
       </c>
-      <c r="H34" s="6" t="s">
+      <c r="H34" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="I34" s="6" t="s">
+      <c r="I34" s="5" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="35" ht="25" customHeight="1" spans="1:9">
-      <c r="A35" s="17" t="s">
+      <c r="A35" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="B35" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C35" s="6" t="s">
+      <c r="C35" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="D35" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E35" s="6" t="s">
+      <c r="D35" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E35" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="F35" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G35" s="6">
+      <c r="F35" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G35" s="5">
         <v>2025</v>
       </c>
-      <c r="H35" s="6" t="s">
+      <c r="H35" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="I35" s="6" t="s">
+      <c r="I35" s="5" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="36" ht="25" customHeight="1" spans="1:9">
-      <c r="A36" s="17" t="s">
+      <c r="A36" s="12" t="s">
         <v>170</v>
       </c>
-      <c r="B36" s="6" t="s">
+      <c r="B36" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C36" s="6" t="s">
+      <c r="C36" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="D36" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E36" s="6" t="s">
+      <c r="D36" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E36" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="F36" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G36" s="6">
+      <c r="F36" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G36" s="5">
         <v>2026</v>
       </c>
-      <c r="H36" s="6" t="s">
+      <c r="H36" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="I36" s="6" t="s">
+      <c r="I36" s="5" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="37" ht="25" customHeight="1" spans="1:9">
-      <c r="A37" s="17" t="s">
+      <c r="A37" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="B37" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C37" s="6" t="s">
+      <c r="C37" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="D37" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E37" s="6" t="s">
+      <c r="D37" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E37" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="F37" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G37" s="6">
+      <c r="F37" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G37" s="5">
         <v>2026</v>
       </c>
-      <c r="H37" s="6" t="s">
+      <c r="H37" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="I37" s="6" t="s">
+      <c r="I37" s="5" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="38" ht="25" customHeight="1" spans="1:9">
-      <c r="A38" s="17" t="s">
+      <c r="A38" s="12" t="s">
         <v>181</v>
       </c>
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="C38" s="6" t="s">
+      <c r="C38" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="D38" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E38" s="18" t="s">
+      <c r="D38" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E38" s="13" t="s">
         <v>184</v>
       </c>
-      <c r="F38" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G38" s="6">
+      <c r="F38" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G38" s="5">
         <v>2025</v>
       </c>
-      <c r="H38" s="6"/>
-      <c r="I38" s="6" t="s">
+      <c r="H38" s="5"/>
+      <c r="I38" s="5" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="39" ht="25" customHeight="1" spans="1:9">
-      <c r="A39" s="17" t="s">
+      <c r="A39" s="12" t="s">
         <v>186</v>
       </c>
-      <c r="B39" s="6" t="s">
+      <c r="B39" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="C39" s="6" t="s">
+      <c r="C39" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="D39" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E39" s="18" t="s">
+      <c r="D39" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E39" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="F39" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G39" s="6">
+      <c r="F39" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G39" s="5">
         <v>2025</v>
       </c>
-      <c r="H39" s="6" t="s">
+      <c r="H39" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="I39" s="6" t="s">
+      <c r="I39" s="5" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="40" ht="25" customHeight="1" spans="1:9">
-      <c r="A40" s="17" t="s">
+      <c r="A40" s="12" t="s">
         <v>192</v>
       </c>
-      <c r="B40" s="6" t="s">
+      <c r="B40" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="C40" s="6" t="s">
+      <c r="C40" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="D40" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E40" s="19" t="s">
+      <c r="D40" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E40" s="13" t="s">
         <v>184</v>
       </c>
-      <c r="F40" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G40" s="6">
+      <c r="F40" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G40" s="5">
         <v>2025</v>
       </c>
-      <c r="H40" s="6"/>
-      <c r="I40" s="6" t="s">
+      <c r="H40" s="5"/>
+      <c r="I40" s="5" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="41" ht="25" customHeight="1" spans="1:9">
-      <c r="A41" s="17" t="s">
+      <c r="A41" s="12" t="s">
         <v>195</v>
       </c>
-      <c r="B41" s="6" t="s">
+      <c r="B41" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="C41" s="6" t="s">
+      <c r="C41" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="D41" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E41" s="6" t="s">
+      <c r="D41" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E41" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="F41" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G41" s="6">
+      <c r="F41" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G41" s="5">
         <v>2026</v>
       </c>
-      <c r="H41" s="6" t="s">
+      <c r="H41" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="I41" s="6" t="s">
+      <c r="I41" s="5" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="42" ht="25" customHeight="1" spans="1:9">
-      <c r="A42" s="17" t="s">
+      <c r="A42" s="12" t="s">
         <v>200</v>
       </c>
-      <c r="B42" s="6"/>
-      <c r="C42" s="6"/>
-      <c r="D42" s="6"/>
-      <c r="E42" s="6"/>
-      <c r="F42" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G42" s="6"/>
-      <c r="H42" s="6"/>
-      <c r="I42" s="6" t="s">
+      <c r="B42" s="5"/>
+      <c r="C42" s="5"/>
+      <c r="D42" s="5"/>
+      <c r="E42" s="5"/>
+      <c r="F42" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G42" s="5"/>
+      <c r="H42" s="5"/>
+      <c r="I42" s="5" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="43" ht="25" customHeight="1" spans="1:9">
-      <c r="A43" s="17" t="s">
+      <c r="A43" s="12" t="s">
         <v>202</v>
       </c>
-      <c r="B43" s="6"/>
-      <c r="C43" s="6"/>
-      <c r="D43" s="6"/>
-      <c r="E43" s="6"/>
-      <c r="F43" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G43" s="6"/>
-      <c r="H43" s="6"/>
-      <c r="I43" s="6" t="s">
+      <c r="B43" s="5"/>
+      <c r="C43" s="5"/>
+      <c r="D43" s="5"/>
+      <c r="E43" s="5"/>
+      <c r="F43" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G43" s="5"/>
+      <c r="H43" s="5"/>
+      <c r="I43" s="5" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="44" ht="25" customHeight="1" spans="1:9">
-      <c r="A44" s="17" t="s">
+      <c r="A44" s="12" t="s">
         <v>204</v>
       </c>
-      <c r="B44" s="6"/>
-      <c r="C44" s="6"/>
-      <c r="D44" s="6"/>
-      <c r="E44" s="6"/>
-      <c r="F44" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G44" s="6"/>
-      <c r="H44" s="6"/>
-      <c r="I44" s="6" t="s">
+      <c r="B44" s="5"/>
+      <c r="C44" s="5"/>
+      <c r="D44" s="5"/>
+      <c r="E44" s="5"/>
+      <c r="F44" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G44" s="5"/>
+      <c r="H44" s="5"/>
+      <c r="I44" s="5" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="45" ht="25" customHeight="1" spans="1:9">
-      <c r="A45" s="17" t="s">
+      <c r="A45" s="12" t="s">
         <v>206</v>
       </c>
-      <c r="B45" s="6"/>
-      <c r="C45" s="6"/>
-      <c r="D45" s="6"/>
-      <c r="E45" s="6"/>
-      <c r="F45" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G45" s="6"/>
-      <c r="H45" s="6"/>
-      <c r="I45" s="6" t="s">
+      <c r="B45" s="5"/>
+      <c r="C45" s="5"/>
+      <c r="D45" s="5"/>
+      <c r="E45" s="5"/>
+      <c r="F45" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G45" s="5"/>
+      <c r="H45" s="5"/>
+      <c r="I45" s="5" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="46" ht="25" customHeight="1" spans="1:9">
-      <c r="A46" s="20" t="s">
+      <c r="A46" s="14" t="s">
         <v>208</v>
       </c>
-      <c r="B46" s="21"/>
-      <c r="C46" s="21"/>
-      <c r="D46" s="21"/>
-      <c r="E46" s="21"/>
-      <c r="F46" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G46" s="21"/>
-      <c r="H46" s="21"/>
-      <c r="I46" s="22" t="s">
+      <c r="B46" s="15"/>
+      <c r="C46" s="15"/>
+      <c r="D46" s="15"/>
+      <c r="E46" s="15"/>
+      <c r="F46" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G46" s="15"/>
+      <c r="H46" s="15"/>
+      <c r="I46" s="16" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="47" ht="25" customHeight="1" spans="1:9">
-      <c r="A47" s="17" t="s">
+      <c r="A47" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="B47" s="6"/>
-      <c r="C47" s="6"/>
-      <c r="D47" s="6"/>
-      <c r="E47" s="6"/>
-      <c r="F47" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G47" s="6"/>
-      <c r="H47" s="6"/>
-      <c r="I47" s="6" t="s">
+      <c r="B47" s="5"/>
+      <c r="C47" s="5"/>
+      <c r="D47" s="5"/>
+      <c r="E47" s="5"/>
+      <c r="F47" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G47" s="5"/>
+      <c r="H47" s="5"/>
+      <c r="I47" s="5" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="48" ht="25" customHeight="1" spans="1:9">
-      <c r="A48" s="17" t="s">
+      <c r="A48" s="12" t="s">
         <v>212</v>
       </c>
-      <c r="B48" s="6"/>
-      <c r="C48" s="6"/>
-      <c r="D48" s="6"/>
-      <c r="E48" s="6"/>
-      <c r="F48" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G48" s="6"/>
-      <c r="H48" s="6"/>
-      <c r="I48" s="6" t="s">
+      <c r="B48" s="5"/>
+      <c r="C48" s="5"/>
+      <c r="D48" s="5"/>
+      <c r="E48" s="5"/>
+      <c r="F48" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G48" s="5"/>
+      <c r="H48" s="5"/>
+      <c r="I48" s="5" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="49" ht="25" customHeight="1" spans="1:9">
-      <c r="A49" s="17" t="s">
+      <c r="A49" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="B49" s="6"/>
-      <c r="C49" s="6"/>
-      <c r="D49" s="6"/>
-      <c r="E49" s="6"/>
-      <c r="F49" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G49" s="6"/>
-      <c r="H49" s="6"/>
-      <c r="I49" s="6" t="s">
+      <c r="B49" s="5"/>
+      <c r="C49" s="5"/>
+      <c r="D49" s="5"/>
+      <c r="E49" s="5"/>
+      <c r="F49" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G49" s="5"/>
+      <c r="H49" s="5"/>
+      <c r="I49" s="5" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="50" ht="25" customHeight="1" spans="1:9">
-      <c r="A50" s="17" t="s">
+      <c r="A50" s="12" t="s">
         <v>216</v>
       </c>
-      <c r="B50" s="6"/>
-      <c r="C50" s="6"/>
-      <c r="D50" s="6"/>
-      <c r="E50" s="6"/>
-      <c r="F50" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G50" s="6"/>
-      <c r="H50" s="6"/>
-      <c r="I50" s="6" t="s">
+      <c r="B50" s="5"/>
+      <c r="C50" s="5"/>
+      <c r="D50" s="5"/>
+      <c r="E50" s="5"/>
+      <c r="F50" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G50" s="5"/>
+      <c r="H50" s="5"/>
+      <c r="I50" s="5" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="51" ht="25" customHeight="1" spans="1:9">
-      <c r="A51" s="17" t="s">
+      <c r="A51" s="12" t="s">
         <v>218</v>
       </c>
-      <c r="B51" s="6"/>
-      <c r="C51" s="6"/>
-      <c r="D51" s="6"/>
-      <c r="E51" s="6"/>
-      <c r="F51" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G51" s="6"/>
-      <c r="H51" s="6"/>
-      <c r="I51" s="6" t="s">
+      <c r="B51" s="5"/>
+      <c r="C51" s="5"/>
+      <c r="D51" s="5"/>
+      <c r="E51" s="5"/>
+      <c r="F51" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G51" s="5"/>
+      <c r="H51" s="5"/>
+      <c r="I51" s="5" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="52" ht="25" customHeight="1" spans="1:9">
-      <c r="A52" s="17" t="s">
+      <c r="A52" s="12" t="s">
         <v>220</v>
       </c>
-      <c r="B52" s="6"/>
-      <c r="C52" s="6"/>
-      <c r="D52" s="6"/>
-      <c r="E52" s="6"/>
-      <c r="F52" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G52" s="6"/>
-      <c r="H52" s="6"/>
-      <c r="I52" s="6" t="s">
+      <c r="B52" s="5"/>
+      <c r="C52" s="5"/>
+      <c r="D52" s="5"/>
+      <c r="E52" s="5"/>
+      <c r="F52" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G52" s="5"/>
+      <c r="H52" s="5"/>
+      <c r="I52" s="5" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="53" customFormat="1" ht="25" customHeight="1" spans="1:9">
-      <c r="A53" s="17" t="s">
+      <c r="A53" s="12" t="s">
         <v>236</v>
       </c>
-      <c r="B53" s="6" t="s">
+      <c r="B53" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C53" s="23" t="s">
+      <c r="C53" s="17" t="s">
         <v>237</v>
       </c>
-      <c r="D53" s="6"/>
-      <c r="E53" s="6" t="s">
+      <c r="D53" s="5"/>
+      <c r="E53" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="F53" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G53" s="6"/>
-      <c r="H53" s="24" t="s">
+      <c r="F53" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G53" s="5"/>
+      <c r="H53" s="18" t="s">
         <v>239</v>
       </c>
-      <c r="I53" s="6" t="s">
+      <c r="I53" s="5" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="54" customFormat="1" ht="25" customHeight="1" spans="1:9">
-      <c r="A54" s="17" t="s">
+      <c r="A54" s="12" t="s">
         <v>241</v>
       </c>
-      <c r="B54" s="6" t="s">
+      <c r="B54" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="C54" s="23" t="s">
+      <c r="C54" s="17" t="s">
         <v>242</v>
       </c>
-      <c r="D54" s="6"/>
-      <c r="E54" s="6" t="s">
+      <c r="D54" s="5"/>
+      <c r="E54" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="F54" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G54" s="6"/>
-      <c r="H54" s="24" t="s">
+      <c r="F54" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G54" s="5"/>
+      <c r="H54" s="18" t="s">
         <v>243</v>
       </c>
-      <c r="I54" s="6" t="s">
+      <c r="I54" s="5" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="55" customFormat="1" ht="25" customHeight="1" spans="1:9">
-      <c r="A55" s="17" t="s">
+      <c r="A55" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="B55" s="6" t="s">
+      <c r="B55" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C55" s="25" t="s">
+      <c r="C55" s="19" t="s">
         <v>246</v>
       </c>
-      <c r="D55" s="6"/>
-      <c r="E55" s="6" t="s">
+      <c r="D55" s="5"/>
+      <c r="E55" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="F55" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G55" s="6"/>
-      <c r="H55" s="24" t="s">
+      <c r="F55" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G55" s="5"/>
+      <c r="H55" s="18" t="s">
         <v>266</v>
       </c>
-      <c r="I55" s="6" t="s">
+      <c r="I55" s="5" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="56" ht="25" customHeight="1" spans="1:9">
-      <c r="A56" s="17" t="s">
+      <c r="A56" s="12" t="s">
         <v>249</v>
       </c>
-      <c r="B56" s="6" t="s">
+      <c r="B56" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C56" s="23" t="s">
+      <c r="C56" s="17" t="s">
         <v>250</v>
       </c>
-      <c r="D56" s="6"/>
-      <c r="E56" s="6" t="s">
+      <c r="D56" s="5"/>
+      <c r="E56" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="F56" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G56" s="6"/>
-      <c r="H56" s="24" t="s">
+      <c r="F56" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G56" s="5"/>
+      <c r="H56" s="18" t="s">
         <v>267</v>
       </c>
-      <c r="I56" s="6" t="s">
+      <c r="I56" s="5" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="57" ht="25" customHeight="1" spans="1:9">
-      <c r="A57" s="17" t="s">
+      <c r="A57" s="12" t="s">
         <v>254</v>
       </c>
-      <c r="B57" s="6" t="s">
+      <c r="B57" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C57" s="23" t="s">
+      <c r="C57" s="17" t="s">
         <v>255</v>
       </c>
-      <c r="D57" s="6"/>
-      <c r="E57" s="6" t="s">
+      <c r="D57" s="5"/>
+      <c r="E57" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="F57" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G57" s="6"/>
-      <c r="H57" s="24" t="s">
+      <c r="F57" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G57" s="5"/>
+      <c r="H57" s="18" t="s">
         <v>268</v>
       </c>
-      <c r="I57" s="6" t="s">
+      <c r="I57" s="5" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="58" ht="25" customHeight="1" spans="1:9">
-      <c r="A58" s="17" t="s">
+      <c r="A58" s="12" t="s">
         <v>258</v>
       </c>
-      <c r="B58" s="6" t="s">
+      <c r="B58" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C58" s="23" t="s">
+      <c r="C58" s="17" t="s">
         <v>259</v>
       </c>
-      <c r="D58" s="6"/>
-      <c r="E58" s="6" t="s">
+      <c r="D58" s="5"/>
+      <c r="E58" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="F58" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G58" s="6"/>
-      <c r="H58" s="24" t="s">
+      <c r="F58" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G58" s="5"/>
+      <c r="H58" s="18" t="s">
         <v>269</v>
       </c>
-      <c r="I58" s="6" t="s">
+      <c r="I58" s="5" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="59" ht="25" customHeight="1" spans="1:9">
-      <c r="A59" s="17" t="s">
+      <c r="A59" s="12" t="s">
         <v>222</v>
       </c>
-      <c r="B59" s="6"/>
-      <c r="C59" s="6"/>
-      <c r="D59" s="6"/>
-      <c r="E59" s="6"/>
-      <c r="F59" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G59" s="6"/>
-      <c r="H59" s="6"/>
-      <c r="I59" s="6" t="s">
+      <c r="B59" s="5"/>
+      <c r="C59" s="5"/>
+      <c r="D59" s="5"/>
+      <c r="E59" s="5"/>
+      <c r="F59" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G59" s="5"/>
+      <c r="H59" s="5"/>
+      <c r="I59" s="5" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="60" ht="25" customHeight="1" spans="1:9">
-      <c r="A60" s="17" t="s">
+      <c r="A60" s="12" t="s">
         <v>224</v>
       </c>
-      <c r="B60" s="6"/>
-      <c r="C60" s="6"/>
-      <c r="D60" s="6"/>
-      <c r="E60" s="6"/>
-      <c r="F60" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G60" s="6"/>
-      <c r="H60" s="6"/>
-      <c r="I60" s="6" t="s">
+      <c r="B60" s="5"/>
+      <c r="C60" s="5"/>
+      <c r="D60" s="5"/>
+      <c r="E60" s="5"/>
+      <c r="F60" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G60" s="5"/>
+      <c r="H60" s="5"/>
+      <c r="I60" s="5" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="61" ht="25" customHeight="1" spans="1:9">
-      <c r="A61" s="17" t="s">
+      <c r="A61" s="12" t="s">
         <v>226</v>
       </c>
-      <c r="B61" s="6"/>
-      <c r="C61" s="6"/>
-      <c r="D61" s="6"/>
-      <c r="E61" s="6"/>
-      <c r="F61" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G61" s="6"/>
-      <c r="H61" s="6"/>
-      <c r="I61" s="6" t="s">
+      <c r="B61" s="5"/>
+      <c r="C61" s="5"/>
+      <c r="D61" s="5"/>
+      <c r="E61" s="5"/>
+      <c r="F61" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G61" s="5"/>
+      <c r="H61" s="5"/>
+      <c r="I61" s="5" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="62" customFormat="1" ht="25" customHeight="1" spans="1:9">
-      <c r="A62" s="17" t="s">
+      <c r="A62" s="12" t="s">
         <v>228</v>
       </c>
-      <c r="B62" s="6"/>
-      <c r="C62" s="6"/>
-      <c r="D62" s="6"/>
-      <c r="E62" s="6"/>
-      <c r="F62" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G62" s="6"/>
-      <c r="H62" s="6"/>
-      <c r="I62" s="6" t="s">
+      <c r="B62" s="5"/>
+      <c r="C62" s="5"/>
+      <c r="D62" s="5"/>
+      <c r="E62" s="5"/>
+      <c r="F62" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G62" s="5"/>
+      <c r="H62" s="5"/>
+      <c r="I62" s="5" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="63" customFormat="1" ht="25" customHeight="1" spans="1:9">
-      <c r="A63" s="17" t="s">
+      <c r="A63" s="12" t="s">
         <v>230</v>
       </c>
-      <c r="B63" s="6"/>
-      <c r="C63" s="6"/>
-      <c r="D63" s="6"/>
-      <c r="E63" s="6"/>
-      <c r="F63" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G63" s="6"/>
-      <c r="H63" s="6"/>
-      <c r="I63" s="6" t="s">
+      <c r="B63" s="5"/>
+      <c r="C63" s="5"/>
+      <c r="D63" s="5"/>
+      <c r="E63" s="5"/>
+      <c r="F63" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G63" s="5"/>
+      <c r="H63" s="5"/>
+      <c r="I63" s="5" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="64" customFormat="1" ht="25" customHeight="1" spans="1:9">
-      <c r="A64" s="17" t="s">
+      <c r="A64" s="12" t="s">
         <v>232</v>
       </c>
-      <c r="B64" s="6"/>
-      <c r="C64" s="6"/>
-      <c r="D64" s="6"/>
-      <c r="E64" s="6"/>
-      <c r="F64" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G64" s="6"/>
-      <c r="H64" s="6"/>
-      <c r="I64" s="6" t="s">
+      <c r="B64" s="5"/>
+      <c r="C64" s="5"/>
+      <c r="D64" s="5"/>
+      <c r="E64" s="5"/>
+      <c r="F64" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G64" s="5"/>
+      <c r="H64" s="5"/>
+      <c r="I64" s="5" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="65" customFormat="1" ht="25" customHeight="1" spans="1:9">
-      <c r="A65" s="17" t="s">
+      <c r="A65" s="12" t="s">
         <v>234</v>
       </c>
-      <c r="B65" s="6"/>
-      <c r="C65" s="6"/>
-      <c r="D65" s="6"/>
-      <c r="E65" s="6"/>
-      <c r="F65" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G65" s="6"/>
-      <c r="H65" s="6"/>
-      <c r="I65" s="6" t="s">
+      <c r="B65" s="5"/>
+      <c r="C65" s="5"/>
+      <c r="D65" s="5"/>
+      <c r="E65" s="5"/>
+      <c r="F65" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G65" s="5"/>
+      <c r="H65" s="5"/>
+      <c r="I65" s="5" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="66" ht="25" customHeight="1" spans="1:9">
-      <c r="A66" s="17"/>
-      <c r="B66" s="6"/>
-      <c r="C66" s="6"/>
-      <c r="D66" s="6"/>
-      <c r="E66" s="6"/>
-      <c r="F66" s="18"/>
-      <c r="G66" s="6"/>
-      <c r="H66" s="6"/>
-      <c r="I66" s="6"/>
+      <c r="A66" s="12"/>
+      <c r="B66" s="5"/>
+      <c r="C66" s="5"/>
+      <c r="D66" s="5"/>
+      <c r="E66" s="5"/>
+      <c r="F66" s="13"/>
+      <c r="G66" s="5"/>
+      <c r="H66" s="5"/>
+      <c r="I66" s="5"/>
     </row>
     <row r="67" ht="25" customHeight="1" spans="1:9">
-      <c r="A67" s="17"/>
-      <c r="B67" s="6"/>
-      <c r="C67" s="6"/>
-      <c r="D67" s="6"/>
-      <c r="E67" s="6"/>
-      <c r="F67" s="18"/>
-      <c r="G67" s="6"/>
-      <c r="H67" s="6"/>
-      <c r="I67" s="6"/>
+      <c r="A67" s="12"/>
+      <c r="B67" s="5"/>
+      <c r="C67" s="5"/>
+      <c r="D67" s="5"/>
+      <c r="E67" s="5"/>
+      <c r="F67" s="13"/>
+      <c r="G67" s="5"/>
+      <c r="H67" s="5"/>
+      <c r="I67" s="5"/>
     </row>
     <row r="68" ht="25" customHeight="1" spans="1:9">
-      <c r="A68" s="17"/>
-      <c r="B68" s="6"/>
-      <c r="C68" s="6"/>
-      <c r="D68" s="6"/>
-      <c r="E68" s="6"/>
-      <c r="F68" s="18"/>
-      <c r="G68" s="6"/>
-      <c r="H68" s="6"/>
-      <c r="I68" s="6"/>
+      <c r="A68" s="12"/>
+      <c r="B68" s="5"/>
+      <c r="C68" s="5"/>
+      <c r="D68" s="5"/>
+      <c r="E68" s="5"/>
+      <c r="F68" s="13"/>
+      <c r="G68" s="5"/>
+      <c r="H68" s="5"/>
+      <c r="I68" s="5"/>
     </row>
     <row r="69" ht="25" customHeight="1" spans="1:9">
-      <c r="A69" s="17"/>
-      <c r="B69" s="6"/>
-      <c r="C69" s="6"/>
-      <c r="D69" s="6"/>
-      <c r="E69" s="6"/>
-      <c r="F69" s="18"/>
-      <c r="G69" s="6"/>
-      <c r="H69" s="6"/>
-      <c r="I69" s="6"/>
+      <c r="A69" s="12"/>
+      <c r="B69" s="5"/>
+      <c r="C69" s="5"/>
+      <c r="D69" s="5"/>
+      <c r="E69" s="5"/>
+      <c r="F69" s="13"/>
+      <c r="G69" s="5"/>
+      <c r="H69" s="5"/>
+      <c r="I69" s="5"/>
     </row>
     <row r="70" ht="25" customHeight="1" spans="1:9">
-      <c r="A70" s="17"/>
-      <c r="B70" s="6"/>
-      <c r="C70" s="6"/>
-      <c r="D70" s="6"/>
-      <c r="E70" s="6"/>
-      <c r="F70" s="18"/>
-      <c r="G70" s="6"/>
-      <c r="H70" s="6"/>
-      <c r="I70" s="6"/>
+      <c r="A70" s="12"/>
+      <c r="B70" s="5"/>
+      <c r="C70" s="5"/>
+      <c r="D70" s="5"/>
+      <c r="E70" s="5"/>
+      <c r="F70" s="13"/>
+      <c r="G70" s="5"/>
+      <c r="H70" s="5"/>
+      <c r="I70" s="5"/>
     </row>
     <row r="71" ht="25" customHeight="1" spans="1:9">
-      <c r="A71" s="17"/>
-      <c r="B71" s="6"/>
-      <c r="C71" s="6"/>
-      <c r="D71" s="6"/>
-      <c r="E71" s="6"/>
-      <c r="F71" s="18"/>
-      <c r="G71" s="6"/>
-      <c r="H71" s="6"/>
-      <c r="I71" s="6"/>
+      <c r="A71" s="12"/>
+      <c r="B71" s="5"/>
+      <c r="C71" s="5"/>
+      <c r="D71" s="5"/>
+      <c r="E71" s="5"/>
+      <c r="F71" s="13"/>
+      <c r="G71" s="5"/>
+      <c r="H71" s="5"/>
+      <c r="I71" s="5"/>
     </row>
     <row r="72" ht="25" customHeight="1" spans="1:9">
-      <c r="A72" s="17"/>
-      <c r="B72" s="6"/>
-      <c r="C72" s="6"/>
-      <c r="D72" s="6"/>
-      <c r="E72" s="6"/>
-      <c r="F72" s="18"/>
-      <c r="G72" s="6"/>
-      <c r="H72" s="6"/>
-      <c r="I72" s="6"/>
+      <c r="A72" s="12"/>
+      <c r="B72" s="5"/>
+      <c r="C72" s="5"/>
+      <c r="D72" s="5"/>
+      <c r="E72" s="5"/>
+      <c r="F72" s="13"/>
+      <c r="G72" s="5"/>
+      <c r="H72" s="5"/>
+      <c r="I72" s="5"/>
     </row>
     <row r="73" ht="25" customHeight="1" spans="1:9">
-      <c r="A73" s="17"/>
-      <c r="B73" s="6"/>
-      <c r="C73" s="6"/>
-      <c r="D73" s="6"/>
-      <c r="E73" s="6"/>
-      <c r="F73" s="18"/>
-      <c r="G73" s="6"/>
-      <c r="H73" s="6"/>
-      <c r="I73" s="6"/>
+      <c r="A73" s="12"/>
+      <c r="B73" s="5"/>
+      <c r="C73" s="5"/>
+      <c r="D73" s="5"/>
+      <c r="E73" s="5"/>
+      <c r="F73" s="13"/>
+      <c r="G73" s="5"/>
+      <c r="H73" s="5"/>
+      <c r="I73" s="5"/>
     </row>
     <row r="74" ht="25" customHeight="1" spans="1:9">
-      <c r="A74" s="17"/>
-      <c r="B74" s="6"/>
-      <c r="C74" s="6"/>
-      <c r="D74" s="6"/>
-      <c r="E74" s="6"/>
-      <c r="F74" s="18"/>
-      <c r="G74" s="6"/>
-      <c r="H74" s="6"/>
-      <c r="I74" s="6"/>
+      <c r="A74" s="12"/>
+      <c r="B74" s="5"/>
+      <c r="C74" s="5"/>
+      <c r="D74" s="5"/>
+      <c r="E74" s="5"/>
+      <c r="F74" s="13"/>
+      <c r="G74" s="5"/>
+      <c r="H74" s="5"/>
+      <c r="I74" s="5"/>
     </row>
     <row r="75" ht="25" customHeight="1" spans="1:9">
-      <c r="A75" s="17"/>
-      <c r="B75" s="6"/>
-      <c r="C75" s="6"/>
-      <c r="D75" s="6"/>
-      <c r="E75" s="6"/>
-      <c r="F75" s="18"/>
-      <c r="G75" s="6"/>
-      <c r="H75" s="6"/>
-      <c r="I75" s="6"/>
+      <c r="A75" s="12"/>
+      <c r="B75" s="5"/>
+      <c r="C75" s="5"/>
+      <c r="D75" s="5"/>
+      <c r="E75" s="5"/>
+      <c r="F75" s="13"/>
+      <c r="G75" s="5"/>
+      <c r="H75" s="5"/>
+      <c r="I75" s="5"/>
     </row>
     <row r="76" ht="25" customHeight="1" spans="1:9">
-      <c r="A76" s="17"/>
-      <c r="B76" s="6"/>
-      <c r="C76" s="6"/>
-      <c r="D76" s="6"/>
-      <c r="E76" s="6"/>
-      <c r="F76" s="18"/>
-      <c r="G76" s="6"/>
-      <c r="H76" s="6"/>
-      <c r="I76" s="6"/>
+      <c r="A76" s="12"/>
+      <c r="B76" s="5"/>
+      <c r="C76" s="5"/>
+      <c r="D76" s="5"/>
+      <c r="E76" s="5"/>
+      <c r="F76" s="13"/>
+      <c r="G76" s="5"/>
+      <c r="H76" s="5"/>
+      <c r="I76" s="5"/>
     </row>
     <row r="77" ht="25" customHeight="1" spans="1:9">
-      <c r="A77" s="17"/>
-      <c r="B77" s="6"/>
-      <c r="C77" s="6"/>
-      <c r="D77" s="6"/>
-      <c r="E77" s="6"/>
-      <c r="F77" s="18"/>
-      <c r="G77" s="6"/>
-      <c r="H77" s="6"/>
-      <c r="I77" s="6"/>
+      <c r="A77" s="12"/>
+      <c r="B77" s="5"/>
+      <c r="C77" s="5"/>
+      <c r="D77" s="5"/>
+      <c r="E77" s="5"/>
+      <c r="F77" s="13"/>
+      <c r="G77" s="5"/>
+      <c r="H77" s="5"/>
+      <c r="I77" s="5"/>
     </row>
     <row r="78" ht="25" customHeight="1" spans="1:9">
-      <c r="A78" s="17"/>
-      <c r="B78" s="6"/>
-      <c r="C78" s="6"/>
-      <c r="D78" s="6"/>
-      <c r="E78" s="6"/>
-      <c r="F78" s="18"/>
-      <c r="G78" s="6"/>
-      <c r="H78" s="6"/>
-      <c r="I78" s="6"/>
+      <c r="A78" s="12"/>
+      <c r="B78" s="5"/>
+      <c r="C78" s="5"/>
+      <c r="D78" s="5"/>
+      <c r="E78" s="5"/>
+      <c r="F78" s="13"/>
+      <c r="G78" s="5"/>
+      <c r="H78" s="5"/>
+      <c r="I78" s="5"/>
     </row>
     <row r="79" ht="25" customHeight="1" spans="1:9">
-      <c r="A79" s="17"/>
-      <c r="B79" s="6"/>
-      <c r="C79" s="6"/>
-      <c r="D79" s="6"/>
-      <c r="E79" s="6"/>
-      <c r="F79" s="18"/>
-      <c r="G79" s="6"/>
-      <c r="H79" s="6"/>
-      <c r="I79" s="6"/>
+      <c r="A79" s="12"/>
+      <c r="B79" s="5"/>
+      <c r="C79" s="5"/>
+      <c r="D79" s="5"/>
+      <c r="E79" s="5"/>
+      <c r="F79" s="13"/>
+      <c r="G79" s="5"/>
+      <c r="H79" s="5"/>
+      <c r="I79" s="5"/>
     </row>
     <row r="80" ht="25" customHeight="1" spans="1:9">
-      <c r="A80" s="17"/>
-      <c r="B80" s="6"/>
-      <c r="C80" s="6"/>
-      <c r="D80" s="6"/>
-      <c r="E80" s="6"/>
-      <c r="F80" s="18"/>
-      <c r="G80" s="6"/>
-      <c r="H80" s="6"/>
-      <c r="I80" s="6"/>
+      <c r="A80" s="12"/>
+      <c r="B80" s="5"/>
+      <c r="C80" s="5"/>
+      <c r="D80" s="5"/>
+      <c r="E80" s="5"/>
+      <c r="F80" s="13"/>
+      <c r="G80" s="5"/>
+      <c r="H80" s="5"/>
+      <c r="I80" s="5"/>
     </row>
     <row r="81" ht="25" customHeight="1" spans="1:9">
-      <c r="A81" s="17"/>
-      <c r="B81" s="6"/>
-      <c r="C81" s="6"/>
-      <c r="D81" s="6"/>
-      <c r="E81" s="6"/>
-      <c r="F81" s="18"/>
-      <c r="G81" s="6"/>
-      <c r="H81" s="6"/>
-      <c r="I81" s="6"/>
+      <c r="A81" s="12"/>
+      <c r="B81" s="5"/>
+      <c r="C81" s="5"/>
+      <c r="D81" s="5"/>
+      <c r="E81" s="5"/>
+      <c r="F81" s="13"/>
+      <c r="G81" s="5"/>
+      <c r="H81" s="5"/>
+      <c r="I81" s="5"/>
     </row>
     <row r="82" ht="25" customHeight="1" spans="1:9">
-      <c r="A82" s="17"/>
-      <c r="B82" s="6"/>
-      <c r="C82" s="6"/>
-      <c r="D82" s="6"/>
-      <c r="E82" s="6"/>
-      <c r="F82" s="18"/>
-      <c r="G82" s="6"/>
-      <c r="H82" s="6"/>
-      <c r="I82" s="6"/>
+      <c r="A82" s="12"/>
+      <c r="B82" s="5"/>
+      <c r="C82" s="5"/>
+      <c r="D82" s="5"/>
+      <c r="E82" s="5"/>
+      <c r="F82" s="13"/>
+      <c r="G82" s="5"/>
+      <c r="H82" s="5"/>
+      <c r="I82" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/资源录入表新.xlsx
+++ b/资源录入表新.xlsx
@@ -16,7 +16,7 @@
     <sheet name="资源录入表 (2)" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">资源录入表!$A$1:$O$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">资源录入表!$A$1:$O$65</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'资源录入表 (2)'!$A$2:$I$20</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="825" uniqueCount="274">
   <si>
     <t>剧名</t>
   </si>
@@ -142,6 +142,56 @@
   </si>
   <si>
     <t xml:space="preserve">链接: https://pan.baidu.com/s/1C11-1DhDULL7qOeytJ9LTw 提取码: fp76 </t>
+  </si>
+  <si>
+    <t>昭阳公主</t>
+  </si>
+  <si>
+    <r>
+      <t>剧情</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF111111"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>爱情</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF111111"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>古装</t>
+    </r>
+  </si>
+  <si>
+    <t>李宏毅/孔雪儿/刘旭威/林小宅</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1C1Dpxyv71CYv6Y7P5TvTDg 提取码: z3ta </t>
   </si>
   <si>
     <t>李熊猫</t>
@@ -1074,7 +1124,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="34">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1123,6 +1173,12 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF111111"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1272,6 +1328,12 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="Helvetica"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF111111"/>
       <name val="Helvetica"/>
       <charset val="134"/>
     </font>
@@ -1663,137 +1725,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1854,13 +1916,31 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2453,210 +2533,210 @@
       <c r="N1" s="5"/>
       <c r="O1" s="5"/>
     </row>
-    <row r="2" ht="25" customHeight="1" spans="1:15">
-      <c r="A2" s="20" t="s">
+    <row r="2" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A2" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="22" t="s">
         <v>14</v>
       </c>
       <c r="E2" s="8">
-        <v>4</v>
-      </c>
-      <c r="F2" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="8">
+      <c r="G2" s="22">
         <v>2026</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-    </row>
-    <row r="3" ht="25" customHeight="1" spans="1:15">
-      <c r="A3" s="20" t="s">
+      <c r="J2" s="23"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="23"/>
+      <c r="M2" s="23"/>
+      <c r="N2" s="23"/>
+      <c r="O2" s="23"/>
+    </row>
+    <row r="3" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A3" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="22" t="s">
         <v>14</v>
       </c>
       <c r="E3" s="8">
-        <v>8</v>
-      </c>
-      <c r="F3" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="8">
+      <c r="G3" s="22">
         <v>2026</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
-    </row>
-    <row r="4" ht="25" customHeight="1" spans="1:15">
-      <c r="A4" s="20" t="s">
+      <c r="J3" s="23"/>
+      <c r="K3" s="23"/>
+      <c r="L3" s="23"/>
+      <c r="M3" s="23"/>
+      <c r="N3" s="23"/>
+      <c r="O3" s="23"/>
+    </row>
+    <row r="4" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A4" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="22" t="s">
         <v>14</v>
       </c>
       <c r="E4" s="8">
-        <v>23</v>
-      </c>
-      <c r="F4" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="8">
+      <c r="G4" s="22">
         <v>2026</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="I4" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5" t="s">
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-    </row>
-    <row r="5" ht="25" customHeight="1" spans="1:15">
-      <c r="A5" s="20" t="s">
+      <c r="M4" s="23"/>
+      <c r="N4" s="23"/>
+      <c r="O4" s="23"/>
+    </row>
+    <row r="5" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A5" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="22" t="s">
         <v>14</v>
       </c>
       <c r="E5" s="8">
-        <v>18</v>
-      </c>
-      <c r="F5" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="8">
+      <c r="G5" s="22">
         <v>2026</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="H5" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="I5" s="8" t="s">
+      <c r="I5" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
-    </row>
-    <row r="6" ht="25" customHeight="1" spans="1:15">
-      <c r="A6" s="20" t="s">
+      <c r="J5" s="23"/>
+      <c r="K5" s="23"/>
+      <c r="L5" s="23"/>
+      <c r="M5" s="23"/>
+      <c r="N5" s="23"/>
+      <c r="O5" s="23"/>
+    </row>
+    <row r="6" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A6" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="22" t="s">
         <v>14</v>
       </c>
       <c r="E6" s="8">
         <v>20</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="22">
         <v>2026</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="H6" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="I6" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="5"/>
-      <c r="O6" s="5"/>
+      <c r="J6" s="23"/>
+      <c r="K6" s="23"/>
+      <c r="L6" s="23"/>
+      <c r="M6" s="23"/>
+      <c r="N6" s="23"/>
+      <c r="O6" s="23"/>
     </row>
     <row r="7" ht="25" customHeight="1" spans="1:15">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="D7" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="11">
+        <v>14</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="5">
+        <v>2026</v>
+      </c>
+      <c r="H7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="8">
-        <v>3</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7" s="8">
-        <v>2026</v>
-      </c>
-      <c r="H7" s="8" t="s">
+      <c r="I7" s="5" t="s">
         <v>38</v>
-      </c>
-      <c r="I7" s="8" t="s">
-        <v>39</v>
       </c>
       <c r="J7" s="5"/>
       <c r="K7" s="5"/>
@@ -2665,497 +2745,495 @@
       <c r="N7" s="5"/>
       <c r="O7" s="5"/>
     </row>
-    <row r="8" ht="25" customHeight="1" spans="1:15">
-      <c r="A8" s="20" t="s">
+    <row r="8" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A8" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="D8" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="8">
+      <c r="D8" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="22">
+        <v>3</v>
+      </c>
+      <c r="F8" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" s="22">
+        <v>2026</v>
+      </c>
+      <c r="H8" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="I8" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="J8" s="23"/>
+      <c r="K8" s="23"/>
+      <c r="L8" s="23"/>
+      <c r="M8" s="23"/>
+      <c r="N8" s="23"/>
+      <c r="O8" s="23"/>
+    </row>
+    <row r="9" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A9" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="22">
         <v>4</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F9" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G9" s="22">
         <v>2026</v>
       </c>
-      <c r="H8" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
-      <c r="M8" s="5"/>
-      <c r="N8" s="5"/>
-      <c r="O8" s="5"/>
-    </row>
-    <row r="9" ht="25" customHeight="1" spans="1:15">
-      <c r="A9" s="20" t="s">
-        <v>44</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="C9" s="8" t="s">
+      <c r="H9" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="D9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" s="8">
+      <c r="I9" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="J9" s="23"/>
+      <c r="K9" s="23"/>
+      <c r="L9" s="23"/>
+      <c r="M9" s="23"/>
+      <c r="N9" s="23"/>
+      <c r="O9" s="23"/>
+    </row>
+    <row r="10" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A10" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="B10" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="22">
         <v>6</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F10" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G10" s="22">
         <v>2026</v>
       </c>
-      <c r="H9" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="M9" s="5"/>
-      <c r="N9" s="5"/>
-      <c r="O9" s="5"/>
-    </row>
-    <row r="10" ht="25" customHeight="1" spans="1:15">
-      <c r="A10" s="20" t="s">
+      <c r="H10" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="I10" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="J10" s="23"/>
+      <c r="K10" s="23"/>
+      <c r="L10" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="M10" s="23"/>
+      <c r="N10" s="23"/>
+      <c r="O10" s="23"/>
+    </row>
+    <row r="11" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A11" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="B11" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="22">
+        <v>6</v>
+      </c>
+      <c r="F11" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" s="22">
+        <v>2026</v>
+      </c>
+      <c r="H11" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="I11" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="J11" s="23"/>
+      <c r="K11" s="23"/>
+      <c r="L11" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="M11" s="23"/>
+      <c r="N11" s="23"/>
+      <c r="O11" s="23"/>
+    </row>
+    <row r="12" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A12" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="B12" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="C12" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="C10" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="8">
+      <c r="D12" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="22">
+        <v>4</v>
+      </c>
+      <c r="F12" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="22">
+        <v>2026</v>
+      </c>
+      <c r="H12" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="I12" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="J12" s="23"/>
+      <c r="K12" s="23"/>
+      <c r="L12" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="M12" s="23"/>
+      <c r="N12" s="23"/>
+      <c r="O12" s="23"/>
+    </row>
+    <row r="13" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A13" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="D13" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="22">
         <v>6</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="F13" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="G10" s="8">
+      <c r="G13" s="22">
         <v>2026</v>
       </c>
-      <c r="H10" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="I10" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
-      <c r="L10" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="M10" s="5"/>
-      <c r="N10" s="5"/>
-      <c r="O10" s="5"/>
-    </row>
-    <row r="11" ht="25" customHeight="1" spans="1:15">
-      <c r="A11" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="8">
+      <c r="H13" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="I13" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="J13" s="23"/>
+      <c r="K13" s="23"/>
+      <c r="L13" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="M13" s="23"/>
+      <c r="N13" s="23"/>
+      <c r="O13" s="23"/>
+    </row>
+    <row r="14" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A14" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="B14" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" s="22">
+        <v>8</v>
+      </c>
+      <c r="F14" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14" s="22">
+        <v>2026</v>
+      </c>
+      <c r="H14" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="I14" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="J14" s="23"/>
+      <c r="K14" s="23"/>
+      <c r="L14" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="M14" s="23"/>
+      <c r="N14" s="23"/>
+      <c r="O14" s="23"/>
+    </row>
+    <row r="15" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A15" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="B15" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="D15" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" s="22">
         <v>4</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="F15" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="G11" s="8">
+      <c r="G15" s="22">
         <v>2026</v>
       </c>
-      <c r="H11" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="I11" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5"/>
-      <c r="L11" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="M11" s="5"/>
-      <c r="N11" s="5"/>
-      <c r="O11" s="5"/>
-    </row>
-    <row r="12" ht="25" customHeight="1" spans="1:15">
-      <c r="A12" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E12" s="8">
-        <v>6</v>
-      </c>
-      <c r="F12" s="8" t="s">
+      <c r="H15" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="I15" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="J15" s="23"/>
+      <c r="K15" s="23"/>
+      <c r="L15" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="M15" s="23"/>
+      <c r="N15" s="23"/>
+      <c r="O15" s="23"/>
+    </row>
+    <row r="16" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A16" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="B16" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="D16" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" s="22">
+        <v>8</v>
+      </c>
+      <c r="F16" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="G12" s="8">
+      <c r="G16" s="22">
         <v>2026</v>
       </c>
-      <c r="H12" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="I12" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5"/>
-      <c r="L12" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="M12" s="5"/>
-      <c r="N12" s="5"/>
-      <c r="O12" s="5"/>
-    </row>
-    <row r="13" ht="25" customHeight="1" spans="1:15">
-      <c r="A13" s="20" t="s">
-        <v>61</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E13" s="8">
-        <v>8</v>
-      </c>
-      <c r="F13" s="8" t="s">
+      <c r="H16" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="I16" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="J16" s="23"/>
+      <c r="K16" s="23"/>
+      <c r="L16" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="M16" s="23"/>
+      <c r="N16" s="23"/>
+      <c r="O16" s="23"/>
+    </row>
+    <row r="17" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A17" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="B17" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>79</v>
+      </c>
+      <c r="D17" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="E17" s="22">
+        <v>7</v>
+      </c>
+      <c r="F17" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="G13" s="8">
+      <c r="G17" s="22">
         <v>2026</v>
       </c>
-      <c r="H13" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="I13" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
-      <c r="L13" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="M13" s="5"/>
-      <c r="N13" s="5"/>
-      <c r="O13" s="5"/>
-    </row>
-    <row r="14" ht="25" customHeight="1" spans="1:15">
-      <c r="A14" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" s="8">
+      <c r="H17" s="22"/>
+      <c r="I17" s="22" t="s">
+        <v>80</v>
+      </c>
+      <c r="J17" s="23"/>
+      <c r="K17" s="23"/>
+      <c r="L17" s="23"/>
+      <c r="M17" s="23"/>
+      <c r="N17" s="23"/>
+      <c r="O17" s="23"/>
+    </row>
+    <row r="18" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A18" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="B18" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="D18" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="22">
         <v>4</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="F18" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="G14" s="8">
+      <c r="G18" s="22">
         <v>2026</v>
       </c>
-      <c r="H14" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="I14" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
-      <c r="L14" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="M14" s="5"/>
-      <c r="N14" s="5"/>
-      <c r="O14" s="5"/>
-    </row>
-    <row r="15" ht="25" customHeight="1" spans="1:15">
-      <c r="A15" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E15" s="8">
-        <v>8</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G15" s="8">
+      <c r="H18" s="22"/>
+      <c r="I18" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="J18" s="23"/>
+      <c r="K18" s="23"/>
+      <c r="L18" s="23"/>
+      <c r="M18" s="23"/>
+      <c r="N18" s="23"/>
+      <c r="O18" s="23"/>
+    </row>
+    <row r="19" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A19" s="25" t="s">
+        <v>84</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="27" t="s">
+        <v>85</v>
+      </c>
+      <c r="D19" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19" s="27"/>
+      <c r="F19" s="27" t="s">
+        <v>86</v>
+      </c>
+      <c r="G19" s="22">
         <v>2026</v>
       </c>
-      <c r="H15" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="I15" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5"/>
-      <c r="L15" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="M15" s="5"/>
-      <c r="N15" s="5"/>
-      <c r="O15" s="5"/>
-    </row>
-    <row r="16" ht="25" customHeight="1" spans="1:15">
-      <c r="A16" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E16" s="8">
-        <v>7</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G16" s="8">
+      <c r="H19" s="22"/>
+      <c r="I19" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="J19" s="23"/>
+      <c r="K19" s="23"/>
+      <c r="L19" s="23"/>
+      <c r="M19" s="23"/>
+      <c r="N19" s="23"/>
+      <c r="O19" s="28"/>
+    </row>
+    <row r="20" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A20" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" s="27" t="s">
+        <v>85</v>
+      </c>
+      <c r="D20" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="E20" s="27"/>
+      <c r="F20" s="27" t="s">
+        <v>86</v>
+      </c>
+      <c r="G20" s="22">
         <v>2026</v>
       </c>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="J16" s="5"/>
-      <c r="K16" s="5"/>
-      <c r="L16" s="5"/>
-      <c r="M16" s="5"/>
-      <c r="N16" s="5"/>
-      <c r="O16" s="5"/>
-    </row>
-    <row r="17" ht="25" customHeight="1" spans="1:15">
-      <c r="A17" s="20" t="s">
-        <v>77</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E17" s="8">
-        <v>4</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G17" s="8">
-        <v>2026</v>
-      </c>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="J17" s="5"/>
-      <c r="K17" s="5"/>
-      <c r="L17" s="5"/>
-      <c r="M17" s="5"/>
-      <c r="N17" s="5"/>
-      <c r="O17" s="5"/>
-    </row>
-    <row r="18" ht="25" customHeight="1" spans="1:15">
-      <c r="A18" s="21" t="s">
-        <v>80</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="C18" s="22" t="s">
-        <v>81</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E18" s="22"/>
-      <c r="F18" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="G18" s="8">
-        <v>2026</v>
-      </c>
-      <c r="H18" s="8"/>
-      <c r="I18" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="J18" s="5"/>
-      <c r="K18" s="5"/>
-      <c r="L18" s="5"/>
-      <c r="M18" s="5"/>
-      <c r="N18" s="5"/>
-      <c r="O18" s="23"/>
-    </row>
-    <row r="19" ht="25" customHeight="1" spans="1:15">
-      <c r="A19" s="21" t="s">
-        <v>84</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="C19" s="22" t="s">
-        <v>81</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E19" s="22"/>
-      <c r="F19" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="G19" s="8">
-        <v>2026</v>
-      </c>
-      <c r="H19" s="8"/>
-      <c r="I19" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="J19" s="5"/>
-      <c r="K19" s="5"/>
-      <c r="L19" s="5"/>
-      <c r="M19" s="5"/>
-      <c r="N19" s="5"/>
-      <c r="O19" s="23"/>
-    </row>
-    <row r="20" ht="25" customHeight="1" spans="1:15">
-      <c r="A20" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="G20" s="5">
-        <v>2026</v>
-      </c>
-      <c r="H20" s="5" t="s">
+      <c r="H20" s="22"/>
+      <c r="I20" s="26" t="s">
         <v>89</v>
       </c>
-      <c r="I20" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="J20" s="5"/>
-      <c r="K20" s="5"/>
-      <c r="L20" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="M20" s="5"/>
-      <c r="N20" s="5"/>
-      <c r="O20" s="5"/>
+      <c r="J20" s="23"/>
+      <c r="K20" s="23"/>
+      <c r="L20" s="23"/>
+      <c r="M20" s="23"/>
+      <c r="N20" s="23"/>
+      <c r="O20" s="28"/>
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:15">
       <c r="A21" s="12" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C21" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="G21" s="5">
+        <v>2026</v>
+      </c>
+      <c r="H21" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="D21" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E21" s="5" t="s">
+      <c r="I21" s="1" t="s">
         <v>94</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="G21" s="5">
-        <v>2025</v>
-      </c>
-      <c r="H21" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>96</v>
       </c>
       <c r="J21" s="5"/>
       <c r="K21" s="5"/>
       <c r="L21" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="M21" s="5"/>
       <c r="N21" s="5"/>
@@ -3163,36 +3241,36 @@
     </row>
     <row r="22" ht="25" customHeight="1" spans="1:15">
       <c r="A22" s="12" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C22" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="G22" s="5">
+        <v>2025</v>
+      </c>
+      <c r="H22" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="D22" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E22" s="5" t="s">
+      <c r="I22" s="1" t="s">
         <v>100</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="G22" s="5">
-        <v>2026</v>
-      </c>
-      <c r="H22" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>102</v>
       </c>
       <c r="J22" s="5"/>
       <c r="K22" s="5"/>
       <c r="L22" s="5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="M22" s="5"/>
       <c r="N22" s="5"/>
@@ -3200,36 +3278,36 @@
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:15">
       <c r="A23" s="12" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G23" s="5">
         <v>2026</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="J23" s="5"/>
       <c r="K23" s="5"/>
       <c r="L23" s="5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M23" s="5"/>
       <c r="N23" s="5"/>
@@ -3237,36 +3315,36 @@
     </row>
     <row r="24" ht="25" customHeight="1" spans="1:15">
       <c r="A24" s="12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C24" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="G24" s="5">
+        <v>2026</v>
+      </c>
+      <c r="H24" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="D24" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E24" s="5" t="s">
+      <c r="I24" s="1" t="s">
         <v>112</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="G24" s="5">
-        <v>2025</v>
-      </c>
-      <c r="H24" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>114</v>
       </c>
       <c r="J24" s="5"/>
       <c r="K24" s="5"/>
       <c r="L24" s="5" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="M24" s="5"/>
       <c r="N24" s="5"/>
@@ -3274,173 +3352,173 @@
     </row>
     <row r="25" ht="25" customHeight="1" spans="1:15">
       <c r="A25" s="12" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C25" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="G25" s="5">
+        <v>2025</v>
+      </c>
+      <c r="H25" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="D25" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E25" s="5" t="s">
+      <c r="I25" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="F25" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="G25" s="5">
-        <v>2026</v>
-      </c>
-      <c r="H25" s="5" t="s">
+      <c r="J25" s="5"/>
+      <c r="K25" s="5"/>
+      <c r="L25" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="I25" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="J25" s="15"/>
-      <c r="K25" s="15"/>
-      <c r="L25" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="M25" s="15"/>
-      <c r="N25" s="15"/>
+      <c r="M25" s="5"/>
+      <c r="N25" s="5"/>
       <c r="O25" s="5"/>
     </row>
     <row r="26" ht="25" customHeight="1" spans="1:15">
       <c r="A26" s="12" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G26" s="5">
         <v>2026</v>
       </c>
       <c r="H26" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="J26" s="15"/>
+      <c r="K26" s="15"/>
+      <c r="L26" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="I26" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="J26" s="5"/>
-      <c r="K26" s="5"/>
-      <c r="L26" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="M26" s="5"/>
-      <c r="N26" s="5"/>
-      <c r="O26" s="23"/>
+      <c r="M26" s="15"/>
+      <c r="N26" s="15"/>
+      <c r="O26" s="5"/>
     </row>
     <row r="27" ht="25" customHeight="1" spans="1:15">
       <c r="A27" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C27" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="G27" s="5">
+        <v>2026</v>
+      </c>
+      <c r="H27" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="D27" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E27" s="5" t="s">
+      <c r="I27" s="5" t="s">
         <v>130</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="G27" s="5">
-        <v>2024</v>
-      </c>
-      <c r="H27" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="I27" s="5" t="s">
-        <v>132</v>
       </c>
       <c r="J27" s="5"/>
       <c r="K27" s="5"/>
       <c r="L27" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="M27" s="5"/>
       <c r="N27" s="5"/>
-      <c r="O27" s="23"/>
+      <c r="O27" s="29"/>
     </row>
     <row r="28" ht="25" customHeight="1" spans="1:15">
       <c r="A28" s="12" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G28" s="5">
         <v>2024</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J28" s="5"/>
       <c r="K28" s="5"/>
       <c r="L28" s="5" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="M28" s="5"/>
       <c r="N28" s="5"/>
-      <c r="O28" s="23"/>
+      <c r="O28" s="29"/>
     </row>
     <row r="29" ht="25" customHeight="1" spans="1:15">
       <c r="A29" s="12" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>105</v>
+        <v>139</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>106</v>
+        <v>140</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G29" s="5">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="H29" s="5" t="s">
         <v>141</v>
@@ -3455,7 +3533,7 @@
       </c>
       <c r="M29" s="5"/>
       <c r="N29" s="5"/>
-      <c r="O29" s="23"/>
+      <c r="O29" s="29"/>
     </row>
     <row r="30" ht="25" customHeight="1" spans="1:15">
       <c r="A30" s="12" t="s">
@@ -3465,298 +3543,300 @@
         <v>12</v>
       </c>
       <c r="C30" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="G30" s="5">
+        <v>2026</v>
+      </c>
+      <c r="H30" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="D30" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E30" s="5" t="s">
+      <c r="I30" s="5" t="s">
         <v>146</v>
-      </c>
-      <c r="F30" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="G30" s="5">
-        <v>2025</v>
-      </c>
-      <c r="H30" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="I30" s="5" t="s">
-        <v>148</v>
       </c>
       <c r="J30" s="5"/>
       <c r="K30" s="5"/>
       <c r="L30" s="5" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="M30" s="5"/>
       <c r="N30" s="5"/>
-      <c r="O30" s="23"/>
+      <c r="O30" s="29"/>
     </row>
     <row r="31" ht="25" customHeight="1" spans="1:15">
       <c r="A31" s="12" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C31" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="G31" s="5">
+        <v>2025</v>
+      </c>
+      <c r="H31" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="D31" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="F31" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="G31" s="5">
-        <v>2026</v>
-      </c>
-      <c r="H31" s="5" t="s">
+      <c r="I31" s="5" t="s">
         <v>152</v>
-      </c>
-      <c r="I31" s="5" t="s">
-        <v>153</v>
       </c>
       <c r="J31" s="5"/>
       <c r="K31" s="5"/>
       <c r="L31" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="M31" s="5"/>
       <c r="N31" s="5"/>
-      <c r="O31" s="23"/>
+      <c r="O31" s="29"/>
     </row>
     <row r="32" ht="25" customHeight="1" spans="1:15">
       <c r="A32" s="12" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G32" s="5">
         <v>2026</v>
       </c>
       <c r="H32" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="I32" s="5" t="s">
         <v>157</v>
-      </c>
-      <c r="I32" s="5" t="s">
-        <v>158</v>
       </c>
       <c r="J32" s="5"/>
       <c r="K32" s="5"/>
       <c r="L32" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="M32" s="5"/>
       <c r="N32" s="5"/>
-      <c r="O32" s="23"/>
+      <c r="O32" s="29"/>
     </row>
     <row r="33" ht="25" customHeight="1" spans="1:15">
       <c r="A33" s="12" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>88</v>
+        <v>128</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G33" s="5">
         <v>2026</v>
       </c>
       <c r="H33" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="I33" s="5" t="s">
         <v>162</v>
-      </c>
-      <c r="I33" s="5" t="s">
-        <v>163</v>
       </c>
       <c r="J33" s="5"/>
       <c r="K33" s="5"/>
       <c r="L33" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="M33" s="5"/>
       <c r="N33" s="5"/>
-      <c r="O33" s="23"/>
+      <c r="O33" s="29"/>
     </row>
     <row r="34" ht="25" customHeight="1" spans="1:15">
       <c r="A34" s="12" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>111</v>
+        <v>165</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E34" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="G34" s="5">
+        <v>2026</v>
+      </c>
+      <c r="H34" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="F34" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="G34" s="5">
-        <v>2025</v>
-      </c>
-      <c r="H34" s="5" t="s">
+      <c r="I34" s="5" t="s">
         <v>167</v>
-      </c>
-      <c r="I34" s="5" t="s">
-        <v>168</v>
       </c>
       <c r="J34" s="5"/>
       <c r="K34" s="5"/>
       <c r="L34" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="M34" s="5"/>
       <c r="N34" s="5"/>
-      <c r="O34" s="23"/>
+      <c r="O34" s="29"/>
     </row>
     <row r="35" ht="25" customHeight="1" spans="1:15">
       <c r="A35" s="12" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C35" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="G35" s="5">
+        <v>2025</v>
+      </c>
+      <c r="H35" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="D35" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E35" s="5" t="s">
+      <c r="I35" s="5" t="s">
         <v>172</v>
-      </c>
-      <c r="F35" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="G35" s="5">
-        <v>2026</v>
-      </c>
-      <c r="H35" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="I35" s="5" t="s">
-        <v>174</v>
       </c>
       <c r="J35" s="5"/>
       <c r="K35" s="5"/>
       <c r="L35" s="5" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="M35" s="5"/>
       <c r="N35" s="5"/>
-      <c r="O35" s="23"/>
+      <c r="O35" s="29"/>
     </row>
     <row r="36" ht="25" customHeight="1" spans="1:15">
       <c r="A36" s="12" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>94</v>
+        <v>176</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G36" s="5">
         <v>2026</v>
       </c>
       <c r="H36" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="I36" s="5" t="s">
         <v>178</v>
-      </c>
-      <c r="I36" s="5" t="s">
-        <v>179</v>
       </c>
       <c r="J36" s="5"/>
       <c r="K36" s="5"/>
       <c r="L36" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="M36" s="5"/>
       <c r="N36" s="5"/>
-      <c r="O36" s="23"/>
+      <c r="O36" s="29"/>
     </row>
     <row r="37" ht="25" customHeight="1" spans="1:15">
       <c r="A37" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C37" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="D37" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="G37" s="5">
+        <v>2026</v>
+      </c>
+      <c r="H37" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="C37" s="5" t="s">
+      <c r="I37" s="5" t="s">
         <v>183</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E37" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="F37" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="G37" s="5">
-        <v>2025</v>
-      </c>
-      <c r="H37" s="5"/>
-      <c r="I37" s="5" t="s">
-        <v>185</v>
       </c>
       <c r="J37" s="5"/>
       <c r="K37" s="5"/>
       <c r="L37" s="5" t="s">
-        <v>45</v>
+        <v>184</v>
       </c>
       <c r="M37" s="5"/>
       <c r="N37" s="5"/>
-      <c r="O37" s="23"/>
+      <c r="O37" s="29"/>
     </row>
     <row r="38" ht="25" customHeight="1" spans="1:15">
       <c r="A38" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="B38" s="5" t="s">
         <v>186</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>182</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>187</v>
@@ -3768,559 +3848,563 @@
         <v>188</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G38" s="5">
         <v>2025</v>
       </c>
-      <c r="H38" s="5" t="s">
+      <c r="H38" s="5"/>
+      <c r="I38" s="5" t="s">
         <v>189</v>
-      </c>
-      <c r="I38" s="5" t="s">
-        <v>190</v>
       </c>
       <c r="J38" s="5"/>
       <c r="K38" s="5"/>
       <c r="L38" s="5" t="s">
-        <v>191</v>
+        <v>49</v>
       </c>
       <c r="M38" s="5"/>
       <c r="N38" s="5"/>
-      <c r="O38" s="23"/>
+      <c r="O38" s="29"/>
     </row>
     <row r="39" ht="25" customHeight="1" spans="1:15">
       <c r="A39" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E39" s="13" t="s">
         <v>192</v>
       </c>
-      <c r="B39" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E39" s="11" t="s">
-        <v>184</v>
-      </c>
       <c r="F39" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G39" s="5">
         <v>2025</v>
       </c>
-      <c r="H39" s="5"/>
+      <c r="H39" s="5" t="s">
+        <v>193</v>
+      </c>
       <c r="I39" s="5" t="s">
         <v>194</v>
       </c>
       <c r="J39" s="5"/>
       <c r="K39" s="5"/>
       <c r="L39" s="5" t="s">
-        <v>45</v>
+        <v>195</v>
       </c>
       <c r="M39" s="5"/>
       <c r="N39" s="5"/>
-      <c r="O39" s="23"/>
+      <c r="O39" s="29"/>
     </row>
     <row r="40" ht="25" customHeight="1" spans="1:15">
       <c r="A40" s="12" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D40" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E40" s="5" t="s">
-        <v>100</v>
+      <c r="E40" s="26" t="s">
+        <v>188</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G40" s="5">
-        <v>2026</v>
-      </c>
-      <c r="H40" s="5" t="s">
-        <v>197</v>
-      </c>
+        <v>2025</v>
+      </c>
+      <c r="H40" s="5"/>
       <c r="I40" s="5" t="s">
         <v>198</v>
       </c>
       <c r="J40" s="5"/>
       <c r="K40" s="5"/>
       <c r="L40" s="5" t="s">
-        <v>199</v>
+        <v>49</v>
       </c>
       <c r="M40" s="5"/>
       <c r="N40" s="5"/>
-      <c r="O40" s="23"/>
+      <c r="O40" s="29"/>
     </row>
     <row r="41" ht="25" customHeight="1" spans="1:15">
       <c r="A41" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="C41" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="B41" s="5"/>
-      <c r="C41" s="5"/>
-      <c r="D41" s="5"/>
-      <c r="E41" s="5"/>
+      <c r="D41" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>104</v>
+      </c>
       <c r="F41" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="G41" s="5"/>
-      <c r="H41" s="5"/>
+        <v>86</v>
+      </c>
+      <c r="G41" s="5">
+        <v>2026</v>
+      </c>
+      <c r="H41" s="5" t="s">
+        <v>201</v>
+      </c>
       <c r="I41" s="5" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="J41" s="5"/>
       <c r="K41" s="5"/>
-      <c r="L41" s="5"/>
+      <c r="L41" s="5" t="s">
+        <v>203</v>
+      </c>
       <c r="M41" s="5"/>
       <c r="N41" s="5"/>
-      <c r="O41" s="23"/>
+      <c r="O41" s="29"/>
     </row>
     <row r="42" ht="25" customHeight="1" spans="1:15">
       <c r="A42" s="12" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5"/>
       <c r="D42" s="5"/>
       <c r="E42" s="5"/>
       <c r="F42" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G42" s="5"/>
       <c r="H42" s="5"/>
       <c r="I42" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="J42" s="5"/>
       <c r="K42" s="5"/>
       <c r="L42" s="5"/>
       <c r="M42" s="5"/>
       <c r="N42" s="5"/>
-      <c r="O42" s="23"/>
+      <c r="O42" s="29"/>
     </row>
     <row r="43" ht="25" customHeight="1" spans="1:15">
       <c r="A43" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5"/>
       <c r="D43" s="5"/>
       <c r="E43" s="5"/>
       <c r="F43" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G43" s="5"/>
       <c r="H43" s="5"/>
       <c r="I43" s="5" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="J43" s="5"/>
       <c r="K43" s="5"/>
       <c r="L43" s="5"/>
       <c r="M43" s="5"/>
       <c r="N43" s="5"/>
-      <c r="O43" s="23"/>
+      <c r="O43" s="29"/>
     </row>
     <row r="44" ht="25" customHeight="1" spans="1:15">
       <c r="A44" s="12" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
       <c r="D44" s="5"/>
       <c r="E44" s="5"/>
       <c r="F44" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G44" s="5"/>
       <c r="H44" s="5"/>
       <c r="I44" s="5" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="J44" s="5"/>
       <c r="K44" s="5"/>
       <c r="L44" s="5"/>
       <c r="M44" s="5"/>
       <c r="N44" s="5"/>
-      <c r="O44" s="23"/>
+      <c r="O44" s="29"/>
     </row>
     <row r="45" ht="25" customHeight="1" spans="1:15">
-      <c r="A45" s="14" t="s">
-        <v>208</v>
-      </c>
-      <c r="B45" s="15"/>
-      <c r="C45" s="15"/>
-      <c r="D45" s="15"/>
-      <c r="E45" s="15"/>
+      <c r="A45" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="B45" s="5"/>
+      <c r="C45" s="5"/>
+      <c r="D45" s="5"/>
+      <c r="E45" s="5"/>
       <c r="F45" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="G45" s="15"/>
-      <c r="H45" s="15"/>
-      <c r="I45" s="16" t="s">
-        <v>209</v>
-      </c>
-      <c r="J45" s="15"/>
+        <v>86</v>
+      </c>
+      <c r="G45" s="5"/>
+      <c r="H45" s="5"/>
+      <c r="I45" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="J45" s="5"/>
       <c r="K45" s="5"/>
       <c r="L45" s="5"/>
       <c r="M45" s="5"/>
       <c r="N45" s="5"/>
-      <c r="O45" s="23"/>
+      <c r="O45" s="29"/>
     </row>
     <row r="46" ht="25" customHeight="1" spans="1:15">
-      <c r="A46" s="12" t="s">
-        <v>210</v>
-      </c>
-      <c r="B46" s="5"/>
-      <c r="C46" s="5"/>
-      <c r="D46" s="5"/>
-      <c r="E46" s="5"/>
+      <c r="A46" s="14" t="s">
+        <v>212</v>
+      </c>
+      <c r="B46" s="15"/>
+      <c r="C46" s="15"/>
+      <c r="D46" s="15"/>
+      <c r="E46" s="15"/>
       <c r="F46" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="G46" s="5"/>
-      <c r="H46" s="5"/>
-      <c r="I46" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="J46" s="5"/>
+        <v>86</v>
+      </c>
+      <c r="G46" s="15"/>
+      <c r="H46" s="15"/>
+      <c r="I46" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="J46" s="15"/>
       <c r="K46" s="5"/>
       <c r="L46" s="5"/>
       <c r="M46" s="5"/>
       <c r="N46" s="5"/>
-      <c r="O46" s="23"/>
+      <c r="O46" s="29"/>
     </row>
     <row r="47" ht="25" customHeight="1" spans="1:15">
       <c r="A47" s="12" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
       <c r="D47" s="5"/>
       <c r="E47" s="5"/>
       <c r="F47" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G47" s="5"/>
       <c r="H47" s="5"/>
       <c r="I47" s="5" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="J47" s="5"/>
       <c r="K47" s="5"/>
       <c r="L47" s="5"/>
       <c r="M47" s="5"/>
       <c r="N47" s="5"/>
-      <c r="O47" s="23"/>
+      <c r="O47" s="29"/>
     </row>
     <row r="48" ht="25" customHeight="1" spans="1:15">
       <c r="A48" s="12" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
       <c r="D48" s="5"/>
       <c r="E48" s="5"/>
       <c r="F48" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G48" s="5"/>
       <c r="H48" s="5"/>
       <c r="I48" s="5" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="J48" s="5"/>
       <c r="K48" s="5"/>
       <c r="L48" s="5"/>
       <c r="M48" s="5"/>
       <c r="N48" s="5"/>
-      <c r="O48" s="23"/>
+      <c r="O48" s="29"/>
     </row>
     <row r="49" ht="25" customHeight="1" spans="1:15">
       <c r="A49" s="12" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
       <c r="D49" s="5"/>
       <c r="E49" s="5"/>
       <c r="F49" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G49" s="5"/>
       <c r="H49" s="5"/>
       <c r="I49" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="J49" s="5"/>
       <c r="K49" s="5"/>
       <c r="L49" s="5"/>
       <c r="M49" s="5"/>
       <c r="N49" s="5"/>
-      <c r="O49" s="23"/>
+      <c r="O49" s="29"/>
     </row>
     <row r="50" ht="25" customHeight="1" spans="1:15">
       <c r="A50" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5"/>
       <c r="D50" s="5"/>
       <c r="E50" s="5"/>
       <c r="F50" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G50" s="5"/>
       <c r="H50" s="5"/>
       <c r="I50" s="5" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="J50" s="5"/>
       <c r="K50" s="5"/>
       <c r="L50" s="5"/>
       <c r="M50" s="5"/>
       <c r="N50" s="5"/>
-      <c r="O50" s="23"/>
+      <c r="O50" s="29"/>
     </row>
     <row r="51" ht="25" customHeight="1" spans="1:15">
       <c r="A51" s="12" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
       <c r="D51" s="5"/>
       <c r="E51" s="5"/>
       <c r="F51" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G51" s="5"/>
       <c r="H51" s="5"/>
       <c r="I51" s="5" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="J51" s="5"/>
       <c r="K51" s="5"/>
       <c r="L51" s="5"/>
       <c r="M51" s="5"/>
       <c r="N51" s="5"/>
-      <c r="O51" s="23"/>
+      <c r="O51" s="29"/>
     </row>
     <row r="52" ht="25" customHeight="1" spans="1:15">
       <c r="A52" s="12" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5"/>
       <c r="D52" s="5"/>
       <c r="E52" s="5"/>
       <c r="F52" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G52" s="5"/>
       <c r="H52" s="5"/>
       <c r="I52" s="5" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="J52" s="5"/>
       <c r="K52" s="5"/>
       <c r="L52" s="5"/>
       <c r="M52" s="5"/>
       <c r="N52" s="5"/>
-      <c r="O52" s="23"/>
+      <c r="O52" s="29"/>
     </row>
     <row r="53" ht="25" customHeight="1" spans="1:15">
       <c r="A53" s="12" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5"/>
       <c r="D53" s="5"/>
       <c r="E53" s="5"/>
       <c r="F53" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G53" s="5"/>
       <c r="H53" s="5"/>
       <c r="I53" s="5" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="J53" s="5"/>
       <c r="K53" s="5"/>
       <c r="L53" s="5"/>
       <c r="M53" s="5"/>
       <c r="N53" s="5"/>
-      <c r="O53" s="23"/>
+      <c r="O53" s="29"/>
     </row>
     <row r="54" ht="25" customHeight="1" spans="1:15">
       <c r="A54" s="12" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
       <c r="D54" s="5"/>
       <c r="E54" s="5"/>
       <c r="F54" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G54" s="5"/>
       <c r="H54" s="5"/>
       <c r="I54" s="5" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="J54" s="5"/>
       <c r="K54" s="5"/>
       <c r="L54" s="5"/>
       <c r="M54" s="5"/>
       <c r="N54" s="5"/>
-      <c r="O54" s="23"/>
-    </row>
-    <row r="55" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="O54" s="29"/>
+    </row>
+    <row r="55" ht="25" customHeight="1" spans="1:15">
       <c r="A55" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B55" s="5"/>
       <c r="C55" s="5"/>
       <c r="D55" s="5"/>
       <c r="E55" s="5"/>
       <c r="F55" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G55" s="5"/>
       <c r="H55" s="5"/>
       <c r="I55" s="5" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="J55" s="5"/>
       <c r="K55" s="5"/>
       <c r="L55" s="5"/>
       <c r="M55" s="5"/>
       <c r="N55" s="5"/>
-      <c r="O55" s="23"/>
+      <c r="O55" s="29"/>
     </row>
     <row r="56" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A56" s="12" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
       <c r="D56" s="5"/>
       <c r="E56" s="5"/>
       <c r="F56" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G56" s="5"/>
       <c r="H56" s="5"/>
       <c r="I56" s="5" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="J56" s="5"/>
       <c r="K56" s="5"/>
       <c r="L56" s="5"/>
       <c r="M56" s="5"/>
       <c r="N56" s="5"/>
-      <c r="O56" s="23"/>
+      <c r="O56" s="29"/>
     </row>
     <row r="57" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A57" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
       <c r="D57" s="5"/>
       <c r="E57" s="5"/>
       <c r="F57" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G57" s="5"/>
       <c r="H57" s="5"/>
       <c r="I57" s="5" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="J57" s="5"/>
       <c r="K57" s="5"/>
       <c r="L57" s="5"/>
       <c r="M57" s="5"/>
       <c r="N57" s="5"/>
-      <c r="O57" s="23"/>
+      <c r="O57" s="29"/>
     </row>
     <row r="58" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A58" s="12" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
       <c r="D58" s="5"/>
       <c r="E58" s="5"/>
       <c r="F58" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G58" s="5"/>
       <c r="H58" s="5"/>
       <c r="I58" s="5" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="J58" s="5"/>
       <c r="K58" s="5"/>
       <c r="L58" s="5"/>
       <c r="M58" s="5"/>
       <c r="N58" s="5"/>
-      <c r="O58" s="23"/>
+      <c r="O58" s="29"/>
     </row>
     <row r="59" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A59" s="12" t="s">
-        <v>236</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C59" s="17" t="s">
-        <v>237</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="B59" s="5"/>
+      <c r="C59" s="5"/>
       <c r="D59" s="5"/>
-      <c r="E59" s="5" t="s">
-        <v>238</v>
-      </c>
+      <c r="E59" s="5"/>
       <c r="F59" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G59" s="5"/>
-      <c r="H59" s="18" t="s">
+      <c r="H59" s="5"/>
+      <c r="I59" s="5" t="s">
         <v>239</v>
-      </c>
-      <c r="I59" s="5" t="s">
-        <v>240</v>
       </c>
       <c r="J59" s="5"/>
       <c r="K59" s="5"/>
       <c r="L59" s="5"/>
       <c r="M59" s="5"/>
       <c r="N59" s="5"/>
-      <c r="O59" s="23"/>
+      <c r="O59" s="29"/>
     </row>
     <row r="60" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A60" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C60" s="17" t="s">
         <v>241</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="C60" s="17" t="s">
-        <v>242</v>
       </c>
       <c r="D60" s="5"/>
       <c r="E60" s="5" t="s">
-        <v>100</v>
+        <v>242</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G60" s="5"/>
       <c r="H60" s="18" t="s">
@@ -4334,24 +4418,24 @@
       <c r="L60" s="5"/>
       <c r="M60" s="5"/>
       <c r="N60" s="5"/>
-      <c r="O60" s="5"/>
+      <c r="O60" s="29"/>
     </row>
     <row r="61" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A61" s="12" t="s">
         <v>245</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C61" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="C61" s="17" t="s">
         <v>246</v>
       </c>
       <c r="D61" s="5"/>
       <c r="E61" s="5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G61" s="5"/>
       <c r="H61" s="18" t="s">
@@ -4365,55 +4449,55 @@
       <c r="L61" s="5"/>
       <c r="M61" s="5"/>
       <c r="N61" s="5"/>
-      <c r="O61" s="23"/>
-    </row>
-    <row r="62" ht="25" customHeight="1" spans="1:15">
+      <c r="O61" s="5"/>
+    </row>
+    <row r="62" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A62" s="12" t="s">
         <v>249</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C62" s="17" t="s">
+      <c r="C62" s="19" t="s">
         <v>250</v>
       </c>
       <c r="D62" s="5"/>
       <c r="E62" s="5" t="s">
-        <v>251</v>
+        <v>110</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G62" s="5"/>
       <c r="H62" s="18" t="s">
+        <v>251</v>
+      </c>
+      <c r="I62" s="5" t="s">
         <v>252</v>
-      </c>
-      <c r="I62" s="5" t="s">
-        <v>253</v>
       </c>
       <c r="J62" s="5"/>
       <c r="K62" s="5"/>
       <c r="L62" s="5"/>
       <c r="M62" s="5"/>
       <c r="N62" s="5"/>
-      <c r="O62" s="23"/>
+      <c r="O62" s="29"/>
     </row>
     <row r="63" ht="25" customHeight="1" spans="1:15">
       <c r="A63" s="12" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C63" s="17" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D63" s="5"/>
       <c r="E63" s="5" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G63" s="5"/>
       <c r="H63" s="18" t="s">
@@ -4427,55 +4511,69 @@
       <c r="L63" s="5"/>
       <c r="M63" s="5"/>
       <c r="N63" s="5"/>
-      <c r="O63" s="23"/>
+      <c r="O63" s="29"/>
     </row>
     <row r="64" ht="25" customHeight="1" spans="1:15">
       <c r="A64" s="12" t="s">
         <v>258</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="C64" s="17" t="s">
         <v>259</v>
       </c>
       <c r="D64" s="5"/>
       <c r="E64" s="5" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G64" s="5"/>
       <c r="H64" s="18" t="s">
+        <v>260</v>
+      </c>
+      <c r="I64" s="5" t="s">
         <v>261</v>
-      </c>
-      <c r="I64" s="5" t="s">
-        <v>262</v>
       </c>
       <c r="J64" s="5"/>
       <c r="K64" s="5"/>
       <c r="L64" s="5"/>
       <c r="M64" s="5"/>
       <c r="N64" s="5"/>
-      <c r="O64" s="23"/>
+      <c r="O64" s="29"/>
     </row>
     <row r="65" ht="25" customHeight="1" spans="1:15">
-      <c r="A65" s="12"/>
-      <c r="B65" s="5"/>
-      <c r="C65" s="5"/>
+      <c r="A65" s="12" t="s">
+        <v>262</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C65" s="17" t="s">
+        <v>263</v>
+      </c>
       <c r="D65" s="5"/>
-      <c r="E65" s="5"/>
-      <c r="F65" s="13"/>
+      <c r="E65" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="F65" s="5" t="s">
+        <v>86</v>
+      </c>
       <c r="G65" s="5"/>
-      <c r="H65" s="5"/>
-      <c r="I65" s="5"/>
+      <c r="H65" s="18" t="s">
+        <v>265</v>
+      </c>
+      <c r="I65" s="5" t="s">
+        <v>266</v>
+      </c>
       <c r="J65" s="5"/>
       <c r="K65" s="5"/>
       <c r="L65" s="5"/>
       <c r="M65" s="5"/>
       <c r="N65" s="5"/>
-      <c r="O65" s="5"/>
+      <c r="O65" s="29"/>
     </row>
     <row r="66" ht="25" customHeight="1" spans="1:15">
       <c r="A66" s="12"/>
@@ -4519,7 +4617,6 @@
       <c r="E68" s="5"/>
       <c r="F68" s="13"/>
       <c r="G68" s="5"/>
-      <c r="H68" s="5"/>
       <c r="I68" s="5"/>
       <c r="J68" s="5"/>
       <c r="K68" s="5"/>
@@ -4750,15 +4847,15 @@
       <c r="O81" s="5"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:O64" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A1:O64">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:O65" etc:filterBottomFollowUsedRange="0">
+    <sortState ref="A1:O65">
       <sortCondition ref="F1"/>
     </sortState>
     <extLst/>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="H60" r:id="rId1" display="普洛伊湘普·素帕莎 / 芭莉雅皮·余 " tooltip="https://www.douban.com/personage/30264980/"/>
-    <hyperlink ref="H15" r:id="rId2" display="金贤叙/郑明哲" tooltip="https://www.douban.com/personage/37338980/"/>
+    <hyperlink ref="H61" r:id="rId1" display="普洛伊湘普·素帕莎 / 芭莉雅皮·余 " tooltip="https://www.douban.com/personage/30264980/"/>
+    <hyperlink ref="H16" r:id="rId2" display="金贤叙/郑明哲" tooltip="https://www.douban.com/personage/37338980/"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -4782,7 +4879,7 @@
   <sheetData>
     <row r="1" ht="33" customHeight="1" spans="1:9">
       <c r="A1" s="3" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -4829,7 +4926,7 @@
         <v>12</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>14</v>
@@ -4968,13 +5065,13 @@
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:9">
       <c r="A8" s="6" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>14</v>
@@ -4989,21 +5086,21 @@
         <v>2026</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:9">
       <c r="A9" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>36</v>
-      </c>
       <c r="C9" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>14</v>
@@ -5018,21 +5115,21 @@
         <v>2026</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:9">
       <c r="A10" s="6" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>14</v>
@@ -5047,21 +5144,21 @@
         <v>2026</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:9">
       <c r="A11" s="6" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>14</v>
@@ -5076,21 +5173,21 @@
         <v>2026</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:9">
       <c r="A12" s="6" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>14</v>
@@ -5105,21 +5202,21 @@
         <v>2026</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:9">
       <c r="A13" s="6" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>14</v>
@@ -5134,21 +5231,21 @@
         <v>2026</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:9">
       <c r="A14" s="6" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>14</v>
@@ -5163,21 +5260,21 @@
         <v>2026</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:9">
       <c r="A15" s="6" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>14</v>
@@ -5192,21 +5289,21 @@
         <v>2026</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:9">
       <c r="A16" s="6" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>14</v>
@@ -5221,21 +5318,21 @@
         <v>2026</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:9">
       <c r="A17" s="6" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>14</v>
@@ -5251,18 +5348,18 @@
       </c>
       <c r="H17" s="7"/>
       <c r="I17" s="8" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:9">
       <c r="A18" s="6" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>14</v>
@@ -5278,1118 +5375,1118 @@
       </c>
       <c r="H18" s="7"/>
       <c r="I18" s="8" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" spans="1:9">
       <c r="A19" s="9" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>14</v>
       </c>
       <c r="E19" s="10"/>
       <c r="F19" s="10" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G19" s="7">
         <v>2026</v>
       </c>
       <c r="H19" s="7"/>
       <c r="I19" s="11" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" spans="1:9">
       <c r="A20" s="9" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>14</v>
       </c>
       <c r="E20" s="10"/>
       <c r="F20" s="10" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G20" s="7">
         <v>2026</v>
       </c>
       <c r="H20" s="7"/>
       <c r="I20" s="11" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1" spans="1:9">
       <c r="A21" s="12" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G21" s="5">
         <v>2026</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1" spans="1:9">
       <c r="A22" s="12" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G22" s="5">
         <v>2025</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1" spans="1:9">
       <c r="A23" s="12" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G23" s="5">
         <v>2026</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1" spans="1:9">
       <c r="A24" s="12" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G24" s="5">
         <v>2026</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1" spans="1:9">
       <c r="A25" s="12" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G25" s="5">
         <v>2025</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1" spans="1:9">
       <c r="A26" s="12" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G26" s="5">
         <v>2026</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1" spans="1:9">
       <c r="A27" s="12" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G27" s="5">
         <v>2026</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1" spans="1:9">
       <c r="A28" s="12" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G28" s="5">
         <v>2024</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="29" ht="25" customHeight="1" spans="1:9">
       <c r="A29" s="12" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G29" s="5">
         <v>2024</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="30" ht="25" customHeight="1" spans="1:9">
       <c r="A30" s="12" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G30" s="5">
         <v>2026</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="31" ht="25" customHeight="1" spans="1:9">
       <c r="A31" s="12" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G31" s="5">
         <v>2025</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="32" ht="25" customHeight="1" spans="1:9">
       <c r="A32" s="12" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G32" s="5">
         <v>2026</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="33" ht="25" customHeight="1" spans="1:9">
       <c r="A33" s="12" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G33" s="5">
         <v>2026</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="I33" s="5" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="34" ht="25" customHeight="1" spans="1:9">
       <c r="A34" s="12" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G34" s="5">
         <v>2026</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="35" ht="25" customHeight="1" spans="1:9">
       <c r="A35" s="12" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G35" s="5">
         <v>2025</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
     </row>
     <row r="36" ht="25" customHeight="1" spans="1:9">
       <c r="A36" s="12" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G36" s="5">
         <v>2026</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="37" ht="25" customHeight="1" spans="1:9">
       <c r="A37" s="12" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G37" s="5">
         <v>2026</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="I37" s="5" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
     </row>
     <row r="38" ht="25" customHeight="1" spans="1:9">
       <c r="A38" s="12" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G38" s="5">
         <v>2025</v>
       </c>
       <c r="H38" s="5"/>
       <c r="I38" s="5" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="39" ht="25" customHeight="1" spans="1:9">
       <c r="A39" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="B39" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="B39" s="5" t="s">
-        <v>182</v>
-      </c>
       <c r="C39" s="5" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G39" s="5">
         <v>2025</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="I39" s="5" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
     </row>
     <row r="40" ht="25" customHeight="1" spans="1:9">
       <c r="A40" s="12" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D40" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G40" s="5">
         <v>2025</v>
       </c>
       <c r="H40" s="5"/>
       <c r="I40" s="5" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
     </row>
     <row r="41" ht="25" customHeight="1" spans="1:9">
       <c r="A41" s="12" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G41" s="5">
         <v>2026</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="I41" s="5" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="42" ht="25" customHeight="1" spans="1:9">
       <c r="A42" s="12" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5"/>
       <c r="D42" s="5"/>
       <c r="E42" s="5"/>
       <c r="F42" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G42" s="5"/>
       <c r="H42" s="5"/>
       <c r="I42" s="5" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
     </row>
     <row r="43" ht="25" customHeight="1" spans="1:9">
       <c r="A43" s="12" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5"/>
       <c r="D43" s="5"/>
       <c r="E43" s="5"/>
       <c r="F43" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G43" s="5"/>
       <c r="H43" s="5"/>
       <c r="I43" s="5" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
     </row>
     <row r="44" ht="25" customHeight="1" spans="1:9">
       <c r="A44" s="12" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
       <c r="D44" s="5"/>
       <c r="E44" s="5"/>
       <c r="F44" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G44" s="5"/>
       <c r="H44" s="5"/>
       <c r="I44" s="5" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
     </row>
     <row r="45" ht="25" customHeight="1" spans="1:9">
       <c r="A45" s="12" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5"/>
       <c r="D45" s="5"/>
       <c r="E45" s="5"/>
       <c r="F45" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G45" s="5"/>
       <c r="H45" s="5"/>
       <c r="I45" s="5" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="46" ht="25" customHeight="1" spans="1:9">
       <c r="A46" s="14" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B46" s="15"/>
       <c r="C46" s="15"/>
       <c r="D46" s="15"/>
       <c r="E46" s="15"/>
       <c r="F46" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G46" s="15"/>
       <c r="H46" s="15"/>
       <c r="I46" s="16" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
     </row>
     <row r="47" ht="25" customHeight="1" spans="1:9">
       <c r="A47" s="12" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
       <c r="D47" s="5"/>
       <c r="E47" s="5"/>
       <c r="F47" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G47" s="5"/>
       <c r="H47" s="5"/>
       <c r="I47" s="5" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="48" ht="25" customHeight="1" spans="1:9">
       <c r="A48" s="12" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
       <c r="D48" s="5"/>
       <c r="E48" s="5"/>
       <c r="F48" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G48" s="5"/>
       <c r="H48" s="5"/>
       <c r="I48" s="5" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
     </row>
     <row r="49" ht="25" customHeight="1" spans="1:9">
       <c r="A49" s="12" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
       <c r="D49" s="5"/>
       <c r="E49" s="5"/>
       <c r="F49" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G49" s="5"/>
       <c r="H49" s="5"/>
       <c r="I49" s="5" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="50" ht="25" customHeight="1" spans="1:9">
       <c r="A50" s="12" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5"/>
       <c r="D50" s="5"/>
       <c r="E50" s="5"/>
       <c r="F50" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G50" s="5"/>
       <c r="H50" s="5"/>
       <c r="I50" s="5" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
     </row>
     <row r="51" ht="25" customHeight="1" spans="1:9">
       <c r="A51" s="12" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
       <c r="D51" s="5"/>
       <c r="E51" s="5"/>
       <c r="F51" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G51" s="5"/>
       <c r="H51" s="5"/>
       <c r="I51" s="5" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
     </row>
     <row r="52" ht="25" customHeight="1" spans="1:9">
       <c r="A52" s="12" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5"/>
       <c r="D52" s="5"/>
       <c r="E52" s="5"/>
       <c r="F52" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G52" s="5"/>
       <c r="H52" s="5"/>
       <c r="I52" s="5" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
     </row>
     <row r="53" customFormat="1" ht="25" customHeight="1" spans="1:9">
       <c r="A53" s="12" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C53" s="17" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D53" s="5"/>
       <c r="E53" s="5" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G53" s="5"/>
       <c r="H53" s="18" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="I53" s="5" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
     </row>
     <row r="54" customFormat="1" ht="25" customHeight="1" spans="1:9">
       <c r="A54" s="12" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C54" s="17" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="D54" s="5"/>
       <c r="E54" s="5" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G54" s="5"/>
       <c r="H54" s="18" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="I54" s="5" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
     </row>
     <row r="55" customFormat="1" ht="25" customHeight="1" spans="1:9">
       <c r="A55" s="12" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C55" s="19" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D55" s="5"/>
       <c r="E55" s="5" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G55" s="5"/>
       <c r="H55" s="18" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="I55" s="5" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
     </row>
     <row r="56" ht="25" customHeight="1" spans="1:9">
       <c r="A56" s="12" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C56" s="17" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="D56" s="5"/>
       <c r="E56" s="5" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G56" s="5"/>
       <c r="H56" s="18" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="I56" s="5" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
     </row>
     <row r="57" ht="25" customHeight="1" spans="1:9">
       <c r="A57" s="12" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C57" s="17" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="D57" s="5"/>
       <c r="E57" s="5" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G57" s="5"/>
       <c r="H57" s="18" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="I57" s="5" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
     </row>
     <row r="58" ht="25" customHeight="1" spans="1:9">
       <c r="A58" s="12" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C58" s="17" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D58" s="5"/>
       <c r="E58" s="5" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G58" s="5"/>
       <c r="H58" s="18" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="I58" s="5" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
     </row>
     <row r="59" ht="25" customHeight="1" spans="1:9">
       <c r="A59" s="12" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
       <c r="D59" s="5"/>
       <c r="E59" s="5"/>
       <c r="F59" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G59" s="5"/>
       <c r="H59" s="5"/>
       <c r="I59" s="5" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="60" ht="25" customHeight="1" spans="1:9">
       <c r="A60" s="12" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
       <c r="D60" s="5"/>
       <c r="E60" s="5"/>
       <c r="F60" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G60" s="5"/>
       <c r="H60" s="5"/>
       <c r="I60" s="5" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
     </row>
     <row r="61" ht="25" customHeight="1" spans="1:9">
       <c r="A61" s="12" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
       <c r="D61" s="5"/>
       <c r="E61" s="5"/>
       <c r="F61" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G61" s="5"/>
       <c r="H61" s="5"/>
       <c r="I61" s="5" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="62" customFormat="1" ht="25" customHeight="1" spans="1:9">
       <c r="A62" s="12" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B62" s="5"/>
       <c r="C62" s="5"/>
       <c r="D62" s="5"/>
       <c r="E62" s="5"/>
       <c r="F62" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G62" s="5"/>
       <c r="H62" s="5"/>
       <c r="I62" s="5" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
     </row>
     <row r="63" customFormat="1" ht="25" customHeight="1" spans="1:9">
       <c r="A63" s="12" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B63" s="5"/>
       <c r="C63" s="5"/>
       <c r="D63" s="5"/>
       <c r="E63" s="5"/>
       <c r="F63" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G63" s="5"/>
       <c r="H63" s="5"/>
       <c r="I63" s="5" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
     </row>
     <row r="64" customFormat="1" ht="25" customHeight="1" spans="1:9">
       <c r="A64" s="12" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B64" s="5"/>
       <c r="C64" s="5"/>
       <c r="D64" s="5"/>
       <c r="E64" s="5"/>
       <c r="F64" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G64" s="5"/>
       <c r="H64" s="5"/>
       <c r="I64" s="5" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="65" customFormat="1" ht="25" customHeight="1" spans="1:9">
       <c r="A65" s="12" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B65" s="5"/>
       <c r="C65" s="5"/>
       <c r="D65" s="5"/>
       <c r="E65" s="5"/>
       <c r="F65" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G65" s="5"/>
       <c r="H65" s="5"/>
       <c r="I65" s="5" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
     </row>
     <row r="66" ht="25" customHeight="1" spans="1:9">

--- a/资源录入表新.xlsx
+++ b/资源录入表新.xlsx
@@ -16,7 +16,7 @@
     <sheet name="资源录入表 (2)" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">资源录入表!$A$1:$O$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">资源录入表!$A$1:$O$66</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'资源录入表 (2)'!$A$2:$I$20</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="825" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="278">
   <si>
     <t>剧名</t>
   </si>
@@ -148,6 +148,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF111111"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>剧情</t>
     </r>
     <r>
@@ -221,10 +227,92 @@
     <t xml:space="preserve">链接: https://pan.baidu.com/s/1xgB5NP2JFKwnC0tnE_vV-Q 提取码: grug </t>
   </si>
   <si>
+    <t>杀手妈咪</t>
+  </si>
+  <si>
+    <t>韩剧</t>
+  </si>
+  <si>
+    <r>
+      <t>剧情</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF111111"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>惊悚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>孔晓振</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>郑浚远</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>李相二</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>成东日</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1nduXuhFEN-emGjxKdEnY-A 提取码: tsum </t>
+  </si>
+  <si>
     <t>给你梦想</t>
-  </si>
-  <si>
-    <t>韩剧</t>
   </si>
   <si>
     <t>喜剧/爱情</t>
@@ -1855,7 +1943,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1925,17 +2013,23 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2479,7 +2573,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O81"/>
+  <dimension ref="A1:O82"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="17.625" style="2" customWidth="1"/>
@@ -2546,7 +2640,7 @@
       <c r="D2" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="8">
+      <c r="E2" s="23">
         <v>6</v>
       </c>
       <c r="F2" s="22" t="s">
@@ -2561,12 +2655,12 @@
       <c r="I2" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="23"/>
-      <c r="K2" s="23"/>
-      <c r="L2" s="23"/>
-      <c r="M2" s="23"/>
-      <c r="N2" s="23"/>
-      <c r="O2" s="23"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="13"/>
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="13"/>
     </row>
     <row r="3" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A3" s="21" t="s">
@@ -2581,7 +2675,7 @@
       <c r="D3" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E3" s="23">
         <v>10</v>
       </c>
       <c r="F3" s="22" t="s">
@@ -2596,12 +2690,12 @@
       <c r="I3" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="J3" s="23"/>
-      <c r="K3" s="23"/>
-      <c r="L3" s="23"/>
-      <c r="M3" s="23"/>
-      <c r="N3" s="23"/>
-      <c r="O3" s="23"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="13"/>
+      <c r="M3" s="13"/>
+      <c r="N3" s="13"/>
+      <c r="O3" s="13"/>
     </row>
     <row r="4" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A4" s="21" t="s">
@@ -2616,7 +2710,7 @@
       <c r="D4" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="23">
         <v>24</v>
       </c>
       <c r="F4" s="22" t="s">
@@ -2631,14 +2725,14 @@
       <c r="I4" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="J4" s="23"/>
-      <c r="K4" s="23"/>
-      <c r="L4" s="23" t="s">
+      <c r="J4" s="13"/>
+      <c r="K4" s="13"/>
+      <c r="L4" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="M4" s="23"/>
-      <c r="N4" s="23"/>
-      <c r="O4" s="23"/>
+      <c r="M4" s="13"/>
+      <c r="N4" s="13"/>
+      <c r="O4" s="13"/>
     </row>
     <row r="5" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A5" s="21" t="s">
@@ -2653,7 +2747,7 @@
       <c r="D5" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="23">
         <v>20</v>
       </c>
       <c r="F5" s="22" t="s">
@@ -2668,12 +2762,12 @@
       <c r="I5" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="J5" s="23"/>
-      <c r="K5" s="23"/>
-      <c r="L5" s="23"/>
-      <c r="M5" s="23"/>
-      <c r="N5" s="23"/>
-      <c r="O5" s="23"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="13"/>
+      <c r="L5" s="13"/>
+      <c r="M5" s="13"/>
+      <c r="N5" s="13"/>
+      <c r="O5" s="13"/>
     </row>
     <row r="6" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A6" s="21" t="s">
@@ -2688,7 +2782,7 @@
       <c r="D6" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="23">
         <v>20</v>
       </c>
       <c r="F6" s="22" t="s">
@@ -2703,12 +2797,12 @@
       <c r="I6" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="J6" s="23"/>
-      <c r="K6" s="23"/>
-      <c r="L6" s="23"/>
-      <c r="M6" s="23"/>
-      <c r="N6" s="23"/>
-      <c r="O6" s="23"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="13"/>
+      <c r="M6" s="13"/>
+      <c r="N6" s="13"/>
+      <c r="O6" s="13"/>
     </row>
     <row r="7" ht="25" customHeight="1" spans="1:15">
       <c r="A7" s="12" t="s">
@@ -2723,7 +2817,7 @@
       <c r="D7" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="11">
+      <c r="E7" s="25">
         <v>14</v>
       </c>
       <c r="F7" s="13" t="s">
@@ -2773,12 +2867,12 @@
       <c r="I8" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="J8" s="23"/>
-      <c r="K8" s="23"/>
-      <c r="L8" s="23"/>
-      <c r="M8" s="23"/>
-      <c r="N8" s="23"/>
-      <c r="O8" s="23"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="13"/>
+      <c r="L8" s="13"/>
+      <c r="M8" s="13"/>
+      <c r="N8" s="13"/>
+      <c r="O8" s="13"/>
     </row>
     <row r="9" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A9" s="21" t="s">
@@ -2808,59 +2902,57 @@
       <c r="I9" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="J9" s="23"/>
-      <c r="K9" s="23"/>
-      <c r="L9" s="23"/>
-      <c r="M9" s="23"/>
-      <c r="N9" s="23"/>
-      <c r="O9" s="23"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="13"/>
+      <c r="L9" s="13"/>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13"/>
+      <c r="O9" s="13"/>
     </row>
     <row r="10" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C10" s="22" t="s">
+      <c r="C10" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="D10" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="22">
-        <v>6</v>
-      </c>
-      <c r="F10" s="22" t="s">
+      <c r="D10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="8">
+        <v>1</v>
+      </c>
+      <c r="F10" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G10" s="22">
+      <c r="G10" s="8">
         <v>2026</v>
       </c>
       <c r="H10" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="I10" s="22" t="s">
+      <c r="I10" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="J10" s="23"/>
-      <c r="K10" s="23"/>
-      <c r="L10" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="M10" s="23"/>
-      <c r="N10" s="23"/>
-      <c r="O10" s="23"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="13"/>
+      <c r="L10" s="13"/>
+      <c r="M10" s="13"/>
+      <c r="N10" s="13"/>
+      <c r="O10" s="13"/>
     </row>
     <row r="11" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A11" s="21" t="s">
         <v>53</v>
       </c>
       <c r="B11" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" s="22" t="s">
         <v>54</v>
-      </c>
-      <c r="C11" s="22" t="s">
-        <v>55</v>
       </c>
       <c r="D11" s="22" t="s">
         <v>14</v>
@@ -2875,35 +2967,35 @@
         <v>2026</v>
       </c>
       <c r="H11" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="I11" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="I11" s="22" t="s">
-        <v>57</v>
-      </c>
-      <c r="J11" s="23"/>
-      <c r="K11" s="23"/>
-      <c r="L11" s="23" t="s">
+      <c r="J11" s="13"/>
+      <c r="K11" s="13"/>
+      <c r="L11" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="M11" s="23"/>
-      <c r="N11" s="23"/>
-      <c r="O11" s="23"/>
+      <c r="M11" s="13"/>
+      <c r="N11" s="13"/>
+      <c r="O11" s="13"/>
     </row>
     <row r="12" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A12" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="B12" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="B12" s="22" t="s">
-        <v>49</v>
-      </c>
       <c r="C12" s="22" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="D12" s="22" t="s">
         <v>14</v>
       </c>
       <c r="E12" s="22">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F12" s="22" t="s">
         <v>15</v>
@@ -2912,35 +3004,35 @@
         <v>2026</v>
       </c>
       <c r="H12" s="22" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I12" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="J12" s="23"/>
-      <c r="K12" s="23"/>
-      <c r="L12" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="J12" s="13"/>
+      <c r="K12" s="13"/>
+      <c r="L12" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="M12" s="23"/>
-      <c r="N12" s="23"/>
-      <c r="O12" s="23"/>
+      <c r="M12" s="13"/>
+      <c r="N12" s="13"/>
+      <c r="O12" s="13"/>
     </row>
     <row r="13" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A13" s="21" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B13" s="22" t="s">
         <v>49</v>
       </c>
       <c r="C13" s="22" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D13" s="22" t="s">
         <v>14</v>
       </c>
       <c r="E13" s="22">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F13" s="22" t="s">
         <v>15</v>
@@ -2954,14 +3046,14 @@
       <c r="I13" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="J13" s="23"/>
-      <c r="K13" s="23"/>
-      <c r="L13" s="23" t="s">
+      <c r="J13" s="13"/>
+      <c r="K13" s="13"/>
+      <c r="L13" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="M13" s="23"/>
-      <c r="N13" s="23"/>
-      <c r="O13" s="23"/>
+      <c r="M13" s="13"/>
+      <c r="N13" s="13"/>
+      <c r="O13" s="13"/>
     </row>
     <row r="14" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A14" s="21" t="s">
@@ -2977,7 +3069,7 @@
         <v>14</v>
       </c>
       <c r="E14" s="22">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F14" s="22" t="s">
         <v>15</v>
@@ -2991,14 +3083,14 @@
       <c r="I14" s="22" t="s">
         <v>68</v>
       </c>
-      <c r="J14" s="23"/>
-      <c r="K14" s="23"/>
-      <c r="L14" s="23" t="s">
+      <c r="J14" s="13"/>
+      <c r="K14" s="13"/>
+      <c r="L14" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="M14" s="23"/>
-      <c r="N14" s="23"/>
-      <c r="O14" s="23"/>
+      <c r="M14" s="13"/>
+      <c r="N14" s="13"/>
+      <c r="O14" s="13"/>
     </row>
     <row r="15" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A15" s="21" t="s">
@@ -3014,7 +3106,7 @@
         <v>14</v>
       </c>
       <c r="E15" s="22">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F15" s="22" t="s">
         <v>15</v>
@@ -3028,30 +3120,30 @@
       <c r="I15" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="J15" s="23"/>
-      <c r="K15" s="23"/>
-      <c r="L15" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="M15" s="23"/>
-      <c r="N15" s="23"/>
-      <c r="O15" s="23"/>
+      <c r="J15" s="13"/>
+      <c r="K15" s="13"/>
+      <c r="L15" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="M15" s="13"/>
+      <c r="N15" s="13"/>
+      <c r="O15" s="13"/>
     </row>
     <row r="16" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A16" s="21" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B16" s="22" t="s">
         <v>49</v>
       </c>
       <c r="C16" s="22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D16" s="22" t="s">
         <v>14</v>
       </c>
       <c r="E16" s="22">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F16" s="22" t="s">
         <v>15</v>
@@ -3060,26 +3152,26 @@
         <v>2026</v>
       </c>
       <c r="H16" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="I16" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="I16" s="22" t="s">
+      <c r="J16" s="13"/>
+      <c r="K16" s="13"/>
+      <c r="L16" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="J16" s="23"/>
-      <c r="K16" s="23"/>
-      <c r="L16" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="M16" s="23"/>
-      <c r="N16" s="23"/>
-      <c r="O16" s="23"/>
+      <c r="M16" s="13"/>
+      <c r="N16" s="13"/>
+      <c r="O16" s="13"/>
     </row>
     <row r="17" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A17" s="21" t="s">
         <v>78</v>
       </c>
       <c r="B17" s="22" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C17" s="22" t="s">
         <v>79</v>
@@ -3088,7 +3180,7 @@
         <v>14</v>
       </c>
       <c r="E17" s="22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F17" s="22" t="s">
         <v>15</v>
@@ -3096,32 +3188,36 @@
       <c r="G17" s="22">
         <v>2026</v>
       </c>
-      <c r="H17" s="22"/>
+      <c r="H17" s="22" t="s">
+        <v>80</v>
+      </c>
       <c r="I17" s="22" t="s">
-        <v>80</v>
-      </c>
-      <c r="J17" s="23"/>
-      <c r="K17" s="23"/>
-      <c r="L17" s="23"/>
-      <c r="M17" s="23"/>
-      <c r="N17" s="23"/>
-      <c r="O17" s="23"/>
+        <v>81</v>
+      </c>
+      <c r="J17" s="13"/>
+      <c r="K17" s="13"/>
+      <c r="L17" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="M17" s="13"/>
+      <c r="N17" s="13"/>
+      <c r="O17" s="13"/>
     </row>
     <row r="18" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A18" s="21" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B18" s="22" t="s">
         <v>40</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D18" s="22" t="s">
         <v>14</v>
       </c>
       <c r="E18" s="22">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F18" s="22" t="s">
         <v>15</v>
@@ -3131,146 +3227,142 @@
       </c>
       <c r="H18" s="22"/>
       <c r="I18" s="22" t="s">
-        <v>83</v>
-      </c>
-      <c r="J18" s="23"/>
-      <c r="K18" s="23"/>
-      <c r="L18" s="23"/>
-      <c r="M18" s="23"/>
-      <c r="N18" s="23"/>
-      <c r="O18" s="23"/>
+        <v>84</v>
+      </c>
+      <c r="J18" s="13"/>
+      <c r="K18" s="13"/>
+      <c r="L18" s="13"/>
+      <c r="M18" s="13"/>
+      <c r="N18" s="13"/>
+      <c r="O18" s="13"/>
     </row>
     <row r="19" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A19" s="25" t="s">
-        <v>84</v>
-      </c>
-      <c r="B19" s="26" t="s">
+      <c r="A19" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="B19" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="C19" s="27" t="s">
-        <v>85</v>
+      <c r="C19" s="22" t="s">
+        <v>86</v>
       </c>
       <c r="D19" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="E19" s="27"/>
-      <c r="F19" s="27" t="s">
-        <v>86</v>
+      <c r="E19" s="22">
+        <v>4</v>
+      </c>
+      <c r="F19" s="22" t="s">
+        <v>15</v>
       </c>
       <c r="G19" s="22">
         <v>2026</v>
       </c>
       <c r="H19" s="22"/>
-      <c r="I19" s="26" t="s">
+      <c r="I19" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="J19" s="23"/>
-      <c r="K19" s="23"/>
-      <c r="L19" s="23"/>
-      <c r="M19" s="23"/>
-      <c r="N19" s="23"/>
-      <c r="O19" s="28"/>
+      <c r="J19" s="13"/>
+      <c r="K19" s="13"/>
+      <c r="L19" s="13"/>
+      <c r="M19" s="13"/>
+      <c r="N19" s="13"/>
+      <c r="O19" s="13"/>
     </row>
     <row r="20" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A20" s="25" t="s">
+      <c r="A20" s="28" t="s">
         <v>88</v>
       </c>
-      <c r="B20" s="26" t="s">
+      <c r="B20" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C20" s="27" t="s">
-        <v>85</v>
+      <c r="C20" s="29" t="s">
+        <v>89</v>
       </c>
       <c r="D20" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="E20" s="27"/>
-      <c r="F20" s="27" t="s">
-        <v>86</v>
+      <c r="E20" s="29"/>
+      <c r="F20" s="29" t="s">
+        <v>90</v>
       </c>
       <c r="G20" s="22">
         <v>2026</v>
       </c>
       <c r="H20" s="22"/>
-      <c r="I20" s="26" t="s">
+      <c r="I20" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="J20" s="13"/>
+      <c r="K20" s="13"/>
+      <c r="L20" s="13"/>
+      <c r="M20" s="13"/>
+      <c r="N20" s="13"/>
+      <c r="O20" s="30"/>
+    </row>
+    <row r="21" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A21" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" s="29" t="s">
         <v>89</v>
       </c>
-      <c r="J20" s="23"/>
-      <c r="K20" s="23"/>
-      <c r="L20" s="23"/>
-      <c r="M20" s="23"/>
-      <c r="N20" s="23"/>
-      <c r="O20" s="28"/>
-    </row>
-    <row r="21" ht="25" customHeight="1" spans="1:15">
-      <c r="A21" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="G21" s="5">
+      <c r="D21" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="E21" s="29"/>
+      <c r="F21" s="29" t="s">
+        <v>90</v>
+      </c>
+      <c r="G21" s="22">
         <v>2026</v>
       </c>
-      <c r="H21" s="5" t="s">
+      <c r="H21" s="22"/>
+      <c r="I21" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="I21" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="J21" s="5"/>
-      <c r="K21" s="5"/>
-      <c r="L21" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="M21" s="5"/>
-      <c r="N21" s="5"/>
-      <c r="O21" s="5"/>
+      <c r="J21" s="13"/>
+      <c r="K21" s="13"/>
+      <c r="L21" s="13"/>
+      <c r="M21" s="13"/>
+      <c r="N21" s="13"/>
+      <c r="O21" s="30"/>
     </row>
     <row r="22" ht="25" customHeight="1" spans="1:15">
       <c r="A22" s="12" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C22" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="G22" s="5">
+        <v>2026</v>
+      </c>
+      <c r="H22" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="D22" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E22" s="5" t="s">
+      <c r="I22" s="1" t="s">
         <v>98</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="G22" s="5">
-        <v>2025</v>
-      </c>
-      <c r="H22" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>100</v>
       </c>
       <c r="J22" s="5"/>
       <c r="K22" s="5"/>
       <c r="L22" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="M22" s="5"/>
       <c r="N22" s="5"/>
@@ -3278,36 +3370,36 @@
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:15">
       <c r="A23" s="12" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C23" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="G23" s="5">
+        <v>2025</v>
+      </c>
+      <c r="H23" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="D23" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E23" s="5" t="s">
+      <c r="I23" s="1" t="s">
         <v>104</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="G23" s="5">
-        <v>2026</v>
-      </c>
-      <c r="H23" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>106</v>
       </c>
       <c r="J23" s="5"/>
       <c r="K23" s="5"/>
       <c r="L23" s="5" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="M23" s="5"/>
       <c r="N23" s="5"/>
@@ -3315,36 +3407,36 @@
     </row>
     <row r="24" ht="25" customHeight="1" spans="1:15">
       <c r="A24" s="12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G24" s="5">
         <v>2026</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="J24" s="5"/>
       <c r="K24" s="5"/>
       <c r="L24" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M24" s="5"/>
       <c r="N24" s="5"/>
@@ -3352,36 +3444,36 @@
     </row>
     <row r="25" ht="25" customHeight="1" spans="1:15">
       <c r="A25" s="12" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C25" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="G25" s="5">
+        <v>2026</v>
+      </c>
+      <c r="H25" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="D25" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E25" s="5" t="s">
+      <c r="I25" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="G25" s="5">
-        <v>2025</v>
-      </c>
-      <c r="H25" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>118</v>
       </c>
       <c r="J25" s="5"/>
       <c r="K25" s="5"/>
       <c r="L25" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="M25" s="5"/>
       <c r="N25" s="5"/>
@@ -3389,173 +3481,173 @@
     </row>
     <row r="26" ht="25" customHeight="1" spans="1:15">
       <c r="A26" s="12" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C26" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="G26" s="5">
+        <v>2025</v>
+      </c>
+      <c r="H26" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="D26" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E26" s="5" t="s">
+      <c r="I26" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="F26" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="G26" s="5">
-        <v>2026</v>
-      </c>
-      <c r="H26" s="5" t="s">
+      <c r="J26" s="5"/>
+      <c r="K26" s="5"/>
+      <c r="L26" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="I26" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="J26" s="15"/>
-      <c r="K26" s="15"/>
-      <c r="L26" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="M26" s="15"/>
-      <c r="N26" s="15"/>
+      <c r="M26" s="5"/>
+      <c r="N26" s="5"/>
       <c r="O26" s="5"/>
     </row>
     <row r="27" ht="25" customHeight="1" spans="1:15">
       <c r="A27" s="12" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G27" s="5">
         <v>2026</v>
       </c>
       <c r="H27" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="J27" s="15"/>
+      <c r="K27" s="15"/>
+      <c r="L27" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="I27" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="J27" s="5"/>
-      <c r="K27" s="5"/>
-      <c r="L27" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="M27" s="5"/>
-      <c r="N27" s="5"/>
-      <c r="O27" s="29"/>
+      <c r="M27" s="15"/>
+      <c r="N27" s="15"/>
+      <c r="O27" s="5"/>
     </row>
     <row r="28" ht="25" customHeight="1" spans="1:15">
       <c r="A28" s="12" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C28" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="G28" s="5">
+        <v>2026</v>
+      </c>
+      <c r="H28" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="D28" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E28" s="5" t="s">
+      <c r="I28" s="5" t="s">
         <v>134</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="G28" s="5">
-        <v>2024</v>
-      </c>
-      <c r="H28" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="I28" s="5" t="s">
-        <v>136</v>
       </c>
       <c r="J28" s="5"/>
       <c r="K28" s="5"/>
       <c r="L28" s="5" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="M28" s="5"/>
       <c r="N28" s="5"/>
-      <c r="O28" s="29"/>
+      <c r="O28" s="31"/>
     </row>
     <row r="29" ht="25" customHeight="1" spans="1:15">
       <c r="A29" s="12" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G29" s="5">
         <v>2024</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="J29" s="5"/>
       <c r="K29" s="5"/>
       <c r="L29" s="5" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="M29" s="5"/>
       <c r="N29" s="5"/>
-      <c r="O29" s="29"/>
+      <c r="O29" s="31"/>
     </row>
     <row r="30" ht="25" customHeight="1" spans="1:15">
       <c r="A30" s="12" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>109</v>
+        <v>143</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>110</v>
+        <v>144</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G30" s="5">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="H30" s="5" t="s">
         <v>145</v>
@@ -3570,7 +3662,7 @@
       </c>
       <c r="M30" s="5"/>
       <c r="N30" s="5"/>
-      <c r="O30" s="29"/>
+      <c r="O30" s="31"/>
     </row>
     <row r="31" ht="25" customHeight="1" spans="1:15">
       <c r="A31" s="12" t="s">
@@ -3580,298 +3672,300 @@
         <v>12</v>
       </c>
       <c r="C31" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="G31" s="5">
+        <v>2026</v>
+      </c>
+      <c r="H31" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="D31" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E31" s="5" t="s">
+      <c r="I31" s="5" t="s">
         <v>150</v>
-      </c>
-      <c r="F31" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="G31" s="5">
-        <v>2025</v>
-      </c>
-      <c r="H31" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="I31" s="5" t="s">
-        <v>152</v>
       </c>
       <c r="J31" s="5"/>
       <c r="K31" s="5"/>
       <c r="L31" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="M31" s="5"/>
       <c r="N31" s="5"/>
-      <c r="O31" s="29"/>
+      <c r="O31" s="31"/>
     </row>
     <row r="32" ht="25" customHeight="1" spans="1:15">
       <c r="A32" s="12" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C32" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="G32" s="5">
+        <v>2025</v>
+      </c>
+      <c r="H32" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="D32" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="F32" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="G32" s="5">
-        <v>2026</v>
-      </c>
-      <c r="H32" s="5" t="s">
+      <c r="I32" s="5" t="s">
         <v>156</v>
-      </c>
-      <c r="I32" s="5" t="s">
-        <v>157</v>
       </c>
       <c r="J32" s="5"/>
       <c r="K32" s="5"/>
       <c r="L32" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="M32" s="5"/>
       <c r="N32" s="5"/>
-      <c r="O32" s="29"/>
+      <c r="O32" s="31"/>
     </row>
     <row r="33" ht="25" customHeight="1" spans="1:15">
       <c r="A33" s="12" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G33" s="5">
         <v>2026</v>
       </c>
       <c r="H33" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="I33" s="5" t="s">
         <v>161</v>
-      </c>
-      <c r="I33" s="5" t="s">
-        <v>162</v>
       </c>
       <c r="J33" s="5"/>
       <c r="K33" s="5"/>
       <c r="L33" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="M33" s="5"/>
       <c r="N33" s="5"/>
-      <c r="O33" s="29"/>
+      <c r="O33" s="31"/>
     </row>
     <row r="34" ht="25" customHeight="1" spans="1:15">
       <c r="A34" s="12" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>92</v>
+        <v>132</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G34" s="5">
         <v>2026</v>
       </c>
       <c r="H34" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="I34" s="5" t="s">
         <v>166</v>
-      </c>
-      <c r="I34" s="5" t="s">
-        <v>167</v>
       </c>
       <c r="J34" s="5"/>
       <c r="K34" s="5"/>
       <c r="L34" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="M34" s="5"/>
       <c r="N34" s="5"/>
-      <c r="O34" s="29"/>
+      <c r="O34" s="31"/>
     </row>
     <row r="35" ht="25" customHeight="1" spans="1:15">
       <c r="A35" s="12" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>115</v>
+        <v>169</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E35" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="G35" s="5">
+        <v>2026</v>
+      </c>
+      <c r="H35" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="F35" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="G35" s="5">
-        <v>2025</v>
-      </c>
-      <c r="H35" s="5" t="s">
+      <c r="I35" s="5" t="s">
         <v>171</v>
-      </c>
-      <c r="I35" s="5" t="s">
-        <v>172</v>
       </c>
       <c r="J35" s="5"/>
       <c r="K35" s="5"/>
       <c r="L35" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="M35" s="5"/>
       <c r="N35" s="5"/>
-      <c r="O35" s="29"/>
+      <c r="O35" s="31"/>
     </row>
     <row r="36" ht="25" customHeight="1" spans="1:15">
       <c r="A36" s="12" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C36" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="G36" s="5">
+        <v>2025</v>
+      </c>
+      <c r="H36" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="D36" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E36" s="5" t="s">
+      <c r="I36" s="5" t="s">
         <v>176</v>
-      </c>
-      <c r="F36" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="G36" s="5">
-        <v>2026</v>
-      </c>
-      <c r="H36" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="I36" s="5" t="s">
-        <v>178</v>
       </c>
       <c r="J36" s="5"/>
       <c r="K36" s="5"/>
       <c r="L36" s="5" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="M36" s="5"/>
       <c r="N36" s="5"/>
-      <c r="O36" s="29"/>
+      <c r="O36" s="31"/>
     </row>
     <row r="37" ht="25" customHeight="1" spans="1:15">
       <c r="A37" s="12" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>98</v>
+        <v>180</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G37" s="5">
         <v>2026</v>
       </c>
       <c r="H37" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="I37" s="5" t="s">
         <v>182</v>
-      </c>
-      <c r="I37" s="5" t="s">
-        <v>183</v>
       </c>
       <c r="J37" s="5"/>
       <c r="K37" s="5"/>
       <c r="L37" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="M37" s="5"/>
       <c r="N37" s="5"/>
-      <c r="O37" s="29"/>
+      <c r="O37" s="31"/>
     </row>
     <row r="38" ht="25" customHeight="1" spans="1:15">
       <c r="A38" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C38" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="D38" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="G38" s="5">
+        <v>2026</v>
+      </c>
+      <c r="H38" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="C38" s="5" t="s">
+      <c r="I38" s="5" t="s">
         <v>187</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E38" s="13" t="s">
-        <v>188</v>
-      </c>
-      <c r="F38" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="G38" s="5">
-        <v>2025</v>
-      </c>
-      <c r="H38" s="5"/>
-      <c r="I38" s="5" t="s">
-        <v>189</v>
       </c>
       <c r="J38" s="5"/>
       <c r="K38" s="5"/>
       <c r="L38" s="5" t="s">
-        <v>49</v>
+        <v>188</v>
       </c>
       <c r="M38" s="5"/>
       <c r="N38" s="5"/>
-      <c r="O38" s="29"/>
+      <c r="O38" s="31"/>
     </row>
     <row r="39" ht="25" customHeight="1" spans="1:15">
       <c r="A39" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="B39" s="5" t="s">
         <v>190</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>186</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>191</v>
@@ -3883,559 +3977,562 @@
         <v>192</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G39" s="5">
         <v>2025</v>
       </c>
-      <c r="H39" s="5" t="s">
+      <c r="H39" s="5"/>
+      <c r="I39" s="5" t="s">
         <v>193</v>
-      </c>
-      <c r="I39" s="5" t="s">
-        <v>194</v>
       </c>
       <c r="J39" s="5"/>
       <c r="K39" s="5"/>
       <c r="L39" s="5" t="s">
-        <v>195</v>
+        <v>49</v>
       </c>
       <c r="M39" s="5"/>
       <c r="N39" s="5"/>
-      <c r="O39" s="29"/>
+      <c r="O39" s="31"/>
     </row>
     <row r="40" ht="25" customHeight="1" spans="1:15">
       <c r="A40" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E40" s="13" t="s">
         <v>196</v>
       </c>
-      <c r="B40" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E40" s="26" t="s">
-        <v>188</v>
-      </c>
       <c r="F40" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G40" s="5">
         <v>2025</v>
       </c>
-      <c r="H40" s="5"/>
+      <c r="H40" s="5" t="s">
+        <v>197</v>
+      </c>
       <c r="I40" s="5" t="s">
         <v>198</v>
       </c>
       <c r="J40" s="5"/>
       <c r="K40" s="5"/>
       <c r="L40" s="5" t="s">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="M40" s="5"/>
       <c r="N40" s="5"/>
-      <c r="O40" s="29"/>
+      <c r="O40" s="31"/>
     </row>
     <row r="41" ht="25" customHeight="1" spans="1:15">
       <c r="A41" s="12" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E41" s="5" t="s">
-        <v>104</v>
+      <c r="E41" s="13" t="s">
+        <v>192</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G41" s="5">
-        <v>2026</v>
-      </c>
-      <c r="H41" s="5" t="s">
-        <v>201</v>
-      </c>
+        <v>2025</v>
+      </c>
+      <c r="H41" s="5"/>
       <c r="I41" s="5" t="s">
         <v>202</v>
       </c>
       <c r="J41" s="5"/>
       <c r="K41" s="5"/>
       <c r="L41" s="5" t="s">
-        <v>203</v>
+        <v>49</v>
       </c>
       <c r="M41" s="5"/>
       <c r="N41" s="5"/>
-      <c r="O41" s="29"/>
+      <c r="O41" s="31"/>
     </row>
     <row r="42" ht="25" customHeight="1" spans="1:15">
       <c r="A42" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="C42" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="B42" s="5"/>
-      <c r="C42" s="5"/>
-      <c r="D42" s="5"/>
-      <c r="E42" s="5"/>
+      <c r="D42" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>108</v>
+      </c>
       <c r="F42" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="G42" s="5"/>
-      <c r="H42" s="5"/>
+        <v>90</v>
+      </c>
+      <c r="G42" s="5">
+        <v>2026</v>
+      </c>
+      <c r="H42" s="5" t="s">
+        <v>205</v>
+      </c>
       <c r="I42" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="J42" s="5"/>
       <c r="K42" s="5"/>
-      <c r="L42" s="5"/>
+      <c r="L42" s="5" t="s">
+        <v>207</v>
+      </c>
       <c r="M42" s="5"/>
       <c r="N42" s="5"/>
-      <c r="O42" s="29"/>
+      <c r="O42" s="31"/>
     </row>
     <row r="43" ht="25" customHeight="1" spans="1:15">
       <c r="A43" s="12" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5"/>
       <c r="D43" s="5"/>
       <c r="E43" s="5"/>
       <c r="F43" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G43" s="5"/>
       <c r="H43" s="5"/>
       <c r="I43" s="5" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="J43" s="5"/>
       <c r="K43" s="5"/>
       <c r="L43" s="5"/>
       <c r="M43" s="5"/>
       <c r="N43" s="5"/>
-      <c r="O43" s="29"/>
+      <c r="O43" s="31"/>
     </row>
     <row r="44" ht="25" customHeight="1" spans="1:15">
       <c r="A44" s="12" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
       <c r="D44" s="5"/>
       <c r="E44" s="5"/>
       <c r="F44" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G44" s="5"/>
       <c r="H44" s="5"/>
       <c r="I44" s="5" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="J44" s="5"/>
       <c r="K44" s="5"/>
       <c r="L44" s="5"/>
       <c r="M44" s="5"/>
       <c r="N44" s="5"/>
-      <c r="O44" s="29"/>
+      <c r="O44" s="31"/>
     </row>
     <row r="45" ht="25" customHeight="1" spans="1:15">
       <c r="A45" s="12" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5"/>
       <c r="D45" s="5"/>
       <c r="E45" s="5"/>
       <c r="F45" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G45" s="5"/>
       <c r="H45" s="5"/>
       <c r="I45" s="5" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="J45" s="5"/>
       <c r="K45" s="5"/>
       <c r="L45" s="5"/>
       <c r="M45" s="5"/>
       <c r="N45" s="5"/>
-      <c r="O45" s="29"/>
+      <c r="O45" s="31"/>
     </row>
     <row r="46" ht="25" customHeight="1" spans="1:15">
-      <c r="A46" s="14" t="s">
-        <v>212</v>
-      </c>
-      <c r="B46" s="15"/>
-      <c r="C46" s="15"/>
-      <c r="D46" s="15"/>
-      <c r="E46" s="15"/>
+      <c r="A46" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="B46" s="5"/>
+      <c r="C46" s="5"/>
+      <c r="D46" s="5"/>
+      <c r="E46" s="5"/>
       <c r="F46" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="G46" s="15"/>
-      <c r="H46" s="15"/>
-      <c r="I46" s="16" t="s">
-        <v>213</v>
-      </c>
-      <c r="J46" s="15"/>
+        <v>90</v>
+      </c>
+      <c r="G46" s="5"/>
+      <c r="H46" s="5"/>
+      <c r="I46" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="J46" s="5"/>
       <c r="K46" s="5"/>
       <c r="L46" s="5"/>
       <c r="M46" s="5"/>
       <c r="N46" s="5"/>
-      <c r="O46" s="29"/>
+      <c r="O46" s="31"/>
     </row>
     <row r="47" ht="25" customHeight="1" spans="1:15">
-      <c r="A47" s="12" t="s">
-        <v>214</v>
-      </c>
-      <c r="B47" s="5"/>
-      <c r="C47" s="5"/>
-      <c r="D47" s="5"/>
-      <c r="E47" s="5"/>
+      <c r="A47" s="14" t="s">
+        <v>216</v>
+      </c>
+      <c r="B47" s="15"/>
+      <c r="C47" s="15"/>
+      <c r="D47" s="15"/>
+      <c r="E47" s="15"/>
       <c r="F47" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="G47" s="5"/>
-      <c r="H47" s="5"/>
-      <c r="I47" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="J47" s="5"/>
+        <v>90</v>
+      </c>
+      <c r="G47" s="15"/>
+      <c r="H47" s="15"/>
+      <c r="I47" s="16" t="s">
+        <v>217</v>
+      </c>
+      <c r="J47" s="15"/>
       <c r="K47" s="5"/>
       <c r="L47" s="5"/>
       <c r="M47" s="5"/>
       <c r="N47" s="5"/>
-      <c r="O47" s="29"/>
+      <c r="O47" s="31"/>
     </row>
     <row r="48" ht="25" customHeight="1" spans="1:15">
       <c r="A48" s="12" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
       <c r="D48" s="5"/>
       <c r="E48" s="5"/>
       <c r="F48" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G48" s="5"/>
       <c r="H48" s="5"/>
       <c r="I48" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="J48" s="5"/>
       <c r="K48" s="5"/>
       <c r="L48" s="5"/>
       <c r="M48" s="5"/>
       <c r="N48" s="5"/>
-      <c r="O48" s="29"/>
+      <c r="O48" s="31"/>
     </row>
     <row r="49" ht="25" customHeight="1" spans="1:15">
       <c r="A49" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
       <c r="D49" s="5"/>
       <c r="E49" s="5"/>
       <c r="F49" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G49" s="5"/>
       <c r="H49" s="5"/>
       <c r="I49" s="5" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="J49" s="5"/>
       <c r="K49" s="5"/>
       <c r="L49" s="5"/>
       <c r="M49" s="5"/>
       <c r="N49" s="5"/>
-      <c r="O49" s="29"/>
+      <c r="O49" s="31"/>
     </row>
     <row r="50" ht="25" customHeight="1" spans="1:15">
       <c r="A50" s="12" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5"/>
       <c r="D50" s="5"/>
       <c r="E50" s="5"/>
       <c r="F50" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G50" s="5"/>
       <c r="H50" s="5"/>
       <c r="I50" s="5" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="J50" s="5"/>
       <c r="K50" s="5"/>
       <c r="L50" s="5"/>
       <c r="M50" s="5"/>
       <c r="N50" s="5"/>
-      <c r="O50" s="29"/>
+      <c r="O50" s="31"/>
     </row>
     <row r="51" ht="25" customHeight="1" spans="1:15">
       <c r="A51" s="12" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
       <c r="D51" s="5"/>
       <c r="E51" s="5"/>
       <c r="F51" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G51" s="5"/>
       <c r="H51" s="5"/>
       <c r="I51" s="5" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="J51" s="5"/>
       <c r="K51" s="5"/>
       <c r="L51" s="5"/>
       <c r="M51" s="5"/>
       <c r="N51" s="5"/>
-      <c r="O51" s="29"/>
+      <c r="O51" s="31"/>
     </row>
     <row r="52" ht="25" customHeight="1" spans="1:15">
       <c r="A52" s="12" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5"/>
       <c r="D52" s="5"/>
       <c r="E52" s="5"/>
       <c r="F52" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G52" s="5"/>
       <c r="H52" s="5"/>
       <c r="I52" s="5" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="J52" s="5"/>
       <c r="K52" s="5"/>
       <c r="L52" s="5"/>
       <c r="M52" s="5"/>
       <c r="N52" s="5"/>
-      <c r="O52" s="29"/>
+      <c r="O52" s="31"/>
     </row>
     <row r="53" ht="25" customHeight="1" spans="1:15">
       <c r="A53" s="12" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5"/>
       <c r="D53" s="5"/>
       <c r="E53" s="5"/>
       <c r="F53" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G53" s="5"/>
       <c r="H53" s="5"/>
       <c r="I53" s="5" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="J53" s="5"/>
       <c r="K53" s="5"/>
       <c r="L53" s="5"/>
       <c r="M53" s="5"/>
       <c r="N53" s="5"/>
-      <c r="O53" s="29"/>
+      <c r="O53" s="31"/>
     </row>
     <row r="54" ht="25" customHeight="1" spans="1:15">
       <c r="A54" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
       <c r="D54" s="5"/>
       <c r="E54" s="5"/>
       <c r="F54" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G54" s="5"/>
       <c r="H54" s="5"/>
       <c r="I54" s="5" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="J54" s="5"/>
       <c r="K54" s="5"/>
       <c r="L54" s="5"/>
       <c r="M54" s="5"/>
       <c r="N54" s="5"/>
-      <c r="O54" s="29"/>
+      <c r="O54" s="31"/>
     </row>
     <row r="55" ht="25" customHeight="1" spans="1:15">
       <c r="A55" s="12" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B55" s="5"/>
       <c r="C55" s="5"/>
       <c r="D55" s="5"/>
       <c r="E55" s="5"/>
       <c r="F55" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G55" s="5"/>
-      <c r="H55" s="5"/>
       <c r="I55" s="5" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="J55" s="5"/>
       <c r="K55" s="5"/>
       <c r="L55" s="5"/>
       <c r="M55" s="5"/>
       <c r="N55" s="5"/>
-      <c r="O55" s="29"/>
-    </row>
-    <row r="56" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="O55" s="31"/>
+    </row>
+    <row r="56" ht="25" customHeight="1" spans="1:15">
       <c r="A56" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
       <c r="D56" s="5"/>
       <c r="E56" s="5"/>
       <c r="F56" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G56" s="5"/>
       <c r="H56" s="5"/>
       <c r="I56" s="5" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="J56" s="5"/>
       <c r="K56" s="5"/>
       <c r="L56" s="5"/>
       <c r="M56" s="5"/>
       <c r="N56" s="5"/>
-      <c r="O56" s="29"/>
+      <c r="O56" s="31"/>
     </row>
     <row r="57" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A57" s="12" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
       <c r="D57" s="5"/>
       <c r="E57" s="5"/>
       <c r="F57" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G57" s="5"/>
       <c r="H57" s="5"/>
       <c r="I57" s="5" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="J57" s="5"/>
       <c r="K57" s="5"/>
       <c r="L57" s="5"/>
       <c r="M57" s="5"/>
       <c r="N57" s="5"/>
-      <c r="O57" s="29"/>
+      <c r="O57" s="31"/>
     </row>
     <row r="58" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A58" s="12" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
       <c r="D58" s="5"/>
       <c r="E58" s="5"/>
       <c r="F58" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G58" s="5"/>
       <c r="H58" s="5"/>
       <c r="I58" s="5" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J58" s="5"/>
       <c r="K58" s="5"/>
       <c r="L58" s="5"/>
       <c r="M58" s="5"/>
       <c r="N58" s="5"/>
-      <c r="O58" s="29"/>
+      <c r="O58" s="31"/>
     </row>
     <row r="59" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A59" s="12" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
       <c r="D59" s="5"/>
       <c r="E59" s="5"/>
       <c r="F59" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G59" s="5"/>
       <c r="H59" s="5"/>
       <c r="I59" s="5" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J59" s="5"/>
       <c r="K59" s="5"/>
       <c r="L59" s="5"/>
       <c r="M59" s="5"/>
       <c r="N59" s="5"/>
-      <c r="O59" s="29"/>
+      <c r="O59" s="31"/>
     </row>
     <row r="60" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A60" s="12" t="s">
-        <v>240</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C60" s="17" t="s">
-        <v>241</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="B60" s="5"/>
+      <c r="C60" s="5"/>
       <c r="D60" s="5"/>
-      <c r="E60" s="5" t="s">
-        <v>242</v>
-      </c>
+      <c r="E60" s="5"/>
       <c r="F60" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G60" s="5"/>
-      <c r="H60" s="18" t="s">
+      <c r="H60" s="5"/>
+      <c r="I60" s="5" t="s">
         <v>243</v>
-      </c>
-      <c r="I60" s="5" t="s">
-        <v>244</v>
       </c>
       <c r="J60" s="5"/>
       <c r="K60" s="5"/>
       <c r="L60" s="5"/>
       <c r="M60" s="5"/>
       <c r="N60" s="5"/>
-      <c r="O60" s="29"/>
+      <c r="O60" s="31"/>
     </row>
     <row r="61" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A61" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C61" s="17" t="s">
         <v>245</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="C61" s="17" t="s">
-        <v>246</v>
       </c>
       <c r="D61" s="5"/>
       <c r="E61" s="5" t="s">
-        <v>104</v>
+        <v>246</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G61" s="5"/>
       <c r="H61" s="18" t="s">
@@ -4449,24 +4546,24 @@
       <c r="L61" s="5"/>
       <c r="M61" s="5"/>
       <c r="N61" s="5"/>
-      <c r="O61" s="5"/>
+      <c r="O61" s="31"/>
     </row>
     <row r="62" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A62" s="12" t="s">
         <v>249</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C62" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="C62" s="17" t="s">
         <v>250</v>
       </c>
       <c r="D62" s="5"/>
       <c r="E62" s="5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G62" s="5"/>
       <c r="H62" s="18" t="s">
@@ -4480,55 +4577,55 @@
       <c r="L62" s="5"/>
       <c r="M62" s="5"/>
       <c r="N62" s="5"/>
-      <c r="O62" s="29"/>
-    </row>
-    <row r="63" ht="25" customHeight="1" spans="1:15">
+      <c r="O62" s="5"/>
+    </row>
+    <row r="63" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A63" s="12" t="s">
         <v>253</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C63" s="17" t="s">
+      <c r="C63" s="19" t="s">
         <v>254</v>
       </c>
       <c r="D63" s="5"/>
       <c r="E63" s="5" t="s">
-        <v>255</v>
+        <v>114</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G63" s="5"/>
       <c r="H63" s="18" t="s">
+        <v>255</v>
+      </c>
+      <c r="I63" s="5" t="s">
         <v>256</v>
-      </c>
-      <c r="I63" s="5" t="s">
-        <v>257</v>
       </c>
       <c r="J63" s="5"/>
       <c r="K63" s="5"/>
       <c r="L63" s="5"/>
       <c r="M63" s="5"/>
       <c r="N63" s="5"/>
-      <c r="O63" s="29"/>
+      <c r="O63" s="31"/>
     </row>
     <row r="64" ht="25" customHeight="1" spans="1:15">
       <c r="A64" s="12" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C64" s="17" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D64" s="5"/>
       <c r="E64" s="5" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G64" s="5"/>
       <c r="H64" s="18" t="s">
@@ -4542,55 +4639,69 @@
       <c r="L64" s="5"/>
       <c r="M64" s="5"/>
       <c r="N64" s="5"/>
-      <c r="O64" s="29"/>
+      <c r="O64" s="31"/>
     </row>
     <row r="65" ht="25" customHeight="1" spans="1:15">
       <c r="A65" s="12" t="s">
         <v>262</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="C65" s="17" t="s">
         <v>263</v>
       </c>
       <c r="D65" s="5"/>
       <c r="E65" s="5" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G65" s="5"/>
       <c r="H65" s="18" t="s">
+        <v>264</v>
+      </c>
+      <c r="I65" s="5" t="s">
         <v>265</v>
-      </c>
-      <c r="I65" s="5" t="s">
-        <v>266</v>
       </c>
       <c r="J65" s="5"/>
       <c r="K65" s="5"/>
       <c r="L65" s="5"/>
       <c r="M65" s="5"/>
       <c r="N65" s="5"/>
-      <c r="O65" s="29"/>
+      <c r="O65" s="31"/>
     </row>
     <row r="66" ht="25" customHeight="1" spans="1:15">
-      <c r="A66" s="12"/>
-      <c r="B66" s="5"/>
-      <c r="C66" s="5"/>
+      <c r="A66" s="12" t="s">
+        <v>266</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C66" s="17" t="s">
+        <v>267</v>
+      </c>
       <c r="D66" s="5"/>
-      <c r="E66" s="5"/>
-      <c r="F66" s="13"/>
+      <c r="E66" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="F66" s="5" t="s">
+        <v>90</v>
+      </c>
       <c r="G66" s="5"/>
-      <c r="H66" s="5"/>
-      <c r="I66" s="5"/>
+      <c r="H66" s="18" t="s">
+        <v>269</v>
+      </c>
+      <c r="I66" s="5" t="s">
+        <v>270</v>
+      </c>
       <c r="J66" s="5"/>
       <c r="K66" s="5"/>
       <c r="L66" s="5"/>
       <c r="M66" s="5"/>
       <c r="N66" s="5"/>
-      <c r="O66" s="5"/>
+      <c r="O66" s="31"/>
     </row>
     <row r="67" ht="25" customHeight="1" spans="1:15">
       <c r="A67" s="12"/>
@@ -4617,6 +4728,7 @@
       <c r="E68" s="5"/>
       <c r="F68" s="13"/>
       <c r="G68" s="5"/>
+      <c r="H68" s="5"/>
       <c r="I68" s="5"/>
       <c r="J68" s="5"/>
       <c r="K68" s="5"/>
@@ -4633,7 +4745,6 @@
       <c r="E69" s="5"/>
       <c r="F69" s="13"/>
       <c r="G69" s="5"/>
-      <c r="H69" s="5"/>
       <c r="I69" s="5"/>
       <c r="J69" s="5"/>
       <c r="K69" s="5"/>
@@ -4846,16 +4957,33 @@
       <c r="N81" s="5"/>
       <c r="O81" s="5"/>
     </row>
+    <row r="82" ht="25" customHeight="1" spans="1:15">
+      <c r="A82" s="12"/>
+      <c r="B82" s="5"/>
+      <c r="C82" s="5"/>
+      <c r="D82" s="5"/>
+      <c r="E82" s="5"/>
+      <c r="F82" s="13"/>
+      <c r="G82" s="5"/>
+      <c r="H82" s="5"/>
+      <c r="I82" s="5"/>
+      <c r="J82" s="5"/>
+      <c r="K82" s="5"/>
+      <c r="L82" s="5"/>
+      <c r="M82" s="5"/>
+      <c r="N82" s="5"/>
+      <c r="O82" s="5"/>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:O65" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A1:O65">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:O66" etc:filterBottomFollowUsedRange="0">
+    <sortState ref="A1:O66">
       <sortCondition ref="F1"/>
     </sortState>
     <extLst/>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="H61" r:id="rId1" display="普洛伊湘普·素帕莎 / 芭莉雅皮·余 " tooltip="https://www.douban.com/personage/30264980/"/>
-    <hyperlink ref="H16" r:id="rId2" display="金贤叙/郑明哲" tooltip="https://www.douban.com/personage/37338980/"/>
+    <hyperlink ref="H62" r:id="rId1" display="普洛伊湘普·素帕莎 / 芭莉雅皮·余 " tooltip="https://www.douban.com/personage/30264980/"/>
+    <hyperlink ref="H17" r:id="rId2" display="金贤叙/郑明哲" tooltip="https://www.douban.com/personage/37338980/"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -4879,7 +5007,7 @@
   <sheetData>
     <row r="1" ht="33" customHeight="1" spans="1:9">
       <c r="A1" s="3" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -4926,7 +5054,7 @@
         <v>12</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>14</v>
@@ -5123,13 +5251,13 @@
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:9">
       <c r="A10" s="6" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>49</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>14</v>
@@ -5144,21 +5272,21 @@
         <v>2026</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:9">
       <c r="A11" s="6" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>14</v>
@@ -5173,21 +5301,21 @@
         <v>2026</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:9">
       <c r="A12" s="6" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>49</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>14</v>
@@ -5202,21 +5330,21 @@
         <v>2026</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:9">
       <c r="A13" s="6" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>49</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>14</v>
@@ -5231,21 +5359,21 @@
         <v>2026</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:9">
       <c r="A14" s="6" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>49</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>14</v>
@@ -5260,21 +5388,21 @@
         <v>2026</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:9">
       <c r="A15" s="6" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>49</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>14</v>
@@ -5289,21 +5417,21 @@
         <v>2026</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:9">
       <c r="A16" s="6" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>49</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>14</v>
@@ -5318,21 +5446,21 @@
         <v>2026</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:9">
       <c r="A17" s="6" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>40</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>14</v>
@@ -5348,18 +5476,18 @@
       </c>
       <c r="H17" s="7"/>
       <c r="I17" s="8" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:9">
       <c r="A18" s="6" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>40</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>14</v>
@@ -5375,1118 +5503,1118 @@
       </c>
       <c r="H18" s="7"/>
       <c r="I18" s="8" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" spans="1:9">
       <c r="A19" s="9" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>40</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>14</v>
       </c>
       <c r="E19" s="10"/>
       <c r="F19" s="10" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G19" s="7">
         <v>2026</v>
       </c>
       <c r="H19" s="7"/>
       <c r="I19" s="11" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" spans="1:9">
       <c r="A20" s="9" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>40</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>14</v>
       </c>
       <c r="E20" s="10"/>
       <c r="F20" s="10" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G20" s="7">
         <v>2026</v>
       </c>
       <c r="H20" s="7"/>
       <c r="I20" s="11" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1" spans="1:9">
       <c r="A21" s="12" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G21" s="5">
         <v>2026</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1" spans="1:9">
       <c r="A22" s="12" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G22" s="5">
         <v>2025</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1" spans="1:9">
       <c r="A23" s="12" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G23" s="5">
         <v>2026</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1" spans="1:9">
       <c r="A24" s="12" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G24" s="5">
         <v>2026</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1" spans="1:9">
       <c r="A25" s="12" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G25" s="5">
         <v>2025</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1" spans="1:9">
       <c r="A26" s="12" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G26" s="5">
         <v>2026</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1" spans="1:9">
       <c r="A27" s="12" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G27" s="5">
         <v>2026</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1" spans="1:9">
       <c r="A28" s="12" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G28" s="5">
         <v>2024</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="29" ht="25" customHeight="1" spans="1:9">
       <c r="A29" s="12" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G29" s="5">
         <v>2024</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="30" ht="25" customHeight="1" spans="1:9">
       <c r="A30" s="12" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G30" s="5">
         <v>2026</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="31" ht="25" customHeight="1" spans="1:9">
       <c r="A31" s="12" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G31" s="5">
         <v>2025</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="32" ht="25" customHeight="1" spans="1:9">
       <c r="A32" s="12" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G32" s="5">
         <v>2026</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="33" ht="25" customHeight="1" spans="1:9">
       <c r="A33" s="12" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G33" s="5">
         <v>2026</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="I33" s="5" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
     </row>
     <row r="34" ht="25" customHeight="1" spans="1:9">
       <c r="A34" s="12" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G34" s="5">
         <v>2026</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="35" ht="25" customHeight="1" spans="1:9">
       <c r="A35" s="12" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G35" s="5">
         <v>2025</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
     </row>
     <row r="36" ht="25" customHeight="1" spans="1:9">
       <c r="A36" s="12" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G36" s="5">
         <v>2026</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
     </row>
     <row r="37" ht="25" customHeight="1" spans="1:9">
       <c r="A37" s="12" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G37" s="5">
         <v>2026</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="I37" s="5" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="38" ht="25" customHeight="1" spans="1:9">
       <c r="A38" s="12" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G38" s="5">
         <v>2025</v>
       </c>
       <c r="H38" s="5"/>
       <c r="I38" s="5" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
     </row>
     <row r="39" ht="25" customHeight="1" spans="1:9">
       <c r="A39" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="B39" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="B39" s="5" t="s">
-        <v>186</v>
-      </c>
       <c r="C39" s="5" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G39" s="5">
         <v>2025</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="I39" s="5" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
     </row>
     <row r="40" ht="25" customHeight="1" spans="1:9">
       <c r="A40" s="12" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="D40" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G40" s="5">
         <v>2025</v>
       </c>
       <c r="H40" s="5"/>
       <c r="I40" s="5" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="41" ht="25" customHeight="1" spans="1:9">
       <c r="A41" s="12" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G41" s="5">
         <v>2026</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="I41" s="5" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
     </row>
     <row r="42" ht="25" customHeight="1" spans="1:9">
       <c r="A42" s="12" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5"/>
       <c r="D42" s="5"/>
       <c r="E42" s="5"/>
       <c r="F42" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G42" s="5"/>
       <c r="H42" s="5"/>
       <c r="I42" s="5" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
     </row>
     <row r="43" ht="25" customHeight="1" spans="1:9">
       <c r="A43" s="12" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5"/>
       <c r="D43" s="5"/>
       <c r="E43" s="5"/>
       <c r="F43" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G43" s="5"/>
       <c r="H43" s="5"/>
       <c r="I43" s="5" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="44" ht="25" customHeight="1" spans="1:9">
       <c r="A44" s="12" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
       <c r="D44" s="5"/>
       <c r="E44" s="5"/>
       <c r="F44" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G44" s="5"/>
       <c r="H44" s="5"/>
       <c r="I44" s="5" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
     </row>
     <row r="45" ht="25" customHeight="1" spans="1:9">
       <c r="A45" s="12" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5"/>
       <c r="D45" s="5"/>
       <c r="E45" s="5"/>
       <c r="F45" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G45" s="5"/>
       <c r="H45" s="5"/>
       <c r="I45" s="5" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="46" ht="25" customHeight="1" spans="1:9">
       <c r="A46" s="14" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B46" s="15"/>
       <c r="C46" s="15"/>
       <c r="D46" s="15"/>
       <c r="E46" s="15"/>
       <c r="F46" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G46" s="15"/>
       <c r="H46" s="15"/>
       <c r="I46" s="16" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
     </row>
     <row r="47" ht="25" customHeight="1" spans="1:9">
       <c r="A47" s="12" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
       <c r="D47" s="5"/>
       <c r="E47" s="5"/>
       <c r="F47" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G47" s="5"/>
       <c r="H47" s="5"/>
       <c r="I47" s="5" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="48" ht="25" customHeight="1" spans="1:9">
       <c r="A48" s="12" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
       <c r="D48" s="5"/>
       <c r="E48" s="5"/>
       <c r="F48" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G48" s="5"/>
       <c r="H48" s="5"/>
       <c r="I48" s="5" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
     </row>
     <row r="49" ht="25" customHeight="1" spans="1:9">
       <c r="A49" s="12" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
       <c r="D49" s="5"/>
       <c r="E49" s="5"/>
       <c r="F49" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G49" s="5"/>
       <c r="H49" s="5"/>
       <c r="I49" s="5" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
     </row>
     <row r="50" ht="25" customHeight="1" spans="1:9">
       <c r="A50" s="12" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5"/>
       <c r="D50" s="5"/>
       <c r="E50" s="5"/>
       <c r="F50" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G50" s="5"/>
       <c r="H50" s="5"/>
       <c r="I50" s="5" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
     </row>
     <row r="51" ht="25" customHeight="1" spans="1:9">
       <c r="A51" s="12" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
       <c r="D51" s="5"/>
       <c r="E51" s="5"/>
       <c r="F51" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G51" s="5"/>
       <c r="H51" s="5"/>
       <c r="I51" s="5" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="52" ht="25" customHeight="1" spans="1:9">
       <c r="A52" s="12" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5"/>
       <c r="D52" s="5"/>
       <c r="E52" s="5"/>
       <c r="F52" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G52" s="5"/>
       <c r="H52" s="5"/>
       <c r="I52" s="5" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
     </row>
     <row r="53" customFormat="1" ht="25" customHeight="1" spans="1:9">
       <c r="A53" s="12" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C53" s="17" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="D53" s="5"/>
       <c r="E53" s="5" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G53" s="5"/>
       <c r="H53" s="18" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="I53" s="5" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
     </row>
     <row r="54" customFormat="1" ht="25" customHeight="1" spans="1:9">
       <c r="A54" s="12" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C54" s="17" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D54" s="5"/>
       <c r="E54" s="5" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G54" s="5"/>
       <c r="H54" s="18" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="I54" s="5" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
     </row>
     <row r="55" customFormat="1" ht="25" customHeight="1" spans="1:9">
       <c r="A55" s="12" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C55" s="19" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="D55" s="5"/>
       <c r="E55" s="5" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G55" s="5"/>
       <c r="H55" s="18" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="I55" s="5" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
     </row>
     <row r="56" ht="25" customHeight="1" spans="1:9">
       <c r="A56" s="12" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C56" s="17" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="D56" s="5"/>
       <c r="E56" s="5" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G56" s="5"/>
       <c r="H56" s="18" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="I56" s="5" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
     </row>
     <row r="57" ht="25" customHeight="1" spans="1:9">
       <c r="A57" s="12" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C57" s="17" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D57" s="5"/>
       <c r="E57" s="5" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G57" s="5"/>
       <c r="H57" s="18" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="I57" s="5" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
     </row>
     <row r="58" ht="25" customHeight="1" spans="1:9">
       <c r="A58" s="12" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>49</v>
       </c>
       <c r="C58" s="17" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D58" s="5"/>
       <c r="E58" s="5" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G58" s="5"/>
       <c r="H58" s="18" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="I58" s="5" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="59" ht="25" customHeight="1" spans="1:9">
       <c r="A59" s="12" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
       <c r="D59" s="5"/>
       <c r="E59" s="5"/>
       <c r="F59" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G59" s="5"/>
       <c r="H59" s="5"/>
       <c r="I59" s="5" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="60" ht="25" customHeight="1" spans="1:9">
       <c r="A60" s="12" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
       <c r="D60" s="5"/>
       <c r="E60" s="5"/>
       <c r="F60" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G60" s="5"/>
       <c r="H60" s="5"/>
       <c r="I60" s="5" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
     </row>
     <row r="61" ht="25" customHeight="1" spans="1:9">
       <c r="A61" s="12" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
       <c r="D61" s="5"/>
       <c r="E61" s="5"/>
       <c r="F61" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G61" s="5"/>
       <c r="H61" s="5"/>
       <c r="I61" s="5" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
     </row>
     <row r="62" customFormat="1" ht="25" customHeight="1" spans="1:9">
       <c r="A62" s="12" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B62" s="5"/>
       <c r="C62" s="5"/>
       <c r="D62" s="5"/>
       <c r="E62" s="5"/>
       <c r="F62" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G62" s="5"/>
       <c r="H62" s="5"/>
       <c r="I62" s="5" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="63" customFormat="1" ht="25" customHeight="1" spans="1:9">
       <c r="A63" s="12" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B63" s="5"/>
       <c r="C63" s="5"/>
       <c r="D63" s="5"/>
       <c r="E63" s="5"/>
       <c r="F63" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G63" s="5"/>
       <c r="H63" s="5"/>
       <c r="I63" s="5" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
     </row>
     <row r="64" customFormat="1" ht="25" customHeight="1" spans="1:9">
       <c r="A64" s="12" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B64" s="5"/>
       <c r="C64" s="5"/>
       <c r="D64" s="5"/>
       <c r="E64" s="5"/>
       <c r="F64" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G64" s="5"/>
       <c r="H64" s="5"/>
       <c r="I64" s="5" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
     </row>
     <row r="65" customFormat="1" ht="25" customHeight="1" spans="1:9">
       <c r="A65" s="12" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B65" s="5"/>
       <c r="C65" s="5"/>
       <c r="D65" s="5"/>
       <c r="E65" s="5"/>
       <c r="F65" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G65" s="5"/>
       <c r="H65" s="5"/>
       <c r="I65" s="5" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
     </row>
     <row r="66" ht="25" customHeight="1" spans="1:9">

--- a/资源录入表新.xlsx
+++ b/资源录入表新.xlsx
@@ -136,6 +136,9 @@
   </si>
   <si>
     <t>古装/权谋</t>
+  </si>
+  <si>
+    <t>已完结</t>
   </si>
   <si>
     <t>张赫/徐轸轸</t>
@@ -234,6 +237,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF111111"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>剧情</t>
     </r>
     <r>
@@ -257,6 +266,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="major"/>
+      </rPr>
       <t>孔晓振</t>
     </r>
     <r>
@@ -445,9 +460,6 @@
       </rPr>
       <t>法术</t>
     </r>
-  </si>
-  <si>
-    <t>已完结</t>
   </si>
   <si>
     <t xml:space="preserve">链接: https://pan.baidu.com/s/1hQKA0Oc-JJIQ4XxdY13YmQ 提取码: j1h2 </t>
@@ -1415,17 +1427,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="Helvetica"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF111111"/>
-      <name val="Helvetica"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="10.5"/>
       <name val="Arial"/>
       <charset val="134"/>
@@ -1436,6 +1437,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF111111"/>
+      <name val="Helvetica"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="12"/>
       <name val="Arial"/>
       <charset val="134"/>
@@ -1443,6 +1450,11 @@
     <font>
       <sz val="12"/>
       <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Helvetica"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1943,7 +1955,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2007,32 +2019,38 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2628,31 +2646,31 @@
       <c r="O1" s="5"/>
     </row>
     <row r="2" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="23">
-        <v>6</v>
-      </c>
-      <c r="F2" s="22" t="s">
+      <c r="D2" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="8">
+        <v>8</v>
+      </c>
+      <c r="F2" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="22">
+      <c r="G2" s="23">
         <v>2026</v>
       </c>
-      <c r="H2" s="22" t="s">
+      <c r="H2" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="22" t="s">
+      <c r="I2" s="23" t="s">
         <v>17</v>
       </c>
       <c r="J2" s="13"/>
@@ -2663,31 +2681,31 @@
       <c r="O2" s="13"/>
     </row>
     <row r="3" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="22" t="s">
+      <c r="D3" s="23" t="s">
         <v>14</v>
       </c>
       <c r="E3" s="23">
         <v>10</v>
       </c>
-      <c r="F3" s="22" t="s">
+      <c r="F3" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="22">
+      <c r="G3" s="23">
         <v>2026</v>
       </c>
-      <c r="H3" s="22" t="s">
+      <c r="H3" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="22" t="s">
+      <c r="I3" s="23" t="s">
         <v>21</v>
       </c>
       <c r="J3" s="13"/>
@@ -2698,31 +2716,31 @@
       <c r="O3" s="13"/>
     </row>
     <row r="4" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="22" t="s">
+      <c r="D4" s="23" t="s">
         <v>14</v>
       </c>
       <c r="E4" s="23">
         <v>24</v>
       </c>
-      <c r="F4" s="22" t="s">
+      <c r="F4" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="22">
+      <c r="G4" s="23">
         <v>2026</v>
       </c>
-      <c r="H4" s="22" t="s">
+      <c r="H4" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="I4" s="22" t="s">
+      <c r="I4" s="23" t="s">
         <v>25</v>
       </c>
       <c r="J4" s="13"/>
@@ -2735,31 +2753,31 @@
       <c r="O4" s="13"/>
     </row>
     <row r="5" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="C5" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="23">
-        <v>20</v>
-      </c>
-      <c r="F5" s="22" t="s">
+      <c r="D5" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="8">
+        <v>22</v>
+      </c>
+      <c r="F5" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="22">
+      <c r="G5" s="23">
         <v>2026</v>
       </c>
-      <c r="H5" s="22" t="s">
+      <c r="H5" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="I5" s="22" t="s">
+      <c r="I5" s="23" t="s">
         <v>30</v>
       </c>
       <c r="J5" s="13"/>
@@ -2770,32 +2788,32 @@
       <c r="O5" s="13"/>
     </row>
     <row r="6" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="23">
-        <v>20</v>
-      </c>
-      <c r="F6" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="G6" s="22">
+      <c r="D6" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="8">
+        <v>24</v>
+      </c>
+      <c r="F6" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" s="23">
         <v>2026</v>
       </c>
-      <c r="H6" s="22" t="s">
-        <v>33</v>
-      </c>
-      <c r="I6" s="22" t="s">
+      <c r="H6" s="23" t="s">
         <v>34</v>
+      </c>
+      <c r="I6" s="23" t="s">
+        <v>35</v>
       </c>
       <c r="J6" s="13"/>
       <c r="K6" s="13"/>
@@ -2806,18 +2824,18 @@
     </row>
     <row r="7" ht="25" customHeight="1" spans="1:15">
       <c r="A7" s="12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="25">
+      <c r="C7" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="13">
         <v>14</v>
       </c>
       <c r="F7" s="13" t="s">
@@ -2827,10 +2845,10 @@
         <v>2026</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J7" s="5"/>
       <c r="K7" s="5"/>
@@ -2840,32 +2858,32 @@
       <c r="O7" s="5"/>
     </row>
     <row r="8" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A8" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="B8" s="22" t="s">
+      <c r="A8" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="22" t="s">
+      <c r="B8" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="D8" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="22">
+      <c r="C8" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="23">
         <v>3</v>
       </c>
-      <c r="F8" s="22" t="s">
+      <c r="F8" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="G8" s="22">
+      <c r="G8" s="23">
         <v>2026</v>
       </c>
-      <c r="H8" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="I8" s="22" t="s">
+      <c r="H8" s="23" t="s">
         <v>43</v>
+      </c>
+      <c r="I8" s="23" t="s">
+        <v>44</v>
       </c>
       <c r="J8" s="13"/>
       <c r="K8" s="13"/>
@@ -2875,32 +2893,32 @@
       <c r="O8" s="13"/>
     </row>
     <row r="9" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A9" s="21" t="s">
-        <v>44</v>
-      </c>
-      <c r="B9" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="C9" s="22" t="s">
+      <c r="A9" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="D9" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" s="22">
+      <c r="B9" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="23">
         <v>4</v>
       </c>
-      <c r="F9" s="22" t="s">
+      <c r="F9" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="G9" s="22">
+      <c r="G9" s="23">
         <v>2026</v>
       </c>
-      <c r="H9" s="22" t="s">
-        <v>46</v>
-      </c>
-      <c r="I9" s="22" t="s">
+      <c r="H9" s="23" t="s">
         <v>47</v>
+      </c>
+      <c r="I9" s="23" t="s">
+        <v>48</v>
       </c>
       <c r="J9" s="13"/>
       <c r="K9" s="13"/>
@@ -2909,325 +2927,325 @@
       <c r="N9" s="13"/>
       <c r="O9" s="13"/>
     </row>
-    <row r="10" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+    <row r="10" s="21" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A10" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="B10" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C10" s="27" t="s">
+      <c r="B10" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="D10" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="8">
+      <c r="C10" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="27">
         <v>1</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="F10" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="G10" s="8">
+      <c r="G10" s="27">
         <v>2026</v>
       </c>
-      <c r="H10" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="I10" s="5" t="s">
+      <c r="H10" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="J10" s="13"/>
-      <c r="K10" s="13"/>
-      <c r="L10" s="13"/>
-      <c r="M10" s="13"/>
-      <c r="N10" s="13"/>
-      <c r="O10" s="13"/>
+      <c r="I10" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="J10" s="30"/>
+      <c r="K10" s="30"/>
+      <c r="L10" s="30"/>
+      <c r="M10" s="30"/>
+      <c r="N10" s="30"/>
+      <c r="O10" s="30"/>
     </row>
     <row r="11" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A11" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="B11" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="C11" s="22" t="s">
+      <c r="A11" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="D11" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="22">
+      <c r="B11" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="23">
         <v>6</v>
       </c>
-      <c r="F11" s="22" t="s">
+      <c r="F11" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="G11" s="22">
+      <c r="G11" s="23">
         <v>2026</v>
       </c>
-      <c r="H11" s="22" t="s">
-        <v>55</v>
-      </c>
-      <c r="I11" s="22" t="s">
+      <c r="H11" s="23" t="s">
         <v>56</v>
+      </c>
+      <c r="I11" s="23" t="s">
+        <v>57</v>
       </c>
       <c r="J11" s="13"/>
       <c r="K11" s="13"/>
       <c r="L11" s="13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M11" s="13"/>
       <c r="N11" s="13"/>
       <c r="O11" s="13"/>
     </row>
     <row r="12" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A12" s="21" t="s">
-        <v>57</v>
-      </c>
-      <c r="B12" s="22" t="s">
+      <c r="A12" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="C12" s="22" t="s">
+      <c r="B12" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="D12" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="E12" s="22">
+      <c r="C12" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="D12" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="23">
         <v>6</v>
       </c>
-      <c r="F12" s="22" t="s">
+      <c r="F12" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="G12" s="22">
+      <c r="G12" s="23">
         <v>2026</v>
       </c>
-      <c r="H12" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="I12" s="22" t="s">
+      <c r="H12" s="23" t="s">
         <v>61</v>
+      </c>
+      <c r="I12" s="23" t="s">
+        <v>62</v>
       </c>
       <c r="J12" s="13"/>
       <c r="K12" s="13"/>
       <c r="L12" s="13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M12" s="13"/>
       <c r="N12" s="13"/>
       <c r="O12" s="13"/>
     </row>
     <row r="13" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A13" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="B13" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="C13" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="D13" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="E13" s="22">
-        <v>4</v>
-      </c>
-      <c r="F13" s="22" t="s">
+      <c r="A13" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="B13" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="D13" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="8">
+        <v>5</v>
+      </c>
+      <c r="F13" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="G13" s="22">
+      <c r="G13" s="23">
         <v>2026</v>
       </c>
-      <c r="H13" s="22" t="s">
-        <v>63</v>
-      </c>
-      <c r="I13" s="22" t="s">
+      <c r="H13" s="23" t="s">
         <v>64</v>
+      </c>
+      <c r="I13" s="23" t="s">
+        <v>65</v>
       </c>
       <c r="J13" s="13"/>
       <c r="K13" s="13"/>
       <c r="L13" s="13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M13" s="13"/>
       <c r="N13" s="13"/>
       <c r="O13" s="13"/>
     </row>
     <row r="14" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A14" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="B14" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="C14" s="22" t="s">
+      <c r="A14" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="D14" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" s="22">
-        <v>6</v>
-      </c>
-      <c r="F14" s="22" t="s">
+      <c r="B14" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="D14" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" s="8">
+        <v>7</v>
+      </c>
+      <c r="F14" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="G14" s="22">
+      <c r="G14" s="23">
         <v>2026</v>
       </c>
-      <c r="H14" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="I14" s="22" t="s">
+      <c r="H14" s="23" t="s">
         <v>68</v>
+      </c>
+      <c r="I14" s="23" t="s">
+        <v>69</v>
       </c>
       <c r="J14" s="13"/>
       <c r="K14" s="13"/>
       <c r="L14" s="13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M14" s="13"/>
       <c r="N14" s="13"/>
       <c r="O14" s="13"/>
     </row>
     <row r="15" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A15" s="21" t="s">
-        <v>69</v>
-      </c>
-      <c r="B15" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="C15" s="22" t="s">
+      <c r="A15" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="D15" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="E15" s="22">
-        <v>8</v>
-      </c>
-      <c r="F15" s="22" t="s">
+      <c r="B15" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="D15" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" s="8">
+        <v>9</v>
+      </c>
+      <c r="F15" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="G15" s="22">
+      <c r="G15" s="23">
         <v>2026</v>
       </c>
-      <c r="H15" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="I15" s="22" t="s">
+      <c r="H15" s="23" t="s">
         <v>72</v>
+      </c>
+      <c r="I15" s="23" t="s">
+        <v>73</v>
       </c>
       <c r="J15" s="13"/>
       <c r="K15" s="13"/>
       <c r="L15" s="13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M15" s="13"/>
       <c r="N15" s="13"/>
       <c r="O15" s="13"/>
     </row>
     <row r="16" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A16" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="B16" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="C16" s="22" t="s">
+      <c r="A16" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="D16" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="E16" s="22">
+      <c r="B16" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="D16" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" s="23">
         <v>4</v>
       </c>
-      <c r="F16" s="22" t="s">
+      <c r="F16" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="G16" s="22">
+      <c r="G16" s="23">
         <v>2026</v>
       </c>
-      <c r="H16" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="I16" s="22" t="s">
+      <c r="H16" s="23" t="s">
         <v>76</v>
+      </c>
+      <c r="I16" s="23" t="s">
+        <v>77</v>
       </c>
       <c r="J16" s="13"/>
       <c r="K16" s="13"/>
       <c r="L16" s="13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M16" s="13"/>
       <c r="N16" s="13"/>
       <c r="O16" s="13"/>
     </row>
     <row r="17" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A17" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="B17" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="C17" s="22" t="s">
+      <c r="A17" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="D17" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="E17" s="22">
+      <c r="B17" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="D17" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E17" s="23">
         <v>8</v>
       </c>
-      <c r="F17" s="22" t="s">
+      <c r="F17" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="G17" s="22">
+      <c r="G17" s="23">
         <v>2026</v>
       </c>
-      <c r="H17" s="22" t="s">
-        <v>80</v>
-      </c>
-      <c r="I17" s="22" t="s">
+      <c r="H17" s="23" t="s">
         <v>81</v>
+      </c>
+      <c r="I17" s="23" t="s">
+        <v>82</v>
       </c>
       <c r="J17" s="13"/>
       <c r="K17" s="13"/>
       <c r="L17" s="13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M17" s="13"/>
       <c r="N17" s="13"/>
       <c r="O17" s="13"/>
     </row>
     <row r="18" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A18" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="B18" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="C18" s="22" t="s">
+      <c r="A18" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="D18" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="E18" s="22">
+      <c r="B18" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="D18" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="23">
         <v>7</v>
       </c>
-      <c r="F18" s="22" t="s">
+      <c r="F18" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="G18" s="22">
+      <c r="G18" s="23">
         <v>2026</v>
       </c>
-      <c r="H18" s="22"/>
-      <c r="I18" s="22" t="s">
-        <v>84</v>
+      <c r="H18" s="23"/>
+      <c r="I18" s="23" t="s">
+        <v>85</v>
       </c>
       <c r="J18" s="13"/>
       <c r="K18" s="13"/>
@@ -3237,30 +3255,30 @@
       <c r="O18" s="13"/>
     </row>
     <row r="19" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A19" s="21" t="s">
-        <v>85</v>
-      </c>
-      <c r="B19" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="C19" s="22" t="s">
+      <c r="A19" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="D19" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="E19" s="22">
-        <v>4</v>
-      </c>
-      <c r="F19" s="22" t="s">
+      <c r="B19" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="D19" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19" s="8">
+        <v>5</v>
+      </c>
+      <c r="F19" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="G19" s="22">
+      <c r="G19" s="23">
         <v>2026</v>
       </c>
-      <c r="H19" s="22"/>
-      <c r="I19" s="22" t="s">
-        <v>87</v>
+      <c r="H19" s="23"/>
+      <c r="I19" s="23" t="s">
+        <v>88</v>
       </c>
       <c r="J19" s="13"/>
       <c r="K19" s="13"/>
@@ -3270,26 +3288,26 @@
       <c r="O19" s="13"/>
     </row>
     <row r="20" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A20" s="28" t="s">
-        <v>88</v>
+      <c r="A20" s="31" t="s">
+        <v>89</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="C20" s="29" t="s">
-        <v>89</v>
-      </c>
-      <c r="D20" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="E20" s="29"/>
-      <c r="F20" s="29" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="G20" s="22">
+      <c r="D20" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E20" s="24"/>
+      <c r="F20" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="G20" s="23">
         <v>2026</v>
       </c>
-      <c r="H20" s="22"/>
+      <c r="H20" s="23"/>
       <c r="I20" s="13" t="s">
         <v>91</v>
       </c>
@@ -3298,29 +3316,29 @@
       <c r="L20" s="13"/>
       <c r="M20" s="13"/>
       <c r="N20" s="13"/>
-      <c r="O20" s="30"/>
+      <c r="O20" s="32"/>
     </row>
     <row r="21" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A21" s="28" t="s">
+      <c r="A21" s="31" t="s">
         <v>92</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="C21" s="29" t="s">
-        <v>89</v>
-      </c>
-      <c r="D21" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="E21" s="29"/>
-      <c r="F21" s="29" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="G21" s="22">
+      <c r="D21" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="G21" s="23">
         <v>2026</v>
       </c>
-      <c r="H21" s="22"/>
+      <c r="H21" s="23"/>
       <c r="I21" s="13" t="s">
         <v>93</v>
       </c>
@@ -3329,7 +3347,7 @@
       <c r="L21" s="13"/>
       <c r="M21" s="13"/>
       <c r="N21" s="13"/>
-      <c r="O21" s="30"/>
+      <c r="O21" s="32"/>
     </row>
     <row r="22" ht="25" customHeight="1" spans="1:15">
       <c r="A22" s="12" t="s">
@@ -3348,7 +3366,7 @@
         <v>96</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G22" s="5">
         <v>2026</v>
@@ -3385,7 +3403,7 @@
         <v>102</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G23" s="5">
         <v>2025</v>
@@ -3422,7 +3440,7 @@
         <v>108</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G24" s="5">
         <v>2026</v>
@@ -3459,7 +3477,7 @@
         <v>114</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G25" s="5">
         <v>2026</v>
@@ -3496,7 +3514,7 @@
         <v>120</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G26" s="5">
         <v>2025</v>
@@ -3533,7 +3551,7 @@
         <v>126</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G27" s="5">
         <v>2026</v>
@@ -3570,7 +3588,7 @@
         <v>132</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G28" s="5">
         <v>2026</v>
@@ -3588,7 +3606,7 @@
       </c>
       <c r="M28" s="5"/>
       <c r="N28" s="5"/>
-      <c r="O28" s="31"/>
+      <c r="O28" s="33"/>
     </row>
     <row r="29" ht="25" customHeight="1" spans="1:15">
       <c r="A29" s="12" t="s">
@@ -3607,7 +3625,7 @@
         <v>138</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G29" s="5">
         <v>2024</v>
@@ -3625,7 +3643,7 @@
       </c>
       <c r="M29" s="5"/>
       <c r="N29" s="5"/>
-      <c r="O29" s="31"/>
+      <c r="O29" s="33"/>
     </row>
     <row r="30" ht="25" customHeight="1" spans="1:15">
       <c r="A30" s="12" t="s">
@@ -3644,7 +3662,7 @@
         <v>144</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G30" s="5">
         <v>2024</v>
@@ -3662,7 +3680,7 @@
       </c>
       <c r="M30" s="5"/>
       <c r="N30" s="5"/>
-      <c r="O30" s="31"/>
+      <c r="O30" s="33"/>
     </row>
     <row r="31" ht="25" customHeight="1" spans="1:15">
       <c r="A31" s="12" t="s">
@@ -3681,7 +3699,7 @@
         <v>114</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G31" s="5">
         <v>2026</v>
@@ -3699,7 +3717,7 @@
       </c>
       <c r="M31" s="5"/>
       <c r="N31" s="5"/>
-      <c r="O31" s="31"/>
+      <c r="O31" s="33"/>
     </row>
     <row r="32" ht="25" customHeight="1" spans="1:15">
       <c r="A32" s="12" t="s">
@@ -3718,7 +3736,7 @@
         <v>154</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G32" s="5">
         <v>2025</v>
@@ -3736,7 +3754,7 @@
       </c>
       <c r="M32" s="5"/>
       <c r="N32" s="5"/>
-      <c r="O32" s="31"/>
+      <c r="O32" s="33"/>
     </row>
     <row r="33" ht="25" customHeight="1" spans="1:15">
       <c r="A33" s="12" t="s">
@@ -3755,7 +3773,7 @@
         <v>132</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G33" s="5">
         <v>2026</v>
@@ -3773,7 +3791,7 @@
       </c>
       <c r="M33" s="5"/>
       <c r="N33" s="5"/>
-      <c r="O33" s="31"/>
+      <c r="O33" s="33"/>
     </row>
     <row r="34" ht="25" customHeight="1" spans="1:15">
       <c r="A34" s="12" t="s">
@@ -3792,7 +3810,7 @@
         <v>132</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G34" s="5">
         <v>2026</v>
@@ -3810,7 +3828,7 @@
       </c>
       <c r="M34" s="5"/>
       <c r="N34" s="5"/>
-      <c r="O34" s="31"/>
+      <c r="O34" s="33"/>
     </row>
     <row r="35" ht="25" customHeight="1" spans="1:15">
       <c r="A35" s="12" t="s">
@@ -3829,7 +3847,7 @@
         <v>96</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G35" s="5">
         <v>2026</v>
@@ -3847,7 +3865,7 @@
       </c>
       <c r="M35" s="5"/>
       <c r="N35" s="5"/>
-      <c r="O35" s="31"/>
+      <c r="O35" s="33"/>
     </row>
     <row r="36" ht="25" customHeight="1" spans="1:15">
       <c r="A36" s="12" t="s">
@@ -3866,7 +3884,7 @@
         <v>174</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G36" s="5">
         <v>2025</v>
@@ -3884,7 +3902,7 @@
       </c>
       <c r="M36" s="5"/>
       <c r="N36" s="5"/>
-      <c r="O36" s="31"/>
+      <c r="O36" s="33"/>
     </row>
     <row r="37" ht="25" customHeight="1" spans="1:15">
       <c r="A37" s="12" t="s">
@@ -3903,7 +3921,7 @@
         <v>180</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G37" s="5">
         <v>2026</v>
@@ -3921,7 +3939,7 @@
       </c>
       <c r="M37" s="5"/>
       <c r="N37" s="5"/>
-      <c r="O37" s="31"/>
+      <c r="O37" s="33"/>
     </row>
     <row r="38" ht="25" customHeight="1" spans="1:15">
       <c r="A38" s="12" t="s">
@@ -3940,7 +3958,7 @@
         <v>102</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G38" s="5">
         <v>2026</v>
@@ -3958,7 +3976,7 @@
       </c>
       <c r="M38" s="5"/>
       <c r="N38" s="5"/>
-      <c r="O38" s="31"/>
+      <c r="O38" s="33"/>
     </row>
     <row r="39" ht="25" customHeight="1" spans="1:15">
       <c r="A39" s="12" t="s">
@@ -3977,7 +3995,7 @@
         <v>192</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G39" s="5">
         <v>2025</v>
@@ -3989,11 +4007,11 @@
       <c r="J39" s="5"/>
       <c r="K39" s="5"/>
       <c r="L39" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M39" s="5"/>
       <c r="N39" s="5"/>
-      <c r="O39" s="31"/>
+      <c r="O39" s="33"/>
     </row>
     <row r="40" ht="25" customHeight="1" spans="1:15">
       <c r="A40" s="12" t="s">
@@ -4012,7 +4030,7 @@
         <v>196</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G40" s="5">
         <v>2025</v>
@@ -4030,7 +4048,7 @@
       </c>
       <c r="M40" s="5"/>
       <c r="N40" s="5"/>
-      <c r="O40" s="31"/>
+      <c r="O40" s="33"/>
     </row>
     <row r="41" ht="25" customHeight="1" spans="1:15">
       <c r="A41" s="12" t="s">
@@ -4049,7 +4067,7 @@
         <v>192</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G41" s="5">
         <v>2025</v>
@@ -4061,11 +4079,11 @@
       <c r="J41" s="5"/>
       <c r="K41" s="5"/>
       <c r="L41" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M41" s="5"/>
       <c r="N41" s="5"/>
-      <c r="O41" s="31"/>
+      <c r="O41" s="33"/>
     </row>
     <row r="42" ht="25" customHeight="1" spans="1:15">
       <c r="A42" s="12" t="s">
@@ -4084,7 +4102,7 @@
         <v>108</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G42" s="5">
         <v>2026</v>
@@ -4102,7 +4120,7 @@
       </c>
       <c r="M42" s="5"/>
       <c r="N42" s="5"/>
-      <c r="O42" s="31"/>
+      <c r="O42" s="33"/>
     </row>
     <row r="43" ht="25" customHeight="1" spans="1:15">
       <c r="A43" s="12" t="s">
@@ -4113,7 +4131,7 @@
       <c r="D43" s="5"/>
       <c r="E43" s="5"/>
       <c r="F43" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G43" s="5"/>
       <c r="H43" s="5"/>
@@ -4125,7 +4143,7 @@
       <c r="L43" s="5"/>
       <c r="M43" s="5"/>
       <c r="N43" s="5"/>
-      <c r="O43" s="31"/>
+      <c r="O43" s="33"/>
     </row>
     <row r="44" ht="25" customHeight="1" spans="1:15">
       <c r="A44" s="12" t="s">
@@ -4136,7 +4154,7 @@
       <c r="D44" s="5"/>
       <c r="E44" s="5"/>
       <c r="F44" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G44" s="5"/>
       <c r="H44" s="5"/>
@@ -4148,7 +4166,7 @@
       <c r="L44" s="5"/>
       <c r="M44" s="5"/>
       <c r="N44" s="5"/>
-      <c r="O44" s="31"/>
+      <c r="O44" s="33"/>
     </row>
     <row r="45" ht="25" customHeight="1" spans="1:15">
       <c r="A45" s="12" t="s">
@@ -4159,7 +4177,7 @@
       <c r="D45" s="5"/>
       <c r="E45" s="5"/>
       <c r="F45" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G45" s="5"/>
       <c r="H45" s="5"/>
@@ -4171,7 +4189,7 @@
       <c r="L45" s="5"/>
       <c r="M45" s="5"/>
       <c r="N45" s="5"/>
-      <c r="O45" s="31"/>
+      <c r="O45" s="33"/>
     </row>
     <row r="46" ht="25" customHeight="1" spans="1:15">
       <c r="A46" s="12" t="s">
@@ -4182,7 +4200,7 @@
       <c r="D46" s="5"/>
       <c r="E46" s="5"/>
       <c r="F46" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G46" s="5"/>
       <c r="H46" s="5"/>
@@ -4194,7 +4212,7 @@
       <c r="L46" s="5"/>
       <c r="M46" s="5"/>
       <c r="N46" s="5"/>
-      <c r="O46" s="31"/>
+      <c r="O46" s="33"/>
     </row>
     <row r="47" ht="25" customHeight="1" spans="1:15">
       <c r="A47" s="14" t="s">
@@ -4205,7 +4223,7 @@
       <c r="D47" s="15"/>
       <c r="E47" s="15"/>
       <c r="F47" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G47" s="15"/>
       <c r="H47" s="15"/>
@@ -4217,7 +4235,7 @@
       <c r="L47" s="5"/>
       <c r="M47" s="5"/>
       <c r="N47" s="5"/>
-      <c r="O47" s="31"/>
+      <c r="O47" s="33"/>
     </row>
     <row r="48" ht="25" customHeight="1" spans="1:15">
       <c r="A48" s="12" t="s">
@@ -4228,7 +4246,7 @@
       <c r="D48" s="5"/>
       <c r="E48" s="5"/>
       <c r="F48" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G48" s="5"/>
       <c r="H48" s="5"/>
@@ -4240,7 +4258,7 @@
       <c r="L48" s="5"/>
       <c r="M48" s="5"/>
       <c r="N48" s="5"/>
-      <c r="O48" s="31"/>
+      <c r="O48" s="33"/>
     </row>
     <row r="49" ht="25" customHeight="1" spans="1:15">
       <c r="A49" s="12" t="s">
@@ -4251,7 +4269,7 @@
       <c r="D49" s="5"/>
       <c r="E49" s="5"/>
       <c r="F49" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G49" s="5"/>
       <c r="H49" s="5"/>
@@ -4263,7 +4281,7 @@
       <c r="L49" s="5"/>
       <c r="M49" s="5"/>
       <c r="N49" s="5"/>
-      <c r="O49" s="31"/>
+      <c r="O49" s="33"/>
     </row>
     <row r="50" ht="25" customHeight="1" spans="1:15">
       <c r="A50" s="12" t="s">
@@ -4274,7 +4292,7 @@
       <c r="D50" s="5"/>
       <c r="E50" s="5"/>
       <c r="F50" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G50" s="5"/>
       <c r="H50" s="5"/>
@@ -4286,7 +4304,7 @@
       <c r="L50" s="5"/>
       <c r="M50" s="5"/>
       <c r="N50" s="5"/>
-      <c r="O50" s="31"/>
+      <c r="O50" s="33"/>
     </row>
     <row r="51" ht="25" customHeight="1" spans="1:15">
       <c r="A51" s="12" t="s">
@@ -4297,7 +4315,7 @@
       <c r="D51" s="5"/>
       <c r="E51" s="5"/>
       <c r="F51" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G51" s="5"/>
       <c r="H51" s="5"/>
@@ -4309,7 +4327,7 @@
       <c r="L51" s="5"/>
       <c r="M51" s="5"/>
       <c r="N51" s="5"/>
-      <c r="O51" s="31"/>
+      <c r="O51" s="33"/>
     </row>
     <row r="52" ht="25" customHeight="1" spans="1:15">
       <c r="A52" s="12" t="s">
@@ -4320,7 +4338,7 @@
       <c r="D52" s="5"/>
       <c r="E52" s="5"/>
       <c r="F52" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G52" s="5"/>
       <c r="H52" s="5"/>
@@ -4332,7 +4350,7 @@
       <c r="L52" s="5"/>
       <c r="M52" s="5"/>
       <c r="N52" s="5"/>
-      <c r="O52" s="31"/>
+      <c r="O52" s="33"/>
     </row>
     <row r="53" ht="25" customHeight="1" spans="1:15">
       <c r="A53" s="12" t="s">
@@ -4343,7 +4361,7 @@
       <c r="D53" s="5"/>
       <c r="E53" s="5"/>
       <c r="F53" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G53" s="5"/>
       <c r="H53" s="5"/>
@@ -4355,7 +4373,7 @@
       <c r="L53" s="5"/>
       <c r="M53" s="5"/>
       <c r="N53" s="5"/>
-      <c r="O53" s="31"/>
+      <c r="O53" s="33"/>
     </row>
     <row r="54" ht="25" customHeight="1" spans="1:15">
       <c r="A54" s="12" t="s">
@@ -4366,7 +4384,7 @@
       <c r="D54" s="5"/>
       <c r="E54" s="5"/>
       <c r="F54" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G54" s="5"/>
       <c r="H54" s="5"/>
@@ -4378,7 +4396,7 @@
       <c r="L54" s="5"/>
       <c r="M54" s="5"/>
       <c r="N54" s="5"/>
-      <c r="O54" s="31"/>
+      <c r="O54" s="33"/>
     </row>
     <row r="55" ht="25" customHeight="1" spans="1:15">
       <c r="A55" s="12" t="s">
@@ -4389,7 +4407,7 @@
       <c r="D55" s="5"/>
       <c r="E55" s="5"/>
       <c r="F55" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G55" s="5"/>
       <c r="I55" s="5" t="s">
@@ -4400,7 +4418,7 @@
       <c r="L55" s="5"/>
       <c r="M55" s="5"/>
       <c r="N55" s="5"/>
-      <c r="O55" s="31"/>
+      <c r="O55" s="33"/>
     </row>
     <row r="56" ht="25" customHeight="1" spans="1:15">
       <c r="A56" s="12" t="s">
@@ -4411,7 +4429,7 @@
       <c r="D56" s="5"/>
       <c r="E56" s="5"/>
       <c r="F56" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G56" s="5"/>
       <c r="H56" s="5"/>
@@ -4423,7 +4441,7 @@
       <c r="L56" s="5"/>
       <c r="M56" s="5"/>
       <c r="N56" s="5"/>
-      <c r="O56" s="31"/>
+      <c r="O56" s="33"/>
     </row>
     <row r="57" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A57" s="12" t="s">
@@ -4434,7 +4452,7 @@
       <c r="D57" s="5"/>
       <c r="E57" s="5"/>
       <c r="F57" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G57" s="5"/>
       <c r="H57" s="5"/>
@@ -4446,7 +4464,7 @@
       <c r="L57" s="5"/>
       <c r="M57" s="5"/>
       <c r="N57" s="5"/>
-      <c r="O57" s="31"/>
+      <c r="O57" s="33"/>
     </row>
     <row r="58" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A58" s="12" t="s">
@@ -4457,7 +4475,7 @@
       <c r="D58" s="5"/>
       <c r="E58" s="5"/>
       <c r="F58" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G58" s="5"/>
       <c r="H58" s="5"/>
@@ -4469,7 +4487,7 @@
       <c r="L58" s="5"/>
       <c r="M58" s="5"/>
       <c r="N58" s="5"/>
-      <c r="O58" s="31"/>
+      <c r="O58" s="33"/>
     </row>
     <row r="59" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A59" s="12" t="s">
@@ -4480,7 +4498,7 @@
       <c r="D59" s="5"/>
       <c r="E59" s="5"/>
       <c r="F59" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G59" s="5"/>
       <c r="H59" s="5"/>
@@ -4492,7 +4510,7 @@
       <c r="L59" s="5"/>
       <c r="M59" s="5"/>
       <c r="N59" s="5"/>
-      <c r="O59" s="31"/>
+      <c r="O59" s="33"/>
     </row>
     <row r="60" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A60" s="12" t="s">
@@ -4503,7 +4521,7 @@
       <c r="D60" s="5"/>
       <c r="E60" s="5"/>
       <c r="F60" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G60" s="5"/>
       <c r="H60" s="5"/>
@@ -4515,7 +4533,7 @@
       <c r="L60" s="5"/>
       <c r="M60" s="5"/>
       <c r="N60" s="5"/>
-      <c r="O60" s="31"/>
+      <c r="O60" s="33"/>
     </row>
     <row r="61" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A61" s="12" t="s">
@@ -4532,7 +4550,7 @@
         <v>246</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G61" s="5"/>
       <c r="H61" s="18" t="s">
@@ -4546,7 +4564,7 @@
       <c r="L61" s="5"/>
       <c r="M61" s="5"/>
       <c r="N61" s="5"/>
-      <c r="O61" s="31"/>
+      <c r="O61" s="33"/>
     </row>
     <row r="62" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A62" s="12" t="s">
@@ -4563,7 +4581,7 @@
         <v>108</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G62" s="5"/>
       <c r="H62" s="18" t="s">
@@ -4594,7 +4612,7 @@
         <v>114</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G63" s="5"/>
       <c r="H63" s="18" t="s">
@@ -4608,7 +4626,7 @@
       <c r="L63" s="5"/>
       <c r="M63" s="5"/>
       <c r="N63" s="5"/>
-      <c r="O63" s="31"/>
+      <c r="O63" s="33"/>
     </row>
     <row r="64" ht="25" customHeight="1" spans="1:15">
       <c r="A64" s="12" t="s">
@@ -4625,7 +4643,7 @@
         <v>259</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G64" s="5"/>
       <c r="H64" s="18" t="s">
@@ -4639,7 +4657,7 @@
       <c r="L64" s="5"/>
       <c r="M64" s="5"/>
       <c r="N64" s="5"/>
-      <c r="O64" s="31"/>
+      <c r="O64" s="33"/>
     </row>
     <row r="65" ht="25" customHeight="1" spans="1:15">
       <c r="A65" s="12" t="s">
@@ -4656,7 +4674,7 @@
         <v>259</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G65" s="5"/>
       <c r="H65" s="18" t="s">
@@ -4670,14 +4688,14 @@
       <c r="L65" s="5"/>
       <c r="M65" s="5"/>
       <c r="N65" s="5"/>
-      <c r="O65" s="31"/>
+      <c r="O65" s="33"/>
     </row>
     <row r="66" ht="25" customHeight="1" spans="1:15">
       <c r="A66" s="12" t="s">
         <v>266</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C66" s="17" t="s">
         <v>267</v>
@@ -4687,7 +4705,7 @@
         <v>268</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G66" s="5"/>
       <c r="H66" s="18" t="s">
@@ -4701,7 +4719,7 @@
       <c r="L66" s="5"/>
       <c r="M66" s="5"/>
       <c r="N66" s="5"/>
-      <c r="O66" s="31"/>
+      <c r="O66" s="33"/>
     </row>
     <row r="67" ht="25" customHeight="1" spans="1:15">
       <c r="A67" s="12"/>
@@ -5185,21 +5203,21 @@
         <v>2026</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:9">
       <c r="A8" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>14</v>
@@ -5214,21 +5232,21 @@
         <v>2026</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:9">
       <c r="A9" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>14</v>
@@ -5243,21 +5261,21 @@
         <v>2026</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:9">
       <c r="A10" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>14</v>
@@ -5272,21 +5290,21 @@
         <v>2026</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:9">
       <c r="A11" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>14</v>
@@ -5301,21 +5319,21 @@
         <v>2026</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:9">
       <c r="A12" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>14</v>
@@ -5330,21 +5348,21 @@
         <v>2026</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:9">
       <c r="A13" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>14</v>
@@ -5359,21 +5377,21 @@
         <v>2026</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:9">
       <c r="A14" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>14</v>
@@ -5388,21 +5406,21 @@
         <v>2026</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:9">
       <c r="A15" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>14</v>
@@ -5417,21 +5435,21 @@
         <v>2026</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:9">
       <c r="A16" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>14</v>
@@ -5446,21 +5464,21 @@
         <v>2026</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:9">
       <c r="A17" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>14</v>
@@ -5476,18 +5494,18 @@
       </c>
       <c r="H17" s="7"/>
       <c r="I17" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:9">
       <c r="A18" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>14</v>
@@ -5503,15 +5521,15 @@
       </c>
       <c r="H18" s="7"/>
       <c r="I18" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" spans="1:9">
       <c r="A19" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C19" s="10" t="s">
         <v>273</v>
@@ -5521,7 +5539,7 @@
       </c>
       <c r="E19" s="10"/>
       <c r="F19" s="10" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G19" s="7">
         <v>2026</v>
@@ -5536,7 +5554,7 @@
         <v>92</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C20" s="10" t="s">
         <v>273</v>
@@ -5546,7 +5564,7 @@
       </c>
       <c r="E20" s="10"/>
       <c r="F20" s="10" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G20" s="7">
         <v>2026</v>
@@ -5573,7 +5591,7 @@
         <v>96</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G21" s="5">
         <v>2026</v>
@@ -5602,7 +5620,7 @@
         <v>102</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G22" s="5">
         <v>2025</v>
@@ -5631,7 +5649,7 @@
         <v>108</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G23" s="5">
         <v>2026</v>
@@ -5660,7 +5678,7 @@
         <v>114</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G24" s="5">
         <v>2026</v>
@@ -5689,7 +5707,7 @@
         <v>120</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G25" s="5">
         <v>2025</v>
@@ -5718,7 +5736,7 @@
         <v>126</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G26" s="5">
         <v>2026</v>
@@ -5747,7 +5765,7 @@
         <v>132</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G27" s="5">
         <v>2026</v>
@@ -5776,7 +5794,7 @@
         <v>138</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G28" s="5">
         <v>2024</v>
@@ -5805,7 +5823,7 @@
         <v>144</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G29" s="5">
         <v>2024</v>
@@ -5834,7 +5852,7 @@
         <v>114</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G30" s="5">
         <v>2026</v>
@@ -5863,7 +5881,7 @@
         <v>154</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G31" s="5">
         <v>2025</v>
@@ -5892,7 +5910,7 @@
         <v>132</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G32" s="5">
         <v>2026</v>
@@ -5921,7 +5939,7 @@
         <v>132</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G33" s="5">
         <v>2026</v>
@@ -5950,7 +5968,7 @@
         <v>96</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G34" s="5">
         <v>2026</v>
@@ -5979,7 +5997,7 @@
         <v>174</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G35" s="5">
         <v>2025</v>
@@ -6008,7 +6026,7 @@
         <v>180</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G36" s="5">
         <v>2026</v>
@@ -6037,7 +6055,7 @@
         <v>102</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G37" s="5">
         <v>2026</v>
@@ -6066,7 +6084,7 @@
         <v>192</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G38" s="5">
         <v>2025</v>
@@ -6093,7 +6111,7 @@
         <v>196</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G39" s="5">
         <v>2025</v>
@@ -6122,7 +6140,7 @@
         <v>192</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G40" s="5">
         <v>2025</v>
@@ -6149,7 +6167,7 @@
         <v>108</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G41" s="5">
         <v>2026</v>
@@ -6170,7 +6188,7 @@
       <c r="D42" s="5"/>
       <c r="E42" s="5"/>
       <c r="F42" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G42" s="5"/>
       <c r="H42" s="5"/>
@@ -6187,7 +6205,7 @@
       <c r="D43" s="5"/>
       <c r="E43" s="5"/>
       <c r="F43" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G43" s="5"/>
       <c r="H43" s="5"/>
@@ -6204,7 +6222,7 @@
       <c r="D44" s="5"/>
       <c r="E44" s="5"/>
       <c r="F44" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G44" s="5"/>
       <c r="H44" s="5"/>
@@ -6221,7 +6239,7 @@
       <c r="D45" s="5"/>
       <c r="E45" s="5"/>
       <c r="F45" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G45" s="5"/>
       <c r="H45" s="5"/>
@@ -6238,7 +6256,7 @@
       <c r="D46" s="15"/>
       <c r="E46" s="15"/>
       <c r="F46" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G46" s="15"/>
       <c r="H46" s="15"/>
@@ -6255,7 +6273,7 @@
       <c r="D47" s="5"/>
       <c r="E47" s="5"/>
       <c r="F47" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G47" s="5"/>
       <c r="H47" s="5"/>
@@ -6272,7 +6290,7 @@
       <c r="D48" s="5"/>
       <c r="E48" s="5"/>
       <c r="F48" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G48" s="5"/>
       <c r="H48" s="5"/>
@@ -6289,7 +6307,7 @@
       <c r="D49" s="5"/>
       <c r="E49" s="5"/>
       <c r="F49" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G49" s="5"/>
       <c r="H49" s="5"/>
@@ -6306,7 +6324,7 @@
       <c r="D50" s="5"/>
       <c r="E50" s="5"/>
       <c r="F50" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G50" s="5"/>
       <c r="H50" s="5"/>
@@ -6323,7 +6341,7 @@
       <c r="D51" s="5"/>
       <c r="E51" s="5"/>
       <c r="F51" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G51" s="5"/>
       <c r="H51" s="5"/>
@@ -6340,7 +6358,7 @@
       <c r="D52" s="5"/>
       <c r="E52" s="5"/>
       <c r="F52" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G52" s="5"/>
       <c r="H52" s="5"/>
@@ -6363,7 +6381,7 @@
         <v>246</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G53" s="5"/>
       <c r="H53" s="18" t="s">
@@ -6388,7 +6406,7 @@
         <v>108</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G54" s="5"/>
       <c r="H54" s="18" t="s">
@@ -6413,7 +6431,7 @@
         <v>114</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G55" s="5"/>
       <c r="H55" s="18" t="s">
@@ -6438,7 +6456,7 @@
         <v>259</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G56" s="5"/>
       <c r="H56" s="18" t="s">
@@ -6463,7 +6481,7 @@
         <v>259</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G57" s="5"/>
       <c r="H57" s="18" t="s">
@@ -6478,7 +6496,7 @@
         <v>266</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C58" s="17" t="s">
         <v>267</v>
@@ -6488,7 +6506,7 @@
         <v>268</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G58" s="5"/>
       <c r="H58" s="18" t="s">
@@ -6507,7 +6525,7 @@
       <c r="D59" s="5"/>
       <c r="E59" s="5"/>
       <c r="F59" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G59" s="5"/>
       <c r="H59" s="5"/>
@@ -6524,7 +6542,7 @@
       <c r="D60" s="5"/>
       <c r="E60" s="5"/>
       <c r="F60" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G60" s="5"/>
       <c r="H60" s="5"/>
@@ -6541,7 +6559,7 @@
       <c r="D61" s="5"/>
       <c r="E61" s="5"/>
       <c r="F61" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G61" s="5"/>
       <c r="H61" s="5"/>
@@ -6558,7 +6576,7 @@
       <c r="D62" s="5"/>
       <c r="E62" s="5"/>
       <c r="F62" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G62" s="5"/>
       <c r="H62" s="5"/>
@@ -6575,7 +6593,7 @@
       <c r="D63" s="5"/>
       <c r="E63" s="5"/>
       <c r="F63" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G63" s="5"/>
       <c r="H63" s="5"/>
@@ -6592,7 +6610,7 @@
       <c r="D64" s="5"/>
       <c r="E64" s="5"/>
       <c r="F64" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G64" s="5"/>
       <c r="H64" s="5"/>
@@ -6609,7 +6627,7 @@
       <c r="D65" s="5"/>
       <c r="E65" s="5"/>
       <c r="F65" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G65" s="5"/>
       <c r="H65" s="5"/>

--- a/资源录入表新.xlsx
+++ b/资源录入表新.xlsx
@@ -1427,6 +1427,21 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Helvetica"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="10.5"/>
       <name val="Arial"/>
       <charset val="134"/>
@@ -1439,21 +1454,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF111111"/>
-      <name val="Helvetica"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="Helvetica"/>
       <charset val="134"/>
     </font>
@@ -1955,7 +1955,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2019,9 +2019,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2035,20 +2032,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2056,6 +2044,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2110,7 +2101,15 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="18">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2304,25 +2303,25 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="6"/>
+      <tableStyleElement type="totalRow" dxfId="5"/>
+      <tableStyleElement type="firstColumn" dxfId="4"/>
+      <tableStyleElement type="lastColumn" dxfId="3"/>
+      <tableStyleElement type="firstRowStripe" dxfId="2"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="1"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="17"/>
+      <tableStyleElement type="totalRow" dxfId="16"/>
+      <tableStyleElement type="firstRowStripe" dxfId="15"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="14"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="13"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="11"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="10"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="9"/>
+      <tableStyleElement type="pageFieldValues" dxfId="8"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -2590,7 +2589,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:O82"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
@@ -2646,31 +2645,31 @@
       <c r="O1" s="5"/>
     </row>
     <row r="2" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="C2" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="23" t="s">
+      <c r="D2" s="22" t="s">
         <v>14</v>
       </c>
       <c r="E2" s="8">
-        <v>8</v>
-      </c>
-      <c r="F2" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="23">
+      <c r="G2" s="22">
         <v>2026</v>
       </c>
-      <c r="H2" s="23" t="s">
+      <c r="H2" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="23" t="s">
+      <c r="I2" s="22" t="s">
         <v>17</v>
       </c>
       <c r="J2" s="13"/>
@@ -2681,31 +2680,31 @@
       <c r="O2" s="13"/>
     </row>
     <row r="3" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="23" t="s">
+      <c r="B3" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="23" t="s">
+      <c r="C3" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="23">
-        <v>10</v>
-      </c>
-      <c r="F3" s="23" t="s">
+      <c r="D3" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="8">
+        <v>11</v>
+      </c>
+      <c r="F3" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="23">
+      <c r="G3" s="22">
         <v>2026</v>
       </c>
-      <c r="H3" s="23" t="s">
+      <c r="H3" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="23" t="s">
+      <c r="I3" s="22" t="s">
         <v>21</v>
       </c>
       <c r="J3" s="13"/>
@@ -2716,31 +2715,31 @@
       <c r="O3" s="13"/>
     </row>
     <row r="4" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="23" t="s">
+      <c r="B4" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="23" t="s">
+      <c r="C4" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="23">
+      <c r="D4" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="8">
+        <v>25</v>
+      </c>
+      <c r="F4" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="22">
+        <v>2026</v>
+      </c>
+      <c r="H4" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="F4" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" s="23">
-        <v>2026</v>
-      </c>
-      <c r="H4" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="I4" s="23" t="s">
+      <c r="I4" s="22" t="s">
         <v>25</v>
       </c>
       <c r="J4" s="13"/>
@@ -2753,31 +2752,31 @@
       <c r="O4" s="13"/>
     </row>
     <row r="5" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="23" t="s">
+      <c r="C5" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="23" t="s">
+      <c r="D5" s="22" t="s">
         <v>14</v>
       </c>
       <c r="E5" s="8">
-        <v>22</v>
-      </c>
-      <c r="F5" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="23">
+      <c r="G5" s="22">
         <v>2026</v>
       </c>
-      <c r="H5" s="23" t="s">
+      <c r="H5" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="I5" s="23" t="s">
+      <c r="I5" s="22" t="s">
         <v>30</v>
       </c>
       <c r="J5" s="13"/>
@@ -2787,32 +2786,32 @@
       <c r="N5" s="13"/>
       <c r="O5" s="13"/>
     </row>
-    <row r="6" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A6" s="22" t="s">
+    <row r="6" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="A6" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="23" t="s">
+      <c r="C6" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="23" t="s">
+      <c r="D6" s="22" t="s">
         <v>14</v>
       </c>
       <c r="E6" s="8">
         <v>24</v>
       </c>
-      <c r="F6" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="G6" s="23">
+      <c r="F6" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" s="22">
         <v>2026</v>
       </c>
-      <c r="H6" s="23" t="s">
+      <c r="H6" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="I6" s="23" t="s">
+      <c r="I6" s="22" t="s">
         <v>35</v>
       </c>
       <c r="J6" s="13"/>
@@ -2829,14 +2828,14 @@
       <c r="B7" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="25" t="s">
+      <c r="C7" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="13">
-        <v>14</v>
+      <c r="D7" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="11">
+        <v>15</v>
       </c>
       <c r="F7" s="13" t="s">
         <v>15</v>
@@ -2857,32 +2856,32 @@
       <c r="N7" s="5"/>
       <c r="O7" s="5"/>
     </row>
-    <row r="8" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A8" s="22" t="s">
+    <row r="8" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="A8" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="B8" s="23" t="s">
+      <c r="B8" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="23" t="s">
+      <c r="C8" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="D8" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="23">
+      <c r="D8" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="25">
         <v>3</v>
       </c>
-      <c r="F8" s="23" t="s">
+      <c r="F8" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="G8" s="23">
+      <c r="G8" s="22">
         <v>2026</v>
       </c>
-      <c r="H8" s="23" t="s">
+      <c r="H8" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="I8" s="23" t="s">
+      <c r="I8" s="22" t="s">
         <v>44</v>
       </c>
       <c r="J8" s="13"/>
@@ -2892,32 +2891,32 @@
       <c r="N8" s="13"/>
       <c r="O8" s="13"/>
     </row>
-    <row r="9" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A9" s="22" t="s">
+    <row r="9" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="A9" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="23" t="s">
+      <c r="B9" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="C9" s="23" t="s">
+      <c r="C9" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="D9" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" s="23">
+      <c r="D9" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="25">
         <v>4</v>
       </c>
-      <c r="F9" s="23" t="s">
+      <c r="F9" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="G9" s="23">
+      <c r="G9" s="22">
         <v>2026</v>
       </c>
-      <c r="H9" s="23" t="s">
+      <c r="H9" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="I9" s="23" t="s">
+      <c r="I9" s="22" t="s">
         <v>48</v>
       </c>
       <c r="J9" s="13"/>
@@ -2927,67 +2926,67 @@
       <c r="N9" s="13"/>
       <c r="O9" s="13"/>
     </row>
-    <row r="10" s="21" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A10" s="26" t="s">
+    <row r="10" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A10" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="B10" s="27" t="s">
+      <c r="B10" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="C10" s="28" t="s">
+      <c r="C10" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="D10" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="27">
-        <v>1</v>
-      </c>
-      <c r="F10" s="27" t="s">
+      <c r="D10" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="8">
+        <v>2</v>
+      </c>
+      <c r="F10" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="G10" s="27">
+      <c r="G10" s="22">
         <v>2026</v>
       </c>
-      <c r="H10" s="29" t="s">
+      <c r="H10" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="I10" s="30" t="s">
+      <c r="I10" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="J10" s="30"/>
-      <c r="K10" s="30"/>
-      <c r="L10" s="30"/>
-      <c r="M10" s="30"/>
-      <c r="N10" s="30"/>
-      <c r="O10" s="30"/>
-    </row>
-    <row r="11" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A11" s="22" t="s">
+      <c r="J10" s="13"/>
+      <c r="K10" s="13"/>
+      <c r="L10" s="13"/>
+      <c r="M10" s="13"/>
+      <c r="N10" s="13"/>
+      <c r="O10" s="13"/>
+    </row>
+    <row r="11" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="A11" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="B11" s="23" t="s">
+      <c r="B11" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="C11" s="23" t="s">
+      <c r="C11" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="D11" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="23">
+      <c r="D11" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="25">
         <v>6</v>
       </c>
-      <c r="F11" s="23" t="s">
+      <c r="F11" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="G11" s="23">
+      <c r="G11" s="22">
         <v>2026</v>
       </c>
-      <c r="H11" s="23" t="s">
+      <c r="H11" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="I11" s="23" t="s">
+      <c r="I11" s="22" t="s">
         <v>57</v>
       </c>
       <c r="J11" s="13"/>
@@ -2999,32 +2998,32 @@
       <c r="N11" s="13"/>
       <c r="O11" s="13"/>
     </row>
-    <row r="12" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A12" s="22" t="s">
+    <row r="12" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="A12" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="B12" s="23" t="s">
+      <c r="B12" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="C12" s="23" t="s">
+      <c r="C12" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="D12" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E12" s="23">
-        <v>6</v>
-      </c>
-      <c r="F12" s="23" t="s">
+      <c r="D12" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="25">
+        <v>7</v>
+      </c>
+      <c r="F12" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="G12" s="23">
+      <c r="G12" s="22">
         <v>2026</v>
       </c>
-      <c r="H12" s="23" t="s">
+      <c r="H12" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="I12" s="23" t="s">
+      <c r="I12" s="22" t="s">
         <v>62</v>
       </c>
       <c r="J12" s="13"/>
@@ -3037,31 +3036,31 @@
       <c r="O12" s="13"/>
     </row>
     <row r="13" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A13" s="22" t="s">
+      <c r="A13" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="B13" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="C13" s="23" t="s">
+      <c r="C13" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="D13" s="23" t="s">
+      <c r="D13" s="22" t="s">
         <v>14</v>
       </c>
       <c r="E13" s="8">
-        <v>5</v>
-      </c>
-      <c r="F13" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="F13" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="G13" s="23">
+      <c r="G13" s="22">
         <v>2026</v>
       </c>
-      <c r="H13" s="23" t="s">
+      <c r="H13" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="I13" s="23" t="s">
+      <c r="I13" s="22" t="s">
         <v>65</v>
       </c>
       <c r="J13" s="13"/>
@@ -3074,31 +3073,31 @@
       <c r="O13" s="13"/>
     </row>
     <row r="14" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A14" s="22" t="s">
+      <c r="A14" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="B14" s="23" t="s">
+      <c r="B14" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="C14" s="23" t="s">
+      <c r="C14" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="D14" s="23" t="s">
+      <c r="D14" s="22" t="s">
         <v>14</v>
       </c>
       <c r="E14" s="8">
-        <v>7</v>
-      </c>
-      <c r="F14" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="G14" s="23">
+      <c r="G14" s="22">
         <v>2026</v>
       </c>
-      <c r="H14" s="23" t="s">
+      <c r="H14" s="22" t="s">
         <v>68</v>
       </c>
-      <c r="I14" s="23" t="s">
+      <c r="I14" s="22" t="s">
         <v>69</v>
       </c>
       <c r="J14" s="13"/>
@@ -3111,31 +3110,31 @@
       <c r="O14" s="13"/>
     </row>
     <row r="15" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A15" s="22" t="s">
+      <c r="A15" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="B15" s="23" t="s">
+      <c r="B15" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="C15" s="23" t="s">
+      <c r="C15" s="22" t="s">
         <v>71</v>
       </c>
-      <c r="D15" s="23" t="s">
+      <c r="D15" s="22" t="s">
         <v>14</v>
       </c>
       <c r="E15" s="8">
-        <v>9</v>
-      </c>
-      <c r="F15" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="G15" s="23">
+      <c r="G15" s="22">
         <v>2026</v>
       </c>
-      <c r="H15" s="23" t="s">
+      <c r="H15" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="I15" s="23" t="s">
+      <c r="I15" s="22" t="s">
         <v>73</v>
       </c>
       <c r="J15" s="13"/>
@@ -3147,32 +3146,32 @@
       <c r="N15" s="13"/>
       <c r="O15" s="13"/>
     </row>
-    <row r="16" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A16" s="22" t="s">
+    <row r="16" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="A16" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="B16" s="23" t="s">
+      <c r="B16" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="C16" s="23" t="s">
+      <c r="C16" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="D16" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E16" s="23">
+      <c r="D16" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" s="25">
         <v>4</v>
       </c>
-      <c r="F16" s="23" t="s">
+      <c r="F16" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="G16" s="23">
+      <c r="G16" s="22">
         <v>2026</v>
       </c>
-      <c r="H16" s="23" t="s">
+      <c r="H16" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="I16" s="23" t="s">
+      <c r="I16" s="22" t="s">
         <v>77</v>
       </c>
       <c r="J16" s="13"/>
@@ -3184,32 +3183,32 @@
       <c r="N16" s="13"/>
       <c r="O16" s="13"/>
     </row>
-    <row r="17" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A17" s="22" t="s">
+    <row r="17" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="A17" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="B17" s="23" t="s">
+      <c r="B17" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="C17" s="23" t="s">
+      <c r="C17" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="D17" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E17" s="23">
+      <c r="D17" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="E17" s="25">
         <v>8</v>
       </c>
-      <c r="F17" s="23" t="s">
+      <c r="F17" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="G17" s="23">
+      <c r="G17" s="22">
         <v>2026</v>
       </c>
-      <c r="H17" s="23" t="s">
+      <c r="H17" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="I17" s="23" t="s">
+      <c r="I17" s="22" t="s">
         <v>82</v>
       </c>
       <c r="J17" s="13"/>
@@ -3221,30 +3220,30 @@
       <c r="N17" s="13"/>
       <c r="O17" s="13"/>
     </row>
-    <row r="18" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A18" s="22" t="s">
+    <row r="18" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="A18" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="B18" s="23" t="s">
+      <c r="B18" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="C18" s="23" t="s">
+      <c r="C18" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="D18" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E18" s="23">
+      <c r="D18" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="25">
         <v>7</v>
       </c>
-      <c r="F18" s="23" t="s">
+      <c r="F18" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="G18" s="23">
+      <c r="G18" s="22">
         <v>2026</v>
       </c>
-      <c r="H18" s="23"/>
-      <c r="I18" s="23" t="s">
+      <c r="H18" s="22"/>
+      <c r="I18" s="22" t="s">
         <v>85</v>
       </c>
       <c r="J18" s="13"/>
@@ -3254,30 +3253,30 @@
       <c r="N18" s="13"/>
       <c r="O18" s="13"/>
     </row>
-    <row r="19" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A19" s="22" t="s">
+    <row r="19" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="A19" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="B19" s="23" t="s">
+      <c r="B19" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="23" t="s">
+      <c r="C19" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="D19" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E19" s="8">
+      <c r="D19" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19" s="25">
         <v>5</v>
       </c>
-      <c r="F19" s="23" t="s">
+      <c r="F19" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="G19" s="23">
+      <c r="G19" s="22">
         <v>2026</v>
       </c>
-      <c r="H19" s="23"/>
-      <c r="I19" s="23" t="s">
+      <c r="H19" s="22"/>
+      <c r="I19" s="22" t="s">
         <v>88</v>
       </c>
       <c r="J19" s="13"/>
@@ -3287,27 +3286,27 @@
       <c r="N19" s="13"/>
       <c r="O19" s="13"/>
     </row>
-    <row r="20" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A20" s="31" t="s">
+    <row r="20" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="A20" s="27" t="s">
         <v>89</v>
       </c>
       <c r="B20" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="C20" s="24" t="s">
+      <c r="C20" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="D20" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E20" s="24"/>
-      <c r="F20" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="G20" s="23">
+      <c r="D20" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="E20" s="23"/>
+      <c r="F20" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="G20" s="22">
         <v>2026</v>
       </c>
-      <c r="H20" s="23"/>
+      <c r="H20" s="22"/>
       <c r="I20" s="13" t="s">
         <v>91</v>
       </c>
@@ -3316,29 +3315,29 @@
       <c r="L20" s="13"/>
       <c r="M20" s="13"/>
       <c r="N20" s="13"/>
-      <c r="O20" s="32"/>
-    </row>
-    <row r="21" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A21" s="31" t="s">
+      <c r="O20" s="28"/>
+    </row>
+    <row r="21" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="A21" s="27" t="s">
         <v>92</v>
       </c>
       <c r="B21" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="C21" s="24" t="s">
+      <c r="C21" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="D21" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E21" s="24"/>
-      <c r="F21" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="G21" s="23">
+      <c r="D21" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="E21" s="23"/>
+      <c r="F21" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="G21" s="22">
         <v>2026</v>
       </c>
-      <c r="H21" s="23"/>
+      <c r="H21" s="22"/>
       <c r="I21" s="13" t="s">
         <v>93</v>
       </c>
@@ -3347,9 +3346,9 @@
       <c r="L21" s="13"/>
       <c r="M21" s="13"/>
       <c r="N21" s="13"/>
-      <c r="O21" s="32"/>
-    </row>
-    <row r="22" ht="25" customHeight="1" spans="1:15">
+      <c r="O21" s="28"/>
+    </row>
+    <row r="22" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A22" s="12" t="s">
         <v>94</v>
       </c>
@@ -3386,7 +3385,7 @@
       <c r="N22" s="5"/>
       <c r="O22" s="5"/>
     </row>
-    <row r="23" ht="25" customHeight="1" spans="1:15">
+    <row r="23" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A23" s="12" t="s">
         <v>100</v>
       </c>
@@ -3423,7 +3422,7 @@
       <c r="N23" s="5"/>
       <c r="O23" s="5"/>
     </row>
-    <row r="24" ht="25" customHeight="1" spans="1:15">
+    <row r="24" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A24" s="12" t="s">
         <v>106</v>
       </c>
@@ -3460,7 +3459,7 @@
       <c r="N24" s="5"/>
       <c r="O24" s="5"/>
     </row>
-    <row r="25" ht="25" customHeight="1" spans="1:15">
+    <row r="25" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A25" s="12" t="s">
         <v>112</v>
       </c>
@@ -3497,7 +3496,7 @@
       <c r="N25" s="5"/>
       <c r="O25" s="5"/>
     </row>
-    <row r="26" ht="25" customHeight="1" spans="1:15">
+    <row r="26" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A26" s="12" t="s">
         <v>118</v>
       </c>
@@ -3534,7 +3533,7 @@
       <c r="N26" s="5"/>
       <c r="O26" s="5"/>
     </row>
-    <row r="27" ht="25" customHeight="1" spans="1:15">
+    <row r="27" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A27" s="12" t="s">
         <v>124</v>
       </c>
@@ -3571,7 +3570,7 @@
       <c r="N27" s="15"/>
       <c r="O27" s="5"/>
     </row>
-    <row r="28" ht="25" customHeight="1" spans="1:15">
+    <row r="28" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A28" s="12" t="s">
         <v>130</v>
       </c>
@@ -3606,9 +3605,9 @@
       </c>
       <c r="M28" s="5"/>
       <c r="N28" s="5"/>
-      <c r="O28" s="33"/>
-    </row>
-    <row r="29" ht="25" customHeight="1" spans="1:15">
+      <c r="O28" s="29"/>
+    </row>
+    <row r="29" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A29" s="12" t="s">
         <v>136</v>
       </c>
@@ -3643,9 +3642,9 @@
       </c>
       <c r="M29" s="5"/>
       <c r="N29" s="5"/>
-      <c r="O29" s="33"/>
-    </row>
-    <row r="30" ht="25" customHeight="1" spans="1:15">
+      <c r="O29" s="29"/>
+    </row>
+    <row r="30" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A30" s="12" t="s">
         <v>142</v>
       </c>
@@ -3680,9 +3679,9 @@
       </c>
       <c r="M30" s="5"/>
       <c r="N30" s="5"/>
-      <c r="O30" s="33"/>
-    </row>
-    <row r="31" ht="25" customHeight="1" spans="1:15">
+      <c r="O30" s="29"/>
+    </row>
+    <row r="31" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A31" s="12" t="s">
         <v>148</v>
       </c>
@@ -3717,9 +3716,9 @@
       </c>
       <c r="M31" s="5"/>
       <c r="N31" s="5"/>
-      <c r="O31" s="33"/>
-    </row>
-    <row r="32" ht="25" customHeight="1" spans="1:15">
+      <c r="O31" s="29"/>
+    </row>
+    <row r="32" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A32" s="12" t="s">
         <v>152</v>
       </c>
@@ -3754,9 +3753,9 @@
       </c>
       <c r="M32" s="5"/>
       <c r="N32" s="5"/>
-      <c r="O32" s="33"/>
-    </row>
-    <row r="33" ht="25" customHeight="1" spans="1:15">
+      <c r="O32" s="29"/>
+    </row>
+    <row r="33" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A33" s="12" t="s">
         <v>158</v>
       </c>
@@ -3791,9 +3790,9 @@
       </c>
       <c r="M33" s="5"/>
       <c r="N33" s="5"/>
-      <c r="O33" s="33"/>
-    </row>
-    <row r="34" ht="25" customHeight="1" spans="1:15">
+      <c r="O33" s="29"/>
+    </row>
+    <row r="34" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A34" s="12" t="s">
         <v>163</v>
       </c>
@@ -3828,9 +3827,9 @@
       </c>
       <c r="M34" s="5"/>
       <c r="N34" s="5"/>
-      <c r="O34" s="33"/>
-    </row>
-    <row r="35" ht="25" customHeight="1" spans="1:15">
+      <c r="O34" s="29"/>
+    </row>
+    <row r="35" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A35" s="12" t="s">
         <v>168</v>
       </c>
@@ -3865,9 +3864,9 @@
       </c>
       <c r="M35" s="5"/>
       <c r="N35" s="5"/>
-      <c r="O35" s="33"/>
-    </row>
-    <row r="36" ht="25" customHeight="1" spans="1:15">
+      <c r="O35" s="29"/>
+    </row>
+    <row r="36" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A36" s="12" t="s">
         <v>173</v>
       </c>
@@ -3902,9 +3901,9 @@
       </c>
       <c r="M36" s="5"/>
       <c r="N36" s="5"/>
-      <c r="O36" s="33"/>
-    </row>
-    <row r="37" ht="25" customHeight="1" spans="1:15">
+      <c r="O36" s="29"/>
+    </row>
+    <row r="37" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A37" s="12" t="s">
         <v>178</v>
       </c>
@@ -3939,9 +3938,9 @@
       </c>
       <c r="M37" s="5"/>
       <c r="N37" s="5"/>
-      <c r="O37" s="33"/>
-    </row>
-    <row r="38" ht="25" customHeight="1" spans="1:15">
+      <c r="O37" s="29"/>
+    </row>
+    <row r="38" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A38" s="12" t="s">
         <v>184</v>
       </c>
@@ -3976,9 +3975,9 @@
       </c>
       <c r="M38" s="5"/>
       <c r="N38" s="5"/>
-      <c r="O38" s="33"/>
-    </row>
-    <row r="39" ht="25" customHeight="1" spans="1:15">
+      <c r="O38" s="29"/>
+    </row>
+    <row r="39" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A39" s="12" t="s">
         <v>189</v>
       </c>
@@ -4011,9 +4010,9 @@
       </c>
       <c r="M39" s="5"/>
       <c r="N39" s="5"/>
-      <c r="O39" s="33"/>
-    </row>
-    <row r="40" ht="25" customHeight="1" spans="1:15">
+      <c r="O39" s="29"/>
+    </row>
+    <row r="40" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A40" s="12" t="s">
         <v>194</v>
       </c>
@@ -4048,9 +4047,9 @@
       </c>
       <c r="M40" s="5"/>
       <c r="N40" s="5"/>
-      <c r="O40" s="33"/>
-    </row>
-    <row r="41" ht="25" customHeight="1" spans="1:15">
+      <c r="O40" s="29"/>
+    </row>
+    <row r="41" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A41" s="12" t="s">
         <v>200</v>
       </c>
@@ -4083,9 +4082,9 @@
       </c>
       <c r="M41" s="5"/>
       <c r="N41" s="5"/>
-      <c r="O41" s="33"/>
-    </row>
-    <row r="42" ht="25" customHeight="1" spans="1:15">
+      <c r="O41" s="29"/>
+    </row>
+    <row r="42" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A42" s="12" t="s">
         <v>203</v>
       </c>
@@ -4120,9 +4119,9 @@
       </c>
       <c r="M42" s="5"/>
       <c r="N42" s="5"/>
-      <c r="O42" s="33"/>
-    </row>
-    <row r="43" ht="25" customHeight="1" spans="1:15">
+      <c r="O42" s="29"/>
+    </row>
+    <row r="43" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A43" s="12" t="s">
         <v>208</v>
       </c>
@@ -4143,9 +4142,9 @@
       <c r="L43" s="5"/>
       <c r="M43" s="5"/>
       <c r="N43" s="5"/>
-      <c r="O43" s="33"/>
-    </row>
-    <row r="44" ht="25" customHeight="1" spans="1:15">
+      <c r="O43" s="29"/>
+    </row>
+    <row r="44" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A44" s="12" t="s">
         <v>210</v>
       </c>
@@ -4166,9 +4165,9 @@
       <c r="L44" s="5"/>
       <c r="M44" s="5"/>
       <c r="N44" s="5"/>
-      <c r="O44" s="33"/>
-    </row>
-    <row r="45" ht="25" customHeight="1" spans="1:15">
+      <c r="O44" s="29"/>
+    </row>
+    <row r="45" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A45" s="12" t="s">
         <v>212</v>
       </c>
@@ -4189,9 +4188,9 @@
       <c r="L45" s="5"/>
       <c r="M45" s="5"/>
       <c r="N45" s="5"/>
-      <c r="O45" s="33"/>
-    </row>
-    <row r="46" ht="25" customHeight="1" spans="1:15">
+      <c r="O45" s="29"/>
+    </row>
+    <row r="46" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A46" s="12" t="s">
         <v>214</v>
       </c>
@@ -4212,9 +4211,9 @@
       <c r="L46" s="5"/>
       <c r="M46" s="5"/>
       <c r="N46" s="5"/>
-      <c r="O46" s="33"/>
-    </row>
-    <row r="47" ht="25" customHeight="1" spans="1:15">
+      <c r="O46" s="29"/>
+    </row>
+    <row r="47" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A47" s="14" t="s">
         <v>216</v>
       </c>
@@ -4235,9 +4234,9 @@
       <c r="L47" s="5"/>
       <c r="M47" s="5"/>
       <c r="N47" s="5"/>
-      <c r="O47" s="33"/>
-    </row>
-    <row r="48" ht="25" customHeight="1" spans="1:15">
+      <c r="O47" s="29"/>
+    </row>
+    <row r="48" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A48" s="12" t="s">
         <v>218</v>
       </c>
@@ -4258,9 +4257,9 @@
       <c r="L48" s="5"/>
       <c r="M48" s="5"/>
       <c r="N48" s="5"/>
-      <c r="O48" s="33"/>
-    </row>
-    <row r="49" ht="25" customHeight="1" spans="1:15">
+      <c r="O48" s="29"/>
+    </row>
+    <row r="49" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A49" s="12" t="s">
         <v>220</v>
       </c>
@@ -4281,9 +4280,9 @@
       <c r="L49" s="5"/>
       <c r="M49" s="5"/>
       <c r="N49" s="5"/>
-      <c r="O49" s="33"/>
-    </row>
-    <row r="50" ht="25" customHeight="1" spans="1:15">
+      <c r="O49" s="29"/>
+    </row>
+    <row r="50" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A50" s="12" t="s">
         <v>222</v>
       </c>
@@ -4304,9 +4303,9 @@
       <c r="L50" s="5"/>
       <c r="M50" s="5"/>
       <c r="N50" s="5"/>
-      <c r="O50" s="33"/>
-    </row>
-    <row r="51" ht="25" customHeight="1" spans="1:15">
+      <c r="O50" s="29"/>
+    </row>
+    <row r="51" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A51" s="12" t="s">
         <v>224</v>
       </c>
@@ -4327,9 +4326,9 @@
       <c r="L51" s="5"/>
       <c r="M51" s="5"/>
       <c r="N51" s="5"/>
-      <c r="O51" s="33"/>
-    </row>
-    <row r="52" ht="25" customHeight="1" spans="1:15">
+      <c r="O51" s="29"/>
+    </row>
+    <row r="52" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A52" s="12" t="s">
         <v>226</v>
       </c>
@@ -4350,9 +4349,9 @@
       <c r="L52" s="5"/>
       <c r="M52" s="5"/>
       <c r="N52" s="5"/>
-      <c r="O52" s="33"/>
-    </row>
-    <row r="53" ht="25" customHeight="1" spans="1:15">
+      <c r="O52" s="29"/>
+    </row>
+    <row r="53" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A53" s="12" t="s">
         <v>228</v>
       </c>
@@ -4373,9 +4372,9 @@
       <c r="L53" s="5"/>
       <c r="M53" s="5"/>
       <c r="N53" s="5"/>
-      <c r="O53" s="33"/>
-    </row>
-    <row r="54" ht="25" customHeight="1" spans="1:15">
+      <c r="O53" s="29"/>
+    </row>
+    <row r="54" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A54" s="12" t="s">
         <v>230</v>
       </c>
@@ -4396,9 +4395,9 @@
       <c r="L54" s="5"/>
       <c r="M54" s="5"/>
       <c r="N54" s="5"/>
-      <c r="O54" s="33"/>
-    </row>
-    <row r="55" ht="25" customHeight="1" spans="1:15">
+      <c r="O54" s="29"/>
+    </row>
+    <row r="55" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A55" s="12" t="s">
         <v>232</v>
       </c>
@@ -4418,9 +4417,9 @@
       <c r="L55" s="5"/>
       <c r="M55" s="5"/>
       <c r="N55" s="5"/>
-      <c r="O55" s="33"/>
-    </row>
-    <row r="56" ht="25" customHeight="1" spans="1:15">
+      <c r="O55" s="29"/>
+    </row>
+    <row r="56" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A56" s="12" t="s">
         <v>234</v>
       </c>
@@ -4441,9 +4440,9 @@
       <c r="L56" s="5"/>
       <c r="M56" s="5"/>
       <c r="N56" s="5"/>
-      <c r="O56" s="33"/>
-    </row>
-    <row r="57" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="O56" s="29"/>
+    </row>
+    <row r="57" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A57" s="12" t="s">
         <v>236</v>
       </c>
@@ -4464,9 +4463,9 @@
       <c r="L57" s="5"/>
       <c r="M57" s="5"/>
       <c r="N57" s="5"/>
-      <c r="O57" s="33"/>
-    </row>
-    <row r="58" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="O57" s="29"/>
+    </row>
+    <row r="58" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A58" s="12" t="s">
         <v>238</v>
       </c>
@@ -4487,9 +4486,9 @@
       <c r="L58" s="5"/>
       <c r="M58" s="5"/>
       <c r="N58" s="5"/>
-      <c r="O58" s="33"/>
-    </row>
-    <row r="59" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="O58" s="29"/>
+    </row>
+    <row r="59" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A59" s="12" t="s">
         <v>240</v>
       </c>
@@ -4510,9 +4509,9 @@
       <c r="L59" s="5"/>
       <c r="M59" s="5"/>
       <c r="N59" s="5"/>
-      <c r="O59" s="33"/>
-    </row>
-    <row r="60" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="O59" s="29"/>
+    </row>
+    <row r="60" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A60" s="12" t="s">
         <v>242</v>
       </c>
@@ -4533,9 +4532,9 @@
       <c r="L60" s="5"/>
       <c r="M60" s="5"/>
       <c r="N60" s="5"/>
-      <c r="O60" s="33"/>
-    </row>
-    <row r="61" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="O60" s="29"/>
+    </row>
+    <row r="61" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A61" s="12" t="s">
         <v>244</v>
       </c>
@@ -4564,9 +4563,9 @@
       <c r="L61" s="5"/>
       <c r="M61" s="5"/>
       <c r="N61" s="5"/>
-      <c r="O61" s="33"/>
-    </row>
-    <row r="62" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="O61" s="29"/>
+    </row>
+    <row r="62" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A62" s="12" t="s">
         <v>249</v>
       </c>
@@ -4597,7 +4596,7 @@
       <c r="N62" s="5"/>
       <c r="O62" s="5"/>
     </row>
-    <row r="63" customFormat="1" ht="25" customHeight="1" spans="1:15">
+    <row r="63" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A63" s="12" t="s">
         <v>253</v>
       </c>
@@ -4626,9 +4625,9 @@
       <c r="L63" s="5"/>
       <c r="M63" s="5"/>
       <c r="N63" s="5"/>
-      <c r="O63" s="33"/>
-    </row>
-    <row r="64" ht="25" customHeight="1" spans="1:15">
+      <c r="O63" s="29"/>
+    </row>
+    <row r="64" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A64" s="12" t="s">
         <v>257</v>
       </c>
@@ -4657,9 +4656,9 @@
       <c r="L64" s="5"/>
       <c r="M64" s="5"/>
       <c r="N64" s="5"/>
-      <c r="O64" s="33"/>
-    </row>
-    <row r="65" ht="25" customHeight="1" spans="1:15">
+      <c r="O64" s="29"/>
+    </row>
+    <row r="65" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A65" s="12" t="s">
         <v>262</v>
       </c>
@@ -4688,9 +4687,9 @@
       <c r="L65" s="5"/>
       <c r="M65" s="5"/>
       <c r="N65" s="5"/>
-      <c r="O65" s="33"/>
-    </row>
-    <row r="66" ht="25" customHeight="1" spans="1:15">
+      <c r="O65" s="29"/>
+    </row>
+    <row r="66" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A66" s="12" t="s">
         <v>266</v>
       </c>
@@ -4719,14 +4718,14 @@
       <c r="L66" s="5"/>
       <c r="M66" s="5"/>
       <c r="N66" s="5"/>
-      <c r="O66" s="33"/>
+      <c r="O66" s="29"/>
     </row>
     <row r="67" ht="25" customHeight="1" spans="1:15">
       <c r="A67" s="12"/>
       <c r="B67" s="5"/>
       <c r="C67" s="5"/>
       <c r="D67" s="5"/>
-      <c r="E67" s="5"/>
+      <c r="E67" s="30"/>
       <c r="F67" s="13"/>
       <c r="G67" s="5"/>
       <c r="H67" s="5"/>
@@ -4994,6 +4993,14 @@
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:O66" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="4">
+      <colorFilter dxfId="0"/>
+    </filterColumn>
+    <filterColumn colId="5">
+      <filters>
+        <filter val="更新中"/>
+      </filters>
+    </filterColumn>
     <sortState ref="A1:O66">
       <sortCondition ref="F1"/>
     </sortState>

--- a/资源录入表新.xlsx
+++ b/资源录入表新.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="283">
   <si>
     <t>剧名</t>
   </si>
@@ -1169,6 +1169,95 @@
     <t xml:space="preserve">链接: https://pan.baidu.com/s/1wvdr54elVEWkt-5xM-qUKQ 提取码: udkd </t>
   </si>
   <si>
+    <t>除恶</t>
+  </si>
+  <si>
+    <t>经典剧</t>
+  </si>
+  <si>
+    <r>
+      <t>剧情</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>悬疑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>犯罪</t>
+    </r>
+  </si>
+  <si>
+    <t>: 任素汐/王骁/蔡文静/李泽锋/王宥</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1j88hGakN1r_Sp4TRaE-qvQ 提取码: zpsm </t>
+  </si>
+  <si>
     <t>网站观影指南</t>
   </si>
   <si>
@@ -1224,7 +1313,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="34">
+  <fonts count="35">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1280,6 +1369,12 @@
       <sz val="11"/>
       <color rgb="FF111111"/>
       <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9.75"/>
+      <color rgb="FF111111"/>
+      <name val="Helvetica"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1427,12 +1522,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10.5"/>
       <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10.5"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1442,12 +1537,12 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10.5"/>
+      <sz val="12"/>
       <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10.5"/>
+      <sz val="12"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1825,137 +1920,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2031,12 +2126,15 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2046,8 +2144,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2101,15 +2199,7 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="18">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2303,25 +2393,25 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="7"/>
-      <tableStyleElement type="headerRow" dxfId="6"/>
-      <tableStyleElement type="totalRow" dxfId="5"/>
-      <tableStyleElement type="firstColumn" dxfId="4"/>
-      <tableStyleElement type="lastColumn" dxfId="3"/>
-      <tableStyleElement type="firstRowStripe" dxfId="2"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="1"/>
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="17"/>
-      <tableStyleElement type="totalRow" dxfId="16"/>
-      <tableStyleElement type="firstRowStripe" dxfId="15"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="14"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="13"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="11"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="10"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="9"/>
-      <tableStyleElement type="pageFieldValues" dxfId="8"/>
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -2658,7 +2748,7 @@
         <v>14</v>
       </c>
       <c r="E2" s="8">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F2" s="22" t="s">
         <v>15</v>
@@ -2693,7 +2783,7 @@
         <v>14</v>
       </c>
       <c r="E3" s="8">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F3" s="22" t="s">
         <v>15</v>
@@ -2728,7 +2818,7 @@
         <v>14</v>
       </c>
       <c r="E4" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F4" s="22" t="s">
         <v>15</v>
@@ -2765,7 +2855,7 @@
         <v>14</v>
       </c>
       <c r="E5" s="8">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F5" s="22" t="s">
         <v>15</v>
@@ -2834,7 +2924,7 @@
       <c r="D7" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="11">
+      <c r="E7" s="25">
         <v>15</v>
       </c>
       <c r="F7" s="13" t="s">
@@ -2856,7 +2946,7 @@
       <c r="N7" s="5"/>
       <c r="O7" s="5"/>
     </row>
-    <row r="8" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
+    <row r="8" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A8" s="21" t="s">
         <v>40</v>
       </c>
@@ -2869,7 +2959,7 @@
       <c r="D8" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="25">
+      <c r="E8" s="22">
         <v>3</v>
       </c>
       <c r="F8" s="22" t="s">
@@ -2891,7 +2981,7 @@
       <c r="N8" s="13"/>
       <c r="O8" s="13"/>
     </row>
-    <row r="9" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
+    <row r="9" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A9" s="21" t="s">
         <v>45</v>
       </c>
@@ -2904,7 +2994,7 @@
       <c r="D9" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="E9" s="25">
+      <c r="E9" s="22">
         <v>4</v>
       </c>
       <c r="F9" s="22" t="s">
@@ -2939,7 +3029,7 @@
       <c r="D10" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="8">
+      <c r="E10" s="27">
         <v>2</v>
       </c>
       <c r="F10" s="22" t="s">
@@ -2961,7 +3051,7 @@
       <c r="N10" s="13"/>
       <c r="O10" s="13"/>
     </row>
-    <row r="11" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
+    <row r="11" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A11" s="21" t="s">
         <v>54</v>
       </c>
@@ -2974,8 +3064,8 @@
       <c r="D11" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="E11" s="25">
-        <v>6</v>
+      <c r="E11" s="8">
+        <v>7</v>
       </c>
       <c r="F11" s="22" t="s">
         <v>15</v>
@@ -2998,7 +3088,7 @@
       <c r="N11" s="13"/>
       <c r="O11" s="13"/>
     </row>
-    <row r="12" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
+    <row r="12" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A12" s="21" t="s">
         <v>58</v>
       </c>
@@ -3011,7 +3101,7 @@
       <c r="D12" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="E12" s="25">
+      <c r="E12" s="22">
         <v>7</v>
       </c>
       <c r="F12" s="22" t="s">
@@ -3048,7 +3138,7 @@
       <c r="D13" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="E13" s="8">
+      <c r="E13" s="27">
         <v>6</v>
       </c>
       <c r="F13" s="22" t="s">
@@ -3085,7 +3175,7 @@
       <c r="D14" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="E14" s="8">
+      <c r="E14" s="27">
         <v>8</v>
       </c>
       <c r="F14" s="22" t="s">
@@ -3122,7 +3212,7 @@
       <c r="D15" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="E15" s="8">
+      <c r="E15" s="27">
         <v>10</v>
       </c>
       <c r="F15" s="22" t="s">
@@ -3146,7 +3236,7 @@
       <c r="N15" s="13"/>
       <c r="O15" s="13"/>
     </row>
-    <row r="16" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
+    <row r="16" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A16" s="21" t="s">
         <v>74</v>
       </c>
@@ -3159,7 +3249,7 @@
       <c r="D16" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="E16" s="25">
+      <c r="E16" s="22">
         <v>4</v>
       </c>
       <c r="F16" s="22" t="s">
@@ -3183,7 +3273,7 @@
       <c r="N16" s="13"/>
       <c r="O16" s="13"/>
     </row>
-    <row r="17" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
+    <row r="17" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A17" s="21" t="s">
         <v>79</v>
       </c>
@@ -3196,7 +3286,7 @@
       <c r="D17" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="E17" s="25">
+      <c r="E17" s="22">
         <v>8</v>
       </c>
       <c r="F17" s="22" t="s">
@@ -3220,7 +3310,7 @@
       <c r="N17" s="13"/>
       <c r="O17" s="13"/>
     </row>
-    <row r="18" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
+    <row r="18" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A18" s="21" t="s">
         <v>83</v>
       </c>
@@ -3233,7 +3323,7 @@
       <c r="D18" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="E18" s="25">
+      <c r="E18" s="22">
         <v>7</v>
       </c>
       <c r="F18" s="22" t="s">
@@ -3253,7 +3343,7 @@
       <c r="N18" s="13"/>
       <c r="O18" s="13"/>
     </row>
-    <row r="19" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
+    <row r="19" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A19" s="21" t="s">
         <v>86</v>
       </c>
@@ -3266,7 +3356,7 @@
       <c r="D19" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="E19" s="25">
+      <c r="E19" s="22">
         <v>5</v>
       </c>
       <c r="F19" s="22" t="s">
@@ -3287,7 +3377,7 @@
       <c r="O19" s="13"/>
     </row>
     <row r="20" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A20" s="27" t="s">
+      <c r="A20" s="28" t="s">
         <v>89</v>
       </c>
       <c r="B20" s="13" t="s">
@@ -3315,10 +3405,10 @@
       <c r="L20" s="13"/>
       <c r="M20" s="13"/>
       <c r="N20" s="13"/>
-      <c r="O20" s="28"/>
+      <c r="O20" s="29"/>
     </row>
     <row r="21" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A21" s="27" t="s">
+      <c r="A21" s="28" t="s">
         <v>92</v>
       </c>
       <c r="B21" s="13" t="s">
@@ -3346,7 +3436,7 @@
       <c r="L21" s="13"/>
       <c r="M21" s="13"/>
       <c r="N21" s="13"/>
-      <c r="O21" s="28"/>
+      <c r="O21" s="29"/>
     </row>
     <row r="22" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A22" s="12" t="s">
@@ -3605,7 +3695,7 @@
       </c>
       <c r="M28" s="5"/>
       <c r="N28" s="5"/>
-      <c r="O28" s="29"/>
+      <c r="O28" s="30"/>
     </row>
     <row r="29" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A29" s="12" t="s">
@@ -3642,7 +3732,7 @@
       </c>
       <c r="M29" s="5"/>
       <c r="N29" s="5"/>
-      <c r="O29" s="29"/>
+      <c r="O29" s="30"/>
     </row>
     <row r="30" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A30" s="12" t="s">
@@ -3679,7 +3769,7 @@
       </c>
       <c r="M30" s="5"/>
       <c r="N30" s="5"/>
-      <c r="O30" s="29"/>
+      <c r="O30" s="30"/>
     </row>
     <row r="31" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A31" s="12" t="s">
@@ -3716,7 +3806,7 @@
       </c>
       <c r="M31" s="5"/>
       <c r="N31" s="5"/>
-      <c r="O31" s="29"/>
+      <c r="O31" s="30"/>
     </row>
     <row r="32" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A32" s="12" t="s">
@@ -3753,7 +3843,7 @@
       </c>
       <c r="M32" s="5"/>
       <c r="N32" s="5"/>
-      <c r="O32" s="29"/>
+      <c r="O32" s="30"/>
     </row>
     <row r="33" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A33" s="12" t="s">
@@ -3790,7 +3880,7 @@
       </c>
       <c r="M33" s="5"/>
       <c r="N33" s="5"/>
-      <c r="O33" s="29"/>
+      <c r="O33" s="30"/>
     </row>
     <row r="34" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A34" s="12" t="s">
@@ -3827,7 +3917,7 @@
       </c>
       <c r="M34" s="5"/>
       <c r="N34" s="5"/>
-      <c r="O34" s="29"/>
+      <c r="O34" s="30"/>
     </row>
     <row r="35" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A35" s="12" t="s">
@@ -3864,7 +3954,7 @@
       </c>
       <c r="M35" s="5"/>
       <c r="N35" s="5"/>
-      <c r="O35" s="29"/>
+      <c r="O35" s="30"/>
     </row>
     <row r="36" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A36" s="12" t="s">
@@ -3901,7 +3991,7 @@
       </c>
       <c r="M36" s="5"/>
       <c r="N36" s="5"/>
-      <c r="O36" s="29"/>
+      <c r="O36" s="30"/>
     </row>
     <row r="37" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A37" s="12" t="s">
@@ -3938,7 +4028,7 @@
       </c>
       <c r="M37" s="5"/>
       <c r="N37" s="5"/>
-      <c r="O37" s="29"/>
+      <c r="O37" s="30"/>
     </row>
     <row r="38" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A38" s="12" t="s">
@@ -3975,7 +4065,7 @@
       </c>
       <c r="M38" s="5"/>
       <c r="N38" s="5"/>
-      <c r="O38" s="29"/>
+      <c r="O38" s="30"/>
     </row>
     <row r="39" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A39" s="12" t="s">
@@ -4010,7 +4100,7 @@
       </c>
       <c r="M39" s="5"/>
       <c r="N39" s="5"/>
-      <c r="O39" s="29"/>
+      <c r="O39" s="30"/>
     </row>
     <row r="40" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A40" s="12" t="s">
@@ -4047,7 +4137,7 @@
       </c>
       <c r="M40" s="5"/>
       <c r="N40" s="5"/>
-      <c r="O40" s="29"/>
+      <c r="O40" s="30"/>
     </row>
     <row r="41" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A41" s="12" t="s">
@@ -4082,7 +4172,7 @@
       </c>
       <c r="M41" s="5"/>
       <c r="N41" s="5"/>
-      <c r="O41" s="29"/>
+      <c r="O41" s="30"/>
     </row>
     <row r="42" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A42" s="12" t="s">
@@ -4119,7 +4209,7 @@
       </c>
       <c r="M42" s="5"/>
       <c r="N42" s="5"/>
-      <c r="O42" s="29"/>
+      <c r="O42" s="30"/>
     </row>
     <row r="43" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A43" s="12" t="s">
@@ -4142,7 +4232,7 @@
       <c r="L43" s="5"/>
       <c r="M43" s="5"/>
       <c r="N43" s="5"/>
-      <c r="O43" s="29"/>
+      <c r="O43" s="30"/>
     </row>
     <row r="44" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A44" s="12" t="s">
@@ -4165,7 +4255,7 @@
       <c r="L44" s="5"/>
       <c r="M44" s="5"/>
       <c r="N44" s="5"/>
-      <c r="O44" s="29"/>
+      <c r="O44" s="30"/>
     </row>
     <row r="45" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A45" s="12" t="s">
@@ -4188,7 +4278,7 @@
       <c r="L45" s="5"/>
       <c r="M45" s="5"/>
       <c r="N45" s="5"/>
-      <c r="O45" s="29"/>
+      <c r="O45" s="30"/>
     </row>
     <row r="46" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A46" s="12" t="s">
@@ -4211,7 +4301,7 @@
       <c r="L46" s="5"/>
       <c r="M46" s="5"/>
       <c r="N46" s="5"/>
-      <c r="O46" s="29"/>
+      <c r="O46" s="30"/>
     </row>
     <row r="47" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A47" s="14" t="s">
@@ -4234,7 +4324,7 @@
       <c r="L47" s="5"/>
       <c r="M47" s="5"/>
       <c r="N47" s="5"/>
-      <c r="O47" s="29"/>
+      <c r="O47" s="30"/>
     </row>
     <row r="48" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A48" s="12" t="s">
@@ -4257,7 +4347,7 @@
       <c r="L48" s="5"/>
       <c r="M48" s="5"/>
       <c r="N48" s="5"/>
-      <c r="O48" s="29"/>
+      <c r="O48" s="30"/>
     </row>
     <row r="49" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A49" s="12" t="s">
@@ -4280,7 +4370,7 @@
       <c r="L49" s="5"/>
       <c r="M49" s="5"/>
       <c r="N49" s="5"/>
-      <c r="O49" s="29"/>
+      <c r="O49" s="30"/>
     </row>
     <row r="50" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A50" s="12" t="s">
@@ -4303,7 +4393,7 @@
       <c r="L50" s="5"/>
       <c r="M50" s="5"/>
       <c r="N50" s="5"/>
-      <c r="O50" s="29"/>
+      <c r="O50" s="30"/>
     </row>
     <row r="51" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A51" s="12" t="s">
@@ -4326,7 +4416,7 @@
       <c r="L51" s="5"/>
       <c r="M51" s="5"/>
       <c r="N51" s="5"/>
-      <c r="O51" s="29"/>
+      <c r="O51" s="30"/>
     </row>
     <row r="52" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A52" s="12" t="s">
@@ -4349,7 +4439,7 @@
       <c r="L52" s="5"/>
       <c r="M52" s="5"/>
       <c r="N52" s="5"/>
-      <c r="O52" s="29"/>
+      <c r="O52" s="30"/>
     </row>
     <row r="53" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A53" s="12" t="s">
@@ -4372,7 +4462,7 @@
       <c r="L53" s="5"/>
       <c r="M53" s="5"/>
       <c r="N53" s="5"/>
-      <c r="O53" s="29"/>
+      <c r="O53" s="30"/>
     </row>
     <row r="54" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A54" s="12" t="s">
@@ -4395,7 +4485,7 @@
       <c r="L54" s="5"/>
       <c r="M54" s="5"/>
       <c r="N54" s="5"/>
-      <c r="O54" s="29"/>
+      <c r="O54" s="30"/>
     </row>
     <row r="55" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A55" s="12" t="s">
@@ -4417,7 +4507,7 @@
       <c r="L55" s="5"/>
       <c r="M55" s="5"/>
       <c r="N55" s="5"/>
-      <c r="O55" s="29"/>
+      <c r="O55" s="30"/>
     </row>
     <row r="56" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A56" s="12" t="s">
@@ -4440,7 +4530,7 @@
       <c r="L56" s="5"/>
       <c r="M56" s="5"/>
       <c r="N56" s="5"/>
-      <c r="O56" s="29"/>
+      <c r="O56" s="30"/>
     </row>
     <row r="57" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A57" s="12" t="s">
@@ -4463,7 +4553,7 @@
       <c r="L57" s="5"/>
       <c r="M57" s="5"/>
       <c r="N57" s="5"/>
-      <c r="O57" s="29"/>
+      <c r="O57" s="30"/>
     </row>
     <row r="58" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A58" s="12" t="s">
@@ -4486,7 +4576,7 @@
       <c r="L58" s="5"/>
       <c r="M58" s="5"/>
       <c r="N58" s="5"/>
-      <c r="O58" s="29"/>
+      <c r="O58" s="30"/>
     </row>
     <row r="59" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A59" s="12" t="s">
@@ -4509,7 +4599,7 @@
       <c r="L59" s="5"/>
       <c r="M59" s="5"/>
       <c r="N59" s="5"/>
-      <c r="O59" s="29"/>
+      <c r="O59" s="30"/>
     </row>
     <row r="60" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A60" s="12" t="s">
@@ -4532,7 +4622,7 @@
       <c r="L60" s="5"/>
       <c r="M60" s="5"/>
       <c r="N60" s="5"/>
-      <c r="O60" s="29"/>
+      <c r="O60" s="30"/>
     </row>
     <row r="61" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A61" s="12" t="s">
@@ -4563,7 +4653,7 @@
       <c r="L61" s="5"/>
       <c r="M61" s="5"/>
       <c r="N61" s="5"/>
-      <c r="O61" s="29"/>
+      <c r="O61" s="30"/>
     </row>
     <row r="62" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A62" s="12" t="s">
@@ -4625,7 +4715,7 @@
       <c r="L63" s="5"/>
       <c r="M63" s="5"/>
       <c r="N63" s="5"/>
-      <c r="O63" s="29"/>
+      <c r="O63" s="30"/>
     </row>
     <row r="64" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A64" s="12" t="s">
@@ -4656,7 +4746,7 @@
       <c r="L64" s="5"/>
       <c r="M64" s="5"/>
       <c r="N64" s="5"/>
-      <c r="O64" s="29"/>
+      <c r="O64" s="30"/>
     </row>
     <row r="65" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A65" s="12" t="s">
@@ -4687,7 +4777,7 @@
       <c r="L65" s="5"/>
       <c r="M65" s="5"/>
       <c r="N65" s="5"/>
-      <c r="O65" s="29"/>
+      <c r="O65" s="30"/>
     </row>
     <row r="66" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A66" s="12" t="s">
@@ -4718,18 +4808,36 @@
       <c r="L66" s="5"/>
       <c r="M66" s="5"/>
       <c r="N66" s="5"/>
-      <c r="O66" s="29"/>
+      <c r="O66" s="30"/>
     </row>
     <row r="67" ht="25" customHeight="1" spans="1:15">
-      <c r="A67" s="12"/>
-      <c r="B67" s="5"/>
-      <c r="C67" s="5"/>
-      <c r="D67" s="5"/>
-      <c r="E67" s="30"/>
-      <c r="F67" s="13"/>
-      <c r="G67" s="5"/>
-      <c r="H67" s="5"/>
-      <c r="I67" s="5"/>
+      <c r="A67" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="C67" s="31" t="s">
+        <v>273</v>
+      </c>
+      <c r="D67" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="E67" s="11">
+        <v>16</v>
+      </c>
+      <c r="F67" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G67" s="22">
+        <v>2026</v>
+      </c>
+      <c r="H67" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="I67" s="5" t="s">
+        <v>275</v>
+      </c>
       <c r="J67" s="5"/>
       <c r="K67" s="5"/>
       <c r="L67" s="5"/>
@@ -4880,7 +4988,6 @@
       <c r="E76" s="5"/>
       <c r="F76" s="13"/>
       <c r="G76" s="5"/>
-      <c r="H76" s="5"/>
       <c r="I76" s="5"/>
       <c r="J76" s="5"/>
       <c r="K76" s="5"/>
@@ -4993,9 +5100,6 @@
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:O66" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="4">
-      <colorFilter dxfId="0"/>
-    </filterColumn>
     <filterColumn colId="5">
       <filters>
         <filter val="更新中"/>
@@ -5032,7 +5136,7 @@
   <sheetData>
     <row r="1" ht="33" customHeight="1" spans="1:9">
       <c r="A1" s="3" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -5079,7 +5183,7 @@
         <v>12</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>14</v>
@@ -5539,7 +5643,7 @@
         <v>41</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>14</v>
@@ -5564,7 +5668,7 @@
         <v>41</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>14</v>
@@ -6442,7 +6546,7 @@
       </c>
       <c r="G55" s="5"/>
       <c r="H55" s="18" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="I55" s="5" t="s">
         <v>256</v>
@@ -6467,7 +6571,7 @@
       </c>
       <c r="G56" s="5"/>
       <c r="H56" s="18" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="I56" s="5" t="s">
         <v>261</v>
@@ -6492,7 +6596,7 @@
       </c>
       <c r="G57" s="5"/>
       <c r="H57" s="18" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="I57" s="5" t="s">
         <v>265</v>
@@ -6517,7 +6621,7 @@
       </c>
       <c r="G58" s="5"/>
       <c r="H58" s="18" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="I58" s="5" t="s">
         <v>270</v>

--- a/资源录入表新.xlsx
+++ b/资源录入表新.xlsx
@@ -16,7 +16,7 @@
     <sheet name="资源录入表 (2)" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">资源录入表!$A$1:$O$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">资源录入表!$A$1:$O$68</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'资源录入表 (2)'!$A$2:$I$20</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="845" uniqueCount="286">
   <si>
     <t>剧名</t>
   </si>
@@ -201,6 +201,145 @@
   </si>
   <si>
     <t xml:space="preserve">链接: https://pan.baidu.com/s/1C1Dpxyv71CYv6Y7P5TvTDg 提取码: z3ta </t>
+  </si>
+  <si>
+    <t>天才，女友</t>
+  </si>
+  <si>
+    <r>
+      <t>剧情</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>爱情</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF3377AA"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>田曦薇</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF3377AA"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>胡一天</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF3377AA"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>赖伟明</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF3377AA"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>安沺</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF3377AA"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>夏</t>
+    </r>
   </si>
   <si>
     <t>李熊猫</t>
@@ -759,46 +898,46 @@
     <t>检察官室的提案</t>
   </si>
   <si>
+    <t>韩剧/律政</t>
+  </si>
+  <si>
+    <t>全10集</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1jvr5zI23AKq4GmnhIAUcQA 提取码: tb3q </t>
+  </si>
+  <si>
+    <t>明天也要上班</t>
+  </si>
+  <si>
+    <t>韩剧/职场</t>
+  </si>
+  <si>
+    <t>全12集</t>
+  </si>
+  <si>
+    <t>姜美娜</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1O5DgZoezv_6Y-YXs2rVA1Q 提取码: 6rfq </t>
+  </si>
+  <si>
+    <t>韩剧 姜美娜主演</t>
+  </si>
+  <si>
+    <t>金特务·本色回归</t>
+  </si>
+  <si>
+    <t>韩剧/动作/悬疑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1Fb4YyOJqWJU5Bnrjpp5Hhg 提取码: e65c </t>
+  </si>
+  <si>
+    <t>聪明镇</t>
+  </si>
+  <si>
     <t>外剧</t>
-  </si>
-  <si>
-    <t>韩剧/律政</t>
-  </si>
-  <si>
-    <t>全10集</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1jvr5zI23AKq4GmnhIAUcQA 提取码: tb3q </t>
-  </si>
-  <si>
-    <t>明天也要上班</t>
-  </si>
-  <si>
-    <t>韩剧/职场</t>
-  </si>
-  <si>
-    <t>全12集</t>
-  </si>
-  <si>
-    <t>姜美娜</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1O5DgZoezv_6Y-YXs2rVA1Q 提取码: 6rfq </t>
-  </si>
-  <si>
-    <t>韩剧 姜美娜主演</t>
-  </si>
-  <si>
-    <t>金特务·本色回归</t>
-  </si>
-  <si>
-    <t>韩剧/动作/悬疑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">链接: https://pan.baidu.com/s/1Fb4YyOJqWJU5Bnrjpp5Hhg 提取码: e65c </t>
-  </si>
-  <si>
-    <t>聪明镇</t>
   </si>
   <si>
     <t>台剧/恐怖/惊悚</t>
@@ -1313,7 +1452,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="35">
+  <fonts count="36">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1533,6 +1672,12 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="Helvetica"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9.75"/>
+      <color rgb="FF3377AA"/>
       <name val="Helvetica"/>
       <charset val="134"/>
     </font>
@@ -2050,7 +2195,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2114,12 +2259,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2129,19 +2283,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -2679,14 +2845,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:O82"/>
+  <sheetPr/>
+  <dimension ref="A1:O83"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="17.625" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="1"/>
     <col min="3" max="3" width="30.5833333333333" style="1" customWidth="1"/>
-    <col min="4" max="7" width="9" style="1"/>
+    <col min="4" max="4" width="9" style="1"/>
+    <col min="5" max="5" width="9" style="21"/>
+    <col min="6" max="7" width="9" style="1"/>
     <col min="8" max="8" width="80.2916666666667" style="1" customWidth="1"/>
     <col min="9" max="9" width="74.25" style="1" customWidth="1"/>
     <col min="10" max="10" width="9" style="1"/>
@@ -2708,7 +2876,7 @@
       <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="22" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="5" t="s">
@@ -2735,31 +2903,31 @@
       <c r="O1" s="5"/>
     </row>
     <row r="2" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="8">
+      <c r="D2" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="25">
         <v>12</v>
       </c>
-      <c r="F2" s="22" t="s">
+      <c r="F2" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="22">
+      <c r="G2" s="24">
         <v>2026</v>
       </c>
-      <c r="H2" s="22" t="s">
+      <c r="H2" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="22" t="s">
+      <c r="I2" s="24" t="s">
         <v>17</v>
       </c>
       <c r="J2" s="13"/>
@@ -2770,31 +2938,31 @@
       <c r="O2" s="13"/>
     </row>
     <row r="3" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="8">
+      <c r="D3" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="25">
         <v>13</v>
       </c>
-      <c r="F3" s="22" t="s">
+      <c r="F3" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="22">
+      <c r="G3" s="24">
         <v>2026</v>
       </c>
-      <c r="H3" s="22" t="s">
+      <c r="H3" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="22" t="s">
+      <c r="I3" s="24" t="s">
         <v>21</v>
       </c>
       <c r="J3" s="13"/>
@@ -2805,31 +2973,31 @@
       <c r="O3" s="13"/>
     </row>
     <row r="4" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="8">
+      <c r="D4" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="25">
         <v>26</v>
       </c>
-      <c r="F4" s="22" t="s">
+      <c r="F4" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="22">
+      <c r="G4" s="24">
         <v>2026</v>
       </c>
-      <c r="H4" s="22" t="s">
+      <c r="H4" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="I4" s="22" t="s">
+      <c r="I4" s="24" t="s">
         <v>25</v>
       </c>
       <c r="J4" s="13"/>
@@ -2842,31 +3010,31 @@
       <c r="O4" s="13"/>
     </row>
     <row r="5" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="C5" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="8">
+      <c r="D5" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="25">
         <v>26</v>
       </c>
-      <c r="F5" s="22" t="s">
+      <c r="F5" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="22">
+      <c r="G5" s="24">
         <v>2026</v>
       </c>
-      <c r="H5" s="22" t="s">
+      <c r="H5" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="I5" s="22" t="s">
+      <c r="I5" s="24" t="s">
         <v>30</v>
       </c>
       <c r="J5" s="13"/>
@@ -2876,32 +3044,32 @@
       <c r="N5" s="13"/>
       <c r="O5" s="13"/>
     </row>
-    <row r="6" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A6" s="21" t="s">
+    <row r="6" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A6" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="8">
+      <c r="D6" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="25">
         <v>24</v>
       </c>
-      <c r="F6" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="G6" s="22">
+      <c r="F6" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" s="24">
         <v>2026</v>
       </c>
-      <c r="H6" s="22" t="s">
+      <c r="H6" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="I6" s="22" t="s">
+      <c r="I6" s="24" t="s">
         <v>35</v>
       </c>
       <c r="J6" s="13"/>
@@ -2918,13 +3086,13 @@
       <c r="B7" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="24" t="s">
+      <c r="C7" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="25">
+      <c r="D7" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="28">
         <v>15</v>
       </c>
       <c r="F7" s="13" t="s">
@@ -2946,68 +3114,66 @@
       <c r="N7" s="5"/>
       <c r="O7" s="5"/>
     </row>
-    <row r="8" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A8" s="21" t="s">
+    <row r="8" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A8" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="22" t="s">
+      <c r="D8" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="11">
+        <v>8</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" s="5">
+        <v>2026</v>
+      </c>
+      <c r="H8" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="D8" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="22">
+      <c r="I8" s="11"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
+    </row>
+    <row r="9" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A9" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="31">
         <v>3</v>
       </c>
-      <c r="F8" s="22" t="s">
+      <c r="F9" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="G8" s="22">
+      <c r="G9" s="24">
         <v>2026</v>
       </c>
-      <c r="H8" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="I8" s="22" t="s">
-        <v>44</v>
-      </c>
-      <c r="J8" s="13"/>
-      <c r="K8" s="13"/>
-      <c r="L8" s="13"/>
-      <c r="M8" s="13"/>
-      <c r="N8" s="13"/>
-      <c r="O8" s="13"/>
-    </row>
-    <row r="9" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A9" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="B9" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="C9" s="22" t="s">
+      <c r="H9" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="D9" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" s="22">
-        <v>4</v>
-      </c>
-      <c r="F9" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="G9" s="22">
-        <v>2026</v>
-      </c>
-      <c r="H9" s="22" t="s">
+      <c r="I9" s="24" t="s">
         <v>47</v>
-      </c>
-      <c r="I9" s="22" t="s">
-        <v>48</v>
       </c>
       <c r="J9" s="13"/>
       <c r="K9" s="13"/>
@@ -3017,32 +3183,32 @@
       <c r="O9" s="13"/>
     </row>
     <row r="10" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="B10" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="D10" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="31">
+        <v>4</v>
+      </c>
+      <c r="F10" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" s="24">
+        <v>2026</v>
+      </c>
+      <c r="H10" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="C10" s="26" t="s">
+      <c r="I10" s="24" t="s">
         <v>51</v>
-      </c>
-      <c r="D10" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="27">
-        <v>2</v>
-      </c>
-      <c r="F10" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="G10" s="22">
-        <v>2026</v>
-      </c>
-      <c r="H10" s="22" t="s">
-        <v>52</v>
-      </c>
-      <c r="I10" s="13" t="s">
-        <v>53</v>
       </c>
       <c r="J10" s="13"/>
       <c r="K10" s="13"/>
@@ -3052,321 +3218,323 @@
       <c r="O10" s="13"/>
     </row>
     <row r="11" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="B11" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="C11" s="22" t="s">
+      <c r="D11" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="25">
+        <v>2</v>
+      </c>
+      <c r="F11" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" s="24">
+        <v>2026</v>
+      </c>
+      <c r="H11" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="D11" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="8">
-        <v>7</v>
-      </c>
-      <c r="F11" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="G11" s="22">
-        <v>2026</v>
-      </c>
-      <c r="H11" s="22" t="s">
+      <c r="I11" s="13" t="s">
         <v>56</v>
-      </c>
-      <c r="I11" s="22" t="s">
-        <v>57</v>
       </c>
       <c r="J11" s="13"/>
       <c r="K11" s="13"/>
-      <c r="L11" s="13" t="s">
-        <v>50</v>
-      </c>
+      <c r="L11" s="13"/>
       <c r="M11" s="13"/>
       <c r="N11" s="13"/>
       <c r="O11" s="13"/>
     </row>
     <row r="12" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A12" s="21" t="s">
+      <c r="A12" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="B12" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="B12" s="22" t="s">
+      <c r="D12" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="25">
+        <v>7</v>
+      </c>
+      <c r="F12" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="24">
+        <v>2026</v>
+      </c>
+      <c r="H12" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="C12" s="22" t="s">
+      <c r="I12" s="24" t="s">
         <v>60</v>
-      </c>
-      <c r="D12" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="E12" s="22">
-        <v>7</v>
-      </c>
-      <c r="F12" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="G12" s="22">
-        <v>2026</v>
-      </c>
-      <c r="H12" s="22" t="s">
-        <v>61</v>
-      </c>
-      <c r="I12" s="22" t="s">
-        <v>62</v>
       </c>
       <c r="J12" s="13"/>
       <c r="K12" s="13"/>
       <c r="L12" s="13" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="M12" s="13"/>
       <c r="N12" s="13"/>
       <c r="O12" s="13"/>
     </row>
     <row r="13" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A13" s="21" t="s">
+      <c r="A13" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="C13" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="B13" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="C13" s="22" t="s">
-        <v>55</v>
-      </c>
-      <c r="D13" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="E13" s="27">
-        <v>6</v>
-      </c>
-      <c r="F13" s="22" t="s">
+      <c r="D13" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="31">
+        <v>7</v>
+      </c>
+      <c r="F13" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="G13" s="22">
+      <c r="G13" s="24">
         <v>2026</v>
       </c>
-      <c r="H13" s="22" t="s">
+      <c r="H13" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="I13" s="22" t="s">
+      <c r="I13" s="24" t="s">
         <v>65</v>
       </c>
       <c r="J13" s="13"/>
       <c r="K13" s="13"/>
       <c r="L13" s="13" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="M13" s="13"/>
       <c r="N13" s="13"/>
       <c r="O13" s="13"/>
     </row>
     <row r="14" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A14" s="21" t="s">
+      <c r="A14" s="23" t="s">
         <v>66</v>
       </c>
-      <c r="B14" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="C14" s="22" t="s">
+      <c r="B14" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="D14" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" s="25">
+        <v>6</v>
+      </c>
+      <c r="F14" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14" s="24">
+        <v>2026</v>
+      </c>
+      <c r="H14" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="D14" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" s="27">
-        <v>8</v>
-      </c>
-      <c r="F14" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="G14" s="22">
-        <v>2026</v>
-      </c>
-      <c r="H14" s="22" t="s">
+      <c r="I14" s="24" t="s">
         <v>68</v>
-      </c>
-      <c r="I14" s="22" t="s">
-        <v>69</v>
       </c>
       <c r="J14" s="13"/>
       <c r="K14" s="13"/>
       <c r="L14" s="13" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="M14" s="13"/>
       <c r="N14" s="13"/>
       <c r="O14" s="13"/>
     </row>
     <row r="15" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A15" s="21" t="s">
+      <c r="A15" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="B15" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="B15" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="C15" s="22" t="s">
+      <c r="D15" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" s="25">
+        <v>8</v>
+      </c>
+      <c r="F15" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" s="24">
+        <v>2026</v>
+      </c>
+      <c r="H15" s="24" t="s">
         <v>71</v>
       </c>
-      <c r="D15" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="E15" s="27">
-        <v>10</v>
-      </c>
-      <c r="F15" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="G15" s="22">
-        <v>2026</v>
-      </c>
-      <c r="H15" s="22" t="s">
+      <c r="I15" s="24" t="s">
         <v>72</v>
-      </c>
-      <c r="I15" s="22" t="s">
-        <v>73</v>
       </c>
       <c r="J15" s="13"/>
       <c r="K15" s="13"/>
       <c r="L15" s="13" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="M15" s="13"/>
       <c r="N15" s="13"/>
       <c r="O15" s="13"/>
     </row>
     <row r="16" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A16" s="21" t="s">
+      <c r="A16" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="B16" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="C16" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="B16" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="C16" s="22" t="s">
+      <c r="D16" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" s="25">
+        <v>10</v>
+      </c>
+      <c r="F16" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16" s="24">
+        <v>2026</v>
+      </c>
+      <c r="H16" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="D16" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="E16" s="22">
-        <v>4</v>
-      </c>
-      <c r="F16" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="G16" s="22">
-        <v>2026</v>
-      </c>
-      <c r="H16" s="22" t="s">
+      <c r="I16" s="24" t="s">
         <v>76</v>
-      </c>
-      <c r="I16" s="22" t="s">
-        <v>77</v>
       </c>
       <c r="J16" s="13"/>
       <c r="K16" s="13"/>
       <c r="L16" s="13" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="M16" s="13"/>
       <c r="N16" s="13"/>
       <c r="O16" s="13"/>
     </row>
     <row r="17" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A17" s="21" t="s">
+      <c r="A17" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="B17" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="C17" s="24" t="s">
+        <v>78</v>
+      </c>
+      <c r="D17" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E17" s="31">
+        <v>4</v>
+      </c>
+      <c r="F17" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="G17" s="24">
+        <v>2026</v>
+      </c>
+      <c r="H17" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="B17" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="C17" s="22" t="s">
+      <c r="I17" s="24" t="s">
         <v>80</v>
-      </c>
-      <c r="D17" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="E17" s="22">
-        <v>8</v>
-      </c>
-      <c r="F17" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="G17" s="22">
-        <v>2026</v>
-      </c>
-      <c r="H17" s="22" t="s">
-        <v>81</v>
-      </c>
-      <c r="I17" s="22" t="s">
-        <v>82</v>
       </c>
       <c r="J17" s="13"/>
       <c r="K17" s="13"/>
       <c r="L17" s="13" t="s">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="M17" s="13"/>
       <c r="N17" s="13"/>
       <c r="O17" s="13"/>
     </row>
     <row r="18" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A18" s="21" t="s">
+      <c r="A18" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="B18" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="B18" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="C18" s="22" t="s">
+      <c r="D18" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="31">
+        <v>8</v>
+      </c>
+      <c r="F18" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="G18" s="24">
+        <v>2026</v>
+      </c>
+      <c r="H18" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="D18" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="E18" s="22">
-        <v>7</v>
-      </c>
-      <c r="F18" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="G18" s="22">
-        <v>2026</v>
-      </c>
-      <c r="H18" s="22"/>
-      <c r="I18" s="22" t="s">
+      <c r="I18" s="24" t="s">
         <v>85</v>
       </c>
       <c r="J18" s="13"/>
       <c r="K18" s="13"/>
-      <c r="L18" s="13"/>
+      <c r="L18" s="13" t="s">
+        <v>53</v>
+      </c>
       <c r="M18" s="13"/>
       <c r="N18" s="13"/>
       <c r="O18" s="13"/>
     </row>
     <row r="19" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A19" s="21" t="s">
+      <c r="A19" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="B19" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="C19" s="22" t="s">
+      <c r="B19" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19" s="24" t="s">
         <v>87</v>
       </c>
-      <c r="D19" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="E19" s="22">
-        <v>5</v>
-      </c>
-      <c r="F19" s="22" t="s">
+      <c r="D19" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19" s="31">
+        <v>7</v>
+      </c>
+      <c r="F19" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="G19" s="22">
+      <c r="G19" s="24">
         <v>2026</v>
       </c>
-      <c r="H19" s="22"/>
-      <c r="I19" s="22" t="s">
+      <c r="H19" s="24"/>
+      <c r="I19" s="24" t="s">
         <v>88</v>
       </c>
       <c r="J19" s="13"/>
@@ -3376,28 +3544,30 @@
       <c r="N19" s="13"/>
       <c r="O19" s="13"/>
     </row>
-    <row r="20" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A20" s="28" t="s">
+    <row r="20" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A20" s="23" t="s">
         <v>89</v>
       </c>
-      <c r="B20" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="C20" s="23" t="s">
+      <c r="B20" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="C20" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="D20" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="E20" s="23"/>
-      <c r="F20" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="G20" s="22">
+      <c r="D20" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E20" s="31">
+        <v>5</v>
+      </c>
+      <c r="F20" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="G20" s="24">
         <v>2026</v>
       </c>
-      <c r="H20" s="22"/>
-      <c r="I20" s="13" t="s">
+      <c r="H20" s="24"/>
+      <c r="I20" s="24" t="s">
         <v>91</v>
       </c>
       <c r="J20" s="13"/>
@@ -3405,165 +3575,159 @@
       <c r="L20" s="13"/>
       <c r="M20" s="13"/>
       <c r="N20" s="13"/>
-      <c r="O20" s="29"/>
-    </row>
-    <row r="21" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A21" s="28" t="s">
+      <c r="O20" s="13"/>
+    </row>
+    <row r="21" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A21" s="33" t="s">
         <v>92</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="C21" s="23" t="s">
-        <v>90</v>
-      </c>
-      <c r="D21" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="E21" s="23"/>
-      <c r="F21" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="G21" s="22">
+        <v>44</v>
+      </c>
+      <c r="C21" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="D21" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E21" s="34"/>
+      <c r="F21" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="G21" s="24">
         <v>2026</v>
       </c>
-      <c r="H21" s="22"/>
+      <c r="H21" s="24"/>
       <c r="I21" s="13" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J21" s="13"/>
       <c r="K21" s="13"/>
       <c r="L21" s="13"/>
       <c r="M21" s="13"/>
       <c r="N21" s="13"/>
-      <c r="O21" s="29"/>
-    </row>
-    <row r="22" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A22" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C22" s="5" t="s">
+      <c r="O21" s="35"/>
+    </row>
+    <row r="22" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A22" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="D22" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E22" s="5" t="s">
+      <c r="B22" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="C22" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="D22" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E22" s="34"/>
+      <c r="F22" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="G22" s="24">
+        <v>2026</v>
+      </c>
+      <c r="H22" s="24"/>
+      <c r="I22" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="F22" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G22" s="5">
-        <v>2026</v>
-      </c>
-      <c r="H22" s="5" t="s">
+      <c r="J22" s="13"/>
+      <c r="K22" s="13"/>
+      <c r="L22" s="13"/>
+      <c r="M22" s="13"/>
+      <c r="N22" s="13"/>
+      <c r="O22" s="35"/>
+    </row>
+    <row r="23" ht="25" customHeight="1" spans="1:15">
+      <c r="A23" s="12" t="s">
         <v>97</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="J22" s="5"/>
-      <c r="K22" s="5"/>
-      <c r="L22" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="M22" s="5"/>
-      <c r="N22" s="5"/>
-      <c r="O22" s="5"/>
-    </row>
-    <row r="23" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A23" s="12" t="s">
-        <v>100</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C23" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E23" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G23" s="5">
+        <v>2026</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="I23" s="1" t="s">
         <v>101</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G23" s="5">
-        <v>2025</v>
-      </c>
-      <c r="H23" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>104</v>
       </c>
       <c r="J23" s="5"/>
       <c r="K23" s="5"/>
       <c r="L23" s="5" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="M23" s="5"/>
       <c r="N23" s="5"/>
       <c r="O23" s="5"/>
     </row>
-    <row r="24" ht="25" hidden="1" customHeight="1" spans="1:15">
+    <row r="24" ht="25" customHeight="1" spans="1:15">
       <c r="A24" s="12" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C24" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E24" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G24" s="5">
+        <v>2025</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="I24" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G24" s="5">
-        <v>2026</v>
-      </c>
-      <c r="H24" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>110</v>
       </c>
       <c r="J24" s="5"/>
       <c r="K24" s="5"/>
       <c r="L24" s="5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="M24" s="5"/>
       <c r="N24" s="5"/>
       <c r="O24" s="5"/>
     </row>
-    <row r="25" ht="25" hidden="1" customHeight="1" spans="1:15">
+    <row r="25" ht="25" customHeight="1" spans="1:15">
       <c r="A25" s="12" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E25" s="5" t="s">
-        <v>114</v>
+      <c r="E25" s="22" t="s">
+        <v>111</v>
       </c>
       <c r="F25" s="5" t="s">
         <v>33</v>
@@ -3572,109 +3736,109 @@
         <v>2026</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="J25" s="5"/>
       <c r="K25" s="5"/>
       <c r="L25" s="5" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="M25" s="5"/>
       <c r="N25" s="5"/>
       <c r="O25" s="5"/>
     </row>
-    <row r="26" ht="25" hidden="1" customHeight="1" spans="1:15">
+    <row r="26" ht="25" customHeight="1" spans="1:15">
       <c r="A26" s="12" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C26" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E26" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G26" s="5">
+        <v>2026</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="I26" s="1" t="s">
         <v>119</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G26" s="5">
-        <v>2025</v>
-      </c>
-      <c r="H26" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>122</v>
       </c>
       <c r="J26" s="5"/>
       <c r="K26" s="5"/>
       <c r="L26" s="5" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="M26" s="5"/>
       <c r="N26" s="5"/>
       <c r="O26" s="5"/>
     </row>
-    <row r="27" ht="25" hidden="1" customHeight="1" spans="1:15">
+    <row r="27" ht="25" customHeight="1" spans="1:15">
       <c r="A27" s="12" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C27" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E27" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G27" s="5">
+        <v>2025</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="I27" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="D27" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E27" s="5" t="s">
+      <c r="J27" s="5"/>
+      <c r="K27" s="5"/>
+      <c r="L27" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="F27" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G27" s="5">
-        <v>2026</v>
-      </c>
-      <c r="H27" s="5" t="s">
+      <c r="M27" s="5"/>
+      <c r="N27" s="5"/>
+      <c r="O27" s="5"/>
+    </row>
+    <row r="28" ht="25" customHeight="1" spans="1:15">
+      <c r="A28" s="12" t="s">
         <v>127</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="J27" s="15"/>
-      <c r="K27" s="15"/>
-      <c r="L27" s="15" t="s">
-        <v>129</v>
-      </c>
-      <c r="M27" s="15"/>
-      <c r="N27" s="15"/>
-      <c r="O27" s="5"/>
-    </row>
-    <row r="28" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A28" s="12" t="s">
-        <v>130</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E28" s="5" t="s">
-        <v>132</v>
+      <c r="E28" s="22" t="s">
+        <v>129</v>
       </c>
       <c r="F28" s="5" t="s">
         <v>33</v>
@@ -3683,72 +3847,72 @@
         <v>2026</v>
       </c>
       <c r="H28" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="J28" s="15"/>
+      <c r="K28" s="15"/>
+      <c r="L28" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="M28" s="15"/>
+      <c r="N28" s="15"/>
+      <c r="O28" s="5"/>
+    </row>
+    <row r="29" ht="25" customHeight="1" spans="1:15">
+      <c r="A29" s="12" t="s">
         <v>133</v>
-      </c>
-      <c r="I28" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="J28" s="5"/>
-      <c r="K28" s="5"/>
-      <c r="L28" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="M28" s="5"/>
-      <c r="N28" s="5"/>
-      <c r="O28" s="30"/>
-    </row>
-    <row r="29" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A29" s="12" t="s">
-        <v>136</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C29" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E29" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G29" s="5">
+        <v>2026</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="I29" s="5" t="s">
         <v>137</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="F29" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G29" s="5">
-        <v>2024</v>
-      </c>
-      <c r="H29" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="I29" s="5" t="s">
-        <v>140</v>
       </c>
       <c r="J29" s="5"/>
       <c r="K29" s="5"/>
       <c r="L29" s="5" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="M29" s="5"/>
       <c r="N29" s="5"/>
-      <c r="O29" s="30"/>
-    </row>
-    <row r="30" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O29" s="36"/>
+    </row>
+    <row r="30" ht="25" customHeight="1" spans="1:15">
       <c r="A30" s="12" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E30" s="5" t="s">
-        <v>144</v>
+      <c r="E30" s="22" t="s">
+        <v>141</v>
       </c>
       <c r="F30" s="5" t="s">
         <v>33</v>
@@ -3757,146 +3921,146 @@
         <v>2024</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="J30" s="5"/>
       <c r="K30" s="5"/>
       <c r="L30" s="5" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="M30" s="5"/>
       <c r="N30" s="5"/>
-      <c r="O30" s="30"/>
-    </row>
-    <row r="31" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O30" s="36"/>
+    </row>
+    <row r="31" ht="25" customHeight="1" spans="1:15">
       <c r="A31" s="12" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>113</v>
+        <v>146</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E31" s="5" t="s">
-        <v>114</v>
+      <c r="E31" s="22" t="s">
+        <v>147</v>
       </c>
       <c r="F31" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G31" s="5">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="H31" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="I31" s="5" t="s">
         <v>149</v>
-      </c>
-      <c r="I31" s="5" t="s">
-        <v>150</v>
       </c>
       <c r="J31" s="5"/>
       <c r="K31" s="5"/>
       <c r="L31" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="M31" s="5"/>
       <c r="N31" s="5"/>
-      <c r="O31" s="30"/>
-    </row>
-    <row r="32" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O31" s="36"/>
+    </row>
+    <row r="32" ht="25" customHeight="1" spans="1:15">
       <c r="A32" s="12" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C32" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E32" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G32" s="5">
+        <v>2026</v>
+      </c>
+      <c r="H32" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="I32" s="5" t="s">
         <v>153</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="F32" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G32" s="5">
-        <v>2025</v>
-      </c>
-      <c r="H32" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="I32" s="5" t="s">
-        <v>156</v>
       </c>
       <c r="J32" s="5"/>
       <c r="K32" s="5"/>
       <c r="L32" s="5" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="M32" s="5"/>
       <c r="N32" s="5"/>
-      <c r="O32" s="30"/>
-    </row>
-    <row r="33" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O32" s="36"/>
+    </row>
+    <row r="33" ht="25" customHeight="1" spans="1:15">
       <c r="A33" s="12" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C33" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E33" s="22" t="s">
+        <v>157</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G33" s="5">
+        <v>2025</v>
+      </c>
+      <c r="H33" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="I33" s="5" t="s">
         <v>159</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="F33" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G33" s="5">
-        <v>2026</v>
-      </c>
-      <c r="H33" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="I33" s="5" t="s">
-        <v>161</v>
       </c>
       <c r="J33" s="5"/>
       <c r="K33" s="5"/>
       <c r="L33" s="5" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="M33" s="5"/>
       <c r="N33" s="5"/>
-      <c r="O33" s="30"/>
-    </row>
-    <row r="34" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O33" s="36"/>
+    </row>
+    <row r="34" ht="25" customHeight="1" spans="1:15">
       <c r="A34" s="12" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E34" s="5" t="s">
-        <v>132</v>
+      <c r="E34" s="22" t="s">
+        <v>135</v>
       </c>
       <c r="F34" s="5" t="s">
         <v>33</v>
@@ -3905,35 +4069,35 @@
         <v>2026</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="J34" s="5"/>
       <c r="K34" s="5"/>
       <c r="L34" s="5" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="M34" s="5"/>
       <c r="N34" s="5"/>
-      <c r="O34" s="30"/>
-    </row>
-    <row r="35" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O34" s="36"/>
+    </row>
+    <row r="35" ht="25" customHeight="1" spans="1:15">
       <c r="A35" s="12" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E35" s="5" t="s">
-        <v>96</v>
+      <c r="E35" s="22" t="s">
+        <v>135</v>
       </c>
       <c r="F35" s="5" t="s">
         <v>33</v>
@@ -3942,109 +4106,109 @@
         <v>2026</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="J35" s="5"/>
       <c r="K35" s="5"/>
       <c r="L35" s="5" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="M35" s="5"/>
       <c r="N35" s="5"/>
-      <c r="O35" s="30"/>
-    </row>
-    <row r="36" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O35" s="36"/>
+    </row>
+    <row r="36" ht="25" customHeight="1" spans="1:15">
       <c r="A36" s="12" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>119</v>
+        <v>172</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E36" s="5" t="s">
+      <c r="E36" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G36" s="5">
+        <v>2026</v>
+      </c>
+      <c r="H36" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="I36" s="5" t="s">
         <v>174</v>
-      </c>
-      <c r="F36" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G36" s="5">
-        <v>2025</v>
-      </c>
-      <c r="H36" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="I36" s="5" t="s">
-        <v>176</v>
       </c>
       <c r="J36" s="5"/>
       <c r="K36" s="5"/>
       <c r="L36" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="M36" s="5"/>
       <c r="N36" s="5"/>
-      <c r="O36" s="30"/>
-    </row>
-    <row r="37" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O36" s="36"/>
+    </row>
+    <row r="37" ht="25" customHeight="1" spans="1:15">
       <c r="A37" s="12" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C37" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E37" s="22" t="s">
+        <v>177</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G37" s="5">
+        <v>2025</v>
+      </c>
+      <c r="H37" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="I37" s="5" t="s">
         <v>179</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E37" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="F37" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G37" s="5">
-        <v>2026</v>
-      </c>
-      <c r="H37" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="I37" s="5" t="s">
-        <v>182</v>
       </c>
       <c r="J37" s="5"/>
       <c r="K37" s="5"/>
       <c r="L37" s="5" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="M37" s="5"/>
       <c r="N37" s="5"/>
-      <c r="O37" s="30"/>
-    </row>
-    <row r="38" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O37" s="36"/>
+    </row>
+    <row r="38" ht="25" customHeight="1" spans="1:15">
       <c r="A38" s="12" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E38" s="5" t="s">
-        <v>102</v>
+      <c r="E38" s="22" t="s">
+        <v>183</v>
       </c>
       <c r="F38" s="5" t="s">
         <v>33</v>
@@ -4053,70 +4217,72 @@
         <v>2026</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="I38" s="5" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="J38" s="5"/>
       <c r="K38" s="5"/>
       <c r="L38" s="5" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="M38" s="5"/>
       <c r="N38" s="5"/>
-      <c r="O38" s="30"/>
-    </row>
-    <row r="39" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O38" s="36"/>
+    </row>
+    <row r="39" ht="25" customHeight="1" spans="1:15">
       <c r="A39" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E39" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G39" s="5">
+        <v>2026</v>
+      </c>
+      <c r="H39" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="I39" s="5" t="s">
         <v>190</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E39" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="F39" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G39" s="5">
-        <v>2025</v>
-      </c>
-      <c r="H39" s="5"/>
-      <c r="I39" s="5" t="s">
-        <v>193</v>
       </c>
       <c r="J39" s="5"/>
       <c r="K39" s="5"/>
       <c r="L39" s="5" t="s">
-        <v>50</v>
+        <v>191</v>
       </c>
       <c r="M39" s="5"/>
       <c r="N39" s="5"/>
-      <c r="O39" s="30"/>
-    </row>
-    <row r="40" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O39" s="36"/>
+    </row>
+    <row r="40" ht="25" customHeight="1" spans="1:15">
       <c r="A40" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="B40" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E40" s="22" t="s">
         <v>194</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E40" s="13" t="s">
-        <v>196</v>
       </c>
       <c r="F40" s="5" t="s">
         <v>33</v>
@@ -4124,36 +4290,34 @@
       <c r="G40" s="5">
         <v>2025</v>
       </c>
-      <c r="H40" s="5" t="s">
-        <v>197</v>
-      </c>
+      <c r="H40" s="5"/>
       <c r="I40" s="5" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="J40" s="5"/>
       <c r="K40" s="5"/>
       <c r="L40" s="5" t="s">
-        <v>199</v>
+        <v>53</v>
       </c>
       <c r="M40" s="5"/>
       <c r="N40" s="5"/>
-      <c r="O40" s="30"/>
-    </row>
-    <row r="41" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O40" s="36"/>
+    </row>
+    <row r="41" ht="25" customHeight="1" spans="1:15">
       <c r="A41" s="12" t="s">
-        <v>200</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>190</v>
+        <v>196</v>
+      </c>
+      <c r="B41" s="24" t="s">
+        <v>53</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E41" s="13" t="s">
-        <v>192</v>
+      <c r="E41" s="22" t="s">
+        <v>198</v>
       </c>
       <c r="F41" s="5" t="s">
         <v>33</v>
@@ -4161,700 +4325,720 @@
       <c r="G41" s="5">
         <v>2025</v>
       </c>
-      <c r="H41" s="5"/>
+      <c r="H41" s="5" t="s">
+        <v>199</v>
+      </c>
       <c r="I41" s="5" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="J41" s="5"/>
       <c r="K41" s="5"/>
       <c r="L41" s="5" t="s">
-        <v>50</v>
+        <v>201</v>
       </c>
       <c r="M41" s="5"/>
       <c r="N41" s="5"/>
-      <c r="O41" s="30"/>
-    </row>
-    <row r="42" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O41" s="36"/>
+    </row>
+    <row r="42" ht="25" customHeight="1" spans="1:15">
       <c r="A42" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="B42" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="C42" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="B42" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="C42" s="5" t="s">
+      <c r="D42" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E42" s="22" t="s">
+        <v>194</v>
+      </c>
+      <c r="F42" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G42" s="5">
+        <v>2025</v>
+      </c>
+      <c r="H42" s="5"/>
+      <c r="I42" s="5" t="s">
         <v>204</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E42" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="F42" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G42" s="5">
-        <v>2026</v>
-      </c>
-      <c r="H42" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="I42" s="5" t="s">
-        <v>206</v>
       </c>
       <c r="J42" s="5"/>
       <c r="K42" s="5"/>
       <c r="L42" s="5" t="s">
-        <v>207</v>
+        <v>53</v>
       </c>
       <c r="M42" s="5"/>
       <c r="N42" s="5"/>
-      <c r="O42" s="30"/>
-    </row>
-    <row r="43" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O42" s="36"/>
+    </row>
+    <row r="43" ht="25" customHeight="1" spans="1:15">
       <c r="A43" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E43" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G43" s="5">
+        <v>2026</v>
+      </c>
+      <c r="H43" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="B43" s="5"/>
-      <c r="C43" s="5"/>
-      <c r="D43" s="5"/>
-      <c r="E43" s="5"/>
-      <c r="F43" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G43" s="5"/>
-      <c r="H43" s="5"/>
       <c r="I43" s="5" t="s">
         <v>209</v>
       </c>
       <c r="J43" s="5"/>
       <c r="K43" s="5"/>
-      <c r="L43" s="5"/>
+      <c r="L43" s="5" t="s">
+        <v>210</v>
+      </c>
       <c r="M43" s="5"/>
       <c r="N43" s="5"/>
-      <c r="O43" s="30"/>
-    </row>
-    <row r="44" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O43" s="36"/>
+    </row>
+    <row r="44" ht="25" customHeight="1" spans="1:15">
       <c r="A44" s="12" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
       <c r="D44" s="5"/>
-      <c r="E44" s="5"/>
+      <c r="E44" s="22"/>
       <c r="F44" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G44" s="5"/>
       <c r="H44" s="5"/>
       <c r="I44" s="5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="J44" s="5"/>
       <c r="K44" s="5"/>
       <c r="L44" s="5"/>
       <c r="M44" s="5"/>
       <c r="N44" s="5"/>
-      <c r="O44" s="30"/>
-    </row>
-    <row r="45" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O44" s="36"/>
+    </row>
+    <row r="45" ht="25" customHeight="1" spans="1:15">
       <c r="A45" s="12" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5"/>
       <c r="D45" s="5"/>
-      <c r="E45" s="5"/>
+      <c r="E45" s="22"/>
       <c r="F45" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G45" s="5"/>
       <c r="H45" s="5"/>
       <c r="I45" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J45" s="5"/>
       <c r="K45" s="5"/>
       <c r="L45" s="5"/>
       <c r="M45" s="5"/>
       <c r="N45" s="5"/>
-      <c r="O45" s="30"/>
-    </row>
-    <row r="46" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O45" s="36"/>
+    </row>
+    <row r="46" ht="25" customHeight="1" spans="1:15">
       <c r="A46" s="12" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5"/>
       <c r="D46" s="5"/>
-      <c r="E46" s="5"/>
+      <c r="E46" s="22"/>
       <c r="F46" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G46" s="5"/>
       <c r="H46" s="5"/>
       <c r="I46" s="5" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J46" s="5"/>
       <c r="K46" s="5"/>
       <c r="L46" s="5"/>
       <c r="M46" s="5"/>
       <c r="N46" s="5"/>
-      <c r="O46" s="30"/>
-    </row>
-    <row r="47" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A47" s="14" t="s">
-        <v>216</v>
-      </c>
-      <c r="B47" s="15"/>
-      <c r="C47" s="15"/>
-      <c r="D47" s="15"/>
-      <c r="E47" s="15"/>
+      <c r="O46" s="36"/>
+    </row>
+    <row r="47" ht="25" customHeight="1" spans="1:15">
+      <c r="A47" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="B47" s="5"/>
+      <c r="C47" s="5"/>
+      <c r="D47" s="5"/>
+      <c r="E47" s="22"/>
       <c r="F47" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G47" s="15"/>
-      <c r="H47" s="15"/>
-      <c r="I47" s="16" t="s">
-        <v>217</v>
-      </c>
-      <c r="J47" s="15"/>
+      <c r="G47" s="5"/>
+      <c r="H47" s="5"/>
+      <c r="I47" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="J47" s="5"/>
       <c r="K47" s="5"/>
       <c r="L47" s="5"/>
       <c r="M47" s="5"/>
       <c r="N47" s="5"/>
-      <c r="O47" s="30"/>
-    </row>
-    <row r="48" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A48" s="12" t="s">
-        <v>218</v>
-      </c>
-      <c r="B48" s="5"/>
-      <c r="C48" s="5"/>
-      <c r="D48" s="5"/>
-      <c r="E48" s="5"/>
+      <c r="O47" s="36"/>
+    </row>
+    <row r="48" ht="25" customHeight="1" spans="1:15">
+      <c r="A48" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="B48" s="15"/>
+      <c r="C48" s="15"/>
+      <c r="D48" s="15"/>
+      <c r="E48" s="37"/>
       <c r="F48" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G48" s="5"/>
-      <c r="H48" s="5"/>
-      <c r="I48" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="J48" s="5"/>
+      <c r="G48" s="15"/>
+      <c r="H48" s="15"/>
+      <c r="I48" s="16" t="s">
+        <v>220</v>
+      </c>
+      <c r="J48" s="15"/>
       <c r="K48" s="5"/>
       <c r="L48" s="5"/>
       <c r="M48" s="5"/>
       <c r="N48" s="5"/>
-      <c r="O48" s="30"/>
-    </row>
-    <row r="49" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O48" s="36"/>
+    </row>
+    <row r="49" ht="25" customHeight="1" spans="1:15">
       <c r="A49" s="12" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
       <c r="D49" s="5"/>
-      <c r="E49" s="5"/>
+      <c r="E49" s="22"/>
       <c r="F49" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G49" s="5"/>
       <c r="H49" s="5"/>
       <c r="I49" s="5" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="J49" s="5"/>
       <c r="K49" s="5"/>
       <c r="L49" s="5"/>
       <c r="M49" s="5"/>
       <c r="N49" s="5"/>
-      <c r="O49" s="30"/>
-    </row>
-    <row r="50" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O49" s="36"/>
+    </row>
+    <row r="50" ht="25" customHeight="1" spans="1:15">
       <c r="A50" s="12" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5"/>
       <c r="D50" s="5"/>
-      <c r="E50" s="5"/>
+      <c r="E50" s="22"/>
       <c r="F50" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G50" s="5"/>
       <c r="H50" s="5"/>
       <c r="I50" s="5" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J50" s="5"/>
       <c r="K50" s="5"/>
       <c r="L50" s="5"/>
       <c r="M50" s="5"/>
       <c r="N50" s="5"/>
-      <c r="O50" s="30"/>
-    </row>
-    <row r="51" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O50" s="36"/>
+    </row>
+    <row r="51" ht="25" customHeight="1" spans="1:15">
       <c r="A51" s="12" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
       <c r="D51" s="5"/>
-      <c r="E51" s="5"/>
+      <c r="E51" s="22"/>
       <c r="F51" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G51" s="5"/>
       <c r="H51" s="5"/>
       <c r="I51" s="5" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="J51" s="5"/>
       <c r="K51" s="5"/>
       <c r="L51" s="5"/>
       <c r="M51" s="5"/>
       <c r="N51" s="5"/>
-      <c r="O51" s="30"/>
-    </row>
-    <row r="52" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O51" s="36"/>
+    </row>
+    <row r="52" ht="25" customHeight="1" spans="1:15">
       <c r="A52" s="12" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5"/>
       <c r="D52" s="5"/>
-      <c r="E52" s="5"/>
+      <c r="E52" s="22"/>
       <c r="F52" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G52" s="5"/>
       <c r="H52" s="5"/>
       <c r="I52" s="5" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="J52" s="5"/>
       <c r="K52" s="5"/>
       <c r="L52" s="5"/>
       <c r="M52" s="5"/>
       <c r="N52" s="5"/>
-      <c r="O52" s="30"/>
-    </row>
-    <row r="53" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O52" s="36"/>
+    </row>
+    <row r="53" ht="25" customHeight="1" spans="1:15">
       <c r="A53" s="12" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5"/>
       <c r="D53" s="5"/>
-      <c r="E53" s="5"/>
+      <c r="E53" s="22"/>
       <c r="F53" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G53" s="5"/>
       <c r="H53" s="5"/>
       <c r="I53" s="5" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="J53" s="5"/>
       <c r="K53" s="5"/>
       <c r="L53" s="5"/>
       <c r="M53" s="5"/>
       <c r="N53" s="5"/>
-      <c r="O53" s="30"/>
-    </row>
-    <row r="54" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O53" s="36"/>
+    </row>
+    <row r="54" ht="25" customHeight="1" spans="1:15">
       <c r="A54" s="12" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
       <c r="D54" s="5"/>
-      <c r="E54" s="5"/>
+      <c r="E54" s="22"/>
       <c r="F54" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G54" s="5"/>
       <c r="H54" s="5"/>
       <c r="I54" s="5" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="J54" s="5"/>
       <c r="K54" s="5"/>
       <c r="L54" s="5"/>
       <c r="M54" s="5"/>
       <c r="N54" s="5"/>
-      <c r="O54" s="30"/>
-    </row>
-    <row r="55" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O54" s="36"/>
+    </row>
+    <row r="55" ht="25" customHeight="1" spans="1:15">
       <c r="A55" s="12" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B55" s="5"/>
       <c r="C55" s="5"/>
       <c r="D55" s="5"/>
-      <c r="E55" s="5"/>
+      <c r="E55" s="22"/>
       <c r="F55" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G55" s="5"/>
+      <c r="H55" s="5"/>
       <c r="I55" s="5" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="J55" s="5"/>
       <c r="K55" s="5"/>
       <c r="L55" s="5"/>
       <c r="M55" s="5"/>
       <c r="N55" s="5"/>
-      <c r="O55" s="30"/>
-    </row>
-    <row r="56" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O55" s="36"/>
+    </row>
+    <row r="56" ht="25" customHeight="1" spans="1:15">
       <c r="A56" s="12" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
       <c r="D56" s="5"/>
-      <c r="E56" s="5"/>
+      <c r="E56" s="22"/>
       <c r="F56" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G56" s="5"/>
-      <c r="H56" s="5"/>
       <c r="I56" s="5" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="J56" s="5"/>
       <c r="K56" s="5"/>
       <c r="L56" s="5"/>
       <c r="M56" s="5"/>
       <c r="N56" s="5"/>
-      <c r="O56" s="30"/>
-    </row>
-    <row r="57" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O56" s="36"/>
+    </row>
+    <row r="57" ht="25" customHeight="1" spans="1:15">
       <c r="A57" s="12" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
       <c r="D57" s="5"/>
-      <c r="E57" s="5"/>
+      <c r="E57" s="22"/>
       <c r="F57" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G57" s="5"/>
       <c r="H57" s="5"/>
       <c r="I57" s="5" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="J57" s="5"/>
       <c r="K57" s="5"/>
       <c r="L57" s="5"/>
       <c r="M57" s="5"/>
       <c r="N57" s="5"/>
-      <c r="O57" s="30"/>
-    </row>
-    <row r="58" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O57" s="36"/>
+    </row>
+    <row r="58" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A58" s="12" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
       <c r="D58" s="5"/>
-      <c r="E58" s="5"/>
+      <c r="E58" s="22"/>
       <c r="F58" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G58" s="5"/>
       <c r="H58" s="5"/>
       <c r="I58" s="5" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="J58" s="5"/>
       <c r="K58" s="5"/>
       <c r="L58" s="5"/>
       <c r="M58" s="5"/>
       <c r="N58" s="5"/>
-      <c r="O58" s="30"/>
-    </row>
-    <row r="59" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O58" s="36"/>
+    </row>
+    <row r="59" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A59" s="12" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
       <c r="D59" s="5"/>
-      <c r="E59" s="5"/>
+      <c r="E59" s="22"/>
       <c r="F59" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G59" s="5"/>
       <c r="H59" s="5"/>
       <c r="I59" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="J59" s="5"/>
       <c r="K59" s="5"/>
       <c r="L59" s="5"/>
       <c r="M59" s="5"/>
       <c r="N59" s="5"/>
-      <c r="O59" s="30"/>
-    </row>
-    <row r="60" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O59" s="36"/>
+    </row>
+    <row r="60" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A60" s="12" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
       <c r="D60" s="5"/>
-      <c r="E60" s="5"/>
+      <c r="E60" s="22"/>
       <c r="F60" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G60" s="5"/>
       <c r="H60" s="5"/>
       <c r="I60" s="5" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="J60" s="5"/>
       <c r="K60" s="5"/>
       <c r="L60" s="5"/>
       <c r="M60" s="5"/>
       <c r="N60" s="5"/>
-      <c r="O60" s="30"/>
-    </row>
-    <row r="61" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O60" s="36"/>
+    </row>
+    <row r="61" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A61" s="12" t="s">
-        <v>244</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C61" s="17" t="s">
         <v>245</v>
       </c>
+      <c r="B61" s="5"/>
+      <c r="C61" s="5"/>
       <c r="D61" s="5"/>
-      <c r="E61" s="5" t="s">
+      <c r="E61" s="22"/>
+      <c r="F61" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G61" s="5"/>
+      <c r="H61" s="5"/>
+      <c r="I61" s="5" t="s">
         <v>246</v>
-      </c>
-      <c r="F61" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G61" s="5"/>
-      <c r="H61" s="18" t="s">
-        <v>247</v>
-      </c>
-      <c r="I61" s="5" t="s">
-        <v>248</v>
       </c>
       <c r="J61" s="5"/>
       <c r="K61" s="5"/>
       <c r="L61" s="5"/>
       <c r="M61" s="5"/>
       <c r="N61" s="5"/>
-      <c r="O61" s="30"/>
-    </row>
-    <row r="62" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O61" s="36"/>
+    </row>
+    <row r="62" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A62" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C62" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="D62" s="5"/>
+      <c r="E62" s="22" t="s">
         <v>249</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="C62" s="17" t="s">
-        <v>250</v>
-      </c>
-      <c r="D62" s="5"/>
-      <c r="E62" s="5" t="s">
-        <v>108</v>
       </c>
       <c r="F62" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G62" s="5"/>
       <c r="H62" s="18" t="s">
+        <v>250</v>
+      </c>
+      <c r="I62" s="5" t="s">
         <v>251</v>
-      </c>
-      <c r="I62" s="5" t="s">
-        <v>252</v>
       </c>
       <c r="J62" s="5"/>
       <c r="K62" s="5"/>
       <c r="L62" s="5"/>
       <c r="M62" s="5"/>
       <c r="N62" s="5"/>
-      <c r="O62" s="5"/>
-    </row>
-    <row r="63" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O62" s="36"/>
+    </row>
+    <row r="63" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A63" s="12" t="s">
+        <v>252</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C63" s="17" t="s">
         <v>253</v>
       </c>
-      <c r="B63" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C63" s="19" t="s">
-        <v>254</v>
-      </c>
       <c r="D63" s="5"/>
-      <c r="E63" s="5" t="s">
-        <v>114</v>
+      <c r="E63" s="22" t="s">
+        <v>111</v>
       </c>
       <c r="F63" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G63" s="5"/>
       <c r="H63" s="18" t="s">
+        <v>254</v>
+      </c>
+      <c r="I63" s="5" t="s">
         <v>255</v>
-      </c>
-      <c r="I63" s="5" t="s">
-        <v>256</v>
       </c>
       <c r="J63" s="5"/>
       <c r="K63" s="5"/>
       <c r="L63" s="5"/>
       <c r="M63" s="5"/>
       <c r="N63" s="5"/>
-      <c r="O63" s="30"/>
-    </row>
-    <row r="64" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O63" s="5"/>
+    </row>
+    <row r="64" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A64" s="12" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C64" s="17" t="s">
-        <v>258</v>
+      <c r="C64" s="19" t="s">
+        <v>257</v>
       </c>
       <c r="D64" s="5"/>
-      <c r="E64" s="5" t="s">
-        <v>259</v>
+      <c r="E64" s="22" t="s">
+        <v>117</v>
       </c>
       <c r="F64" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G64" s="5"/>
       <c r="H64" s="18" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="I64" s="5" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="J64" s="5"/>
       <c r="K64" s="5"/>
       <c r="L64" s="5"/>
       <c r="M64" s="5"/>
       <c r="N64" s="5"/>
-      <c r="O64" s="30"/>
-    </row>
-    <row r="65" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O64" s="36"/>
+    </row>
+    <row r="65" ht="25" customHeight="1" spans="1:15">
       <c r="A65" s="12" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C65" s="17" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D65" s="5"/>
-      <c r="E65" s="5" t="s">
-        <v>259</v>
+      <c r="E65" s="22" t="s">
+        <v>262</v>
       </c>
       <c r="F65" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G65" s="5"/>
       <c r="H65" s="18" t="s">
+        <v>263</v>
+      </c>
+      <c r="I65" s="5" t="s">
         <v>264</v>
-      </c>
-      <c r="I65" s="5" t="s">
-        <v>265</v>
       </c>
       <c r="J65" s="5"/>
       <c r="K65" s="5"/>
       <c r="L65" s="5"/>
       <c r="M65" s="5"/>
       <c r="N65" s="5"/>
-      <c r="O65" s="30"/>
-    </row>
-    <row r="66" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O65" s="36"/>
+    </row>
+    <row r="66" ht="25" customHeight="1" spans="1:15">
       <c r="A66" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C66" s="17" t="s">
         <v>266</v>
       </c>
-      <c r="B66" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C66" s="17" t="s">
-        <v>267</v>
-      </c>
       <c r="D66" s="5"/>
-      <c r="E66" s="5" t="s">
-        <v>268</v>
+      <c r="E66" s="22" t="s">
+        <v>262</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G66" s="5"/>
       <c r="H66" s="18" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="I66" s="5" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="J66" s="5"/>
       <c r="K66" s="5"/>
       <c r="L66" s="5"/>
       <c r="M66" s="5"/>
       <c r="N66" s="5"/>
-      <c r="O66" s="30"/>
+      <c r="O66" s="36"/>
     </row>
     <row r="67" ht="25" customHeight="1" spans="1:15">
       <c r="A67" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C67" s="17" t="s">
+        <v>270</v>
+      </c>
+      <c r="D67" s="5"/>
+      <c r="E67" s="22" t="s">
         <v>271</v>
       </c>
-      <c r="B67" s="5" t="s">
+      <c r="F67" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G67" s="5"/>
+      <c r="H67" s="18" t="s">
         <v>272</v>
       </c>
-      <c r="C67" s="31" t="s">
+      <c r="I67" s="5" t="s">
         <v>273</v>
-      </c>
-      <c r="D67" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="E67" s="11">
-        <v>16</v>
-      </c>
-      <c r="F67" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="G67" s="22">
-        <v>2026</v>
-      </c>
-      <c r="H67" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="I67" s="5" t="s">
-        <v>275</v>
       </c>
       <c r="J67" s="5"/>
       <c r="K67" s="5"/>
       <c r="L67" s="5"/>
       <c r="M67" s="5"/>
       <c r="N67" s="5"/>
-      <c r="O67" s="5"/>
+      <c r="O67" s="36"/>
     </row>
     <row r="68" ht="25" customHeight="1" spans="1:15">
-      <c r="A68" s="12"/>
-      <c r="B68" s="5"/>
-      <c r="C68" s="5"/>
-      <c r="D68" s="5"/>
-      <c r="E68" s="5"/>
-      <c r="F68" s="13"/>
-      <c r="G68" s="5"/>
-      <c r="H68" s="5"/>
-      <c r="I68" s="5"/>
+      <c r="A68" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="C68" s="38" t="s">
+        <v>276</v>
+      </c>
+      <c r="D68" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E68" s="28">
+        <v>16</v>
+      </c>
+      <c r="F68" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G68" s="24">
+        <v>2026</v>
+      </c>
+      <c r="H68" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="I68" s="5" t="s">
+        <v>278</v>
+      </c>
       <c r="J68" s="5"/>
       <c r="K68" s="5"/>
       <c r="L68" s="5"/>
@@ -4867,9 +5051,10 @@
       <c r="B69" s="5"/>
       <c r="C69" s="5"/>
       <c r="D69" s="5"/>
-      <c r="E69" s="5"/>
+      <c r="E69" s="22"/>
       <c r="F69" s="13"/>
       <c r="G69" s="5"/>
+      <c r="H69" s="5"/>
       <c r="I69" s="5"/>
       <c r="J69" s="5"/>
       <c r="K69" s="5"/>
@@ -4883,10 +5068,9 @@
       <c r="B70" s="5"/>
       <c r="C70" s="5"/>
       <c r="D70" s="5"/>
-      <c r="E70" s="5"/>
+      <c r="E70" s="22"/>
       <c r="F70" s="13"/>
       <c r="G70" s="5"/>
-      <c r="H70" s="5"/>
       <c r="I70" s="5"/>
       <c r="J70" s="5"/>
       <c r="K70" s="5"/>
@@ -4900,7 +5084,7 @@
       <c r="B71" s="5"/>
       <c r="C71" s="5"/>
       <c r="D71" s="5"/>
-      <c r="E71" s="5"/>
+      <c r="E71" s="22"/>
       <c r="F71" s="13"/>
       <c r="G71" s="5"/>
       <c r="H71" s="5"/>
@@ -4917,7 +5101,7 @@
       <c r="B72" s="5"/>
       <c r="C72" s="5"/>
       <c r="D72" s="5"/>
-      <c r="E72" s="5"/>
+      <c r="E72" s="22"/>
       <c r="F72" s="13"/>
       <c r="G72" s="5"/>
       <c r="H72" s="5"/>
@@ -4934,7 +5118,7 @@
       <c r="B73" s="5"/>
       <c r="C73" s="5"/>
       <c r="D73" s="5"/>
-      <c r="E73" s="5"/>
+      <c r="E73" s="22"/>
       <c r="F73" s="13"/>
       <c r="G73" s="5"/>
       <c r="H73" s="5"/>
@@ -4951,7 +5135,7 @@
       <c r="B74" s="5"/>
       <c r="C74" s="5"/>
       <c r="D74" s="5"/>
-      <c r="E74" s="5"/>
+      <c r="E74" s="22"/>
       <c r="F74" s="13"/>
       <c r="G74" s="5"/>
       <c r="H74" s="5"/>
@@ -4968,7 +5152,7 @@
       <c r="B75" s="5"/>
       <c r="C75" s="5"/>
       <c r="D75" s="5"/>
-      <c r="E75" s="5"/>
+      <c r="E75" s="22"/>
       <c r="F75" s="13"/>
       <c r="G75" s="5"/>
       <c r="H75" s="5"/>
@@ -4985,9 +5169,10 @@
       <c r="B76" s="5"/>
       <c r="C76" s="5"/>
       <c r="D76" s="5"/>
-      <c r="E76" s="5"/>
+      <c r="E76" s="22"/>
       <c r="F76" s="13"/>
       <c r="G76" s="5"/>
+      <c r="H76" s="5"/>
       <c r="I76" s="5"/>
       <c r="J76" s="5"/>
       <c r="K76" s="5"/>
@@ -5001,10 +5186,9 @@
       <c r="B77" s="5"/>
       <c r="C77" s="5"/>
       <c r="D77" s="5"/>
-      <c r="E77" s="5"/>
+      <c r="E77" s="22"/>
       <c r="F77" s="13"/>
       <c r="G77" s="5"/>
-      <c r="H77" s="5"/>
       <c r="I77" s="5"/>
       <c r="J77" s="5"/>
       <c r="K77" s="5"/>
@@ -5018,7 +5202,7 @@
       <c r="B78" s="5"/>
       <c r="C78" s="5"/>
       <c r="D78" s="5"/>
-      <c r="E78" s="5"/>
+      <c r="E78" s="22"/>
       <c r="F78" s="13"/>
       <c r="G78" s="5"/>
       <c r="H78" s="5"/>
@@ -5035,7 +5219,7 @@
       <c r="B79" s="5"/>
       <c r="C79" s="5"/>
       <c r="D79" s="5"/>
-      <c r="E79" s="5"/>
+      <c r="E79" s="22"/>
       <c r="F79" s="13"/>
       <c r="G79" s="5"/>
       <c r="H79" s="5"/>
@@ -5052,7 +5236,7 @@
       <c r="B80" s="5"/>
       <c r="C80" s="5"/>
       <c r="D80" s="5"/>
-      <c r="E80" s="5"/>
+      <c r="E80" s="22"/>
       <c r="F80" s="13"/>
       <c r="G80" s="5"/>
       <c r="H80" s="5"/>
@@ -5069,7 +5253,7 @@
       <c r="B81" s="5"/>
       <c r="C81" s="5"/>
       <c r="D81" s="5"/>
-      <c r="E81" s="5"/>
+      <c r="E81" s="22"/>
       <c r="F81" s="13"/>
       <c r="G81" s="5"/>
       <c r="H81" s="5"/>
@@ -5086,7 +5270,7 @@
       <c r="B82" s="5"/>
       <c r="C82" s="5"/>
       <c r="D82" s="5"/>
-      <c r="E82" s="5"/>
+      <c r="E82" s="22"/>
       <c r="F82" s="13"/>
       <c r="G82" s="5"/>
       <c r="H82" s="5"/>
@@ -5098,21 +5282,33 @@
       <c r="N82" s="5"/>
       <c r="O82" s="5"/>
     </row>
+    <row r="83" ht="25" customHeight="1" spans="1:15">
+      <c r="A83" s="12"/>
+      <c r="B83" s="5"/>
+      <c r="C83" s="5"/>
+      <c r="D83" s="5"/>
+      <c r="E83" s="22"/>
+      <c r="F83" s="13"/>
+      <c r="G83" s="5"/>
+      <c r="H83" s="5"/>
+      <c r="I83" s="5"/>
+      <c r="J83" s="5"/>
+      <c r="K83" s="5"/>
+      <c r="L83" s="5"/>
+      <c r="M83" s="5"/>
+      <c r="N83" s="5"/>
+      <c r="O83" s="5"/>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:O66" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="5">
-      <filters>
-        <filter val="更新中"/>
-      </filters>
-    </filterColumn>
-    <sortState ref="A1:O66">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:O68" etc:filterBottomFollowUsedRange="0">
+    <sortState ref="A1:O68">
       <sortCondition ref="F1"/>
     </sortState>
     <extLst/>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="H62" r:id="rId1" display="普洛伊湘普·素帕莎 / 芭莉雅皮·余 " tooltip="https://www.douban.com/personage/30264980/"/>
-    <hyperlink ref="H17" r:id="rId2" display="金贤叙/郑明哲" tooltip="https://www.douban.com/personage/37338980/"/>
+    <hyperlink ref="H63" r:id="rId1" display="普洛伊湘普·素帕莎 / 芭莉雅皮·余 " tooltip="https://www.douban.com/personage/30264980/"/>
+    <hyperlink ref="H18" r:id="rId2" display="金贤叙/郑明哲" tooltip="https://www.douban.com/personage/37338980/"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -5136,7 +5332,7 @@
   <sheetData>
     <row r="1" ht="33" customHeight="1" spans="1:9">
       <c r="A1" s="3" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -5183,7 +5379,7 @@
         <v>12</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>14</v>
@@ -5322,13 +5518,13 @@
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:9">
       <c r="A8" s="6" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>14</v>
@@ -5343,21 +5539,21 @@
         <v>2026</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:9">
       <c r="A9" s="6" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>14</v>
@@ -5372,21 +5568,21 @@
         <v>2026</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:9">
       <c r="A10" s="6" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>14</v>
@@ -5401,21 +5597,21 @@
         <v>2026</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:9">
       <c r="A11" s="6" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>14</v>
@@ -5430,21 +5626,21 @@
         <v>2026</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:9">
       <c r="A12" s="6" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>14</v>
@@ -5459,21 +5655,21 @@
         <v>2026</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:9">
       <c r="A13" s="6" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>14</v>
@@ -5488,21 +5684,21 @@
         <v>2026</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:9">
       <c r="A14" s="6" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>14</v>
@@ -5517,21 +5713,21 @@
         <v>2026</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:9">
       <c r="A15" s="6" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>14</v>
@@ -5546,21 +5742,21 @@
         <v>2026</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:9">
       <c r="A16" s="6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>14</v>
@@ -5575,21 +5771,21 @@
         <v>2026</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:9">
       <c r="A17" s="6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>14</v>
@@ -5605,18 +5801,18 @@
       </c>
       <c r="H17" s="7"/>
       <c r="I17" s="8" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:9">
       <c r="A18" s="6" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>14</v>
@@ -5632,18 +5828,18 @@
       </c>
       <c r="H18" s="7"/>
       <c r="I18" s="8" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" spans="1:9">
       <c r="A19" s="9" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>14</v>
@@ -5657,18 +5853,18 @@
       </c>
       <c r="H19" s="7"/>
       <c r="I19" s="11" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" spans="1:9">
       <c r="A20" s="9" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>14</v>
@@ -5682,24 +5878,24 @@
       </c>
       <c r="H20" s="7"/>
       <c r="I20" s="11" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1" spans="1:9">
       <c r="A21" s="12" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>33</v>
@@ -5708,27 +5904,27 @@
         <v>2026</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1" spans="1:9">
       <c r="A22" s="12" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>33</v>
@@ -5737,27 +5933,27 @@
         <v>2025</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1" spans="1:9">
       <c r="A23" s="12" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>33</v>
@@ -5766,27 +5962,27 @@
         <v>2026</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1" spans="1:9">
       <c r="A24" s="12" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>33</v>
@@ -5795,27 +5991,27 @@
         <v>2026</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1" spans="1:9">
       <c r="A25" s="12" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F25" s="5" t="s">
         <v>33</v>
@@ -5824,27 +6020,27 @@
         <v>2025</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1" spans="1:9">
       <c r="A26" s="12" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F26" s="5" t="s">
         <v>33</v>
@@ -5853,27 +6049,27 @@
         <v>2026</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1" spans="1:9">
       <c r="A27" s="12" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F27" s="5" t="s">
         <v>33</v>
@@ -5882,27 +6078,27 @@
         <v>2026</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1" spans="1:9">
       <c r="A28" s="12" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="F28" s="5" t="s">
         <v>33</v>
@@ -5911,27 +6107,27 @@
         <v>2024</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="29" ht="25" customHeight="1" spans="1:9">
       <c r="A29" s="12" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="F29" s="5" t="s">
         <v>33</v>
@@ -5940,27 +6136,27 @@
         <v>2024</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="30" ht="25" customHeight="1" spans="1:9">
       <c r="A30" s="12" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="F30" s="5" t="s">
         <v>33</v>
@@ -5969,27 +6165,27 @@
         <v>2026</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="31" ht="25" customHeight="1" spans="1:9">
       <c r="A31" s="12" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="F31" s="5" t="s">
         <v>33</v>
@@ -5998,27 +6194,27 @@
         <v>2025</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="32" ht="25" customHeight="1" spans="1:9">
       <c r="A32" s="12" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F32" s="5" t="s">
         <v>33</v>
@@ -6027,27 +6223,27 @@
         <v>2026</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="33" ht="25" customHeight="1" spans="1:9">
       <c r="A33" s="12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F33" s="5" t="s">
         <v>33</v>
@@ -6056,27 +6252,27 @@
         <v>2026</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="I33" s="5" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="34" ht="25" customHeight="1" spans="1:9">
       <c r="A34" s="12" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F34" s="5" t="s">
         <v>33</v>
@@ -6085,27 +6281,27 @@
         <v>2026</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="35" ht="25" customHeight="1" spans="1:9">
       <c r="A35" s="12" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="F35" s="5" t="s">
         <v>33</v>
@@ -6114,27 +6310,27 @@
         <v>2025</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="36" ht="25" customHeight="1" spans="1:9">
       <c r="A36" s="12" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="F36" s="5" t="s">
         <v>33</v>
@@ -6143,27 +6339,27 @@
         <v>2026</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="37" ht="25" customHeight="1" spans="1:9">
       <c r="A37" s="12" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F37" s="5" t="s">
         <v>33</v>
@@ -6172,27 +6368,27 @@
         <v>2026</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="I37" s="5" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="38" ht="25" customHeight="1" spans="1:9">
       <c r="A38" s="12" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F38" s="5" t="s">
         <v>33</v>
@@ -6202,24 +6398,24 @@
       </c>
       <c r="H38" s="5"/>
       <c r="I38" s="5" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="39" ht="25" customHeight="1" spans="1:9">
       <c r="A39" s="12" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F39" s="5" t="s">
         <v>33</v>
@@ -6228,27 +6424,27 @@
         <v>2025</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="I39" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="40" ht="25" customHeight="1" spans="1:9">
       <c r="A40" s="12" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D40" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F40" s="5" t="s">
         <v>33</v>
@@ -6258,24 +6454,24 @@
       </c>
       <c r="H40" s="5"/>
       <c r="I40" s="5" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="41" ht="25" customHeight="1" spans="1:9">
       <c r="A41" s="12" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F41" s="5" t="s">
         <v>33</v>
@@ -6284,15 +6480,15 @@
         <v>2026</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="I41" s="5" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
     </row>
     <row r="42" ht="25" customHeight="1" spans="1:9">
       <c r="A42" s="12" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5"/>
@@ -6304,12 +6500,12 @@
       <c r="G42" s="5"/>
       <c r="H42" s="5"/>
       <c r="I42" s="5" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="43" ht="25" customHeight="1" spans="1:9">
       <c r="A43" s="12" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5"/>
@@ -6321,12 +6517,12 @@
       <c r="G43" s="5"/>
       <c r="H43" s="5"/>
       <c r="I43" s="5" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="44" ht="25" customHeight="1" spans="1:9">
       <c r="A44" s="12" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
@@ -6338,12 +6534,12 @@
       <c r="G44" s="5"/>
       <c r="H44" s="5"/>
       <c r="I44" s="5" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="45" ht="25" customHeight="1" spans="1:9">
       <c r="A45" s="12" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5"/>
@@ -6355,12 +6551,12 @@
       <c r="G45" s="5"/>
       <c r="H45" s="5"/>
       <c r="I45" s="5" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
     <row r="46" ht="25" customHeight="1" spans="1:9">
       <c r="A46" s="14" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B46" s="15"/>
       <c r="C46" s="15"/>
@@ -6372,12 +6568,12 @@
       <c r="G46" s="15"/>
       <c r="H46" s="15"/>
       <c r="I46" s="16" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="47" ht="25" customHeight="1" spans="1:9">
       <c r="A47" s="12" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
@@ -6389,12 +6585,12 @@
       <c r="G47" s="5"/>
       <c r="H47" s="5"/>
       <c r="I47" s="5" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="48" ht="25" customHeight="1" spans="1:9">
       <c r="A48" s="12" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
@@ -6406,12 +6602,12 @@
       <c r="G48" s="5"/>
       <c r="H48" s="5"/>
       <c r="I48" s="5" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="49" ht="25" customHeight="1" spans="1:9">
       <c r="A49" s="12" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
@@ -6423,12 +6619,12 @@
       <c r="G49" s="5"/>
       <c r="H49" s="5"/>
       <c r="I49" s="5" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="50" ht="25" customHeight="1" spans="1:9">
       <c r="A50" s="12" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5"/>
@@ -6440,12 +6636,12 @@
       <c r="G50" s="5"/>
       <c r="H50" s="5"/>
       <c r="I50" s="5" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="51" ht="25" customHeight="1" spans="1:9">
       <c r="A51" s="12" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
@@ -6457,12 +6653,12 @@
       <c r="G51" s="5"/>
       <c r="H51" s="5"/>
       <c r="I51" s="5" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="52" ht="25" customHeight="1" spans="1:9">
       <c r="A52" s="12" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5"/>
@@ -6474,162 +6670,162 @@
       <c r="G52" s="5"/>
       <c r="H52" s="5"/>
       <c r="I52" s="5" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="53" customFormat="1" ht="25" customHeight="1" spans="1:9">
       <c r="A53" s="12" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C53" s="17" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="D53" s="5"/>
       <c r="E53" s="5" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="F53" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G53" s="5"/>
       <c r="H53" s="18" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="I53" s="5" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
     </row>
     <row r="54" customFormat="1" ht="25" customHeight="1" spans="1:9">
       <c r="A54" s="12" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="C54" s="17" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D54" s="5"/>
       <c r="E54" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F54" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G54" s="5"/>
       <c r="H54" s="18" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="I54" s="5" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row r="55" customFormat="1" ht="25" customHeight="1" spans="1:9">
       <c r="A55" s="12" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C55" s="19" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="D55" s="5"/>
       <c r="E55" s="5" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="F55" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G55" s="5"/>
       <c r="H55" s="18" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="I55" s="5" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
     </row>
     <row r="56" ht="25" customHeight="1" spans="1:9">
       <c r="A56" s="12" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C56" s="17" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="D56" s="5"/>
       <c r="E56" s="5" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="F56" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G56" s="5"/>
       <c r="H56" s="18" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="I56" s="5" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="57" ht="25" customHeight="1" spans="1:9">
       <c r="A57" s="12" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C57" s="17" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="D57" s="5"/>
       <c r="E57" s="5" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="F57" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G57" s="5"/>
       <c r="H57" s="18" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="I57" s="5" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="58" ht="25" customHeight="1" spans="1:9">
       <c r="A58" s="12" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C58" s="17" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="D58" s="5"/>
       <c r="E58" s="5" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="F58" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G58" s="5"/>
       <c r="H58" s="18" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="I58" s="5" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="59" ht="25" customHeight="1" spans="1:9">
       <c r="A59" s="12" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
@@ -6641,12 +6837,12 @@
       <c r="G59" s="5"/>
       <c r="H59" s="5"/>
       <c r="I59" s="5" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="60" ht="25" customHeight="1" spans="1:9">
       <c r="A60" s="12" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
@@ -6658,12 +6854,12 @@
       <c r="G60" s="5"/>
       <c r="H60" s="5"/>
       <c r="I60" s="5" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="61" ht="25" customHeight="1" spans="1:9">
       <c r="A61" s="12" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
@@ -6675,12 +6871,12 @@
       <c r="G61" s="5"/>
       <c r="H61" s="5"/>
       <c r="I61" s="5" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="62" customFormat="1" ht="25" customHeight="1" spans="1:9">
       <c r="A62" s="12" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B62" s="5"/>
       <c r="C62" s="5"/>
@@ -6692,12 +6888,12 @@
       <c r="G62" s="5"/>
       <c r="H62" s="5"/>
       <c r="I62" s="5" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="63" customFormat="1" ht="25" customHeight="1" spans="1:9">
       <c r="A63" s="12" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B63" s="5"/>
       <c r="C63" s="5"/>
@@ -6709,12 +6905,12 @@
       <c r="G63" s="5"/>
       <c r="H63" s="5"/>
       <c r="I63" s="5" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
     </row>
     <row r="64" customFormat="1" ht="25" customHeight="1" spans="1:9">
       <c r="A64" s="12" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B64" s="5"/>
       <c r="C64" s="5"/>
@@ -6726,12 +6922,12 @@
       <c r="G64" s="5"/>
       <c r="H64" s="5"/>
       <c r="I64" s="5" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="65" customFormat="1" ht="25" customHeight="1" spans="1:9">
       <c r="A65" s="12" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B65" s="5"/>
       <c r="C65" s="5"/>
@@ -6743,7 +6939,7 @@
       <c r="G65" s="5"/>
       <c r="H65" s="5"/>
       <c r="I65" s="5" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="66" ht="25" customHeight="1" spans="1:9">

--- a/资源录入表新.xlsx
+++ b/资源录入表新.xlsx
@@ -16,7 +16,7 @@
     <sheet name="资源录入表 (2)" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">资源录入表!$A$1:$O$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">资源录入表!$A$1:$O$69</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'资源录入表 (2)'!$A$2:$I$20</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="845" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="853" uniqueCount="291">
   <si>
     <t>剧名</t>
   </si>
@@ -211,66 +211,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="9.75"/>
-        <color rgb="FF111111"/>
-        <rFont val="Helvetica"/>
-        <charset val="134"/>
-      </rPr>
-      <t> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.75"/>
-        <color rgb="FF111111"/>
-        <rFont val="Helvetica"/>
-        <charset val="134"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.75"/>
-        <color rgb="FF111111"/>
-        <rFont val="Helvetica"/>
-        <charset val="134"/>
-      </rPr>
-      <t> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.75"/>
-        <color rgb="FF111111"/>
-        <rFont val="Helvetica"/>
-        <charset val="134"/>
-      </rPr>
-      <t>爱情</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.75"/>
-        <color rgb="FF111111"/>
-        <rFont val="Helvetica"/>
-        <charset val="134"/>
-      </rPr>
-      <t> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.75"/>
-        <color rgb="FF3377AA"/>
-        <rFont val="Helvetica"/>
-        <charset val="134"/>
-      </rPr>
-      <t>田曦薇</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.75"/>
+        <sz val="11"/>
         <color rgb="FF111111"/>
         <rFont val="Helvetica"/>
         <charset val="134"/>
@@ -279,17 +220,29 @@
     </r>
     <r>
       <rPr>
-        <sz val="9.75"/>
-        <color rgb="FF3377AA"/>
-        <rFont val="Helvetica"/>
+        <sz val="11"/>
+        <color rgb="FF111111"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>胡一天</t>
+      <t>爱情</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>: </t>
     </r>
     <r>
       <rPr>
-        <sz val="9.75"/>
-        <color rgb="FF111111"/>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>田曦薇</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
         <rFont val="Helvetica"/>
         <charset val="134"/>
       </rPr>
@@ -297,17 +250,15 @@
     </r>
     <r>
       <rPr>
-        <sz val="9.75"/>
-        <color rgb="FF3377AA"/>
-        <rFont val="Helvetica"/>
+        <sz val="11"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>赖伟明</t>
+      <t>胡一天</t>
     </r>
     <r>
       <rPr>
-        <sz val="9.75"/>
-        <color rgb="FF111111"/>
+        <sz val="11"/>
         <rFont val="Helvetica"/>
         <charset val="134"/>
       </rPr>
@@ -315,17 +266,15 @@
     </r>
     <r>
       <rPr>
-        <sz val="9.75"/>
-        <color rgb="FF3377AA"/>
-        <rFont val="Helvetica"/>
+        <sz val="11"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>安沺</t>
+      <t>赖伟明</t>
     </r>
     <r>
       <rPr>
-        <sz val="9.75"/>
-        <color rgb="FF111111"/>
+        <sz val="11"/>
         <rFont val="Helvetica"/>
         <charset val="134"/>
       </rPr>
@@ -333,13 +282,117 @@
     </r>
     <r>
       <rPr>
-        <sz val="9.75"/>
-        <color rgb="FF3377AA"/>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>安沺</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
         <rFont val="Helvetica"/>
         <charset val="134"/>
       </rPr>
+      <t> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>夏</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1amwrPfcBx1NrOHPksJq5gw 提取码: fu65 </t>
+  </si>
+  <si>
+    <t>夜语记</t>
+  </si>
+  <si>
+    <t>剧情 / 爱情</t>
+  </si>
+  <si>
+    <r>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>李汶翰</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>鹤男</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>李泊文</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>徐新驰</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>李牧芸</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/17U0bb5O2Zwtfhoa2zjCtYA 提取码: pyuj </t>
   </si>
   <si>
     <t>李熊猫</t>
@@ -1452,7 +1505,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="36">
+  <fonts count="35">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1676,12 +1729,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9.75"/>
-      <color rgb="FF3377AA"/>
-      <name val="Helvetica"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="12"/>
       <name val="Arial"/>
       <charset val="134"/>
@@ -1698,12 +1745,18 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -2071,7 +2124,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2095,16 +2148,16 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -2113,89 +2166,89 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2280,38 +2333,56 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2846,7 +2917,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O83"/>
+  <dimension ref="A1:O84"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="17.625" style="2" customWidth="1"/>
@@ -3089,10 +3160,10 @@
       <c r="C7" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="28">
+      <c r="D7" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="29">
         <v>15</v>
       </c>
       <c r="F7" s="13" t="s">
@@ -3115,31 +3186,33 @@
       <c r="O7" s="5"/>
     </row>
     <row r="8" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A8" s="29" t="s">
+      <c r="A8" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="27" t="s">
+      <c r="C8" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="D8" s="24" t="s">
+      <c r="D8" s="33" t="s">
         <v>14</v>
       </c>
       <c r="E8" s="11">
         <v>8</v>
       </c>
-      <c r="F8" s="13" t="s">
+      <c r="F8" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="G8" s="5">
+      <c r="G8" s="31">
         <v>2026</v>
       </c>
-      <c r="H8" s="30" t="s">
+      <c r="H8" s="35" t="s">
         <v>42</v>
       </c>
-      <c r="I8" s="11"/>
+      <c r="I8" s="31" t="s">
+        <v>43</v>
+      </c>
       <c r="J8" s="5"/>
       <c r="K8" s="5"/>
       <c r="L8" s="5"/>
@@ -3147,56 +3220,56 @@
       <c r="N8" s="5"/>
       <c r="O8" s="5"/>
     </row>
-    <row r="9" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A9" s="23" t="s">
-        <v>43</v>
-      </c>
-      <c r="B9" s="24" t="s">
+    <row r="9" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A9" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="C9" s="24" t="s">
+      <c r="B9" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="D9" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" s="31">
-        <v>3</v>
-      </c>
-      <c r="F9" s="24" t="s">
+      <c r="D9" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="11">
+        <v>8</v>
+      </c>
+      <c r="F9" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="G9" s="24">
+      <c r="G9" s="31">
         <v>2026</v>
       </c>
-      <c r="H9" s="24" t="s">
+      <c r="H9" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="I9" s="24" t="s">
+      <c r="I9" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13"/>
-      <c r="L9" s="13"/>
-      <c r="M9" s="13"/>
-      <c r="N9" s="13"/>
-      <c r="O9" s="13"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5"/>
+      <c r="M9" s="5"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
     </row>
     <row r="10" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A10" s="23" t="s">
         <v>48</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D10" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="31">
-        <v>4</v>
+      <c r="E10" s="36">
+        <v>3</v>
       </c>
       <c r="F10" s="24" t="s">
         <v>15</v>
@@ -3205,10 +3278,10 @@
         <v>2026</v>
       </c>
       <c r="H10" s="24" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I10" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J10" s="13"/>
       <c r="K10" s="13"/>
@@ -3219,19 +3292,19 @@
     </row>
     <row r="11" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A11" s="23" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="C11" s="32" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" s="24" t="s">
         <v>54</v>
       </c>
       <c r="D11" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E11" s="25">
-        <v>2</v>
+      <c r="E11" s="36">
+        <v>4</v>
       </c>
       <c r="F11" s="24" t="s">
         <v>15</v>
@@ -3242,7 +3315,7 @@
       <c r="H11" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="I11" s="13" t="s">
+      <c r="I11" s="24" t="s">
         <v>56</v>
       </c>
       <c r="J11" s="13"/>
@@ -3257,16 +3330,16 @@
         <v>57</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="C12" s="24" t="s">
         <v>58</v>
       </c>
+      <c r="C12" s="37" t="s">
+        <v>59</v>
+      </c>
       <c r="D12" s="24" t="s">
         <v>14</v>
       </c>
       <c r="E12" s="25">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F12" s="24" t="s">
         <v>15</v>
@@ -3275,26 +3348,24 @@
         <v>2026</v>
       </c>
       <c r="H12" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="I12" s="24" t="s">
         <v>60</v>
+      </c>
+      <c r="I12" s="13" t="s">
+        <v>61</v>
       </c>
       <c r="J12" s="13"/>
       <c r="K12" s="13"/>
-      <c r="L12" s="13" t="s">
-        <v>53</v>
-      </c>
+      <c r="L12" s="13"/>
       <c r="M12" s="13"/>
       <c r="N12" s="13"/>
       <c r="O12" s="13"/>
     </row>
     <row r="13" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A13" s="23" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C13" s="24" t="s">
         <v>63</v>
@@ -3302,7 +3373,7 @@
       <c r="D13" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E13" s="31">
+      <c r="E13" s="25">
         <v>7</v>
       </c>
       <c r="F13" s="24" t="s">
@@ -3320,7 +3391,7 @@
       <c r="J13" s="13"/>
       <c r="K13" s="13"/>
       <c r="L13" s="13" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="M13" s="13"/>
       <c r="N13" s="13"/>
@@ -3331,16 +3402,16 @@
         <v>66</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="D14" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E14" s="25">
-        <v>6</v>
+      <c r="E14" s="36">
+        <v>7</v>
       </c>
       <c r="F14" s="24" t="s">
         <v>15</v>
@@ -3349,15 +3420,15 @@
         <v>2026</v>
       </c>
       <c r="H14" s="24" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I14" s="24" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J14" s="13"/>
       <c r="K14" s="13"/>
       <c r="L14" s="13" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="M14" s="13"/>
       <c r="N14" s="13"/>
@@ -3365,19 +3436,19 @@
     </row>
     <row r="15" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A15" s="23" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C15" s="24" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D15" s="24" t="s">
         <v>14</v>
       </c>
       <c r="E15" s="25">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F15" s="24" t="s">
         <v>15</v>
@@ -3386,15 +3457,15 @@
         <v>2026</v>
       </c>
       <c r="H15" s="24" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I15" s="24" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J15" s="13"/>
       <c r="K15" s="13"/>
       <c r="L15" s="13" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="M15" s="13"/>
       <c r="N15" s="13"/>
@@ -3402,19 +3473,19 @@
     </row>
     <row r="16" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A16" s="23" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D16" s="24" t="s">
         <v>14</v>
       </c>
       <c r="E16" s="25">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F16" s="24" t="s">
         <v>15</v>
@@ -3423,15 +3494,15 @@
         <v>2026</v>
       </c>
       <c r="H16" s="24" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I16" s="24" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J16" s="13"/>
       <c r="K16" s="13"/>
       <c r="L16" s="13" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="M16" s="13"/>
       <c r="N16" s="13"/>
@@ -3439,19 +3510,19 @@
     </row>
     <row r="17" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A17" s="23" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B17" s="24" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C17" s="24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D17" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E17" s="31">
-        <v>4</v>
+      <c r="E17" s="25">
+        <v>10</v>
       </c>
       <c r="F17" s="24" t="s">
         <v>15</v>
@@ -3460,15 +3531,15 @@
         <v>2026</v>
       </c>
       <c r="H17" s="24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I17" s="24" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J17" s="13"/>
       <c r="K17" s="13"/>
       <c r="L17" s="13" t="s">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="M17" s="13"/>
       <c r="N17" s="13"/>
@@ -3479,7 +3550,7 @@
         <v>82</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C18" s="24" t="s">
         <v>83</v>
@@ -3487,8 +3558,8 @@
       <c r="D18" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E18" s="31">
-        <v>8</v>
+      <c r="E18" s="36">
+        <v>4</v>
       </c>
       <c r="F18" s="24" t="s">
         <v>15</v>
@@ -3505,7 +3576,7 @@
       <c r="J18" s="13"/>
       <c r="K18" s="13"/>
       <c r="L18" s="13" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="M18" s="13"/>
       <c r="N18" s="13"/>
@@ -3513,19 +3584,19 @@
     </row>
     <row r="19" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A19" s="23" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B19" s="24" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="C19" s="24" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D19" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E19" s="31">
-        <v>7</v>
+      <c r="E19" s="36">
+        <v>8</v>
       </c>
       <c r="F19" s="24" t="s">
         <v>15</v>
@@ -3533,32 +3604,36 @@
       <c r="G19" s="24">
         <v>2026</v>
       </c>
-      <c r="H19" s="24"/>
+      <c r="H19" s="24" t="s">
+        <v>89</v>
+      </c>
       <c r="I19" s="24" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="J19" s="13"/>
       <c r="K19" s="13"/>
-      <c r="L19" s="13"/>
+      <c r="L19" s="13" t="s">
+        <v>58</v>
+      </c>
       <c r="M19" s="13"/>
       <c r="N19" s="13"/>
       <c r="O19" s="13"/>
     </row>
     <row r="20" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A20" s="23" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B20" s="24" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C20" s="24" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D20" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E20" s="31">
-        <v>5</v>
+      <c r="E20" s="36">
+        <v>7</v>
       </c>
       <c r="F20" s="24" t="s">
         <v>15</v>
@@ -3568,7 +3643,7 @@
       </c>
       <c r="H20" s="24"/>
       <c r="I20" s="24" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J20" s="13"/>
       <c r="K20" s="13"/>
@@ -3578,50 +3653,52 @@
       <c r="O20" s="13"/>
     </row>
     <row r="21" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A21" s="33" t="s">
-        <v>92</v>
-      </c>
-      <c r="B21" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="C21" s="26" t="s">
-        <v>93</v>
+      <c r="A21" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="B21" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="C21" s="24" t="s">
+        <v>95</v>
       </c>
       <c r="D21" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E21" s="34"/>
-      <c r="F21" s="26" t="s">
-        <v>33</v>
+      <c r="E21" s="36">
+        <v>5</v>
+      </c>
+      <c r="F21" s="24" t="s">
+        <v>15</v>
       </c>
       <c r="G21" s="24">
         <v>2026</v>
       </c>
       <c r="H21" s="24"/>
-      <c r="I21" s="13" t="s">
-        <v>94</v>
+      <c r="I21" s="24" t="s">
+        <v>96</v>
       </c>
       <c r="J21" s="13"/>
       <c r="K21" s="13"/>
       <c r="L21" s="13"/>
       <c r="M21" s="13"/>
       <c r="N21" s="13"/>
-      <c r="O21" s="35"/>
+      <c r="O21" s="13"/>
     </row>
     <row r="22" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A22" s="33" t="s">
-        <v>95</v>
+      <c r="A22" s="38" t="s">
+        <v>97</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C22" s="26" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D22" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E22" s="34"/>
+      <c r="E22" s="39"/>
       <c r="F22" s="26" t="s">
         <v>33</v>
       </c>
@@ -3630,84 +3707,78 @@
       </c>
       <c r="H22" s="24"/>
       <c r="I22" s="13" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="J22" s="13"/>
       <c r="K22" s="13"/>
       <c r="L22" s="13"/>
       <c r="M22" s="13"/>
       <c r="N22" s="13"/>
-      <c r="O22" s="35"/>
-    </row>
-    <row r="23" ht="25" customHeight="1" spans="1:15">
-      <c r="A23" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C23" s="5" t="s">
+      <c r="O22" s="40"/>
+    </row>
+    <row r="23" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A23" s="38" t="s">
+        <v>100</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="C23" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="D23" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E23" s="22" t="s">
-        <v>99</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G23" s="5">
+      <c r="D23" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E23" s="39"/>
+      <c r="F23" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="G23" s="24">
         <v>2026</v>
       </c>
-      <c r="H23" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="I23" s="1" t="s">
+      <c r="H23" s="24"/>
+      <c r="I23" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="J23" s="5"/>
-      <c r="K23" s="5"/>
-      <c r="L23" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="M23" s="5"/>
-      <c r="N23" s="5"/>
-      <c r="O23" s="5"/>
+      <c r="J23" s="13"/>
+      <c r="K23" s="13"/>
+      <c r="L23" s="13"/>
+      <c r="M23" s="13"/>
+      <c r="N23" s="13"/>
+      <c r="O23" s="40"/>
     </row>
     <row r="24" ht="25" customHeight="1" spans="1:15">
       <c r="A24" s="12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C24" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E24" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="D24" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E24" s="22" t="s">
+      <c r="F24" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G24" s="5">
+        <v>2026</v>
+      </c>
+      <c r="H24" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="F24" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G24" s="5">
-        <v>2025</v>
-      </c>
-      <c r="H24" s="5" t="s">
+      <c r="I24" s="1" t="s">
         <v>106</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>107</v>
       </c>
       <c r="J24" s="5"/>
       <c r="K24" s="5"/>
       <c r="L24" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M24" s="5"/>
       <c r="N24" s="5"/>
@@ -3715,36 +3786,36 @@
     </row>
     <row r="25" ht="25" customHeight="1" spans="1:15">
       <c r="A25" s="12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C25" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E25" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="D25" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E25" s="22" t="s">
+      <c r="F25" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G25" s="5">
+        <v>2025</v>
+      </c>
+      <c r="H25" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="F25" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G25" s="5">
-        <v>2026</v>
-      </c>
-      <c r="H25" s="5" t="s">
+      <c r="I25" s="1" t="s">
         <v>112</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>113</v>
       </c>
       <c r="J25" s="5"/>
       <c r="K25" s="5"/>
       <c r="L25" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M25" s="5"/>
       <c r="N25" s="5"/>
@@ -3752,19 +3823,19 @@
     </row>
     <row r="26" ht="25" customHeight="1" spans="1:15">
       <c r="A26" s="12" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C26" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E26" s="22" t="s">
         <v>116</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E26" s="22" t="s">
-        <v>117</v>
       </c>
       <c r="F26" s="5" t="s">
         <v>33</v>
@@ -3773,15 +3844,15 @@
         <v>2026</v>
       </c>
       <c r="H26" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="I26" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>119</v>
       </c>
       <c r="J26" s="5"/>
       <c r="K26" s="5"/>
       <c r="L26" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M26" s="5"/>
       <c r="N26" s="5"/>
@@ -3789,36 +3860,36 @@
     </row>
     <row r="27" ht="25" customHeight="1" spans="1:15">
       <c r="A27" s="12" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C27" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E27" s="22" t="s">
         <v>122</v>
       </c>
-      <c r="D27" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E27" s="22" t="s">
+      <c r="F27" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G27" s="5">
+        <v>2026</v>
+      </c>
+      <c r="H27" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="F27" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G27" s="5">
-        <v>2025</v>
-      </c>
-      <c r="H27" s="5" t="s">
+      <c r="I27" s="1" t="s">
         <v>124</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>125</v>
       </c>
       <c r="J27" s="5"/>
       <c r="K27" s="5"/>
       <c r="L27" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M27" s="5"/>
       <c r="N27" s="5"/>
@@ -3826,56 +3897,56 @@
     </row>
     <row r="28" ht="25" customHeight="1" spans="1:15">
       <c r="A28" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C28" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E28" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="D28" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E28" s="22" t="s">
+      <c r="F28" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G28" s="5">
+        <v>2025</v>
+      </c>
+      <c r="H28" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="F28" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G28" s="5">
-        <v>2026</v>
-      </c>
-      <c r="H28" s="5" t="s">
+      <c r="I28" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="I28" s="1" t="s">
+      <c r="J28" s="5"/>
+      <c r="K28" s="5"/>
+      <c r="L28" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="J28" s="15"/>
-      <c r="K28" s="15"/>
-      <c r="L28" s="15" t="s">
-        <v>132</v>
-      </c>
-      <c r="M28" s="15"/>
-      <c r="N28" s="15"/>
+      <c r="M28" s="5"/>
+      <c r="N28" s="5"/>
       <c r="O28" s="5"/>
     </row>
     <row r="29" ht="25" customHeight="1" spans="1:15">
       <c r="A29" s="12" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C29" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E29" s="22" t="s">
         <v>134</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E29" s="22" t="s">
-        <v>135</v>
       </c>
       <c r="F29" s="5" t="s">
         <v>33</v>
@@ -3884,72 +3955,72 @@
         <v>2026</v>
       </c>
       <c r="H29" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="I29" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="I29" s="5" t="s">
+      <c r="J29" s="15"/>
+      <c r="K29" s="15"/>
+      <c r="L29" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="J29" s="5"/>
-      <c r="K29" s="5"/>
-      <c r="L29" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="M29" s="5"/>
-      <c r="N29" s="5"/>
-      <c r="O29" s="36"/>
+      <c r="M29" s="15"/>
+      <c r="N29" s="15"/>
+      <c r="O29" s="5"/>
     </row>
     <row r="30" ht="25" customHeight="1" spans="1:15">
       <c r="A30" s="12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C30" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E30" s="22" t="s">
         <v>140</v>
       </c>
-      <c r="D30" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E30" s="22" t="s">
+      <c r="F30" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G30" s="5">
+        <v>2026</v>
+      </c>
+      <c r="H30" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="F30" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G30" s="5">
-        <v>2024</v>
-      </c>
-      <c r="H30" s="5" t="s">
+      <c r="I30" s="5" t="s">
         <v>142</v>
-      </c>
-      <c r="I30" s="5" t="s">
-        <v>143</v>
       </c>
       <c r="J30" s="5"/>
       <c r="K30" s="5"/>
       <c r="L30" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="M30" s="5"/>
       <c r="N30" s="5"/>
-      <c r="O30" s="36"/>
+      <c r="O30" s="41"/>
     </row>
     <row r="31" ht="25" customHeight="1" spans="1:15">
       <c r="A31" s="12" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C31" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E31" s="22" t="s">
         <v>146</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E31" s="22" t="s">
-        <v>147</v>
       </c>
       <c r="F31" s="5" t="s">
         <v>33</v>
@@ -3958,115 +4029,115 @@
         <v>2024</v>
       </c>
       <c r="H31" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="I31" s="5" t="s">
         <v>148</v>
-      </c>
-      <c r="I31" s="5" t="s">
-        <v>149</v>
       </c>
       <c r="J31" s="5"/>
       <c r="K31" s="5"/>
       <c r="L31" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="M31" s="5"/>
       <c r="N31" s="5"/>
-      <c r="O31" s="36"/>
+      <c r="O31" s="41"/>
     </row>
     <row r="32" ht="25" customHeight="1" spans="1:15">
       <c r="A32" s="12" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>116</v>
+        <v>151</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E32" s="22" t="s">
-        <v>117</v>
+        <v>152</v>
       </c>
       <c r="F32" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G32" s="5">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="J32" s="5"/>
       <c r="K32" s="5"/>
       <c r="L32" s="5" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M32" s="5"/>
       <c r="N32" s="5"/>
-      <c r="O32" s="36"/>
+      <c r="O32" s="41"/>
     </row>
     <row r="33" ht="25" customHeight="1" spans="1:15">
       <c r="A33" s="12" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>156</v>
+        <v>121</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E33" s="22" t="s">
+        <v>122</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G33" s="5">
+        <v>2026</v>
+      </c>
+      <c r="H33" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="F33" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G33" s="5">
-        <v>2025</v>
-      </c>
-      <c r="H33" s="5" t="s">
+      <c r="I33" s="5" t="s">
         <v>158</v>
-      </c>
-      <c r="I33" s="5" t="s">
-        <v>159</v>
       </c>
       <c r="J33" s="5"/>
       <c r="K33" s="5"/>
       <c r="L33" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M33" s="5"/>
       <c r="N33" s="5"/>
-      <c r="O33" s="36"/>
+      <c r="O33" s="41"/>
     </row>
     <row r="34" ht="25" customHeight="1" spans="1:15">
       <c r="A34" s="12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C34" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E34" s="22" t="s">
         <v>162</v>
       </c>
-      <c r="D34" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E34" s="22" t="s">
-        <v>135</v>
-      </c>
       <c r="F34" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G34" s="5">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="H34" s="5" t="s">
         <v>163</v>
@@ -4081,7 +4152,7 @@
       </c>
       <c r="M34" s="5"/>
       <c r="N34" s="5"/>
-      <c r="O34" s="36"/>
+      <c r="O34" s="41"/>
     </row>
     <row r="35" ht="25" customHeight="1" spans="1:15">
       <c r="A35" s="12" t="s">
@@ -4097,7 +4168,7 @@
         <v>14</v>
       </c>
       <c r="E35" s="22" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="F35" s="5" t="s">
         <v>33</v>
@@ -4118,7 +4189,7 @@
       </c>
       <c r="M35" s="5"/>
       <c r="N35" s="5"/>
-      <c r="O35" s="36"/>
+      <c r="O35" s="41"/>
     </row>
     <row r="36" ht="25" customHeight="1" spans="1:15">
       <c r="A36" s="12" t="s">
@@ -4134,7 +4205,7 @@
         <v>14</v>
       </c>
       <c r="E36" s="22" t="s">
-        <v>99</v>
+        <v>140</v>
       </c>
       <c r="F36" s="5" t="s">
         <v>33</v>
@@ -4155,7 +4226,7 @@
       </c>
       <c r="M36" s="5"/>
       <c r="N36" s="5"/>
-      <c r="O36" s="36"/>
+      <c r="O36" s="41"/>
     </row>
     <row r="37" ht="25" customHeight="1" spans="1:15">
       <c r="A37" s="12" t="s">
@@ -4165,19 +4236,19 @@
         <v>12</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>122</v>
+        <v>177</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E37" s="22" t="s">
-        <v>177</v>
+        <v>104</v>
       </c>
       <c r="F37" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G37" s="5">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="H37" s="5" t="s">
         <v>178</v>
@@ -4192,7 +4263,7 @@
       </c>
       <c r="M37" s="5"/>
       <c r="N37" s="5"/>
-      <c r="O37" s="36"/>
+      <c r="O37" s="41"/>
     </row>
     <row r="38" ht="25" customHeight="1" spans="1:15">
       <c r="A38" s="12" t="s">
@@ -4202,50 +4273,50 @@
         <v>12</v>
       </c>
       <c r="C38" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E38" s="22" t="s">
         <v>182</v>
       </c>
-      <c r="D38" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E38" s="22" t="s">
+      <c r="F38" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G38" s="5">
+        <v>2025</v>
+      </c>
+      <c r="H38" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="F38" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G38" s="5">
-        <v>2026</v>
-      </c>
-      <c r="H38" s="5" t="s">
+      <c r="I38" s="5" t="s">
         <v>184</v>
-      </c>
-      <c r="I38" s="5" t="s">
-        <v>185</v>
       </c>
       <c r="J38" s="5"/>
       <c r="K38" s="5"/>
       <c r="L38" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="M38" s="5"/>
       <c r="N38" s="5"/>
-      <c r="O38" s="36"/>
+      <c r="O38" s="41"/>
     </row>
     <row r="39" ht="25" customHeight="1" spans="1:15">
       <c r="A39" s="12" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C39" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E39" s="22" t="s">
         <v>188</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E39" s="22" t="s">
-        <v>105</v>
       </c>
       <c r="F39" s="5" t="s">
         <v>33</v>
@@ -4266,14 +4337,14 @@
       </c>
       <c r="M39" s="5"/>
       <c r="N39" s="5"/>
-      <c r="O39" s="36"/>
+      <c r="O39" s="41"/>
     </row>
     <row r="40" ht="25" customHeight="1" spans="1:15">
       <c r="A40" s="12" t="s">
         <v>192</v>
       </c>
-      <c r="B40" s="24" t="s">
-        <v>53</v>
+      <c r="B40" s="5" t="s">
+        <v>12</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>193</v>
@@ -4282,42 +4353,44 @@
         <v>14</v>
       </c>
       <c r="E40" s="22" t="s">
+        <v>110</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G40" s="5">
+        <v>2026</v>
+      </c>
+      <c r="H40" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="F40" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G40" s="5">
-        <v>2025</v>
-      </c>
-      <c r="H40" s="5"/>
       <c r="I40" s="5" t="s">
         <v>195</v>
       </c>
       <c r="J40" s="5"/>
       <c r="K40" s="5"/>
       <c r="L40" s="5" t="s">
-        <v>53</v>
+        <v>196</v>
       </c>
       <c r="M40" s="5"/>
       <c r="N40" s="5"/>
-      <c r="O40" s="36"/>
+      <c r="O40" s="41"/>
     </row>
     <row r="41" ht="25" customHeight="1" spans="1:15">
       <c r="A41" s="12" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B41" s="24" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E41" s="22" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F41" s="5" t="s">
         <v>33</v>
@@ -4325,36 +4398,34 @@
       <c r="G41" s="5">
         <v>2025</v>
       </c>
-      <c r="H41" s="5" t="s">
-        <v>199</v>
-      </c>
+      <c r="H41" s="5"/>
       <c r="I41" s="5" t="s">
         <v>200</v>
       </c>
       <c r="J41" s="5"/>
       <c r="K41" s="5"/>
       <c r="L41" s="5" t="s">
-        <v>201</v>
+        <v>58</v>
       </c>
       <c r="M41" s="5"/>
       <c r="N41" s="5"/>
-      <c r="O41" s="36"/>
+      <c r="O41" s="41"/>
     </row>
     <row r="42" ht="25" customHeight="1" spans="1:15">
       <c r="A42" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="B42" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="C42" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="B42" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="C42" s="5" t="s">
+      <c r="D42" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E42" s="22" t="s">
         <v>203</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E42" s="22" t="s">
-        <v>194</v>
       </c>
       <c r="F42" s="5" t="s">
         <v>33</v>
@@ -4362,82 +4433,96 @@
       <c r="G42" s="5">
         <v>2025</v>
       </c>
-      <c r="H42" s="5"/>
+      <c r="H42" s="5" t="s">
+        <v>204</v>
+      </c>
       <c r="I42" s="5" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="J42" s="5"/>
       <c r="K42" s="5"/>
       <c r="L42" s="5" t="s">
-        <v>53</v>
+        <v>206</v>
       </c>
       <c r="M42" s="5"/>
       <c r="N42" s="5"/>
-      <c r="O42" s="36"/>
+      <c r="O42" s="41"/>
     </row>
     <row r="43" ht="25" customHeight="1" spans="1:15">
       <c r="A43" s="12" t="s">
-        <v>205</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>206</v>
+        <v>207</v>
+      </c>
+      <c r="B43" s="24" t="s">
+        <v>58</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D43" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E43" s="22" t="s">
-        <v>111</v>
+        <v>199</v>
       </c>
       <c r="F43" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G43" s="5">
-        <v>2026</v>
-      </c>
-      <c r="H43" s="5" t="s">
-        <v>208</v>
-      </c>
+        <v>2025</v>
+      </c>
+      <c r="H43" s="5"/>
       <c r="I43" s="5" t="s">
         <v>209</v>
       </c>
       <c r="J43" s="5"/>
       <c r="K43" s="5"/>
       <c r="L43" s="5" t="s">
-        <v>210</v>
+        <v>58</v>
       </c>
       <c r="M43" s="5"/>
       <c r="N43" s="5"/>
-      <c r="O43" s="36"/>
+      <c r="O43" s="41"/>
     </row>
     <row r="44" ht="25" customHeight="1" spans="1:15">
       <c r="A44" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="B44" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="B44" s="5"/>
-      <c r="C44" s="5"/>
-      <c r="D44" s="5"/>
-      <c r="E44" s="22"/>
+      <c r="C44" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E44" s="22" t="s">
+        <v>116</v>
+      </c>
       <c r="F44" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G44" s="5"/>
-      <c r="H44" s="5"/>
+      <c r="G44" s="5">
+        <v>2026</v>
+      </c>
+      <c r="H44" s="5" t="s">
+        <v>213</v>
+      </c>
       <c r="I44" s="5" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J44" s="5"/>
       <c r="K44" s="5"/>
-      <c r="L44" s="5"/>
+      <c r="L44" s="5" t="s">
+        <v>215</v>
+      </c>
       <c r="M44" s="5"/>
       <c r="N44" s="5"/>
-      <c r="O44" s="36"/>
+      <c r="O44" s="41"/>
     </row>
     <row r="45" ht="25" customHeight="1" spans="1:15">
       <c r="A45" s="12" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5"/>
@@ -4449,18 +4534,18 @@
       <c r="G45" s="5"/>
       <c r="H45" s="5"/>
       <c r="I45" s="5" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="J45" s="5"/>
       <c r="K45" s="5"/>
       <c r="L45" s="5"/>
       <c r="M45" s="5"/>
       <c r="N45" s="5"/>
-      <c r="O45" s="36"/>
+      <c r="O45" s="41"/>
     </row>
     <row r="46" ht="25" customHeight="1" spans="1:15">
       <c r="A46" s="12" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5"/>
@@ -4472,18 +4557,18 @@
       <c r="G46" s="5"/>
       <c r="H46" s="5"/>
       <c r="I46" s="5" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="J46" s="5"/>
       <c r="K46" s="5"/>
       <c r="L46" s="5"/>
       <c r="M46" s="5"/>
       <c r="N46" s="5"/>
-      <c r="O46" s="36"/>
+      <c r="O46" s="41"/>
     </row>
     <row r="47" ht="25" customHeight="1" spans="1:15">
       <c r="A47" s="12" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
@@ -4495,64 +4580,64 @@
       <c r="G47" s="5"/>
       <c r="H47" s="5"/>
       <c r="I47" s="5" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="J47" s="5"/>
       <c r="K47" s="5"/>
       <c r="L47" s="5"/>
       <c r="M47" s="5"/>
       <c r="N47" s="5"/>
-      <c r="O47" s="36"/>
+      <c r="O47" s="41"/>
     </row>
     <row r="48" ht="25" customHeight="1" spans="1:15">
-      <c r="A48" s="14" t="s">
-        <v>219</v>
-      </c>
-      <c r="B48" s="15"/>
-      <c r="C48" s="15"/>
-      <c r="D48" s="15"/>
-      <c r="E48" s="37"/>
+      <c r="A48" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="B48" s="5"/>
+      <c r="C48" s="5"/>
+      <c r="D48" s="5"/>
+      <c r="E48" s="22"/>
       <c r="F48" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G48" s="15"/>
-      <c r="H48" s="15"/>
-      <c r="I48" s="16" t="s">
-        <v>220</v>
-      </c>
-      <c r="J48" s="15"/>
+      <c r="G48" s="5"/>
+      <c r="H48" s="5"/>
+      <c r="I48" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="J48" s="5"/>
       <c r="K48" s="5"/>
       <c r="L48" s="5"/>
       <c r="M48" s="5"/>
       <c r="N48" s="5"/>
-      <c r="O48" s="36"/>
+      <c r="O48" s="41"/>
     </row>
     <row r="49" ht="25" customHeight="1" spans="1:15">
-      <c r="A49" s="12" t="s">
-        <v>221</v>
-      </c>
-      <c r="B49" s="5"/>
-      <c r="C49" s="5"/>
-      <c r="D49" s="5"/>
-      <c r="E49" s="22"/>
+      <c r="A49" s="14" t="s">
+        <v>224</v>
+      </c>
+      <c r="B49" s="15"/>
+      <c r="C49" s="15"/>
+      <c r="D49" s="15"/>
+      <c r="E49" s="42"/>
       <c r="F49" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G49" s="5"/>
-      <c r="H49" s="5"/>
-      <c r="I49" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="J49" s="5"/>
+      <c r="G49" s="15"/>
+      <c r="H49" s="15"/>
+      <c r="I49" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="J49" s="15"/>
       <c r="K49" s="5"/>
       <c r="L49" s="5"/>
       <c r="M49" s="5"/>
       <c r="N49" s="5"/>
-      <c r="O49" s="36"/>
+      <c r="O49" s="41"/>
     </row>
     <row r="50" ht="25" customHeight="1" spans="1:15">
       <c r="A50" s="12" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5"/>
@@ -4564,18 +4649,18 @@
       <c r="G50" s="5"/>
       <c r="H50" s="5"/>
       <c r="I50" s="5" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="J50" s="5"/>
       <c r="K50" s="5"/>
       <c r="L50" s="5"/>
       <c r="M50" s="5"/>
       <c r="N50" s="5"/>
-      <c r="O50" s="36"/>
+      <c r="O50" s="41"/>
     </row>
     <row r="51" ht="25" customHeight="1" spans="1:15">
       <c r="A51" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
@@ -4587,18 +4672,18 @@
       <c r="G51" s="5"/>
       <c r="H51" s="5"/>
       <c r="I51" s="5" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="J51" s="5"/>
       <c r="K51" s="5"/>
       <c r="L51" s="5"/>
       <c r="M51" s="5"/>
       <c r="N51" s="5"/>
-      <c r="O51" s="36"/>
+      <c r="O51" s="41"/>
     </row>
     <row r="52" ht="25" customHeight="1" spans="1:15">
       <c r="A52" s="12" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5"/>
@@ -4610,18 +4695,18 @@
       <c r="G52" s="5"/>
       <c r="H52" s="5"/>
       <c r="I52" s="5" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="J52" s="5"/>
       <c r="K52" s="5"/>
       <c r="L52" s="5"/>
       <c r="M52" s="5"/>
       <c r="N52" s="5"/>
-      <c r="O52" s="36"/>
+      <c r="O52" s="41"/>
     </row>
     <row r="53" ht="25" customHeight="1" spans="1:15">
       <c r="A53" s="12" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5"/>
@@ -4631,20 +4716,19 @@
         <v>33</v>
       </c>
       <c r="G53" s="5"/>
-      <c r="H53" s="5"/>
       <c r="I53" s="5" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="J53" s="5"/>
       <c r="K53" s="5"/>
       <c r="L53" s="5"/>
       <c r="M53" s="5"/>
       <c r="N53" s="5"/>
-      <c r="O53" s="36"/>
+      <c r="O53" s="41"/>
     </row>
     <row r="54" ht="25" customHeight="1" spans="1:15">
       <c r="A54" s="12" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
@@ -4656,18 +4740,18 @@
       <c r="G54" s="5"/>
       <c r="H54" s="5"/>
       <c r="I54" s="5" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="J54" s="5"/>
       <c r="K54" s="5"/>
       <c r="L54" s="5"/>
       <c r="M54" s="5"/>
       <c r="N54" s="5"/>
-      <c r="O54" s="36"/>
+      <c r="O54" s="41"/>
     </row>
     <row r="55" ht="25" customHeight="1" spans="1:15">
       <c r="A55" s="12" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B55" s="5"/>
       <c r="C55" s="5"/>
@@ -4679,18 +4763,18 @@
       <c r="G55" s="5"/>
       <c r="H55" s="5"/>
       <c r="I55" s="5" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="J55" s="5"/>
       <c r="K55" s="5"/>
       <c r="L55" s="5"/>
       <c r="M55" s="5"/>
       <c r="N55" s="5"/>
-      <c r="O55" s="36"/>
+      <c r="O55" s="41"/>
     </row>
     <row r="56" ht="25" customHeight="1" spans="1:15">
       <c r="A56" s="12" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
@@ -4700,19 +4784,20 @@
         <v>33</v>
       </c>
       <c r="G56" s="5"/>
+      <c r="H56" s="5"/>
       <c r="I56" s="5" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="J56" s="5"/>
       <c r="K56" s="5"/>
       <c r="L56" s="5"/>
       <c r="M56" s="5"/>
       <c r="N56" s="5"/>
-      <c r="O56" s="36"/>
+      <c r="O56" s="41"/>
     </row>
     <row r="57" ht="25" customHeight="1" spans="1:15">
       <c r="A57" s="12" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
@@ -4722,20 +4807,19 @@
         <v>33</v>
       </c>
       <c r="G57" s="5"/>
-      <c r="H57" s="5"/>
       <c r="I57" s="5" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="J57" s="5"/>
       <c r="K57" s="5"/>
       <c r="L57" s="5"/>
       <c r="M57" s="5"/>
       <c r="N57" s="5"/>
-      <c r="O57" s="36"/>
-    </row>
-    <row r="58" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="O57" s="41"/>
+    </row>
+    <row r="58" ht="25" customHeight="1" spans="1:15">
       <c r="A58" s="12" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
@@ -4747,18 +4831,18 @@
       <c r="G58" s="5"/>
       <c r="H58" s="5"/>
       <c r="I58" s="5" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="J58" s="5"/>
       <c r="K58" s="5"/>
       <c r="L58" s="5"/>
       <c r="M58" s="5"/>
       <c r="N58" s="5"/>
-      <c r="O58" s="36"/>
+      <c r="O58" s="41"/>
     </row>
     <row r="59" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A59" s="12" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
@@ -4770,18 +4854,18 @@
       <c r="G59" s="5"/>
       <c r="H59" s="5"/>
       <c r="I59" s="5" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="J59" s="5"/>
       <c r="K59" s="5"/>
       <c r="L59" s="5"/>
       <c r="M59" s="5"/>
       <c r="N59" s="5"/>
-      <c r="O59" s="36"/>
+      <c r="O59" s="41"/>
     </row>
     <row r="60" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A60" s="12" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
@@ -4793,18 +4877,18 @@
       <c r="G60" s="5"/>
       <c r="H60" s="5"/>
       <c r="I60" s="5" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="J60" s="5"/>
       <c r="K60" s="5"/>
       <c r="L60" s="5"/>
       <c r="M60" s="5"/>
       <c r="N60" s="5"/>
-      <c r="O60" s="36"/>
+      <c r="O60" s="41"/>
     </row>
     <row r="61" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A61" s="12" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
@@ -4816,36 +4900,28 @@
       <c r="G61" s="5"/>
       <c r="H61" s="5"/>
       <c r="I61" s="5" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="J61" s="5"/>
       <c r="K61" s="5"/>
       <c r="L61" s="5"/>
       <c r="M61" s="5"/>
       <c r="N61" s="5"/>
-      <c r="O61" s="36"/>
+      <c r="O61" s="41"/>
     </row>
     <row r="62" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A62" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C62" s="17" t="s">
-        <v>248</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="B62" s="5"/>
+      <c r="C62" s="5"/>
       <c r="D62" s="5"/>
-      <c r="E62" s="22" t="s">
-        <v>249</v>
-      </c>
+      <c r="E62" s="22"/>
       <c r="F62" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G62" s="5"/>
-      <c r="H62" s="18" t="s">
-        <v>250</v>
-      </c>
+      <c r="H62" s="5"/>
       <c r="I62" s="5" t="s">
         <v>251</v>
       </c>
@@ -4854,83 +4930,83 @@
       <c r="L62" s="5"/>
       <c r="M62" s="5"/>
       <c r="N62" s="5"/>
-      <c r="O62" s="36"/>
+      <c r="O62" s="41"/>
     </row>
     <row r="63" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A63" s="12" t="s">
         <v>252</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>62</v>
+        <v>12</v>
       </c>
       <c r="C63" s="17" t="s">
         <v>253</v>
       </c>
       <c r="D63" s="5"/>
       <c r="E63" s="22" t="s">
-        <v>111</v>
+        <v>254</v>
       </c>
       <c r="F63" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G63" s="5"/>
       <c r="H63" s="18" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="I63" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="J63" s="5"/>
       <c r="K63" s="5"/>
       <c r="L63" s="5"/>
       <c r="M63" s="5"/>
       <c r="N63" s="5"/>
-      <c r="O63" s="5"/>
+      <c r="O63" s="41"/>
     </row>
     <row r="64" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A64" s="12" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C64" s="19" t="s">
-        <v>257</v>
+        <v>67</v>
+      </c>
+      <c r="C64" s="17" t="s">
+        <v>258</v>
       </c>
       <c r="D64" s="5"/>
       <c r="E64" s="22" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F64" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G64" s="5"/>
       <c r="H64" s="18" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I64" s="5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="J64" s="5"/>
       <c r="K64" s="5"/>
       <c r="L64" s="5"/>
       <c r="M64" s="5"/>
       <c r="N64" s="5"/>
-      <c r="O64" s="36"/>
-    </row>
-    <row r="65" ht="25" customHeight="1" spans="1:15">
+      <c r="O64" s="5"/>
+    </row>
+    <row r="65" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A65" s="12" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C65" s="17" t="s">
-        <v>261</v>
+      <c r="C65" s="19" t="s">
+        <v>262</v>
       </c>
       <c r="D65" s="5"/>
       <c r="E65" s="22" t="s">
-        <v>262</v>
+        <v>122</v>
       </c>
       <c r="F65" s="5" t="s">
         <v>33</v>
@@ -4947,7 +5023,7 @@
       <c r="L65" s="5"/>
       <c r="M65" s="5"/>
       <c r="N65" s="5"/>
-      <c r="O65" s="36"/>
+      <c r="O65" s="41"/>
     </row>
     <row r="66" ht="25" customHeight="1" spans="1:15">
       <c r="A66" s="12" t="s">
@@ -4961,38 +5037,38 @@
       </c>
       <c r="D66" s="5"/>
       <c r="E66" s="22" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G66" s="5"/>
       <c r="H66" s="18" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I66" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="J66" s="5"/>
       <c r="K66" s="5"/>
       <c r="L66" s="5"/>
       <c r="M66" s="5"/>
       <c r="N66" s="5"/>
-      <c r="O66" s="36"/>
+      <c r="O66" s="41"/>
     </row>
     <row r="67" ht="25" customHeight="1" spans="1:15">
       <c r="A67" s="12" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="C67" s="17" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D67" s="5"/>
       <c r="E67" s="22" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="F67" s="5" t="s">
         <v>33</v>
@@ -5009,31 +5085,27 @@
       <c r="L67" s="5"/>
       <c r="M67" s="5"/>
       <c r="N67" s="5"/>
-      <c r="O67" s="36"/>
+      <c r="O67" s="41"/>
     </row>
     <row r="68" ht="25" customHeight="1" spans="1:15">
       <c r="A68" s="12" t="s">
         <v>274</v>
       </c>
       <c r="B68" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C68" s="17" t="s">
         <v>275</v>
       </c>
-      <c r="C68" s="38" t="s">
+      <c r="D68" s="5"/>
+      <c r="E68" s="22" t="s">
         <v>276</v>
       </c>
-      <c r="D68" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="E68" s="28">
-        <v>16</v>
-      </c>
-      <c r="F68" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="G68" s="24">
-        <v>2026</v>
-      </c>
-      <c r="H68" s="5" t="s">
+      <c r="F68" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G68" s="5"/>
+      <c r="H68" s="18" t="s">
         <v>277</v>
       </c>
       <c r="I68" s="5" t="s">
@@ -5044,18 +5116,36 @@
       <c r="L68" s="5"/>
       <c r="M68" s="5"/>
       <c r="N68" s="5"/>
-      <c r="O68" s="5"/>
+      <c r="O68" s="41"/>
     </row>
     <row r="69" ht="25" customHeight="1" spans="1:15">
-      <c r="A69" s="12"/>
-      <c r="B69" s="5"/>
-      <c r="C69" s="5"/>
-      <c r="D69" s="5"/>
-      <c r="E69" s="22"/>
-      <c r="F69" s="13"/>
-      <c r="G69" s="5"/>
-      <c r="H69" s="5"/>
-      <c r="I69" s="5"/>
+      <c r="A69" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="C69" s="43" t="s">
+        <v>281</v>
+      </c>
+      <c r="D69" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E69" s="44">
+        <v>16</v>
+      </c>
+      <c r="F69" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G69" s="24">
+        <v>2026</v>
+      </c>
+      <c r="H69" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="I69" s="5" t="s">
+        <v>283</v>
+      </c>
       <c r="J69" s="5"/>
       <c r="K69" s="5"/>
       <c r="L69" s="5"/>
@@ -5071,6 +5161,7 @@
       <c r="E70" s="22"/>
       <c r="F70" s="13"/>
       <c r="G70" s="5"/>
+      <c r="H70" s="5"/>
       <c r="I70" s="5"/>
       <c r="J70" s="5"/>
       <c r="K70" s="5"/>
@@ -5087,7 +5178,6 @@
       <c r="E71" s="22"/>
       <c r="F71" s="13"/>
       <c r="G71" s="5"/>
-      <c r="H71" s="5"/>
       <c r="I71" s="5"/>
       <c r="J71" s="5"/>
       <c r="K71" s="5"/>
@@ -5138,7 +5228,6 @@
       <c r="E74" s="22"/>
       <c r="F74" s="13"/>
       <c r="G74" s="5"/>
-      <c r="H74" s="5"/>
       <c r="I74" s="5"/>
       <c r="J74" s="5"/>
       <c r="K74" s="5"/>
@@ -5189,6 +5278,7 @@
       <c r="E77" s="22"/>
       <c r="F77" s="13"/>
       <c r="G77" s="5"/>
+      <c r="H77" s="5"/>
       <c r="I77" s="5"/>
       <c r="J77" s="5"/>
       <c r="K77" s="5"/>
@@ -5205,7 +5295,6 @@
       <c r="E78" s="22"/>
       <c r="F78" s="13"/>
       <c r="G78" s="5"/>
-      <c r="H78" s="5"/>
       <c r="I78" s="5"/>
       <c r="J78" s="5"/>
       <c r="K78" s="5"/>
@@ -5299,16 +5388,33 @@
       <c r="N83" s="5"/>
       <c r="O83" s="5"/>
     </row>
+    <row r="84" ht="25" customHeight="1" spans="1:15">
+      <c r="A84" s="12"/>
+      <c r="B84" s="5"/>
+      <c r="C84" s="5"/>
+      <c r="D84" s="5"/>
+      <c r="E84" s="22"/>
+      <c r="F84" s="13"/>
+      <c r="G84" s="5"/>
+      <c r="H84" s="5"/>
+      <c r="I84" s="5"/>
+      <c r="J84" s="5"/>
+      <c r="K84" s="5"/>
+      <c r="L84" s="5"/>
+      <c r="M84" s="5"/>
+      <c r="N84" s="5"/>
+      <c r="O84" s="5"/>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:O68" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A1:O68">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:O69" etc:filterBottomFollowUsedRange="0">
+    <sortState ref="A1:O69">
       <sortCondition ref="F1"/>
     </sortState>
     <extLst/>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="H63" r:id="rId1" display="普洛伊湘普·素帕莎 / 芭莉雅皮·余 " tooltip="https://www.douban.com/personage/30264980/"/>
-    <hyperlink ref="H18" r:id="rId2" display="金贤叙/郑明哲" tooltip="https://www.douban.com/personage/37338980/"/>
+    <hyperlink ref="H64" r:id="rId1" display="普洛伊湘普·素帕莎 / 芭莉雅皮·余 " tooltip="https://www.douban.com/personage/30264980/"/>
+    <hyperlink ref="H19" r:id="rId2" display="金贤叙/郑明哲" tooltip="https://www.douban.com/personage/37338980/"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -5332,7 +5438,7 @@
   <sheetData>
     <row r="1" ht="33" customHeight="1" spans="1:9">
       <c r="A1" s="3" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -5379,7 +5485,7 @@
         <v>12</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>14</v>
@@ -5518,13 +5624,13 @@
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:9">
       <c r="A8" s="6" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>14</v>
@@ -5539,21 +5645,21 @@
         <v>2026</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:9">
       <c r="A9" s="6" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>14</v>
@@ -5568,21 +5674,21 @@
         <v>2026</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:9">
       <c r="A10" s="6" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>14</v>
@@ -5597,21 +5703,21 @@
         <v>2026</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:9">
       <c r="A11" s="6" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>14</v>
@@ -5626,21 +5732,21 @@
         <v>2026</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:9">
       <c r="A12" s="6" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>14</v>
@@ -5655,21 +5761,21 @@
         <v>2026</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:9">
       <c r="A13" s="6" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>14</v>
@@ -5684,21 +5790,21 @@
         <v>2026</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:9">
       <c r="A14" s="6" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>14</v>
@@ -5713,21 +5819,21 @@
         <v>2026</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:9">
       <c r="A15" s="6" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>14</v>
@@ -5742,21 +5848,21 @@
         <v>2026</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:9">
       <c r="A16" s="6" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>14</v>
@@ -5771,21 +5877,21 @@
         <v>2026</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:9">
       <c r="A17" s="6" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>14</v>
@@ -5801,18 +5907,18 @@
       </c>
       <c r="H17" s="7"/>
       <c r="I17" s="8" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:9">
       <c r="A18" s="6" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>14</v>
@@ -5828,18 +5934,18 @@
       </c>
       <c r="H18" s="7"/>
       <c r="I18" s="8" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" spans="1:9">
       <c r="A19" s="9" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>14</v>
@@ -5853,18 +5959,18 @@
       </c>
       <c r="H19" s="7"/>
       <c r="I19" s="11" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" spans="1:9">
       <c r="A20" s="9" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>14</v>
@@ -5878,24 +5984,24 @@
       </c>
       <c r="H20" s="7"/>
       <c r="I20" s="11" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1" spans="1:9">
       <c r="A21" s="12" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>33</v>
@@ -5904,27 +6010,27 @@
         <v>2026</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1" spans="1:9">
       <c r="A22" s="12" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>33</v>
@@ -5933,27 +6039,27 @@
         <v>2025</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1" spans="1:9">
       <c r="A23" s="12" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>33</v>
@@ -5962,27 +6068,27 @@
         <v>2026</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1" spans="1:9">
       <c r="A24" s="12" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>33</v>
@@ -5991,27 +6097,27 @@
         <v>2026</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1" spans="1:9">
       <c r="A25" s="12" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="F25" s="5" t="s">
         <v>33</v>
@@ -6020,27 +6126,27 @@
         <v>2025</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1" spans="1:9">
       <c r="A26" s="12" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="F26" s="5" t="s">
         <v>33</v>
@@ -6049,27 +6155,27 @@
         <v>2026</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1" spans="1:9">
       <c r="A27" s="12" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="F27" s="5" t="s">
         <v>33</v>
@@ -6078,27 +6184,27 @@
         <v>2026</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1" spans="1:9">
       <c r="A28" s="12" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="F28" s="5" t="s">
         <v>33</v>
@@ -6107,27 +6213,27 @@
         <v>2024</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
     </row>
     <row r="29" ht="25" customHeight="1" spans="1:9">
       <c r="A29" s="12" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="F29" s="5" t="s">
         <v>33</v>
@@ -6136,27 +6242,27 @@
         <v>2024</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="30" ht="25" customHeight="1" spans="1:9">
       <c r="A30" s="12" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="F30" s="5" t="s">
         <v>33</v>
@@ -6165,27 +6271,27 @@
         <v>2026</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
     </row>
     <row r="31" ht="25" customHeight="1" spans="1:9">
       <c r="A31" s="12" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="F31" s="5" t="s">
         <v>33</v>
@@ -6194,27 +6300,27 @@
         <v>2025</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
     </row>
     <row r="32" ht="25" customHeight="1" spans="1:9">
       <c r="A32" s="12" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="F32" s="5" t="s">
         <v>33</v>
@@ -6223,27 +6329,27 @@
         <v>2026</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
     </row>
     <row r="33" ht="25" customHeight="1" spans="1:9">
       <c r="A33" s="12" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="F33" s="5" t="s">
         <v>33</v>
@@ -6252,27 +6358,27 @@
         <v>2026</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="I33" s="5" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="34" ht="25" customHeight="1" spans="1:9">
       <c r="A34" s="12" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="F34" s="5" t="s">
         <v>33</v>
@@ -6281,27 +6387,27 @@
         <v>2026</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" ht="25" customHeight="1" spans="1:9">
       <c r="A35" s="12" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="F35" s="5" t="s">
         <v>33</v>
@@ -6310,27 +6416,27 @@
         <v>2025</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
     </row>
     <row r="36" ht="25" customHeight="1" spans="1:9">
       <c r="A36" s="12" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="F36" s="5" t="s">
         <v>33</v>
@@ -6339,27 +6445,27 @@
         <v>2026</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
     </row>
     <row r="37" ht="25" customHeight="1" spans="1:9">
       <c r="A37" s="12" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F37" s="5" t="s">
         <v>33</v>
@@ -6368,27 +6474,27 @@
         <v>2026</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="I37" s="5" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
     </row>
     <row r="38" ht="25" customHeight="1" spans="1:9">
       <c r="A38" s="12" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="F38" s="5" t="s">
         <v>33</v>
@@ -6398,24 +6504,24 @@
       </c>
       <c r="H38" s="5"/>
       <c r="I38" s="5" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
     </row>
     <row r="39" ht="25" customHeight="1" spans="1:9">
       <c r="A39" s="12" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="F39" s="5" t="s">
         <v>33</v>
@@ -6424,27 +6530,27 @@
         <v>2025</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="I39" s="5" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
     </row>
     <row r="40" ht="25" customHeight="1" spans="1:9">
       <c r="A40" s="12" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="D40" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="F40" s="5" t="s">
         <v>33</v>
@@ -6454,24 +6560,24 @@
       </c>
       <c r="H40" s="5"/>
       <c r="I40" s="5" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
     </row>
     <row r="41" ht="25" customHeight="1" spans="1:9">
       <c r="A41" s="12" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="F41" s="5" t="s">
         <v>33</v>
@@ -6480,15 +6586,15 @@
         <v>2026</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="I41" s="5" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
     </row>
     <row r="42" ht="25" customHeight="1" spans="1:9">
       <c r="A42" s="12" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5"/>
@@ -6500,12 +6606,12 @@
       <c r="G42" s="5"/>
       <c r="H42" s="5"/>
       <c r="I42" s="5" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
     </row>
     <row r="43" ht="25" customHeight="1" spans="1:9">
       <c r="A43" s="12" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5"/>
@@ -6517,12 +6623,12 @@
       <c r="G43" s="5"/>
       <c r="H43" s="5"/>
       <c r="I43" s="5" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
     </row>
     <row r="44" ht="25" customHeight="1" spans="1:9">
       <c r="A44" s="12" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
@@ -6534,12 +6640,12 @@
       <c r="G44" s="5"/>
       <c r="H44" s="5"/>
       <c r="I44" s="5" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
     </row>
     <row r="45" ht="25" customHeight="1" spans="1:9">
       <c r="A45" s="12" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5"/>
@@ -6551,12 +6657,12 @@
       <c r="G45" s="5"/>
       <c r="H45" s="5"/>
       <c r="I45" s="5" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
     </row>
     <row r="46" ht="25" customHeight="1" spans="1:9">
       <c r="A46" s="14" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="B46" s="15"/>
       <c r="C46" s="15"/>
@@ -6568,12 +6674,12 @@
       <c r="G46" s="15"/>
       <c r="H46" s="15"/>
       <c r="I46" s="16" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
     </row>
     <row r="47" ht="25" customHeight="1" spans="1:9">
       <c r="A47" s="12" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
@@ -6585,12 +6691,12 @@
       <c r="G47" s="5"/>
       <c r="H47" s="5"/>
       <c r="I47" s="5" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
     </row>
     <row r="48" ht="25" customHeight="1" spans="1:9">
       <c r="A48" s="12" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
@@ -6602,12 +6708,12 @@
       <c r="G48" s="5"/>
       <c r="H48" s="5"/>
       <c r="I48" s="5" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
     </row>
     <row r="49" ht="25" customHeight="1" spans="1:9">
       <c r="A49" s="12" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
@@ -6619,12 +6725,12 @@
       <c r="G49" s="5"/>
       <c r="H49" s="5"/>
       <c r="I49" s="5" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
     </row>
     <row r="50" ht="25" customHeight="1" spans="1:9">
       <c r="A50" s="12" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5"/>
@@ -6636,12 +6742,12 @@
       <c r="G50" s="5"/>
       <c r="H50" s="5"/>
       <c r="I50" s="5" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
     </row>
     <row r="51" ht="25" customHeight="1" spans="1:9">
       <c r="A51" s="12" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
@@ -6653,12 +6759,12 @@
       <c r="G51" s="5"/>
       <c r="H51" s="5"/>
       <c r="I51" s="5" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
     </row>
     <row r="52" ht="25" customHeight="1" spans="1:9">
       <c r="A52" s="12" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5"/>
@@ -6670,162 +6776,162 @@
       <c r="G52" s="5"/>
       <c r="H52" s="5"/>
       <c r="I52" s="5" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
     </row>
     <row r="53" customFormat="1" ht="25" customHeight="1" spans="1:9">
       <c r="A53" s="12" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C53" s="17" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="D53" s="5"/>
       <c r="E53" s="5" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="F53" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G53" s="5"/>
       <c r="H53" s="18" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="I53" s="5" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
     </row>
     <row r="54" customFormat="1" ht="25" customHeight="1" spans="1:9">
       <c r="A54" s="12" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C54" s="17" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="D54" s="5"/>
       <c r="E54" s="5" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="F54" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G54" s="5"/>
       <c r="H54" s="18" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="I54" s="5" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
     </row>
     <row r="55" customFormat="1" ht="25" customHeight="1" spans="1:9">
       <c r="A55" s="12" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C55" s="19" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="D55" s="5"/>
       <c r="E55" s="5" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="F55" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G55" s="5"/>
       <c r="H55" s="18" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="I55" s="5" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
     </row>
     <row r="56" ht="25" customHeight="1" spans="1:9">
       <c r="A56" s="12" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C56" s="17" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D56" s="5"/>
       <c r="E56" s="5" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="F56" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G56" s="5"/>
       <c r="H56" s="18" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="I56" s="5" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
     </row>
     <row r="57" ht="25" customHeight="1" spans="1:9">
       <c r="A57" s="12" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C57" s="17" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="D57" s="5"/>
       <c r="E57" s="5" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="F57" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G57" s="5"/>
       <c r="H57" s="18" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="I57" s="5" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
     </row>
     <row r="58" ht="25" customHeight="1" spans="1:9">
       <c r="A58" s="12" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C58" s="17" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="D58" s="5"/>
       <c r="E58" s="5" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="F58" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G58" s="5"/>
       <c r="H58" s="18" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="I58" s="5" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
     </row>
     <row r="59" ht="25" customHeight="1" spans="1:9">
       <c r="A59" s="12" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
@@ -6837,12 +6943,12 @@
       <c r="G59" s="5"/>
       <c r="H59" s="5"/>
       <c r="I59" s="5" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
     </row>
     <row r="60" ht="25" customHeight="1" spans="1:9">
       <c r="A60" s="12" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
@@ -6854,12 +6960,12 @@
       <c r="G60" s="5"/>
       <c r="H60" s="5"/>
       <c r="I60" s="5" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
     </row>
     <row r="61" ht="25" customHeight="1" spans="1:9">
       <c r="A61" s="12" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
@@ -6871,12 +6977,12 @@
       <c r="G61" s="5"/>
       <c r="H61" s="5"/>
       <c r="I61" s="5" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
     </row>
     <row r="62" customFormat="1" ht="25" customHeight="1" spans="1:9">
       <c r="A62" s="12" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="B62" s="5"/>
       <c r="C62" s="5"/>
@@ -6888,12 +6994,12 @@
       <c r="G62" s="5"/>
       <c r="H62" s="5"/>
       <c r="I62" s="5" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
     </row>
     <row r="63" customFormat="1" ht="25" customHeight="1" spans="1:9">
       <c r="A63" s="12" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="B63" s="5"/>
       <c r="C63" s="5"/>
@@ -6905,12 +7011,12 @@
       <c r="G63" s="5"/>
       <c r="H63" s="5"/>
       <c r="I63" s="5" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
     </row>
     <row r="64" customFormat="1" ht="25" customHeight="1" spans="1:9">
       <c r="A64" s="12" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="B64" s="5"/>
       <c r="C64" s="5"/>
@@ -6922,12 +7028,12 @@
       <c r="G64" s="5"/>
       <c r="H64" s="5"/>
       <c r="I64" s="5" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
     </row>
     <row r="65" customFormat="1" ht="25" customHeight="1" spans="1:9">
       <c r="A65" s="12" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B65" s="5"/>
       <c r="C65" s="5"/>
@@ -6939,7 +7045,7 @@
       <c r="G65" s="5"/>
       <c r="H65" s="5"/>
       <c r="I65" s="5" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
     </row>
     <row r="66" ht="25" customHeight="1" spans="1:9">

--- a/资源录入表新.xlsx
+++ b/资源录入表新.xlsx
@@ -16,7 +16,7 @@
     <sheet name="资源录入表 (2)" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">资源录入表!$A$1:$O$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">资源录入表!$A$1:$O$70</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'资源录入表 (2)'!$A$2:$I$20</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="853" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="295">
   <si>
     <t>剧名</t>
   </si>
@@ -517,6 +517,70 @@
   </si>
   <si>
     <t xml:space="preserve">链接: https://pan.baidu.com/s/1nduXuhFEN-emGjxKdEnY-A 提取码: tsum </t>
+  </si>
+  <si>
+    <t>我的偶像总裁</t>
+  </si>
+  <si>
+    <r>
+      <t>喜剧</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>爱情</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>姜勋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>金慧埈</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>车禹闵</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1b4kgz-PlK3oQ_N89iSuweg 提取码: 98fh </t>
   </si>
   <si>
     <t>给你梦想</t>
@@ -1714,6 +1778,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <name val="Helvetica"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="10.5"/>
       <name val="Arial"/>
       <charset val="134"/>
@@ -1721,11 +1790,6 @@
     <font>
       <sz val="10.5"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Helvetica"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1745,18 +1809,12 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -2124,7 +2182,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2148,16 +2206,16 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -2166,89 +2224,89 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2312,6 +2370,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2339,22 +2403,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2363,6 +2421,18 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2380,9 +2450,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2917,14 +2984,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O84"/>
+  <dimension ref="A1:O85"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="17.625" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="1"/>
     <col min="3" max="3" width="30.5833333333333" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
-    <col min="5" max="5" width="9" style="21"/>
+    <col min="5" max="5" width="9" style="23"/>
     <col min="6" max="7" width="9" style="1"/>
     <col min="8" max="8" width="80.2916666666667" style="1" customWidth="1"/>
     <col min="9" max="9" width="74.25" style="1" customWidth="1"/>
@@ -2947,7 +3014,7 @@
       <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="22" t="s">
+      <c r="E1" s="24" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="5" t="s">
@@ -2974,31 +3041,31 @@
       <c r="O1" s="5"/>
     </row>
     <row r="2" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="25">
+      <c r="D2" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="27">
         <v>12</v>
       </c>
-      <c r="F2" s="24" t="s">
+      <c r="F2" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="24">
+      <c r="G2" s="26">
         <v>2026</v>
       </c>
-      <c r="H2" s="24" t="s">
+      <c r="H2" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="24" t="s">
+      <c r="I2" s="26" t="s">
         <v>17</v>
       </c>
       <c r="J2" s="13"/>
@@ -3009,31 +3076,31 @@
       <c r="O2" s="13"/>
     </row>
     <row r="3" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="24" t="s">
+      <c r="C3" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="25">
+      <c r="D3" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="27">
         <v>13</v>
       </c>
-      <c r="F3" s="24" t="s">
+      <c r="F3" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="24">
+      <c r="G3" s="26">
         <v>2026</v>
       </c>
-      <c r="H3" s="24" t="s">
+      <c r="H3" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="24" t="s">
+      <c r="I3" s="26" t="s">
         <v>21</v>
       </c>
       <c r="J3" s="13"/>
@@ -3044,31 +3111,31 @@
       <c r="O3" s="13"/>
     </row>
     <row r="4" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="24" t="s">
+      <c r="B4" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="24" t="s">
+      <c r="C4" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="25">
+      <c r="D4" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="27">
         <v>26</v>
       </c>
-      <c r="F4" s="24" t="s">
+      <c r="F4" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="24">
+      <c r="G4" s="26">
         <v>2026</v>
       </c>
-      <c r="H4" s="24" t="s">
+      <c r="H4" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="I4" s="24" t="s">
+      <c r="I4" s="26" t="s">
         <v>25</v>
       </c>
       <c r="J4" s="13"/>
@@ -3081,31 +3148,31 @@
       <c r="O4" s="13"/>
     </row>
     <row r="5" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A5" s="23" t="s">
+      <c r="A5" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="24" t="s">
+      <c r="B5" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="24" t="s">
+      <c r="C5" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="25">
+      <c r="D5" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="27">
         <v>26</v>
       </c>
-      <c r="F5" s="24" t="s">
+      <c r="F5" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="24">
+      <c r="G5" s="26">
         <v>2026</v>
       </c>
-      <c r="H5" s="24" t="s">
+      <c r="H5" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="I5" s="24" t="s">
+      <c r="I5" s="26" t="s">
         <v>30</v>
       </c>
       <c r="J5" s="13"/>
@@ -3116,31 +3183,31 @@
       <c r="O5" s="13"/>
     </row>
     <row r="6" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="24" t="s">
+      <c r="C6" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="25">
+      <c r="D6" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="27">
         <v>24</v>
       </c>
-      <c r="F6" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="G6" s="24">
+      <c r="F6" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" s="26">
         <v>2026</v>
       </c>
-      <c r="H6" s="24" t="s">
+      <c r="H6" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="I6" s="24" t="s">
+      <c r="I6" s="26" t="s">
         <v>35</v>
       </c>
       <c r="J6" s="13"/>
@@ -3157,13 +3224,13 @@
       <c r="B7" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="27" t="s">
+      <c r="C7" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="29">
+      <c r="D7" s="30" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="31">
         <v>15</v>
       </c>
       <c r="F7" s="13" t="s">
@@ -3185,102 +3252,102 @@
       <c r="N7" s="5"/>
       <c r="O7" s="5"/>
     </row>
-    <row r="8" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A8" s="30" t="s">
+    <row r="8" s="21" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A8" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="B8" s="31" t="s">
+      <c r="B8" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="32" t="s">
+      <c r="C8" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="D8" s="33" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="11">
+      <c r="D8" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="33">
         <v>8</v>
       </c>
-      <c r="F8" s="34" t="s">
+      <c r="F8" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="G8" s="31">
+      <c r="G8" s="33">
         <v>2026</v>
       </c>
       <c r="H8" s="35" t="s">
         <v>42</v>
       </c>
-      <c r="I8" s="31" t="s">
+      <c r="I8" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
-      <c r="M8" s="5"/>
-      <c r="N8" s="5"/>
-      <c r="O8" s="5"/>
-    </row>
-    <row r="9" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A9" s="30" t="s">
+      <c r="J8" s="24"/>
+      <c r="K8" s="24"/>
+      <c r="L8" s="24"/>
+      <c r="M8" s="24"/>
+      <c r="N8" s="24"/>
+      <c r="O8" s="24"/>
+    </row>
+    <row r="9" s="21" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A9" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="B9" s="31" t="s">
+      <c r="B9" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="32" t="s">
+      <c r="C9" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="D9" s="33" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" s="11">
+      <c r="D9" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="33">
         <v>8</v>
       </c>
-      <c r="F9" s="34" t="s">
+      <c r="F9" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="G9" s="31">
+      <c r="G9" s="33">
         <v>2026</v>
       </c>
       <c r="H9" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="I9" s="31" t="s">
+      <c r="I9" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5"/>
-      <c r="M9" s="5"/>
-      <c r="N9" s="5"/>
-      <c r="O9" s="5"/>
+      <c r="J9" s="24"/>
+      <c r="K9" s="24"/>
+      <c r="L9" s="24"/>
+      <c r="M9" s="24"/>
+      <c r="N9" s="24"/>
+      <c r="O9" s="24"/>
     </row>
     <row r="10" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A10" s="23" t="s">
+      <c r="A10" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="B10" s="24" t="s">
+      <c r="B10" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="C10" s="24" t="s">
+      <c r="C10" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="D10" s="24" t="s">
+      <c r="D10" s="26" t="s">
         <v>14</v>
       </c>
       <c r="E10" s="36">
         <v>3</v>
       </c>
-      <c r="F10" s="24" t="s">
+      <c r="F10" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="G10" s="24">
+      <c r="G10" s="26">
         <v>2026</v>
       </c>
-      <c r="H10" s="24" t="s">
+      <c r="H10" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="I10" s="24" t="s">
+      <c r="I10" s="26" t="s">
         <v>52</v>
       </c>
       <c r="J10" s="13"/>
@@ -3291,31 +3358,31 @@
       <c r="O10" s="13"/>
     </row>
     <row r="11" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A11" s="23" t="s">
+      <c r="A11" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="C11" s="24" t="s">
+      <c r="C11" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="D11" s="24" t="s">
+      <c r="D11" s="26" t="s">
         <v>14</v>
       </c>
       <c r="E11" s="36">
         <v>4</v>
       </c>
-      <c r="F11" s="24" t="s">
+      <c r="F11" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="G11" s="24">
+      <c r="G11" s="26">
         <v>2026</v>
       </c>
-      <c r="H11" s="24" t="s">
+      <c r="H11" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="I11" s="24" t="s">
+      <c r="I11" s="26" t="s">
         <v>56</v>
       </c>
       <c r="J11" s="13"/>
@@ -3326,28 +3393,28 @@
       <c r="O11" s="13"/>
     </row>
     <row r="12" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A12" s="23" t="s">
+      <c r="A12" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="B12" s="24" t="s">
+      <c r="B12" s="26" t="s">
         <v>58</v>
       </c>
       <c r="C12" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="D12" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="E12" s="25">
+      <c r="D12" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="27">
         <v>2</v>
       </c>
-      <c r="F12" s="24" t="s">
+      <c r="F12" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="G12" s="24">
+      <c r="G12" s="26">
         <v>2026</v>
       </c>
-      <c r="H12" s="24" t="s">
+      <c r="H12" s="26" t="s">
         <v>60</v>
       </c>
       <c r="I12" s="13" t="s">
@@ -3360,70 +3427,68 @@
       <c r="N12" s="13"/>
       <c r="O12" s="13"/>
     </row>
-    <row r="13" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A13" s="23" t="s">
+    <row r="13" s="22" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A13" s="38" t="s">
         <v>62</v>
       </c>
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="C13" s="24" t="s">
+      <c r="C13" s="39" t="s">
         <v>63</v>
       </c>
-      <c r="D13" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="E13" s="25">
+      <c r="D13" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="8">
+        <v>1</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" s="8">
+        <v>2026</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="I13" s="40" t="s">
+        <v>65</v>
+      </c>
+      <c r="J13" s="41"/>
+      <c r="K13" s="41"/>
+      <c r="L13" s="41"/>
+      <c r="M13" s="41"/>
+      <c r="N13" s="41"/>
+      <c r="O13" s="41"/>
+    </row>
+    <row r="14" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A14" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="C14" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="D14" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" s="27">
         <v>7</v>
       </c>
-      <c r="F13" s="24" t="s">
+      <c r="F14" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="G13" s="24">
+      <c r="G14" s="26">
         <v>2026</v>
       </c>
-      <c r="H13" s="24" t="s">
-        <v>64</v>
-      </c>
-      <c r="I13" s="24" t="s">
-        <v>65</v>
-      </c>
-      <c r="J13" s="13"/>
-      <c r="K13" s="13"/>
-      <c r="L13" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="M13" s="13"/>
-      <c r="N13" s="13"/>
-      <c r="O13" s="13"/>
-    </row>
-    <row r="14" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A14" s="23" t="s">
-        <v>66</v>
-      </c>
-      <c r="B14" s="24" t="s">
-        <v>67</v>
-      </c>
-      <c r="C14" s="24" t="s">
+      <c r="H14" s="26" t="s">
         <v>68</v>
       </c>
-      <c r="D14" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" s="36">
-        <v>7</v>
-      </c>
-      <c r="F14" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="G14" s="24">
-        <v>2026</v>
-      </c>
-      <c r="H14" s="24" t="s">
+      <c r="I14" s="26" t="s">
         <v>69</v>
-      </c>
-      <c r="I14" s="24" t="s">
-        <v>70</v>
       </c>
       <c r="J14" s="13"/>
       <c r="K14" s="13"/>
@@ -3435,32 +3500,32 @@
       <c r="O14" s="13"/>
     </row>
     <row r="15" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A15" s="23" t="s">
+      <c r="A15" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="B15" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="B15" s="24" t="s">
-        <v>58</v>
-      </c>
-      <c r="C15" s="24" t="s">
-        <v>63</v>
-      </c>
-      <c r="D15" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="E15" s="25">
-        <v>6</v>
-      </c>
-      <c r="F15" s="24" t="s">
+      <c r="C15" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="D15" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" s="36">
+        <v>7</v>
+      </c>
+      <c r="F15" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="G15" s="24">
+      <c r="G15" s="26">
         <v>2026</v>
       </c>
-      <c r="H15" s="24" t="s">
-        <v>72</v>
-      </c>
-      <c r="I15" s="24" t="s">
+      <c r="H15" s="26" t="s">
         <v>73</v>
+      </c>
+      <c r="I15" s="26" t="s">
+        <v>74</v>
       </c>
       <c r="J15" s="13"/>
       <c r="K15" s="13"/>
@@ -3472,31 +3537,31 @@
       <c r="O15" s="13"/>
     </row>
     <row r="16" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A16" s="23" t="s">
-        <v>74</v>
-      </c>
-      <c r="B16" s="24" t="s">
+      <c r="A16" s="25" t="s">
+        <v>75</v>
+      </c>
+      <c r="B16" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="C16" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="D16" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="E16" s="25">
-        <v>8</v>
-      </c>
-      <c r="F16" s="24" t="s">
+      <c r="C16" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="D16" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" s="27">
+        <v>6</v>
+      </c>
+      <c r="F16" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="G16" s="24">
+      <c r="G16" s="26">
         <v>2026</v>
       </c>
-      <c r="H16" s="24" t="s">
+      <c r="H16" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="I16" s="24" t="s">
+      <c r="I16" s="26" t="s">
         <v>77</v>
       </c>
       <c r="J16" s="13"/>
@@ -3509,31 +3574,31 @@
       <c r="O16" s="13"/>
     </row>
     <row r="17" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A17" s="23" t="s">
+      <c r="A17" s="25" t="s">
         <v>78</v>
       </c>
-      <c r="B17" s="24" t="s">
+      <c r="B17" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="C17" s="24" t="s">
+      <c r="C17" s="26" t="s">
         <v>79</v>
       </c>
-      <c r="D17" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="E17" s="25">
-        <v>10</v>
-      </c>
-      <c r="F17" s="24" t="s">
+      <c r="D17" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="E17" s="27">
+        <v>8</v>
+      </c>
+      <c r="F17" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="G17" s="24">
+      <c r="G17" s="26">
         <v>2026</v>
       </c>
-      <c r="H17" s="24" t="s">
+      <c r="H17" s="26" t="s">
         <v>80</v>
       </c>
-      <c r="I17" s="24" t="s">
+      <c r="I17" s="26" t="s">
         <v>81</v>
       </c>
       <c r="J17" s="13"/>
@@ -3546,137 +3611,141 @@
       <c r="O17" s="13"/>
     </row>
     <row r="18" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A18" s="23" t="s">
+      <c r="A18" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="B18" s="24" t="s">
+      <c r="B18" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="C18" s="24" t="s">
+      <c r="C18" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="D18" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="E18" s="36">
-        <v>4</v>
-      </c>
-      <c r="F18" s="24" t="s">
+      <c r="D18" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="27">
+        <v>10</v>
+      </c>
+      <c r="F18" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="G18" s="24">
+      <c r="G18" s="26">
         <v>2026</v>
       </c>
-      <c r="H18" s="24" t="s">
+      <c r="H18" s="26" t="s">
         <v>84</v>
       </c>
-      <c r="I18" s="24" t="s">
+      <c r="I18" s="26" t="s">
         <v>85</v>
       </c>
       <c r="J18" s="13"/>
       <c r="K18" s="13"/>
       <c r="L18" s="13" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="M18" s="13"/>
       <c r="N18" s="13"/>
       <c r="O18" s="13"/>
     </row>
     <row r="19" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A19" s="23" t="s">
+      <c r="A19" s="25" t="s">
+        <v>86</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="C19" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="B19" s="24" t="s">
-        <v>58</v>
-      </c>
-      <c r="C19" s="24" t="s">
+      <c r="D19" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19" s="36">
+        <v>4</v>
+      </c>
+      <c r="F19" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="G19" s="26">
+        <v>2026</v>
+      </c>
+      <c r="H19" s="26" t="s">
         <v>88</v>
       </c>
-      <c r="D19" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="E19" s="36">
-        <v>8</v>
-      </c>
-      <c r="F19" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="G19" s="24">
-        <v>2026</v>
-      </c>
-      <c r="H19" s="24" t="s">
+      <c r="I19" s="26" t="s">
         <v>89</v>
-      </c>
-      <c r="I19" s="24" t="s">
-        <v>90</v>
       </c>
       <c r="J19" s="13"/>
       <c r="K19" s="13"/>
       <c r="L19" s="13" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="M19" s="13"/>
       <c r="N19" s="13"/>
       <c r="O19" s="13"/>
     </row>
     <row r="20" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A20" s="23" t="s">
+      <c r="A20" s="25" t="s">
         <v>91</v>
       </c>
-      <c r="B20" s="24" t="s">
-        <v>49</v>
-      </c>
-      <c r="C20" s="24" t="s">
+      <c r="B20" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="C20" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="D20" s="24" t="s">
+      <c r="D20" s="26" t="s">
         <v>14</v>
       </c>
       <c r="E20" s="36">
-        <v>7</v>
-      </c>
-      <c r="F20" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="G20" s="24">
+      <c r="G20" s="26">
         <v>2026</v>
       </c>
-      <c r="H20" s="24"/>
-      <c r="I20" s="24" t="s">
+      <c r="H20" s="26" t="s">
         <v>93</v>
+      </c>
+      <c r="I20" s="26" t="s">
+        <v>94</v>
       </c>
       <c r="J20" s="13"/>
       <c r="K20" s="13"/>
-      <c r="L20" s="13"/>
+      <c r="L20" s="13" t="s">
+        <v>58</v>
+      </c>
       <c r="M20" s="13"/>
       <c r="N20" s="13"/>
       <c r="O20" s="13"/>
     </row>
     <row r="21" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A21" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B21" s="24" t="s">
+      <c r="A21" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="B21" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="C21" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="D21" s="24" t="s">
+      <c r="C21" s="26" t="s">
+        <v>96</v>
+      </c>
+      <c r="D21" s="26" t="s">
         <v>14</v>
       </c>
       <c r="E21" s="36">
-        <v>5</v>
-      </c>
-      <c r="F21" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="F21" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="G21" s="24">
+      <c r="G21" s="26">
         <v>2026</v>
       </c>
-      <c r="H21" s="24"/>
-      <c r="I21" s="24" t="s">
-        <v>96</v>
+      <c r="H21" s="26"/>
+      <c r="I21" s="26" t="s">
+        <v>97</v>
       </c>
       <c r="J21" s="13"/>
       <c r="K21" s="13"/>
@@ -3686,136 +3755,131 @@
       <c r="O21" s="13"/>
     </row>
     <row r="22" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A22" s="38" t="s">
-        <v>97</v>
-      </c>
-      <c r="B22" s="13" t="s">
+      <c r="A22" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="B22" s="26" t="s">
         <v>49</v>
       </c>
       <c r="C22" s="26" t="s">
-        <v>98</v>
-      </c>
-      <c r="D22" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="E22" s="39"/>
+        <v>99</v>
+      </c>
+      <c r="D22" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="E22" s="36">
+        <v>5</v>
+      </c>
       <c r="F22" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="G22" s="24">
+        <v>15</v>
+      </c>
+      <c r="G22" s="26">
         <v>2026</v>
       </c>
-      <c r="H22" s="24"/>
-      <c r="I22" s="13" t="s">
-        <v>99</v>
+      <c r="I22" s="26" t="s">
+        <v>100</v>
       </c>
       <c r="J22" s="13"/>
       <c r="K22" s="13"/>
       <c r="L22" s="13"/>
       <c r="M22" s="13"/>
       <c r="N22" s="13"/>
-      <c r="O22" s="40"/>
+      <c r="O22" s="13"/>
     </row>
     <row r="23" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A23" s="38" t="s">
-        <v>100</v>
+      <c r="A23" s="42" t="s">
+        <v>101</v>
       </c>
       <c r="B23" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="C23" s="26" t="s">
-        <v>98</v>
-      </c>
-      <c r="D23" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="E23" s="39"/>
-      <c r="F23" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="G23" s="24">
+      <c r="C23" s="28" t="s">
+        <v>102</v>
+      </c>
+      <c r="D23" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="E23" s="43"/>
+      <c r="F23" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="G23" s="26">
         <v>2026</v>
       </c>
-      <c r="H23" s="24"/>
+      <c r="H23" s="26"/>
       <c r="I23" s="13" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="J23" s="13"/>
       <c r="K23" s="13"/>
       <c r="L23" s="13"/>
       <c r="M23" s="13"/>
       <c r="N23" s="13"/>
-      <c r="O23" s="40"/>
-    </row>
-    <row r="24" ht="25" customHeight="1" spans="1:15">
-      <c r="A24" s="12" t="s">
+      <c r="O23" s="44"/>
+    </row>
+    <row r="24" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A24" s="42" t="s">
+        <v>104</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="C24" s="28" t="s">
         <v>102</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E24" s="22" t="s">
-        <v>104</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G24" s="5">
+      <c r="D24" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="E24" s="43"/>
+      <c r="F24" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="G24" s="26">
         <v>2026</v>
       </c>
-      <c r="H24" s="5" t="s">
+      <c r="H24" s="26"/>
+      <c r="I24" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="I24" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="J24" s="5"/>
-      <c r="K24" s="5"/>
-      <c r="L24" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="M24" s="5"/>
-      <c r="N24" s="5"/>
-      <c r="O24" s="5"/>
+      <c r="J24" s="13"/>
+      <c r="K24" s="13"/>
+      <c r="L24" s="13"/>
+      <c r="M24" s="13"/>
+      <c r="N24" s="13"/>
+      <c r="O24" s="44"/>
     </row>
     <row r="25" ht="25" customHeight="1" spans="1:15">
       <c r="A25" s="12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C25" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E25" s="24" t="s">
+        <v>108</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G25" s="5">
+        <v>2026</v>
+      </c>
+      <c r="H25" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="D25" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E25" s="22" t="s">
+      <c r="I25" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G25" s="5">
-        <v>2025</v>
-      </c>
-      <c r="H25" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>112</v>
       </c>
       <c r="J25" s="5"/>
       <c r="K25" s="5"/>
       <c r="L25" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M25" s="5"/>
       <c r="N25" s="5"/>
@@ -3823,36 +3887,36 @@
     </row>
     <row r="26" ht="25" customHeight="1" spans="1:15">
       <c r="A26" s="12" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C26" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E26" s="24" t="s">
+        <v>114</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G26" s="5">
+        <v>2025</v>
+      </c>
+      <c r="H26" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="D26" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E26" s="22" t="s">
+      <c r="I26" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G26" s="5">
-        <v>2026</v>
-      </c>
-      <c r="H26" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>118</v>
       </c>
       <c r="J26" s="5"/>
       <c r="K26" s="5"/>
       <c r="L26" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="M26" s="5"/>
       <c r="N26" s="5"/>
@@ -3860,19 +3924,19 @@
     </row>
     <row r="27" ht="25" customHeight="1" spans="1:15">
       <c r="A27" s="12" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E27" s="22" t="s">
-        <v>122</v>
+      <c r="E27" s="24" t="s">
+        <v>120</v>
       </c>
       <c r="F27" s="5" t="s">
         <v>33</v>
@@ -3881,15 +3945,15 @@
         <v>2026</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="J27" s="5"/>
       <c r="K27" s="5"/>
       <c r="L27" s="5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="M27" s="5"/>
       <c r="N27" s="5"/>
@@ -3897,36 +3961,36 @@
     </row>
     <row r="28" ht="25" customHeight="1" spans="1:15">
       <c r="A28" s="12" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C28" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E28" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G28" s="5">
+        <v>2026</v>
+      </c>
+      <c r="H28" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="D28" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E28" s="22" t="s">
+      <c r="I28" s="1" t="s">
         <v>128</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G28" s="5">
-        <v>2025</v>
-      </c>
-      <c r="H28" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>130</v>
       </c>
       <c r="J28" s="5"/>
       <c r="K28" s="5"/>
       <c r="L28" s="5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="M28" s="5"/>
       <c r="N28" s="5"/>
@@ -3934,56 +3998,56 @@
     </row>
     <row r="29" ht="25" customHeight="1" spans="1:15">
       <c r="A29" s="12" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C29" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E29" s="24" t="s">
+        <v>132</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G29" s="5">
+        <v>2025</v>
+      </c>
+      <c r="H29" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="D29" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E29" s="22" t="s">
+      <c r="I29" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="F29" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G29" s="5">
-        <v>2026</v>
-      </c>
-      <c r="H29" s="5" t="s">
+      <c r="J29" s="5"/>
+      <c r="K29" s="5"/>
+      <c r="L29" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="I29" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="J29" s="15"/>
-      <c r="K29" s="15"/>
-      <c r="L29" s="15" t="s">
-        <v>137</v>
-      </c>
-      <c r="M29" s="15"/>
-      <c r="N29" s="15"/>
+      <c r="M29" s="5"/>
+      <c r="N29" s="5"/>
       <c r="O29" s="5"/>
     </row>
     <row r="30" ht="25" customHeight="1" spans="1:15">
       <c r="A30" s="12" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E30" s="22" t="s">
-        <v>140</v>
+      <c r="E30" s="24" t="s">
+        <v>138</v>
       </c>
       <c r="F30" s="5" t="s">
         <v>33</v>
@@ -3992,72 +4056,72 @@
         <v>2026</v>
       </c>
       <c r="H30" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J30" s="15"/>
+      <c r="K30" s="15"/>
+      <c r="L30" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="I30" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="J30" s="5"/>
-      <c r="K30" s="5"/>
-      <c r="L30" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="M30" s="5"/>
-      <c r="N30" s="5"/>
-      <c r="O30" s="41"/>
+      <c r="M30" s="15"/>
+      <c r="N30" s="15"/>
+      <c r="O30" s="5"/>
     </row>
     <row r="31" ht="25" customHeight="1" spans="1:15">
       <c r="A31" s="12" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C31" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E31" s="24" t="s">
+        <v>144</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G31" s="5">
+        <v>2026</v>
+      </c>
+      <c r="H31" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="D31" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E31" s="22" t="s">
+      <c r="I31" s="5" t="s">
         <v>146</v>
-      </c>
-      <c r="F31" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G31" s="5">
-        <v>2024</v>
-      </c>
-      <c r="H31" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="I31" s="5" t="s">
-        <v>148</v>
       </c>
       <c r="J31" s="5"/>
       <c r="K31" s="5"/>
       <c r="L31" s="5" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="M31" s="5"/>
       <c r="N31" s="5"/>
-      <c r="O31" s="41"/>
+      <c r="O31" s="45"/>
     </row>
     <row r="32" ht="25" customHeight="1" spans="1:15">
       <c r="A32" s="12" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E32" s="22" t="s">
-        <v>152</v>
+      <c r="E32" s="24" t="s">
+        <v>150</v>
       </c>
       <c r="F32" s="5" t="s">
         <v>33</v>
@@ -4066,41 +4130,41 @@
         <v>2024</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="J32" s="5"/>
       <c r="K32" s="5"/>
       <c r="L32" s="5" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="M32" s="5"/>
       <c r="N32" s="5"/>
-      <c r="O32" s="41"/>
+      <c r="O32" s="45"/>
     </row>
     <row r="33" ht="25" customHeight="1" spans="1:15">
       <c r="A33" s="12" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>121</v>
+        <v>155</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E33" s="22" t="s">
-        <v>122</v>
+      <c r="E33" s="24" t="s">
+        <v>156</v>
       </c>
       <c r="F33" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G33" s="5">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="H33" s="5" t="s">
         <v>157</v>
@@ -4115,7 +4179,7 @@
       </c>
       <c r="M33" s="5"/>
       <c r="N33" s="5"/>
-      <c r="O33" s="41"/>
+      <c r="O33" s="45"/>
     </row>
     <row r="34" ht="25" customHeight="1" spans="1:15">
       <c r="A34" s="12" t="s">
@@ -4125,87 +4189,87 @@
         <v>12</v>
       </c>
       <c r="C34" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E34" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G34" s="5">
+        <v>2026</v>
+      </c>
+      <c r="H34" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="D34" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E34" s="22" t="s">
+      <c r="I34" s="5" t="s">
         <v>162</v>
-      </c>
-      <c r="F34" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G34" s="5">
-        <v>2025</v>
-      </c>
-      <c r="H34" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="I34" s="5" t="s">
-        <v>164</v>
       </c>
       <c r="J34" s="5"/>
       <c r="K34" s="5"/>
       <c r="L34" s="5" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="M34" s="5"/>
       <c r="N34" s="5"/>
-      <c r="O34" s="41"/>
+      <c r="O34" s="45"/>
     </row>
     <row r="35" ht="25" customHeight="1" spans="1:15">
       <c r="A35" s="12" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C35" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E35" s="24" t="s">
+        <v>166</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G35" s="5">
+        <v>2025</v>
+      </c>
+      <c r="H35" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="D35" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E35" s="22" t="s">
-        <v>140</v>
-      </c>
-      <c r="F35" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G35" s="5">
-        <v>2026</v>
-      </c>
-      <c r="H35" s="5" t="s">
+      <c r="I35" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="I35" s="5" t="s">
-        <v>169</v>
       </c>
       <c r="J35" s="5"/>
       <c r="K35" s="5"/>
       <c r="L35" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="M35" s="5"/>
       <c r="N35" s="5"/>
-      <c r="O35" s="41"/>
+      <c r="O35" s="45"/>
     </row>
     <row r="36" ht="25" customHeight="1" spans="1:15">
       <c r="A36" s="12" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E36" s="22" t="s">
-        <v>140</v>
+      <c r="E36" s="24" t="s">
+        <v>144</v>
       </c>
       <c r="F36" s="5" t="s">
         <v>33</v>
@@ -4214,35 +4278,35 @@
         <v>2026</v>
       </c>
       <c r="H36" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="I36" s="5" t="s">
         <v>173</v>
-      </c>
-      <c r="I36" s="5" t="s">
-        <v>174</v>
       </c>
       <c r="J36" s="5"/>
       <c r="K36" s="5"/>
       <c r="L36" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="M36" s="5"/>
       <c r="N36" s="5"/>
-      <c r="O36" s="41"/>
+      <c r="O36" s="45"/>
     </row>
     <row r="37" ht="25" customHeight="1" spans="1:15">
       <c r="A37" s="12" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E37" s="22" t="s">
-        <v>104</v>
+      <c r="E37" s="24" t="s">
+        <v>144</v>
       </c>
       <c r="F37" s="5" t="s">
         <v>33</v>
@@ -4251,109 +4315,109 @@
         <v>2026</v>
       </c>
       <c r="H37" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="I37" s="5" t="s">
         <v>178</v>
-      </c>
-      <c r="I37" s="5" t="s">
-        <v>179</v>
       </c>
       <c r="J37" s="5"/>
       <c r="K37" s="5"/>
       <c r="L37" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="M37" s="5"/>
       <c r="N37" s="5"/>
-      <c r="O37" s="41"/>
+      <c r="O37" s="45"/>
     </row>
     <row r="38" ht="25" customHeight="1" spans="1:15">
       <c r="A38" s="12" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E38" s="22" t="s">
+      <c r="E38" s="24" t="s">
+        <v>108</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G38" s="5">
+        <v>2026</v>
+      </c>
+      <c r="H38" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="F38" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G38" s="5">
-        <v>2025</v>
-      </c>
-      <c r="H38" s="5" t="s">
+      <c r="I38" s="5" t="s">
         <v>183</v>
-      </c>
-      <c r="I38" s="5" t="s">
-        <v>184</v>
       </c>
       <c r="J38" s="5"/>
       <c r="K38" s="5"/>
       <c r="L38" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="M38" s="5"/>
       <c r="N38" s="5"/>
-      <c r="O38" s="41"/>
+      <c r="O38" s="45"/>
     </row>
     <row r="39" ht="25" customHeight="1" spans="1:15">
       <c r="A39" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C39" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E39" s="24" t="s">
+        <v>186</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G39" s="5">
+        <v>2025</v>
+      </c>
+      <c r="H39" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="D39" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E39" s="22" t="s">
+      <c r="I39" s="5" t="s">
         <v>188</v>
-      </c>
-      <c r="F39" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G39" s="5">
-        <v>2026</v>
-      </c>
-      <c r="H39" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="I39" s="5" t="s">
-        <v>190</v>
       </c>
       <c r="J39" s="5"/>
       <c r="K39" s="5"/>
       <c r="L39" s="5" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="M39" s="5"/>
       <c r="N39" s="5"/>
-      <c r="O39" s="41"/>
+      <c r="O39" s="45"/>
     </row>
     <row r="40" ht="25" customHeight="1" spans="1:15">
       <c r="A40" s="12" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D40" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E40" s="22" t="s">
-        <v>110</v>
+      <c r="E40" s="24" t="s">
+        <v>192</v>
       </c>
       <c r="F40" s="5" t="s">
         <v>33</v>
@@ -4362,60 +4426,62 @@
         <v>2026</v>
       </c>
       <c r="H40" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="I40" s="5" t="s">
         <v>194</v>
-      </c>
-      <c r="I40" s="5" t="s">
-        <v>195</v>
       </c>
       <c r="J40" s="5"/>
       <c r="K40" s="5"/>
       <c r="L40" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="M40" s="5"/>
       <c r="N40" s="5"/>
-      <c r="O40" s="41"/>
+      <c r="O40" s="45"/>
     </row>
     <row r="41" ht="25" customHeight="1" spans="1:15">
       <c r="A41" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C41" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="B41" s="24" t="s">
-        <v>58</v>
-      </c>
-      <c r="C41" s="5" t="s">
+      <c r="D41" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E41" s="24" t="s">
+        <v>114</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G41" s="5">
+        <v>2026</v>
+      </c>
+      <c r="H41" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="D41" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E41" s="22" t="s">
+      <c r="I41" s="5" t="s">
         <v>199</v>
-      </c>
-      <c r="F41" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G41" s="5">
-        <v>2025</v>
-      </c>
-      <c r="H41" s="5"/>
-      <c r="I41" s="5" t="s">
-        <v>200</v>
       </c>
       <c r="J41" s="5"/>
       <c r="K41" s="5"/>
       <c r="L41" s="5" t="s">
-        <v>58</v>
+        <v>200</v>
       </c>
       <c r="M41" s="5"/>
       <c r="N41" s="5"/>
-      <c r="O41" s="41"/>
+      <c r="O41" s="45"/>
     </row>
     <row r="42" ht="25" customHeight="1" spans="1:15">
       <c r="A42" s="12" t="s">
         <v>201</v>
       </c>
-      <c r="B42" s="24" t="s">
+      <c r="B42" s="26" t="s">
         <v>58</v>
       </c>
       <c r="C42" s="5" t="s">
@@ -4424,7 +4490,7 @@
       <c r="D42" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E42" s="22" t="s">
+      <c r="E42" s="24" t="s">
         <v>203</v>
       </c>
       <c r="F42" s="5" t="s">
@@ -4433,36 +4499,34 @@
       <c r="G42" s="5">
         <v>2025</v>
       </c>
-      <c r="H42" s="5" t="s">
+      <c r="H42" s="5"/>
+      <c r="I42" s="5" t="s">
         <v>204</v>
-      </c>
-      <c r="I42" s="5" t="s">
-        <v>205</v>
       </c>
       <c r="J42" s="5"/>
       <c r="K42" s="5"/>
       <c r="L42" s="5" t="s">
-        <v>206</v>
+        <v>58</v>
       </c>
       <c r="M42" s="5"/>
       <c r="N42" s="5"/>
-      <c r="O42" s="41"/>
+      <c r="O42" s="45"/>
     </row>
     <row r="43" ht="25" customHeight="1" spans="1:15">
       <c r="A43" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="B43" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E43" s="24" t="s">
         <v>207</v>
-      </c>
-      <c r="B43" s="24" t="s">
-        <v>58</v>
-      </c>
-      <c r="C43" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E43" s="22" t="s">
-        <v>199</v>
       </c>
       <c r="F43" s="5" t="s">
         <v>33</v>
@@ -4470,25 +4534,27 @@
       <c r="G43" s="5">
         <v>2025</v>
       </c>
-      <c r="H43" s="5"/>
+      <c r="H43" s="5" t="s">
+        <v>208</v>
+      </c>
       <c r="I43" s="5" t="s">
         <v>209</v>
       </c>
       <c r="J43" s="5"/>
       <c r="K43" s="5"/>
       <c r="L43" s="5" t="s">
-        <v>58</v>
+        <v>210</v>
       </c>
       <c r="M43" s="5"/>
       <c r="N43" s="5"/>
-      <c r="O43" s="41"/>
+      <c r="O43" s="45"/>
     </row>
     <row r="44" ht="25" customHeight="1" spans="1:15">
       <c r="A44" s="12" t="s">
-        <v>210</v>
-      </c>
-      <c r="B44" s="5" t="s">
         <v>211</v>
+      </c>
+      <c r="B44" s="26" t="s">
+        <v>58</v>
       </c>
       <c r="C44" s="5" t="s">
         <v>212</v>
@@ -4496,486 +4562,490 @@
       <c r="D44" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E44" s="22" t="s">
-        <v>116</v>
+      <c r="E44" s="24" t="s">
+        <v>203</v>
       </c>
       <c r="F44" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G44" s="5">
-        <v>2026</v>
-      </c>
-      <c r="H44" s="5" t="s">
+        <v>2025</v>
+      </c>
+      <c r="H44" s="5"/>
+      <c r="I44" s="5" t="s">
         <v>213</v>
-      </c>
-      <c r="I44" s="5" t="s">
-        <v>214</v>
       </c>
       <c r="J44" s="5"/>
       <c r="K44" s="5"/>
       <c r="L44" s="5" t="s">
-        <v>215</v>
+        <v>58</v>
       </c>
       <c r="M44" s="5"/>
       <c r="N44" s="5"/>
-      <c r="O44" s="41"/>
+      <c r="O44" s="45"/>
     </row>
     <row r="45" ht="25" customHeight="1" spans="1:15">
       <c r="A45" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="C45" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="B45" s="5"/>
-      <c r="C45" s="5"/>
-      <c r="D45" s="5"/>
-      <c r="E45" s="22"/>
+      <c r="D45" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E45" s="24" t="s">
+        <v>120</v>
+      </c>
       <c r="F45" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G45" s="5"/>
-      <c r="H45" s="5"/>
+      <c r="G45" s="5">
+        <v>2026</v>
+      </c>
+      <c r="H45" s="5" t="s">
+        <v>217</v>
+      </c>
       <c r="I45" s="5" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="J45" s="5"/>
       <c r="K45" s="5"/>
-      <c r="L45" s="5"/>
+      <c r="L45" s="5" t="s">
+        <v>219</v>
+      </c>
       <c r="M45" s="5"/>
       <c r="N45" s="5"/>
-      <c r="O45" s="41"/>
+      <c r="O45" s="45"/>
     </row>
     <row r="46" ht="25" customHeight="1" spans="1:15">
       <c r="A46" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5"/>
       <c r="D46" s="5"/>
-      <c r="E46" s="22"/>
+      <c r="E46" s="24"/>
       <c r="F46" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G46" s="5"/>
       <c r="H46" s="5"/>
       <c r="I46" s="5" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="J46" s="5"/>
       <c r="K46" s="5"/>
       <c r="L46" s="5"/>
       <c r="M46" s="5"/>
       <c r="N46" s="5"/>
-      <c r="O46" s="41"/>
+      <c r="O46" s="45"/>
     </row>
     <row r="47" ht="25" customHeight="1" spans="1:15">
       <c r="A47" s="12" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
       <c r="D47" s="5"/>
-      <c r="E47" s="22"/>
+      <c r="E47" s="24"/>
       <c r="F47" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G47" s="5"/>
       <c r="H47" s="5"/>
       <c r="I47" s="5" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="J47" s="5"/>
       <c r="K47" s="5"/>
       <c r="L47" s="5"/>
       <c r="M47" s="5"/>
       <c r="N47" s="5"/>
-      <c r="O47" s="41"/>
+      <c r="O47" s="45"/>
     </row>
     <row r="48" ht="25" customHeight="1" spans="1:15">
       <c r="A48" s="12" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
       <c r="D48" s="5"/>
-      <c r="E48" s="22"/>
+      <c r="E48" s="24"/>
       <c r="F48" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G48" s="5"/>
       <c r="H48" s="5"/>
       <c r="I48" s="5" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="J48" s="5"/>
       <c r="K48" s="5"/>
       <c r="L48" s="5"/>
       <c r="M48" s="5"/>
       <c r="N48" s="5"/>
-      <c r="O48" s="41"/>
+      <c r="O48" s="45"/>
     </row>
     <row r="49" ht="25" customHeight="1" spans="1:15">
-      <c r="A49" s="14" t="s">
-        <v>224</v>
-      </c>
-      <c r="B49" s="15"/>
-      <c r="C49" s="15"/>
-      <c r="D49" s="15"/>
-      <c r="E49" s="42"/>
+      <c r="A49" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="B49" s="5"/>
+      <c r="C49" s="5"/>
+      <c r="D49" s="5"/>
+      <c r="E49" s="24"/>
       <c r="F49" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G49" s="15"/>
-      <c r="H49" s="15"/>
-      <c r="I49" s="16" t="s">
-        <v>225</v>
-      </c>
-      <c r="J49" s="15"/>
+      <c r="G49" s="5"/>
+      <c r="H49" s="5"/>
+      <c r="I49" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="J49" s="5"/>
       <c r="K49" s="5"/>
       <c r="L49" s="5"/>
       <c r="M49" s="5"/>
       <c r="N49" s="5"/>
-      <c r="O49" s="41"/>
+      <c r="O49" s="45"/>
     </row>
     <row r="50" ht="25" customHeight="1" spans="1:15">
-      <c r="A50" s="12" t="s">
-        <v>226</v>
-      </c>
-      <c r="B50" s="5"/>
-      <c r="C50" s="5"/>
-      <c r="D50" s="5"/>
-      <c r="E50" s="22"/>
+      <c r="A50" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="B50" s="15"/>
+      <c r="C50" s="15"/>
+      <c r="D50" s="15"/>
+      <c r="E50" s="46"/>
       <c r="F50" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G50" s="5"/>
-      <c r="H50" s="5"/>
-      <c r="I50" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="J50" s="5"/>
+      <c r="G50" s="15"/>
+      <c r="H50" s="15"/>
+      <c r="I50" s="16" t="s">
+        <v>229</v>
+      </c>
+      <c r="J50" s="15"/>
       <c r="K50" s="5"/>
       <c r="L50" s="5"/>
       <c r="M50" s="5"/>
       <c r="N50" s="5"/>
-      <c r="O50" s="41"/>
+      <c r="O50" s="45"/>
     </row>
     <row r="51" ht="25" customHeight="1" spans="1:15">
       <c r="A51" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
       <c r="D51" s="5"/>
-      <c r="E51" s="22"/>
+      <c r="E51" s="24"/>
       <c r="F51" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G51" s="5"/>
       <c r="H51" s="5"/>
       <c r="I51" s="5" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="J51" s="5"/>
       <c r="K51" s="5"/>
       <c r="L51" s="5"/>
       <c r="M51" s="5"/>
       <c r="N51" s="5"/>
-      <c r="O51" s="41"/>
+      <c r="O51" s="45"/>
     </row>
     <row r="52" ht="25" customHeight="1" spans="1:15">
       <c r="A52" s="12" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5"/>
       <c r="D52" s="5"/>
-      <c r="E52" s="22"/>
+      <c r="E52" s="24"/>
       <c r="F52" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G52" s="5"/>
       <c r="H52" s="5"/>
       <c r="I52" s="5" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="J52" s="5"/>
       <c r="K52" s="5"/>
       <c r="L52" s="5"/>
       <c r="M52" s="5"/>
       <c r="N52" s="5"/>
-      <c r="O52" s="41"/>
+      <c r="O52" s="45"/>
     </row>
     <row r="53" ht="25" customHeight="1" spans="1:15">
       <c r="A53" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5"/>
       <c r="D53" s="5"/>
-      <c r="E53" s="22"/>
+      <c r="E53" s="24"/>
       <c r="F53" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G53" s="5"/>
+      <c r="H53" s="5"/>
       <c r="I53" s="5" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="J53" s="5"/>
       <c r="K53" s="5"/>
       <c r="L53" s="5"/>
       <c r="M53" s="5"/>
       <c r="N53" s="5"/>
-      <c r="O53" s="41"/>
+      <c r="O53" s="45"/>
     </row>
     <row r="54" ht="25" customHeight="1" spans="1:15">
       <c r="A54" s="12" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
       <c r="D54" s="5"/>
-      <c r="E54" s="22"/>
+      <c r="E54" s="24"/>
       <c r="F54" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G54" s="5"/>
-      <c r="H54" s="5"/>
       <c r="I54" s="5" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="J54" s="5"/>
       <c r="K54" s="5"/>
       <c r="L54" s="5"/>
       <c r="M54" s="5"/>
       <c r="N54" s="5"/>
-      <c r="O54" s="41"/>
+      <c r="O54" s="45"/>
     </row>
     <row r="55" ht="25" customHeight="1" spans="1:15">
       <c r="A55" s="12" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B55" s="5"/>
       <c r="C55" s="5"/>
       <c r="D55" s="5"/>
-      <c r="E55" s="22"/>
+      <c r="E55" s="24"/>
       <c r="F55" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G55" s="5"/>
       <c r="H55" s="5"/>
       <c r="I55" s="5" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J55" s="5"/>
       <c r="K55" s="5"/>
       <c r="L55" s="5"/>
       <c r="M55" s="5"/>
       <c r="N55" s="5"/>
-      <c r="O55" s="41"/>
+      <c r="O55" s="45"/>
     </row>
     <row r="56" ht="25" customHeight="1" spans="1:15">
       <c r="A56" s="12" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
       <c r="D56" s="5"/>
-      <c r="E56" s="22"/>
+      <c r="E56" s="24"/>
       <c r="F56" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G56" s="5"/>
       <c r="H56" s="5"/>
       <c r="I56" s="5" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J56" s="5"/>
       <c r="K56" s="5"/>
       <c r="L56" s="5"/>
       <c r="M56" s="5"/>
       <c r="N56" s="5"/>
-      <c r="O56" s="41"/>
+      <c r="O56" s="45"/>
     </row>
     <row r="57" ht="25" customHeight="1" spans="1:15">
       <c r="A57" s="12" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
       <c r="D57" s="5"/>
-      <c r="E57" s="22"/>
+      <c r="E57" s="24"/>
       <c r="F57" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G57" s="5"/>
+      <c r="H57" s="5"/>
       <c r="I57" s="5" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="J57" s="5"/>
       <c r="K57" s="5"/>
       <c r="L57" s="5"/>
       <c r="M57" s="5"/>
       <c r="N57" s="5"/>
-      <c r="O57" s="41"/>
+      <c r="O57" s="45"/>
     </row>
     <row r="58" ht="25" customHeight="1" spans="1:15">
       <c r="A58" s="12" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
       <c r="D58" s="5"/>
-      <c r="E58" s="22"/>
+      <c r="E58" s="24"/>
       <c r="F58" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G58" s="5"/>
-      <c r="H58" s="5"/>
       <c r="I58" s="5" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="J58" s="5"/>
       <c r="K58" s="5"/>
       <c r="L58" s="5"/>
       <c r="M58" s="5"/>
       <c r="N58" s="5"/>
-      <c r="O58" s="41"/>
-    </row>
-    <row r="59" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="O58" s="45"/>
+    </row>
+    <row r="59" ht="25" customHeight="1" spans="1:15">
       <c r="A59" s="12" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
       <c r="D59" s="5"/>
-      <c r="E59" s="22"/>
+      <c r="E59" s="24"/>
       <c r="F59" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G59" s="5"/>
       <c r="H59" s="5"/>
       <c r="I59" s="5" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="J59" s="5"/>
       <c r="K59" s="5"/>
       <c r="L59" s="5"/>
       <c r="M59" s="5"/>
       <c r="N59" s="5"/>
-      <c r="O59" s="41"/>
+      <c r="O59" s="45"/>
     </row>
     <row r="60" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A60" s="12" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
       <c r="D60" s="5"/>
-      <c r="E60" s="22"/>
+      <c r="E60" s="24"/>
       <c r="F60" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G60" s="5"/>
       <c r="H60" s="5"/>
       <c r="I60" s="5" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="J60" s="5"/>
       <c r="K60" s="5"/>
       <c r="L60" s="5"/>
       <c r="M60" s="5"/>
       <c r="N60" s="5"/>
-      <c r="O60" s="41"/>
+      <c r="O60" s="45"/>
     </row>
     <row r="61" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A61" s="12" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
       <c r="D61" s="5"/>
-      <c r="E61" s="22"/>
+      <c r="E61" s="24"/>
       <c r="F61" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G61" s="5"/>
       <c r="H61" s="5"/>
       <c r="I61" s="5" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="J61" s="5"/>
       <c r="K61" s="5"/>
       <c r="L61" s="5"/>
       <c r="M61" s="5"/>
       <c r="N61" s="5"/>
-      <c r="O61" s="41"/>
+      <c r="O61" s="45"/>
     </row>
     <row r="62" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A62" s="12" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B62" s="5"/>
       <c r="C62" s="5"/>
       <c r="D62" s="5"/>
-      <c r="E62" s="22"/>
+      <c r="E62" s="24"/>
       <c r="F62" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G62" s="5"/>
       <c r="H62" s="5"/>
       <c r="I62" s="5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="J62" s="5"/>
       <c r="K62" s="5"/>
       <c r="L62" s="5"/>
       <c r="M62" s="5"/>
       <c r="N62" s="5"/>
-      <c r="O62" s="41"/>
+      <c r="O62" s="45"/>
     </row>
     <row r="63" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A63" s="12" t="s">
-        <v>252</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C63" s="17" t="s">
-        <v>253</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="B63" s="5"/>
+      <c r="C63" s="5"/>
       <c r="D63" s="5"/>
-      <c r="E63" s="22" t="s">
-        <v>254</v>
-      </c>
+      <c r="E63" s="24"/>
       <c r="F63" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G63" s="5"/>
-      <c r="H63" s="18" t="s">
+      <c r="H63" s="5"/>
+      <c r="I63" s="5" t="s">
         <v>255</v>
-      </c>
-      <c r="I63" s="5" t="s">
-        <v>256</v>
       </c>
       <c r="J63" s="5"/>
       <c r="K63" s="5"/>
       <c r="L63" s="5"/>
       <c r="M63" s="5"/>
       <c r="N63" s="5"/>
-      <c r="O63" s="41"/>
+      <c r="O63" s="45"/>
     </row>
     <row r="64" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A64" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C64" s="17" t="s">
         <v>257</v>
       </c>
-      <c r="B64" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C64" s="17" t="s">
+      <c r="D64" s="5"/>
+      <c r="E64" s="24" t="s">
         <v>258</v>
-      </c>
-      <c r="D64" s="5"/>
-      <c r="E64" s="22" t="s">
-        <v>116</v>
       </c>
       <c r="F64" s="5" t="s">
         <v>33</v>
@@ -4992,21 +5062,21 @@
       <c r="L64" s="5"/>
       <c r="M64" s="5"/>
       <c r="N64" s="5"/>
-      <c r="O64" s="5"/>
+      <c r="O64" s="45"/>
     </row>
     <row r="65" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A65" s="12" t="s">
         <v>261</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C65" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="C65" s="17" t="s">
         <v>262</v>
       </c>
       <c r="D65" s="5"/>
-      <c r="E65" s="22" t="s">
-        <v>122</v>
+      <c r="E65" s="24" t="s">
+        <v>120</v>
       </c>
       <c r="F65" s="5" t="s">
         <v>33</v>
@@ -5023,52 +5093,52 @@
       <c r="L65" s="5"/>
       <c r="M65" s="5"/>
       <c r="N65" s="5"/>
-      <c r="O65" s="41"/>
-    </row>
-    <row r="66" ht="25" customHeight="1" spans="1:15">
+      <c r="O65" s="5"/>
+    </row>
+    <row r="66" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A66" s="12" t="s">
         <v>265</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C66" s="17" t="s">
+      <c r="C66" s="19" t="s">
         <v>266</v>
       </c>
       <c r="D66" s="5"/>
-      <c r="E66" s="22" t="s">
-        <v>267</v>
+      <c r="E66" s="24" t="s">
+        <v>126</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G66" s="5"/>
       <c r="H66" s="18" t="s">
+        <v>267</v>
+      </c>
+      <c r="I66" s="5" t="s">
         <v>268</v>
-      </c>
-      <c r="I66" s="5" t="s">
-        <v>269</v>
       </c>
       <c r="J66" s="5"/>
       <c r="K66" s="5"/>
       <c r="L66" s="5"/>
       <c r="M66" s="5"/>
       <c r="N66" s="5"/>
-      <c r="O66" s="41"/>
+      <c r="O66" s="45"/>
     </row>
     <row r="67" ht="25" customHeight="1" spans="1:15">
       <c r="A67" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C67" s="17" t="s">
+        <v>270</v>
+      </c>
+      <c r="D67" s="5"/>
+      <c r="E67" s="24" t="s">
         <v>271</v>
-      </c>
-      <c r="D67" s="5"/>
-      <c r="E67" s="22" t="s">
-        <v>267</v>
       </c>
       <c r="F67" s="5" t="s">
         <v>33</v>
@@ -5085,84 +5155,98 @@
       <c r="L67" s="5"/>
       <c r="M67" s="5"/>
       <c r="N67" s="5"/>
-      <c r="O67" s="41"/>
+      <c r="O67" s="45"/>
     </row>
     <row r="68" ht="25" customHeight="1" spans="1:15">
       <c r="A68" s="12" t="s">
         <v>274</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
       <c r="C68" s="17" t="s">
         <v>275</v>
       </c>
       <c r="D68" s="5"/>
-      <c r="E68" s="22" t="s">
-        <v>276</v>
+      <c r="E68" s="24" t="s">
+        <v>271</v>
       </c>
       <c r="F68" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G68" s="5"/>
       <c r="H68" s="18" t="s">
+        <v>276</v>
+      </c>
+      <c r="I68" s="5" t="s">
         <v>277</v>
-      </c>
-      <c r="I68" s="5" t="s">
-        <v>278</v>
       </c>
       <c r="J68" s="5"/>
       <c r="K68" s="5"/>
       <c r="L68" s="5"/>
       <c r="M68" s="5"/>
       <c r="N68" s="5"/>
-      <c r="O68" s="41"/>
+      <c r="O68" s="45"/>
     </row>
     <row r="69" ht="25" customHeight="1" spans="1:15">
       <c r="A69" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C69" s="17" t="s">
         <v>279</v>
       </c>
-      <c r="B69" s="5" t="s">
+      <c r="D69" s="5"/>
+      <c r="E69" s="24" t="s">
         <v>280</v>
       </c>
-      <c r="C69" s="43" t="s">
+      <c r="F69" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G69" s="5"/>
+      <c r="H69" s="18" t="s">
         <v>281</v>
       </c>
-      <c r="D69" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="E69" s="44">
-        <v>16</v>
-      </c>
-      <c r="F69" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="G69" s="24">
-        <v>2026</v>
-      </c>
-      <c r="H69" s="5" t="s">
+      <c r="I69" s="5" t="s">
         <v>282</v>
-      </c>
-      <c r="I69" s="5" t="s">
-        <v>283</v>
       </c>
       <c r="J69" s="5"/>
       <c r="K69" s="5"/>
       <c r="L69" s="5"/>
       <c r="M69" s="5"/>
       <c r="N69" s="5"/>
-      <c r="O69" s="5"/>
+      <c r="O69" s="45"/>
     </row>
     <row r="70" ht="25" customHeight="1" spans="1:15">
-      <c r="A70" s="12"/>
-      <c r="B70" s="5"/>
-      <c r="C70" s="5"/>
-      <c r="D70" s="5"/>
-      <c r="E70" s="22"/>
-      <c r="F70" s="13"/>
-      <c r="G70" s="5"/>
-      <c r="H70" s="5"/>
-      <c r="I70" s="5"/>
+      <c r="A70" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="C70" s="47" t="s">
+        <v>285</v>
+      </c>
+      <c r="D70" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="E70" s="33">
+        <v>16</v>
+      </c>
+      <c r="F70" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G70" s="26">
+        <v>2026</v>
+      </c>
+      <c r="H70" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="I70" s="5" t="s">
+        <v>287</v>
+      </c>
       <c r="J70" s="5"/>
       <c r="K70" s="5"/>
       <c r="L70" s="5"/>
@@ -5175,9 +5259,10 @@
       <c r="B71" s="5"/>
       <c r="C71" s="5"/>
       <c r="D71" s="5"/>
-      <c r="E71" s="22"/>
+      <c r="E71" s="24"/>
       <c r="F71" s="13"/>
       <c r="G71" s="5"/>
+      <c r="H71" s="5"/>
       <c r="I71" s="5"/>
       <c r="J71" s="5"/>
       <c r="K71" s="5"/>
@@ -5191,10 +5276,9 @@
       <c r="B72" s="5"/>
       <c r="C72" s="5"/>
       <c r="D72" s="5"/>
-      <c r="E72" s="22"/>
+      <c r="E72" s="24"/>
       <c r="F72" s="13"/>
       <c r="G72" s="5"/>
-      <c r="H72" s="5"/>
       <c r="I72" s="5"/>
       <c r="J72" s="5"/>
       <c r="K72" s="5"/>
@@ -5208,7 +5292,7 @@
       <c r="B73" s="5"/>
       <c r="C73" s="5"/>
       <c r="D73" s="5"/>
-      <c r="E73" s="22"/>
+      <c r="E73" s="24"/>
       <c r="F73" s="13"/>
       <c r="G73" s="5"/>
       <c r="H73" s="5"/>
@@ -5225,9 +5309,10 @@
       <c r="B74" s="5"/>
       <c r="C74" s="5"/>
       <c r="D74" s="5"/>
-      <c r="E74" s="22"/>
+      <c r="E74" s="24"/>
       <c r="F74" s="13"/>
       <c r="G74" s="5"/>
+      <c r="H74" s="5"/>
       <c r="I74" s="5"/>
       <c r="J74" s="5"/>
       <c r="K74" s="5"/>
@@ -5241,10 +5326,9 @@
       <c r="B75" s="5"/>
       <c r="C75" s="5"/>
       <c r="D75" s="5"/>
-      <c r="E75" s="22"/>
+      <c r="E75" s="24"/>
       <c r="F75" s="13"/>
       <c r="G75" s="5"/>
-      <c r="H75" s="5"/>
       <c r="I75" s="5"/>
       <c r="J75" s="5"/>
       <c r="K75" s="5"/>
@@ -5258,7 +5342,7 @@
       <c r="B76" s="5"/>
       <c r="C76" s="5"/>
       <c r="D76" s="5"/>
-      <c r="E76" s="22"/>
+      <c r="E76" s="24"/>
       <c r="F76" s="13"/>
       <c r="G76" s="5"/>
       <c r="H76" s="5"/>
@@ -5275,7 +5359,7 @@
       <c r="B77" s="5"/>
       <c r="C77" s="5"/>
       <c r="D77" s="5"/>
-      <c r="E77" s="22"/>
+      <c r="E77" s="24"/>
       <c r="F77" s="13"/>
       <c r="G77" s="5"/>
       <c r="H77" s="5"/>
@@ -5292,9 +5376,10 @@
       <c r="B78" s="5"/>
       <c r="C78" s="5"/>
       <c r="D78" s="5"/>
-      <c r="E78" s="22"/>
+      <c r="E78" s="24"/>
       <c r="F78" s="13"/>
       <c r="G78" s="5"/>
+      <c r="H78" s="5"/>
       <c r="I78" s="5"/>
       <c r="J78" s="5"/>
       <c r="K78" s="5"/>
@@ -5308,10 +5393,9 @@
       <c r="B79" s="5"/>
       <c r="C79" s="5"/>
       <c r="D79" s="5"/>
-      <c r="E79" s="22"/>
+      <c r="E79" s="24"/>
       <c r="F79" s="13"/>
       <c r="G79" s="5"/>
-      <c r="H79" s="5"/>
       <c r="I79" s="5"/>
       <c r="J79" s="5"/>
       <c r="K79" s="5"/>
@@ -5325,7 +5409,7 @@
       <c r="B80" s="5"/>
       <c r="C80" s="5"/>
       <c r="D80" s="5"/>
-      <c r="E80" s="22"/>
+      <c r="E80" s="24"/>
       <c r="F80" s="13"/>
       <c r="G80" s="5"/>
       <c r="H80" s="5"/>
@@ -5342,7 +5426,7 @@
       <c r="B81" s="5"/>
       <c r="C81" s="5"/>
       <c r="D81" s="5"/>
-      <c r="E81" s="22"/>
+      <c r="E81" s="24"/>
       <c r="F81" s="13"/>
       <c r="G81" s="5"/>
       <c r="H81" s="5"/>
@@ -5359,7 +5443,7 @@
       <c r="B82" s="5"/>
       <c r="C82" s="5"/>
       <c r="D82" s="5"/>
-      <c r="E82" s="22"/>
+      <c r="E82" s="24"/>
       <c r="F82" s="13"/>
       <c r="G82" s="5"/>
       <c r="H82" s="5"/>
@@ -5376,7 +5460,7 @@
       <c r="B83" s="5"/>
       <c r="C83" s="5"/>
       <c r="D83" s="5"/>
-      <c r="E83" s="22"/>
+      <c r="E83" s="24"/>
       <c r="F83" s="13"/>
       <c r="G83" s="5"/>
       <c r="H83" s="5"/>
@@ -5393,7 +5477,7 @@
       <c r="B84" s="5"/>
       <c r="C84" s="5"/>
       <c r="D84" s="5"/>
-      <c r="E84" s="22"/>
+      <c r="E84" s="24"/>
       <c r="F84" s="13"/>
       <c r="G84" s="5"/>
       <c r="H84" s="5"/>
@@ -5405,16 +5489,33 @@
       <c r="N84" s="5"/>
       <c r="O84" s="5"/>
     </row>
+    <row r="85" ht="25" customHeight="1" spans="1:15">
+      <c r="A85" s="12"/>
+      <c r="B85" s="5"/>
+      <c r="C85" s="5"/>
+      <c r="D85" s="5"/>
+      <c r="E85" s="24"/>
+      <c r="F85" s="13"/>
+      <c r="G85" s="5"/>
+      <c r="H85" s="5"/>
+      <c r="I85" s="5"/>
+      <c r="J85" s="5"/>
+      <c r="K85" s="5"/>
+      <c r="L85" s="5"/>
+      <c r="M85" s="5"/>
+      <c r="N85" s="5"/>
+      <c r="O85" s="5"/>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:O69" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A1:O69">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:O70" etc:filterBottomFollowUsedRange="0">
+    <sortState ref="A1:O70">
       <sortCondition ref="F1"/>
     </sortState>
     <extLst/>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="H64" r:id="rId1" display="普洛伊湘普·素帕莎 / 芭莉雅皮·余 " tooltip="https://www.douban.com/personage/30264980/"/>
-    <hyperlink ref="H19" r:id="rId2" display="金贤叙/郑明哲" tooltip="https://www.douban.com/personage/37338980/"/>
+    <hyperlink ref="H65" r:id="rId1" display="普洛伊湘普·素帕莎 / 芭莉雅皮·余 " tooltip="https://www.douban.com/personage/30264980/"/>
+    <hyperlink ref="H20" r:id="rId2" display="金贤叙/郑明哲" tooltip="https://www.douban.com/personage/37338980/"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -5438,7 +5539,7 @@
   <sheetData>
     <row r="1" ht="33" customHeight="1" spans="1:9">
       <c r="A1" s="3" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -5485,7 +5586,7 @@
         <v>12</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>14</v>
@@ -5682,13 +5783,13 @@
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:9">
       <c r="A10" s="6" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>58</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>14</v>
@@ -5703,21 +5804,21 @@
         <v>2026</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:9">
       <c r="A11" s="6" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>14</v>
@@ -5732,21 +5833,21 @@
         <v>2026</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:9">
       <c r="A12" s="6" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>58</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>14</v>
@@ -5761,21 +5862,21 @@
         <v>2026</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:9">
       <c r="A13" s="6" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>58</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>14</v>
@@ -5790,21 +5891,21 @@
         <v>2026</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:9">
       <c r="A14" s="6" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>58</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>14</v>
@@ -5819,21 +5920,21 @@
         <v>2026</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:9">
       <c r="A15" s="6" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>58</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>14</v>
@@ -5848,21 +5949,21 @@
         <v>2026</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:9">
       <c r="A16" s="6" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>58</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>14</v>
@@ -5877,21 +5978,21 @@
         <v>2026</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:9">
       <c r="A17" s="6" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>49</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>14</v>
@@ -5907,18 +6008,18 @@
       </c>
       <c r="H17" s="7"/>
       <c r="I17" s="8" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:9">
       <c r="A18" s="6" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>49</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>14</v>
@@ -5934,18 +6035,18 @@
       </c>
       <c r="H18" s="7"/>
       <c r="I18" s="8" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" spans="1:9">
       <c r="A19" s="9" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>49</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>14</v>
@@ -5959,18 +6060,18 @@
       </c>
       <c r="H19" s="7"/>
       <c r="I19" s="11" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" spans="1:9">
       <c r="A20" s="9" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>49</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>14</v>
@@ -5984,24 +6085,24 @@
       </c>
       <c r="H20" s="7"/>
       <c r="I20" s="11" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1" spans="1:9">
       <c r="A21" s="12" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>33</v>
@@ -6010,27 +6111,27 @@
         <v>2026</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1" spans="1:9">
       <c r="A22" s="12" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>33</v>
@@ -6039,27 +6140,27 @@
         <v>2025</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1" spans="1:9">
       <c r="A23" s="12" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>33</v>
@@ -6068,27 +6169,27 @@
         <v>2026</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1" spans="1:9">
       <c r="A24" s="12" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>33</v>
@@ -6097,27 +6198,27 @@
         <v>2026</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1" spans="1:9">
       <c r="A25" s="12" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="F25" s="5" t="s">
         <v>33</v>
@@ -6126,27 +6227,27 @@
         <v>2025</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1" spans="1:9">
       <c r="A26" s="12" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="F26" s="5" t="s">
         <v>33</v>
@@ -6155,27 +6256,27 @@
         <v>2026</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1" spans="1:9">
       <c r="A27" s="12" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="F27" s="5" t="s">
         <v>33</v>
@@ -6184,27 +6285,27 @@
         <v>2026</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1" spans="1:9">
       <c r="A28" s="12" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="F28" s="5" t="s">
         <v>33</v>
@@ -6213,27 +6314,27 @@
         <v>2024</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="29" ht="25" customHeight="1" spans="1:9">
       <c r="A29" s="12" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="F29" s="5" t="s">
         <v>33</v>
@@ -6242,27 +6343,27 @@
         <v>2024</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
     </row>
     <row r="30" ht="25" customHeight="1" spans="1:9">
       <c r="A30" s="12" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F30" s="5" t="s">
         <v>33</v>
@@ -6271,27 +6372,27 @@
         <v>2026</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="31" ht="25" customHeight="1" spans="1:9">
       <c r="A31" s="12" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="F31" s="5" t="s">
         <v>33</v>
@@ -6300,27 +6401,27 @@
         <v>2025</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
     </row>
     <row r="32" ht="25" customHeight="1" spans="1:9">
       <c r="A32" s="12" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="F32" s="5" t="s">
         <v>33</v>
@@ -6329,27 +6430,27 @@
         <v>2026</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
     </row>
     <row r="33" ht="25" customHeight="1" spans="1:9">
       <c r="A33" s="12" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="F33" s="5" t="s">
         <v>33</v>
@@ -6358,27 +6459,27 @@
         <v>2026</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="I33" s="5" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" ht="25" customHeight="1" spans="1:9">
       <c r="A34" s="12" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F34" s="5" t="s">
         <v>33</v>
@@ -6387,27 +6488,27 @@
         <v>2026</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
     </row>
     <row r="35" ht="25" customHeight="1" spans="1:9">
       <c r="A35" s="12" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="F35" s="5" t="s">
         <v>33</v>
@@ -6416,27 +6517,27 @@
         <v>2025</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
     </row>
     <row r="36" ht="25" customHeight="1" spans="1:9">
       <c r="A36" s="12" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="F36" s="5" t="s">
         <v>33</v>
@@ -6445,27 +6546,27 @@
         <v>2026</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
     </row>
     <row r="37" ht="25" customHeight="1" spans="1:9">
       <c r="A37" s="12" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="F37" s="5" t="s">
         <v>33</v>
@@ -6474,27 +6575,27 @@
         <v>2026</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="I37" s="5" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="38" ht="25" customHeight="1" spans="1:9">
       <c r="A38" s="12" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="F38" s="5" t="s">
         <v>33</v>
@@ -6504,24 +6605,24 @@
       </c>
       <c r="H38" s="5"/>
       <c r="I38" s="5" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
     </row>
     <row r="39" ht="25" customHeight="1" spans="1:9">
       <c r="A39" s="12" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="F39" s="5" t="s">
         <v>33</v>
@@ -6530,27 +6631,27 @@
         <v>2025</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="I39" s="5" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
     </row>
     <row r="40" ht="25" customHeight="1" spans="1:9">
       <c r="A40" s="12" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="D40" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="F40" s="5" t="s">
         <v>33</v>
@@ -6560,24 +6661,24 @@
       </c>
       <c r="H40" s="5"/>
       <c r="I40" s="5" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
     </row>
     <row r="41" ht="25" customHeight="1" spans="1:9">
       <c r="A41" s="12" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="F41" s="5" t="s">
         <v>33</v>
@@ -6586,15 +6687,15 @@
         <v>2026</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="I41" s="5" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
     </row>
     <row r="42" ht="25" customHeight="1" spans="1:9">
       <c r="A42" s="12" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5"/>
@@ -6606,12 +6707,12 @@
       <c r="G42" s="5"/>
       <c r="H42" s="5"/>
       <c r="I42" s="5" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
     </row>
     <row r="43" ht="25" customHeight="1" spans="1:9">
       <c r="A43" s="12" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5"/>
@@ -6623,12 +6724,12 @@
       <c r="G43" s="5"/>
       <c r="H43" s="5"/>
       <c r="I43" s="5" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
     </row>
     <row r="44" ht="25" customHeight="1" spans="1:9">
       <c r="A44" s="12" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
@@ -6640,12 +6741,12 @@
       <c r="G44" s="5"/>
       <c r="H44" s="5"/>
       <c r="I44" s="5" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
     </row>
     <row r="45" ht="25" customHeight="1" spans="1:9">
       <c r="A45" s="12" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5"/>
@@ -6657,12 +6758,12 @@
       <c r="G45" s="5"/>
       <c r="H45" s="5"/>
       <c r="I45" s="5" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="46" ht="25" customHeight="1" spans="1:9">
       <c r="A46" s="14" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B46" s="15"/>
       <c r="C46" s="15"/>
@@ -6674,12 +6775,12 @@
       <c r="G46" s="15"/>
       <c r="H46" s="15"/>
       <c r="I46" s="16" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
     </row>
     <row r="47" ht="25" customHeight="1" spans="1:9">
       <c r="A47" s="12" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
@@ -6691,12 +6792,12 @@
       <c r="G47" s="5"/>
       <c r="H47" s="5"/>
       <c r="I47" s="5" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="48" ht="25" customHeight="1" spans="1:9">
       <c r="A48" s="12" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
@@ -6708,12 +6809,12 @@
       <c r="G48" s="5"/>
       <c r="H48" s="5"/>
       <c r="I48" s="5" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
     </row>
     <row r="49" ht="25" customHeight="1" spans="1:9">
       <c r="A49" s="12" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
@@ -6725,12 +6826,12 @@
       <c r="G49" s="5"/>
       <c r="H49" s="5"/>
       <c r="I49" s="5" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
     </row>
     <row r="50" ht="25" customHeight="1" spans="1:9">
       <c r="A50" s="12" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5"/>
@@ -6742,12 +6843,12 @@
       <c r="G50" s="5"/>
       <c r="H50" s="5"/>
       <c r="I50" s="5" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="51" ht="25" customHeight="1" spans="1:9">
       <c r="A51" s="12" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
@@ -6759,12 +6860,12 @@
       <c r="G51" s="5"/>
       <c r="H51" s="5"/>
       <c r="I51" s="5" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
     </row>
     <row r="52" ht="25" customHeight="1" spans="1:9">
       <c r="A52" s="12" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5"/>
@@ -6776,162 +6877,162 @@
       <c r="G52" s="5"/>
       <c r="H52" s="5"/>
       <c r="I52" s="5" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
     </row>
     <row r="53" customFormat="1" ht="25" customHeight="1" spans="1:9">
       <c r="A53" s="12" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C53" s="17" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="D53" s="5"/>
       <c r="E53" s="5" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="F53" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G53" s="5"/>
       <c r="H53" s="18" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="I53" s="5" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
     </row>
     <row r="54" customFormat="1" ht="25" customHeight="1" spans="1:9">
       <c r="A54" s="12" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="C54" s="17" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D54" s="5"/>
       <c r="E54" s="5" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="F54" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G54" s="5"/>
       <c r="H54" s="18" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I54" s="5" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
     </row>
     <row r="55" customFormat="1" ht="25" customHeight="1" spans="1:9">
       <c r="A55" s="12" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C55" s="19" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D55" s="5"/>
       <c r="E55" s="5" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F55" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G55" s="5"/>
       <c r="H55" s="18" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="I55" s="5" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="56" ht="25" customHeight="1" spans="1:9">
       <c r="A56" s="12" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C56" s="17" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D56" s="5"/>
       <c r="E56" s="5" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="F56" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G56" s="5"/>
       <c r="H56" s="18" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="I56" s="5" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="57" ht="25" customHeight="1" spans="1:9">
       <c r="A57" s="12" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C57" s="17" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="D57" s="5"/>
       <c r="E57" s="5" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="F57" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G57" s="5"/>
       <c r="H57" s="18" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="I57" s="5" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="58" ht="25" customHeight="1" spans="1:9">
       <c r="A58" s="12" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>58</v>
       </c>
       <c r="C58" s="17" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="D58" s="5"/>
       <c r="E58" s="5" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="F58" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G58" s="5"/>
       <c r="H58" s="18" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="I58" s="5" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="59" ht="25" customHeight="1" spans="1:9">
       <c r="A59" s="12" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
@@ -6943,12 +7044,12 @@
       <c r="G59" s="5"/>
       <c r="H59" s="5"/>
       <c r="I59" s="5" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
     </row>
     <row r="60" ht="25" customHeight="1" spans="1:9">
       <c r="A60" s="12" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
@@ -6960,12 +7061,12 @@
       <c r="G60" s="5"/>
       <c r="H60" s="5"/>
       <c r="I60" s="5" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
     </row>
     <row r="61" ht="25" customHeight="1" spans="1:9">
       <c r="A61" s="12" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
@@ -6977,12 +7078,12 @@
       <c r="G61" s="5"/>
       <c r="H61" s="5"/>
       <c r="I61" s="5" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
     </row>
     <row r="62" customFormat="1" ht="25" customHeight="1" spans="1:9">
       <c r="A62" s="12" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B62" s="5"/>
       <c r="C62" s="5"/>
@@ -6994,12 +7095,12 @@
       <c r="G62" s="5"/>
       <c r="H62" s="5"/>
       <c r="I62" s="5" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
     </row>
     <row r="63" customFormat="1" ht="25" customHeight="1" spans="1:9">
       <c r="A63" s="12" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B63" s="5"/>
       <c r="C63" s="5"/>
@@ -7011,12 +7112,12 @@
       <c r="G63" s="5"/>
       <c r="H63" s="5"/>
       <c r="I63" s="5" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
     </row>
     <row r="64" customFormat="1" ht="25" customHeight="1" spans="1:9">
       <c r="A64" s="12" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B64" s="5"/>
       <c r="C64" s="5"/>
@@ -7028,12 +7129,12 @@
       <c r="G64" s="5"/>
       <c r="H64" s="5"/>
       <c r="I64" s="5" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
     </row>
     <row r="65" customFormat="1" ht="25" customHeight="1" spans="1:9">
       <c r="A65" s="12" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="B65" s="5"/>
       <c r="C65" s="5"/>
@@ -7045,7 +7146,7 @@
       <c r="G65" s="5"/>
       <c r="H65" s="5"/>
       <c r="I65" s="5" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
     </row>
     <row r="66" ht="25" customHeight="1" spans="1:9">

--- a/资源录入表新.xlsx
+++ b/资源录入表新.xlsx
@@ -207,6 +207,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF111111"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>剧情</t>
     </r>
     <r>
@@ -230,6 +236,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>: </t>
     </r>
     <r>
@@ -316,6 +329,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t> </t>
     </r>
     <r>
@@ -523,6 +543,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>喜剧</t>
     </r>
     <r>
@@ -544,6 +569,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="major"/>
+      </rPr>
       <t>姜勋</t>
     </r>
     <r>
@@ -1432,6 +1463,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF111111"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
       <t>剧情</t>
     </r>
     <r>
@@ -1783,13 +1820,9 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10.5"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <name val="宋体"/>
+      <sz val="11"/>
+      <color rgb="FF111111"/>
+      <name val="Helvetica"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1803,9 +1836,13 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF111111"/>
-      <name val="Helvetica"/>
+      <sz val="10.5"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -2306,7 +2343,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2370,82 +2407,61 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -2991,7 +3007,7 @@
     <col min="2" max="2" width="9" style="1"/>
     <col min="3" max="3" width="30.5833333333333" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
-    <col min="5" max="5" width="9" style="23"/>
+    <col min="5" max="5" width="9" style="22"/>
     <col min="6" max="7" width="9" style="1"/>
     <col min="8" max="8" width="80.2916666666667" style="1" customWidth="1"/>
     <col min="9" max="9" width="74.25" style="1" customWidth="1"/>
@@ -3014,7 +3030,7 @@
       <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="24" t="s">
+      <c r="E1" s="13" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="5" t="s">
@@ -3041,31 +3057,31 @@
       <c r="O1" s="5"/>
     </row>
     <row r="2" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="26" t="s">
+      <c r="B2" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="26" t="s">
+      <c r="C2" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="27">
-        <v>12</v>
-      </c>
-      <c r="F2" s="26" t="s">
+      <c r="D2" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="8">
+        <v>13</v>
+      </c>
+      <c r="F2" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="26">
+      <c r="G2" s="24">
         <v>2026</v>
       </c>
-      <c r="H2" s="26" t="s">
+      <c r="H2" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="26" t="s">
+      <c r="I2" s="24" t="s">
         <v>17</v>
       </c>
       <c r="J2" s="13"/>
@@ -3076,31 +3092,31 @@
       <c r="O2" s="13"/>
     </row>
     <row r="3" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="26" t="s">
+      <c r="C3" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="27">
-        <v>13</v>
-      </c>
-      <c r="F3" s="26" t="s">
+      <c r="D3" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="8">
         <v>15</v>
       </c>
-      <c r="G3" s="26">
+      <c r="F3" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="24">
         <v>2026</v>
       </c>
-      <c r="H3" s="26" t="s">
+      <c r="H3" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="26" t="s">
+      <c r="I3" s="24" t="s">
         <v>21</v>
       </c>
       <c r="J3" s="13"/>
@@ -3111,31 +3127,31 @@
       <c r="O3" s="13"/>
     </row>
     <row r="4" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="C4" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="27">
+      <c r="D4" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="24">
         <v>26</v>
       </c>
-      <c r="F4" s="26" t="s">
+      <c r="F4" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="26">
+      <c r="G4" s="24">
         <v>2026</v>
       </c>
-      <c r="H4" s="26" t="s">
+      <c r="H4" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="I4" s="26" t="s">
+      <c r="I4" s="24" t="s">
         <v>25</v>
       </c>
       <c r="J4" s="13"/>
@@ -3148,31 +3164,31 @@
       <c r="O4" s="13"/>
     </row>
     <row r="5" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A5" s="25" t="s">
+      <c r="A5" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="26" t="s">
+      <c r="C5" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="27">
+      <c r="D5" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="24">
         <v>26</v>
       </c>
-      <c r="F5" s="26" t="s">
+      <c r="F5" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="26">
+      <c r="G5" s="24">
         <v>2026</v>
       </c>
-      <c r="H5" s="26" t="s">
+      <c r="H5" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="I5" s="26" t="s">
+      <c r="I5" s="24" t="s">
         <v>30</v>
       </c>
       <c r="J5" s="13"/>
@@ -3183,31 +3199,31 @@
       <c r="O5" s="13"/>
     </row>
     <row r="6" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="27">
+      <c r="D6" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="24">
         <v>24</v>
       </c>
-      <c r="F6" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="G6" s="26">
+      <c r="F6" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" s="24">
         <v>2026</v>
       </c>
-      <c r="H6" s="26" t="s">
+      <c r="H6" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="I6" s="26" t="s">
+      <c r="I6" s="24" t="s">
         <v>35</v>
       </c>
       <c r="J6" s="13"/>
@@ -3224,13 +3240,13 @@
       <c r="B7" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="29" t="s">
+      <c r="C7" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="31">
+      <c r="D7" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="28">
         <v>15</v>
       </c>
       <c r="F7" s="13" t="s">
@@ -3252,102 +3268,102 @@
       <c r="N7" s="5"/>
       <c r="O7" s="5"/>
     </row>
-    <row r="8" s="21" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A8" s="32" t="s">
+    <row r="8" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A8" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="B8" s="33" t="s">
+      <c r="B8" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="34" t="s">
+      <c r="C8" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="D8" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="33">
+      <c r="D8" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="13">
         <v>8</v>
       </c>
-      <c r="F8" s="33" t="s">
+      <c r="F8" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="G8" s="33">
+      <c r="G8" s="13">
         <v>2026</v>
       </c>
-      <c r="H8" s="35" t="s">
+      <c r="H8" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="I8" s="33" t="s">
+      <c r="I8" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="J8" s="24"/>
-      <c r="K8" s="24"/>
-      <c r="L8" s="24"/>
-      <c r="M8" s="24"/>
-      <c r="N8" s="24"/>
-      <c r="O8" s="24"/>
-    </row>
-    <row r="9" s="21" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A9" s="32" t="s">
+      <c r="J8" s="13"/>
+      <c r="K8" s="13"/>
+      <c r="L8" s="13"/>
+      <c r="M8" s="13"/>
+      <c r="N8" s="13"/>
+      <c r="O8" s="13"/>
+    </row>
+    <row r="9" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A9" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="B9" s="33" t="s">
+      <c r="B9" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="34" t="s">
+      <c r="C9" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="D9" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" s="33">
+      <c r="D9" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="13">
         <v>8</v>
       </c>
-      <c r="F9" s="33" t="s">
+      <c r="F9" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="G9" s="33">
+      <c r="G9" s="13">
         <v>2026</v>
       </c>
-      <c r="H9" s="35" t="s">
+      <c r="H9" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="I9" s="33" t="s">
+      <c r="I9" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="J9" s="24"/>
-      <c r="K9" s="24"/>
-      <c r="L9" s="24"/>
-      <c r="M9" s="24"/>
-      <c r="N9" s="24"/>
-      <c r="O9" s="24"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="13"/>
+      <c r="L9" s="13"/>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13"/>
+      <c r="O9" s="13"/>
     </row>
     <row r="10" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A10" s="25" t="s">
+      <c r="A10" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="B10" s="26" t="s">
+      <c r="B10" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="C10" s="26" t="s">
+      <c r="C10" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="D10" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="36">
+      <c r="D10" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="24">
         <v>3</v>
       </c>
-      <c r="F10" s="26" t="s">
+      <c r="F10" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="G10" s="26">
+      <c r="G10" s="24">
         <v>2026</v>
       </c>
-      <c r="H10" s="26" t="s">
+      <c r="H10" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="I10" s="26" t="s">
+      <c r="I10" s="24" t="s">
         <v>52</v>
       </c>
       <c r="J10" s="13"/>
@@ -3358,31 +3374,31 @@
       <c r="O10" s="13"/>
     </row>
     <row r="11" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A11" s="25" t="s">
+      <c r="A11" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="B11" s="26" t="s">
+      <c r="B11" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="C11" s="26" t="s">
+      <c r="C11" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="D11" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="36">
+      <c r="D11" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="24">
         <v>4</v>
       </c>
-      <c r="F11" s="26" t="s">
+      <c r="F11" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="G11" s="26">
+      <c r="G11" s="24">
         <v>2026</v>
       </c>
-      <c r="H11" s="26" t="s">
+      <c r="H11" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="I11" s="26" t="s">
+      <c r="I11" s="24" t="s">
         <v>56</v>
       </c>
       <c r="J11" s="13"/>
@@ -3393,28 +3409,28 @@
       <c r="O11" s="13"/>
     </row>
     <row r="12" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A12" s="25" t="s">
+      <c r="A12" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="B12" s="26" t="s">
+      <c r="B12" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="C12" s="37" t="s">
+      <c r="C12" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="D12" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="E12" s="27">
+      <c r="D12" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="24">
         <v>2</v>
       </c>
-      <c r="F12" s="26" t="s">
+      <c r="F12" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="G12" s="26">
+      <c r="G12" s="24">
         <v>2026</v>
       </c>
-      <c r="H12" s="26" t="s">
+      <c r="H12" s="24" t="s">
         <v>60</v>
       </c>
       <c r="I12" s="13" t="s">
@@ -3427,67 +3443,67 @@
       <c r="N12" s="13"/>
       <c r="O12" s="13"/>
     </row>
-    <row r="13" s="22" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A13" s="38" t="s">
+    <row r="13" s="21" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A13" s="33" t="s">
         <v>62</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="34" t="s">
         <v>58</v>
       </c>
-      <c r="C13" s="39" t="s">
+      <c r="C13" s="35" t="s">
         <v>63</v>
       </c>
-      <c r="D13" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E13" s="8">
+      <c r="D13" s="34" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="34">
         <v>1</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="F13" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="G13" s="8">
+      <c r="G13" s="34">
         <v>2026</v>
       </c>
-      <c r="H13" s="8" t="s">
+      <c r="H13" s="34" t="s">
         <v>64</v>
       </c>
-      <c r="I13" s="40" t="s">
+      <c r="I13" s="36" t="s">
         <v>65</v>
       </c>
-      <c r="J13" s="41"/>
-      <c r="K13" s="41"/>
-      <c r="L13" s="41"/>
-      <c r="M13" s="41"/>
-      <c r="N13" s="41"/>
-      <c r="O13" s="41"/>
+      <c r="J13" s="37"/>
+      <c r="K13" s="37"/>
+      <c r="L13" s="37"/>
+      <c r="M13" s="37"/>
+      <c r="N13" s="37"/>
+      <c r="O13" s="37"/>
     </row>
     <row r="14" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A14" s="25" t="s">
+      <c r="A14" s="23" t="s">
         <v>66</v>
       </c>
-      <c r="B14" s="26" t="s">
+      <c r="B14" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="C14" s="26" t="s">
+      <c r="C14" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="D14" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" s="27">
+      <c r="D14" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" s="24">
         <v>7</v>
       </c>
-      <c r="F14" s="26" t="s">
+      <c r="F14" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="G14" s="26">
+      <c r="G14" s="24">
         <v>2026</v>
       </c>
-      <c r="H14" s="26" t="s">
+      <c r="H14" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="I14" s="26" t="s">
+      <c r="I14" s="24" t="s">
         <v>69</v>
       </c>
       <c r="J14" s="13"/>
@@ -3500,31 +3516,31 @@
       <c r="O14" s="13"/>
     </row>
     <row r="15" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A15" s="25" t="s">
+      <c r="A15" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="B15" s="26" t="s">
+      <c r="B15" s="24" t="s">
         <v>71</v>
       </c>
-      <c r="C15" s="26" t="s">
+      <c r="C15" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="D15" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="E15" s="36">
+      <c r="D15" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" s="24">
         <v>7</v>
       </c>
-      <c r="F15" s="26" t="s">
+      <c r="F15" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="G15" s="26">
+      <c r="G15" s="24">
         <v>2026</v>
       </c>
-      <c r="H15" s="26" t="s">
+      <c r="H15" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="I15" s="26" t="s">
+      <c r="I15" s="24" t="s">
         <v>74</v>
       </c>
       <c r="J15" s="13"/>
@@ -3537,31 +3553,31 @@
       <c r="O15" s="13"/>
     </row>
     <row r="16" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A16" s="25" t="s">
+      <c r="A16" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="B16" s="26" t="s">
+      <c r="B16" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="C16" s="26" t="s">
+      <c r="C16" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="D16" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="E16" s="27">
+      <c r="D16" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" s="24">
         <v>6</v>
       </c>
-      <c r="F16" s="26" t="s">
+      <c r="F16" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="G16" s="26">
+      <c r="G16" s="24">
         <v>2026</v>
       </c>
-      <c r="H16" s="26" t="s">
+      <c r="H16" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="I16" s="26" t="s">
+      <c r="I16" s="24" t="s">
         <v>77</v>
       </c>
       <c r="J16" s="13"/>
@@ -3574,31 +3590,31 @@
       <c r="O16" s="13"/>
     </row>
     <row r="17" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A17" s="25" t="s">
+      <c r="A17" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="B17" s="26" t="s">
+      <c r="B17" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="C17" s="26" t="s">
+      <c r="C17" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="D17" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="E17" s="27">
+      <c r="D17" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E17" s="24">
         <v>8</v>
       </c>
-      <c r="F17" s="26" t="s">
+      <c r="F17" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="G17" s="26">
+      <c r="G17" s="24">
         <v>2026</v>
       </c>
-      <c r="H17" s="26" t="s">
+      <c r="H17" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="I17" s="26" t="s">
+      <c r="I17" s="24" t="s">
         <v>81</v>
       </c>
       <c r="J17" s="13"/>
@@ -3611,31 +3627,31 @@
       <c r="O17" s="13"/>
     </row>
     <row r="18" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A18" s="25" t="s">
+      <c r="A18" s="23" t="s">
         <v>82</v>
       </c>
-      <c r="B18" s="26" t="s">
+      <c r="B18" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="C18" s="26" t="s">
+      <c r="C18" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="D18" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="E18" s="27">
+      <c r="D18" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="24">
         <v>10</v>
       </c>
-      <c r="F18" s="26" t="s">
+      <c r="F18" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="G18" s="26">
+      <c r="G18" s="24">
         <v>2026</v>
       </c>
-      <c r="H18" s="26" t="s">
+      <c r="H18" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="I18" s="26" t="s">
+      <c r="I18" s="24" t="s">
         <v>85</v>
       </c>
       <c r="J18" s="13"/>
@@ -3648,31 +3664,31 @@
       <c r="O18" s="13"/>
     </row>
     <row r="19" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A19" s="25" t="s">
+      <c r="A19" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="B19" s="26" t="s">
+      <c r="B19" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="C19" s="26" t="s">
+      <c r="C19" s="24" t="s">
         <v>87</v>
       </c>
-      <c r="D19" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="E19" s="36">
+      <c r="D19" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19" s="24">
         <v>4</v>
       </c>
-      <c r="F19" s="26" t="s">
+      <c r="F19" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="G19" s="26">
+      <c r="G19" s="24">
         <v>2026</v>
       </c>
-      <c r="H19" s="26" t="s">
+      <c r="H19" s="24" t="s">
         <v>88</v>
       </c>
-      <c r="I19" s="26" t="s">
+      <c r="I19" s="24" t="s">
         <v>89</v>
       </c>
       <c r="J19" s="13"/>
@@ -3685,31 +3701,31 @@
       <c r="O19" s="13"/>
     </row>
     <row r="20" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A20" s="25" t="s">
+      <c r="A20" s="23" t="s">
         <v>91</v>
       </c>
-      <c r="B20" s="26" t="s">
+      <c r="B20" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="C20" s="26" t="s">
+      <c r="C20" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="D20" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="E20" s="36">
+      <c r="D20" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E20" s="24">
         <v>8</v>
       </c>
-      <c r="F20" s="26" t="s">
+      <c r="F20" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="G20" s="26">
+      <c r="G20" s="24">
         <v>2026</v>
       </c>
-      <c r="H20" s="26" t="s">
+      <c r="H20" s="24" t="s">
         <v>93</v>
       </c>
-      <c r="I20" s="26" t="s">
+      <c r="I20" s="24" t="s">
         <v>94</v>
       </c>
       <c r="J20" s="13"/>
@@ -3722,29 +3738,29 @@
       <c r="O20" s="13"/>
     </row>
     <row r="21" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A21" s="25" t="s">
+      <c r="A21" s="23" t="s">
         <v>95</v>
       </c>
-      <c r="B21" s="26" t="s">
+      <c r="B21" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="C21" s="26" t="s">
+      <c r="C21" s="24" t="s">
         <v>96</v>
       </c>
-      <c r="D21" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="E21" s="36">
+      <c r="D21" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E21" s="24">
         <v>7</v>
       </c>
-      <c r="F21" s="26" t="s">
+      <c r="F21" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="G21" s="26">
+      <c r="G21" s="24">
         <v>2026</v>
       </c>
-      <c r="H21" s="26"/>
-      <c r="I21" s="26" t="s">
+      <c r="H21" s="24"/>
+      <c r="I21" s="24" t="s">
         <v>97</v>
       </c>
       <c r="J21" s="13"/>
@@ -3755,28 +3771,28 @@
       <c r="O21" s="13"/>
     </row>
     <row r="22" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A22" s="25" t="s">
+      <c r="A22" s="23" t="s">
         <v>98</v>
       </c>
-      <c r="B22" s="26" t="s">
+      <c r="B22" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="C22" s="26" t="s">
+      <c r="C22" s="24" t="s">
         <v>99</v>
       </c>
-      <c r="D22" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="E22" s="36">
+      <c r="D22" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E22" s="24">
         <v>5</v>
       </c>
-      <c r="F22" s="26" t="s">
+      <c r="F22" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="G22" s="26">
+      <c r="G22" s="24">
         <v>2026</v>
       </c>
-      <c r="I22" s="26" t="s">
+      <c r="I22" s="24" t="s">
         <v>100</v>
       </c>
       <c r="J22" s="13"/>
@@ -3787,26 +3803,26 @@
       <c r="O22" s="13"/>
     </row>
     <row r="23" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A23" s="42" t="s">
+      <c r="A23" s="29" t="s">
         <v>101</v>
       </c>
       <c r="B23" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="C23" s="28" t="s">
+      <c r="C23" s="25" t="s">
         <v>102</v>
       </c>
-      <c r="D23" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="E23" s="43"/>
-      <c r="F23" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="G23" s="26">
+      <c r="D23" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E23" s="25"/>
+      <c r="F23" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="G23" s="24">
         <v>2026</v>
       </c>
-      <c r="H23" s="26"/>
+      <c r="H23" s="24"/>
       <c r="I23" s="13" t="s">
         <v>103</v>
       </c>
@@ -3815,29 +3831,29 @@
       <c r="L23" s="13"/>
       <c r="M23" s="13"/>
       <c r="N23" s="13"/>
-      <c r="O23" s="44"/>
+      <c r="O23" s="38"/>
     </row>
     <row r="24" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A24" s="42" t="s">
+      <c r="A24" s="29" t="s">
         <v>104</v>
       </c>
       <c r="B24" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="C24" s="28" t="s">
+      <c r="C24" s="25" t="s">
         <v>102</v>
       </c>
-      <c r="D24" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="E24" s="43"/>
-      <c r="F24" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="G24" s="26">
+      <c r="D24" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E24" s="25"/>
+      <c r="F24" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="G24" s="24">
         <v>2026</v>
       </c>
-      <c r="H24" s="26"/>
+      <c r="H24" s="24"/>
       <c r="I24" s="13" t="s">
         <v>105</v>
       </c>
@@ -3846,7 +3862,7 @@
       <c r="L24" s="13"/>
       <c r="M24" s="13"/>
       <c r="N24" s="13"/>
-      <c r="O24" s="44"/>
+      <c r="O24" s="38"/>
     </row>
     <row r="25" ht="25" customHeight="1" spans="1:15">
       <c r="A25" s="12" t="s">
@@ -3861,7 +3877,7 @@
       <c r="D25" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E25" s="24" t="s">
+      <c r="E25" s="13" t="s">
         <v>108</v>
       </c>
       <c r="F25" s="5" t="s">
@@ -3898,7 +3914,7 @@
       <c r="D26" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E26" s="24" t="s">
+      <c r="E26" s="13" t="s">
         <v>114</v>
       </c>
       <c r="F26" s="5" t="s">
@@ -3935,7 +3951,7 @@
       <c r="D27" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E27" s="24" t="s">
+      <c r="E27" s="13" t="s">
         <v>120</v>
       </c>
       <c r="F27" s="5" t="s">
@@ -3972,7 +3988,7 @@
       <c r="D28" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E28" s="24" t="s">
+      <c r="E28" s="13" t="s">
         <v>126</v>
       </c>
       <c r="F28" s="5" t="s">
@@ -4009,7 +4025,7 @@
       <c r="D29" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E29" s="24" t="s">
+      <c r="E29" s="13" t="s">
         <v>132</v>
       </c>
       <c r="F29" s="5" t="s">
@@ -4046,7 +4062,7 @@
       <c r="D30" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E30" s="24" t="s">
+      <c r="E30" s="13" t="s">
         <v>138</v>
       </c>
       <c r="F30" s="5" t="s">
@@ -4083,7 +4099,7 @@
       <c r="D31" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E31" s="24" t="s">
+      <c r="E31" s="13" t="s">
         <v>144</v>
       </c>
       <c r="F31" s="5" t="s">
@@ -4105,7 +4121,7 @@
       </c>
       <c r="M31" s="5"/>
       <c r="N31" s="5"/>
-      <c r="O31" s="45"/>
+      <c r="O31" s="39"/>
     </row>
     <row r="32" ht="25" customHeight="1" spans="1:15">
       <c r="A32" s="12" t="s">
@@ -4120,7 +4136,7 @@
       <c r="D32" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E32" s="24" t="s">
+      <c r="E32" s="13" t="s">
         <v>150</v>
       </c>
       <c r="F32" s="5" t="s">
@@ -4142,7 +4158,7 @@
       </c>
       <c r="M32" s="5"/>
       <c r="N32" s="5"/>
-      <c r="O32" s="45"/>
+      <c r="O32" s="39"/>
     </row>
     <row r="33" ht="25" customHeight="1" spans="1:15">
       <c r="A33" s="12" t="s">
@@ -4157,7 +4173,7 @@
       <c r="D33" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E33" s="24" t="s">
+      <c r="E33" s="13" t="s">
         <v>156</v>
       </c>
       <c r="F33" s="5" t="s">
@@ -4179,7 +4195,7 @@
       </c>
       <c r="M33" s="5"/>
       <c r="N33" s="5"/>
-      <c r="O33" s="45"/>
+      <c r="O33" s="39"/>
     </row>
     <row r="34" ht="25" customHeight="1" spans="1:15">
       <c r="A34" s="12" t="s">
@@ -4194,7 +4210,7 @@
       <c r="D34" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E34" s="24" t="s">
+      <c r="E34" s="13" t="s">
         <v>126</v>
       </c>
       <c r="F34" s="5" t="s">
@@ -4216,7 +4232,7 @@
       </c>
       <c r="M34" s="5"/>
       <c r="N34" s="5"/>
-      <c r="O34" s="45"/>
+      <c r="O34" s="39"/>
     </row>
     <row r="35" ht="25" customHeight="1" spans="1:15">
       <c r="A35" s="12" t="s">
@@ -4231,7 +4247,7 @@
       <c r="D35" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E35" s="24" t="s">
+      <c r="E35" s="13" t="s">
         <v>166</v>
       </c>
       <c r="F35" s="5" t="s">
@@ -4253,7 +4269,7 @@
       </c>
       <c r="M35" s="5"/>
       <c r="N35" s="5"/>
-      <c r="O35" s="45"/>
+      <c r="O35" s="39"/>
     </row>
     <row r="36" ht="25" customHeight="1" spans="1:15">
       <c r="A36" s="12" t="s">
@@ -4268,7 +4284,7 @@
       <c r="D36" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E36" s="24" t="s">
+      <c r="E36" s="13" t="s">
         <v>144</v>
       </c>
       <c r="F36" s="5" t="s">
@@ -4290,7 +4306,7 @@
       </c>
       <c r="M36" s="5"/>
       <c r="N36" s="5"/>
-      <c r="O36" s="45"/>
+      <c r="O36" s="39"/>
     </row>
     <row r="37" ht="25" customHeight="1" spans="1:15">
       <c r="A37" s="12" t="s">
@@ -4305,7 +4321,7 @@
       <c r="D37" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E37" s="24" t="s">
+      <c r="E37" s="13" t="s">
         <v>144</v>
       </c>
       <c r="F37" s="5" t="s">
@@ -4327,7 +4343,7 @@
       </c>
       <c r="M37" s="5"/>
       <c r="N37" s="5"/>
-      <c r="O37" s="45"/>
+      <c r="O37" s="39"/>
     </row>
     <row r="38" ht="25" customHeight="1" spans="1:15">
       <c r="A38" s="12" t="s">
@@ -4342,7 +4358,7 @@
       <c r="D38" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E38" s="24" t="s">
+      <c r="E38" s="13" t="s">
         <v>108</v>
       </c>
       <c r="F38" s="5" t="s">
@@ -4364,7 +4380,7 @@
       </c>
       <c r="M38" s="5"/>
       <c r="N38" s="5"/>
-      <c r="O38" s="45"/>
+      <c r="O38" s="39"/>
     </row>
     <row r="39" ht="25" customHeight="1" spans="1:15">
       <c r="A39" s="12" t="s">
@@ -4379,7 +4395,7 @@
       <c r="D39" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E39" s="24" t="s">
+      <c r="E39" s="13" t="s">
         <v>186</v>
       </c>
       <c r="F39" s="5" t="s">
@@ -4401,7 +4417,7 @@
       </c>
       <c r="M39" s="5"/>
       <c r="N39" s="5"/>
-      <c r="O39" s="45"/>
+      <c r="O39" s="39"/>
     </row>
     <row r="40" ht="25" customHeight="1" spans="1:15">
       <c r="A40" s="12" t="s">
@@ -4416,7 +4432,7 @@
       <c r="D40" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E40" s="24" t="s">
+      <c r="E40" s="13" t="s">
         <v>192</v>
       </c>
       <c r="F40" s="5" t="s">
@@ -4438,7 +4454,7 @@
       </c>
       <c r="M40" s="5"/>
       <c r="N40" s="5"/>
-      <c r="O40" s="45"/>
+      <c r="O40" s="39"/>
     </row>
     <row r="41" ht="25" customHeight="1" spans="1:15">
       <c r="A41" s="12" t="s">
@@ -4453,7 +4469,7 @@
       <c r="D41" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E41" s="24" t="s">
+      <c r="E41" s="13" t="s">
         <v>114</v>
       </c>
       <c r="F41" s="5" t="s">
@@ -4475,13 +4491,13 @@
       </c>
       <c r="M41" s="5"/>
       <c r="N41" s="5"/>
-      <c r="O41" s="45"/>
+      <c r="O41" s="39"/>
     </row>
     <row r="42" ht="25" customHeight="1" spans="1:15">
       <c r="A42" s="12" t="s">
         <v>201</v>
       </c>
-      <c r="B42" s="26" t="s">
+      <c r="B42" s="24" t="s">
         <v>58</v>
       </c>
       <c r="C42" s="5" t="s">
@@ -4490,7 +4506,7 @@
       <c r="D42" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E42" s="24" t="s">
+      <c r="E42" s="13" t="s">
         <v>203</v>
       </c>
       <c r="F42" s="5" t="s">
@@ -4510,13 +4526,13 @@
       </c>
       <c r="M42" s="5"/>
       <c r="N42" s="5"/>
-      <c r="O42" s="45"/>
+      <c r="O42" s="39"/>
     </row>
     <row r="43" ht="25" customHeight="1" spans="1:15">
       <c r="A43" s="12" t="s">
         <v>205</v>
       </c>
-      <c r="B43" s="26" t="s">
+      <c r="B43" s="24" t="s">
         <v>58</v>
       </c>
       <c r="C43" s="5" t="s">
@@ -4525,7 +4541,7 @@
       <c r="D43" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E43" s="24" t="s">
+      <c r="E43" s="13" t="s">
         <v>207</v>
       </c>
       <c r="F43" s="5" t="s">
@@ -4547,13 +4563,13 @@
       </c>
       <c r="M43" s="5"/>
       <c r="N43" s="5"/>
-      <c r="O43" s="45"/>
+      <c r="O43" s="39"/>
     </row>
     <row r="44" ht="25" customHeight="1" spans="1:15">
       <c r="A44" s="12" t="s">
         <v>211</v>
       </c>
-      <c r="B44" s="26" t="s">
+      <c r="B44" s="24" t="s">
         <v>58</v>
       </c>
       <c r="C44" s="5" t="s">
@@ -4562,7 +4578,7 @@
       <c r="D44" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E44" s="24" t="s">
+      <c r="E44" s="13" t="s">
         <v>203</v>
       </c>
       <c r="F44" s="5" t="s">
@@ -4582,7 +4598,7 @@
       </c>
       <c r="M44" s="5"/>
       <c r="N44" s="5"/>
-      <c r="O44" s="45"/>
+      <c r="O44" s="39"/>
     </row>
     <row r="45" ht="25" customHeight="1" spans="1:15">
       <c r="A45" s="12" t="s">
@@ -4597,7 +4613,7 @@
       <c r="D45" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E45" s="24" t="s">
+      <c r="E45" s="13" t="s">
         <v>120</v>
       </c>
       <c r="F45" s="5" t="s">
@@ -4619,7 +4635,7 @@
       </c>
       <c r="M45" s="5"/>
       <c r="N45" s="5"/>
-      <c r="O45" s="45"/>
+      <c r="O45" s="39"/>
     </row>
     <row r="46" ht="25" customHeight="1" spans="1:15">
       <c r="A46" s="12" t="s">
@@ -4628,7 +4644,7 @@
       <c r="B46" s="5"/>
       <c r="C46" s="5"/>
       <c r="D46" s="5"/>
-      <c r="E46" s="24"/>
+      <c r="E46" s="13"/>
       <c r="F46" s="5" t="s">
         <v>33</v>
       </c>
@@ -4642,7 +4658,7 @@
       <c r="L46" s="5"/>
       <c r="M46" s="5"/>
       <c r="N46" s="5"/>
-      <c r="O46" s="45"/>
+      <c r="O46" s="39"/>
     </row>
     <row r="47" ht="25" customHeight="1" spans="1:15">
       <c r="A47" s="12" t="s">
@@ -4651,7 +4667,7 @@
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
       <c r="D47" s="5"/>
-      <c r="E47" s="24"/>
+      <c r="E47" s="13"/>
       <c r="F47" s="5" t="s">
         <v>33</v>
       </c>
@@ -4665,7 +4681,7 @@
       <c r="L47" s="5"/>
       <c r="M47" s="5"/>
       <c r="N47" s="5"/>
-      <c r="O47" s="45"/>
+      <c r="O47" s="39"/>
     </row>
     <row r="48" ht="25" customHeight="1" spans="1:15">
       <c r="A48" s="12" t="s">
@@ -4674,7 +4690,7 @@
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
       <c r="D48" s="5"/>
-      <c r="E48" s="24"/>
+      <c r="E48" s="13"/>
       <c r="F48" s="5" t="s">
         <v>33</v>
       </c>
@@ -4688,7 +4704,7 @@
       <c r="L48" s="5"/>
       <c r="M48" s="5"/>
       <c r="N48" s="5"/>
-      <c r="O48" s="45"/>
+      <c r="O48" s="39"/>
     </row>
     <row r="49" ht="25" customHeight="1" spans="1:15">
       <c r="A49" s="12" t="s">
@@ -4697,7 +4713,7 @@
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
       <c r="D49" s="5"/>
-      <c r="E49" s="24"/>
+      <c r="E49" s="13"/>
       <c r="F49" s="5" t="s">
         <v>33</v>
       </c>
@@ -4711,7 +4727,7 @@
       <c r="L49" s="5"/>
       <c r="M49" s="5"/>
       <c r="N49" s="5"/>
-      <c r="O49" s="45"/>
+      <c r="O49" s="39"/>
     </row>
     <row r="50" ht="25" customHeight="1" spans="1:15">
       <c r="A50" s="14" t="s">
@@ -4720,7 +4736,7 @@
       <c r="B50" s="15"/>
       <c r="C50" s="15"/>
       <c r="D50" s="15"/>
-      <c r="E50" s="46"/>
+      <c r="E50" s="28"/>
       <c r="F50" s="5" t="s">
         <v>33</v>
       </c>
@@ -4734,7 +4750,7 @@
       <c r="L50" s="5"/>
       <c r="M50" s="5"/>
       <c r="N50" s="5"/>
-      <c r="O50" s="45"/>
+      <c r="O50" s="39"/>
     </row>
     <row r="51" ht="25" customHeight="1" spans="1:15">
       <c r="A51" s="12" t="s">
@@ -4743,7 +4759,7 @@
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
       <c r="D51" s="5"/>
-      <c r="E51" s="24"/>
+      <c r="E51" s="13"/>
       <c r="F51" s="5" t="s">
         <v>33</v>
       </c>
@@ -4757,7 +4773,7 @@
       <c r="L51" s="5"/>
       <c r="M51" s="5"/>
       <c r="N51" s="5"/>
-      <c r="O51" s="45"/>
+      <c r="O51" s="39"/>
     </row>
     <row r="52" ht="25" customHeight="1" spans="1:15">
       <c r="A52" s="12" t="s">
@@ -4766,7 +4782,7 @@
       <c r="B52" s="5"/>
       <c r="C52" s="5"/>
       <c r="D52" s="5"/>
-      <c r="E52" s="24"/>
+      <c r="E52" s="13"/>
       <c r="F52" s="5" t="s">
         <v>33</v>
       </c>
@@ -4780,7 +4796,7 @@
       <c r="L52" s="5"/>
       <c r="M52" s="5"/>
       <c r="N52" s="5"/>
-      <c r="O52" s="45"/>
+      <c r="O52" s="39"/>
     </row>
     <row r="53" ht="25" customHeight="1" spans="1:15">
       <c r="A53" s="12" t="s">
@@ -4789,7 +4805,7 @@
       <c r="B53" s="5"/>
       <c r="C53" s="5"/>
       <c r="D53" s="5"/>
-      <c r="E53" s="24"/>
+      <c r="E53" s="13"/>
       <c r="F53" s="5" t="s">
         <v>33</v>
       </c>
@@ -4803,7 +4819,7 @@
       <c r="L53" s="5"/>
       <c r="M53" s="5"/>
       <c r="N53" s="5"/>
-      <c r="O53" s="45"/>
+      <c r="O53" s="39"/>
     </row>
     <row r="54" ht="25" customHeight="1" spans="1:15">
       <c r="A54" s="12" t="s">
@@ -4812,7 +4828,7 @@
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
       <c r="D54" s="5"/>
-      <c r="E54" s="24"/>
+      <c r="E54" s="13"/>
       <c r="F54" s="5" t="s">
         <v>33</v>
       </c>
@@ -4825,7 +4841,7 @@
       <c r="L54" s="5"/>
       <c r="M54" s="5"/>
       <c r="N54" s="5"/>
-      <c r="O54" s="45"/>
+      <c r="O54" s="39"/>
     </row>
     <row r="55" ht="25" customHeight="1" spans="1:15">
       <c r="A55" s="12" t="s">
@@ -4834,7 +4850,7 @@
       <c r="B55" s="5"/>
       <c r="C55" s="5"/>
       <c r="D55" s="5"/>
-      <c r="E55" s="24"/>
+      <c r="E55" s="13"/>
       <c r="F55" s="5" t="s">
         <v>33</v>
       </c>
@@ -4848,7 +4864,7 @@
       <c r="L55" s="5"/>
       <c r="M55" s="5"/>
       <c r="N55" s="5"/>
-      <c r="O55" s="45"/>
+      <c r="O55" s="39"/>
     </row>
     <row r="56" ht="25" customHeight="1" spans="1:15">
       <c r="A56" s="12" t="s">
@@ -4857,7 +4873,7 @@
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
       <c r="D56" s="5"/>
-      <c r="E56" s="24"/>
+      <c r="E56" s="13"/>
       <c r="F56" s="5" t="s">
         <v>33</v>
       </c>
@@ -4871,7 +4887,7 @@
       <c r="L56" s="5"/>
       <c r="M56" s="5"/>
       <c r="N56" s="5"/>
-      <c r="O56" s="45"/>
+      <c r="O56" s="39"/>
     </row>
     <row r="57" ht="25" customHeight="1" spans="1:15">
       <c r="A57" s="12" t="s">
@@ -4880,7 +4896,7 @@
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
       <c r="D57" s="5"/>
-      <c r="E57" s="24"/>
+      <c r="E57" s="13"/>
       <c r="F57" s="5" t="s">
         <v>33</v>
       </c>
@@ -4894,7 +4910,7 @@
       <c r="L57" s="5"/>
       <c r="M57" s="5"/>
       <c r="N57" s="5"/>
-      <c r="O57" s="45"/>
+      <c r="O57" s="39"/>
     </row>
     <row r="58" ht="25" customHeight="1" spans="1:15">
       <c r="A58" s="12" t="s">
@@ -4903,7 +4919,7 @@
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
       <c r="D58" s="5"/>
-      <c r="E58" s="24"/>
+      <c r="E58" s="13"/>
       <c r="F58" s="5" t="s">
         <v>33</v>
       </c>
@@ -4916,7 +4932,7 @@
       <c r="L58" s="5"/>
       <c r="M58" s="5"/>
       <c r="N58" s="5"/>
-      <c r="O58" s="45"/>
+      <c r="O58" s="39"/>
     </row>
     <row r="59" ht="25" customHeight="1" spans="1:15">
       <c r="A59" s="12" t="s">
@@ -4925,7 +4941,7 @@
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
       <c r="D59" s="5"/>
-      <c r="E59" s="24"/>
+      <c r="E59" s="13"/>
       <c r="F59" s="5" t="s">
         <v>33</v>
       </c>
@@ -4939,7 +4955,7 @@
       <c r="L59" s="5"/>
       <c r="M59" s="5"/>
       <c r="N59" s="5"/>
-      <c r="O59" s="45"/>
+      <c r="O59" s="39"/>
     </row>
     <row r="60" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A60" s="12" t="s">
@@ -4948,7 +4964,7 @@
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
       <c r="D60" s="5"/>
-      <c r="E60" s="24"/>
+      <c r="E60" s="13"/>
       <c r="F60" s="5" t="s">
         <v>33</v>
       </c>
@@ -4962,7 +4978,7 @@
       <c r="L60" s="5"/>
       <c r="M60" s="5"/>
       <c r="N60" s="5"/>
-      <c r="O60" s="45"/>
+      <c r="O60" s="39"/>
     </row>
     <row r="61" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A61" s="12" t="s">
@@ -4971,7 +4987,7 @@
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
       <c r="D61" s="5"/>
-      <c r="E61" s="24"/>
+      <c r="E61" s="13"/>
       <c r="F61" s="5" t="s">
         <v>33</v>
       </c>
@@ -4985,7 +5001,7 @@
       <c r="L61" s="5"/>
       <c r="M61" s="5"/>
       <c r="N61" s="5"/>
-      <c r="O61" s="45"/>
+      <c r="O61" s="39"/>
     </row>
     <row r="62" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A62" s="12" t="s">
@@ -4994,7 +5010,7 @@
       <c r="B62" s="5"/>
       <c r="C62" s="5"/>
       <c r="D62" s="5"/>
-      <c r="E62" s="24"/>
+      <c r="E62" s="13"/>
       <c r="F62" s="5" t="s">
         <v>33</v>
       </c>
@@ -5008,7 +5024,7 @@
       <c r="L62" s="5"/>
       <c r="M62" s="5"/>
       <c r="N62" s="5"/>
-      <c r="O62" s="45"/>
+      <c r="O62" s="39"/>
     </row>
     <row r="63" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A63" s="12" t="s">
@@ -5017,7 +5033,7 @@
       <c r="B63" s="5"/>
       <c r="C63" s="5"/>
       <c r="D63" s="5"/>
-      <c r="E63" s="24"/>
+      <c r="E63" s="13"/>
       <c r="F63" s="5" t="s">
         <v>33</v>
       </c>
@@ -5031,7 +5047,7 @@
       <c r="L63" s="5"/>
       <c r="M63" s="5"/>
       <c r="N63" s="5"/>
-      <c r="O63" s="45"/>
+      <c r="O63" s="39"/>
     </row>
     <row r="64" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A64" s="12" t="s">
@@ -5044,7 +5060,7 @@
         <v>257</v>
       </c>
       <c r="D64" s="5"/>
-      <c r="E64" s="24" t="s">
+      <c r="E64" s="13" t="s">
         <v>258</v>
       </c>
       <c r="F64" s="5" t="s">
@@ -5062,7 +5078,7 @@
       <c r="L64" s="5"/>
       <c r="M64" s="5"/>
       <c r="N64" s="5"/>
-      <c r="O64" s="45"/>
+      <c r="O64" s="39"/>
     </row>
     <row r="65" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A65" s="12" t="s">
@@ -5075,7 +5091,7 @@
         <v>262</v>
       </c>
       <c r="D65" s="5"/>
-      <c r="E65" s="24" t="s">
+      <c r="E65" s="13" t="s">
         <v>120</v>
       </c>
       <c r="F65" s="5" t="s">
@@ -5106,7 +5122,7 @@
         <v>266</v>
       </c>
       <c r="D66" s="5"/>
-      <c r="E66" s="24" t="s">
+      <c r="E66" s="13" t="s">
         <v>126</v>
       </c>
       <c r="F66" s="5" t="s">
@@ -5124,7 +5140,7 @@
       <c r="L66" s="5"/>
       <c r="M66" s="5"/>
       <c r="N66" s="5"/>
-      <c r="O66" s="45"/>
+      <c r="O66" s="39"/>
     </row>
     <row r="67" ht="25" customHeight="1" spans="1:15">
       <c r="A67" s="12" t="s">
@@ -5137,7 +5153,7 @@
         <v>270</v>
       </c>
       <c r="D67" s="5"/>
-      <c r="E67" s="24" t="s">
+      <c r="E67" s="13" t="s">
         <v>271</v>
       </c>
       <c r="F67" s="5" t="s">
@@ -5155,7 +5171,7 @@
       <c r="L67" s="5"/>
       <c r="M67" s="5"/>
       <c r="N67" s="5"/>
-      <c r="O67" s="45"/>
+      <c r="O67" s="39"/>
     </row>
     <row r="68" ht="25" customHeight="1" spans="1:15">
       <c r="A68" s="12" t="s">
@@ -5168,7 +5184,7 @@
         <v>275</v>
       </c>
       <c r="D68" s="5"/>
-      <c r="E68" s="24" t="s">
+      <c r="E68" s="13" t="s">
         <v>271</v>
       </c>
       <c r="F68" s="5" t="s">
@@ -5186,7 +5202,7 @@
       <c r="L68" s="5"/>
       <c r="M68" s="5"/>
       <c r="N68" s="5"/>
-      <c r="O68" s="45"/>
+      <c r="O68" s="39"/>
     </row>
     <row r="69" ht="25" customHeight="1" spans="1:15">
       <c r="A69" s="12" t="s">
@@ -5199,7 +5215,7 @@
         <v>279</v>
       </c>
       <c r="D69" s="5"/>
-      <c r="E69" s="24" t="s">
+      <c r="E69" s="13" t="s">
         <v>280</v>
       </c>
       <c r="F69" s="5" t="s">
@@ -5217,7 +5233,7 @@
       <c r="L69" s="5"/>
       <c r="M69" s="5"/>
       <c r="N69" s="5"/>
-      <c r="O69" s="45"/>
+      <c r="O69" s="39"/>
     </row>
     <row r="70" ht="25" customHeight="1" spans="1:15">
       <c r="A70" s="12" t="s">
@@ -5226,19 +5242,19 @@
       <c r="B70" s="5" t="s">
         <v>284</v>
       </c>
-      <c r="C70" s="47" t="s">
+      <c r="C70" s="40" t="s">
         <v>285</v>
       </c>
-      <c r="D70" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="E70" s="33">
+      <c r="D70" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E70" s="13">
         <v>16</v>
       </c>
       <c r="F70" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="G70" s="26">
+      <c r="G70" s="24">
         <v>2026</v>
       </c>
       <c r="H70" s="5" t="s">
@@ -5259,7 +5275,7 @@
       <c r="B71" s="5"/>
       <c r="C71" s="5"/>
       <c r="D71" s="5"/>
-      <c r="E71" s="24"/>
+      <c r="E71" s="13"/>
       <c r="F71" s="13"/>
       <c r="G71" s="5"/>
       <c r="H71" s="5"/>
@@ -5276,7 +5292,7 @@
       <c r="B72" s="5"/>
       <c r="C72" s="5"/>
       <c r="D72" s="5"/>
-      <c r="E72" s="24"/>
+      <c r="E72" s="13"/>
       <c r="F72" s="13"/>
       <c r="G72" s="5"/>
       <c r="I72" s="5"/>
@@ -5292,7 +5308,7 @@
       <c r="B73" s="5"/>
       <c r="C73" s="5"/>
       <c r="D73" s="5"/>
-      <c r="E73" s="24"/>
+      <c r="E73" s="13"/>
       <c r="F73" s="13"/>
       <c r="G73" s="5"/>
       <c r="H73" s="5"/>
@@ -5309,7 +5325,7 @@
       <c r="B74" s="5"/>
       <c r="C74" s="5"/>
       <c r="D74" s="5"/>
-      <c r="E74" s="24"/>
+      <c r="E74" s="13"/>
       <c r="F74" s="13"/>
       <c r="G74" s="5"/>
       <c r="H74" s="5"/>
@@ -5326,7 +5342,7 @@
       <c r="B75" s="5"/>
       <c r="C75" s="5"/>
       <c r="D75" s="5"/>
-      <c r="E75" s="24"/>
+      <c r="E75" s="13"/>
       <c r="F75" s="13"/>
       <c r="G75" s="5"/>
       <c r="I75" s="5"/>
@@ -5342,7 +5358,7 @@
       <c r="B76" s="5"/>
       <c r="C76" s="5"/>
       <c r="D76" s="5"/>
-      <c r="E76" s="24"/>
+      <c r="E76" s="13"/>
       <c r="F76" s="13"/>
       <c r="G76" s="5"/>
       <c r="H76" s="5"/>
@@ -5359,7 +5375,7 @@
       <c r="B77" s="5"/>
       <c r="C77" s="5"/>
       <c r="D77" s="5"/>
-      <c r="E77" s="24"/>
+      <c r="E77" s="13"/>
       <c r="F77" s="13"/>
       <c r="G77" s="5"/>
       <c r="H77" s="5"/>
@@ -5376,7 +5392,7 @@
       <c r="B78" s="5"/>
       <c r="C78" s="5"/>
       <c r="D78" s="5"/>
-      <c r="E78" s="24"/>
+      <c r="E78" s="13"/>
       <c r="F78" s="13"/>
       <c r="G78" s="5"/>
       <c r="H78" s="5"/>
@@ -5393,7 +5409,7 @@
       <c r="B79" s="5"/>
       <c r="C79" s="5"/>
       <c r="D79" s="5"/>
-      <c r="E79" s="24"/>
+      <c r="E79" s="13"/>
       <c r="F79" s="13"/>
       <c r="G79" s="5"/>
       <c r="I79" s="5"/>
@@ -5409,7 +5425,7 @@
       <c r="B80" s="5"/>
       <c r="C80" s="5"/>
       <c r="D80" s="5"/>
-      <c r="E80" s="24"/>
+      <c r="E80" s="13"/>
       <c r="F80" s="13"/>
       <c r="G80" s="5"/>
       <c r="H80" s="5"/>
@@ -5426,7 +5442,7 @@
       <c r="B81" s="5"/>
       <c r="C81" s="5"/>
       <c r="D81" s="5"/>
-      <c r="E81" s="24"/>
+      <c r="E81" s="13"/>
       <c r="F81" s="13"/>
       <c r="G81" s="5"/>
       <c r="H81" s="5"/>
@@ -5443,7 +5459,7 @@
       <c r="B82" s="5"/>
       <c r="C82" s="5"/>
       <c r="D82" s="5"/>
-      <c r="E82" s="24"/>
+      <c r="E82" s="13"/>
       <c r="F82" s="13"/>
       <c r="G82" s="5"/>
       <c r="H82" s="5"/>
@@ -5460,7 +5476,7 @@
       <c r="B83" s="5"/>
       <c r="C83" s="5"/>
       <c r="D83" s="5"/>
-      <c r="E83" s="24"/>
+      <c r="E83" s="13"/>
       <c r="F83" s="13"/>
       <c r="G83" s="5"/>
       <c r="H83" s="5"/>
@@ -5477,7 +5493,7 @@
       <c r="B84" s="5"/>
       <c r="C84" s="5"/>
       <c r="D84" s="5"/>
-      <c r="E84" s="24"/>
+      <c r="E84" s="13"/>
       <c r="F84" s="13"/>
       <c r="G84" s="5"/>
       <c r="H84" s="5"/>
@@ -5494,7 +5510,7 @@
       <c r="B85" s="5"/>
       <c r="C85" s="5"/>
       <c r="D85" s="5"/>
-      <c r="E85" s="24"/>
+      <c r="E85" s="13"/>
       <c r="F85" s="13"/>
       <c r="G85" s="5"/>
       <c r="H85" s="5"/>

--- a/资源录入表新.xlsx
+++ b/资源录入表新.xlsx
@@ -2343,7 +2343,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2419,6 +2419,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2428,7 +2431,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2443,25 +2446,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -3069,7 +3063,7 @@
       <c r="D2" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="8">
+      <c r="E2" s="25">
         <v>13</v>
       </c>
       <c r="F2" s="24" t="s">
@@ -3104,7 +3098,7 @@
       <c r="D3" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E3" s="25">
         <v>15</v>
       </c>
       <c r="F3" s="24" t="s">
@@ -3139,8 +3133,8 @@
       <c r="D4" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="24">
-        <v>26</v>
+      <c r="E4" s="8">
+        <v>27</v>
       </c>
       <c r="F4" s="24" t="s">
         <v>15</v>
@@ -3176,8 +3170,8 @@
       <c r="D5" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="24">
-        <v>26</v>
+      <c r="E5" s="8">
+        <v>28</v>
       </c>
       <c r="F5" s="24" t="s">
         <v>15</v>
@@ -3214,7 +3208,7 @@
       <c r="E6" s="24">
         <v>24</v>
       </c>
-      <c r="F6" s="25" t="s">
+      <c r="F6" s="26" t="s">
         <v>33</v>
       </c>
       <c r="G6" s="24">
@@ -3240,14 +3234,14 @@
       <c r="B7" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="26" t="s">
+      <c r="C7" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="28">
-        <v>15</v>
+      <c r="D7" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="29">
+        <v>16</v>
       </c>
       <c r="F7" s="13" t="s">
         <v>15</v>
@@ -3269,20 +3263,20 @@
       <c r="O7" s="5"/>
     </row>
     <row r="8" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A8" s="29" t="s">
+      <c r="A8" s="30" t="s">
         <v>40</v>
       </c>
       <c r="B8" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="30" t="s">
+      <c r="C8" s="31" t="s">
         <v>41</v>
       </c>
       <c r="D8" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="13">
-        <v>8</v>
+      <c r="E8" s="11">
+        <v>10</v>
       </c>
       <c r="F8" s="13" t="s">
         <v>15</v>
@@ -3290,7 +3284,7 @@
       <c r="G8" s="13">
         <v>2026</v>
       </c>
-      <c r="H8" s="31" t="s">
+      <c r="H8" s="32" t="s">
         <v>42</v>
       </c>
       <c r="I8" s="13" t="s">
@@ -3304,20 +3298,20 @@
       <c r="O8" s="13"/>
     </row>
     <row r="9" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A9" s="29" t="s">
+      <c r="A9" s="30" t="s">
         <v>44</v>
       </c>
       <c r="B9" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="30" t="s">
+      <c r="C9" s="31" t="s">
         <v>45</v>
       </c>
       <c r="D9" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E9" s="13">
-        <v>8</v>
+      <c r="E9" s="11">
+        <v>10</v>
       </c>
       <c r="F9" s="13" t="s">
         <v>15</v>
@@ -3325,7 +3319,7 @@
       <c r="G9" s="13">
         <v>2026</v>
       </c>
-      <c r="H9" s="31" t="s">
+      <c r="H9" s="32" t="s">
         <v>46</v>
       </c>
       <c r="I9" s="13" t="s">
@@ -3351,8 +3345,8 @@
       <c r="D10" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="24">
-        <v>3</v>
+      <c r="E10" s="8">
+        <v>4</v>
       </c>
       <c r="F10" s="24" t="s">
         <v>15</v>
@@ -3415,7 +3409,7 @@
       <c r="B12" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="C12" s="32" t="s">
+      <c r="C12" s="33" t="s">
         <v>59</v>
       </c>
       <c r="D12" s="24" t="s">
@@ -3444,39 +3438,39 @@
       <c r="O12" s="13"/>
     </row>
     <row r="13" s="21" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A13" s="33" t="s">
+      <c r="A13" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="B13" s="34" t="s">
+      <c r="B13" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="C13" s="35" t="s">
+      <c r="C13" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="D13" s="34" t="s">
-        <v>14</v>
-      </c>
-      <c r="E13" s="34">
+      <c r="D13" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="24">
         <v>1</v>
       </c>
-      <c r="F13" s="34" t="s">
+      <c r="F13" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="G13" s="34">
+      <c r="G13" s="24">
         <v>2026</v>
       </c>
-      <c r="H13" s="34" t="s">
+      <c r="H13" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="I13" s="36" t="s">
+      <c r="I13" s="26" t="s">
         <v>65</v>
       </c>
-      <c r="J13" s="37"/>
-      <c r="K13" s="37"/>
-      <c r="L13" s="37"/>
-      <c r="M13" s="37"/>
-      <c r="N13" s="37"/>
-      <c r="O13" s="37"/>
+      <c r="J13" s="26"/>
+      <c r="K13" s="26"/>
+      <c r="L13" s="26"/>
+      <c r="M13" s="26"/>
+      <c r="N13" s="26"/>
+      <c r="O13" s="26"/>
     </row>
     <row r="14" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A14" s="23" t="s">
@@ -3803,20 +3797,20 @@
       <c r="O22" s="13"/>
     </row>
     <row r="23" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A23" s="29" t="s">
+      <c r="A23" s="30" t="s">
         <v>101</v>
       </c>
       <c r="B23" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="C23" s="25" t="s">
+      <c r="C23" s="26" t="s">
         <v>102</v>
       </c>
       <c r="D23" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E23" s="25"/>
-      <c r="F23" s="25" t="s">
+      <c r="E23" s="26"/>
+      <c r="F23" s="26" t="s">
         <v>33</v>
       </c>
       <c r="G23" s="24">
@@ -3831,23 +3825,23 @@
       <c r="L23" s="13"/>
       <c r="M23" s="13"/>
       <c r="N23" s="13"/>
-      <c r="O23" s="38"/>
+      <c r="O23" s="35"/>
     </row>
     <row r="24" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A24" s="29" t="s">
+      <c r="A24" s="30" t="s">
         <v>104</v>
       </c>
       <c r="B24" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="C24" s="25" t="s">
+      <c r="C24" s="26" t="s">
         <v>102</v>
       </c>
       <c r="D24" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E24" s="25"/>
-      <c r="F24" s="25" t="s">
+      <c r="E24" s="26"/>
+      <c r="F24" s="26" t="s">
         <v>33</v>
       </c>
       <c r="G24" s="24">
@@ -3862,7 +3856,7 @@
       <c r="L24" s="13"/>
       <c r="M24" s="13"/>
       <c r="N24" s="13"/>
-      <c r="O24" s="38"/>
+      <c r="O24" s="35"/>
     </row>
     <row r="25" ht="25" customHeight="1" spans="1:15">
       <c r="A25" s="12" t="s">
@@ -4121,7 +4115,7 @@
       </c>
       <c r="M31" s="5"/>
       <c r="N31" s="5"/>
-      <c r="O31" s="39"/>
+      <c r="O31" s="36"/>
     </row>
     <row r="32" ht="25" customHeight="1" spans="1:15">
       <c r="A32" s="12" t="s">
@@ -4158,7 +4152,7 @@
       </c>
       <c r="M32" s="5"/>
       <c r="N32" s="5"/>
-      <c r="O32" s="39"/>
+      <c r="O32" s="36"/>
     </row>
     <row r="33" ht="25" customHeight="1" spans="1:15">
       <c r="A33" s="12" t="s">
@@ -4195,7 +4189,7 @@
       </c>
       <c r="M33" s="5"/>
       <c r="N33" s="5"/>
-      <c r="O33" s="39"/>
+      <c r="O33" s="36"/>
     </row>
     <row r="34" ht="25" customHeight="1" spans="1:15">
       <c r="A34" s="12" t="s">
@@ -4232,7 +4226,7 @@
       </c>
       <c r="M34" s="5"/>
       <c r="N34" s="5"/>
-      <c r="O34" s="39"/>
+      <c r="O34" s="36"/>
     </row>
     <row r="35" ht="25" customHeight="1" spans="1:15">
       <c r="A35" s="12" t="s">
@@ -4269,7 +4263,7 @@
       </c>
       <c r="M35" s="5"/>
       <c r="N35" s="5"/>
-      <c r="O35" s="39"/>
+      <c r="O35" s="36"/>
     </row>
     <row r="36" ht="25" customHeight="1" spans="1:15">
       <c r="A36" s="12" t="s">
@@ -4306,7 +4300,7 @@
       </c>
       <c r="M36" s="5"/>
       <c r="N36" s="5"/>
-      <c r="O36" s="39"/>
+      <c r="O36" s="36"/>
     </row>
     <row r="37" ht="25" customHeight="1" spans="1:15">
       <c r="A37" s="12" t="s">
@@ -4343,7 +4337,7 @@
       </c>
       <c r="M37" s="5"/>
       <c r="N37" s="5"/>
-      <c r="O37" s="39"/>
+      <c r="O37" s="36"/>
     </row>
     <row r="38" ht="25" customHeight="1" spans="1:15">
       <c r="A38" s="12" t="s">
@@ -4380,7 +4374,7 @@
       </c>
       <c r="M38" s="5"/>
       <c r="N38" s="5"/>
-      <c r="O38" s="39"/>
+      <c r="O38" s="36"/>
     </row>
     <row r="39" ht="25" customHeight="1" spans="1:15">
       <c r="A39" s="12" t="s">
@@ -4417,7 +4411,7 @@
       </c>
       <c r="M39" s="5"/>
       <c r="N39" s="5"/>
-      <c r="O39" s="39"/>
+      <c r="O39" s="36"/>
     </row>
     <row r="40" ht="25" customHeight="1" spans="1:15">
       <c r="A40" s="12" t="s">
@@ -4454,7 +4448,7 @@
       </c>
       <c r="M40" s="5"/>
       <c r="N40" s="5"/>
-      <c r="O40" s="39"/>
+      <c r="O40" s="36"/>
     </row>
     <row r="41" ht="25" customHeight="1" spans="1:15">
       <c r="A41" s="12" t="s">
@@ -4491,7 +4485,7 @@
       </c>
       <c r="M41" s="5"/>
       <c r="N41" s="5"/>
-      <c r="O41" s="39"/>
+      <c r="O41" s="36"/>
     </row>
     <row r="42" ht="25" customHeight="1" spans="1:15">
       <c r="A42" s="12" t="s">
@@ -4526,7 +4520,7 @@
       </c>
       <c r="M42" s="5"/>
       <c r="N42" s="5"/>
-      <c r="O42" s="39"/>
+      <c r="O42" s="36"/>
     </row>
     <row r="43" ht="25" customHeight="1" spans="1:15">
       <c r="A43" s="12" t="s">
@@ -4563,7 +4557,7 @@
       </c>
       <c r="M43" s="5"/>
       <c r="N43" s="5"/>
-      <c r="O43" s="39"/>
+      <c r="O43" s="36"/>
     </row>
     <row r="44" ht="25" customHeight="1" spans="1:15">
       <c r="A44" s="12" t="s">
@@ -4598,7 +4592,7 @@
       </c>
       <c r="M44" s="5"/>
       <c r="N44" s="5"/>
-      <c r="O44" s="39"/>
+      <c r="O44" s="36"/>
     </row>
     <row r="45" ht="25" customHeight="1" spans="1:15">
       <c r="A45" s="12" t="s">
@@ -4635,7 +4629,7 @@
       </c>
       <c r="M45" s="5"/>
       <c r="N45" s="5"/>
-      <c r="O45" s="39"/>
+      <c r="O45" s="36"/>
     </row>
     <row r="46" ht="25" customHeight="1" spans="1:15">
       <c r="A46" s="12" t="s">
@@ -4658,7 +4652,7 @@
       <c r="L46" s="5"/>
       <c r="M46" s="5"/>
       <c r="N46" s="5"/>
-      <c r="O46" s="39"/>
+      <c r="O46" s="36"/>
     </row>
     <row r="47" ht="25" customHeight="1" spans="1:15">
       <c r="A47" s="12" t="s">
@@ -4681,7 +4675,7 @@
       <c r="L47" s="5"/>
       <c r="M47" s="5"/>
       <c r="N47" s="5"/>
-      <c r="O47" s="39"/>
+      <c r="O47" s="36"/>
     </row>
     <row r="48" ht="25" customHeight="1" spans="1:15">
       <c r="A48" s="12" t="s">
@@ -4704,7 +4698,7 @@
       <c r="L48" s="5"/>
       <c r="M48" s="5"/>
       <c r="N48" s="5"/>
-      <c r="O48" s="39"/>
+      <c r="O48" s="36"/>
     </row>
     <row r="49" ht="25" customHeight="1" spans="1:15">
       <c r="A49" s="12" t="s">
@@ -4727,7 +4721,7 @@
       <c r="L49" s="5"/>
       <c r="M49" s="5"/>
       <c r="N49" s="5"/>
-      <c r="O49" s="39"/>
+      <c r="O49" s="36"/>
     </row>
     <row r="50" ht="25" customHeight="1" spans="1:15">
       <c r="A50" s="14" t="s">
@@ -4736,7 +4730,7 @@
       <c r="B50" s="15"/>
       <c r="C50" s="15"/>
       <c r="D50" s="15"/>
-      <c r="E50" s="28"/>
+      <c r="E50" s="37"/>
       <c r="F50" s="5" t="s">
         <v>33</v>
       </c>
@@ -4750,7 +4744,7 @@
       <c r="L50" s="5"/>
       <c r="M50" s="5"/>
       <c r="N50" s="5"/>
-      <c r="O50" s="39"/>
+      <c r="O50" s="36"/>
     </row>
     <row r="51" ht="25" customHeight="1" spans="1:15">
       <c r="A51" s="12" t="s">
@@ -4773,7 +4767,7 @@
       <c r="L51" s="5"/>
       <c r="M51" s="5"/>
       <c r="N51" s="5"/>
-      <c r="O51" s="39"/>
+      <c r="O51" s="36"/>
     </row>
     <row r="52" ht="25" customHeight="1" spans="1:15">
       <c r="A52" s="12" t="s">
@@ -4796,7 +4790,7 @@
       <c r="L52" s="5"/>
       <c r="M52" s="5"/>
       <c r="N52" s="5"/>
-      <c r="O52" s="39"/>
+      <c r="O52" s="36"/>
     </row>
     <row r="53" ht="25" customHeight="1" spans="1:15">
       <c r="A53" s="12" t="s">
@@ -4819,7 +4813,7 @@
       <c r="L53" s="5"/>
       <c r="M53" s="5"/>
       <c r="N53" s="5"/>
-      <c r="O53" s="39"/>
+      <c r="O53" s="36"/>
     </row>
     <row r="54" ht="25" customHeight="1" spans="1:15">
       <c r="A54" s="12" t="s">
@@ -4841,7 +4835,7 @@
       <c r="L54" s="5"/>
       <c r="M54" s="5"/>
       <c r="N54" s="5"/>
-      <c r="O54" s="39"/>
+      <c r="O54" s="36"/>
     </row>
     <row r="55" ht="25" customHeight="1" spans="1:15">
       <c r="A55" s="12" t="s">
@@ -4864,7 +4858,7 @@
       <c r="L55" s="5"/>
       <c r="M55" s="5"/>
       <c r="N55" s="5"/>
-      <c r="O55" s="39"/>
+      <c r="O55" s="36"/>
     </row>
     <row r="56" ht="25" customHeight="1" spans="1:15">
       <c r="A56" s="12" t="s">
@@ -4887,7 +4881,7 @@
       <c r="L56" s="5"/>
       <c r="M56" s="5"/>
       <c r="N56" s="5"/>
-      <c r="O56" s="39"/>
+      <c r="O56" s="36"/>
     </row>
     <row r="57" ht="25" customHeight="1" spans="1:15">
       <c r="A57" s="12" t="s">
@@ -4910,7 +4904,7 @@
       <c r="L57" s="5"/>
       <c r="M57" s="5"/>
       <c r="N57" s="5"/>
-      <c r="O57" s="39"/>
+      <c r="O57" s="36"/>
     </row>
     <row r="58" ht="25" customHeight="1" spans="1:15">
       <c r="A58" s="12" t="s">
@@ -4932,7 +4926,7 @@
       <c r="L58" s="5"/>
       <c r="M58" s="5"/>
       <c r="N58" s="5"/>
-      <c r="O58" s="39"/>
+      <c r="O58" s="36"/>
     </row>
     <row r="59" ht="25" customHeight="1" spans="1:15">
       <c r="A59" s="12" t="s">
@@ -4955,7 +4949,7 @@
       <c r="L59" s="5"/>
       <c r="M59" s="5"/>
       <c r="N59" s="5"/>
-      <c r="O59" s="39"/>
+      <c r="O59" s="36"/>
     </row>
     <row r="60" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A60" s="12" t="s">
@@ -4978,7 +4972,7 @@
       <c r="L60" s="5"/>
       <c r="M60" s="5"/>
       <c r="N60" s="5"/>
-      <c r="O60" s="39"/>
+      <c r="O60" s="36"/>
     </row>
     <row r="61" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A61" s="12" t="s">
@@ -5001,7 +4995,7 @@
       <c r="L61" s="5"/>
       <c r="M61" s="5"/>
       <c r="N61" s="5"/>
-      <c r="O61" s="39"/>
+      <c r="O61" s="36"/>
     </row>
     <row r="62" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A62" s="12" t="s">
@@ -5024,7 +5018,7 @@
       <c r="L62" s="5"/>
       <c r="M62" s="5"/>
       <c r="N62" s="5"/>
-      <c r="O62" s="39"/>
+      <c r="O62" s="36"/>
     </row>
     <row r="63" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A63" s="12" t="s">
@@ -5047,7 +5041,7 @@
       <c r="L63" s="5"/>
       <c r="M63" s="5"/>
       <c r="N63" s="5"/>
-      <c r="O63" s="39"/>
+      <c r="O63" s="36"/>
     </row>
     <row r="64" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A64" s="12" t="s">
@@ -5078,7 +5072,7 @@
       <c r="L64" s="5"/>
       <c r="M64" s="5"/>
       <c r="N64" s="5"/>
-      <c r="O64" s="39"/>
+      <c r="O64" s="36"/>
     </row>
     <row r="65" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A65" s="12" t="s">
@@ -5140,7 +5134,7 @@
       <c r="L66" s="5"/>
       <c r="M66" s="5"/>
       <c r="N66" s="5"/>
-      <c r="O66" s="39"/>
+      <c r="O66" s="36"/>
     </row>
     <row r="67" ht="25" customHeight="1" spans="1:15">
       <c r="A67" s="12" t="s">
@@ -5171,7 +5165,7 @@
       <c r="L67" s="5"/>
       <c r="M67" s="5"/>
       <c r="N67" s="5"/>
-      <c r="O67" s="39"/>
+      <c r="O67" s="36"/>
     </row>
     <row r="68" ht="25" customHeight="1" spans="1:15">
       <c r="A68" s="12" t="s">
@@ -5202,7 +5196,7 @@
       <c r="L68" s="5"/>
       <c r="M68" s="5"/>
       <c r="N68" s="5"/>
-      <c r="O68" s="39"/>
+      <c r="O68" s="36"/>
     </row>
     <row r="69" ht="25" customHeight="1" spans="1:15">
       <c r="A69" s="12" t="s">
@@ -5233,7 +5227,7 @@
       <c r="L69" s="5"/>
       <c r="M69" s="5"/>
       <c r="N69" s="5"/>
-      <c r="O69" s="39"/>
+      <c r="O69" s="36"/>
     </row>
     <row r="70" ht="25" customHeight="1" spans="1:15">
       <c r="A70" s="12" t="s">
@@ -5242,7 +5236,7 @@
       <c r="B70" s="5" t="s">
         <v>284</v>
       </c>
-      <c r="C70" s="40" t="s">
+      <c r="C70" s="38" t="s">
         <v>285</v>
       </c>
       <c r="D70" s="24" t="s">

--- a/资源录入表新.xlsx
+++ b/资源录入表新.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="861" uniqueCount="296">
   <si>
     <t>剧名</t>
   </si>
@@ -111,6 +111,9 @@
     <t>民国/虐恋</t>
   </si>
   <si>
+    <t>已完结</t>
+  </si>
+  <si>
     <t>张凌赫/王楚然/付辛博</t>
   </si>
   <si>
@@ -136,9 +139,6 @@
   </si>
   <si>
     <t>古装/权谋</t>
-  </si>
-  <si>
-    <t>已完结</t>
   </si>
   <si>
     <t>张赫/徐轸轸</t>
@@ -1462,87 +1462,10 @@
     <t>经典剧</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9.75"/>
-        <color rgb="FF111111"/>
-        <rFont val="Helvetica"/>
-        <charset val="134"/>
-      </rPr>
-      <t>剧情</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.75"/>
-        <color rgb="FF111111"/>
-        <rFont val="Helvetica"/>
-        <charset val="134"/>
-      </rPr>
-      <t> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.75"/>
-        <color rgb="FF111111"/>
-        <rFont val="Helvetica"/>
-        <charset val="134"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.75"/>
-        <color rgb="FF111111"/>
-        <rFont val="Helvetica"/>
-        <charset val="134"/>
-      </rPr>
-      <t> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.75"/>
-        <color rgb="FF111111"/>
-        <rFont val="Helvetica"/>
-        <charset val="134"/>
-      </rPr>
-      <t>悬疑</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.75"/>
-        <color rgb="FF111111"/>
-        <rFont val="Helvetica"/>
-        <charset val="134"/>
-      </rPr>
-      <t> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.75"/>
-        <color rgb="FF111111"/>
-        <rFont val="Helvetica"/>
-        <charset val="134"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.75"/>
-        <color rgb="FF111111"/>
-        <rFont val="Helvetica"/>
-        <charset val="134"/>
-      </rPr>
-      <t> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.75"/>
-        <color rgb="FF111111"/>
-        <rFont val="Helvetica"/>
-        <charset val="134"/>
-      </rPr>
-      <t>犯罪</t>
-    </r>
+    <t>剧情/悬疑/犯罪</t>
+  </si>
+  <si>
+    <t>16集全</t>
   </si>
   <si>
     <t>: 任素汐/王骁/蔡文静/李泽锋/王宥</t>
@@ -1665,10 +1588,11 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9.75"/>
+      <sz val="11"/>
       <color rgb="FF111111"/>
-      <name val="Helvetica"/>
+      <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="major"/>
     </font>
     <font>
       <u/>
@@ -1816,12 +1740,12 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF111111"/>
       <name val="Helvetica"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF111111"/>
       <name val="Helvetica"/>
       <charset val="134"/>
     </font>
@@ -2343,7 +2267,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2419,9 +2343,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2458,8 +2379,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2513,7 +2434,15 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="18">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2707,25 +2636,25 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="6"/>
+      <tableStyleElement type="totalRow" dxfId="5"/>
+      <tableStyleElement type="firstColumn" dxfId="4"/>
+      <tableStyleElement type="lastColumn" dxfId="3"/>
+      <tableStyleElement type="firstRowStripe" dxfId="2"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="1"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="17"/>
+      <tableStyleElement type="totalRow" dxfId="16"/>
+      <tableStyleElement type="firstRowStripe" dxfId="15"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="14"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="13"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="11"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="10"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="9"/>
+      <tableStyleElement type="pageFieldValues" dxfId="8"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -2993,7 +2922,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:O85"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
@@ -3063,8 +2992,8 @@
       <c r="D2" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="25">
-        <v>13</v>
+      <c r="E2" s="8">
+        <v>15</v>
       </c>
       <c r="F2" s="24" t="s">
         <v>15</v>
@@ -3098,8 +3027,8 @@
       <c r="D3" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="25">
-        <v>15</v>
+      <c r="E3" s="8">
+        <v>17</v>
       </c>
       <c r="F3" s="24" t="s">
         <v>15</v>
@@ -3134,24 +3063,24 @@
         <v>14</v>
       </c>
       <c r="E4" s="8">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F4" s="24" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="G4" s="24">
         <v>2026</v>
       </c>
       <c r="H4" s="24" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I4" s="24" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J4" s="13"/>
       <c r="K4" s="13"/>
       <c r="L4" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M4" s="13"/>
       <c r="N4" s="13"/>
@@ -3159,19 +3088,19 @@
     </row>
     <row r="5" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A5" s="23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B5" s="24" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D5" s="24" t="s">
         <v>14</v>
       </c>
       <c r="E5" s="8">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F5" s="24" t="s">
         <v>15</v>
@@ -3180,10 +3109,10 @@
         <v>2026</v>
       </c>
       <c r="H5" s="24" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I5" s="24" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J5" s="13"/>
       <c r="K5" s="13"/>
@@ -3192,15 +3121,15 @@
       <c r="N5" s="13"/>
       <c r="O5" s="13"/>
     </row>
-    <row r="6" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+    <row r="6" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A6" s="23" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B6" s="24" t="s">
         <v>12</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D6" s="24" t="s">
         <v>14</v>
@@ -3208,8 +3137,8 @@
       <c r="E6" s="24">
         <v>24</v>
       </c>
-      <c r="F6" s="26" t="s">
-        <v>33</v>
+      <c r="F6" s="25" t="s">
+        <v>24</v>
       </c>
       <c r="G6" s="24">
         <v>2026</v>
@@ -3234,14 +3163,14 @@
       <c r="B7" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="27" t="s">
+      <c r="C7" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="29">
-        <v>16</v>
+      <c r="D7" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="28">
+        <v>17</v>
       </c>
       <c r="F7" s="13" t="s">
         <v>15</v>
@@ -3263,20 +3192,20 @@
       <c r="O7" s="5"/>
     </row>
     <row r="8" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A8" s="30" t="s">
+      <c r="A8" s="29" t="s">
         <v>40</v>
       </c>
       <c r="B8" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="31" t="s">
+      <c r="C8" s="30" t="s">
         <v>41</v>
       </c>
       <c r="D8" s="24" t="s">
         <v>14</v>
       </c>
       <c r="E8" s="11">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F8" s="13" t="s">
         <v>15</v>
@@ -3284,7 +3213,7 @@
       <c r="G8" s="13">
         <v>2026</v>
       </c>
-      <c r="H8" s="32" t="s">
+      <c r="H8" s="31" t="s">
         <v>42</v>
       </c>
       <c r="I8" s="13" t="s">
@@ -3298,20 +3227,20 @@
       <c r="O8" s="13"/>
     </row>
     <row r="9" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A9" s="30" t="s">
+      <c r="A9" s="29" t="s">
         <v>44</v>
       </c>
       <c r="B9" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="31" t="s">
+      <c r="C9" s="30" t="s">
         <v>45</v>
       </c>
       <c r="D9" s="24" t="s">
         <v>14</v>
       </c>
       <c r="E9" s="11">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F9" s="13" t="s">
         <v>15</v>
@@ -3319,7 +3248,7 @@
       <c r="G9" s="13">
         <v>2026</v>
       </c>
-      <c r="H9" s="32" t="s">
+      <c r="H9" s="31" t="s">
         <v>46</v>
       </c>
       <c r="I9" s="13" t="s">
@@ -3332,7 +3261,7 @@
       <c r="N9" s="13"/>
       <c r="O9" s="13"/>
     </row>
-    <row r="10" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+    <row r="10" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A10" s="23" t="s">
         <v>48</v>
       </c>
@@ -3345,7 +3274,7 @@
       <c r="D10" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="8">
+      <c r="E10" s="24">
         <v>4</v>
       </c>
       <c r="F10" s="24" t="s">
@@ -3367,7 +3296,7 @@
       <c r="N10" s="13"/>
       <c r="O10" s="13"/>
     </row>
-    <row r="11" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+    <row r="11" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A11" s="23" t="s">
         <v>53</v>
       </c>
@@ -3402,14 +3331,14 @@
       <c r="N11" s="13"/>
       <c r="O11" s="13"/>
     </row>
-    <row r="12" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+    <row r="12" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A12" s="23" t="s">
         <v>57</v>
       </c>
       <c r="B12" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="C12" s="33" t="s">
+      <c r="C12" s="32" t="s">
         <v>59</v>
       </c>
       <c r="D12" s="24" t="s">
@@ -3437,21 +3366,21 @@
       <c r="N12" s="13"/>
       <c r="O12" s="13"/>
     </row>
-    <row r="13" s="21" customFormat="1" ht="25" customHeight="1" spans="1:15">
+    <row r="13" s="21" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A13" s="23" t="s">
         <v>62</v>
       </c>
       <c r="B13" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="C13" s="34" t="s">
+      <c r="C13" s="33" t="s">
         <v>63</v>
       </c>
       <c r="D13" s="24" t="s">
         <v>14</v>
       </c>
       <c r="E13" s="24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" s="24" t="s">
         <v>15</v>
@@ -3462,17 +3391,17 @@
       <c r="H13" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="I13" s="26" t="s">
+      <c r="I13" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="J13" s="26"/>
-      <c r="K13" s="26"/>
-      <c r="L13" s="26"/>
-      <c r="M13" s="26"/>
-      <c r="N13" s="26"/>
-      <c r="O13" s="26"/>
-    </row>
-    <row r="14" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="J13" s="25"/>
+      <c r="K13" s="25"/>
+      <c r="L13" s="25"/>
+      <c r="M13" s="25"/>
+      <c r="N13" s="25"/>
+      <c r="O13" s="25"/>
+    </row>
+    <row r="14" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A14" s="23" t="s">
         <v>66</v>
       </c>
@@ -3486,7 +3415,7 @@
         <v>14</v>
       </c>
       <c r="E14" s="24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F14" s="24" t="s">
         <v>15</v>
@@ -3509,7 +3438,7 @@
       <c r="N14" s="13"/>
       <c r="O14" s="13"/>
     </row>
-    <row r="15" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+    <row r="15" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A15" s="23" t="s">
         <v>70</v>
       </c>
@@ -3546,7 +3475,7 @@
       <c r="N15" s="13"/>
       <c r="O15" s="13"/>
     </row>
-    <row r="16" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+    <row r="16" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A16" s="23" t="s">
         <v>75</v>
       </c>
@@ -3583,7 +3512,7 @@
       <c r="N16" s="13"/>
       <c r="O16" s="13"/>
     </row>
-    <row r="17" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+    <row r="17" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A17" s="23" t="s">
         <v>78</v>
       </c>
@@ -3620,7 +3549,7 @@
       <c r="N17" s="13"/>
       <c r="O17" s="13"/>
     </row>
-    <row r="18" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+    <row r="18" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A18" s="23" t="s">
         <v>82</v>
       </c>
@@ -3670,8 +3599,8 @@
       <c r="D19" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E19" s="24">
-        <v>4</v>
+      <c r="E19" s="8">
+        <v>6</v>
       </c>
       <c r="F19" s="24" t="s">
         <v>15</v>
@@ -3707,8 +3636,8 @@
       <c r="D20" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E20" s="24">
-        <v>8</v>
+      <c r="E20" s="8">
+        <v>9</v>
       </c>
       <c r="F20" s="24" t="s">
         <v>15</v>
@@ -3731,7 +3660,7 @@
       <c r="N20" s="13"/>
       <c r="O20" s="13"/>
     </row>
-    <row r="21" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+    <row r="21" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A21" s="23" t="s">
         <v>95</v>
       </c>
@@ -3764,7 +3693,7 @@
       <c r="N21" s="13"/>
       <c r="O21" s="13"/>
     </row>
-    <row r="22" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+    <row r="22" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A22" s="23" t="s">
         <v>98</v>
       </c>
@@ -3796,22 +3725,22 @@
       <c r="N22" s="13"/>
       <c r="O22" s="13"/>
     </row>
-    <row r="23" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A23" s="30" t="s">
+    <row r="23" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="A23" s="29" t="s">
         <v>101</v>
       </c>
       <c r="B23" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="C23" s="26" t="s">
+      <c r="C23" s="25" t="s">
         <v>102</v>
       </c>
       <c r="D23" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E23" s="26"/>
-      <c r="F23" s="26" t="s">
-        <v>33</v>
+      <c r="E23" s="25"/>
+      <c r="F23" s="25" t="s">
+        <v>24</v>
       </c>
       <c r="G23" s="24">
         <v>2026</v>
@@ -3825,24 +3754,24 @@
       <c r="L23" s="13"/>
       <c r="M23" s="13"/>
       <c r="N23" s="13"/>
-      <c r="O23" s="35"/>
-    </row>
-    <row r="24" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A24" s="30" t="s">
+      <c r="O23" s="34"/>
+    </row>
+    <row r="24" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="A24" s="29" t="s">
         <v>104</v>
       </c>
       <c r="B24" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="C24" s="26" t="s">
+      <c r="C24" s="25" t="s">
         <v>102</v>
       </c>
       <c r="D24" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E24" s="26"/>
-      <c r="F24" s="26" t="s">
-        <v>33</v>
+      <c r="E24" s="25"/>
+      <c r="F24" s="25" t="s">
+        <v>24</v>
       </c>
       <c r="G24" s="24">
         <v>2026</v>
@@ -3856,9 +3785,9 @@
       <c r="L24" s="13"/>
       <c r="M24" s="13"/>
       <c r="N24" s="13"/>
-      <c r="O24" s="35"/>
-    </row>
-    <row r="25" ht="25" customHeight="1" spans="1:15">
+      <c r="O24" s="34"/>
+    </row>
+    <row r="25" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A25" s="12" t="s">
         <v>106</v>
       </c>
@@ -3875,7 +3804,7 @@
         <v>108</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G25" s="5">
         <v>2026</v>
@@ -3895,7 +3824,7 @@
       <c r="N25" s="5"/>
       <c r="O25" s="5"/>
     </row>
-    <row r="26" ht="25" customHeight="1" spans="1:15">
+    <row r="26" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A26" s="12" t="s">
         <v>112</v>
       </c>
@@ -3912,7 +3841,7 @@
         <v>114</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G26" s="5">
         <v>2025</v>
@@ -3932,7 +3861,7 @@
       <c r="N26" s="5"/>
       <c r="O26" s="5"/>
     </row>
-    <row r="27" ht="25" customHeight="1" spans="1:15">
+    <row r="27" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A27" s="12" t="s">
         <v>118</v>
       </c>
@@ -3949,7 +3878,7 @@
         <v>120</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G27" s="5">
         <v>2026</v>
@@ -3969,7 +3898,7 @@
       <c r="N27" s="5"/>
       <c r="O27" s="5"/>
     </row>
-    <row r="28" ht="25" customHeight="1" spans="1:15">
+    <row r="28" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A28" s="12" t="s">
         <v>124</v>
       </c>
@@ -3986,7 +3915,7 @@
         <v>126</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G28" s="5">
         <v>2026</v>
@@ -4006,7 +3935,7 @@
       <c r="N28" s="5"/>
       <c r="O28" s="5"/>
     </row>
-    <row r="29" ht="25" customHeight="1" spans="1:15">
+    <row r="29" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A29" s="12" t="s">
         <v>130</v>
       </c>
@@ -4023,7 +3952,7 @@
         <v>132</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G29" s="5">
         <v>2025</v>
@@ -4043,7 +3972,7 @@
       <c r="N29" s="5"/>
       <c r="O29" s="5"/>
     </row>
-    <row r="30" ht="25" customHeight="1" spans="1:15">
+    <row r="30" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A30" s="12" t="s">
         <v>136</v>
       </c>
@@ -4060,7 +3989,7 @@
         <v>138</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G30" s="5">
         <v>2026</v>
@@ -4080,7 +4009,7 @@
       <c r="N30" s="15"/>
       <c r="O30" s="5"/>
     </row>
-    <row r="31" ht="25" customHeight="1" spans="1:15">
+    <row r="31" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A31" s="12" t="s">
         <v>142</v>
       </c>
@@ -4097,7 +4026,7 @@
         <v>144</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G31" s="5">
         <v>2026</v>
@@ -4115,9 +4044,9 @@
       </c>
       <c r="M31" s="5"/>
       <c r="N31" s="5"/>
-      <c r="O31" s="36"/>
-    </row>
-    <row r="32" ht="25" customHeight="1" spans="1:15">
+      <c r="O31" s="35"/>
+    </row>
+    <row r="32" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A32" s="12" t="s">
         <v>148</v>
       </c>
@@ -4134,7 +4063,7 @@
         <v>150</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G32" s="5">
         <v>2024</v>
@@ -4152,9 +4081,9 @@
       </c>
       <c r="M32" s="5"/>
       <c r="N32" s="5"/>
-      <c r="O32" s="36"/>
-    </row>
-    <row r="33" ht="25" customHeight="1" spans="1:15">
+      <c r="O32" s="35"/>
+    </row>
+    <row r="33" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A33" s="12" t="s">
         <v>154</v>
       </c>
@@ -4171,7 +4100,7 @@
         <v>156</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G33" s="5">
         <v>2024</v>
@@ -4189,9 +4118,9 @@
       </c>
       <c r="M33" s="5"/>
       <c r="N33" s="5"/>
-      <c r="O33" s="36"/>
-    </row>
-    <row r="34" ht="25" customHeight="1" spans="1:15">
+      <c r="O33" s="35"/>
+    </row>
+    <row r="34" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A34" s="12" t="s">
         <v>160</v>
       </c>
@@ -4208,7 +4137,7 @@
         <v>126</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G34" s="5">
         <v>2026</v>
@@ -4226,9 +4155,9 @@
       </c>
       <c r="M34" s="5"/>
       <c r="N34" s="5"/>
-      <c r="O34" s="36"/>
-    </row>
-    <row r="35" ht="25" customHeight="1" spans="1:15">
+      <c r="O34" s="35"/>
+    </row>
+    <row r="35" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A35" s="12" t="s">
         <v>164</v>
       </c>
@@ -4245,7 +4174,7 @@
         <v>166</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G35" s="5">
         <v>2025</v>
@@ -4263,9 +4192,9 @@
       </c>
       <c r="M35" s="5"/>
       <c r="N35" s="5"/>
-      <c r="O35" s="36"/>
-    </row>
-    <row r="36" ht="25" customHeight="1" spans="1:15">
+      <c r="O35" s="35"/>
+    </row>
+    <row r="36" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A36" s="12" t="s">
         <v>170</v>
       </c>
@@ -4282,7 +4211,7 @@
         <v>144</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G36" s="5">
         <v>2026</v>
@@ -4300,9 +4229,9 @@
       </c>
       <c r="M36" s="5"/>
       <c r="N36" s="5"/>
-      <c r="O36" s="36"/>
-    </row>
-    <row r="37" ht="25" customHeight="1" spans="1:15">
+      <c r="O36" s="35"/>
+    </row>
+    <row r="37" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A37" s="12" t="s">
         <v>175</v>
       </c>
@@ -4319,7 +4248,7 @@
         <v>144</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G37" s="5">
         <v>2026</v>
@@ -4337,9 +4266,9 @@
       </c>
       <c r="M37" s="5"/>
       <c r="N37" s="5"/>
-      <c r="O37" s="36"/>
-    </row>
-    <row r="38" ht="25" customHeight="1" spans="1:15">
+      <c r="O37" s="35"/>
+    </row>
+    <row r="38" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A38" s="12" t="s">
         <v>180</v>
       </c>
@@ -4356,7 +4285,7 @@
         <v>108</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G38" s="5">
         <v>2026</v>
@@ -4374,9 +4303,9 @@
       </c>
       <c r="M38" s="5"/>
       <c r="N38" s="5"/>
-      <c r="O38" s="36"/>
-    </row>
-    <row r="39" ht="25" customHeight="1" spans="1:15">
+      <c r="O38" s="35"/>
+    </row>
+    <row r="39" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A39" s="12" t="s">
         <v>185</v>
       </c>
@@ -4393,7 +4322,7 @@
         <v>186</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G39" s="5">
         <v>2025</v>
@@ -4411,9 +4340,9 @@
       </c>
       <c r="M39" s="5"/>
       <c r="N39" s="5"/>
-      <c r="O39" s="36"/>
-    </row>
-    <row r="40" ht="25" customHeight="1" spans="1:15">
+      <c r="O39" s="35"/>
+    </row>
+    <row r="40" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A40" s="12" t="s">
         <v>190</v>
       </c>
@@ -4430,7 +4359,7 @@
         <v>192</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G40" s="5">
         <v>2026</v>
@@ -4448,9 +4377,9 @@
       </c>
       <c r="M40" s="5"/>
       <c r="N40" s="5"/>
-      <c r="O40" s="36"/>
-    </row>
-    <row r="41" ht="25" customHeight="1" spans="1:15">
+      <c r="O40" s="35"/>
+    </row>
+    <row r="41" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A41" s="12" t="s">
         <v>196</v>
       </c>
@@ -4467,7 +4396,7 @@
         <v>114</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G41" s="5">
         <v>2026</v>
@@ -4485,9 +4414,9 @@
       </c>
       <c r="M41" s="5"/>
       <c r="N41" s="5"/>
-      <c r="O41" s="36"/>
-    </row>
-    <row r="42" ht="25" customHeight="1" spans="1:15">
+      <c r="O41" s="35"/>
+    </row>
+    <row r="42" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A42" s="12" t="s">
         <v>201</v>
       </c>
@@ -4504,7 +4433,7 @@
         <v>203</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G42" s="5">
         <v>2025</v>
@@ -4520,9 +4449,9 @@
       </c>
       <c r="M42" s="5"/>
       <c r="N42" s="5"/>
-      <c r="O42" s="36"/>
-    </row>
-    <row r="43" ht="25" customHeight="1" spans="1:15">
+      <c r="O42" s="35"/>
+    </row>
+    <row r="43" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A43" s="12" t="s">
         <v>205</v>
       </c>
@@ -4539,7 +4468,7 @@
         <v>207</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G43" s="5">
         <v>2025</v>
@@ -4557,9 +4486,9 @@
       </c>
       <c r="M43" s="5"/>
       <c r="N43" s="5"/>
-      <c r="O43" s="36"/>
-    </row>
-    <row r="44" ht="25" customHeight="1" spans="1:15">
+      <c r="O43" s="35"/>
+    </row>
+    <row r="44" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A44" s="12" t="s">
         <v>211</v>
       </c>
@@ -4576,7 +4505,7 @@
         <v>203</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G44" s="5">
         <v>2025</v>
@@ -4592,9 +4521,9 @@
       </c>
       <c r="M44" s="5"/>
       <c r="N44" s="5"/>
-      <c r="O44" s="36"/>
-    </row>
-    <row r="45" ht="25" customHeight="1" spans="1:15">
+      <c r="O44" s="35"/>
+    </row>
+    <row r="45" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A45" s="12" t="s">
         <v>214</v>
       </c>
@@ -4611,7 +4540,7 @@
         <v>120</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G45" s="5">
         <v>2026</v>
@@ -4629,9 +4558,9 @@
       </c>
       <c r="M45" s="5"/>
       <c r="N45" s="5"/>
-      <c r="O45" s="36"/>
-    </row>
-    <row r="46" ht="25" customHeight="1" spans="1:15">
+      <c r="O45" s="35"/>
+    </row>
+    <row r="46" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A46" s="12" t="s">
         <v>220</v>
       </c>
@@ -4640,7 +4569,7 @@
       <c r="D46" s="5"/>
       <c r="E46" s="13"/>
       <c r="F46" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G46" s="5"/>
       <c r="H46" s="5"/>
@@ -4652,9 +4581,9 @@
       <c r="L46" s="5"/>
       <c r="M46" s="5"/>
       <c r="N46" s="5"/>
-      <c r="O46" s="36"/>
-    </row>
-    <row r="47" ht="25" customHeight="1" spans="1:15">
+      <c r="O46" s="35"/>
+    </row>
+    <row r="47" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A47" s="12" t="s">
         <v>222</v>
       </c>
@@ -4663,7 +4592,7 @@
       <c r="D47" s="5"/>
       <c r="E47" s="13"/>
       <c r="F47" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G47" s="5"/>
       <c r="H47" s="5"/>
@@ -4675,9 +4604,9 @@
       <c r="L47" s="5"/>
       <c r="M47" s="5"/>
       <c r="N47" s="5"/>
-      <c r="O47" s="36"/>
-    </row>
-    <row r="48" ht="25" customHeight="1" spans="1:15">
+      <c r="O47" s="35"/>
+    </row>
+    <row r="48" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A48" s="12" t="s">
         <v>224</v>
       </c>
@@ -4686,7 +4615,7 @@
       <c r="D48" s="5"/>
       <c r="E48" s="13"/>
       <c r="F48" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G48" s="5"/>
       <c r="H48" s="5"/>
@@ -4698,9 +4627,9 @@
       <c r="L48" s="5"/>
       <c r="M48" s="5"/>
       <c r="N48" s="5"/>
-      <c r="O48" s="36"/>
-    </row>
-    <row r="49" ht="25" customHeight="1" spans="1:15">
+      <c r="O48" s="35"/>
+    </row>
+    <row r="49" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A49" s="12" t="s">
         <v>226</v>
       </c>
@@ -4709,7 +4638,7 @@
       <c r="D49" s="5"/>
       <c r="E49" s="13"/>
       <c r="F49" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G49" s="5"/>
       <c r="H49" s="5"/>
@@ -4721,18 +4650,18 @@
       <c r="L49" s="5"/>
       <c r="M49" s="5"/>
       <c r="N49" s="5"/>
-      <c r="O49" s="36"/>
-    </row>
-    <row r="50" ht="25" customHeight="1" spans="1:15">
+      <c r="O49" s="35"/>
+    </row>
+    <row r="50" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A50" s="14" t="s">
         <v>228</v>
       </c>
       <c r="B50" s="15"/>
       <c r="C50" s="15"/>
       <c r="D50" s="15"/>
-      <c r="E50" s="37"/>
+      <c r="E50" s="36"/>
       <c r="F50" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G50" s="15"/>
       <c r="H50" s="15"/>
@@ -4744,9 +4673,9 @@
       <c r="L50" s="5"/>
       <c r="M50" s="5"/>
       <c r="N50" s="5"/>
-      <c r="O50" s="36"/>
-    </row>
-    <row r="51" ht="25" customHeight="1" spans="1:15">
+      <c r="O50" s="35"/>
+    </row>
+    <row r="51" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A51" s="12" t="s">
         <v>230</v>
       </c>
@@ -4755,7 +4684,7 @@
       <c r="D51" s="5"/>
       <c r="E51" s="13"/>
       <c r="F51" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G51" s="5"/>
       <c r="H51" s="5"/>
@@ -4767,9 +4696,9 @@
       <c r="L51" s="5"/>
       <c r="M51" s="5"/>
       <c r="N51" s="5"/>
-      <c r="O51" s="36"/>
-    </row>
-    <row r="52" ht="25" customHeight="1" spans="1:15">
+      <c r="O51" s="35"/>
+    </row>
+    <row r="52" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A52" s="12" t="s">
         <v>232</v>
       </c>
@@ -4778,7 +4707,7 @@
       <c r="D52" s="5"/>
       <c r="E52" s="13"/>
       <c r="F52" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G52" s="5"/>
       <c r="H52" s="5"/>
@@ -4790,9 +4719,9 @@
       <c r="L52" s="5"/>
       <c r="M52" s="5"/>
       <c r="N52" s="5"/>
-      <c r="O52" s="36"/>
-    </row>
-    <row r="53" ht="25" customHeight="1" spans="1:15">
+      <c r="O52" s="35"/>
+    </row>
+    <row r="53" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A53" s="12" t="s">
         <v>234</v>
       </c>
@@ -4801,7 +4730,7 @@
       <c r="D53" s="5"/>
       <c r="E53" s="13"/>
       <c r="F53" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G53" s="5"/>
       <c r="H53" s="5"/>
@@ -4813,9 +4742,9 @@
       <c r="L53" s="5"/>
       <c r="M53" s="5"/>
       <c r="N53" s="5"/>
-      <c r="O53" s="36"/>
-    </row>
-    <row r="54" ht="25" customHeight="1" spans="1:15">
+      <c r="O53" s="35"/>
+    </row>
+    <row r="54" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A54" s="12" t="s">
         <v>236</v>
       </c>
@@ -4824,7 +4753,7 @@
       <c r="D54" s="5"/>
       <c r="E54" s="13"/>
       <c r="F54" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G54" s="5"/>
       <c r="I54" s="5" t="s">
@@ -4835,9 +4764,9 @@
       <c r="L54" s="5"/>
       <c r="M54" s="5"/>
       <c r="N54" s="5"/>
-      <c r="O54" s="36"/>
-    </row>
-    <row r="55" ht="25" customHeight="1" spans="1:15">
+      <c r="O54" s="35"/>
+    </row>
+    <row r="55" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A55" s="12" t="s">
         <v>238</v>
       </c>
@@ -4846,7 +4775,7 @@
       <c r="D55" s="5"/>
       <c r="E55" s="13"/>
       <c r="F55" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G55" s="5"/>
       <c r="H55" s="5"/>
@@ -4858,9 +4787,9 @@
       <c r="L55" s="5"/>
       <c r="M55" s="5"/>
       <c r="N55" s="5"/>
-      <c r="O55" s="36"/>
-    </row>
-    <row r="56" ht="25" customHeight="1" spans="1:15">
+      <c r="O55" s="35"/>
+    </row>
+    <row r="56" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A56" s="12" t="s">
         <v>240</v>
       </c>
@@ -4869,7 +4798,7 @@
       <c r="D56" s="5"/>
       <c r="E56" s="13"/>
       <c r="F56" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G56" s="5"/>
       <c r="H56" s="5"/>
@@ -4881,9 +4810,9 @@
       <c r="L56" s="5"/>
       <c r="M56" s="5"/>
       <c r="N56" s="5"/>
-      <c r="O56" s="36"/>
-    </row>
-    <row r="57" ht="25" customHeight="1" spans="1:15">
+      <c r="O56" s="35"/>
+    </row>
+    <row r="57" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A57" s="12" t="s">
         <v>242</v>
       </c>
@@ -4892,7 +4821,7 @@
       <c r="D57" s="5"/>
       <c r="E57" s="13"/>
       <c r="F57" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G57" s="5"/>
       <c r="H57" s="5"/>
@@ -4904,9 +4833,9 @@
       <c r="L57" s="5"/>
       <c r="M57" s="5"/>
       <c r="N57" s="5"/>
-      <c r="O57" s="36"/>
-    </row>
-    <row r="58" ht="25" customHeight="1" spans="1:15">
+      <c r="O57" s="35"/>
+    </row>
+    <row r="58" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A58" s="12" t="s">
         <v>244</v>
       </c>
@@ -4915,7 +4844,7 @@
       <c r="D58" s="5"/>
       <c r="E58" s="13"/>
       <c r="F58" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G58" s="5"/>
       <c r="I58" s="5" t="s">
@@ -4926,9 +4855,9 @@
       <c r="L58" s="5"/>
       <c r="M58" s="5"/>
       <c r="N58" s="5"/>
-      <c r="O58" s="36"/>
-    </row>
-    <row r="59" ht="25" customHeight="1" spans="1:15">
+      <c r="O58" s="35"/>
+    </row>
+    <row r="59" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A59" s="12" t="s">
         <v>246</v>
       </c>
@@ -4937,7 +4866,7 @@
       <c r="D59" s="5"/>
       <c r="E59" s="13"/>
       <c r="F59" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G59" s="5"/>
       <c r="H59" s="5"/>
@@ -4949,9 +4878,9 @@
       <c r="L59" s="5"/>
       <c r="M59" s="5"/>
       <c r="N59" s="5"/>
-      <c r="O59" s="36"/>
-    </row>
-    <row r="60" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="O59" s="35"/>
+    </row>
+    <row r="60" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A60" s="12" t="s">
         <v>248</v>
       </c>
@@ -4960,7 +4889,7 @@
       <c r="D60" s="5"/>
       <c r="E60" s="13"/>
       <c r="F60" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G60" s="5"/>
       <c r="H60" s="5"/>
@@ -4972,9 +4901,9 @@
       <c r="L60" s="5"/>
       <c r="M60" s="5"/>
       <c r="N60" s="5"/>
-      <c r="O60" s="36"/>
-    </row>
-    <row r="61" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="O60" s="35"/>
+    </row>
+    <row r="61" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A61" s="12" t="s">
         <v>250</v>
       </c>
@@ -4983,7 +4912,7 @@
       <c r="D61" s="5"/>
       <c r="E61" s="13"/>
       <c r="F61" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G61" s="5"/>
       <c r="H61" s="5"/>
@@ -4995,9 +4924,9 @@
       <c r="L61" s="5"/>
       <c r="M61" s="5"/>
       <c r="N61" s="5"/>
-      <c r="O61" s="36"/>
-    </row>
-    <row r="62" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="O61" s="35"/>
+    </row>
+    <row r="62" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A62" s="12" t="s">
         <v>252</v>
       </c>
@@ -5006,7 +4935,7 @@
       <c r="D62" s="5"/>
       <c r="E62" s="13"/>
       <c r="F62" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G62" s="5"/>
       <c r="H62" s="5"/>
@@ -5018,9 +4947,9 @@
       <c r="L62" s="5"/>
       <c r="M62" s="5"/>
       <c r="N62" s="5"/>
-      <c r="O62" s="36"/>
-    </row>
-    <row r="63" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="O62" s="35"/>
+    </row>
+    <row r="63" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A63" s="12" t="s">
         <v>254</v>
       </c>
@@ -5029,7 +4958,7 @@
       <c r="D63" s="5"/>
       <c r="E63" s="13"/>
       <c r="F63" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G63" s="5"/>
       <c r="H63" s="5"/>
@@ -5041,9 +4970,9 @@
       <c r="L63" s="5"/>
       <c r="M63" s="5"/>
       <c r="N63" s="5"/>
-      <c r="O63" s="36"/>
-    </row>
-    <row r="64" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="O63" s="35"/>
+    </row>
+    <row r="64" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A64" s="12" t="s">
         <v>256</v>
       </c>
@@ -5058,7 +4987,7 @@
         <v>258</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G64" s="5"/>
       <c r="H64" s="18" t="s">
@@ -5072,9 +5001,9 @@
       <c r="L64" s="5"/>
       <c r="M64" s="5"/>
       <c r="N64" s="5"/>
-      <c r="O64" s="36"/>
-    </row>
-    <row r="65" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="O64" s="35"/>
+    </row>
+    <row r="65" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A65" s="12" t="s">
         <v>261</v>
       </c>
@@ -5089,7 +5018,7 @@
         <v>120</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G65" s="5"/>
       <c r="H65" s="18" t="s">
@@ -5105,7 +5034,7 @@
       <c r="N65" s="5"/>
       <c r="O65" s="5"/>
     </row>
-    <row r="66" customFormat="1" ht="25" customHeight="1" spans="1:15">
+    <row r="66" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A66" s="12" t="s">
         <v>265</v>
       </c>
@@ -5120,7 +5049,7 @@
         <v>126</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G66" s="5"/>
       <c r="H66" s="18" t="s">
@@ -5134,9 +5063,9 @@
       <c r="L66" s="5"/>
       <c r="M66" s="5"/>
       <c r="N66" s="5"/>
-      <c r="O66" s="36"/>
-    </row>
-    <row r="67" ht="25" customHeight="1" spans="1:15">
+      <c r="O66" s="35"/>
+    </row>
+    <row r="67" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A67" s="12" t="s">
         <v>269</v>
       </c>
@@ -5151,7 +5080,7 @@
         <v>271</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G67" s="5"/>
       <c r="H67" s="18" t="s">
@@ -5165,9 +5094,9 @@
       <c r="L67" s="5"/>
       <c r="M67" s="5"/>
       <c r="N67" s="5"/>
-      <c r="O67" s="36"/>
-    </row>
-    <row r="68" ht="25" customHeight="1" spans="1:15">
+      <c r="O67" s="35"/>
+    </row>
+    <row r="68" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A68" s="12" t="s">
         <v>274</v>
       </c>
@@ -5182,7 +5111,7 @@
         <v>271</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G68" s="5"/>
       <c r="H68" s="18" t="s">
@@ -5196,9 +5125,9 @@
       <c r="L68" s="5"/>
       <c r="M68" s="5"/>
       <c r="N68" s="5"/>
-      <c r="O68" s="36"/>
-    </row>
-    <row r="69" ht="25" customHeight="1" spans="1:15">
+      <c r="O68" s="35"/>
+    </row>
+    <row r="69" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A69" s="12" t="s">
         <v>278</v>
       </c>
@@ -5213,7 +5142,7 @@
         <v>280</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G69" s="5"/>
       <c r="H69" s="18" t="s">
@@ -5227,35 +5156,35 @@
       <c r="L69" s="5"/>
       <c r="M69" s="5"/>
       <c r="N69" s="5"/>
-      <c r="O69" s="36"/>
-    </row>
-    <row r="70" ht="25" customHeight="1" spans="1:15">
+      <c r="O69" s="35"/>
+    </row>
+    <row r="70" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A70" s="12" t="s">
         <v>283</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>284</v>
       </c>
-      <c r="C70" s="38" t="s">
+      <c r="C70" s="37" t="s">
         <v>285</v>
       </c>
       <c r="D70" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E70" s="13">
-        <v>16</v>
+      <c r="E70" s="13" t="s">
+        <v>286</v>
       </c>
       <c r="F70" s="13" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G70" s="24">
         <v>2026</v>
       </c>
       <c r="H70" s="5" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="I70" s="5" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="J70" s="5"/>
       <c r="K70" s="5"/>
@@ -5518,6 +5447,9 @@
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:O70" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="4">
+      <colorFilter dxfId="0"/>
+    </filterColumn>
     <sortState ref="A1:O70">
       <sortCondition ref="F1"/>
     </sortState>
@@ -5549,7 +5481,7 @@
   <sheetData>
     <row r="1" ht="33" customHeight="1" spans="1:9">
       <c r="A1" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -5596,7 +5528,7 @@
         <v>12</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>14</v>
@@ -5669,21 +5601,21 @@
         <v>2026</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:9">
       <c r="A6" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>14</v>
@@ -5698,21 +5630,21 @@
         <v>2026</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:9">
       <c r="A7" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>14</v>
@@ -6056,14 +5988,14 @@
         <v>49</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>14</v>
       </c>
       <c r="E19" s="10"/>
       <c r="F19" s="10" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G19" s="7">
         <v>2026</v>
@@ -6081,14 +6013,14 @@
         <v>49</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>14</v>
       </c>
       <c r="E20" s="10"/>
       <c r="F20" s="10" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G20" s="7">
         <v>2026</v>
@@ -6115,7 +6047,7 @@
         <v>108</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G21" s="5">
         <v>2026</v>
@@ -6144,7 +6076,7 @@
         <v>114</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G22" s="5">
         <v>2025</v>
@@ -6173,7 +6105,7 @@
         <v>120</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G23" s="5">
         <v>2026</v>
@@ -6202,7 +6134,7 @@
         <v>126</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G24" s="5">
         <v>2026</v>
@@ -6231,7 +6163,7 @@
         <v>132</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G25" s="5">
         <v>2025</v>
@@ -6260,7 +6192,7 @@
         <v>138</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G26" s="5">
         <v>2026</v>
@@ -6289,7 +6221,7 @@
         <v>144</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G27" s="5">
         <v>2026</v>
@@ -6318,7 +6250,7 @@
         <v>150</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G28" s="5">
         <v>2024</v>
@@ -6347,7 +6279,7 @@
         <v>156</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G29" s="5">
         <v>2024</v>
@@ -6376,7 +6308,7 @@
         <v>126</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G30" s="5">
         <v>2026</v>
@@ -6405,7 +6337,7 @@
         <v>166</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G31" s="5">
         <v>2025</v>
@@ -6434,7 +6366,7 @@
         <v>144</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G32" s="5">
         <v>2026</v>
@@ -6463,7 +6395,7 @@
         <v>144</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G33" s="5">
         <v>2026</v>
@@ -6492,7 +6424,7 @@
         <v>108</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G34" s="5">
         <v>2026</v>
@@ -6521,7 +6453,7 @@
         <v>186</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G35" s="5">
         <v>2025</v>
@@ -6550,7 +6482,7 @@
         <v>192</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G36" s="5">
         <v>2026</v>
@@ -6579,7 +6511,7 @@
         <v>114</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G37" s="5">
         <v>2026</v>
@@ -6608,7 +6540,7 @@
         <v>203</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G38" s="5">
         <v>2025</v>
@@ -6635,7 +6567,7 @@
         <v>207</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G39" s="5">
         <v>2025</v>
@@ -6664,7 +6596,7 @@
         <v>203</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G40" s="5">
         <v>2025</v>
@@ -6691,7 +6623,7 @@
         <v>120</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G41" s="5">
         <v>2026</v>
@@ -6712,7 +6644,7 @@
       <c r="D42" s="5"/>
       <c r="E42" s="5"/>
       <c r="F42" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G42" s="5"/>
       <c r="H42" s="5"/>
@@ -6729,7 +6661,7 @@
       <c r="D43" s="5"/>
       <c r="E43" s="5"/>
       <c r="F43" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G43" s="5"/>
       <c r="H43" s="5"/>
@@ -6746,7 +6678,7 @@
       <c r="D44" s="5"/>
       <c r="E44" s="5"/>
       <c r="F44" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G44" s="5"/>
       <c r="H44" s="5"/>
@@ -6763,7 +6695,7 @@
       <c r="D45" s="5"/>
       <c r="E45" s="5"/>
       <c r="F45" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G45" s="5"/>
       <c r="H45" s="5"/>
@@ -6780,7 +6712,7 @@
       <c r="D46" s="15"/>
       <c r="E46" s="15"/>
       <c r="F46" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G46" s="15"/>
       <c r="H46" s="15"/>
@@ -6797,7 +6729,7 @@
       <c r="D47" s="5"/>
       <c r="E47" s="5"/>
       <c r="F47" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G47" s="5"/>
       <c r="H47" s="5"/>
@@ -6814,7 +6746,7 @@
       <c r="D48" s="5"/>
       <c r="E48" s="5"/>
       <c r="F48" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G48" s="5"/>
       <c r="H48" s="5"/>
@@ -6831,7 +6763,7 @@
       <c r="D49" s="5"/>
       <c r="E49" s="5"/>
       <c r="F49" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G49" s="5"/>
       <c r="H49" s="5"/>
@@ -6848,7 +6780,7 @@
       <c r="D50" s="5"/>
       <c r="E50" s="5"/>
       <c r="F50" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G50" s="5"/>
       <c r="H50" s="5"/>
@@ -6865,7 +6797,7 @@
       <c r="D51" s="5"/>
       <c r="E51" s="5"/>
       <c r="F51" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G51" s="5"/>
       <c r="H51" s="5"/>
@@ -6882,7 +6814,7 @@
       <c r="D52" s="5"/>
       <c r="E52" s="5"/>
       <c r="F52" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G52" s="5"/>
       <c r="H52" s="5"/>
@@ -6905,7 +6837,7 @@
         <v>258</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G53" s="5"/>
       <c r="H53" s="18" t="s">
@@ -6930,7 +6862,7 @@
         <v>120</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G54" s="5"/>
       <c r="H54" s="18" t="s">
@@ -6955,11 +6887,11 @@
         <v>126</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G55" s="5"/>
       <c r="H55" s="18" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="I55" s="5" t="s">
         <v>268</v>
@@ -6980,11 +6912,11 @@
         <v>271</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G56" s="5"/>
       <c r="H56" s="18" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="I56" s="5" t="s">
         <v>273</v>
@@ -7005,11 +6937,11 @@
         <v>271</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G57" s="5"/>
       <c r="H57" s="18" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="I57" s="5" t="s">
         <v>277</v>
@@ -7030,11 +6962,11 @@
         <v>280</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G58" s="5"/>
       <c r="H58" s="18" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I58" s="5" t="s">
         <v>282</v>
@@ -7049,7 +6981,7 @@
       <c r="D59" s="5"/>
       <c r="E59" s="5"/>
       <c r="F59" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G59" s="5"/>
       <c r="H59" s="5"/>
@@ -7066,7 +6998,7 @@
       <c r="D60" s="5"/>
       <c r="E60" s="5"/>
       <c r="F60" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G60" s="5"/>
       <c r="H60" s="5"/>
@@ -7083,7 +7015,7 @@
       <c r="D61" s="5"/>
       <c r="E61" s="5"/>
       <c r="F61" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G61" s="5"/>
       <c r="H61" s="5"/>
@@ -7100,7 +7032,7 @@
       <c r="D62" s="5"/>
       <c r="E62" s="5"/>
       <c r="F62" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G62" s="5"/>
       <c r="H62" s="5"/>
@@ -7117,7 +7049,7 @@
       <c r="D63" s="5"/>
       <c r="E63" s="5"/>
       <c r="F63" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G63" s="5"/>
       <c r="H63" s="5"/>
@@ -7134,7 +7066,7 @@
       <c r="D64" s="5"/>
       <c r="E64" s="5"/>
       <c r="F64" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G64" s="5"/>
       <c r="H64" s="5"/>
@@ -7151,7 +7083,7 @@
       <c r="D65" s="5"/>
       <c r="E65" s="5"/>
       <c r="F65" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G65" s="5"/>
       <c r="H65" s="5"/>

--- a/资源录入表新.xlsx
+++ b/资源录入表新.xlsx
@@ -1739,9 +1739,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF111111"/>
-      <name val="Helvetica"/>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1750,13 +1754,9 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="宋体"/>
+      <sz val="11"/>
+      <color rgb="FF111111"/>
+      <name val="Helvetica"/>
       <charset val="134"/>
     </font>
     <font>
@@ -2267,7 +2267,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2339,6 +2339,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2434,15 +2437,7 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="18">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2636,25 +2631,25 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="7"/>
-      <tableStyleElement type="headerRow" dxfId="6"/>
-      <tableStyleElement type="totalRow" dxfId="5"/>
-      <tableStyleElement type="firstColumn" dxfId="4"/>
-      <tableStyleElement type="lastColumn" dxfId="3"/>
-      <tableStyleElement type="firstRowStripe" dxfId="2"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="1"/>
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="17"/>
-      <tableStyleElement type="totalRow" dxfId="16"/>
-      <tableStyleElement type="firstRowStripe" dxfId="15"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="14"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="13"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="11"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="10"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="9"/>
-      <tableStyleElement type="pageFieldValues" dxfId="8"/>
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -2993,7 +2988,7 @@
         <v>14</v>
       </c>
       <c r="E2" s="8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F2" s="24" t="s">
         <v>15</v>
@@ -3028,7 +3023,7 @@
         <v>14</v>
       </c>
       <c r="E3" s="8">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F3" s="24" t="s">
         <v>15</v>
@@ -3049,7 +3044,7 @@
       <c r="N3" s="13"/>
       <c r="O3" s="13"/>
     </row>
-    <row r="4" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+    <row r="4" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A4" s="23" t="s">
         <v>22</v>
       </c>
@@ -3062,7 +3057,7 @@
       <c r="D4" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="25">
         <v>33</v>
       </c>
       <c r="F4" s="24" t="s">
@@ -3100,10 +3095,10 @@
         <v>14</v>
       </c>
       <c r="E5" s="8">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F5" s="24" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="G5" s="24">
         <v>2026</v>
@@ -3137,7 +3132,7 @@
       <c r="E6" s="24">
         <v>24</v>
       </c>
-      <c r="F6" s="25" t="s">
+      <c r="F6" s="26" t="s">
         <v>24</v>
       </c>
       <c r="G6" s="24">
@@ -3163,17 +3158,17 @@
       <c r="B7" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="26" t="s">
+      <c r="C7" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="28">
-        <v>17</v>
-      </c>
-      <c r="F7" s="13" t="s">
-        <v>15</v>
+      <c r="D7" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="29">
+        <v>18</v>
+      </c>
+      <c r="F7" s="24" t="s">
+        <v>24</v>
       </c>
       <c r="G7" s="5">
         <v>2026</v>
@@ -3192,20 +3187,20 @@
       <c r="O7" s="5"/>
     </row>
     <row r="8" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A8" s="29" t="s">
+      <c r="A8" s="30" t="s">
         <v>40</v>
       </c>
       <c r="B8" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="30" t="s">
+      <c r="C8" s="31" t="s">
         <v>41</v>
       </c>
       <c r="D8" s="24" t="s">
         <v>14</v>
       </c>
       <c r="E8" s="11">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F8" s="13" t="s">
         <v>15</v>
@@ -3213,7 +3208,7 @@
       <c r="G8" s="13">
         <v>2026</v>
       </c>
-      <c r="H8" s="31" t="s">
+      <c r="H8" s="32" t="s">
         <v>42</v>
       </c>
       <c r="I8" s="13" t="s">
@@ -3227,20 +3222,20 @@
       <c r="O8" s="13"/>
     </row>
     <row r="9" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A9" s="29" t="s">
+      <c r="A9" s="30" t="s">
         <v>44</v>
       </c>
       <c r="B9" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="30" t="s">
+      <c r="C9" s="31" t="s">
         <v>45</v>
       </c>
       <c r="D9" s="24" t="s">
         <v>14</v>
       </c>
       <c r="E9" s="11">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F9" s="13" t="s">
         <v>15</v>
@@ -3248,7 +3243,7 @@
       <c r="G9" s="13">
         <v>2026</v>
       </c>
-      <c r="H9" s="31" t="s">
+      <c r="H9" s="32" t="s">
         <v>46</v>
       </c>
       <c r="I9" s="13" t="s">
@@ -3261,7 +3256,7 @@
       <c r="N9" s="13"/>
       <c r="O9" s="13"/>
     </row>
-    <row r="10" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
+    <row r="10" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A10" s="23" t="s">
         <v>48</v>
       </c>
@@ -3296,7 +3291,7 @@
       <c r="N10" s="13"/>
       <c r="O10" s="13"/>
     </row>
-    <row r="11" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
+    <row r="11" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A11" s="23" t="s">
         <v>53</v>
       </c>
@@ -3331,14 +3326,14 @@
       <c r="N11" s="13"/>
       <c r="O11" s="13"/>
     </row>
-    <row r="12" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
+    <row r="12" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A12" s="23" t="s">
         <v>57</v>
       </c>
       <c r="B12" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="C12" s="32" t="s">
+      <c r="C12" s="33" t="s">
         <v>59</v>
       </c>
       <c r="D12" s="24" t="s">
@@ -3366,14 +3361,14 @@
       <c r="N12" s="13"/>
       <c r="O12" s="13"/>
     </row>
-    <row r="13" s="21" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
+    <row r="13" s="21" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A13" s="23" t="s">
         <v>62</v>
       </c>
       <c r="B13" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="C13" s="33" t="s">
+      <c r="C13" s="34" t="s">
         <v>63</v>
       </c>
       <c r="D13" s="24" t="s">
@@ -3391,17 +3386,17 @@
       <c r="H13" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="I13" s="25" t="s">
+      <c r="I13" s="26" t="s">
         <v>65</v>
       </c>
-      <c r="J13" s="25"/>
-      <c r="K13" s="25"/>
-      <c r="L13" s="25"/>
-      <c r="M13" s="25"/>
-      <c r="N13" s="25"/>
-      <c r="O13" s="25"/>
-    </row>
-    <row r="14" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="J13" s="26"/>
+      <c r="K13" s="26"/>
+      <c r="L13" s="26"/>
+      <c r="M13" s="26"/>
+      <c r="N13" s="26"/>
+      <c r="O13" s="26"/>
+    </row>
+    <row r="14" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A14" s="23" t="s">
         <v>66</v>
       </c>
@@ -3438,7 +3433,7 @@
       <c r="N14" s="13"/>
       <c r="O14" s="13"/>
     </row>
-    <row r="15" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
+    <row r="15" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A15" s="23" t="s">
         <v>70</v>
       </c>
@@ -3475,7 +3470,7 @@
       <c r="N15" s="13"/>
       <c r="O15" s="13"/>
     </row>
-    <row r="16" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
+    <row r="16" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A16" s="23" t="s">
         <v>75</v>
       </c>
@@ -3512,7 +3507,7 @@
       <c r="N16" s="13"/>
       <c r="O16" s="13"/>
     </row>
-    <row r="17" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
+    <row r="17" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A17" s="23" t="s">
         <v>78</v>
       </c>
@@ -3549,7 +3544,7 @@
       <c r="N17" s="13"/>
       <c r="O17" s="13"/>
     </row>
-    <row r="18" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
+    <row r="18" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A18" s="23" t="s">
         <v>82</v>
       </c>
@@ -3599,7 +3594,7 @@
       <c r="D19" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E19" s="8">
+      <c r="E19" s="25">
         <v>6</v>
       </c>
       <c r="F19" s="24" t="s">
@@ -3636,7 +3631,7 @@
       <c r="D20" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E20" s="8">
+      <c r="E20" s="25">
         <v>9</v>
       </c>
       <c r="F20" s="24" t="s">
@@ -3660,7 +3655,7 @@
       <c r="N20" s="13"/>
       <c r="O20" s="13"/>
     </row>
-    <row r="21" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
+    <row r="21" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A21" s="23" t="s">
         <v>95</v>
       </c>
@@ -3693,7 +3688,7 @@
       <c r="N21" s="13"/>
       <c r="O21" s="13"/>
     </row>
-    <row r="22" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
+    <row r="22" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A22" s="23" t="s">
         <v>98</v>
       </c>
@@ -3726,20 +3721,20 @@
       <c r="O22" s="13"/>
     </row>
     <row r="23" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A23" s="29" t="s">
+      <c r="A23" s="30" t="s">
         <v>101</v>
       </c>
       <c r="B23" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="C23" s="25" t="s">
+      <c r="C23" s="26" t="s">
         <v>102</v>
       </c>
       <c r="D23" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E23" s="25"/>
-      <c r="F23" s="25" t="s">
+      <c r="E23" s="26"/>
+      <c r="F23" s="26" t="s">
         <v>24</v>
       </c>
       <c r="G23" s="24">
@@ -3754,23 +3749,23 @@
       <c r="L23" s="13"/>
       <c r="M23" s="13"/>
       <c r="N23" s="13"/>
-      <c r="O23" s="34"/>
+      <c r="O23" s="35"/>
     </row>
     <row r="24" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A24" s="29" t="s">
+      <c r="A24" s="30" t="s">
         <v>104</v>
       </c>
       <c r="B24" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="C24" s="25" t="s">
+      <c r="C24" s="26" t="s">
         <v>102</v>
       </c>
       <c r="D24" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E24" s="25"/>
-      <c r="F24" s="25" t="s">
+      <c r="E24" s="26"/>
+      <c r="F24" s="26" t="s">
         <v>24</v>
       </c>
       <c r="G24" s="24">
@@ -3785,7 +3780,7 @@
       <c r="L24" s="13"/>
       <c r="M24" s="13"/>
       <c r="N24" s="13"/>
-      <c r="O24" s="34"/>
+      <c r="O24" s="35"/>
     </row>
     <row r="25" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A25" s="12" t="s">
@@ -4044,7 +4039,7 @@
       </c>
       <c r="M31" s="5"/>
       <c r="N31" s="5"/>
-      <c r="O31" s="35"/>
+      <c r="O31" s="36"/>
     </row>
     <row r="32" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A32" s="12" t="s">
@@ -4081,7 +4076,7 @@
       </c>
       <c r="M32" s="5"/>
       <c r="N32" s="5"/>
-      <c r="O32" s="35"/>
+      <c r="O32" s="36"/>
     </row>
     <row r="33" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A33" s="12" t="s">
@@ -4118,7 +4113,7 @@
       </c>
       <c r="M33" s="5"/>
       <c r="N33" s="5"/>
-      <c r="O33" s="35"/>
+      <c r="O33" s="36"/>
     </row>
     <row r="34" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A34" s="12" t="s">
@@ -4155,7 +4150,7 @@
       </c>
       <c r="M34" s="5"/>
       <c r="N34" s="5"/>
-      <c r="O34" s="35"/>
+      <c r="O34" s="36"/>
     </row>
     <row r="35" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A35" s="12" t="s">
@@ -4192,7 +4187,7 @@
       </c>
       <c r="M35" s="5"/>
       <c r="N35" s="5"/>
-      <c r="O35" s="35"/>
+      <c r="O35" s="36"/>
     </row>
     <row r="36" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A36" s="12" t="s">
@@ -4229,7 +4224,7 @@
       </c>
       <c r="M36" s="5"/>
       <c r="N36" s="5"/>
-      <c r="O36" s="35"/>
+      <c r="O36" s="36"/>
     </row>
     <row r="37" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A37" s="12" t="s">
@@ -4266,7 +4261,7 @@
       </c>
       <c r="M37" s="5"/>
       <c r="N37" s="5"/>
-      <c r="O37" s="35"/>
+      <c r="O37" s="36"/>
     </row>
     <row r="38" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A38" s="12" t="s">
@@ -4303,7 +4298,7 @@
       </c>
       <c r="M38" s="5"/>
       <c r="N38" s="5"/>
-      <c r="O38" s="35"/>
+      <c r="O38" s="36"/>
     </row>
     <row r="39" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A39" s="12" t="s">
@@ -4340,7 +4335,7 @@
       </c>
       <c r="M39" s="5"/>
       <c r="N39" s="5"/>
-      <c r="O39" s="35"/>
+      <c r="O39" s="36"/>
     </row>
     <row r="40" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A40" s="12" t="s">
@@ -4377,7 +4372,7 @@
       </c>
       <c r="M40" s="5"/>
       <c r="N40" s="5"/>
-      <c r="O40" s="35"/>
+      <c r="O40" s="36"/>
     </row>
     <row r="41" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A41" s="12" t="s">
@@ -4414,7 +4409,7 @@
       </c>
       <c r="M41" s="5"/>
       <c r="N41" s="5"/>
-      <c r="O41" s="35"/>
+      <c r="O41" s="36"/>
     </row>
     <row r="42" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A42" s="12" t="s">
@@ -4449,7 +4444,7 @@
       </c>
       <c r="M42" s="5"/>
       <c r="N42" s="5"/>
-      <c r="O42" s="35"/>
+      <c r="O42" s="36"/>
     </row>
     <row r="43" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A43" s="12" t="s">
@@ -4486,7 +4481,7 @@
       </c>
       <c r="M43" s="5"/>
       <c r="N43" s="5"/>
-      <c r="O43" s="35"/>
+      <c r="O43" s="36"/>
     </row>
     <row r="44" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A44" s="12" t="s">
@@ -4521,7 +4516,7 @@
       </c>
       <c r="M44" s="5"/>
       <c r="N44" s="5"/>
-      <c r="O44" s="35"/>
+      <c r="O44" s="36"/>
     </row>
     <row r="45" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A45" s="12" t="s">
@@ -4558,7 +4553,7 @@
       </c>
       <c r="M45" s="5"/>
       <c r="N45" s="5"/>
-      <c r="O45" s="35"/>
+      <c r="O45" s="36"/>
     </row>
     <row r="46" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A46" s="12" t="s">
@@ -4581,7 +4576,7 @@
       <c r="L46" s="5"/>
       <c r="M46" s="5"/>
       <c r="N46" s="5"/>
-      <c r="O46" s="35"/>
+      <c r="O46" s="36"/>
     </row>
     <row r="47" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A47" s="12" t="s">
@@ -4604,7 +4599,7 @@
       <c r="L47" s="5"/>
       <c r="M47" s="5"/>
       <c r="N47" s="5"/>
-      <c r="O47" s="35"/>
+      <c r="O47" s="36"/>
     </row>
     <row r="48" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A48" s="12" t="s">
@@ -4627,7 +4622,7 @@
       <c r="L48" s="5"/>
       <c r="M48" s="5"/>
       <c r="N48" s="5"/>
-      <c r="O48" s="35"/>
+      <c r="O48" s="36"/>
     </row>
     <row r="49" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A49" s="12" t="s">
@@ -4650,7 +4645,7 @@
       <c r="L49" s="5"/>
       <c r="M49" s="5"/>
       <c r="N49" s="5"/>
-      <c r="O49" s="35"/>
+      <c r="O49" s="36"/>
     </row>
     <row r="50" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A50" s="14" t="s">
@@ -4659,7 +4654,7 @@
       <c r="B50" s="15"/>
       <c r="C50" s="15"/>
       <c r="D50" s="15"/>
-      <c r="E50" s="36"/>
+      <c r="E50" s="37"/>
       <c r="F50" s="5" t="s">
         <v>24</v>
       </c>
@@ -4673,7 +4668,7 @@
       <c r="L50" s="5"/>
       <c r="M50" s="5"/>
       <c r="N50" s="5"/>
-      <c r="O50" s="35"/>
+      <c r="O50" s="36"/>
     </row>
     <row r="51" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A51" s="12" t="s">
@@ -4696,7 +4691,7 @@
       <c r="L51" s="5"/>
       <c r="M51" s="5"/>
       <c r="N51" s="5"/>
-      <c r="O51" s="35"/>
+      <c r="O51" s="36"/>
     </row>
     <row r="52" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A52" s="12" t="s">
@@ -4719,7 +4714,7 @@
       <c r="L52" s="5"/>
       <c r="M52" s="5"/>
       <c r="N52" s="5"/>
-      <c r="O52" s="35"/>
+      <c r="O52" s="36"/>
     </row>
     <row r="53" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A53" s="12" t="s">
@@ -4742,7 +4737,7 @@
       <c r="L53" s="5"/>
       <c r="M53" s="5"/>
       <c r="N53" s="5"/>
-      <c r="O53" s="35"/>
+      <c r="O53" s="36"/>
     </row>
     <row r="54" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A54" s="12" t="s">
@@ -4764,7 +4759,7 @@
       <c r="L54" s="5"/>
       <c r="M54" s="5"/>
       <c r="N54" s="5"/>
-      <c r="O54" s="35"/>
+      <c r="O54" s="36"/>
     </row>
     <row r="55" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A55" s="12" t="s">
@@ -4787,7 +4782,7 @@
       <c r="L55" s="5"/>
       <c r="M55" s="5"/>
       <c r="N55" s="5"/>
-      <c r="O55" s="35"/>
+      <c r="O55" s="36"/>
     </row>
     <row r="56" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A56" s="12" t="s">
@@ -4810,7 +4805,7 @@
       <c r="L56" s="5"/>
       <c r="M56" s="5"/>
       <c r="N56" s="5"/>
-      <c r="O56" s="35"/>
+      <c r="O56" s="36"/>
     </row>
     <row r="57" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A57" s="12" t="s">
@@ -4833,7 +4828,7 @@
       <c r="L57" s="5"/>
       <c r="M57" s="5"/>
       <c r="N57" s="5"/>
-      <c r="O57" s="35"/>
+      <c r="O57" s="36"/>
     </row>
     <row r="58" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A58" s="12" t="s">
@@ -4855,7 +4850,7 @@
       <c r="L58" s="5"/>
       <c r="M58" s="5"/>
       <c r="N58" s="5"/>
-      <c r="O58" s="35"/>
+      <c r="O58" s="36"/>
     </row>
     <row r="59" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A59" s="12" t="s">
@@ -4878,7 +4873,7 @@
       <c r="L59" s="5"/>
       <c r="M59" s="5"/>
       <c r="N59" s="5"/>
-      <c r="O59" s="35"/>
+      <c r="O59" s="36"/>
     </row>
     <row r="60" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A60" s="12" t="s">
@@ -4901,7 +4896,7 @@
       <c r="L60" s="5"/>
       <c r="M60" s="5"/>
       <c r="N60" s="5"/>
-      <c r="O60" s="35"/>
+      <c r="O60" s="36"/>
     </row>
     <row r="61" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A61" s="12" t="s">
@@ -4924,7 +4919,7 @@
       <c r="L61" s="5"/>
       <c r="M61" s="5"/>
       <c r="N61" s="5"/>
-      <c r="O61" s="35"/>
+      <c r="O61" s="36"/>
     </row>
     <row r="62" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A62" s="12" t="s">
@@ -4947,7 +4942,7 @@
       <c r="L62" s="5"/>
       <c r="M62" s="5"/>
       <c r="N62" s="5"/>
-      <c r="O62" s="35"/>
+      <c r="O62" s="36"/>
     </row>
     <row r="63" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A63" s="12" t="s">
@@ -4970,7 +4965,7 @@
       <c r="L63" s="5"/>
       <c r="M63" s="5"/>
       <c r="N63" s="5"/>
-      <c r="O63" s="35"/>
+      <c r="O63" s="36"/>
     </row>
     <row r="64" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A64" s="12" t="s">
@@ -5001,7 +4996,7 @@
       <c r="L64" s="5"/>
       <c r="M64" s="5"/>
       <c r="N64" s="5"/>
-      <c r="O64" s="35"/>
+      <c r="O64" s="36"/>
     </row>
     <row r="65" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A65" s="12" t="s">
@@ -5063,7 +5058,7 @@
       <c r="L66" s="5"/>
       <c r="M66" s="5"/>
       <c r="N66" s="5"/>
-      <c r="O66" s="35"/>
+      <c r="O66" s="36"/>
     </row>
     <row r="67" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A67" s="12" t="s">
@@ -5094,7 +5089,7 @@
       <c r="L67" s="5"/>
       <c r="M67" s="5"/>
       <c r="N67" s="5"/>
-      <c r="O67" s="35"/>
+      <c r="O67" s="36"/>
     </row>
     <row r="68" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A68" s="12" t="s">
@@ -5125,7 +5120,7 @@
       <c r="L68" s="5"/>
       <c r="M68" s="5"/>
       <c r="N68" s="5"/>
-      <c r="O68" s="35"/>
+      <c r="O68" s="36"/>
     </row>
     <row r="69" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A69" s="12" t="s">
@@ -5156,7 +5151,7 @@
       <c r="L69" s="5"/>
       <c r="M69" s="5"/>
       <c r="N69" s="5"/>
-      <c r="O69" s="35"/>
+      <c r="O69" s="36"/>
     </row>
     <row r="70" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A70" s="12" t="s">
@@ -5165,7 +5160,7 @@
       <c r="B70" s="5" t="s">
         <v>284</v>
       </c>
-      <c r="C70" s="37" t="s">
+      <c r="C70" s="38" t="s">
         <v>285</v>
       </c>
       <c r="D70" s="24" t="s">
@@ -5447,8 +5442,10 @@
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:O70" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="4">
-      <colorFilter dxfId="0"/>
+    <filterColumn colId="5">
+      <filters>
+        <filter val="更新中"/>
+      </filters>
     </filterColumn>
     <sortState ref="A1:O70">
       <sortCondition ref="F1"/>

--- a/资源录入表新.xlsx
+++ b/资源录入表新.xlsx
@@ -16,7 +16,7 @@
     <sheet name="资源录入表 (2)" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">资源录入表!$A$1:$O$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">资源录入表!$A$1:$O$71</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'资源录入表 (2)'!$A$2:$I$20</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="861" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="868" uniqueCount="300">
   <si>
     <t>剧名</t>
   </si>
@@ -442,10 +442,99 @@
     <t xml:space="preserve">链接: https://pan.baidu.com/s/1xgB5NP2JFKwnC0tnE_vV-Q 提取码: grug </t>
   </si>
   <si>
+    <t>财阀X刑警 第二季</t>
+  </si>
+  <si>
+    <t>韩剧</t>
+  </si>
+  <si>
+    <r>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF111111"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>剧情</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>安普贤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>郑恩彩</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>姜相准</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>金伸比</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>俞承豪</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1wgjy7lmRdrram3NRT7dqUQ 提取码: 6tsv </t>
+  </si>
+  <si>
     <t>杀手妈咪</t>
-  </si>
-  <si>
-    <t>韩剧</t>
   </si>
   <si>
     <r>
@@ -1739,16 +1828,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="11"/>
       <name val="Helvetica"/>
       <charset val="134"/>
@@ -1766,6 +1845,16 @@
     </font>
     <font>
       <sz val="10.5"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -2343,43 +2432,43 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2917,8 +3006,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:O85"/>
+  <sheetPr/>
+  <dimension ref="A1:O86"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="17.625" style="2" customWidth="1"/>
@@ -2988,7 +3077,7 @@
         <v>14</v>
       </c>
       <c r="E2" s="8">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F2" s="24" t="s">
         <v>15</v>
@@ -3023,7 +3112,7 @@
         <v>14</v>
       </c>
       <c r="E3" s="8">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F3" s="24" t="s">
         <v>15</v>
@@ -3044,7 +3133,7 @@
       <c r="N3" s="13"/>
       <c r="O3" s="13"/>
     </row>
-    <row r="4" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
+    <row r="4" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A4" s="23" t="s">
         <v>22</v>
       </c>
@@ -3057,7 +3146,7 @@
       <c r="D4" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="25">
+      <c r="E4" s="24">
         <v>33</v>
       </c>
       <c r="F4" s="24" t="s">
@@ -3094,7 +3183,7 @@
       <c r="D5" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="24">
         <v>36</v>
       </c>
       <c r="F5" s="24" t="s">
@@ -3116,7 +3205,7 @@
       <c r="N5" s="13"/>
       <c r="O5" s="13"/>
     </row>
-    <row r="6" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
+    <row r="6" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A6" s="23" t="s">
         <v>32</v>
       </c>
@@ -3132,7 +3221,7 @@
       <c r="E6" s="24">
         <v>24</v>
       </c>
-      <c r="F6" s="26" t="s">
+      <c r="F6" s="25" t="s">
         <v>24</v>
       </c>
       <c r="G6" s="24">
@@ -3158,13 +3247,13 @@
       <c r="B7" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="27" t="s">
+      <c r="C7" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="29">
+      <c r="D7" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="28">
         <v>18</v>
       </c>
       <c r="F7" s="24" t="s">
@@ -3187,20 +3276,20 @@
       <c r="O7" s="5"/>
     </row>
     <row r="8" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A8" s="30" t="s">
+      <c r="A8" s="29" t="s">
         <v>40</v>
       </c>
       <c r="B8" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="31" t="s">
+      <c r="C8" s="30" t="s">
         <v>41</v>
       </c>
       <c r="D8" s="24" t="s">
         <v>14</v>
       </c>
       <c r="E8" s="11">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F8" s="13" t="s">
         <v>15</v>
@@ -3208,7 +3297,7 @@
       <c r="G8" s="13">
         <v>2026</v>
       </c>
-      <c r="H8" s="32" t="s">
+      <c r="H8" s="31" t="s">
         <v>42</v>
       </c>
       <c r="I8" s="13" t="s">
@@ -3222,20 +3311,20 @@
       <c r="O8" s="13"/>
     </row>
     <row r="9" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A9" s="30" t="s">
+      <c r="A9" s="29" t="s">
         <v>44</v>
       </c>
       <c r="B9" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="31" t="s">
+      <c r="C9" s="30" t="s">
         <v>45</v>
       </c>
       <c r="D9" s="24" t="s">
         <v>14</v>
       </c>
       <c r="E9" s="11">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F9" s="13" t="s">
         <v>15</v>
@@ -3243,7 +3332,7 @@
       <c r="G9" s="13">
         <v>2026</v>
       </c>
-      <c r="H9" s="32" t="s">
+      <c r="H9" s="31" t="s">
         <v>46</v>
       </c>
       <c r="I9" s="13" t="s">
@@ -3304,8 +3393,8 @@
       <c r="D11" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E11" s="24">
-        <v>4</v>
+      <c r="E11" s="8">
+        <v>5</v>
       </c>
       <c r="F11" s="24" t="s">
         <v>15</v>
@@ -3327,31 +3416,31 @@
       <c r="O11" s="13"/>
     </row>
     <row r="12" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A12" s="23" t="s">
+      <c r="A12" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="B12" s="24" t="s">
+      <c r="B12" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="C12" s="33" t="s">
+      <c r="C12" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="D12" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="E12" s="24">
-        <v>2</v>
-      </c>
-      <c r="F12" s="24" t="s">
+      <c r="D12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="8">
+        <v>1</v>
+      </c>
+      <c r="F12" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G12" s="24">
+      <c r="G12" s="8">
         <v>2026</v>
       </c>
-      <c r="H12" s="24" t="s">
+      <c r="H12" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="I12" s="13" t="s">
+      <c r="I12" s="11" t="s">
         <v>61</v>
       </c>
       <c r="J12" s="13"/>
@@ -3361,21 +3450,21 @@
       <c r="N12" s="13"/>
       <c r="O12" s="13"/>
     </row>
-    <row r="13" s="21" customFormat="1" ht="25" customHeight="1" spans="1:15">
+    <row r="13" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A13" s="23" t="s">
         <v>62</v>
       </c>
       <c r="B13" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="C13" s="34" t="s">
+      <c r="C13" s="33" t="s">
         <v>63</v>
       </c>
       <c r="D13" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E13" s="24">
-        <v>2</v>
+      <c r="E13" s="8">
+        <v>3</v>
       </c>
       <c r="F13" s="24" t="s">
         <v>15</v>
@@ -3386,31 +3475,31 @@
       <c r="H13" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="I13" s="26" t="s">
+      <c r="I13" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="J13" s="26"/>
-      <c r="K13" s="26"/>
-      <c r="L13" s="26"/>
-      <c r="M13" s="26"/>
-      <c r="N13" s="26"/>
-      <c r="O13" s="26"/>
-    </row>
-    <row r="14" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="J13" s="13"/>
+      <c r="K13" s="13"/>
+      <c r="L13" s="13"/>
+      <c r="M13" s="13"/>
+      <c r="N13" s="13"/>
+      <c r="O13" s="13"/>
+    </row>
+    <row r="14" s="21" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A14" s="23" t="s">
         <v>66</v>
       </c>
       <c r="B14" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="C14" s="24" t="s">
+      <c r="C14" s="34" t="s">
         <v>67</v>
       </c>
       <c r="D14" s="24" t="s">
         <v>14</v>
       </c>
       <c r="E14" s="24">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F14" s="24" t="s">
         <v>15</v>
@@ -3421,33 +3510,31 @@
       <c r="H14" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="I14" s="24" t="s">
+      <c r="I14" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="J14" s="13"/>
-      <c r="K14" s="13"/>
-      <c r="L14" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="M14" s="13"/>
-      <c r="N14" s="13"/>
-      <c r="O14" s="13"/>
+      <c r="J14" s="25"/>
+      <c r="K14" s="25"/>
+      <c r="L14" s="25"/>
+      <c r="M14" s="25"/>
+      <c r="N14" s="25"/>
+      <c r="O14" s="25"/>
     </row>
     <row r="15" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A15" s="23" t="s">
         <v>70</v>
       </c>
       <c r="B15" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15" s="24" t="s">
         <v>71</v>
       </c>
-      <c r="C15" s="24" t="s">
-        <v>72</v>
-      </c>
       <c r="D15" s="24" t="s">
         <v>14</v>
       </c>
       <c r="E15" s="24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F15" s="24" t="s">
         <v>15</v>
@@ -3456,10 +3543,10 @@
         <v>2026</v>
       </c>
       <c r="H15" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="I15" s="24" t="s">
         <v>73</v>
-      </c>
-      <c r="I15" s="24" t="s">
-        <v>74</v>
       </c>
       <c r="J15" s="13"/>
       <c r="K15" s="13"/>
@@ -3472,19 +3559,19 @@
     </row>
     <row r="16" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A16" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="B16" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="B16" s="24" t="s">
-        <v>58</v>
-      </c>
       <c r="C16" s="24" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="D16" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E16" s="24">
-        <v>6</v>
+      <c r="E16" s="8">
+        <v>8</v>
       </c>
       <c r="F16" s="24" t="s">
         <v>15</v>
@@ -3493,10 +3580,10 @@
         <v>2026</v>
       </c>
       <c r="H16" s="24" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I16" s="24" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J16" s="13"/>
       <c r="K16" s="13"/>
@@ -3509,19 +3596,19 @@
     </row>
     <row r="17" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A17" s="23" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B17" s="24" t="s">
         <v>58</v>
       </c>
       <c r="C17" s="24" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="D17" s="24" t="s">
         <v>14</v>
       </c>
       <c r="E17" s="24">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F17" s="24" t="s">
         <v>15</v>
@@ -3557,8 +3644,8 @@
       <c r="D18" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E18" s="24">
-        <v>10</v>
+      <c r="E18" s="35">
+        <v>8</v>
       </c>
       <c r="F18" s="24" t="s">
         <v>15</v>
@@ -3594,8 +3681,8 @@
       <c r="D19" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E19" s="25">
-        <v>6</v>
+      <c r="E19" s="35">
+        <v>10</v>
       </c>
       <c r="F19" s="24" t="s">
         <v>15</v>
@@ -3612,7 +3699,7 @@
       <c r="J19" s="13"/>
       <c r="K19" s="13"/>
       <c r="L19" s="13" t="s">
-        <v>90</v>
+        <v>58</v>
       </c>
       <c r="M19" s="13"/>
       <c r="N19" s="13"/>
@@ -3620,19 +3707,19 @@
     </row>
     <row r="20" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A20" s="23" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B20" s="24" t="s">
         <v>58</v>
       </c>
       <c r="C20" s="24" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D20" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E20" s="25">
-        <v>9</v>
+      <c r="E20" s="24">
+        <v>6</v>
       </c>
       <c r="F20" s="24" t="s">
         <v>15</v>
@@ -3641,15 +3728,15 @@
         <v>2026</v>
       </c>
       <c r="H20" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="I20" s="24" t="s">
         <v>93</v>
-      </c>
-      <c r="I20" s="24" t="s">
-        <v>94</v>
       </c>
       <c r="J20" s="13"/>
       <c r="K20" s="13"/>
       <c r="L20" s="13" t="s">
-        <v>58</v>
+        <v>94</v>
       </c>
       <c r="M20" s="13"/>
       <c r="N20" s="13"/>
@@ -3660,7 +3747,7 @@
         <v>95</v>
       </c>
       <c r="B21" s="24" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="C21" s="24" t="s">
         <v>96</v>
@@ -3669,40 +3756,44 @@
         <v>14</v>
       </c>
       <c r="E21" s="24">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F21" s="24" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="G21" s="24">
         <v>2026</v>
       </c>
-      <c r="H21" s="24"/>
+      <c r="H21" s="24" t="s">
+        <v>97</v>
+      </c>
       <c r="I21" s="24" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J21" s="13"/>
       <c r="K21" s="13"/>
-      <c r="L21" s="13"/>
+      <c r="L21" s="13" t="s">
+        <v>58</v>
+      </c>
       <c r="M21" s="13"/>
       <c r="N21" s="13"/>
       <c r="O21" s="13"/>
     </row>
     <row r="22" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A22" s="23" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B22" s="24" t="s">
         <v>49</v>
       </c>
       <c r="C22" s="24" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D22" s="24" t="s">
         <v>14</v>
       </c>
       <c r="E22" s="24">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F22" s="24" t="s">
         <v>15</v>
@@ -3710,8 +3801,9 @@
       <c r="G22" s="24">
         <v>2026</v>
       </c>
+      <c r="H22" s="24"/>
       <c r="I22" s="24" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J22" s="13"/>
       <c r="K22" s="13"/>
@@ -3720,52 +3812,53 @@
       <c r="N22" s="13"/>
       <c r="O22" s="13"/>
     </row>
-    <row r="23" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A23" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B23" s="13" t="s">
+    <row r="23" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A23" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="B23" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="C23" s="26" t="s">
-        <v>102</v>
+      <c r="C23" s="24" t="s">
+        <v>103</v>
       </c>
       <c r="D23" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E23" s="26"/>
-      <c r="F23" s="26" t="s">
-        <v>24</v>
+      <c r="E23" s="24">
+        <v>5</v>
+      </c>
+      <c r="F23" s="24" t="s">
+        <v>15</v>
       </c>
       <c r="G23" s="24">
         <v>2026</v>
       </c>
-      <c r="H23" s="24"/>
-      <c r="I23" s="13" t="s">
-        <v>103</v>
+      <c r="I23" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="J23" s="13"/>
       <c r="K23" s="13"/>
       <c r="L23" s="13"/>
       <c r="M23" s="13"/>
       <c r="N23" s="13"/>
-      <c r="O23" s="35"/>
-    </row>
-    <row r="24" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A24" s="30" t="s">
-        <v>104</v>
+      <c r="O23" s="13"/>
+    </row>
+    <row r="24" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A24" s="29" t="s">
+        <v>105</v>
       </c>
       <c r="B24" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="C24" s="26" t="s">
-        <v>102</v>
+      <c r="C24" s="25" t="s">
+        <v>106</v>
       </c>
       <c r="D24" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E24" s="26"/>
-      <c r="F24" s="26" t="s">
+      <c r="E24" s="25"/>
+      <c r="F24" s="25" t="s">
         <v>24</v>
       </c>
       <c r="G24" s="24">
@@ -3773,141 +3866,135 @@
       </c>
       <c r="H24" s="24"/>
       <c r="I24" s="13" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="J24" s="13"/>
       <c r="K24" s="13"/>
       <c r="L24" s="13"/>
       <c r="M24" s="13"/>
       <c r="N24" s="13"/>
-      <c r="O24" s="35"/>
-    </row>
-    <row r="25" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A25" s="12" t="s">
+      <c r="O24" s="36"/>
+    </row>
+    <row r="25" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A25" s="29" t="s">
+        <v>108</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="C25" s="25" t="s">
         <v>106</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G25" s="5">
+      <c r="D25" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E25" s="25"/>
+      <c r="F25" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="G25" s="24">
         <v>2026</v>
       </c>
-      <c r="H25" s="5" t="s">
+      <c r="H25" s="24"/>
+      <c r="I25" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="I25" s="1" t="s">
+      <c r="J25" s="13"/>
+      <c r="K25" s="13"/>
+      <c r="L25" s="13"/>
+      <c r="M25" s="13"/>
+      <c r="N25" s="13"/>
+      <c r="O25" s="36"/>
+    </row>
+    <row r="26" ht="25" customHeight="1" spans="1:15">
+      <c r="A26" s="12" t="s">
         <v>110</v>
-      </c>
-      <c r="J25" s="5"/>
-      <c r="K25" s="5"/>
-      <c r="L25" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="M25" s="5"/>
-      <c r="N25" s="5"/>
-      <c r="O25" s="5"/>
-    </row>
-    <row r="26" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A26" s="12" t="s">
-        <v>112</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C26" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E26" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G26" s="5">
+        <v>2026</v>
+      </c>
+      <c r="H26" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="D26" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E26" s="13" t="s">
+      <c r="I26" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G26" s="5">
-        <v>2025</v>
-      </c>
-      <c r="H26" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>116</v>
       </c>
       <c r="J26" s="5"/>
       <c r="K26" s="5"/>
       <c r="L26" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="M26" s="5"/>
       <c r="N26" s="5"/>
       <c r="O26" s="5"/>
     </row>
-    <row r="27" ht="25" hidden="1" customHeight="1" spans="1:15">
+    <row r="27" ht="25" customHeight="1" spans="1:15">
       <c r="A27" s="12" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C27" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G27" s="5">
+        <v>2025</v>
+      </c>
+      <c r="H27" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="D27" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E27" s="13" t="s">
+      <c r="I27" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G27" s="5">
-        <v>2026</v>
-      </c>
-      <c r="H27" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>122</v>
       </c>
       <c r="J27" s="5"/>
       <c r="K27" s="5"/>
       <c r="L27" s="5" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="M27" s="5"/>
       <c r="N27" s="5"/>
       <c r="O27" s="5"/>
     </row>
-    <row r="28" ht="25" hidden="1" customHeight="1" spans="1:15">
+    <row r="28" ht="25" customHeight="1" spans="1:15">
       <c r="A28" s="12" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F28" s="5" t="s">
         <v>24</v>
@@ -3916,109 +4003,109 @@
         <v>2026</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="J28" s="5"/>
       <c r="K28" s="5"/>
       <c r="L28" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="M28" s="5"/>
       <c r="N28" s="5"/>
       <c r="O28" s="5"/>
     </row>
-    <row r="29" ht="25" hidden="1" customHeight="1" spans="1:15">
+    <row r="29" ht="25" customHeight="1" spans="1:15">
       <c r="A29" s="12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C29" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G29" s="5">
+        <v>2026</v>
+      </c>
+      <c r="H29" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="D29" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E29" s="13" t="s">
+      <c r="I29" s="1" t="s">
         <v>132</v>
-      </c>
-      <c r="F29" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G29" s="5">
-        <v>2025</v>
-      </c>
-      <c r="H29" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I29" s="1" t="s">
-        <v>134</v>
       </c>
       <c r="J29" s="5"/>
       <c r="K29" s="5"/>
       <c r="L29" s="5" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="M29" s="5"/>
       <c r="N29" s="5"/>
       <c r="O29" s="5"/>
     </row>
-    <row r="30" ht="25" hidden="1" customHeight="1" spans="1:15">
+    <row r="30" ht="25" customHeight="1" spans="1:15">
       <c r="A30" s="12" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C30" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G30" s="5">
+        <v>2025</v>
+      </c>
+      <c r="H30" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="D30" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E30" s="13" t="s">
+      <c r="I30" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F30" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G30" s="5">
-        <v>2026</v>
-      </c>
-      <c r="H30" s="5" t="s">
+      <c r="J30" s="5"/>
+      <c r="K30" s="5"/>
+      <c r="L30" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="I30" s="1" t="s">
+      <c r="M30" s="5"/>
+      <c r="N30" s="5"/>
+      <c r="O30" s="5"/>
+    </row>
+    <row r="31" ht="25" customHeight="1" spans="1:15">
+      <c r="A31" s="12" t="s">
         <v>140</v>
-      </c>
-      <c r="J30" s="15"/>
-      <c r="K30" s="15"/>
-      <c r="L30" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="M30" s="15"/>
-      <c r="N30" s="15"/>
-      <c r="O30" s="5"/>
-    </row>
-    <row r="31" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A31" s="12" t="s">
-        <v>142</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F31" s="5" t="s">
         <v>24</v>
@@ -4027,72 +4114,72 @@
         <v>2026</v>
       </c>
       <c r="H31" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="J31" s="15"/>
+      <c r="K31" s="15"/>
+      <c r="L31" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="I31" s="5" t="s">
+      <c r="M31" s="15"/>
+      <c r="N31" s="15"/>
+      <c r="O31" s="5"/>
+    </row>
+    <row r="32" ht="25" customHeight="1" spans="1:15">
+      <c r="A32" s="12" t="s">
         <v>146</v>
-      </c>
-      <c r="J31" s="5"/>
-      <c r="K31" s="5"/>
-      <c r="L31" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="M31" s="5"/>
-      <c r="N31" s="5"/>
-      <c r="O31" s="36"/>
-    </row>
-    <row r="32" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A32" s="12" t="s">
-        <v>148</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C32" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E32" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G32" s="5">
+        <v>2026</v>
+      </c>
+      <c r="H32" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="D32" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E32" s="13" t="s">
+      <c r="I32" s="5" t="s">
         <v>150</v>
-      </c>
-      <c r="F32" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G32" s="5">
-        <v>2024</v>
-      </c>
-      <c r="H32" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="I32" s="5" t="s">
-        <v>152</v>
       </c>
       <c r="J32" s="5"/>
       <c r="K32" s="5"/>
       <c r="L32" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="M32" s="5"/>
       <c r="N32" s="5"/>
-      <c r="O32" s="36"/>
-    </row>
-    <row r="33" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O32" s="37"/>
+    </row>
+    <row r="33" ht="25" customHeight="1" spans="1:15">
       <c r="A33" s="12" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F33" s="5" t="s">
         <v>24</v>
@@ -4101,41 +4188,41 @@
         <v>2024</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I33" s="5" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="J33" s="5"/>
       <c r="K33" s="5"/>
       <c r="L33" s="5" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="M33" s="5"/>
       <c r="N33" s="5"/>
-      <c r="O33" s="36"/>
-    </row>
-    <row r="34" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O33" s="37"/>
+    </row>
+    <row r="34" ht="25" customHeight="1" spans="1:15">
       <c r="A34" s="12" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>125</v>
+        <v>159</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>126</v>
+        <v>160</v>
       </c>
       <c r="F34" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G34" s="5">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="H34" s="5" t="s">
         <v>161</v>
@@ -4150,9 +4237,9 @@
       </c>
       <c r="M34" s="5"/>
       <c r="N34" s="5"/>
-      <c r="O34" s="36"/>
-    </row>
-    <row r="35" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O34" s="37"/>
+    </row>
+    <row r="35" ht="25" customHeight="1" spans="1:15">
       <c r="A35" s="12" t="s">
         <v>164</v>
       </c>
@@ -4160,87 +4247,87 @@
         <v>12</v>
       </c>
       <c r="C35" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E35" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G35" s="5">
+        <v>2026</v>
+      </c>
+      <c r="H35" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="D35" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E35" s="13" t="s">
+      <c r="I35" s="5" t="s">
         <v>166</v>
-      </c>
-      <c r="F35" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G35" s="5">
-        <v>2025</v>
-      </c>
-      <c r="H35" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="I35" s="5" t="s">
-        <v>168</v>
       </c>
       <c r="J35" s="5"/>
       <c r="K35" s="5"/>
       <c r="L35" s="5" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="M35" s="5"/>
       <c r="N35" s="5"/>
-      <c r="O35" s="36"/>
-    </row>
-    <row r="36" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O35" s="37"/>
+    </row>
+    <row r="36" ht="25" customHeight="1" spans="1:15">
       <c r="A36" s="12" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C36" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E36" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G36" s="5">
+        <v>2025</v>
+      </c>
+      <c r="H36" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="D36" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E36" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="F36" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G36" s="5">
-        <v>2026</v>
-      </c>
-      <c r="H36" s="5" t="s">
+      <c r="I36" s="5" t="s">
         <v>172</v>
-      </c>
-      <c r="I36" s="5" t="s">
-        <v>173</v>
       </c>
       <c r="J36" s="5"/>
       <c r="K36" s="5"/>
       <c r="L36" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="M36" s="5"/>
       <c r="N36" s="5"/>
-      <c r="O36" s="36"/>
-    </row>
-    <row r="37" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O36" s="37"/>
+    </row>
+    <row r="37" ht="25" customHeight="1" spans="1:15">
       <c r="A37" s="12" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="F37" s="5" t="s">
         <v>24</v>
@@ -4249,35 +4336,35 @@
         <v>2026</v>
       </c>
       <c r="H37" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="I37" s="5" t="s">
         <v>177</v>
-      </c>
-      <c r="I37" s="5" t="s">
-        <v>178</v>
       </c>
       <c r="J37" s="5"/>
       <c r="K37" s="5"/>
       <c r="L37" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="M37" s="5"/>
       <c r="N37" s="5"/>
-      <c r="O37" s="36"/>
-    </row>
-    <row r="38" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O37" s="37"/>
+    </row>
+    <row r="38" ht="25" customHeight="1" spans="1:15">
       <c r="A38" s="12" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>108</v>
+        <v>148</v>
       </c>
       <c r="F38" s="5" t="s">
         <v>24</v>
@@ -4286,109 +4373,109 @@
         <v>2026</v>
       </c>
       <c r="H38" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="I38" s="5" t="s">
         <v>182</v>
-      </c>
-      <c r="I38" s="5" t="s">
-        <v>183</v>
       </c>
       <c r="J38" s="5"/>
       <c r="K38" s="5"/>
       <c r="L38" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="M38" s="5"/>
       <c r="N38" s="5"/>
-      <c r="O38" s="36"/>
-    </row>
-    <row r="39" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O38" s="37"/>
+    </row>
+    <row r="39" ht="25" customHeight="1" spans="1:15">
       <c r="A39" s="12" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>131</v>
+        <v>185</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E39" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G39" s="5">
+        <v>2026</v>
+      </c>
+      <c r="H39" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="F39" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G39" s="5">
-        <v>2025</v>
-      </c>
-      <c r="H39" s="5" t="s">
+      <c r="I39" s="5" t="s">
         <v>187</v>
-      </c>
-      <c r="I39" s="5" t="s">
-        <v>188</v>
       </c>
       <c r="J39" s="5"/>
       <c r="K39" s="5"/>
       <c r="L39" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="M39" s="5"/>
       <c r="N39" s="5"/>
-      <c r="O39" s="36"/>
-    </row>
-    <row r="40" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O39" s="37"/>
+    </row>
+    <row r="40" ht="25" customHeight="1" spans="1:15">
       <c r="A40" s="12" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C40" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E40" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G40" s="5">
+        <v>2025</v>
+      </c>
+      <c r="H40" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="D40" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E40" s="13" t="s">
+      <c r="I40" s="5" t="s">
         <v>192</v>
-      </c>
-      <c r="F40" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G40" s="5">
-        <v>2026</v>
-      </c>
-      <c r="H40" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="I40" s="5" t="s">
-        <v>194</v>
       </c>
       <c r="J40" s="5"/>
       <c r="K40" s="5"/>
       <c r="L40" s="5" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="M40" s="5"/>
       <c r="N40" s="5"/>
-      <c r="O40" s="36"/>
-    </row>
-    <row r="41" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O40" s="37"/>
+    </row>
+    <row r="41" ht="25" customHeight="1" spans="1:15">
       <c r="A41" s="12" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E41" s="13" t="s">
-        <v>114</v>
+        <v>196</v>
       </c>
       <c r="F41" s="5" t="s">
         <v>24</v>
@@ -4397,56 +4484,58 @@
         <v>2026</v>
       </c>
       <c r="H41" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="I41" s="5" t="s">
         <v>198</v>
-      </c>
-      <c r="I41" s="5" t="s">
-        <v>199</v>
       </c>
       <c r="J41" s="5"/>
       <c r="K41" s="5"/>
       <c r="L41" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="M41" s="5"/>
       <c r="N41" s="5"/>
-      <c r="O41" s="36"/>
-    </row>
-    <row r="42" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O41" s="37"/>
+    </row>
+    <row r="42" ht="25" customHeight="1" spans="1:15">
       <c r="A42" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C42" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="B42" s="24" t="s">
-        <v>58</v>
-      </c>
-      <c r="C42" s="5" t="s">
+      <c r="D42" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E42" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="F42" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G42" s="5">
+        <v>2026</v>
+      </c>
+      <c r="H42" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="D42" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E42" s="13" t="s">
+      <c r="I42" s="5" t="s">
         <v>203</v>
-      </c>
-      <c r="F42" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G42" s="5">
-        <v>2025</v>
-      </c>
-      <c r="H42" s="5"/>
-      <c r="I42" s="5" t="s">
-        <v>204</v>
       </c>
       <c r="J42" s="5"/>
       <c r="K42" s="5"/>
       <c r="L42" s="5" t="s">
-        <v>58</v>
+        <v>204</v>
       </c>
       <c r="M42" s="5"/>
       <c r="N42" s="5"/>
-      <c r="O42" s="36"/>
-    </row>
-    <row r="43" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O42" s="37"/>
+    </row>
+    <row r="43" ht="25" customHeight="1" spans="1:15">
       <c r="A43" s="12" t="s">
         <v>205</v>
       </c>
@@ -4468,36 +4557,34 @@
       <c r="G43" s="5">
         <v>2025</v>
       </c>
-      <c r="H43" s="5" t="s">
+      <c r="H43" s="5"/>
+      <c r="I43" s="5" t="s">
         <v>208</v>
-      </c>
-      <c r="I43" s="5" t="s">
-        <v>209</v>
       </c>
       <c r="J43" s="5"/>
       <c r="K43" s="5"/>
       <c r="L43" s="5" t="s">
-        <v>210</v>
+        <v>58</v>
       </c>
       <c r="M43" s="5"/>
       <c r="N43" s="5"/>
-      <c r="O43" s="36"/>
-    </row>
-    <row r="44" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O43" s="37"/>
+    </row>
+    <row r="44" ht="25" customHeight="1" spans="1:15">
       <c r="A44" s="12" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B44" s="24" t="s">
         <v>58</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="F44" s="5" t="s">
         <v>24</v>
@@ -4505,25 +4592,27 @@
       <c r="G44" s="5">
         <v>2025</v>
       </c>
-      <c r="H44" s="5"/>
+      <c r="H44" s="5" t="s">
+        <v>212</v>
+      </c>
       <c r="I44" s="5" t="s">
         <v>213</v>
       </c>
       <c r="J44" s="5"/>
       <c r="K44" s="5"/>
       <c r="L44" s="5" t="s">
-        <v>58</v>
+        <v>214</v>
       </c>
       <c r="M44" s="5"/>
       <c r="N44" s="5"/>
-      <c r="O44" s="36"/>
-    </row>
-    <row r="45" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O44" s="37"/>
+    </row>
+    <row r="45" ht="25" customHeight="1" spans="1:15">
       <c r="A45" s="12" t="s">
-        <v>214</v>
-      </c>
-      <c r="B45" s="5" t="s">
         <v>215</v>
+      </c>
+      <c r="B45" s="24" t="s">
+        <v>58</v>
       </c>
       <c r="C45" s="5" t="s">
         <v>216</v>
@@ -4532,55 +4621,67 @@
         <v>14</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>120</v>
+        <v>207</v>
       </c>
       <c r="F45" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G45" s="5">
-        <v>2026</v>
-      </c>
-      <c r="H45" s="5" t="s">
+        <v>2025</v>
+      </c>
+      <c r="H45" s="5"/>
+      <c r="I45" s="5" t="s">
         <v>217</v>
-      </c>
-      <c r="I45" s="5" t="s">
-        <v>218</v>
       </c>
       <c r="J45" s="5"/>
       <c r="K45" s="5"/>
       <c r="L45" s="5" t="s">
-        <v>219</v>
+        <v>58</v>
       </c>
       <c r="M45" s="5"/>
       <c r="N45" s="5"/>
-      <c r="O45" s="36"/>
-    </row>
-    <row r="46" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O45" s="37"/>
+    </row>
+    <row r="46" ht="25" customHeight="1" spans="1:15">
       <c r="A46" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="C46" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="B46" s="5"/>
-      <c r="C46" s="5"/>
-      <c r="D46" s="5"/>
-      <c r="E46" s="13"/>
+      <c r="D46" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E46" s="13" t="s">
+        <v>124</v>
+      </c>
       <c r="F46" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G46" s="5"/>
-      <c r="H46" s="5"/>
+      <c r="G46" s="5">
+        <v>2026</v>
+      </c>
+      <c r="H46" s="5" t="s">
+        <v>221</v>
+      </c>
       <c r="I46" s="5" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="J46" s="5"/>
       <c r="K46" s="5"/>
-      <c r="L46" s="5"/>
+      <c r="L46" s="5" t="s">
+        <v>223</v>
+      </c>
       <c r="M46" s="5"/>
       <c r="N46" s="5"/>
-      <c r="O46" s="36"/>
-    </row>
-    <row r="47" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O46" s="37"/>
+    </row>
+    <row r="47" ht="25" customHeight="1" spans="1:15">
       <c r="A47" s="12" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
@@ -4592,18 +4693,18 @@
       <c r="G47" s="5"/>
       <c r="H47" s="5"/>
       <c r="I47" s="5" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="J47" s="5"/>
       <c r="K47" s="5"/>
       <c r="L47" s="5"/>
       <c r="M47" s="5"/>
       <c r="N47" s="5"/>
-      <c r="O47" s="36"/>
-    </row>
-    <row r="48" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O47" s="37"/>
+    </row>
+    <row r="48" ht="25" customHeight="1" spans="1:15">
       <c r="A48" s="12" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
@@ -4615,18 +4716,18 @@
       <c r="G48" s="5"/>
       <c r="H48" s="5"/>
       <c r="I48" s="5" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="J48" s="5"/>
       <c r="K48" s="5"/>
       <c r="L48" s="5"/>
       <c r="M48" s="5"/>
       <c r="N48" s="5"/>
-      <c r="O48" s="36"/>
-    </row>
-    <row r="49" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O48" s="37"/>
+    </row>
+    <row r="49" ht="25" customHeight="1" spans="1:15">
       <c r="A49" s="12" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
@@ -4638,64 +4739,64 @@
       <c r="G49" s="5"/>
       <c r="H49" s="5"/>
       <c r="I49" s="5" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="J49" s="5"/>
       <c r="K49" s="5"/>
       <c r="L49" s="5"/>
       <c r="M49" s="5"/>
       <c r="N49" s="5"/>
-      <c r="O49" s="36"/>
-    </row>
-    <row r="50" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A50" s="14" t="s">
-        <v>228</v>
-      </c>
-      <c r="B50" s="15"/>
-      <c r="C50" s="15"/>
-      <c r="D50" s="15"/>
-      <c r="E50" s="37"/>
+      <c r="O49" s="37"/>
+    </row>
+    <row r="50" ht="25" customHeight="1" spans="1:15">
+      <c r="A50" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="B50" s="5"/>
+      <c r="C50" s="5"/>
+      <c r="D50" s="5"/>
+      <c r="E50" s="13"/>
       <c r="F50" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G50" s="15"/>
-      <c r="H50" s="15"/>
-      <c r="I50" s="16" t="s">
-        <v>229</v>
-      </c>
-      <c r="J50" s="15"/>
+      <c r="G50" s="5"/>
+      <c r="H50" s="5"/>
+      <c r="I50" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="J50" s="5"/>
       <c r="K50" s="5"/>
       <c r="L50" s="5"/>
       <c r="M50" s="5"/>
       <c r="N50" s="5"/>
-      <c r="O50" s="36"/>
-    </row>
-    <row r="51" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A51" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="B51" s="5"/>
-      <c r="C51" s="5"/>
-      <c r="D51" s="5"/>
-      <c r="E51" s="13"/>
+      <c r="O50" s="37"/>
+    </row>
+    <row r="51" ht="25" customHeight="1" spans="1:15">
+      <c r="A51" s="14" t="s">
+        <v>232</v>
+      </c>
+      <c r="B51" s="15"/>
+      <c r="C51" s="15"/>
+      <c r="D51" s="15"/>
+      <c r="E51" s="28"/>
       <c r="F51" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G51" s="5"/>
-      <c r="H51" s="5"/>
-      <c r="I51" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="J51" s="5"/>
+      <c r="G51" s="15"/>
+      <c r="H51" s="15"/>
+      <c r="I51" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="J51" s="15"/>
       <c r="K51" s="5"/>
       <c r="L51" s="5"/>
       <c r="M51" s="5"/>
       <c r="N51" s="5"/>
-      <c r="O51" s="36"/>
-    </row>
-    <row r="52" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O51" s="37"/>
+    </row>
+    <row r="52" ht="25" customHeight="1" spans="1:15">
       <c r="A52" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5"/>
@@ -4705,20 +4806,19 @@
         <v>24</v>
       </c>
       <c r="G52" s="5"/>
-      <c r="H52" s="5"/>
       <c r="I52" s="5" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="J52" s="5"/>
       <c r="K52" s="5"/>
       <c r="L52" s="5"/>
       <c r="M52" s="5"/>
       <c r="N52" s="5"/>
-      <c r="O52" s="36"/>
-    </row>
-    <row r="53" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O52" s="37"/>
+    </row>
+    <row r="53" ht="25" customHeight="1" spans="1:15">
       <c r="A53" s="12" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5"/>
@@ -4730,18 +4830,18 @@
       <c r="G53" s="5"/>
       <c r="H53" s="5"/>
       <c r="I53" s="5" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="J53" s="5"/>
       <c r="K53" s="5"/>
       <c r="L53" s="5"/>
       <c r="M53" s="5"/>
       <c r="N53" s="5"/>
-      <c r="O53" s="36"/>
-    </row>
-    <row r="54" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O53" s="37"/>
+    </row>
+    <row r="54" ht="25" customHeight="1" spans="1:15">
       <c r="A54" s="12" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
@@ -4751,19 +4851,20 @@
         <v>24</v>
       </c>
       <c r="G54" s="5"/>
+      <c r="H54" s="5"/>
       <c r="I54" s="5" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J54" s="5"/>
       <c r="K54" s="5"/>
       <c r="L54" s="5"/>
       <c r="M54" s="5"/>
       <c r="N54" s="5"/>
-      <c r="O54" s="36"/>
-    </row>
-    <row r="55" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O54" s="37"/>
+    </row>
+    <row r="55" ht="25" customHeight="1" spans="1:15">
       <c r="A55" s="12" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B55" s="5"/>
       <c r="C55" s="5"/>
@@ -4773,20 +4874,19 @@
         <v>24</v>
       </c>
       <c r="G55" s="5"/>
-      <c r="H55" s="5"/>
       <c r="I55" s="5" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J55" s="5"/>
       <c r="K55" s="5"/>
       <c r="L55" s="5"/>
       <c r="M55" s="5"/>
       <c r="N55" s="5"/>
-      <c r="O55" s="36"/>
-    </row>
-    <row r="56" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O55" s="37"/>
+    </row>
+    <row r="56" ht="25" customHeight="1" spans="1:15">
       <c r="A56" s="12" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
@@ -4798,18 +4898,18 @@
       <c r="G56" s="5"/>
       <c r="H56" s="5"/>
       <c r="I56" s="5" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="J56" s="5"/>
       <c r="K56" s="5"/>
       <c r="L56" s="5"/>
       <c r="M56" s="5"/>
       <c r="N56" s="5"/>
-      <c r="O56" s="36"/>
-    </row>
-    <row r="57" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O56" s="37"/>
+    </row>
+    <row r="57" ht="25" customHeight="1" spans="1:15">
       <c r="A57" s="12" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
@@ -4821,18 +4921,18 @@
       <c r="G57" s="5"/>
       <c r="H57" s="5"/>
       <c r="I57" s="5" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="J57" s="5"/>
       <c r="K57" s="5"/>
       <c r="L57" s="5"/>
       <c r="M57" s="5"/>
       <c r="N57" s="5"/>
-      <c r="O57" s="36"/>
-    </row>
-    <row r="58" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O57" s="37"/>
+    </row>
+    <row r="58" ht="25" customHeight="1" spans="1:15">
       <c r="A58" s="12" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
@@ -4842,19 +4942,20 @@
         <v>24</v>
       </c>
       <c r="G58" s="5"/>
+      <c r="H58" s="5"/>
       <c r="I58" s="5" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="J58" s="5"/>
       <c r="K58" s="5"/>
       <c r="L58" s="5"/>
       <c r="M58" s="5"/>
       <c r="N58" s="5"/>
-      <c r="O58" s="36"/>
-    </row>
-    <row r="59" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O58" s="37"/>
+    </row>
+    <row r="59" ht="25" customHeight="1" spans="1:15">
       <c r="A59" s="12" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
@@ -4864,20 +4965,19 @@
         <v>24</v>
       </c>
       <c r="G59" s="5"/>
-      <c r="H59" s="5"/>
       <c r="I59" s="5" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="J59" s="5"/>
       <c r="K59" s="5"/>
       <c r="L59" s="5"/>
       <c r="M59" s="5"/>
       <c r="N59" s="5"/>
-      <c r="O59" s="36"/>
-    </row>
-    <row r="60" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O59" s="37"/>
+    </row>
+    <row r="60" ht="25" customHeight="1" spans="1:15">
       <c r="A60" s="12" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
@@ -4889,18 +4989,18 @@
       <c r="G60" s="5"/>
       <c r="H60" s="5"/>
       <c r="I60" s="5" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="J60" s="5"/>
       <c r="K60" s="5"/>
       <c r="L60" s="5"/>
       <c r="M60" s="5"/>
       <c r="N60" s="5"/>
-      <c r="O60" s="36"/>
-    </row>
-    <row r="61" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O60" s="37"/>
+    </row>
+    <row r="61" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A61" s="12" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
@@ -4912,18 +5012,18 @@
       <c r="G61" s="5"/>
       <c r="H61" s="5"/>
       <c r="I61" s="5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="J61" s="5"/>
       <c r="K61" s="5"/>
       <c r="L61" s="5"/>
       <c r="M61" s="5"/>
       <c r="N61" s="5"/>
-      <c r="O61" s="36"/>
-    </row>
-    <row r="62" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O61" s="37"/>
+    </row>
+    <row r="62" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A62" s="12" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B62" s="5"/>
       <c r="C62" s="5"/>
@@ -4935,18 +5035,18 @@
       <c r="G62" s="5"/>
       <c r="H62" s="5"/>
       <c r="I62" s="5" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="J62" s="5"/>
       <c r="K62" s="5"/>
       <c r="L62" s="5"/>
       <c r="M62" s="5"/>
       <c r="N62" s="5"/>
-      <c r="O62" s="36"/>
-    </row>
-    <row r="63" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O62" s="37"/>
+    </row>
+    <row r="63" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A63" s="12" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B63" s="5"/>
       <c r="C63" s="5"/>
@@ -4958,59 +5058,51 @@
       <c r="G63" s="5"/>
       <c r="H63" s="5"/>
       <c r="I63" s="5" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="J63" s="5"/>
       <c r="K63" s="5"/>
       <c r="L63" s="5"/>
       <c r="M63" s="5"/>
       <c r="N63" s="5"/>
-      <c r="O63" s="36"/>
-    </row>
-    <row r="64" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O63" s="37"/>
+    </row>
+    <row r="64" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A64" s="12" t="s">
-        <v>256</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C64" s="17" t="s">
-        <v>257</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="B64" s="5"/>
+      <c r="C64" s="5"/>
       <c r="D64" s="5"/>
-      <c r="E64" s="13" t="s">
-        <v>258</v>
-      </c>
+      <c r="E64" s="13"/>
       <c r="F64" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G64" s="5"/>
-      <c r="H64" s="18" t="s">
+      <c r="H64" s="5"/>
+      <c r="I64" s="5" t="s">
         <v>259</v>
-      </c>
-      <c r="I64" s="5" t="s">
-        <v>260</v>
       </c>
       <c r="J64" s="5"/>
       <c r="K64" s="5"/>
       <c r="L64" s="5"/>
       <c r="M64" s="5"/>
       <c r="N64" s="5"/>
-      <c r="O64" s="36"/>
-    </row>
-    <row r="65" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O64" s="37"/>
+    </row>
+    <row r="65" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A65" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C65" s="17" t="s">
         <v>261</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C65" s="17" t="s">
-        <v>262</v>
       </c>
       <c r="D65" s="5"/>
       <c r="E65" s="13" t="s">
-        <v>120</v>
+        <v>262</v>
       </c>
       <c r="F65" s="5" t="s">
         <v>24</v>
@@ -5027,21 +5119,21 @@
       <c r="L65" s="5"/>
       <c r="M65" s="5"/>
       <c r="N65" s="5"/>
-      <c r="O65" s="5"/>
-    </row>
-    <row r="66" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O65" s="37"/>
+    </row>
+    <row r="66" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A66" s="12" t="s">
         <v>265</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C66" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="C66" s="17" t="s">
         <v>266</v>
       </c>
       <c r="D66" s="5"/>
       <c r="E66" s="13" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>24</v>
@@ -5058,52 +5150,52 @@
       <c r="L66" s="5"/>
       <c r="M66" s="5"/>
       <c r="N66" s="5"/>
-      <c r="O66" s="36"/>
-    </row>
-    <row r="67" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O66" s="5"/>
+    </row>
+    <row r="67" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A67" s="12" t="s">
         <v>269</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C67" s="17" t="s">
+      <c r="C67" s="19" t="s">
         <v>270</v>
       </c>
       <c r="D67" s="5"/>
       <c r="E67" s="13" t="s">
-        <v>271</v>
+        <v>130</v>
       </c>
       <c r="F67" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G67" s="5"/>
       <c r="H67" s="18" t="s">
+        <v>271</v>
+      </c>
+      <c r="I67" s="5" t="s">
         <v>272</v>
-      </c>
-      <c r="I67" s="5" t="s">
-        <v>273</v>
       </c>
       <c r="J67" s="5"/>
       <c r="K67" s="5"/>
       <c r="L67" s="5"/>
       <c r="M67" s="5"/>
       <c r="N67" s="5"/>
-      <c r="O67" s="36"/>
-    </row>
-    <row r="68" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O67" s="37"/>
+    </row>
+    <row r="68" ht="25" customHeight="1" spans="1:15">
       <c r="A68" s="12" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C68" s="17" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D68" s="5"/>
       <c r="E68" s="13" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="F68" s="5" t="s">
         <v>24</v>
@@ -5120,84 +5212,98 @@
       <c r="L68" s="5"/>
       <c r="M68" s="5"/>
       <c r="N68" s="5"/>
-      <c r="O68" s="36"/>
-    </row>
-    <row r="69" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O68" s="37"/>
+    </row>
+    <row r="69" ht="25" customHeight="1" spans="1:15">
       <c r="A69" s="12" t="s">
         <v>278</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
       <c r="C69" s="17" t="s">
         <v>279</v>
       </c>
       <c r="D69" s="5"/>
       <c r="E69" s="13" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="F69" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G69" s="5"/>
       <c r="H69" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="I69" s="5" t="s">
         <v>281</v>
-      </c>
-      <c r="I69" s="5" t="s">
-        <v>282</v>
       </c>
       <c r="J69" s="5"/>
       <c r="K69" s="5"/>
       <c r="L69" s="5"/>
       <c r="M69" s="5"/>
       <c r="N69" s="5"/>
-      <c r="O69" s="36"/>
-    </row>
-    <row r="70" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O69" s="37"/>
+    </row>
+    <row r="70" ht="25" customHeight="1" spans="1:15">
       <c r="A70" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C70" s="17" t="s">
         <v>283</v>
       </c>
-      <c r="B70" s="5" t="s">
+      <c r="D70" s="5"/>
+      <c r="E70" s="13" t="s">
         <v>284</v>
       </c>
-      <c r="C70" s="38" t="s">
+      <c r="F70" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G70" s="5"/>
+      <c r="H70" s="18" t="s">
         <v>285</v>
       </c>
-      <c r="D70" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="E70" s="13" t="s">
+      <c r="I70" s="5" t="s">
         <v>286</v>
-      </c>
-      <c r="F70" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="G70" s="24">
-        <v>2026</v>
-      </c>
-      <c r="H70" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="I70" s="5" t="s">
-        <v>288</v>
       </c>
       <c r="J70" s="5"/>
       <c r="K70" s="5"/>
       <c r="L70" s="5"/>
       <c r="M70" s="5"/>
       <c r="N70" s="5"/>
-      <c r="O70" s="5"/>
+      <c r="O70" s="37"/>
     </row>
     <row r="71" ht="25" customHeight="1" spans="1:15">
-      <c r="A71" s="12"/>
-      <c r="B71" s="5"/>
-      <c r="C71" s="5"/>
-      <c r="D71" s="5"/>
-      <c r="E71" s="13"/>
-      <c r="F71" s="13"/>
-      <c r="G71" s="5"/>
-      <c r="H71" s="5"/>
-      <c r="I71" s="5"/>
+      <c r="A71" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="C71" s="38" t="s">
+        <v>289</v>
+      </c>
+      <c r="D71" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E71" s="13" t="s">
+        <v>290</v>
+      </c>
+      <c r="F71" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="G71" s="24">
+        <v>2026</v>
+      </c>
+      <c r="H71" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="I71" s="5" t="s">
+        <v>292</v>
+      </c>
       <c r="J71" s="5"/>
       <c r="K71" s="5"/>
       <c r="L71" s="5"/>
@@ -5213,6 +5319,7 @@
       <c r="E72" s="13"/>
       <c r="F72" s="13"/>
       <c r="G72" s="5"/>
+      <c r="H72" s="5"/>
       <c r="I72" s="5"/>
       <c r="J72" s="5"/>
       <c r="K72" s="5"/>
@@ -5229,7 +5336,6 @@
       <c r="E73" s="13"/>
       <c r="F73" s="13"/>
       <c r="G73" s="5"/>
-      <c r="H73" s="5"/>
       <c r="I73" s="5"/>
       <c r="J73" s="5"/>
       <c r="K73" s="5"/>
@@ -5263,6 +5369,7 @@
       <c r="E75" s="13"/>
       <c r="F75" s="13"/>
       <c r="G75" s="5"/>
+      <c r="H75" s="5"/>
       <c r="I75" s="5"/>
       <c r="J75" s="5"/>
       <c r="K75" s="5"/>
@@ -5279,7 +5386,6 @@
       <c r="E76" s="13"/>
       <c r="F76" s="13"/>
       <c r="G76" s="5"/>
-      <c r="H76" s="5"/>
       <c r="I76" s="5"/>
       <c r="J76" s="5"/>
       <c r="K76" s="5"/>
@@ -5330,6 +5436,7 @@
       <c r="E79" s="13"/>
       <c r="F79" s="13"/>
       <c r="G79" s="5"/>
+      <c r="H79" s="5"/>
       <c r="I79" s="5"/>
       <c r="J79" s="5"/>
       <c r="K79" s="5"/>
@@ -5346,7 +5453,6 @@
       <c r="E80" s="13"/>
       <c r="F80" s="13"/>
       <c r="G80" s="5"/>
-      <c r="H80" s="5"/>
       <c r="I80" s="5"/>
       <c r="J80" s="5"/>
       <c r="K80" s="5"/>
@@ -5440,21 +5546,33 @@
       <c r="N85" s="5"/>
       <c r="O85" s="5"/>
     </row>
+    <row r="86" ht="25" customHeight="1" spans="1:15">
+      <c r="A86" s="12"/>
+      <c r="B86" s="5"/>
+      <c r="C86" s="5"/>
+      <c r="D86" s="5"/>
+      <c r="E86" s="13"/>
+      <c r="F86" s="13"/>
+      <c r="G86" s="5"/>
+      <c r="H86" s="5"/>
+      <c r="I86" s="5"/>
+      <c r="J86" s="5"/>
+      <c r="K86" s="5"/>
+      <c r="L86" s="5"/>
+      <c r="M86" s="5"/>
+      <c r="N86" s="5"/>
+      <c r="O86" s="5"/>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:O70" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="5">
-      <filters>
-        <filter val="更新中"/>
-      </filters>
-    </filterColumn>
-    <sortState ref="A1:O70">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:O71" etc:filterBottomFollowUsedRange="0">
+    <sortState ref="A1:O71">
       <sortCondition ref="F1"/>
     </sortState>
     <extLst/>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="H65" r:id="rId1" display="普洛伊湘普·素帕莎 / 芭莉雅皮·余 " tooltip="https://www.douban.com/personage/30264980/"/>
-    <hyperlink ref="H20" r:id="rId2" display="金贤叙/郑明哲" tooltip="https://www.douban.com/personage/37338980/"/>
+    <hyperlink ref="H66" r:id="rId1" display="普洛伊湘普·素帕莎 / 芭莉雅皮·余 " tooltip="https://www.douban.com/personage/30264980/"/>
+    <hyperlink ref="H21" r:id="rId2" display="金贤叙/郑明哲" tooltip="https://www.douban.com/personage/37338980/"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -5478,7 +5596,7 @@
   <sheetData>
     <row r="1" ht="33" customHeight="1" spans="1:9">
       <c r="A1" s="3" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -5525,7 +5643,7 @@
         <v>12</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>14</v>
@@ -5722,13 +5840,13 @@
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:9">
       <c r="A10" s="6" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>58</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>14</v>
@@ -5743,21 +5861,21 @@
         <v>2026</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:9">
       <c r="A11" s="6" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>14</v>
@@ -5772,21 +5890,21 @@
         <v>2026</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:9">
       <c r="A12" s="6" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>58</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>14</v>
@@ -5801,21 +5919,21 @@
         <v>2026</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:9">
       <c r="A13" s="6" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>58</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>14</v>
@@ -5830,21 +5948,21 @@
         <v>2026</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:9">
       <c r="A14" s="6" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>58</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>14</v>
@@ -5859,21 +5977,21 @@
         <v>2026</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:9">
       <c r="A15" s="6" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>58</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>14</v>
@@ -5888,21 +6006,21 @@
         <v>2026</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:9">
       <c r="A16" s="6" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>58</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>14</v>
@@ -5917,21 +6035,21 @@
         <v>2026</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:9">
       <c r="A17" s="6" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>49</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>14</v>
@@ -5947,18 +6065,18 @@
       </c>
       <c r="H17" s="7"/>
       <c r="I17" s="8" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:9">
       <c r="A18" s="6" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>49</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>14</v>
@@ -5974,18 +6092,18 @@
       </c>
       <c r="H18" s="7"/>
       <c r="I18" s="8" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" spans="1:9">
       <c r="A19" s="9" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>49</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>14</v>
@@ -5999,18 +6117,18 @@
       </c>
       <c r="H19" s="7"/>
       <c r="I19" s="11" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" spans="1:9">
       <c r="A20" s="9" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>49</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>14</v>
@@ -6024,24 +6142,24 @@
       </c>
       <c r="H20" s="7"/>
       <c r="I20" s="11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1" spans="1:9">
       <c r="A21" s="12" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>24</v>
@@ -6050,27 +6168,27 @@
         <v>2026</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1" spans="1:9">
       <c r="A22" s="12" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>24</v>
@@ -6079,27 +6197,27 @@
         <v>2025</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1" spans="1:9">
       <c r="A23" s="12" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>24</v>
@@ -6108,27 +6226,27 @@
         <v>2026</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1" spans="1:9">
       <c r="A24" s="12" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>24</v>
@@ -6137,27 +6255,27 @@
         <v>2026</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1" spans="1:9">
       <c r="A25" s="12" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="F25" s="5" t="s">
         <v>24</v>
@@ -6166,27 +6284,27 @@
         <v>2025</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1" spans="1:9">
       <c r="A26" s="12" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="F26" s="5" t="s">
         <v>24</v>
@@ -6195,27 +6313,27 @@
         <v>2026</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1" spans="1:9">
       <c r="A27" s="12" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="F27" s="5" t="s">
         <v>24</v>
@@ -6224,27 +6342,27 @@
         <v>2026</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1" spans="1:9">
       <c r="A28" s="12" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="F28" s="5" t="s">
         <v>24</v>
@@ -6253,27 +6371,27 @@
         <v>2024</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="29" ht="25" customHeight="1" spans="1:9">
       <c r="A29" s="12" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="F29" s="5" t="s">
         <v>24</v>
@@ -6282,27 +6400,27 @@
         <v>2024</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="30" ht="25" customHeight="1" spans="1:9">
       <c r="A30" s="12" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="F30" s="5" t="s">
         <v>24</v>
@@ -6311,27 +6429,27 @@
         <v>2026</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
     </row>
     <row r="31" ht="25" customHeight="1" spans="1:9">
       <c r="A31" s="12" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="F31" s="5" t="s">
         <v>24</v>
@@ -6340,27 +6458,27 @@
         <v>2025</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
     </row>
     <row r="32" ht="25" customHeight="1" spans="1:9">
       <c r="A32" s="12" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="F32" s="5" t="s">
         <v>24</v>
@@ -6369,27 +6487,27 @@
         <v>2026</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" ht="25" customHeight="1" spans="1:9">
       <c r="A33" s="12" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="F33" s="5" t="s">
         <v>24</v>
@@ -6398,27 +6516,27 @@
         <v>2026</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="I33" s="5" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
     </row>
     <row r="34" ht="25" customHeight="1" spans="1:9">
       <c r="A34" s="12" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F34" s="5" t="s">
         <v>24</v>
@@ -6427,27 +6545,27 @@
         <v>2026</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="35" ht="25" customHeight="1" spans="1:9">
       <c r="A35" s="12" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="F35" s="5" t="s">
         <v>24</v>
@@ -6456,27 +6574,27 @@
         <v>2025</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="36" ht="25" customHeight="1" spans="1:9">
       <c r="A36" s="12" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="F36" s="5" t="s">
         <v>24</v>
@@ -6485,27 +6603,27 @@
         <v>2026</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
     </row>
     <row r="37" ht="25" customHeight="1" spans="1:9">
       <c r="A37" s="12" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F37" s="5" t="s">
         <v>24</v>
@@ -6514,27 +6632,27 @@
         <v>2026</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="I37" s="5" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
     </row>
     <row r="38" ht="25" customHeight="1" spans="1:9">
       <c r="A38" s="12" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="F38" s="5" t="s">
         <v>24</v>
@@ -6544,24 +6662,24 @@
       </c>
       <c r="H38" s="5"/>
       <c r="I38" s="5" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
     </row>
     <row r="39" ht="25" customHeight="1" spans="1:9">
       <c r="A39" s="12" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="F39" s="5" t="s">
         <v>24</v>
@@ -6570,27 +6688,27 @@
         <v>2025</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="I39" s="5" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
     </row>
     <row r="40" ht="25" customHeight="1" spans="1:9">
       <c r="A40" s="12" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D40" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="F40" s="5" t="s">
         <v>24</v>
@@ -6600,24 +6718,24 @@
       </c>
       <c r="H40" s="5"/>
       <c r="I40" s="5" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
     </row>
     <row r="41" ht="25" customHeight="1" spans="1:9">
       <c r="A41" s="12" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F41" s="5" t="s">
         <v>24</v>
@@ -6626,15 +6744,15 @@
         <v>2026</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="I41" s="5" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="42" ht="25" customHeight="1" spans="1:9">
       <c r="A42" s="12" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5"/>
@@ -6646,12 +6764,12 @@
       <c r="G42" s="5"/>
       <c r="H42" s="5"/>
       <c r="I42" s="5" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
     </row>
     <row r="43" ht="25" customHeight="1" spans="1:9">
       <c r="A43" s="12" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5"/>
@@ -6663,12 +6781,12 @@
       <c r="G43" s="5"/>
       <c r="H43" s="5"/>
       <c r="I43" s="5" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="44" ht="25" customHeight="1" spans="1:9">
       <c r="A44" s="12" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
@@ -6680,12 +6798,12 @@
       <c r="G44" s="5"/>
       <c r="H44" s="5"/>
       <c r="I44" s="5" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
     </row>
     <row r="45" ht="25" customHeight="1" spans="1:9">
       <c r="A45" s="12" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5"/>
@@ -6697,12 +6815,12 @@
       <c r="G45" s="5"/>
       <c r="H45" s="5"/>
       <c r="I45" s="5" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="46" ht="25" customHeight="1" spans="1:9">
       <c r="A46" s="14" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B46" s="15"/>
       <c r="C46" s="15"/>
@@ -6714,12 +6832,12 @@
       <c r="G46" s="15"/>
       <c r="H46" s="15"/>
       <c r="I46" s="16" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
     </row>
     <row r="47" ht="25" customHeight="1" spans="1:9">
       <c r="A47" s="12" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
@@ -6731,12 +6849,12 @@
       <c r="G47" s="5"/>
       <c r="H47" s="5"/>
       <c r="I47" s="5" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
     </row>
     <row r="48" ht="25" customHeight="1" spans="1:9">
       <c r="A48" s="12" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
@@ -6748,12 +6866,12 @@
       <c r="G48" s="5"/>
       <c r="H48" s="5"/>
       <c r="I48" s="5" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="49" ht="25" customHeight="1" spans="1:9">
       <c r="A49" s="12" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
@@ -6765,12 +6883,12 @@
       <c r="G49" s="5"/>
       <c r="H49" s="5"/>
       <c r="I49" s="5" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
     </row>
     <row r="50" ht="25" customHeight="1" spans="1:9">
       <c r="A50" s="12" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5"/>
@@ -6782,12 +6900,12 @@
       <c r="G50" s="5"/>
       <c r="H50" s="5"/>
       <c r="I50" s="5" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
     </row>
     <row r="51" ht="25" customHeight="1" spans="1:9">
       <c r="A51" s="12" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
@@ -6799,12 +6917,12 @@
       <c r="G51" s="5"/>
       <c r="H51" s="5"/>
       <c r="I51" s="5" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
     </row>
     <row r="52" ht="25" customHeight="1" spans="1:9">
       <c r="A52" s="12" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5"/>
@@ -6816,162 +6934,162 @@
       <c r="G52" s="5"/>
       <c r="H52" s="5"/>
       <c r="I52" s="5" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
     </row>
     <row r="53" customFormat="1" ht="25" customHeight="1" spans="1:9">
       <c r="A53" s="12" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C53" s="17" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="D53" s="5"/>
       <c r="E53" s="5" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="F53" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G53" s="5"/>
       <c r="H53" s="18" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I53" s="5" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
     </row>
     <row r="54" customFormat="1" ht="25" customHeight="1" spans="1:9">
       <c r="A54" s="12" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C54" s="17" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D54" s="5"/>
       <c r="E54" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F54" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G54" s="5"/>
       <c r="H54" s="18" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="I54" s="5" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="55" customFormat="1" ht="25" customHeight="1" spans="1:9">
       <c r="A55" s="12" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C55" s="19" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D55" s="5"/>
       <c r="E55" s="5" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="F55" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G55" s="5"/>
       <c r="H55" s="18" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="I55" s="5" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="56" ht="25" customHeight="1" spans="1:9">
       <c r="A56" s="12" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C56" s="17" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="D56" s="5"/>
       <c r="E56" s="5" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="F56" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G56" s="5"/>
       <c r="H56" s="18" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="I56" s="5" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="57" ht="25" customHeight="1" spans="1:9">
       <c r="A57" s="12" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C57" s="17" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="D57" s="5"/>
       <c r="E57" s="5" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="F57" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G57" s="5"/>
       <c r="H57" s="18" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="I57" s="5" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="58" ht="25" customHeight="1" spans="1:9">
       <c r="A58" s="12" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>58</v>
       </c>
       <c r="C58" s="17" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="D58" s="5"/>
       <c r="E58" s="5" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="F58" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G58" s="5"/>
       <c r="H58" s="18" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="I58" s="5" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="59" ht="25" customHeight="1" spans="1:9">
       <c r="A59" s="12" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
@@ -6983,12 +7101,12 @@
       <c r="G59" s="5"/>
       <c r="H59" s="5"/>
       <c r="I59" s="5" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
     </row>
     <row r="60" ht="25" customHeight="1" spans="1:9">
       <c r="A60" s="12" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
@@ -7000,12 +7118,12 @@
       <c r="G60" s="5"/>
       <c r="H60" s="5"/>
       <c r="I60" s="5" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
     </row>
     <row r="61" ht="25" customHeight="1" spans="1:9">
       <c r="A61" s="12" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
@@ -7017,12 +7135,12 @@
       <c r="G61" s="5"/>
       <c r="H61" s="5"/>
       <c r="I61" s="5" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
     </row>
     <row r="62" customFormat="1" ht="25" customHeight="1" spans="1:9">
       <c r="A62" s="12" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B62" s="5"/>
       <c r="C62" s="5"/>
@@ -7034,12 +7152,12 @@
       <c r="G62" s="5"/>
       <c r="H62" s="5"/>
       <c r="I62" s="5" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
     </row>
     <row r="63" customFormat="1" ht="25" customHeight="1" spans="1:9">
       <c r="A63" s="12" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="B63" s="5"/>
       <c r="C63" s="5"/>
@@ -7051,12 +7169,12 @@
       <c r="G63" s="5"/>
       <c r="H63" s="5"/>
       <c r="I63" s="5" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
     </row>
     <row r="64" customFormat="1" ht="25" customHeight="1" spans="1:9">
       <c r="A64" s="12" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B64" s="5"/>
       <c r="C64" s="5"/>
@@ -7068,12 +7186,12 @@
       <c r="G64" s="5"/>
       <c r="H64" s="5"/>
       <c r="I64" s="5" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
     </row>
     <row r="65" customFormat="1" ht="25" customHeight="1" spans="1:9">
       <c r="A65" s="12" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B65" s="5"/>
       <c r="C65" s="5"/>
@@ -7085,7 +7203,7 @@
       <c r="G65" s="5"/>
       <c r="H65" s="5"/>
       <c r="I65" s="5" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
     </row>
     <row r="66" ht="25" customHeight="1" spans="1:9">

--- a/资源录入表新.xlsx
+++ b/资源录入表新.xlsx
@@ -2526,7 +2526,15 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="18">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2720,25 +2728,25 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="6"/>
+      <tableStyleElement type="totalRow" dxfId="5"/>
+      <tableStyleElement type="firstColumn" dxfId="4"/>
+      <tableStyleElement type="lastColumn" dxfId="3"/>
+      <tableStyleElement type="firstRowStripe" dxfId="2"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="1"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="17"/>
+      <tableStyleElement type="totalRow" dxfId="16"/>
+      <tableStyleElement type="firstRowStripe" dxfId="15"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="14"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="13"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="11"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="10"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="9"/>
+      <tableStyleElement type="pageFieldValues" dxfId="8"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -3006,7 +3014,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:O86"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
@@ -3016,7 +3024,7 @@
     <col min="4" max="4" width="9" style="1"/>
     <col min="5" max="5" width="9" style="22"/>
     <col min="6" max="7" width="9" style="1"/>
-    <col min="8" max="8" width="80.2916666666667" style="1" customWidth="1"/>
+    <col min="8" max="8" width="45.875" style="1" customWidth="1"/>
     <col min="9" max="9" width="74.25" style="1" customWidth="1"/>
     <col min="10" max="10" width="9" style="1"/>
     <col min="11" max="11" width="9.99166666666667" style="1" customWidth="1"/>
@@ -3133,7 +3141,7 @@
       <c r="N3" s="13"/>
       <c r="O3" s="13"/>
     </row>
-    <row r="4" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+    <row r="4" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A4" s="23" t="s">
         <v>22</v>
       </c>
@@ -3170,7 +3178,7 @@
       <c r="N4" s="13"/>
       <c r="O4" s="13"/>
     </row>
-    <row r="5" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+    <row r="5" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A5" s="23" t="s">
         <v>28</v>
       </c>
@@ -3205,7 +3213,7 @@
       <c r="N5" s="13"/>
       <c r="O5" s="13"/>
     </row>
-    <row r="6" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+    <row r="6" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A6" s="23" t="s">
         <v>32</v>
       </c>
@@ -3240,7 +3248,7 @@
       <c r="N6" s="13"/>
       <c r="O6" s="13"/>
     </row>
-    <row r="7" ht="25" customHeight="1" spans="1:15">
+    <row r="7" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A7" s="12" t="s">
         <v>36</v>
       </c>
@@ -3345,7 +3353,7 @@
       <c r="N9" s="13"/>
       <c r="O9" s="13"/>
     </row>
-    <row r="10" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+    <row r="10" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A10" s="23" t="s">
         <v>48</v>
       </c>
@@ -3485,7 +3493,7 @@
       <c r="N13" s="13"/>
       <c r="O13" s="13"/>
     </row>
-    <row r="14" s="21" customFormat="1" ht="25" customHeight="1" spans="1:15">
+    <row r="14" s="21" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A14" s="23" t="s">
         <v>66</v>
       </c>
@@ -3520,7 +3528,7 @@
       <c r="N14" s="25"/>
       <c r="O14" s="25"/>
     </row>
-    <row r="15" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+    <row r="15" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A15" s="23" t="s">
         <v>70</v>
       </c>
@@ -3594,7 +3602,7 @@
       <c r="N16" s="13"/>
       <c r="O16" s="13"/>
     </row>
-    <row r="17" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+    <row r="17" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A17" s="23" t="s">
         <v>79</v>
       </c>
@@ -3631,7 +3639,7 @@
       <c r="N17" s="13"/>
       <c r="O17" s="13"/>
     </row>
-    <row r="18" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+    <row r="18" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A18" s="23" t="s">
         <v>82</v>
       </c>
@@ -3668,7 +3676,7 @@
       <c r="N18" s="13"/>
       <c r="O18" s="13"/>
     </row>
-    <row r="19" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+    <row r="19" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A19" s="23" t="s">
         <v>86</v>
       </c>
@@ -3705,7 +3713,7 @@
       <c r="N19" s="13"/>
       <c r="O19" s="13"/>
     </row>
-    <row r="20" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+    <row r="20" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A20" s="23" t="s">
         <v>90</v>
       </c>
@@ -3742,7 +3750,7 @@
       <c r="N20" s="13"/>
       <c r="O20" s="13"/>
     </row>
-    <row r="21" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+    <row r="21" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A21" s="23" t="s">
         <v>95</v>
       </c>
@@ -3779,7 +3787,7 @@
       <c r="N21" s="13"/>
       <c r="O21" s="13"/>
     </row>
-    <row r="22" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+    <row r="22" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A22" s="23" t="s">
         <v>99</v>
       </c>
@@ -3812,7 +3820,7 @@
       <c r="N22" s="13"/>
       <c r="O22" s="13"/>
     </row>
-    <row r="23" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+    <row r="23" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A23" s="23" t="s">
         <v>102</v>
       </c>
@@ -3844,7 +3852,7 @@
       <c r="N23" s="13"/>
       <c r="O23" s="13"/>
     </row>
-    <row r="24" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+    <row r="24" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A24" s="29" t="s">
         <v>105</v>
       </c>
@@ -3875,7 +3883,7 @@
       <c r="N24" s="13"/>
       <c r="O24" s="36"/>
     </row>
-    <row r="25" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+    <row r="25" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A25" s="29" t="s">
         <v>108</v>
       </c>
@@ -3906,7 +3914,7 @@
       <c r="N25" s="13"/>
       <c r="O25" s="36"/>
     </row>
-    <row r="26" ht="25" customHeight="1" spans="1:15">
+    <row r="26" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A26" s="12" t="s">
         <v>110</v>
       </c>
@@ -3943,7 +3951,7 @@
       <c r="N26" s="5"/>
       <c r="O26" s="5"/>
     </row>
-    <row r="27" ht="25" customHeight="1" spans="1:15">
+    <row r="27" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A27" s="12" t="s">
         <v>116</v>
       </c>
@@ -3980,7 +3988,7 @@
       <c r="N27" s="5"/>
       <c r="O27" s="5"/>
     </row>
-    <row r="28" ht="25" customHeight="1" spans="1:15">
+    <row r="28" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A28" s="12" t="s">
         <v>122</v>
       </c>
@@ -4017,7 +4025,7 @@
       <c r="N28" s="5"/>
       <c r="O28" s="5"/>
     </row>
-    <row r="29" ht="25" customHeight="1" spans="1:15">
+    <row r="29" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A29" s="12" t="s">
         <v>128</v>
       </c>
@@ -4054,7 +4062,7 @@
       <c r="N29" s="5"/>
       <c r="O29" s="5"/>
     </row>
-    <row r="30" ht="25" customHeight="1" spans="1:15">
+    <row r="30" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A30" s="12" t="s">
         <v>134</v>
       </c>
@@ -4091,7 +4099,7 @@
       <c r="N30" s="5"/>
       <c r="O30" s="5"/>
     </row>
-    <row r="31" ht="25" customHeight="1" spans="1:15">
+    <row r="31" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A31" s="12" t="s">
         <v>140</v>
       </c>
@@ -4128,7 +4136,7 @@
       <c r="N31" s="15"/>
       <c r="O31" s="5"/>
     </row>
-    <row r="32" ht="25" customHeight="1" spans="1:15">
+    <row r="32" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A32" s="12" t="s">
         <v>146</v>
       </c>
@@ -4165,7 +4173,7 @@
       <c r="N32" s="5"/>
       <c r="O32" s="37"/>
     </row>
-    <row r="33" ht="25" customHeight="1" spans="1:15">
+    <row r="33" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A33" s="12" t="s">
         <v>152</v>
       </c>
@@ -4202,7 +4210,7 @@
       <c r="N33" s="5"/>
       <c r="O33" s="37"/>
     </row>
-    <row r="34" ht="25" customHeight="1" spans="1:15">
+    <row r="34" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A34" s="12" t="s">
         <v>158</v>
       </c>
@@ -4239,7 +4247,7 @@
       <c r="N34" s="5"/>
       <c r="O34" s="37"/>
     </row>
-    <row r="35" ht="25" customHeight="1" spans="1:15">
+    <row r="35" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A35" s="12" t="s">
         <v>164</v>
       </c>
@@ -4276,7 +4284,7 @@
       <c r="N35" s="5"/>
       <c r="O35" s="37"/>
     </row>
-    <row r="36" ht="25" customHeight="1" spans="1:15">
+    <row r="36" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A36" s="12" t="s">
         <v>168</v>
       </c>
@@ -4313,7 +4321,7 @@
       <c r="N36" s="5"/>
       <c r="O36" s="37"/>
     </row>
-    <row r="37" ht="25" customHeight="1" spans="1:15">
+    <row r="37" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A37" s="12" t="s">
         <v>174</v>
       </c>
@@ -4350,7 +4358,7 @@
       <c r="N37" s="5"/>
       <c r="O37" s="37"/>
     </row>
-    <row r="38" ht="25" customHeight="1" spans="1:15">
+    <row r="38" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A38" s="12" t="s">
         <v>179</v>
       </c>
@@ -4387,7 +4395,7 @@
       <c r="N38" s="5"/>
       <c r="O38" s="37"/>
     </row>
-    <row r="39" ht="25" customHeight="1" spans="1:15">
+    <row r="39" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A39" s="12" t="s">
         <v>184</v>
       </c>
@@ -4424,7 +4432,7 @@
       <c r="N39" s="5"/>
       <c r="O39" s="37"/>
     </row>
-    <row r="40" ht="25" customHeight="1" spans="1:15">
+    <row r="40" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A40" s="12" t="s">
         <v>189</v>
       </c>
@@ -4461,7 +4469,7 @@
       <c r="N40" s="5"/>
       <c r="O40" s="37"/>
     </row>
-    <row r="41" ht="25" customHeight="1" spans="1:15">
+    <row r="41" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A41" s="12" t="s">
         <v>194</v>
       </c>
@@ -4498,7 +4506,7 @@
       <c r="N41" s="5"/>
       <c r="O41" s="37"/>
     </row>
-    <row r="42" ht="25" customHeight="1" spans="1:15">
+    <row r="42" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A42" s="12" t="s">
         <v>200</v>
       </c>
@@ -4535,7 +4543,7 @@
       <c r="N42" s="5"/>
       <c r="O42" s="37"/>
     </row>
-    <row r="43" ht="25" customHeight="1" spans="1:15">
+    <row r="43" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A43" s="12" t="s">
         <v>205</v>
       </c>
@@ -4570,7 +4578,7 @@
       <c r="N43" s="5"/>
       <c r="O43" s="37"/>
     </row>
-    <row r="44" ht="25" customHeight="1" spans="1:15">
+    <row r="44" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A44" s="12" t="s">
         <v>209</v>
       </c>
@@ -4607,7 +4615,7 @@
       <c r="N44" s="5"/>
       <c r="O44" s="37"/>
     </row>
-    <row r="45" ht="25" customHeight="1" spans="1:15">
+    <row r="45" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A45" s="12" t="s">
         <v>215</v>
       </c>
@@ -4642,7 +4650,7 @@
       <c r="N45" s="5"/>
       <c r="O45" s="37"/>
     </row>
-    <row r="46" ht="25" customHeight="1" spans="1:15">
+    <row r="46" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A46" s="12" t="s">
         <v>218</v>
       </c>
@@ -4679,7 +4687,7 @@
       <c r="N46" s="5"/>
       <c r="O46" s="37"/>
     </row>
-    <row r="47" ht="25" customHeight="1" spans="1:15">
+    <row r="47" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A47" s="12" t="s">
         <v>224</v>
       </c>
@@ -4702,7 +4710,7 @@
       <c r="N47" s="5"/>
       <c r="O47" s="37"/>
     </row>
-    <row r="48" ht="25" customHeight="1" spans="1:15">
+    <row r="48" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A48" s="12" t="s">
         <v>226</v>
       </c>
@@ -4725,7 +4733,7 @@
       <c r="N48" s="5"/>
       <c r="O48" s="37"/>
     </row>
-    <row r="49" ht="25" customHeight="1" spans="1:15">
+    <row r="49" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A49" s="12" t="s">
         <v>228</v>
       </c>
@@ -4748,7 +4756,7 @@
       <c r="N49" s="5"/>
       <c r="O49" s="37"/>
     </row>
-    <row r="50" ht="25" customHeight="1" spans="1:15">
+    <row r="50" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A50" s="12" t="s">
         <v>230</v>
       </c>
@@ -4771,7 +4779,7 @@
       <c r="N50" s="5"/>
       <c r="O50" s="37"/>
     </row>
-    <row r="51" ht="25" customHeight="1" spans="1:15">
+    <row r="51" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A51" s="14" t="s">
         <v>232</v>
       </c>
@@ -4794,7 +4802,7 @@
       <c r="N51" s="5"/>
       <c r="O51" s="37"/>
     </row>
-    <row r="52" ht="25" customHeight="1" spans="1:15">
+    <row r="52" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A52" s="12" t="s">
         <v>234</v>
       </c>
@@ -4816,7 +4824,7 @@
       <c r="N52" s="5"/>
       <c r="O52" s="37"/>
     </row>
-    <row r="53" ht="25" customHeight="1" spans="1:15">
+    <row r="53" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A53" s="12" t="s">
         <v>236</v>
       </c>
@@ -4839,7 +4847,7 @@
       <c r="N53" s="5"/>
       <c r="O53" s="37"/>
     </row>
-    <row r="54" ht="25" customHeight="1" spans="1:15">
+    <row r="54" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A54" s="12" t="s">
         <v>238</v>
       </c>
@@ -4862,7 +4870,7 @@
       <c r="N54" s="5"/>
       <c r="O54" s="37"/>
     </row>
-    <row r="55" ht="25" customHeight="1" spans="1:15">
+    <row r="55" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A55" s="12" t="s">
         <v>240</v>
       </c>
@@ -4884,7 +4892,7 @@
       <c r="N55" s="5"/>
       <c r="O55" s="37"/>
     </row>
-    <row r="56" ht="25" customHeight="1" spans="1:15">
+    <row r="56" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A56" s="12" t="s">
         <v>242</v>
       </c>
@@ -4907,7 +4915,7 @@
       <c r="N56" s="5"/>
       <c r="O56" s="37"/>
     </row>
-    <row r="57" ht="25" customHeight="1" spans="1:15">
+    <row r="57" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A57" s="12" t="s">
         <v>244</v>
       </c>
@@ -4930,7 +4938,7 @@
       <c r="N57" s="5"/>
       <c r="O57" s="37"/>
     </row>
-    <row r="58" ht="25" customHeight="1" spans="1:15">
+    <row r="58" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A58" s="12" t="s">
         <v>246</v>
       </c>
@@ -4953,7 +4961,7 @@
       <c r="N58" s="5"/>
       <c r="O58" s="37"/>
     </row>
-    <row r="59" ht="25" customHeight="1" spans="1:15">
+    <row r="59" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A59" s="12" t="s">
         <v>248</v>
       </c>
@@ -4975,7 +4983,7 @@
       <c r="N59" s="5"/>
       <c r="O59" s="37"/>
     </row>
-    <row r="60" ht="25" customHeight="1" spans="1:15">
+    <row r="60" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A60" s="12" t="s">
         <v>250</v>
       </c>
@@ -4998,7 +5006,7 @@
       <c r="N60" s="5"/>
       <c r="O60" s="37"/>
     </row>
-    <row r="61" customFormat="1" ht="25" customHeight="1" spans="1:15">
+    <row r="61" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A61" s="12" t="s">
         <v>252</v>
       </c>
@@ -5021,7 +5029,7 @@
       <c r="N61" s="5"/>
       <c r="O61" s="37"/>
     </row>
-    <row r="62" customFormat="1" ht="25" customHeight="1" spans="1:15">
+    <row r="62" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A62" s="12" t="s">
         <v>254</v>
       </c>
@@ -5044,7 +5052,7 @@
       <c r="N62" s="5"/>
       <c r="O62" s="37"/>
     </row>
-    <row r="63" customFormat="1" ht="25" customHeight="1" spans="1:15">
+    <row r="63" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A63" s="12" t="s">
         <v>256</v>
       </c>
@@ -5067,7 +5075,7 @@
       <c r="N63" s="5"/>
       <c r="O63" s="37"/>
     </row>
-    <row r="64" customFormat="1" ht="25" customHeight="1" spans="1:15">
+    <row r="64" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A64" s="12" t="s">
         <v>258</v>
       </c>
@@ -5090,7 +5098,7 @@
       <c r="N64" s="5"/>
       <c r="O64" s="37"/>
     </row>
-    <row r="65" customFormat="1" ht="25" customHeight="1" spans="1:15">
+    <row r="65" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A65" s="12" t="s">
         <v>260</v>
       </c>
@@ -5121,7 +5129,7 @@
       <c r="N65" s="5"/>
       <c r="O65" s="37"/>
     </row>
-    <row r="66" customFormat="1" ht="25" customHeight="1" spans="1:15">
+    <row r="66" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A66" s="12" t="s">
         <v>265</v>
       </c>
@@ -5152,7 +5160,7 @@
       <c r="N66" s="5"/>
       <c r="O66" s="5"/>
     </row>
-    <row r="67" customFormat="1" ht="25" customHeight="1" spans="1:15">
+    <row r="67" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A67" s="12" t="s">
         <v>269</v>
       </c>
@@ -5183,7 +5191,7 @@
       <c r="N67" s="5"/>
       <c r="O67" s="37"/>
     </row>
-    <row r="68" ht="25" customHeight="1" spans="1:15">
+    <row r="68" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A68" s="12" t="s">
         <v>273</v>
       </c>
@@ -5214,7 +5222,7 @@
       <c r="N68" s="5"/>
       <c r="O68" s="37"/>
     </row>
-    <row r="69" ht="25" customHeight="1" spans="1:15">
+    <row r="69" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A69" s="12" t="s">
         <v>278</v>
       </c>
@@ -5245,7 +5253,7 @@
       <c r="N69" s="5"/>
       <c r="O69" s="37"/>
     </row>
-    <row r="70" ht="25" customHeight="1" spans="1:15">
+    <row r="70" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A70" s="12" t="s">
         <v>282</v>
       </c>
@@ -5276,7 +5284,7 @@
       <c r="N70" s="5"/>
       <c r="O70" s="37"/>
     </row>
-    <row r="71" ht="25" customHeight="1" spans="1:15">
+    <row r="71" ht="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A71" s="12" t="s">
         <v>287</v>
       </c>
@@ -5565,6 +5573,9 @@
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:O71" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="4">
+      <colorFilter dxfId="0"/>
+    </filterColumn>
     <sortState ref="A1:O71">
       <sortCondition ref="F1"/>
     </sortState>

--- a/资源录入表新.xlsx
+++ b/资源录入表新.xlsx
@@ -16,7 +16,7 @@
     <sheet name="资源录入表 (2)" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">资源录入表!$A$1:$O$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">资源录入表!$A$1:$O$72</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'资源录入表 (2)'!$A$2:$I$20</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="868" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="303">
   <si>
     <t>剧名</t>
   </si>
@@ -91,6 +91,15 @@
   </si>
   <si>
     <t xml:space="preserve">链接: https://pan.baidu.com/s/1V8VWsfDlUm1NhfIO2dMB0Q 提取码: a5m2 </t>
+  </si>
+  <si>
+    <t>花开锦绣</t>
+  </si>
+  <si>
+    <t>剧情/古装</t>
+  </si>
+  <si>
+    <t>丁禹兮/邓恩熙/尤靖茹/白澍/吕晓霖</t>
   </si>
   <si>
     <t>御廷谣</t>
@@ -2356,7 +2365,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2420,18 +2429,33 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2450,10 +2474,13 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2462,7 +2489,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2526,15 +2553,7 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="18">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2728,25 +2747,25 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="7"/>
-      <tableStyleElement type="headerRow" dxfId="6"/>
-      <tableStyleElement type="totalRow" dxfId="5"/>
-      <tableStyleElement type="firstColumn" dxfId="4"/>
-      <tableStyleElement type="lastColumn" dxfId="3"/>
-      <tableStyleElement type="firstRowStripe" dxfId="2"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="1"/>
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="17"/>
-      <tableStyleElement type="totalRow" dxfId="16"/>
-      <tableStyleElement type="firstRowStripe" dxfId="15"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="14"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="13"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="11"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="10"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="9"/>
-      <tableStyleElement type="pageFieldValues" dxfId="8"/>
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -3014,15 +3033,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:O86"/>
+  <sheetPr/>
+  <dimension ref="A1:O87"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="17.625" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="1"/>
     <col min="3" max="3" width="30.5833333333333" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
-    <col min="5" max="5" width="9" style="22"/>
+    <col min="5" max="5" width="9" style="23"/>
     <col min="6" max="7" width="9" style="1"/>
     <col min="8" max="8" width="45.875" style="1" customWidth="1"/>
     <col min="9" max="9" width="74.25" style="1" customWidth="1"/>
@@ -3045,7 +3064,7 @@
       <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="24" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="5" t="s">
@@ -3072,31 +3091,31 @@
       <c r="O1" s="5"/>
     </row>
     <row r="2" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="8">
+      <c r="D2" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="27">
         <v>20</v>
       </c>
-      <c r="F2" s="24" t="s">
+      <c r="F2" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="24">
+      <c r="G2" s="26">
         <v>2026</v>
       </c>
-      <c r="H2" s="24" t="s">
+      <c r="H2" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="24" t="s">
+      <c r="I2" s="26" t="s">
         <v>17</v>
       </c>
       <c r="J2" s="13"/>
@@ -3107,33 +3126,29 @@
       <c r="O2" s="13"/>
     </row>
     <row r="3" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="24" t="s">
+      <c r="C3" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="8">
-        <v>21</v>
-      </c>
-      <c r="F3" s="24" t="s">
+      <c r="D3" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="24">
+      <c r="G3" s="8">
         <v>2026</v>
       </c>
-      <c r="H3" s="24" t="s">
+      <c r="H3" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="24" t="s">
-        <v>21</v>
-      </c>
+      <c r="I3" s="8"/>
       <c r="J3" s="13"/>
       <c r="K3" s="13"/>
       <c r="L3" s="13"/>
@@ -3141,105 +3156,105 @@
       <c r="N3" s="13"/>
       <c r="O3" s="13"/>
     </row>
-    <row r="4" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A4" s="23" t="s">
+    <row r="4" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A4" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="24" t="s">
+      <c r="D4" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="27">
+        <v>21</v>
+      </c>
+      <c r="F4" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="26">
+        <v>2026</v>
+      </c>
+      <c r="H4" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="24">
-        <v>33</v>
-      </c>
-      <c r="F4" s="24" t="s">
+      <c r="I4" s="26" t="s">
         <v>24</v>
-      </c>
-      <c r="G4" s="24">
-        <v>2026</v>
-      </c>
-      <c r="H4" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="I4" s="24" t="s">
-        <v>26</v>
       </c>
       <c r="J4" s="13"/>
       <c r="K4" s="13"/>
-      <c r="L4" s="13" t="s">
-        <v>27</v>
-      </c>
+      <c r="L4" s="13"/>
       <c r="M4" s="13"/>
       <c r="N4" s="13"/>
       <c r="O4" s="13"/>
     </row>
-    <row r="5" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A5" s="23" t="s">
+    <row r="5" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A5" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="29">
+        <v>33</v>
+      </c>
+      <c r="F5" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" s="26">
+        <v>2026</v>
+      </c>
+      <c r="H5" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="24" t="s">
+      <c r="I5" s="26" t="s">
         <v>29</v>
-      </c>
-      <c r="D5" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="24">
-        <v>36</v>
-      </c>
-      <c r="F5" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="G5" s="24">
-        <v>2026</v>
-      </c>
-      <c r="H5" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="I5" s="24" t="s">
-        <v>31</v>
       </c>
       <c r="J5" s="13"/>
       <c r="K5" s="13"/>
-      <c r="L5" s="13"/>
+      <c r="L5" s="13" t="s">
+        <v>30</v>
+      </c>
       <c r="M5" s="13"/>
       <c r="N5" s="13"/>
       <c r="O5" s="13"/>
     </row>
-    <row r="6" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A6" s="23" t="s">
+    <row r="6" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A6" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="24" t="s">
+      <c r="D6" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="29">
+        <v>36</v>
+      </c>
+      <c r="F6" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" s="26">
+        <v>2026</v>
+      </c>
+      <c r="H6" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="24">
-        <v>24</v>
-      </c>
-      <c r="F6" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="G6" s="24">
-        <v>2026</v>
-      </c>
-      <c r="H6" s="24" t="s">
+      <c r="I6" s="26" t="s">
         <v>34</v>
-      </c>
-      <c r="I6" s="24" t="s">
-        <v>35</v>
       </c>
       <c r="J6" s="13"/>
       <c r="K6" s="13"/>
@@ -3248,91 +3263,91 @@
       <c r="N6" s="13"/>
       <c r="O6" s="13"/>
     </row>
-    <row r="7" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A7" s="12" t="s">
+    <row r="7" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A7" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="D7" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="29">
+        <v>24</v>
+      </c>
+      <c r="F7" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" s="26">
+        <v>2026</v>
+      </c>
+      <c r="H7" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="J7" s="13"/>
+      <c r="K7" s="13"/>
+      <c r="L7" s="13"/>
+      <c r="M7" s="13"/>
+      <c r="N7" s="13"/>
+      <c r="O7" s="13"/>
+    </row>
+    <row r="8" ht="25" customHeight="1" spans="1:15">
+      <c r="A8" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="26" t="s">
-        <v>37</v>
-      </c>
-      <c r="D7" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="28">
+      <c r="C8" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="33">
         <v>18</v>
       </c>
-      <c r="F7" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="G7" s="5">
+      <c r="F8" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" s="5">
         <v>2026</v>
       </c>
-      <c r="H7" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
-      <c r="M7" s="5"/>
-      <c r="N7" s="5"/>
-      <c r="O7" s="5"/>
-    </row>
-    <row r="8" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A8" s="29" t="s">
-        <v>40</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="30" t="s">
+      <c r="H8" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D8" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="11">
-        <v>18</v>
-      </c>
-      <c r="F8" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="G8" s="13">
-        <v>2026</v>
-      </c>
-      <c r="H8" s="31" t="s">
+      <c r="I8" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="I8" s="13" t="s">
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
+    </row>
+    <row r="9" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A9" s="34" t="s">
         <v>43</v>
-      </c>
-      <c r="J8" s="13"/>
-      <c r="K8" s="13"/>
-      <c r="L8" s="13"/>
-      <c r="M8" s="13"/>
-      <c r="N8" s="13"/>
-      <c r="O8" s="13"/>
-    </row>
-    <row r="9" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A9" s="29" t="s">
-        <v>44</v>
       </c>
       <c r="B9" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="30" t="s">
-        <v>45</v>
-      </c>
-      <c r="D9" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" s="11">
-        <v>17</v>
+      <c r="C9" s="35" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="36">
+        <v>18</v>
       </c>
       <c r="F9" s="13" t="s">
         <v>15</v>
@@ -3340,11 +3355,11 @@
       <c r="G9" s="13">
         <v>2026</v>
       </c>
-      <c r="H9" s="31" t="s">
+      <c r="H9" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="I9" s="13" t="s">
         <v>46</v>
-      </c>
-      <c r="I9" s="13" t="s">
-        <v>47</v>
       </c>
       <c r="J9" s="13"/>
       <c r="K9" s="13"/>
@@ -3353,33 +3368,33 @@
       <c r="N9" s="13"/>
       <c r="O9" s="13"/>
     </row>
-    <row r="10" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A10" s="23" t="s">
+    <row r="10" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A10" s="34" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="B10" s="24" t="s">
+      <c r="D10" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="36">
+        <v>17</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" s="13">
+        <v>2026</v>
+      </c>
+      <c r="H10" s="37" t="s">
         <v>49</v>
       </c>
-      <c r="C10" s="24" t="s">
+      <c r="I10" s="13" t="s">
         <v>50</v>
-      </c>
-      <c r="D10" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="24">
-        <v>4</v>
-      </c>
-      <c r="F10" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="G10" s="24">
-        <v>2026</v>
-      </c>
-      <c r="H10" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="I10" s="24" t="s">
-        <v>52</v>
       </c>
       <c r="J10" s="13"/>
       <c r="K10" s="13"/>
@@ -3389,32 +3404,32 @@
       <c r="O10" s="13"/>
     </row>
     <row r="11" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A11" s="23" t="s">
+      <c r="A11" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="B11" s="24" t="s">
-        <v>49</v>
-      </c>
-      <c r="C11" s="24" t="s">
+      <c r="D11" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="29">
+        <v>4</v>
+      </c>
+      <c r="F11" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" s="26">
+        <v>2026</v>
+      </c>
+      <c r="H11" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="D11" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="8">
-        <v>5</v>
-      </c>
-      <c r="F11" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="G11" s="24">
-        <v>2026</v>
-      </c>
-      <c r="H11" s="24" t="s">
+      <c r="I11" s="26" t="s">
         <v>55</v>
-      </c>
-      <c r="I11" s="24" t="s">
-        <v>56</v>
       </c>
       <c r="J11" s="13"/>
       <c r="K11" s="13"/>
@@ -3424,32 +3439,32 @@
       <c r="O11" s="13"/>
     </row>
     <row r="12" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A12" s="32" t="s">
+      <c r="A12" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="B12" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="D12" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="27">
+        <v>5</v>
+      </c>
+      <c r="F12" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="26">
+        <v>2026</v>
+      </c>
+      <c r="H12" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="I12" s="26" t="s">
         <v>59</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E12" s="8">
-        <v>1</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G12" s="8">
-        <v>2026</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="I12" s="11" t="s">
-        <v>61</v>
       </c>
       <c r="J12" s="13"/>
       <c r="K12" s="13"/>
@@ -3458,391 +3473,394 @@
       <c r="N12" s="13"/>
       <c r="O12" s="13"/>
     </row>
-    <row r="13" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A13" s="23" t="s">
+    <row r="13" s="21" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A13" s="38" t="s">
+        <v>60</v>
+      </c>
+      <c r="B13" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13" s="27" t="s">
         <v>62</v>
       </c>
-      <c r="B13" s="24" t="s">
-        <v>58</v>
-      </c>
-      <c r="C13" s="33" t="s">
+      <c r="D13" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="27">
+        <v>1</v>
+      </c>
+      <c r="F13" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" s="27">
+        <v>2026</v>
+      </c>
+      <c r="H13" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="D13" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="E13" s="8">
+      <c r="I13" s="36" t="s">
+        <v>64</v>
+      </c>
+      <c r="J13" s="24"/>
+      <c r="K13" s="24"/>
+      <c r="L13" s="24"/>
+      <c r="M13" s="24"/>
+      <c r="N13" s="24"/>
+      <c r="O13" s="24"/>
+    </row>
+    <row r="14" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A14" s="25" t="s">
+        <v>65</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="C14" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" s="27">
         <v>3</v>
       </c>
-      <c r="F13" s="24" t="s">
+      <c r="F14" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="G13" s="24">
+      <c r="G14" s="26">
         <v>2026</v>
       </c>
-      <c r="H13" s="24" t="s">
-        <v>64</v>
-      </c>
-      <c r="I13" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="J13" s="13"/>
-      <c r="K13" s="13"/>
-      <c r="L13" s="13"/>
-      <c r="M13" s="13"/>
-      <c r="N13" s="13"/>
-      <c r="O13" s="13"/>
-    </row>
-    <row r="14" s="21" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A14" s="23" t="s">
-        <v>66</v>
-      </c>
-      <c r="B14" s="24" t="s">
-        <v>58</v>
-      </c>
-      <c r="C14" s="34" t="s">
+      <c r="H14" s="26" t="s">
         <v>67</v>
       </c>
-      <c r="D14" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" s="24">
+      <c r="I14" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="J14" s="13"/>
+      <c r="K14" s="13"/>
+      <c r="L14" s="13"/>
+      <c r="M14" s="13"/>
+      <c r="N14" s="13"/>
+      <c r="O14" s="13"/>
+    </row>
+    <row r="15" s="22" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A15" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="C15" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="D15" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" s="29">
         <v>2</v>
       </c>
-      <c r="F14" s="24" t="s">
+      <c r="F15" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="G14" s="24">
+      <c r="G15" s="26">
         <v>2026</v>
       </c>
-      <c r="H14" s="24" t="s">
-        <v>68</v>
-      </c>
-      <c r="I14" s="25" t="s">
-        <v>69</v>
-      </c>
-      <c r="J14" s="25"/>
-      <c r="K14" s="25"/>
-      <c r="L14" s="25"/>
-      <c r="M14" s="25"/>
-      <c r="N14" s="25"/>
-      <c r="O14" s="25"/>
-    </row>
-    <row r="15" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A15" s="23" t="s">
-        <v>70</v>
-      </c>
-      <c r="B15" s="24" t="s">
-        <v>58</v>
-      </c>
-      <c r="C15" s="24" t="s">
+      <c r="H15" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="D15" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="E15" s="24">
+      <c r="I15" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="J15" s="30"/>
+      <c r="K15" s="30"/>
+      <c r="L15" s="30"/>
+      <c r="M15" s="30"/>
+      <c r="N15" s="30"/>
+      <c r="O15" s="30"/>
+    </row>
+    <row r="16" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A16" s="25" t="s">
+        <v>73</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="C16" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="D16" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" s="29">
         <v>8</v>
       </c>
-      <c r="F15" s="24" t="s">
+      <c r="F16" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="G15" s="24">
+      <c r="G16" s="26">
         <v>2026</v>
       </c>
-      <c r="H15" s="24" t="s">
-        <v>72</v>
-      </c>
-      <c r="I15" s="24" t="s">
-        <v>73</v>
-      </c>
-      <c r="J15" s="13"/>
-      <c r="K15" s="13"/>
-      <c r="L15" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="M15" s="13"/>
-      <c r="N15" s="13"/>
-      <c r="O15" s="13"/>
-    </row>
-    <row r="16" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A16" s="23" t="s">
-        <v>74</v>
-      </c>
-      <c r="B16" s="24" t="s">
+      <c r="H16" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="C16" s="24" t="s">
+      <c r="I16" s="26" t="s">
         <v>76</v>
-      </c>
-      <c r="D16" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="E16" s="8">
-        <v>8</v>
-      </c>
-      <c r="F16" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="G16" s="24">
-        <v>2026</v>
-      </c>
-      <c r="H16" s="24" t="s">
-        <v>77</v>
-      </c>
-      <c r="I16" s="24" t="s">
-        <v>78</v>
       </c>
       <c r="J16" s="13"/>
       <c r="K16" s="13"/>
       <c r="L16" s="13" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="M16" s="13"/>
       <c r="N16" s="13"/>
       <c r="O16" s="13"/>
     </row>
-    <row r="17" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A17" s="23" t="s">
+    <row r="17" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A17" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="C17" s="26" t="s">
         <v>79</v>
       </c>
-      <c r="B17" s="24" t="s">
-        <v>58</v>
-      </c>
-      <c r="C17" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="D17" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="E17" s="24">
-        <v>6</v>
-      </c>
-      <c r="F17" s="24" t="s">
+      <c r="D17" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="E17" s="27">
+        <v>8</v>
+      </c>
+      <c r="F17" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="G17" s="24">
+      <c r="G17" s="26">
         <v>2026</v>
       </c>
-      <c r="H17" s="24" t="s">
+      <c r="H17" s="26" t="s">
         <v>80</v>
       </c>
-      <c r="I17" s="24" t="s">
+      <c r="I17" s="26" t="s">
         <v>81</v>
       </c>
       <c r="J17" s="13"/>
       <c r="K17" s="13"/>
       <c r="L17" s="13" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="M17" s="13"/>
       <c r="N17" s="13"/>
       <c r="O17" s="13"/>
     </row>
-    <row r="18" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A18" s="23" t="s">
+    <row r="18" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A18" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="B18" s="24" t="s">
-        <v>58</v>
-      </c>
-      <c r="C18" s="24" t="s">
+      <c r="B18" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="C18" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="D18" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="29">
+        <v>6</v>
+      </c>
+      <c r="F18" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="G18" s="26">
+        <v>2026</v>
+      </c>
+      <c r="H18" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="D18" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="E18" s="35">
-        <v>8</v>
-      </c>
-      <c r="F18" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="G18" s="24">
-        <v>2026</v>
-      </c>
-      <c r="H18" s="24" t="s">
+      <c r="I18" s="26" t="s">
         <v>84</v>
-      </c>
-      <c r="I18" s="24" t="s">
-        <v>85</v>
       </c>
       <c r="J18" s="13"/>
       <c r="K18" s="13"/>
       <c r="L18" s="13" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="M18" s="13"/>
       <c r="N18" s="13"/>
       <c r="O18" s="13"/>
     </row>
-    <row r="19" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A19" s="23" t="s">
+    <row r="19" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A19" s="25" t="s">
+        <v>85</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="C19" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="B19" s="24" t="s">
-        <v>58</v>
-      </c>
-      <c r="C19" s="24" t="s">
+      <c r="D19" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19" s="27">
+        <v>8</v>
+      </c>
+      <c r="F19" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="G19" s="26">
+        <v>2026</v>
+      </c>
+      <c r="H19" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="D19" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="E19" s="35">
-        <v>10</v>
-      </c>
-      <c r="F19" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="G19" s="24">
-        <v>2026</v>
-      </c>
-      <c r="H19" s="24" t="s">
+      <c r="I19" s="26" t="s">
         <v>88</v>
-      </c>
-      <c r="I19" s="24" t="s">
-        <v>89</v>
       </c>
       <c r="J19" s="13"/>
       <c r="K19" s="13"/>
       <c r="L19" s="13" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="M19" s="13"/>
       <c r="N19" s="13"/>
       <c r="O19" s="13"/>
     </row>
-    <row r="20" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A20" s="23" t="s">
+    <row r="20" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A20" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20" s="26" t="s">
         <v>90</v>
       </c>
-      <c r="B20" s="24" t="s">
-        <v>58</v>
-      </c>
-      <c r="C20" s="24" t="s">
+      <c r="D20" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="E20" s="27">
+        <v>10</v>
+      </c>
+      <c r="F20" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="G20" s="26">
+        <v>2026</v>
+      </c>
+      <c r="H20" s="26" t="s">
         <v>91</v>
       </c>
-      <c r="D20" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="E20" s="24">
-        <v>6</v>
-      </c>
-      <c r="F20" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="G20" s="24">
-        <v>2026</v>
-      </c>
-      <c r="H20" s="24" t="s">
+      <c r="I20" s="26" t="s">
         <v>92</v>
-      </c>
-      <c r="I20" s="24" t="s">
-        <v>93</v>
       </c>
       <c r="J20" s="13"/>
       <c r="K20" s="13"/>
       <c r="L20" s="13" t="s">
-        <v>94</v>
+        <v>61</v>
       </c>
       <c r="M20" s="13"/>
       <c r="N20" s="13"/>
       <c r="O20" s="13"/>
     </row>
-    <row r="21" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A21" s="23" t="s">
+    <row r="21" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A21" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="C21" s="26" t="s">
+        <v>94</v>
+      </c>
+      <c r="D21" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="E21" s="29">
+        <v>6</v>
+      </c>
+      <c r="F21" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="G21" s="26">
+        <v>2026</v>
+      </c>
+      <c r="H21" s="26" t="s">
         <v>95</v>
       </c>
-      <c r="B21" s="24" t="s">
-        <v>58</v>
-      </c>
-      <c r="C21" s="24" t="s">
+      <c r="I21" s="26" t="s">
         <v>96</v>
-      </c>
-      <c r="D21" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="E21" s="24">
-        <v>10</v>
-      </c>
-      <c r="F21" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="G21" s="24">
-        <v>2026</v>
-      </c>
-      <c r="H21" s="24" t="s">
-        <v>97</v>
-      </c>
-      <c r="I21" s="24" t="s">
-        <v>98</v>
       </c>
       <c r="J21" s="13"/>
       <c r="K21" s="13"/>
       <c r="L21" s="13" t="s">
-        <v>58</v>
+        <v>97</v>
       </c>
       <c r="M21" s="13"/>
       <c r="N21" s="13"/>
       <c r="O21" s="13"/>
     </row>
-    <row r="22" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A22" s="23" t="s">
+    <row r="22" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A22" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="C22" s="26" t="s">
         <v>99</v>
       </c>
-      <c r="B22" s="24" t="s">
-        <v>49</v>
-      </c>
-      <c r="C22" s="24" t="s">
+      <c r="D22" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="E22" s="29">
+        <v>10</v>
+      </c>
+      <c r="F22" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="G22" s="26">
+        <v>2026</v>
+      </c>
+      <c r="H22" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="D22" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="E22" s="24">
-        <v>7</v>
-      </c>
-      <c r="F22" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="G22" s="24">
-        <v>2026</v>
-      </c>
-      <c r="H22" s="24"/>
-      <c r="I22" s="24" t="s">
+      <c r="I22" s="26" t="s">
         <v>101</v>
       </c>
       <c r="J22" s="13"/>
       <c r="K22" s="13"/>
-      <c r="L22" s="13"/>
+      <c r="L22" s="13" t="s">
+        <v>61</v>
+      </c>
       <c r="M22" s="13"/>
       <c r="N22" s="13"/>
       <c r="O22" s="13"/>
     </row>
-    <row r="23" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A23" s="23" t="s">
+    <row r="23" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A23" s="25" t="s">
         <v>102</v>
       </c>
-      <c r="B23" s="24" t="s">
-        <v>49</v>
-      </c>
-      <c r="C23" s="24" t="s">
+      <c r="B23" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C23" s="26" t="s">
         <v>103</v>
       </c>
-      <c r="D23" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="E23" s="24">
-        <v>5</v>
-      </c>
-      <c r="F23" s="24" t="s">
+      <c r="D23" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="E23" s="29">
+        <v>7</v>
+      </c>
+      <c r="F23" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="G23" s="24">
+      <c r="G23" s="26">
         <v>2026</v>
       </c>
-      <c r="I23" s="24" t="s">
+      <c r="H23" s="26"/>
+      <c r="I23" s="26" t="s">
         <v>104</v>
       </c>
       <c r="J23" s="13"/>
@@ -3852,28 +3870,29 @@
       <c r="N23" s="13"/>
       <c r="O23" s="13"/>
     </row>
-    <row r="24" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A24" s="29" t="s">
+    <row r="24" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A24" s="25" t="s">
         <v>105</v>
       </c>
-      <c r="B24" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="C24" s="25" t="s">
+      <c r="B24" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C24" s="26" t="s">
         <v>106</v>
       </c>
-      <c r="D24" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="E24" s="25"/>
-      <c r="F24" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="G24" s="24">
+      <c r="D24" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="E24" s="29">
+        <v>5</v>
+      </c>
+      <c r="F24" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="G24" s="26">
         <v>2026</v>
       </c>
-      <c r="H24" s="24"/>
-      <c r="I24" s="13" t="s">
+      <c r="I24" s="26" t="s">
         <v>107</v>
       </c>
       <c r="J24" s="13"/>
@@ -3881,1454 +3900,1468 @@
       <c r="L24" s="13"/>
       <c r="M24" s="13"/>
       <c r="N24" s="13"/>
-      <c r="O24" s="36"/>
-    </row>
-    <row r="25" s="20" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A25" s="29" t="s">
+      <c r="O24" s="13"/>
+    </row>
+    <row r="25" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A25" s="34" t="s">
         <v>108</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="C25" s="25" t="s">
-        <v>106</v>
-      </c>
-      <c r="D25" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="E25" s="25"/>
-      <c r="F25" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="G25" s="24">
+        <v>52</v>
+      </c>
+      <c r="C25" s="30" t="s">
+        <v>109</v>
+      </c>
+      <c r="D25" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="E25" s="41"/>
+      <c r="F25" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="G25" s="26">
         <v>2026</v>
       </c>
-      <c r="H25" s="24"/>
+      <c r="H25" s="26"/>
       <c r="I25" s="13" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J25" s="13"/>
       <c r="K25" s="13"/>
       <c r="L25" s="13"/>
       <c r="M25" s="13"/>
       <c r="N25" s="13"/>
-      <c r="O25" s="36"/>
-    </row>
-    <row r="26" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A26" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C26" s="5" t="s">
+      <c r="O25" s="42"/>
+    </row>
+    <row r="26" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A26" s="34" t="s">
         <v>111</v>
       </c>
-      <c r="D26" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E26" s="13" t="s">
+      <c r="B26" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="C26" s="30" t="s">
+        <v>109</v>
+      </c>
+      <c r="D26" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="E26" s="41"/>
+      <c r="F26" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="G26" s="26">
+        <v>2026</v>
+      </c>
+      <c r="H26" s="26"/>
+      <c r="I26" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="F26" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G26" s="5">
-        <v>2026</v>
-      </c>
-      <c r="H26" s="5" t="s">
+      <c r="J26" s="13"/>
+      <c r="K26" s="13"/>
+      <c r="L26" s="13"/>
+      <c r="M26" s="13"/>
+      <c r="N26" s="13"/>
+      <c r="O26" s="42"/>
+    </row>
+    <row r="27" ht="25" customHeight="1" spans="1:15">
+      <c r="A27" s="12" t="s">
         <v>113</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="J26" s="5"/>
-      <c r="K26" s="5"/>
-      <c r="L26" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="M26" s="5"/>
-      <c r="N26" s="5"/>
-      <c r="O26" s="5"/>
-    </row>
-    <row r="27" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A27" s="12" t="s">
-        <v>116</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C27" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E27" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G27" s="5">
+        <v>2026</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="I27" s="1" t="s">
         <v>117</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G27" s="5">
-        <v>2025</v>
-      </c>
-      <c r="H27" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>120</v>
       </c>
       <c r="J27" s="5"/>
       <c r="K27" s="5"/>
       <c r="L27" s="5" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="M27" s="5"/>
       <c r="N27" s="5"/>
       <c r="O27" s="5"/>
     </row>
-    <row r="28" ht="25" hidden="1" customHeight="1" spans="1:15">
+    <row r="28" ht="25" customHeight="1" spans="1:15">
       <c r="A28" s="12" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C28" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E28" s="24" t="s">
+        <v>121</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G28" s="5">
+        <v>2025</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="I28" s="1" t="s">
         <v>123</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>124</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G28" s="5">
-        <v>2026</v>
-      </c>
-      <c r="H28" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>126</v>
       </c>
       <c r="J28" s="5"/>
       <c r="K28" s="5"/>
       <c r="L28" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="M28" s="5"/>
       <c r="N28" s="5"/>
       <c r="O28" s="5"/>
     </row>
-    <row r="29" ht="25" hidden="1" customHeight="1" spans="1:15">
+    <row r="29" ht="25" customHeight="1" spans="1:15">
       <c r="A29" s="12" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E29" s="13" t="s">
-        <v>130</v>
+      <c r="E29" s="24" t="s">
+        <v>127</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G29" s="5">
         <v>2026</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="J29" s="5"/>
       <c r="K29" s="5"/>
       <c r="L29" s="5" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="M29" s="5"/>
       <c r="N29" s="5"/>
       <c r="O29" s="5"/>
     </row>
-    <row r="30" ht="25" hidden="1" customHeight="1" spans="1:15">
+    <row r="30" ht="25" customHeight="1" spans="1:15">
       <c r="A30" s="12" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C30" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E30" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G30" s="5">
+        <v>2026</v>
+      </c>
+      <c r="H30" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="I30" s="1" t="s">
         <v>135</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="F30" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G30" s="5">
-        <v>2025</v>
-      </c>
-      <c r="H30" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="I30" s="1" t="s">
-        <v>138</v>
       </c>
       <c r="J30" s="5"/>
       <c r="K30" s="5"/>
       <c r="L30" s="5" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="M30" s="5"/>
       <c r="N30" s="5"/>
       <c r="O30" s="5"/>
     </row>
-    <row r="31" ht="25" hidden="1" customHeight="1" spans="1:15">
+    <row r="31" ht="25" customHeight="1" spans="1:15">
       <c r="A31" s="12" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C31" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E31" s="24" t="s">
+        <v>139</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G31" s="5">
+        <v>2025</v>
+      </c>
+      <c r="H31" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="I31" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="D31" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E31" s="13" t="s">
+      <c r="J31" s="5"/>
+      <c r="K31" s="5"/>
+      <c r="L31" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="F31" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G31" s="5">
-        <v>2026</v>
-      </c>
-      <c r="H31" s="5" t="s">
+      <c r="M31" s="5"/>
+      <c r="N31" s="5"/>
+      <c r="O31" s="5"/>
+    </row>
+    <row r="32" ht="25" customHeight="1" spans="1:15">
+      <c r="A32" s="12" t="s">
         <v>143</v>
-      </c>
-      <c r="I31" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="J31" s="15"/>
-      <c r="K31" s="15"/>
-      <c r="L31" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="M31" s="15"/>
-      <c r="N31" s="15"/>
-      <c r="O31" s="5"/>
-    </row>
-    <row r="32" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A32" s="12" t="s">
-        <v>146</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E32" s="13" t="s">
-        <v>148</v>
+      <c r="E32" s="24" t="s">
+        <v>145</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G32" s="5">
         <v>2026</v>
       </c>
       <c r="H32" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="J32" s="15"/>
+      <c r="K32" s="15"/>
+      <c r="L32" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="M32" s="15"/>
+      <c r="N32" s="15"/>
+      <c r="O32" s="5"/>
+    </row>
+    <row r="33" ht="25" customHeight="1" spans="1:15">
+      <c r="A33" s="12" t="s">
         <v>149</v>
-      </c>
-      <c r="I32" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="J32" s="5"/>
-      <c r="K32" s="5"/>
-      <c r="L32" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="M32" s="5"/>
-      <c r="N32" s="5"/>
-      <c r="O32" s="37"/>
-    </row>
-    <row r="33" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A33" s="12" t="s">
-        <v>152</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C33" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E33" s="24" t="s">
+        <v>151</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G33" s="5">
+        <v>2026</v>
+      </c>
+      <c r="H33" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="I33" s="5" t="s">
         <v>153</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="F33" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G33" s="5">
-        <v>2024</v>
-      </c>
-      <c r="H33" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="I33" s="5" t="s">
-        <v>156</v>
       </c>
       <c r="J33" s="5"/>
       <c r="K33" s="5"/>
       <c r="L33" s="5" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="M33" s="5"/>
       <c r="N33" s="5"/>
-      <c r="O33" s="37"/>
-    </row>
-    <row r="34" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O33" s="43"/>
+    </row>
+    <row r="34" ht="25" customHeight="1" spans="1:15">
       <c r="A34" s="12" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E34" s="13" t="s">
-        <v>160</v>
+      <c r="E34" s="24" t="s">
+        <v>157</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G34" s="5">
         <v>2024</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="J34" s="5"/>
       <c r="K34" s="5"/>
       <c r="L34" s="5" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="M34" s="5"/>
       <c r="N34" s="5"/>
-      <c r="O34" s="37"/>
-    </row>
-    <row r="35" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O34" s="43"/>
+    </row>
+    <row r="35" ht="25" customHeight="1" spans="1:15">
       <c r="A35" s="12" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>129</v>
+        <v>162</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E35" s="13" t="s">
-        <v>130</v>
+      <c r="E35" s="24" t="s">
+        <v>163</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G35" s="5">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="H35" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="I35" s="5" t="s">
         <v>165</v>
-      </c>
-      <c r="I35" s="5" t="s">
-        <v>166</v>
       </c>
       <c r="J35" s="5"/>
       <c r="K35" s="5"/>
       <c r="L35" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="M35" s="5"/>
       <c r="N35" s="5"/>
-      <c r="O35" s="37"/>
-    </row>
-    <row r="36" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O35" s="43"/>
+    </row>
+    <row r="36" ht="25" customHeight="1" spans="1:15">
       <c r="A36" s="12" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C36" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E36" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G36" s="5">
+        <v>2026</v>
+      </c>
+      <c r="H36" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="I36" s="5" t="s">
         <v>169</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E36" s="13" t="s">
-        <v>170</v>
-      </c>
-      <c r="F36" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G36" s="5">
-        <v>2025</v>
-      </c>
-      <c r="H36" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="I36" s="5" t="s">
-        <v>172</v>
       </c>
       <c r="J36" s="5"/>
       <c r="K36" s="5"/>
       <c r="L36" s="5" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="M36" s="5"/>
       <c r="N36" s="5"/>
-      <c r="O36" s="37"/>
-    </row>
-    <row r="37" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O36" s="43"/>
+    </row>
+    <row r="37" ht="25" customHeight="1" spans="1:15">
       <c r="A37" s="12" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C37" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E37" s="24" t="s">
+        <v>173</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G37" s="5">
+        <v>2025</v>
+      </c>
+      <c r="H37" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="I37" s="5" t="s">
         <v>175</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E37" s="13" t="s">
-        <v>148</v>
-      </c>
-      <c r="F37" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G37" s="5">
-        <v>2026</v>
-      </c>
-      <c r="H37" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="I37" s="5" t="s">
-        <v>177</v>
       </c>
       <c r="J37" s="5"/>
       <c r="K37" s="5"/>
       <c r="L37" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="M37" s="5"/>
       <c r="N37" s="5"/>
-      <c r="O37" s="37"/>
-    </row>
-    <row r="38" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O37" s="43"/>
+    </row>
+    <row r="38" ht="25" customHeight="1" spans="1:15">
       <c r="A38" s="12" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E38" s="13" t="s">
-        <v>148</v>
+      <c r="E38" s="24" t="s">
+        <v>151</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G38" s="5">
         <v>2026</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I38" s="5" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="J38" s="5"/>
       <c r="K38" s="5"/>
       <c r="L38" s="5" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="M38" s="5"/>
       <c r="N38" s="5"/>
-      <c r="O38" s="37"/>
-    </row>
-    <row r="39" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O38" s="43"/>
+    </row>
+    <row r="39" ht="25" customHeight="1" spans="1:15">
       <c r="A39" s="12" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E39" s="13" t="s">
-        <v>112</v>
+      <c r="E39" s="24" t="s">
+        <v>151</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G39" s="5">
         <v>2026</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="I39" s="5" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="J39" s="5"/>
       <c r="K39" s="5"/>
       <c r="L39" s="5" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="M39" s="5"/>
       <c r="N39" s="5"/>
-      <c r="O39" s="37"/>
-    </row>
-    <row r="40" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O39" s="43"/>
+    </row>
+    <row r="40" ht="25" customHeight="1" spans="1:15">
       <c r="A40" s="12" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>135</v>
+        <v>188</v>
       </c>
       <c r="D40" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E40" s="13" t="s">
+      <c r="E40" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G40" s="5">
+        <v>2026</v>
+      </c>
+      <c r="H40" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="I40" s="5" t="s">
         <v>190</v>
-      </c>
-      <c r="F40" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G40" s="5">
-        <v>2025</v>
-      </c>
-      <c r="H40" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="I40" s="5" t="s">
-        <v>192</v>
       </c>
       <c r="J40" s="5"/>
       <c r="K40" s="5"/>
       <c r="L40" s="5" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="M40" s="5"/>
       <c r="N40" s="5"/>
-      <c r="O40" s="37"/>
-    </row>
-    <row r="41" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O40" s="43"/>
+    </row>
+    <row r="41" ht="25" customHeight="1" spans="1:15">
       <c r="A41" s="12" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C41" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E41" s="24" t="s">
+        <v>193</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G41" s="5">
+        <v>2025</v>
+      </c>
+      <c r="H41" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="I41" s="5" t="s">
         <v>195</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E41" s="13" t="s">
-        <v>196</v>
-      </c>
-      <c r="F41" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G41" s="5">
-        <v>2026</v>
-      </c>
-      <c r="H41" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="I41" s="5" t="s">
-        <v>198</v>
       </c>
       <c r="J41" s="5"/>
       <c r="K41" s="5"/>
       <c r="L41" s="5" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="M41" s="5"/>
       <c r="N41" s="5"/>
-      <c r="O41" s="37"/>
-    </row>
-    <row r="42" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O41" s="43"/>
+    </row>
+    <row r="42" ht="25" customHeight="1" spans="1:15">
       <c r="A42" s="12" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="D42" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E42" s="13" t="s">
-        <v>118</v>
+      <c r="E42" s="24" t="s">
+        <v>199</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G42" s="5">
         <v>2026</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I42" s="5" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="J42" s="5"/>
       <c r="K42" s="5"/>
       <c r="L42" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="M42" s="5"/>
       <c r="N42" s="5"/>
-      <c r="O42" s="37"/>
-    </row>
-    <row r="43" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O42" s="43"/>
+    </row>
+    <row r="43" ht="25" customHeight="1" spans="1:15">
       <c r="A43" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E43" s="24" t="s">
+        <v>121</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G43" s="5">
+        <v>2026</v>
+      </c>
+      <c r="H43" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="B43" s="24" t="s">
-        <v>58</v>
-      </c>
-      <c r="C43" s="5" t="s">
+      <c r="I43" s="5" t="s">
         <v>206</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E43" s="13" t="s">
-        <v>207</v>
-      </c>
-      <c r="F43" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G43" s="5">
-        <v>2025</v>
-      </c>
-      <c r="H43" s="5"/>
-      <c r="I43" s="5" t="s">
-        <v>208</v>
       </c>
       <c r="J43" s="5"/>
       <c r="K43" s="5"/>
       <c r="L43" s="5" t="s">
-        <v>58</v>
+        <v>207</v>
       </c>
       <c r="M43" s="5"/>
       <c r="N43" s="5"/>
-      <c r="O43" s="37"/>
-    </row>
-    <row r="44" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O43" s="43"/>
+    </row>
+    <row r="44" ht="25" customHeight="1" spans="1:15">
       <c r="A44" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="B44" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="C44" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="B44" s="24" t="s">
-        <v>58</v>
-      </c>
-      <c r="C44" s="5" t="s">
+      <c r="D44" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E44" s="24" t="s">
         <v>210</v>
       </c>
-      <c r="D44" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E44" s="13" t="s">
-        <v>211</v>
-      </c>
       <c r="F44" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G44" s="5">
         <v>2025</v>
       </c>
-      <c r="H44" s="5" t="s">
-        <v>212</v>
-      </c>
+      <c r="H44" s="5"/>
       <c r="I44" s="5" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="J44" s="5"/>
       <c r="K44" s="5"/>
       <c r="L44" s="5" t="s">
-        <v>214</v>
+        <v>61</v>
       </c>
       <c r="M44" s="5"/>
       <c r="N44" s="5"/>
-      <c r="O44" s="37"/>
-    </row>
-    <row r="45" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O44" s="43"/>
+    </row>
+    <row r="45" ht="25" customHeight="1" spans="1:15">
       <c r="A45" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="B45" s="24" t="s">
-        <v>58</v>
+        <v>212</v>
+      </c>
+      <c r="B45" s="26" t="s">
+        <v>61</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="D45" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E45" s="13" t="s">
-        <v>207</v>
+      <c r="E45" s="24" t="s">
+        <v>214</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G45" s="5">
         <v>2025</v>
       </c>
-      <c r="H45" s="5"/>
+      <c r="H45" s="5" t="s">
+        <v>215</v>
+      </c>
       <c r="I45" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="J45" s="5"/>
       <c r="K45" s="5"/>
       <c r="L45" s="5" t="s">
-        <v>58</v>
+        <v>217</v>
       </c>
       <c r="M45" s="5"/>
       <c r="N45" s="5"/>
-      <c r="O45" s="37"/>
-    </row>
-    <row r="46" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O45" s="43"/>
+    </row>
+    <row r="46" ht="25" customHeight="1" spans="1:15">
       <c r="A46" s="12" t="s">
         <v>218</v>
       </c>
-      <c r="B46" s="5" t="s">
+      <c r="B46" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="C46" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="C46" s="5" t="s">
+      <c r="D46" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E46" s="24" t="s">
+        <v>210</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G46" s="5">
+        <v>2025</v>
+      </c>
+      <c r="H46" s="5"/>
+      <c r="I46" s="5" t="s">
         <v>220</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E46" s="13" t="s">
-        <v>124</v>
-      </c>
-      <c r="F46" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G46" s="5">
-        <v>2026</v>
-      </c>
-      <c r="H46" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="I46" s="5" t="s">
-        <v>222</v>
       </c>
       <c r="J46" s="5"/>
       <c r="K46" s="5"/>
       <c r="L46" s="5" t="s">
-        <v>223</v>
+        <v>61</v>
       </c>
       <c r="M46" s="5"/>
       <c r="N46" s="5"/>
-      <c r="O46" s="37"/>
-    </row>
-    <row r="47" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O46" s="43"/>
+    </row>
+    <row r="47" ht="25" customHeight="1" spans="1:15">
       <c r="A47" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E47" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="F47" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G47" s="5">
+        <v>2026</v>
+      </c>
+      <c r="H47" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="B47" s="5"/>
-      <c r="C47" s="5"/>
-      <c r="D47" s="5"/>
-      <c r="E47" s="13"/>
-      <c r="F47" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G47" s="5"/>
-      <c r="H47" s="5"/>
       <c r="I47" s="5" t="s">
         <v>225</v>
       </c>
       <c r="J47" s="5"/>
       <c r="K47" s="5"/>
-      <c r="L47" s="5"/>
+      <c r="L47" s="5" t="s">
+        <v>226</v>
+      </c>
       <c r="M47" s="5"/>
       <c r="N47" s="5"/>
-      <c r="O47" s="37"/>
-    </row>
-    <row r="48" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O47" s="43"/>
+    </row>
+    <row r="48" ht="25" customHeight="1" spans="1:15">
       <c r="A48" s="12" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
       <c r="D48" s="5"/>
-      <c r="E48" s="13"/>
+      <c r="E48" s="24"/>
       <c r="F48" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G48" s="5"/>
       <c r="H48" s="5"/>
       <c r="I48" s="5" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="J48" s="5"/>
       <c r="K48" s="5"/>
       <c r="L48" s="5"/>
       <c r="M48" s="5"/>
       <c r="N48" s="5"/>
-      <c r="O48" s="37"/>
-    </row>
-    <row r="49" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O48" s="43"/>
+    </row>
+    <row r="49" ht="25" customHeight="1" spans="1:15">
       <c r="A49" s="12" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
       <c r="D49" s="5"/>
-      <c r="E49" s="13"/>
+      <c r="E49" s="24"/>
       <c r="F49" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G49" s="5"/>
       <c r="H49" s="5"/>
       <c r="I49" s="5" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="J49" s="5"/>
       <c r="K49" s="5"/>
       <c r="L49" s="5"/>
       <c r="M49" s="5"/>
       <c r="N49" s="5"/>
-      <c r="O49" s="37"/>
-    </row>
-    <row r="50" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O49" s="43"/>
+    </row>
+    <row r="50" ht="25" customHeight="1" spans="1:15">
       <c r="A50" s="12" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5"/>
       <c r="D50" s="5"/>
-      <c r="E50" s="13"/>
+      <c r="E50" s="24"/>
       <c r="F50" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G50" s="5"/>
       <c r="H50" s="5"/>
       <c r="I50" s="5" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="J50" s="5"/>
       <c r="K50" s="5"/>
       <c r="L50" s="5"/>
       <c r="M50" s="5"/>
       <c r="N50" s="5"/>
-      <c r="O50" s="37"/>
-    </row>
-    <row r="51" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A51" s="14" t="s">
-        <v>232</v>
-      </c>
-      <c r="B51" s="15"/>
-      <c r="C51" s="15"/>
-      <c r="D51" s="15"/>
-      <c r="E51" s="28"/>
+      <c r="O50" s="43"/>
+    </row>
+    <row r="51" ht="25" customHeight="1" spans="1:15">
+      <c r="A51" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="B51" s="5"/>
+      <c r="C51" s="5"/>
+      <c r="D51" s="5"/>
+      <c r="E51" s="24"/>
       <c r="F51" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G51" s="15"/>
-      <c r="H51" s="15"/>
-      <c r="I51" s="16" t="s">
-        <v>233</v>
-      </c>
-      <c r="J51" s="15"/>
+        <v>27</v>
+      </c>
+      <c r="G51" s="5"/>
+      <c r="H51" s="5"/>
+      <c r="I51" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="J51" s="5"/>
       <c r="K51" s="5"/>
       <c r="L51" s="5"/>
       <c r="M51" s="5"/>
       <c r="N51" s="5"/>
-      <c r="O51" s="37"/>
-    </row>
-    <row r="52" ht="25" hidden="1" customHeight="1" spans="1:15">
-      <c r="A52" s="12" t="s">
-        <v>234</v>
-      </c>
-      <c r="B52" s="5"/>
-      <c r="C52" s="5"/>
-      <c r="D52" s="5"/>
-      <c r="E52" s="13"/>
+      <c r="O51" s="43"/>
+    </row>
+    <row r="52" ht="25" customHeight="1" spans="1:15">
+      <c r="A52" s="14" t="s">
+        <v>235</v>
+      </c>
+      <c r="B52" s="15"/>
+      <c r="C52" s="15"/>
+      <c r="D52" s="15"/>
+      <c r="E52" s="33"/>
       <c r="F52" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G52" s="5"/>
-      <c r="I52" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="J52" s="5"/>
+        <v>27</v>
+      </c>
+      <c r="G52" s="15"/>
+      <c r="H52" s="15"/>
+      <c r="I52" s="16" t="s">
+        <v>236</v>
+      </c>
+      <c r="J52" s="15"/>
       <c r="K52" s="5"/>
       <c r="L52" s="5"/>
       <c r="M52" s="5"/>
       <c r="N52" s="5"/>
-      <c r="O52" s="37"/>
-    </row>
-    <row r="53" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O52" s="43"/>
+    </row>
+    <row r="53" ht="25" customHeight="1" spans="1:15">
       <c r="A53" s="12" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5"/>
       <c r="D53" s="5"/>
-      <c r="E53" s="13"/>
+      <c r="E53" s="24"/>
       <c r="F53" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G53" s="5"/>
-      <c r="H53" s="5"/>
       <c r="I53" s="5" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="J53" s="5"/>
       <c r="K53" s="5"/>
       <c r="L53" s="5"/>
       <c r="M53" s="5"/>
       <c r="N53" s="5"/>
-      <c r="O53" s="37"/>
-    </row>
-    <row r="54" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O53" s="43"/>
+    </row>
+    <row r="54" ht="25" customHeight="1" spans="1:15">
       <c r="A54" s="12" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
       <c r="D54" s="5"/>
-      <c r="E54" s="13"/>
+      <c r="E54" s="24"/>
       <c r="F54" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G54" s="5"/>
       <c r="H54" s="5"/>
       <c r="I54" s="5" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="J54" s="5"/>
       <c r="K54" s="5"/>
       <c r="L54" s="5"/>
       <c r="M54" s="5"/>
       <c r="N54" s="5"/>
-      <c r="O54" s="37"/>
-    </row>
-    <row r="55" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O54" s="43"/>
+    </row>
+    <row r="55" ht="25" customHeight="1" spans="1:15">
       <c r="A55" s="12" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B55" s="5"/>
       <c r="C55" s="5"/>
       <c r="D55" s="5"/>
-      <c r="E55" s="13"/>
+      <c r="E55" s="24"/>
       <c r="F55" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G55" s="5"/>
+      <c r="H55" s="5"/>
       <c r="I55" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="J55" s="5"/>
       <c r="K55" s="5"/>
       <c r="L55" s="5"/>
       <c r="M55" s="5"/>
       <c r="N55" s="5"/>
-      <c r="O55" s="37"/>
-    </row>
-    <row r="56" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O55" s="43"/>
+    </row>
+    <row r="56" ht="25" customHeight="1" spans="1:15">
       <c r="A56" s="12" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
       <c r="D56" s="5"/>
-      <c r="E56" s="13"/>
+      <c r="E56" s="24"/>
       <c r="F56" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G56" s="5"/>
-      <c r="H56" s="5"/>
       <c r="I56" s="5" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="J56" s="5"/>
       <c r="K56" s="5"/>
       <c r="L56" s="5"/>
       <c r="M56" s="5"/>
       <c r="N56" s="5"/>
-      <c r="O56" s="37"/>
-    </row>
-    <row r="57" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O56" s="43"/>
+    </row>
+    <row r="57" ht="25" customHeight="1" spans="1:15">
       <c r="A57" s="12" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
       <c r="D57" s="5"/>
-      <c r="E57" s="13"/>
+      <c r="E57" s="24"/>
       <c r="F57" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G57" s="5"/>
       <c r="H57" s="5"/>
       <c r="I57" s="5" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="J57" s="5"/>
       <c r="K57" s="5"/>
       <c r="L57" s="5"/>
       <c r="M57" s="5"/>
       <c r="N57" s="5"/>
-      <c r="O57" s="37"/>
-    </row>
-    <row r="58" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O57" s="43"/>
+    </row>
+    <row r="58" ht="25" customHeight="1" spans="1:15">
       <c r="A58" s="12" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
       <c r="D58" s="5"/>
-      <c r="E58" s="13"/>
+      <c r="E58" s="24"/>
       <c r="F58" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G58" s="5"/>
       <c r="H58" s="5"/>
       <c r="I58" s="5" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="J58" s="5"/>
       <c r="K58" s="5"/>
       <c r="L58" s="5"/>
       <c r="M58" s="5"/>
       <c r="N58" s="5"/>
-      <c r="O58" s="37"/>
-    </row>
-    <row r="59" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O58" s="43"/>
+    </row>
+    <row r="59" ht="25" customHeight="1" spans="1:15">
       <c r="A59" s="12" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
       <c r="D59" s="5"/>
-      <c r="E59" s="13"/>
+      <c r="E59" s="24"/>
       <c r="F59" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G59" s="5"/>
+      <c r="H59" s="5"/>
       <c r="I59" s="5" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="J59" s="5"/>
       <c r="K59" s="5"/>
       <c r="L59" s="5"/>
       <c r="M59" s="5"/>
       <c r="N59" s="5"/>
-      <c r="O59" s="37"/>
-    </row>
-    <row r="60" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O59" s="43"/>
+    </row>
+    <row r="60" ht="25" customHeight="1" spans="1:15">
       <c r="A60" s="12" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
       <c r="D60" s="5"/>
-      <c r="E60" s="13"/>
+      <c r="E60" s="24"/>
       <c r="F60" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G60" s="5"/>
-      <c r="H60" s="5"/>
       <c r="I60" s="5" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="J60" s="5"/>
       <c r="K60" s="5"/>
       <c r="L60" s="5"/>
       <c r="M60" s="5"/>
       <c r="N60" s="5"/>
-      <c r="O60" s="37"/>
-    </row>
-    <row r="61" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O60" s="43"/>
+    </row>
+    <row r="61" ht="25" customHeight="1" spans="1:15">
       <c r="A61" s="12" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
       <c r="D61" s="5"/>
-      <c r="E61" s="13"/>
+      <c r="E61" s="24"/>
       <c r="F61" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G61" s="5"/>
       <c r="H61" s="5"/>
       <c r="I61" s="5" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="J61" s="5"/>
       <c r="K61" s="5"/>
       <c r="L61" s="5"/>
       <c r="M61" s="5"/>
       <c r="N61" s="5"/>
-      <c r="O61" s="37"/>
-    </row>
-    <row r="62" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O61" s="43"/>
+    </row>
+    <row r="62" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A62" s="12" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B62" s="5"/>
       <c r="C62" s="5"/>
       <c r="D62" s="5"/>
-      <c r="E62" s="13"/>
+      <c r="E62" s="24"/>
       <c r="F62" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G62" s="5"/>
       <c r="H62" s="5"/>
       <c r="I62" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="J62" s="5"/>
       <c r="K62" s="5"/>
       <c r="L62" s="5"/>
       <c r="M62" s="5"/>
       <c r="N62" s="5"/>
-      <c r="O62" s="37"/>
-    </row>
-    <row r="63" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O62" s="43"/>
+    </row>
+    <row r="63" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A63" s="12" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B63" s="5"/>
       <c r="C63" s="5"/>
       <c r="D63" s="5"/>
-      <c r="E63" s="13"/>
+      <c r="E63" s="24"/>
       <c r="F63" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G63" s="5"/>
       <c r="H63" s="5"/>
       <c r="I63" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="J63" s="5"/>
       <c r="K63" s="5"/>
       <c r="L63" s="5"/>
       <c r="M63" s="5"/>
       <c r="N63" s="5"/>
-      <c r="O63" s="37"/>
-    </row>
-    <row r="64" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O63" s="43"/>
+    </row>
+    <row r="64" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A64" s="12" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B64" s="5"/>
       <c r="C64" s="5"/>
       <c r="D64" s="5"/>
-      <c r="E64" s="13"/>
+      <c r="E64" s="24"/>
       <c r="F64" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G64" s="5"/>
       <c r="H64" s="5"/>
       <c r="I64" s="5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="J64" s="5"/>
       <c r="K64" s="5"/>
       <c r="L64" s="5"/>
       <c r="M64" s="5"/>
       <c r="N64" s="5"/>
-      <c r="O64" s="37"/>
-    </row>
-    <row r="65" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O64" s="43"/>
+    </row>
+    <row r="65" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A65" s="12" t="s">
-        <v>260</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C65" s="17" t="s">
         <v>261</v>
       </c>
+      <c r="B65" s="5"/>
+      <c r="C65" s="5"/>
       <c r="D65" s="5"/>
-      <c r="E65" s="13" t="s">
+      <c r="E65" s="24"/>
+      <c r="F65" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G65" s="5"/>
+      <c r="H65" s="5"/>
+      <c r="I65" s="5" t="s">
         <v>262</v>
-      </c>
-      <c r="F65" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G65" s="5"/>
-      <c r="H65" s="18" t="s">
-        <v>263</v>
-      </c>
-      <c r="I65" s="5" t="s">
-        <v>264</v>
       </c>
       <c r="J65" s="5"/>
       <c r="K65" s="5"/>
       <c r="L65" s="5"/>
       <c r="M65" s="5"/>
       <c r="N65" s="5"/>
-      <c r="O65" s="37"/>
-    </row>
-    <row r="66" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O65" s="43"/>
+    </row>
+    <row r="66" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A66" s="12" t="s">
+        <v>263</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C66" s="17" t="s">
+        <v>264</v>
+      </c>
+      <c r="D66" s="5"/>
+      <c r="E66" s="24" t="s">
         <v>265</v>
       </c>
-      <c r="B66" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C66" s="17" t="s">
-        <v>266</v>
-      </c>
-      <c r="D66" s="5"/>
-      <c r="E66" s="13" t="s">
-        <v>124</v>
-      </c>
       <c r="F66" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G66" s="5"/>
       <c r="H66" s="18" t="s">
+        <v>266</v>
+      </c>
+      <c r="I66" s="5" t="s">
         <v>267</v>
-      </c>
-      <c r="I66" s="5" t="s">
-        <v>268</v>
       </c>
       <c r="J66" s="5"/>
       <c r="K66" s="5"/>
       <c r="L66" s="5"/>
       <c r="M66" s="5"/>
       <c r="N66" s="5"/>
-      <c r="O66" s="5"/>
-    </row>
-    <row r="67" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O66" s="43"/>
+    </row>
+    <row r="67" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A67" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C67" s="17" t="s">
         <v>269</v>
       </c>
-      <c r="B67" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C67" s="19" t="s">
-        <v>270</v>
-      </c>
       <c r="D67" s="5"/>
-      <c r="E67" s="13" t="s">
-        <v>130</v>
+      <c r="E67" s="24" t="s">
+        <v>127</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G67" s="5"/>
       <c r="H67" s="18" t="s">
+        <v>270</v>
+      </c>
+      <c r="I67" s="5" t="s">
         <v>271</v>
-      </c>
-      <c r="I67" s="5" t="s">
-        <v>272</v>
       </c>
       <c r="J67" s="5"/>
       <c r="K67" s="5"/>
       <c r="L67" s="5"/>
       <c r="M67" s="5"/>
       <c r="N67" s="5"/>
-      <c r="O67" s="37"/>
-    </row>
-    <row r="68" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O67" s="5"/>
+    </row>
+    <row r="68" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A68" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C68" s="17" t="s">
-        <v>274</v>
+      <c r="C68" s="19" t="s">
+        <v>273</v>
       </c>
       <c r="D68" s="5"/>
-      <c r="E68" s="13" t="s">
-        <v>275</v>
+      <c r="E68" s="24" t="s">
+        <v>133</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G68" s="5"/>
       <c r="H68" s="18" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I68" s="5" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="J68" s="5"/>
       <c r="K68" s="5"/>
       <c r="L68" s="5"/>
       <c r="M68" s="5"/>
       <c r="N68" s="5"/>
-      <c r="O68" s="37"/>
-    </row>
-    <row r="69" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O68" s="43"/>
+    </row>
+    <row r="69" ht="25" customHeight="1" spans="1:15">
       <c r="A69" s="12" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C69" s="17" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D69" s="5"/>
-      <c r="E69" s="13" t="s">
-        <v>275</v>
+      <c r="E69" s="24" t="s">
+        <v>278</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G69" s="5"/>
       <c r="H69" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="I69" s="5" t="s">
         <v>280</v>
-      </c>
-      <c r="I69" s="5" t="s">
-        <v>281</v>
       </c>
       <c r="J69" s="5"/>
       <c r="K69" s="5"/>
       <c r="L69" s="5"/>
       <c r="M69" s="5"/>
       <c r="N69" s="5"/>
-      <c r="O69" s="37"/>
-    </row>
-    <row r="70" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O69" s="43"/>
+    </row>
+    <row r="70" ht="25" customHeight="1" spans="1:15">
       <c r="A70" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C70" s="17" t="s">
         <v>282</v>
       </c>
-      <c r="B70" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C70" s="17" t="s">
-        <v>283</v>
-      </c>
       <c r="D70" s="5"/>
-      <c r="E70" s="13" t="s">
-        <v>284</v>
+      <c r="E70" s="24" t="s">
+        <v>278</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G70" s="5"/>
       <c r="H70" s="18" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="I70" s="5" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="J70" s="5"/>
       <c r="K70" s="5"/>
       <c r="L70" s="5"/>
       <c r="M70" s="5"/>
       <c r="N70" s="5"/>
-      <c r="O70" s="37"/>
-    </row>
-    <row r="71" ht="25" hidden="1" customHeight="1" spans="1:15">
+      <c r="O70" s="43"/>
+    </row>
+    <row r="71" ht="25" customHeight="1" spans="1:15">
       <c r="A71" s="12" t="s">
+        <v>285</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C71" s="17" t="s">
+        <v>286</v>
+      </c>
+      <c r="D71" s="5"/>
+      <c r="E71" s="24" t="s">
         <v>287</v>
       </c>
-      <c r="B71" s="5" t="s">
+      <c r="F71" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G71" s="5"/>
+      <c r="H71" s="18" t="s">
         <v>288</v>
       </c>
-      <c r="C71" s="38" t="s">
+      <c r="I71" s="5" t="s">
         <v>289</v>
-      </c>
-      <c r="D71" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="E71" s="13" t="s">
-        <v>290</v>
-      </c>
-      <c r="F71" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="G71" s="24">
-        <v>2026</v>
-      </c>
-      <c r="H71" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="I71" s="5" t="s">
-        <v>292</v>
       </c>
       <c r="J71" s="5"/>
       <c r="K71" s="5"/>
       <c r="L71" s="5"/>
       <c r="M71" s="5"/>
       <c r="N71" s="5"/>
-      <c r="O71" s="5"/>
+      <c r="O71" s="43"/>
     </row>
     <row r="72" ht="25" customHeight="1" spans="1:15">
-      <c r="A72" s="12"/>
-      <c r="B72" s="5"/>
-      <c r="C72" s="5"/>
-      <c r="D72" s="5"/>
-      <c r="E72" s="13"/>
-      <c r="F72" s="13"/>
-      <c r="G72" s="5"/>
-      <c r="H72" s="5"/>
-      <c r="I72" s="5"/>
+      <c r="A72" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="C72" s="44" t="s">
+        <v>292</v>
+      </c>
+      <c r="D72" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="E72" s="24" t="s">
+        <v>293</v>
+      </c>
+      <c r="F72" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="G72" s="26">
+        <v>2026</v>
+      </c>
+      <c r="H72" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="I72" s="5" t="s">
+        <v>295</v>
+      </c>
       <c r="J72" s="5"/>
       <c r="K72" s="5"/>
       <c r="L72" s="5"/>
@@ -5341,9 +5374,10 @@
       <c r="B73" s="5"/>
       <c r="C73" s="5"/>
       <c r="D73" s="5"/>
-      <c r="E73" s="13"/>
+      <c r="E73" s="24"/>
       <c r="F73" s="13"/>
       <c r="G73" s="5"/>
+      <c r="H73" s="5"/>
       <c r="I73" s="5"/>
       <c r="J73" s="5"/>
       <c r="K73" s="5"/>
@@ -5357,10 +5391,9 @@
       <c r="B74" s="5"/>
       <c r="C74" s="5"/>
       <c r="D74" s="5"/>
-      <c r="E74" s="13"/>
+      <c r="E74" s="24"/>
       <c r="F74" s="13"/>
       <c r="G74" s="5"/>
-      <c r="H74" s="5"/>
       <c r="I74" s="5"/>
       <c r="J74" s="5"/>
       <c r="K74" s="5"/>
@@ -5374,7 +5407,7 @@
       <c r="B75" s="5"/>
       <c r="C75" s="5"/>
       <c r="D75" s="5"/>
-      <c r="E75" s="13"/>
+      <c r="E75" s="24"/>
       <c r="F75" s="13"/>
       <c r="G75" s="5"/>
       <c r="H75" s="5"/>
@@ -5391,9 +5424,10 @@
       <c r="B76" s="5"/>
       <c r="C76" s="5"/>
       <c r="D76" s="5"/>
-      <c r="E76" s="13"/>
+      <c r="E76" s="24"/>
       <c r="F76" s="13"/>
       <c r="G76" s="5"/>
+      <c r="H76" s="5"/>
       <c r="I76" s="5"/>
       <c r="J76" s="5"/>
       <c r="K76" s="5"/>
@@ -5407,10 +5441,9 @@
       <c r="B77" s="5"/>
       <c r="C77" s="5"/>
       <c r="D77" s="5"/>
-      <c r="E77" s="13"/>
+      <c r="E77" s="24"/>
       <c r="F77" s="13"/>
       <c r="G77" s="5"/>
-      <c r="H77" s="5"/>
       <c r="I77" s="5"/>
       <c r="J77" s="5"/>
       <c r="K77" s="5"/>
@@ -5424,7 +5457,7 @@
       <c r="B78" s="5"/>
       <c r="C78" s="5"/>
       <c r="D78" s="5"/>
-      <c r="E78" s="13"/>
+      <c r="E78" s="24"/>
       <c r="F78" s="13"/>
       <c r="G78" s="5"/>
       <c r="H78" s="5"/>
@@ -5441,7 +5474,7 @@
       <c r="B79" s="5"/>
       <c r="C79" s="5"/>
       <c r="D79" s="5"/>
-      <c r="E79" s="13"/>
+      <c r="E79" s="24"/>
       <c r="F79" s="13"/>
       <c r="G79" s="5"/>
       <c r="H79" s="5"/>
@@ -5458,9 +5491,10 @@
       <c r="B80" s="5"/>
       <c r="C80" s="5"/>
       <c r="D80" s="5"/>
-      <c r="E80" s="13"/>
+      <c r="E80" s="24"/>
       <c r="F80" s="13"/>
       <c r="G80" s="5"/>
+      <c r="H80" s="5"/>
       <c r="I80" s="5"/>
       <c r="J80" s="5"/>
       <c r="K80" s="5"/>
@@ -5474,10 +5508,9 @@
       <c r="B81" s="5"/>
       <c r="C81" s="5"/>
       <c r="D81" s="5"/>
-      <c r="E81" s="13"/>
+      <c r="E81" s="24"/>
       <c r="F81" s="13"/>
       <c r="G81" s="5"/>
-      <c r="H81" s="5"/>
       <c r="I81" s="5"/>
       <c r="J81" s="5"/>
       <c r="K81" s="5"/>
@@ -5491,7 +5524,7 @@
       <c r="B82" s="5"/>
       <c r="C82" s="5"/>
       <c r="D82" s="5"/>
-      <c r="E82" s="13"/>
+      <c r="E82" s="24"/>
       <c r="F82" s="13"/>
       <c r="G82" s="5"/>
       <c r="H82" s="5"/>
@@ -5508,7 +5541,7 @@
       <c r="B83" s="5"/>
       <c r="C83" s="5"/>
       <c r="D83" s="5"/>
-      <c r="E83" s="13"/>
+      <c r="E83" s="24"/>
       <c r="F83" s="13"/>
       <c r="G83" s="5"/>
       <c r="H83" s="5"/>
@@ -5525,7 +5558,7 @@
       <c r="B84" s="5"/>
       <c r="C84" s="5"/>
       <c r="D84" s="5"/>
-      <c r="E84" s="13"/>
+      <c r="E84" s="24"/>
       <c r="F84" s="13"/>
       <c r="G84" s="5"/>
       <c r="H84" s="5"/>
@@ -5542,7 +5575,7 @@
       <c r="B85" s="5"/>
       <c r="C85" s="5"/>
       <c r="D85" s="5"/>
-      <c r="E85" s="13"/>
+      <c r="E85" s="24"/>
       <c r="F85" s="13"/>
       <c r="G85" s="5"/>
       <c r="H85" s="5"/>
@@ -5559,7 +5592,7 @@
       <c r="B86" s="5"/>
       <c r="C86" s="5"/>
       <c r="D86" s="5"/>
-      <c r="E86" s="13"/>
+      <c r="E86" s="24"/>
       <c r="F86" s="13"/>
       <c r="G86" s="5"/>
       <c r="H86" s="5"/>
@@ -5571,19 +5604,33 @@
       <c r="N86" s="5"/>
       <c r="O86" s="5"/>
     </row>
+    <row r="87" ht="25" customHeight="1" spans="1:15">
+      <c r="A87" s="12"/>
+      <c r="B87" s="5"/>
+      <c r="C87" s="5"/>
+      <c r="D87" s="5"/>
+      <c r="E87" s="24"/>
+      <c r="F87" s="13"/>
+      <c r="G87" s="5"/>
+      <c r="H87" s="5"/>
+      <c r="I87" s="5"/>
+      <c r="J87" s="5"/>
+      <c r="K87" s="5"/>
+      <c r="L87" s="5"/>
+      <c r="M87" s="5"/>
+      <c r="N87" s="5"/>
+      <c r="O87" s="5"/>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:O71" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="4">
-      <colorFilter dxfId="0"/>
-    </filterColumn>
-    <sortState ref="A1:O71">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:O72" etc:filterBottomFollowUsedRange="0">
+    <sortState ref="A1:O72">
       <sortCondition ref="F1"/>
     </sortState>
     <extLst/>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="H66" r:id="rId1" display="普洛伊湘普·素帕莎 / 芭莉雅皮·余 " tooltip="https://www.douban.com/personage/30264980/"/>
-    <hyperlink ref="H21" r:id="rId2" display="金贤叙/郑明哲" tooltip="https://www.douban.com/personage/37338980/"/>
+    <hyperlink ref="H67" r:id="rId1" display="普洛伊湘普·素帕莎 / 芭莉雅皮·余 " tooltip="https://www.douban.com/personage/30264980/"/>
+    <hyperlink ref="H22" r:id="rId2" display="金贤叙/郑明哲" tooltip="https://www.douban.com/personage/37338980/"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -5607,7 +5654,7 @@
   <sheetData>
     <row r="1" ht="33" customHeight="1" spans="1:9">
       <c r="A1" s="3" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -5654,7 +5701,7 @@
         <v>12</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>14</v>
@@ -5677,13 +5724,13 @@
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:9">
       <c r="A4" s="6" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>14</v>
@@ -5698,21 +5745,21 @@
         <v>2026</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:9">
       <c r="A5" s="6" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>14</v>
@@ -5727,21 +5774,21 @@
         <v>2026</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:9">
       <c r="A6" s="6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>14</v>
@@ -5756,21 +5803,21 @@
         <v>2026</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:9">
       <c r="A7" s="6" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>14</v>
@@ -5785,21 +5832,21 @@
         <v>2026</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:9">
       <c r="A8" s="6" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>14</v>
@@ -5814,21 +5861,21 @@
         <v>2026</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:9">
       <c r="A9" s="6" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>14</v>
@@ -5843,21 +5890,21 @@
         <v>2026</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:9">
       <c r="A10" s="6" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>14</v>
@@ -5872,21 +5919,21 @@
         <v>2026</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:9">
       <c r="A11" s="6" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>14</v>
@@ -5901,21 +5948,21 @@
         <v>2026</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:9">
       <c r="A12" s="6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>14</v>
@@ -5930,21 +5977,21 @@
         <v>2026</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:9">
       <c r="A13" s="6" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>14</v>
@@ -5959,21 +6006,21 @@
         <v>2026</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:9">
       <c r="A14" s="6" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>14</v>
@@ -5988,21 +6035,21 @@
         <v>2026</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:9">
       <c r="A15" s="6" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>14</v>
@@ -6017,21 +6064,21 @@
         <v>2026</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:9">
       <c r="A16" s="6" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>14</v>
@@ -6046,21 +6093,21 @@
         <v>2026</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:9">
       <c r="A17" s="6" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>14</v>
@@ -6076,18 +6123,18 @@
       </c>
       <c r="H17" s="7"/>
       <c r="I17" s="8" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:9">
       <c r="A18" s="6" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>14</v>
@@ -6103,1118 +6150,1118 @@
       </c>
       <c r="H18" s="7"/>
       <c r="I18" s="8" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" spans="1:9">
       <c r="A19" s="9" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>14</v>
       </c>
       <c r="E19" s="10"/>
       <c r="F19" s="10" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G19" s="7">
         <v>2026</v>
       </c>
       <c r="H19" s="7"/>
       <c r="I19" s="11" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" spans="1:9">
       <c r="A20" s="9" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>14</v>
       </c>
       <c r="E20" s="10"/>
       <c r="F20" s="10" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G20" s="7">
         <v>2026</v>
       </c>
       <c r="H20" s="7"/>
       <c r="I20" s="11" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1" spans="1:9">
       <c r="A21" s="12" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G21" s="5">
         <v>2026</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1" spans="1:9">
       <c r="A22" s="12" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G22" s="5">
         <v>2025</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1" spans="1:9">
       <c r="A23" s="12" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G23" s="5">
         <v>2026</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1" spans="1:9">
       <c r="A24" s="12" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G24" s="5">
         <v>2026</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1" spans="1:9">
       <c r="A25" s="12" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G25" s="5">
         <v>2025</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1" spans="1:9">
       <c r="A26" s="12" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G26" s="5">
         <v>2026</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1" spans="1:9">
       <c r="A27" s="12" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G27" s="5">
         <v>2026</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1" spans="1:9">
       <c r="A28" s="12" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G28" s="5">
         <v>2024</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="29" ht="25" customHeight="1" spans="1:9">
       <c r="A29" s="12" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G29" s="5">
         <v>2024</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="30" ht="25" customHeight="1" spans="1:9">
       <c r="A30" s="12" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G30" s="5">
         <v>2026</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="31" ht="25" customHeight="1" spans="1:9">
       <c r="A31" s="12" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G31" s="5">
         <v>2025</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="32" ht="25" customHeight="1" spans="1:9">
       <c r="A32" s="12" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G32" s="5">
         <v>2026</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
     </row>
     <row r="33" ht="25" customHeight="1" spans="1:9">
       <c r="A33" s="12" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G33" s="5">
         <v>2026</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="I33" s="5" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="34" ht="25" customHeight="1" spans="1:9">
       <c r="A34" s="12" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G34" s="5">
         <v>2026</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="35" ht="25" customHeight="1" spans="1:9">
       <c r="A35" s="12" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G35" s="5">
         <v>2025</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="36" ht="25" customHeight="1" spans="1:9">
       <c r="A36" s="12" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G36" s="5">
         <v>2026</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="37" ht="25" customHeight="1" spans="1:9">
       <c r="A37" s="12" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G37" s="5">
         <v>2026</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="I37" s="5" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="38" ht="25" customHeight="1" spans="1:9">
       <c r="A38" s="12" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G38" s="5">
         <v>2025</v>
       </c>
       <c r="H38" s="5"/>
       <c r="I38" s="5" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="39" ht="25" customHeight="1" spans="1:9">
       <c r="A39" s="12" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G39" s="5">
         <v>2025</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="I39" s="5" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="40" ht="25" customHeight="1" spans="1:9">
       <c r="A40" s="12" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B40" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="C40" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="C40" s="5" t="s">
-        <v>216</v>
-      </c>
       <c r="D40" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G40" s="5">
         <v>2025</v>
       </c>
       <c r="H40" s="5"/>
       <c r="I40" s="5" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="41" ht="25" customHeight="1" spans="1:9">
       <c r="A41" s="12" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G41" s="5">
         <v>2026</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="I41" s="5" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="42" ht="25" customHeight="1" spans="1:9">
       <c r="A42" s="12" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5"/>
       <c r="D42" s="5"/>
       <c r="E42" s="5"/>
       <c r="F42" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G42" s="5"/>
       <c r="H42" s="5"/>
       <c r="I42" s="5" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="43" ht="25" customHeight="1" spans="1:9">
       <c r="A43" s="12" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5"/>
       <c r="D43" s="5"/>
       <c r="E43" s="5"/>
       <c r="F43" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G43" s="5"/>
       <c r="H43" s="5"/>
       <c r="I43" s="5" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="44" ht="25" customHeight="1" spans="1:9">
       <c r="A44" s="12" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
       <c r="D44" s="5"/>
       <c r="E44" s="5"/>
       <c r="F44" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G44" s="5"/>
       <c r="H44" s="5"/>
       <c r="I44" s="5" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="45" ht="25" customHeight="1" spans="1:9">
       <c r="A45" s="12" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5"/>
       <c r="D45" s="5"/>
       <c r="E45" s="5"/>
       <c r="F45" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G45" s="5"/>
       <c r="H45" s="5"/>
       <c r="I45" s="5" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="46" ht="25" customHeight="1" spans="1:9">
       <c r="A46" s="14" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B46" s="15"/>
       <c r="C46" s="15"/>
       <c r="D46" s="15"/>
       <c r="E46" s="15"/>
       <c r="F46" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G46" s="15"/>
       <c r="H46" s="15"/>
       <c r="I46" s="16" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="47" ht="25" customHeight="1" spans="1:9">
       <c r="A47" s="12" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
       <c r="D47" s="5"/>
       <c r="E47" s="5"/>
       <c r="F47" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G47" s="5"/>
       <c r="H47" s="5"/>
       <c r="I47" s="5" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="48" ht="25" customHeight="1" spans="1:9">
       <c r="A48" s="12" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
       <c r="D48" s="5"/>
       <c r="E48" s="5"/>
       <c r="F48" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G48" s="5"/>
       <c r="H48" s="5"/>
       <c r="I48" s="5" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="49" ht="25" customHeight="1" spans="1:9">
       <c r="A49" s="12" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
       <c r="D49" s="5"/>
       <c r="E49" s="5"/>
       <c r="F49" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G49" s="5"/>
       <c r="H49" s="5"/>
       <c r="I49" s="5" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
     </row>
     <row r="50" ht="25" customHeight="1" spans="1:9">
       <c r="A50" s="12" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5"/>
       <c r="D50" s="5"/>
       <c r="E50" s="5"/>
       <c r="F50" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G50" s="5"/>
       <c r="H50" s="5"/>
       <c r="I50" s="5" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="51" ht="25" customHeight="1" spans="1:9">
       <c r="A51" s="12" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
       <c r="D51" s="5"/>
       <c r="E51" s="5"/>
       <c r="F51" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G51" s="5"/>
       <c r="H51" s="5"/>
       <c r="I51" s="5" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="52" ht="25" customHeight="1" spans="1:9">
       <c r="A52" s="12" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5"/>
       <c r="D52" s="5"/>
       <c r="E52" s="5"/>
       <c r="F52" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G52" s="5"/>
       <c r="H52" s="5"/>
       <c r="I52" s="5" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
     </row>
     <row r="53" customFormat="1" ht="25" customHeight="1" spans="1:9">
       <c r="A53" s="12" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C53" s="17" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D53" s="5"/>
       <c r="E53" s="5" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G53" s="5"/>
       <c r="H53" s="18" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="I53" s="5" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="54" customFormat="1" ht="25" customHeight="1" spans="1:9">
       <c r="A54" s="12" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C54" s="17" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="D54" s="5"/>
       <c r="E54" s="5" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G54" s="5"/>
       <c r="H54" s="18" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="I54" s="5" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="55" customFormat="1" ht="25" customHeight="1" spans="1:9">
       <c r="A55" s="12" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C55" s="19" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="D55" s="5"/>
       <c r="E55" s="5" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G55" s="5"/>
       <c r="H55" s="18" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="I55" s="5" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="56" ht="25" customHeight="1" spans="1:9">
       <c r="A56" s="12" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C56" s="17" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="D56" s="5"/>
       <c r="E56" s="5" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G56" s="5"/>
       <c r="H56" s="18" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="I56" s="5" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="57" ht="25" customHeight="1" spans="1:9">
       <c r="A57" s="12" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C57" s="17" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="D57" s="5"/>
       <c r="E57" s="5" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G57" s="5"/>
       <c r="H57" s="18" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="I57" s="5" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="58" ht="25" customHeight="1" spans="1:9">
       <c r="A58" s="12" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C58" s="17" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D58" s="5"/>
       <c r="E58" s="5" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G58" s="5"/>
       <c r="H58" s="18" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="I58" s="5" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="59" ht="25" customHeight="1" spans="1:9">
       <c r="A59" s="12" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
       <c r="D59" s="5"/>
       <c r="E59" s="5"/>
       <c r="F59" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G59" s="5"/>
       <c r="H59" s="5"/>
       <c r="I59" s="5" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="60" ht="25" customHeight="1" spans="1:9">
       <c r="A60" s="12" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
       <c r="D60" s="5"/>
       <c r="E60" s="5"/>
       <c r="F60" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G60" s="5"/>
       <c r="H60" s="5"/>
       <c r="I60" s="5" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="61" ht="25" customHeight="1" spans="1:9">
       <c r="A61" s="12" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
       <c r="D61" s="5"/>
       <c r="E61" s="5"/>
       <c r="F61" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G61" s="5"/>
       <c r="H61" s="5"/>
       <c r="I61" s="5" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="62" customFormat="1" ht="25" customHeight="1" spans="1:9">
       <c r="A62" s="12" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B62" s="5"/>
       <c r="C62" s="5"/>
       <c r="D62" s="5"/>
       <c r="E62" s="5"/>
       <c r="F62" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G62" s="5"/>
       <c r="H62" s="5"/>
       <c r="I62" s="5" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
     </row>
     <row r="63" customFormat="1" ht="25" customHeight="1" spans="1:9">
       <c r="A63" s="12" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B63" s="5"/>
       <c r="C63" s="5"/>
       <c r="D63" s="5"/>
       <c r="E63" s="5"/>
       <c r="F63" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G63" s="5"/>
       <c r="H63" s="5"/>
       <c r="I63" s="5" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
     </row>
     <row r="64" customFormat="1" ht="25" customHeight="1" spans="1:9">
       <c r="A64" s="12" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B64" s="5"/>
       <c r="C64" s="5"/>
       <c r="D64" s="5"/>
       <c r="E64" s="5"/>
       <c r="F64" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G64" s="5"/>
       <c r="H64" s="5"/>
       <c r="I64" s="5" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
     </row>
     <row r="65" customFormat="1" ht="25" customHeight="1" spans="1:9">
       <c r="A65" s="12" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B65" s="5"/>
       <c r="C65" s="5"/>
       <c r="D65" s="5"/>
       <c r="E65" s="5"/>
       <c r="F65" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G65" s="5"/>
       <c r="H65" s="5"/>
       <c r="I65" s="5" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
     </row>
     <row r="66" ht="25" customHeight="1" spans="1:9">

--- a/资源录入表新.xlsx
+++ b/资源录入表新.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="875" uniqueCount="304">
   <si>
     <t>剧名</t>
   </si>
@@ -100,6 +100,9 @@
   </si>
   <si>
     <t>丁禹兮/邓恩熙/尤靖茹/白澍/吕晓霖</t>
+  </si>
+  <si>
+    <t xml:space="preserve">链接: https://pan.baidu.com/s/1PZzUg_FVUpXshewzBoLd0w 提取码: xec9 </t>
   </si>
   <si>
     <t>御廷谣</t>
@@ -458,6 +461,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="major"/>
+      </rPr>
       <t> </t>
     </r>
     <r>
@@ -472,6 +481,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="major"/>
+      </rPr>
       <t>安普贤</t>
     </r>
     <r>
@@ -1842,12 +1857,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF111111"/>
-      <name val="Helvetica"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="10.5"/>
       <name val="Arial"/>
       <charset val="134"/>
@@ -1865,6 +1874,12 @@
     <font>
       <sz val="12"/>
       <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF111111"/>
+      <name val="Helvetica"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -2365,7 +2380,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2429,33 +2444,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2474,22 +2477,13 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3041,7 +3035,7 @@
     <col min="2" max="2" width="9" style="1"/>
     <col min="3" max="3" width="30.5833333333333" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
-    <col min="5" max="5" width="9" style="23"/>
+    <col min="5" max="5" width="9" style="22"/>
     <col min="6" max="7" width="9" style="1"/>
     <col min="8" max="8" width="45.875" style="1" customWidth="1"/>
     <col min="9" max="9" width="74.25" style="1" customWidth="1"/>
@@ -3064,7 +3058,7 @@
       <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="24" t="s">
+      <c r="E1" s="13" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="5" t="s">
@@ -3091,31 +3085,31 @@
       <c r="O1" s="5"/>
     </row>
     <row r="2" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="26" t="s">
+      <c r="B2" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="26" t="s">
+      <c r="C2" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="27">
+      <c r="D2" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="24">
         <v>20</v>
       </c>
-      <c r="F2" s="26" t="s">
+      <c r="F2" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="26">
+      <c r="G2" s="24">
         <v>2026</v>
       </c>
-      <c r="H2" s="26" t="s">
+      <c r="H2" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="26" t="s">
+      <c r="I2" s="24" t="s">
         <v>17</v>
       </c>
       <c r="J2" s="13"/>
@@ -3126,7 +3120,7 @@
       <c r="O2" s="13"/>
     </row>
     <row r="3" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A3" s="28" t="s">
+      <c r="A3" s="25" t="s">
         <v>18</v>
       </c>
       <c r="B3" s="8" t="s">
@@ -3138,7 +3132,9 @@
       <c r="D3" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="8"/>
+      <c r="E3" s="8">
+        <v>3</v>
+      </c>
       <c r="F3" s="8" t="s">
         <v>15</v>
       </c>
@@ -3148,7 +3144,9 @@
       <c r="H3" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="8"/>
+      <c r="I3" s="5" t="s">
+        <v>21</v>
+      </c>
       <c r="J3" s="13"/>
       <c r="K3" s="13"/>
       <c r="L3" s="13"/>
@@ -3157,32 +3155,32 @@
       <c r="O3" s="13"/>
     </row>
     <row r="4" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="24">
         <v>21</v>
       </c>
-      <c r="B4" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="27">
-        <v>21</v>
-      </c>
-      <c r="F4" s="26" t="s">
+      <c r="F4" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="26">
+      <c r="G4" s="24">
         <v>2026</v>
       </c>
-      <c r="H4" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="I4" s="26" t="s">
+      <c r="H4" s="24" t="s">
         <v>24</v>
+      </c>
+      <c r="I4" s="24" t="s">
+        <v>25</v>
       </c>
       <c r="J4" s="13"/>
       <c r="K4" s="13"/>
@@ -3192,69 +3190,69 @@
       <c r="O4" s="13"/>
     </row>
     <row r="5" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A5" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" s="26" t="s">
+      <c r="A5" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="29">
+      <c r="C5" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="24">
         <v>33</v>
       </c>
-      <c r="F5" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="G5" s="26">
+      <c r="F5" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" s="24">
         <v>2026</v>
       </c>
-      <c r="H5" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="I5" s="26" t="s">
+      <c r="H5" s="24" t="s">
         <v>29</v>
+      </c>
+      <c r="I5" s="24" t="s">
+        <v>30</v>
       </c>
       <c r="J5" s="13"/>
       <c r="K5" s="13"/>
       <c r="L5" s="13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M5" s="13"/>
       <c r="N5" s="13"/>
       <c r="O5" s="13"/>
     </row>
     <row r="6" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A6" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6" s="26" t="s">
+      <c r="A6" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="29">
+      <c r="C6" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="24">
         <v>36</v>
       </c>
-      <c r="F6" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="G6" s="26">
+      <c r="F6" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" s="24">
         <v>2026</v>
       </c>
-      <c r="H6" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="I6" s="26" t="s">
+      <c r="H6" s="24" t="s">
         <v>34</v>
+      </c>
+      <c r="I6" s="24" t="s">
+        <v>35</v>
       </c>
       <c r="J6" s="13"/>
       <c r="K6" s="13"/>
@@ -3264,32 +3262,32 @@
       <c r="O6" s="13"/>
     </row>
     <row r="7" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A7" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" s="26" t="s">
+      <c r="A7" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="29">
+      <c r="C7" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="24">
         <v>24</v>
       </c>
-      <c r="F7" s="30" t="s">
-        <v>27</v>
-      </c>
-      <c r="G7" s="26">
+      <c r="F7" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" s="24">
         <v>2026</v>
       </c>
-      <c r="H7" s="26" t="s">
-        <v>37</v>
-      </c>
-      <c r="I7" s="26" t="s">
+      <c r="H7" s="24" t="s">
         <v>38</v>
+      </c>
+      <c r="I7" s="24" t="s">
+        <v>39</v>
       </c>
       <c r="J7" s="13"/>
       <c r="K7" s="13"/>
@@ -3300,31 +3298,31 @@
     </row>
     <row r="8" ht="25" customHeight="1" spans="1:15">
       <c r="A8" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="D8" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="33">
+      <c r="C8" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="29">
         <v>18</v>
       </c>
-      <c r="F8" s="26" t="s">
-        <v>27</v>
+      <c r="F8" s="24" t="s">
+        <v>28</v>
       </c>
       <c r="G8" s="5">
         <v>2026</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J8" s="5"/>
       <c r="K8" s="5"/>
@@ -3334,19 +3332,19 @@
       <c r="O8" s="5"/>
     </row>
     <row r="9" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A9" s="34" t="s">
-        <v>43</v>
+      <c r="A9" s="30" t="s">
+        <v>44</v>
       </c>
       <c r="B9" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="35" t="s">
-        <v>44</v>
-      </c>
-      <c r="D9" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" s="36">
+      <c r="C9" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="13">
         <v>18</v>
       </c>
       <c r="F9" s="13" t="s">
@@ -3355,11 +3353,11 @@
       <c r="G9" s="13">
         <v>2026</v>
       </c>
-      <c r="H9" s="37" t="s">
-        <v>45</v>
+      <c r="H9" s="32" t="s">
+        <v>46</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J9" s="13"/>
       <c r="K9" s="13"/>
@@ -3369,19 +3367,19 @@
       <c r="O9" s="13"/>
     </row>
     <row r="10" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A10" s="34" t="s">
-        <v>47</v>
+      <c r="A10" s="30" t="s">
+        <v>48</v>
       </c>
       <c r="B10" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="35" t="s">
-        <v>48</v>
-      </c>
-      <c r="D10" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="36">
+      <c r="C10" s="31" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="13">
         <v>17</v>
       </c>
       <c r="F10" s="13" t="s">
@@ -3390,11 +3388,11 @@
       <c r="G10" s="13">
         <v>2026</v>
       </c>
-      <c r="H10" s="37" t="s">
-        <v>49</v>
+      <c r="H10" s="32" t="s">
+        <v>50</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J10" s="13"/>
       <c r="K10" s="13"/>
@@ -3404,32 +3402,32 @@
       <c r="O10" s="13"/>
     </row>
     <row r="11" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A11" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="B11" s="26" t="s">
+      <c r="A11" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="C11" s="26" t="s">
+      <c r="B11" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="D11" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="29">
+      <c r="C11" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="D11" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="24">
         <v>4</v>
       </c>
-      <c r="F11" s="26" t="s">
+      <c r="F11" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="G11" s="26">
+      <c r="G11" s="24">
         <v>2026</v>
       </c>
-      <c r="H11" s="26" t="s">
-        <v>54</v>
-      </c>
-      <c r="I11" s="26" t="s">
+      <c r="H11" s="24" t="s">
         <v>55</v>
+      </c>
+      <c r="I11" s="24" t="s">
+        <v>56</v>
       </c>
       <c r="J11" s="13"/>
       <c r="K11" s="13"/>
@@ -3439,32 +3437,32 @@
       <c r="O11" s="13"/>
     </row>
     <row r="12" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A12" s="25" t="s">
-        <v>56</v>
-      </c>
-      <c r="B12" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="C12" s="26" t="s">
+      <c r="A12" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="D12" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="E12" s="27">
+      <c r="B12" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="D12" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="24">
         <v>5</v>
       </c>
-      <c r="F12" s="26" t="s">
+      <c r="F12" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="G12" s="26">
+      <c r="G12" s="24">
         <v>2026</v>
       </c>
-      <c r="H12" s="26" t="s">
-        <v>58</v>
-      </c>
-      <c r="I12" s="26" t="s">
+      <c r="H12" s="24" t="s">
         <v>59</v>
+      </c>
+      <c r="I12" s="24" t="s">
+        <v>60</v>
       </c>
       <c r="J12" s="13"/>
       <c r="K12" s="13"/>
@@ -3473,68 +3471,68 @@
       <c r="N12" s="13"/>
       <c r="O12" s="13"/>
     </row>
-    <row r="13" s="21" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A13" s="38" t="s">
-        <v>60</v>
-      </c>
-      <c r="B13" s="27" t="s">
+    <row r="13" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A13" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="C13" s="27" t="s">
+      <c r="B13" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="D13" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="E13" s="27">
+      <c r="C13" s="24" t="s">
+        <v>63</v>
+      </c>
+      <c r="D13" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="24">
         <v>1</v>
       </c>
-      <c r="F13" s="27" t="s">
+      <c r="F13" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="G13" s="27">
+      <c r="G13" s="24">
         <v>2026</v>
       </c>
-      <c r="H13" s="27" t="s">
-        <v>63</v>
-      </c>
-      <c r="I13" s="36" t="s">
+      <c r="H13" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="J13" s="24"/>
-      <c r="K13" s="24"/>
-      <c r="L13" s="24"/>
-      <c r="M13" s="24"/>
-      <c r="N13" s="24"/>
-      <c r="O13" s="24"/>
+      <c r="I13" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="J13" s="13"/>
+      <c r="K13" s="13"/>
+      <c r="L13" s="13"/>
+      <c r="M13" s="13"/>
+      <c r="N13" s="13"/>
+      <c r="O13" s="13"/>
     </row>
     <row r="14" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A14" s="25" t="s">
-        <v>65</v>
-      </c>
-      <c r="B14" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="C14" s="39" t="s">
+      <c r="A14" s="23" t="s">
         <v>66</v>
       </c>
-      <c r="D14" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" s="27">
+      <c r="B14" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="C14" s="33" t="s">
+        <v>67</v>
+      </c>
+      <c r="D14" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" s="24">
         <v>3</v>
       </c>
-      <c r="F14" s="26" t="s">
+      <c r="F14" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="G14" s="26">
+      <c r="G14" s="24">
         <v>2026</v>
       </c>
-      <c r="H14" s="26" t="s">
-        <v>67</v>
+      <c r="H14" s="24" t="s">
+        <v>68</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J14" s="13"/>
       <c r="K14" s="13"/>
@@ -3543,325 +3541,325 @@
       <c r="N14" s="13"/>
       <c r="O14" s="13"/>
     </row>
-    <row r="15" s="22" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A15" s="25" t="s">
-        <v>69</v>
-      </c>
-      <c r="B15" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="C15" s="40" t="s">
+    <row r="15" s="21" customFormat="1" ht="25" customHeight="1" spans="1:15">
+      <c r="A15" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="D15" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="E15" s="29">
+      <c r="B15" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="C15" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="D15" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" s="24">
         <v>2</v>
       </c>
-      <c r="F15" s="26" t="s">
+      <c r="F15" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="G15" s="26">
+      <c r="G15" s="24">
         <v>2026</v>
       </c>
-      <c r="H15" s="26" t="s">
-        <v>71</v>
-      </c>
-      <c r="I15" s="30" t="s">
+      <c r="H15" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="J15" s="30"/>
-      <c r="K15" s="30"/>
-      <c r="L15" s="30"/>
-      <c r="M15" s="30"/>
-      <c r="N15" s="30"/>
-      <c r="O15" s="30"/>
+      <c r="I15" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="J15" s="26"/>
+      <c r="K15" s="26"/>
+      <c r="L15" s="26"/>
+      <c r="M15" s="26"/>
+      <c r="N15" s="26"/>
+      <c r="O15" s="26"/>
     </row>
     <row r="16" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A16" s="25" t="s">
-        <v>73</v>
-      </c>
-      <c r="B16" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="C16" s="26" t="s">
+      <c r="A16" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="D16" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="E16" s="29">
+      <c r="B16" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="C16" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="D16" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" s="24">
         <v>8</v>
       </c>
-      <c r="F16" s="26" t="s">
+      <c r="F16" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="G16" s="26">
+      <c r="G16" s="24">
         <v>2026</v>
       </c>
-      <c r="H16" s="26" t="s">
-        <v>75</v>
-      </c>
-      <c r="I16" s="26" t="s">
+      <c r="H16" s="24" t="s">
         <v>76</v>
+      </c>
+      <c r="I16" s="24" t="s">
+        <v>77</v>
       </c>
       <c r="J16" s="13"/>
       <c r="K16" s="13"/>
       <c r="L16" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M16" s="13"/>
       <c r="N16" s="13"/>
       <c r="O16" s="13"/>
     </row>
     <row r="17" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A17" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="B17" s="26" t="s">
+      <c r="A17" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="C17" s="26" t="s">
+      <c r="B17" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="D17" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="E17" s="27">
+      <c r="C17" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="D17" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E17" s="24">
         <v>8</v>
       </c>
-      <c r="F17" s="26" t="s">
+      <c r="F17" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="G17" s="26">
+      <c r="G17" s="24">
         <v>2026</v>
       </c>
-      <c r="H17" s="26" t="s">
-        <v>80</v>
-      </c>
-      <c r="I17" s="26" t="s">
+      <c r="H17" s="24" t="s">
         <v>81</v>
+      </c>
+      <c r="I17" s="24" t="s">
+        <v>82</v>
       </c>
       <c r="J17" s="13"/>
       <c r="K17" s="13"/>
       <c r="L17" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M17" s="13"/>
       <c r="N17" s="13"/>
       <c r="O17" s="13"/>
     </row>
     <row r="18" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A18" s="25" t="s">
-        <v>82</v>
-      </c>
-      <c r="B18" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="C18" s="26" t="s">
-        <v>74</v>
-      </c>
-      <c r="D18" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="E18" s="29">
+      <c r="A18" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="B18" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="C18" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="D18" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="24">
         <v>6</v>
       </c>
-      <c r="F18" s="26" t="s">
+      <c r="F18" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="G18" s="26">
+      <c r="G18" s="24">
         <v>2026</v>
       </c>
-      <c r="H18" s="26" t="s">
-        <v>83</v>
-      </c>
-      <c r="I18" s="26" t="s">
+      <c r="H18" s="24" t="s">
         <v>84</v>
+      </c>
+      <c r="I18" s="24" t="s">
+        <v>85</v>
       </c>
       <c r="J18" s="13"/>
       <c r="K18" s="13"/>
       <c r="L18" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M18" s="13"/>
       <c r="N18" s="13"/>
       <c r="O18" s="13"/>
     </row>
     <row r="19" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A19" s="25" t="s">
-        <v>85</v>
-      </c>
-      <c r="B19" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="C19" s="26" t="s">
+      <c r="A19" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="D19" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="E19" s="27">
+      <c r="B19" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="C19" s="24" t="s">
+        <v>87</v>
+      </c>
+      <c r="D19" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19" s="24">
         <v>8</v>
       </c>
-      <c r="F19" s="26" t="s">
+      <c r="F19" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="G19" s="26">
+      <c r="G19" s="24">
         <v>2026</v>
       </c>
-      <c r="H19" s="26" t="s">
-        <v>87</v>
-      </c>
-      <c r="I19" s="26" t="s">
+      <c r="H19" s="24" t="s">
         <v>88</v>
+      </c>
+      <c r="I19" s="24" t="s">
+        <v>89</v>
       </c>
       <c r="J19" s="13"/>
       <c r="K19" s="13"/>
       <c r="L19" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M19" s="13"/>
       <c r="N19" s="13"/>
       <c r="O19" s="13"/>
     </row>
     <row r="20" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A20" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="B20" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="C20" s="26" t="s">
+      <c r="A20" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="D20" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="E20" s="27">
+      <c r="B20" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="C20" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="D20" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E20" s="24">
         <v>10</v>
       </c>
-      <c r="F20" s="26" t="s">
+      <c r="F20" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="G20" s="26">
+      <c r="G20" s="24">
         <v>2026</v>
       </c>
-      <c r="H20" s="26" t="s">
-        <v>91</v>
-      </c>
-      <c r="I20" s="26" t="s">
+      <c r="H20" s="24" t="s">
         <v>92</v>
+      </c>
+      <c r="I20" s="24" t="s">
+        <v>93</v>
       </c>
       <c r="J20" s="13"/>
       <c r="K20" s="13"/>
       <c r="L20" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M20" s="13"/>
       <c r="N20" s="13"/>
       <c r="O20" s="13"/>
     </row>
     <row r="21" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A21" s="25" t="s">
-        <v>93</v>
-      </c>
-      <c r="B21" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="C21" s="26" t="s">
+      <c r="A21" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="D21" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="E21" s="29">
+      <c r="B21" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="C21" s="24" t="s">
+        <v>95</v>
+      </c>
+      <c r="D21" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E21" s="24">
         <v>6</v>
       </c>
-      <c r="F21" s="26" t="s">
+      <c r="F21" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="G21" s="26">
+      <c r="G21" s="24">
         <v>2026</v>
       </c>
-      <c r="H21" s="26" t="s">
-        <v>95</v>
-      </c>
-      <c r="I21" s="26" t="s">
+      <c r="H21" s="24" t="s">
         <v>96</v>
+      </c>
+      <c r="I21" s="24" t="s">
+        <v>97</v>
       </c>
       <c r="J21" s="13"/>
       <c r="K21" s="13"/>
       <c r="L21" s="13" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M21" s="13"/>
       <c r="N21" s="13"/>
       <c r="O21" s="13"/>
     </row>
     <row r="22" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A22" s="25" t="s">
-        <v>98</v>
-      </c>
-      <c r="B22" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="C22" s="26" t="s">
+      <c r="A22" s="23" t="s">
         <v>99</v>
       </c>
-      <c r="D22" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="E22" s="29">
+      <c r="B22" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="C22" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="D22" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E22" s="24">
         <v>10</v>
       </c>
-      <c r="F22" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="G22" s="26">
+      <c r="F22" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="G22" s="24">
         <v>2026</v>
       </c>
-      <c r="H22" s="26" t="s">
-        <v>100</v>
-      </c>
-      <c r="I22" s="26" t="s">
+      <c r="H22" s="24" t="s">
         <v>101</v>
+      </c>
+      <c r="I22" s="24" t="s">
+        <v>102</v>
       </c>
       <c r="J22" s="13"/>
       <c r="K22" s="13"/>
       <c r="L22" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M22" s="13"/>
       <c r="N22" s="13"/>
       <c r="O22" s="13"/>
     </row>
     <row r="23" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A23" s="25" t="s">
-        <v>102</v>
-      </c>
-      <c r="B23" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="C23" s="26" t="s">
+      <c r="A23" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="D23" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="E23" s="29">
+      <c r="B23" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="C23" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="D23" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E23" s="24">
         <v>7</v>
       </c>
-      <c r="F23" s="26" t="s">
+      <c r="F23" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="G23" s="26">
+      <c r="G23" s="24">
         <v>2026</v>
       </c>
-      <c r="H23" s="26"/>
-      <c r="I23" s="26" t="s">
-        <v>104</v>
+      <c r="H23" s="24"/>
+      <c r="I23" s="24" t="s">
+        <v>105</v>
       </c>
       <c r="J23" s="13"/>
       <c r="K23" s="13"/>
@@ -3871,29 +3869,29 @@
       <c r="O23" s="13"/>
     </row>
     <row r="24" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A24" s="25" t="s">
-        <v>105</v>
-      </c>
-      <c r="B24" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="C24" s="26" t="s">
+      <c r="A24" s="23" t="s">
         <v>106</v>
       </c>
-      <c r="D24" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="E24" s="29">
+      <c r="B24" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="C24" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="D24" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E24" s="24">
         <v>5</v>
       </c>
-      <c r="F24" s="26" t="s">
+      <c r="F24" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="G24" s="26">
+      <c r="G24" s="24">
         <v>2026</v>
       </c>
-      <c r="I24" s="26" t="s">
-        <v>107</v>
+      <c r="I24" s="24" t="s">
+        <v>108</v>
       </c>
       <c r="J24" s="13"/>
       <c r="K24" s="13"/>
@@ -3903,99 +3901,99 @@
       <c r="O24" s="13"/>
     </row>
     <row r="25" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A25" s="34" t="s">
-        <v>108</v>
+      <c r="A25" s="30" t="s">
+        <v>109</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="C25" s="30" t="s">
-        <v>109</v>
-      </c>
-      <c r="D25" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="E25" s="41"/>
-      <c r="F25" s="30" t="s">
-        <v>27</v>
-      </c>
-      <c r="G25" s="26">
+        <v>53</v>
+      </c>
+      <c r="C25" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="D25" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E25" s="26"/>
+      <c r="F25" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="G25" s="24">
         <v>2026</v>
       </c>
-      <c r="H25" s="26"/>
+      <c r="H25" s="24"/>
       <c r="I25" s="13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J25" s="13"/>
       <c r="K25" s="13"/>
       <c r="L25" s="13"/>
       <c r="M25" s="13"/>
       <c r="N25" s="13"/>
-      <c r="O25" s="42"/>
+      <c r="O25" s="35"/>
     </row>
     <row r="26" s="20" customFormat="1" ht="25" customHeight="1" spans="1:15">
-      <c r="A26" s="34" t="s">
-        <v>111</v>
+      <c r="A26" s="30" t="s">
+        <v>112</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="C26" s="30" t="s">
-        <v>109</v>
-      </c>
-      <c r="D26" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="E26" s="41"/>
-      <c r="F26" s="30" t="s">
-        <v>27</v>
-      </c>
-      <c r="G26" s="26">
+        <v>53</v>
+      </c>
+      <c r="C26" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="D26" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E26" s="26"/>
+      <c r="F26" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="G26" s="24">
         <v>2026</v>
       </c>
-      <c r="H26" s="26"/>
+      <c r="H26" s="24"/>
       <c r="I26" s="13" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J26" s="13"/>
       <c r="K26" s="13"/>
       <c r="L26" s="13"/>
       <c r="M26" s="13"/>
       <c r="N26" s="13"/>
-      <c r="O26" s="42"/>
+      <c r="O26" s="35"/>
     </row>
     <row r="27" ht="25" customHeight="1" spans="1:15">
       <c r="A27" s="12" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E27" s="24" t="s">
-        <v>115</v>
+      <c r="E27" s="13" t="s">
+        <v>116</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G27" s="5">
         <v>2026</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J27" s="5"/>
       <c r="K27" s="5"/>
       <c r="L27" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M27" s="5"/>
       <c r="N27" s="5"/>
@@ -4003,36 +4001,36 @@
     </row>
     <row r="28" ht="25" customHeight="1" spans="1:15">
       <c r="A28" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E28" s="24" t="s">
-        <v>121</v>
+      <c r="E28" s="13" t="s">
+        <v>122</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G28" s="5">
         <v>2025</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J28" s="5"/>
       <c r="K28" s="5"/>
       <c r="L28" s="5" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="M28" s="5"/>
       <c r="N28" s="5"/>
@@ -4040,36 +4038,36 @@
     </row>
     <row r="29" ht="25" customHeight="1" spans="1:15">
       <c r="A29" s="12" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E29" s="24" t="s">
-        <v>127</v>
+      <c r="E29" s="13" t="s">
+        <v>128</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G29" s="5">
         <v>2026</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="J29" s="5"/>
       <c r="K29" s="5"/>
       <c r="L29" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M29" s="5"/>
       <c r="N29" s="5"/>
@@ -4077,36 +4075,36 @@
     </row>
     <row r="30" ht="25" customHeight="1" spans="1:15">
       <c r="A30" s="12" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E30" s="24" t="s">
-        <v>133</v>
+      <c r="E30" s="13" t="s">
+        <v>134</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G30" s="5">
         <v>2026</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="J30" s="5"/>
       <c r="K30" s="5"/>
       <c r="L30" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M30" s="5"/>
       <c r="N30" s="5"/>
@@ -4114,36 +4112,36 @@
     </row>
     <row r="31" ht="25" customHeight="1" spans="1:15">
       <c r="A31" s="12" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E31" s="24" t="s">
-        <v>139</v>
+      <c r="E31" s="13" t="s">
+        <v>140</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G31" s="5">
         <v>2025</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J31" s="5"/>
       <c r="K31" s="5"/>
       <c r="L31" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="M31" s="5"/>
       <c r="N31" s="5"/>
@@ -4151,36 +4149,36 @@
     </row>
     <row r="32" ht="25" customHeight="1" spans="1:15">
       <c r="A32" s="12" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E32" s="24" t="s">
-        <v>145</v>
+      <c r="E32" s="13" t="s">
+        <v>146</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G32" s="5">
         <v>2026</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J32" s="15"/>
       <c r="K32" s="15"/>
       <c r="L32" s="15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M32" s="15"/>
       <c r="N32" s="15"/>
@@ -4188,1020 +4186,1019 @@
     </row>
     <row r="33" ht="25" customHeight="1" spans="1:15">
       <c r="A33" s="12" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E33" s="24" t="s">
-        <v>151</v>
+      <c r="E33" s="13" t="s">
+        <v>152</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G33" s="5">
         <v>2026</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I33" s="5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="J33" s="5"/>
       <c r="K33" s="5"/>
       <c r="L33" s="5" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M33" s="5"/>
       <c r="N33" s="5"/>
-      <c r="O33" s="43"/>
+      <c r="O33" s="36"/>
     </row>
     <row r="34" ht="25" customHeight="1" spans="1:15">
       <c r="A34" s="12" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E34" s="24" t="s">
-        <v>157</v>
+      <c r="E34" s="13" t="s">
+        <v>158</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G34" s="5">
         <v>2024</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J34" s="5"/>
       <c r="K34" s="5"/>
       <c r="L34" s="5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M34" s="5"/>
       <c r="N34" s="5"/>
-      <c r="O34" s="43"/>
+      <c r="O34" s="36"/>
     </row>
     <row r="35" ht="25" customHeight="1" spans="1:15">
       <c r="A35" s="12" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E35" s="24" t="s">
-        <v>163</v>
+      <c r="E35" s="13" t="s">
+        <v>164</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G35" s="5">
         <v>2024</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="J35" s="5"/>
       <c r="K35" s="5"/>
       <c r="L35" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M35" s="5"/>
       <c r="N35" s="5"/>
-      <c r="O35" s="43"/>
+      <c r="O35" s="36"/>
     </row>
     <row r="36" ht="25" customHeight="1" spans="1:15">
       <c r="A36" s="12" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E36" s="24" t="s">
-        <v>133</v>
+      <c r="E36" s="13" t="s">
+        <v>134</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G36" s="5">
         <v>2026</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="J36" s="5"/>
       <c r="K36" s="5"/>
       <c r="L36" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M36" s="5"/>
       <c r="N36" s="5"/>
-      <c r="O36" s="43"/>
+      <c r="O36" s="36"/>
     </row>
     <row r="37" ht="25" customHeight="1" spans="1:15">
       <c r="A37" s="12" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E37" s="24" t="s">
-        <v>173</v>
+      <c r="E37" s="13" t="s">
+        <v>174</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G37" s="5">
         <v>2025</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I37" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J37" s="5"/>
       <c r="K37" s="5"/>
       <c r="L37" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M37" s="5"/>
       <c r="N37" s="5"/>
-      <c r="O37" s="43"/>
+      <c r="O37" s="36"/>
     </row>
     <row r="38" ht="25" customHeight="1" spans="1:15">
       <c r="A38" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E38" s="24" t="s">
-        <v>151</v>
+      <c r="E38" s="13" t="s">
+        <v>152</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G38" s="5">
         <v>2026</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I38" s="5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="J38" s="5"/>
       <c r="K38" s="5"/>
       <c r="L38" s="5" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M38" s="5"/>
       <c r="N38" s="5"/>
-      <c r="O38" s="43"/>
+      <c r="O38" s="36"/>
     </row>
     <row r="39" ht="25" customHeight="1" spans="1:15">
       <c r="A39" s="12" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E39" s="24" t="s">
-        <v>151</v>
+      <c r="E39" s="13" t="s">
+        <v>152</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G39" s="5">
         <v>2026</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I39" s="5" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J39" s="5"/>
       <c r="K39" s="5"/>
       <c r="L39" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M39" s="5"/>
       <c r="N39" s="5"/>
-      <c r="O39" s="43"/>
+      <c r="O39" s="36"/>
     </row>
     <row r="40" ht="25" customHeight="1" spans="1:15">
       <c r="A40" s="12" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D40" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E40" s="24" t="s">
-        <v>115</v>
+      <c r="E40" s="13" t="s">
+        <v>116</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G40" s="5">
         <v>2026</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I40" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J40" s="5"/>
       <c r="K40" s="5"/>
       <c r="L40" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="M40" s="5"/>
       <c r="N40" s="5"/>
-      <c r="O40" s="43"/>
+      <c r="O40" s="36"/>
     </row>
     <row r="41" ht="25" customHeight="1" spans="1:15">
       <c r="A41" s="12" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E41" s="24" t="s">
-        <v>193</v>
+      <c r="E41" s="13" t="s">
+        <v>194</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G41" s="5">
         <v>2025</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I41" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="J41" s="5"/>
       <c r="K41" s="5"/>
       <c r="L41" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M41" s="5"/>
       <c r="N41" s="5"/>
-      <c r="O41" s="43"/>
+      <c r="O41" s="36"/>
     </row>
     <row r="42" ht="25" customHeight="1" spans="1:15">
       <c r="A42" s="12" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D42" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E42" s="24" t="s">
-        <v>199</v>
+      <c r="E42" s="13" t="s">
+        <v>200</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G42" s="5">
         <v>2026</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I42" s="5" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="J42" s="5"/>
       <c r="K42" s="5"/>
       <c r="L42" s="5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M42" s="5"/>
       <c r="N42" s="5"/>
-      <c r="O42" s="43"/>
+      <c r="O42" s="36"/>
     </row>
     <row r="43" ht="25" customHeight="1" spans="1:15">
       <c r="A43" s="12" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D43" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E43" s="24" t="s">
-        <v>121</v>
+      <c r="E43" s="13" t="s">
+        <v>122</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G43" s="5">
         <v>2026</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I43" s="5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="J43" s="5"/>
       <c r="K43" s="5"/>
       <c r="L43" s="5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M43" s="5"/>
       <c r="N43" s="5"/>
-      <c r="O43" s="43"/>
+      <c r="O43" s="36"/>
     </row>
     <row r="44" ht="25" customHeight="1" spans="1:15">
       <c r="A44" s="12" t="s">
-        <v>208</v>
-      </c>
-      <c r="B44" s="26" t="s">
-        <v>61</v>
+        <v>209</v>
+      </c>
+      <c r="B44" s="24" t="s">
+        <v>62</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E44" s="24" t="s">
-        <v>210</v>
+      <c r="E44" s="13" t="s">
+        <v>211</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G44" s="5">
         <v>2025</v>
       </c>
       <c r="H44" s="5"/>
       <c r="I44" s="5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="J44" s="5"/>
       <c r="K44" s="5"/>
       <c r="L44" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M44" s="5"/>
       <c r="N44" s="5"/>
-      <c r="O44" s="43"/>
+      <c r="O44" s="36"/>
     </row>
     <row r="45" ht="25" customHeight="1" spans="1:15">
       <c r="A45" s="12" t="s">
-        <v>212</v>
-      </c>
-      <c r="B45" s="26" t="s">
-        <v>61</v>
+        <v>213</v>
+      </c>
+      <c r="B45" s="24" t="s">
+        <v>62</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D45" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E45" s="24" t="s">
-        <v>214</v>
+      <c r="E45" s="13" t="s">
+        <v>215</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G45" s="5">
         <v>2025</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I45" s="5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J45" s="5"/>
       <c r="K45" s="5"/>
       <c r="L45" s="5" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M45" s="5"/>
       <c r="N45" s="5"/>
-      <c r="O45" s="43"/>
+      <c r="O45" s="36"/>
     </row>
     <row r="46" ht="25" customHeight="1" spans="1:15">
       <c r="A46" s="12" t="s">
-        <v>218</v>
-      </c>
-      <c r="B46" s="26" t="s">
-        <v>61</v>
+        <v>219</v>
+      </c>
+      <c r="B46" s="24" t="s">
+        <v>62</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D46" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E46" s="24" t="s">
-        <v>210</v>
+      <c r="E46" s="13" t="s">
+        <v>211</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G46" s="5">
         <v>2025</v>
       </c>
       <c r="H46" s="5"/>
       <c r="I46" s="5" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="J46" s="5"/>
       <c r="K46" s="5"/>
       <c r="L46" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M46" s="5"/>
       <c r="N46" s="5"/>
-      <c r="O46" s="43"/>
+      <c r="O46" s="36"/>
     </row>
     <row r="47" ht="25" customHeight="1" spans="1:15">
       <c r="A47" s="12" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D47" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E47" s="24" t="s">
-        <v>127</v>
+      <c r="E47" s="13" t="s">
+        <v>128</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G47" s="5">
         <v>2026</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I47" s="5" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="J47" s="5"/>
       <c r="K47" s="5"/>
       <c r="L47" s="5" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="M47" s="5"/>
       <c r="N47" s="5"/>
-      <c r="O47" s="43"/>
+      <c r="O47" s="36"/>
     </row>
     <row r="48" ht="25" customHeight="1" spans="1:15">
       <c r="A48" s="12" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
       <c r="D48" s="5"/>
-      <c r="E48" s="24"/>
+      <c r="E48" s="13"/>
       <c r="F48" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G48" s="5"/>
       <c r="H48" s="5"/>
       <c r="I48" s="5" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="J48" s="5"/>
       <c r="K48" s="5"/>
       <c r="L48" s="5"/>
       <c r="M48" s="5"/>
       <c r="N48" s="5"/>
-      <c r="O48" s="43"/>
+      <c r="O48" s="36"/>
     </row>
     <row r="49" ht="25" customHeight="1" spans="1:15">
       <c r="A49" s="12" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
       <c r="D49" s="5"/>
-      <c r="E49" s="24"/>
+      <c r="E49" s="13"/>
       <c r="F49" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G49" s="5"/>
       <c r="H49" s="5"/>
       <c r="I49" s="5" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="J49" s="5"/>
       <c r="K49" s="5"/>
       <c r="L49" s="5"/>
       <c r="M49" s="5"/>
       <c r="N49" s="5"/>
-      <c r="O49" s="43"/>
+      <c r="O49" s="36"/>
     </row>
     <row r="50" ht="25" customHeight="1" spans="1:15">
       <c r="A50" s="12" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5"/>
       <c r="D50" s="5"/>
-      <c r="E50" s="24"/>
+      <c r="E50" s="13"/>
       <c r="F50" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G50" s="5"/>
       <c r="H50" s="5"/>
       <c r="I50" s="5" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="J50" s="5"/>
       <c r="K50" s="5"/>
       <c r="L50" s="5"/>
       <c r="M50" s="5"/>
       <c r="N50" s="5"/>
-      <c r="O50" s="43"/>
+      <c r="O50" s="36"/>
     </row>
     <row r="51" ht="25" customHeight="1" spans="1:15">
       <c r="A51" s="12" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
       <c r="D51" s="5"/>
-      <c r="E51" s="24"/>
+      <c r="E51" s="13"/>
       <c r="F51" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G51" s="5"/>
-      <c r="H51" s="5"/>
       <c r="I51" s="5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="J51" s="5"/>
       <c r="K51" s="5"/>
       <c r="L51" s="5"/>
       <c r="M51" s="5"/>
       <c r="N51" s="5"/>
-      <c r="O51" s="43"/>
+      <c r="O51" s="36"/>
     </row>
     <row r="52" ht="25" customHeight="1" spans="1:15">
       <c r="A52" s="14" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B52" s="15"/>
       <c r="C52" s="15"/>
       <c r="D52" s="15"/>
-      <c r="E52" s="33"/>
+      <c r="E52" s="29"/>
       <c r="F52" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G52" s="15"/>
       <c r="H52" s="15"/>
       <c r="I52" s="16" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="J52" s="15"/>
       <c r="K52" s="5"/>
       <c r="L52" s="5"/>
       <c r="M52" s="5"/>
       <c r="N52" s="5"/>
-      <c r="O52" s="43"/>
+      <c r="O52" s="36"/>
     </row>
     <row r="53" ht="25" customHeight="1" spans="1:15">
       <c r="A53" s="12" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5"/>
       <c r="D53" s="5"/>
-      <c r="E53" s="24"/>
+      <c r="E53" s="13"/>
       <c r="F53" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G53" s="5"/>
       <c r="I53" s="5" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="J53" s="5"/>
       <c r="K53" s="5"/>
       <c r="L53" s="5"/>
       <c r="M53" s="5"/>
       <c r="N53" s="5"/>
-      <c r="O53" s="43"/>
+      <c r="O53" s="36"/>
     </row>
     <row r="54" ht="25" customHeight="1" spans="1:15">
       <c r="A54" s="12" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
       <c r="D54" s="5"/>
-      <c r="E54" s="24"/>
+      <c r="E54" s="13"/>
       <c r="F54" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G54" s="5"/>
       <c r="H54" s="5"/>
       <c r="I54" s="5" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="J54" s="5"/>
       <c r="K54" s="5"/>
       <c r="L54" s="5"/>
       <c r="M54" s="5"/>
       <c r="N54" s="5"/>
-      <c r="O54" s="43"/>
+      <c r="O54" s="36"/>
     </row>
     <row r="55" ht="25" customHeight="1" spans="1:15">
       <c r="A55" s="12" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B55" s="5"/>
       <c r="C55" s="5"/>
       <c r="D55" s="5"/>
-      <c r="E55" s="24"/>
+      <c r="E55" s="13"/>
       <c r="F55" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G55" s="5"/>
       <c r="H55" s="5"/>
       <c r="I55" s="5" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="J55" s="5"/>
       <c r="K55" s="5"/>
       <c r="L55" s="5"/>
       <c r="M55" s="5"/>
       <c r="N55" s="5"/>
-      <c r="O55" s="43"/>
+      <c r="O55" s="36"/>
     </row>
     <row r="56" ht="25" customHeight="1" spans="1:15">
       <c r="A56" s="12" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
       <c r="D56" s="5"/>
-      <c r="E56" s="24"/>
+      <c r="E56" s="13"/>
       <c r="F56" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G56" s="5"/>
       <c r="I56" s="5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="J56" s="5"/>
       <c r="K56" s="5"/>
       <c r="L56" s="5"/>
       <c r="M56" s="5"/>
       <c r="N56" s="5"/>
-      <c r="O56" s="43"/>
+      <c r="O56" s="36"/>
     </row>
     <row r="57" ht="25" customHeight="1" spans="1:15">
       <c r="A57" s="12" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
       <c r="D57" s="5"/>
-      <c r="E57" s="24"/>
+      <c r="E57" s="13"/>
       <c r="F57" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G57" s="5"/>
       <c r="H57" s="5"/>
       <c r="I57" s="5" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="J57" s="5"/>
       <c r="K57" s="5"/>
       <c r="L57" s="5"/>
       <c r="M57" s="5"/>
       <c r="N57" s="5"/>
-      <c r="O57" s="43"/>
+      <c r="O57" s="36"/>
     </row>
     <row r="58" ht="25" customHeight="1" spans="1:15">
       <c r="A58" s="12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
       <c r="D58" s="5"/>
-      <c r="E58" s="24"/>
+      <c r="E58" s="13"/>
       <c r="F58" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G58" s="5"/>
       <c r="H58" s="5"/>
       <c r="I58" s="5" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="J58" s="5"/>
       <c r="K58" s="5"/>
       <c r="L58" s="5"/>
       <c r="M58" s="5"/>
       <c r="N58" s="5"/>
-      <c r="O58" s="43"/>
+      <c r="O58" s="36"/>
     </row>
     <row r="59" ht="25" customHeight="1" spans="1:15">
       <c r="A59" s="12" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
       <c r="D59" s="5"/>
-      <c r="E59" s="24"/>
+      <c r="E59" s="13"/>
       <c r="F59" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G59" s="5"/>
       <c r="H59" s="5"/>
       <c r="I59" s="5" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="J59" s="5"/>
       <c r="K59" s="5"/>
       <c r="L59" s="5"/>
       <c r="M59" s="5"/>
       <c r="N59" s="5"/>
-      <c r="O59" s="43"/>
+      <c r="O59" s="36"/>
     </row>
     <row r="60" ht="25" customHeight="1" spans="1:15">
       <c r="A60" s="12" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
       <c r="D60" s="5"/>
-      <c r="E60" s="24"/>
+      <c r="E60" s="13"/>
       <c r="F60" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G60" s="5"/>
       <c r="I60" s="5" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J60" s="5"/>
       <c r="K60" s="5"/>
       <c r="L60" s="5"/>
       <c r="M60" s="5"/>
       <c r="N60" s="5"/>
-      <c r="O60" s="43"/>
+      <c r="O60" s="36"/>
     </row>
     <row r="61" ht="25" customHeight="1" spans="1:15">
       <c r="A61" s="12" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
       <c r="D61" s="5"/>
-      <c r="E61" s="24"/>
+      <c r="E61" s="13"/>
       <c r="F61" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G61" s="5"/>
       <c r="H61" s="5"/>
       <c r="I61" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="J61" s="5"/>
       <c r="K61" s="5"/>
       <c r="L61" s="5"/>
       <c r="M61" s="5"/>
       <c r="N61" s="5"/>
-      <c r="O61" s="43"/>
+      <c r="O61" s="36"/>
     </row>
     <row r="62" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A62" s="12" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B62" s="5"/>
       <c r="C62" s="5"/>
       <c r="D62" s="5"/>
-      <c r="E62" s="24"/>
+      <c r="E62" s="13"/>
       <c r="F62" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G62" s="5"/>
       <c r="H62" s="5"/>
       <c r="I62" s="5" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J62" s="5"/>
       <c r="K62" s="5"/>
       <c r="L62" s="5"/>
       <c r="M62" s="5"/>
       <c r="N62" s="5"/>
-      <c r="O62" s="43"/>
+      <c r="O62" s="36"/>
     </row>
     <row r="63" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A63" s="12" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B63" s="5"/>
       <c r="C63" s="5"/>
       <c r="D63" s="5"/>
-      <c r="E63" s="24"/>
+      <c r="E63" s="13"/>
       <c r="F63" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G63" s="5"/>
       <c r="H63" s="5"/>
       <c r="I63" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="J63" s="5"/>
       <c r="K63" s="5"/>
       <c r="L63" s="5"/>
       <c r="M63" s="5"/>
       <c r="N63" s="5"/>
-      <c r="O63" s="43"/>
+      <c r="O63" s="36"/>
     </row>
     <row r="64" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A64" s="12" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B64" s="5"/>
       <c r="C64" s="5"/>
       <c r="D64" s="5"/>
-      <c r="E64" s="24"/>
+      <c r="E64" s="13"/>
       <c r="F64" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G64" s="5"/>
       <c r="H64" s="5"/>
       <c r="I64" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="J64" s="5"/>
       <c r="K64" s="5"/>
       <c r="L64" s="5"/>
       <c r="M64" s="5"/>
       <c r="N64" s="5"/>
-      <c r="O64" s="43"/>
+      <c r="O64" s="36"/>
     </row>
     <row r="65" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A65" s="12" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B65" s="5"/>
       <c r="C65" s="5"/>
       <c r="D65" s="5"/>
-      <c r="E65" s="24"/>
+      <c r="E65" s="13"/>
       <c r="F65" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G65" s="5"/>
       <c r="H65" s="5"/>
       <c r="I65" s="5" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="J65" s="5"/>
       <c r="K65" s="5"/>
       <c r="L65" s="5"/>
       <c r="M65" s="5"/>
       <c r="N65" s="5"/>
-      <c r="O65" s="43"/>
+      <c r="O65" s="36"/>
     </row>
     <row r="66" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A66" s="12" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C66" s="17" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D66" s="5"/>
-      <c r="E66" s="24" t="s">
-        <v>265</v>
+      <c r="E66" s="13" t="s">
+        <v>266</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G66" s="5"/>
       <c r="H66" s="18" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="I66" s="5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J66" s="5"/>
       <c r="K66" s="5"/>
       <c r="L66" s="5"/>
       <c r="M66" s="5"/>
       <c r="N66" s="5"/>
-      <c r="O66" s="43"/>
+      <c r="O66" s="36"/>
     </row>
     <row r="67" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A67" s="12" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C67" s="17" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D67" s="5"/>
-      <c r="E67" s="24" t="s">
-        <v>127</v>
+      <c r="E67" s="13" t="s">
+        <v>128</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G67" s="5"/>
       <c r="H67" s="18" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="I67" s="5" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="J67" s="5"/>
       <c r="K67" s="5"/>
@@ -5212,155 +5209,155 @@
     </row>
     <row r="68" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="A68" s="12" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C68" s="19" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D68" s="5"/>
-      <c r="E68" s="24" t="s">
-        <v>133</v>
+      <c r="E68" s="13" t="s">
+        <v>134</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G68" s="5"/>
       <c r="H68" s="18" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I68" s="5" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="J68" s="5"/>
       <c r="K68" s="5"/>
       <c r="L68" s="5"/>
       <c r="M68" s="5"/>
       <c r="N68" s="5"/>
-      <c r="O68" s="43"/>
+      <c r="O68" s="36"/>
     </row>
     <row r="69" ht="25" customHeight="1" spans="1:15">
       <c r="A69" s="12" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C69" s="17" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D69" s="5"/>
-      <c r="E69" s="24" t="s">
-        <v>278</v>
+      <c r="E69" s="13" t="s">
+        <v>279</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G69" s="5"/>
       <c r="H69" s="18" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I69" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J69" s="5"/>
       <c r="K69" s="5"/>
       <c r="L69" s="5"/>
       <c r="M69" s="5"/>
       <c r="N69" s="5"/>
-      <c r="O69" s="43"/>
+      <c r="O69" s="36"/>
     </row>
     <row r="70" ht="25" customHeight="1" spans="1:15">
       <c r="A70" s="12" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C70" s="17" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D70" s="5"/>
-      <c r="E70" s="24" t="s">
-        <v>278</v>
+      <c r="E70" s="13" t="s">
+        <v>279</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G70" s="5"/>
       <c r="H70" s="18" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I70" s="5" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="J70" s="5"/>
       <c r="K70" s="5"/>
       <c r="L70" s="5"/>
       <c r="M70" s="5"/>
       <c r="N70" s="5"/>
-      <c r="O70" s="43"/>
+      <c r="O70" s="36"/>
     </row>
     <row r="71" ht="25" customHeight="1" spans="1:15">
       <c r="A71" s="12" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C71" s="17" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D71" s="5"/>
-      <c r="E71" s="24" t="s">
-        <v>287</v>
+      <c r="E71" s="13" t="s">
+        <v>288</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G71" s="5"/>
       <c r="H71" s="18" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="I71" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J71" s="5"/>
       <c r="K71" s="5"/>
       <c r="L71" s="5"/>
       <c r="M71" s="5"/>
       <c r="N71" s="5"/>
-      <c r="O71" s="43"/>
+      <c r="O71" s="36"/>
     </row>
     <row r="72" ht="25" customHeight="1" spans="1:15">
       <c r="A72" s="12" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="C72" s="44" t="s">
         <v>292</v>
       </c>
-      <c r="D72" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="E72" s="24" t="s">
+      <c r="C72" s="37" t="s">
         <v>293</v>
       </c>
+      <c r="D72" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E72" s="13" t="s">
+        <v>294</v>
+      </c>
       <c r="F72" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="G72" s="26">
+        <v>28</v>
+      </c>
+      <c r="G72" s="24">
         <v>2026</v>
       </c>
       <c r="H72" s="5" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I72" s="5" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="J72" s="5"/>
       <c r="K72" s="5"/>
@@ -5374,7 +5371,7 @@
       <c r="B73" s="5"/>
       <c r="C73" s="5"/>
       <c r="D73" s="5"/>
-      <c r="E73" s="24"/>
+      <c r="E73" s="13"/>
       <c r="F73" s="13"/>
       <c r="G73" s="5"/>
       <c r="H73" s="5"/>
@@ -5391,7 +5388,7 @@
       <c r="B74" s="5"/>
       <c r="C74" s="5"/>
       <c r="D74" s="5"/>
-      <c r="E74" s="24"/>
+      <c r="E74" s="13"/>
       <c r="F74" s="13"/>
       <c r="G74" s="5"/>
       <c r="I74" s="5"/>
@@ -5407,7 +5404,7 @@
       <c r="B75" s="5"/>
       <c r="C75" s="5"/>
       <c r="D75" s="5"/>
-      <c r="E75" s="24"/>
+      <c r="E75" s="13"/>
       <c r="F75" s="13"/>
       <c r="G75" s="5"/>
       <c r="H75" s="5"/>
@@ -5424,7 +5421,7 @@
       <c r="B76" s="5"/>
       <c r="C76" s="5"/>
       <c r="D76" s="5"/>
-      <c r="E76" s="24"/>
+      <c r="E76" s="13"/>
       <c r="F76" s="13"/>
       <c r="G76" s="5"/>
       <c r="H76" s="5"/>
@@ -5441,7 +5438,7 @@
       <c r="B77" s="5"/>
       <c r="C77" s="5"/>
       <c r="D77" s="5"/>
-      <c r="E77" s="24"/>
+      <c r="E77" s="13"/>
       <c r="F77" s="13"/>
       <c r="G77" s="5"/>
       <c r="I77" s="5"/>
@@ -5457,7 +5454,7 @@
       <c r="B78" s="5"/>
       <c r="C78" s="5"/>
       <c r="D78" s="5"/>
-      <c r="E78" s="24"/>
+      <c r="E78" s="13"/>
       <c r="F78" s="13"/>
       <c r="G78" s="5"/>
       <c r="H78" s="5"/>
@@ -5474,7 +5471,7 @@
       <c r="B79" s="5"/>
       <c r="C79" s="5"/>
       <c r="D79" s="5"/>
-      <c r="E79" s="24"/>
+      <c r="E79" s="13"/>
       <c r="F79" s="13"/>
       <c r="G79" s="5"/>
       <c r="H79" s="5"/>
@@ -5491,7 +5488,7 @@
       <c r="B80" s="5"/>
       <c r="C80" s="5"/>
       <c r="D80" s="5"/>
-      <c r="E80" s="24"/>
+      <c r="E80" s="13"/>
       <c r="F80" s="13"/>
       <c r="G80" s="5"/>
       <c r="H80" s="5"/>
@@ -5508,7 +5505,7 @@
       <c r="B81" s="5"/>
       <c r="C81" s="5"/>
       <c r="D81" s="5"/>
-      <c r="E81" s="24"/>
+      <c r="E81" s="13"/>
       <c r="F81" s="13"/>
       <c r="G81" s="5"/>
       <c r="I81" s="5"/>
@@ -5524,7 +5521,7 @@
       <c r="B82" s="5"/>
       <c r="C82" s="5"/>
       <c r="D82" s="5"/>
-      <c r="E82" s="24"/>
+      <c r="E82" s="13"/>
       <c r="F82" s="13"/>
       <c r="G82" s="5"/>
       <c r="H82" s="5"/>
@@ -5541,7 +5538,7 @@
       <c r="B83" s="5"/>
       <c r="C83" s="5"/>
       <c r="D83" s="5"/>
-      <c r="E83" s="24"/>
+      <c r="E83" s="13"/>
       <c r="F83" s="13"/>
       <c r="G83" s="5"/>
       <c r="H83" s="5"/>
@@ -5558,7 +5555,7 @@
       <c r="B84" s="5"/>
       <c r="C84" s="5"/>
       <c r="D84" s="5"/>
-      <c r="E84" s="24"/>
+      <c r="E84" s="13"/>
       <c r="F84" s="13"/>
       <c r="G84" s="5"/>
       <c r="H84" s="5"/>
@@ -5575,7 +5572,7 @@
       <c r="B85" s="5"/>
       <c r="C85" s="5"/>
       <c r="D85" s="5"/>
-      <c r="E85" s="24"/>
+      <c r="E85" s="13"/>
       <c r="F85" s="13"/>
       <c r="G85" s="5"/>
       <c r="H85" s="5"/>
@@ -5592,7 +5589,7 @@
       <c r="B86" s="5"/>
       <c r="C86" s="5"/>
       <c r="D86" s="5"/>
-      <c r="E86" s="24"/>
+      <c r="E86" s="13"/>
       <c r="F86" s="13"/>
       <c r="G86" s="5"/>
       <c r="H86" s="5"/>
@@ -5609,7 +5606,7 @@
       <c r="B87" s="5"/>
       <c r="C87" s="5"/>
       <c r="D87" s="5"/>
-      <c r="E87" s="24"/>
+      <c r="E87" s="13"/>
       <c r="F87" s="13"/>
       <c r="G87" s="5"/>
       <c r="H87" s="5"/>
@@ -5654,7 +5651,7 @@
   <sheetData>
     <row r="1" ht="33" customHeight="1" spans="1:9">
       <c r="A1" s="3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -5701,7 +5698,7 @@
         <v>12</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>14</v>
@@ -5724,13 +5721,13 @@
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:9">
       <c r="A4" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>14</v>
@@ -5745,21 +5742,21 @@
         <v>2026</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:9">
       <c r="A5" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>14</v>
@@ -5774,21 +5771,21 @@
         <v>2026</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:9">
       <c r="A6" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>14</v>
@@ -5803,21 +5800,21 @@
         <v>2026</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:9">
       <c r="A7" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>14</v>
@@ -5832,21 +5829,21 @@
         <v>2026</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:9">
       <c r="A8" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>14</v>
@@ -5861,21 +5858,21 @@
         <v>2026</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:9">
       <c r="A9" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>14</v>
@@ -5890,21 +5887,21 @@
         <v>2026</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:9">
       <c r="A10" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>14</v>
@@ -5919,21 +5916,21 @@
         <v>2026</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:9">
       <c r="A11" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>14</v>
@@ -5948,21 +5945,21 @@
         <v>2026</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:9">
       <c r="A12" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>14</v>
@@ -5977,21 +5974,21 @@
         <v>2026</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:9">
       <c r="A13" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>14</v>
@@ -6006,21 +6003,21 @@
         <v>2026</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:9">
       <c r="A14" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>14</v>
@@ -6035,21 +6032,21 @@
         <v>2026</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:9">
       <c r="A15" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>14</v>
@@ -6064,21 +6061,21 @@
         <v>2026</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:9">
       <c r="A16" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>14</v>
@@ -6093,21 +6090,21 @@
         <v>2026</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:9">
       <c r="A17" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>14</v>
@@ -6123,18 +6120,18 @@
       </c>
       <c r="H17" s="7"/>
       <c r="I17" s="8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:9">
       <c r="A18" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>14</v>
@@ -6150,1118 +6147,1118 @@
       </c>
       <c r="H18" s="7"/>
       <c r="I18" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" spans="1:9">
       <c r="A19" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>14</v>
       </c>
       <c r="E19" s="10"/>
       <c r="F19" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G19" s="7">
         <v>2026</v>
       </c>
       <c r="H19" s="7"/>
       <c r="I19" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" spans="1:9">
       <c r="A20" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>14</v>
       </c>
       <c r="E20" s="10"/>
       <c r="F20" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G20" s="7">
         <v>2026</v>
       </c>
       <c r="H20" s="7"/>
       <c r="I20" s="11" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1" spans="1:9">
       <c r="A21" s="12" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G21" s="5">
         <v>2026</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1" spans="1:9">
       <c r="A22" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G22" s="5">
         <v>2025</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1" spans="1:9">
       <c r="A23" s="12" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G23" s="5">
         <v>2026</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1" spans="1:9">
       <c r="A24" s="12" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G24" s="5">
         <v>2026</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1" spans="1:9">
       <c r="A25" s="12" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G25" s="5">
         <v>2025</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1" spans="1:9">
       <c r="A26" s="12" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G26" s="5">
         <v>2026</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1" spans="1:9">
       <c r="A27" s="12" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G27" s="5">
         <v>2026</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1" spans="1:9">
       <c r="A28" s="12" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G28" s="5">
         <v>2024</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="29" ht="25" customHeight="1" spans="1:9">
       <c r="A29" s="12" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G29" s="5">
         <v>2024</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="30" ht="25" customHeight="1" spans="1:9">
       <c r="A30" s="12" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G30" s="5">
         <v>2026</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="31" ht="25" customHeight="1" spans="1:9">
       <c r="A31" s="12" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G31" s="5">
         <v>2025</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" ht="25" customHeight="1" spans="1:9">
       <c r="A32" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G32" s="5">
         <v>2026</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="33" ht="25" customHeight="1" spans="1:9">
       <c r="A33" s="12" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G33" s="5">
         <v>2026</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I33" s="5" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="34" ht="25" customHeight="1" spans="1:9">
       <c r="A34" s="12" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G34" s="5">
         <v>2026</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="35" ht="25" customHeight="1" spans="1:9">
       <c r="A35" s="12" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G35" s="5">
         <v>2025</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="36" ht="25" customHeight="1" spans="1:9">
       <c r="A36" s="12" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G36" s="5">
         <v>2026</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="37" ht="25" customHeight="1" spans="1:9">
       <c r="A37" s="12" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G37" s="5">
         <v>2026</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I37" s="5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="38" ht="25" customHeight="1" spans="1:9">
       <c r="A38" s="12" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G38" s="5">
         <v>2025</v>
       </c>
       <c r="H38" s="5"/>
       <c r="I38" s="5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="39" ht="25" customHeight="1" spans="1:9">
       <c r="A39" s="12" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G39" s="5">
         <v>2025</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I39" s="5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="40" ht="25" customHeight="1" spans="1:9">
       <c r="A40" s="12" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D40" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G40" s="5">
         <v>2025</v>
       </c>
       <c r="H40" s="5"/>
       <c r="I40" s="5" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="41" ht="25" customHeight="1" spans="1:9">
       <c r="A41" s="12" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G41" s="5">
         <v>2026</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I41" s="5" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="42" ht="25" customHeight="1" spans="1:9">
       <c r="A42" s="12" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5"/>
       <c r="D42" s="5"/>
       <c r="E42" s="5"/>
       <c r="F42" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G42" s="5"/>
       <c r="H42" s="5"/>
       <c r="I42" s="5" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="43" ht="25" customHeight="1" spans="1:9">
       <c r="A43" s="12" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5"/>
       <c r="D43" s="5"/>
       <c r="E43" s="5"/>
       <c r="F43" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G43" s="5"/>
       <c r="H43" s="5"/>
       <c r="I43" s="5" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="44" ht="25" customHeight="1" spans="1:9">
       <c r="A44" s="12" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
       <c r="D44" s="5"/>
       <c r="E44" s="5"/>
       <c r="F44" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G44" s="5"/>
       <c r="H44" s="5"/>
       <c r="I44" s="5" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="45" ht="25" customHeight="1" spans="1:9">
       <c r="A45" s="12" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5"/>
       <c r="D45" s="5"/>
       <c r="E45" s="5"/>
       <c r="F45" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G45" s="5"/>
       <c r="H45" s="5"/>
       <c r="I45" s="5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="46" ht="25" customHeight="1" spans="1:9">
       <c r="A46" s="14" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B46" s="15"/>
       <c r="C46" s="15"/>
       <c r="D46" s="15"/>
       <c r="E46" s="15"/>
       <c r="F46" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G46" s="15"/>
       <c r="H46" s="15"/>
       <c r="I46" s="16" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="47" ht="25" customHeight="1" spans="1:9">
       <c r="A47" s="12" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
       <c r="D47" s="5"/>
       <c r="E47" s="5"/>
       <c r="F47" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G47" s="5"/>
       <c r="H47" s="5"/>
       <c r="I47" s="5" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="48" ht="25" customHeight="1" spans="1:9">
       <c r="A48" s="12" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
       <c r="D48" s="5"/>
       <c r="E48" s="5"/>
       <c r="F48" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G48" s="5"/>
       <c r="H48" s="5"/>
       <c r="I48" s="5" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="49" ht="25" customHeight="1" spans="1:9">
       <c r="A49" s="12" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
       <c r="D49" s="5"/>
       <c r="E49" s="5"/>
       <c r="F49" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G49" s="5"/>
       <c r="H49" s="5"/>
       <c r="I49" s="5" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="50" ht="25" customHeight="1" spans="1:9">
       <c r="A50" s="12" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5"/>
       <c r="D50" s="5"/>
       <c r="E50" s="5"/>
       <c r="F50" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G50" s="5"/>
       <c r="H50" s="5"/>
       <c r="I50" s="5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="51" ht="25" customHeight="1" spans="1:9">
       <c r="A51" s="12" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
       <c r="D51" s="5"/>
       <c r="E51" s="5"/>
       <c r="F51" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G51" s="5"/>
       <c r="H51" s="5"/>
       <c r="I51" s="5" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="52" ht="25" customHeight="1" spans="1:9">
       <c r="A52" s="12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5"/>
       <c r="D52" s="5"/>
       <c r="E52" s="5"/>
       <c r="F52" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G52" s="5"/>
       <c r="H52" s="5"/>
       <c r="I52" s="5" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="53" customFormat="1" ht="25" customHeight="1" spans="1:9">
       <c r="A53" s="12" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C53" s="17" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D53" s="5"/>
       <c r="E53" s="5" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G53" s="5"/>
       <c r="H53" s="18" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="I53" s="5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="54" customFormat="1" ht="25" customHeight="1" spans="1:9">
       <c r="A54" s="12" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C54" s="17" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D54" s="5"/>
       <c r="E54" s="5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G54" s="5"/>
       <c r="H54" s="18" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="I54" s="5" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="55" customFormat="1" ht="25" customHeight="1" spans="1:9">
       <c r="A55" s="12" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C55" s="19" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D55" s="5"/>
       <c r="E55" s="5" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G55" s="5"/>
       <c r="H55" s="18" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="I55" s="5" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="56" ht="25" customHeight="1" spans="1:9">
       <c r="A56" s="12" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C56" s="17" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D56" s="5"/>
       <c r="E56" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G56" s="5"/>
       <c r="H56" s="18" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="I56" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="57" ht="25" customHeight="1" spans="1:9">
       <c r="A57" s="12" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C57" s="17" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D57" s="5"/>
       <c r="E57" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G57" s="5"/>
       <c r="H57" s="18" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="I57" s="5" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="58" ht="25" customHeight="1" spans="1:9">
       <c r="A58" s="12" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C58" s="17" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D58" s="5"/>
       <c r="E58" s="5" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G58" s="5"/>
       <c r="H58" s="18" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="I58" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="59" ht="25" customHeight="1" spans="1:9">
       <c r="A59" s="12" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
       <c r="D59" s="5"/>
       <c r="E59" s="5"/>
       <c r="F59" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G59" s="5"/>
       <c r="H59" s="5"/>
       <c r="I59" s="5" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="60" ht="25" customHeight="1" spans="1:9">
       <c r="A60" s="12" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
       <c r="D60" s="5"/>
       <c r="E60" s="5"/>
       <c r="F60" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G60" s="5"/>
       <c r="H60" s="5"/>
       <c r="I60" s="5" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="61" ht="25" customHeight="1" spans="1:9">
       <c r="A61" s="12" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
       <c r="D61" s="5"/>
       <c r="E61" s="5"/>
       <c r="F61" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G61" s="5"/>
       <c r="H61" s="5"/>
       <c r="I61" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="62" customFormat="1" ht="25" customHeight="1" sp